--- a/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
@@ -33,7 +33,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="82">
+  <fonts count="84">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -499,6 +499,16 @@
       <color rgb="00163A70"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="52">
     <fill>
@@ -758,7 +768,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="290">
+  <borders count="314">
     <border>
       <left/>
       <right/>
@@ -3898,11 +3908,249 @@
         <color rgb="000078D4"/>
       </bottom>
     </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="394">
+  <cellXfs count="492">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4831,6 +5079,238 @@
     <xf numFmtId="0" fontId="17" fillId="7" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="294" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="295" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="296" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="300" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="47" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="6" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="8" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="301" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="7" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="302" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="48" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="50" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="51" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="311" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="307" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="312" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="309" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="310" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="313" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="306" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="308" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="311" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="307" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="312" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="309" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="310" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="313" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="306" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="308" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -4924,74 +5404,6 @@
     </comment>
   </commentList>
 </comments>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="/xl/media/image1.png"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5253,2035 +5665,2303 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="267" t="inlineStr"/>
-      <c r="B1" s="268" t="n"/>
-      <c r="C1" s="268" t="n"/>
-      <c r="D1" s="268" t="n"/>
-      <c r="E1" s="268" t="n"/>
-      <c r="F1" s="268" t="n"/>
-      <c r="G1" s="268" t="n"/>
-      <c r="H1" s="268" t="n"/>
-      <c r="I1" s="332" t="inlineStr">
+      <c r="A1" s="394" t="inlineStr"/>
+      <c r="B1" s="483" t="n"/>
+      <c r="C1" s="483" t="n"/>
+      <c r="D1" s="483" t="n"/>
+      <c r="E1" s="483" t="n"/>
+      <c r="F1" s="483" t="n"/>
+      <c r="G1" s="483" t="n"/>
+      <c r="H1" s="483" t="n"/>
+      <c r="I1" s="396" t="inlineStr">
         <is>
           <t>HIGH-RISK JOB READINESS REVIEW</t>
         </is>
       </c>
-      <c r="J1" s="268" t="n"/>
-      <c r="K1" s="268" t="n"/>
-      <c r="L1" s="268" t="n"/>
-      <c r="M1" s="268" t="n"/>
-      <c r="N1" s="268" t="n"/>
-      <c r="O1" s="268" t="n"/>
-      <c r="P1" s="268" t="n"/>
-      <c r="Q1" s="268" t="n"/>
-      <c r="R1" s="268" t="n"/>
-      <c r="S1" s="268" t="n"/>
-      <c r="T1" s="268" t="n"/>
-      <c r="U1" s="268" t="n"/>
-      <c r="V1" s="268" t="n"/>
-      <c r="W1" s="268" t="n"/>
-      <c r="X1" s="268" t="n"/>
-      <c r="Y1" s="268" t="n"/>
-      <c r="Z1" s="268" t="n"/>
-      <c r="AA1" s="268" t="n"/>
-      <c r="AB1" s="268" t="n"/>
-      <c r="AC1" s="268" t="n"/>
-      <c r="AD1" s="268" t="n"/>
-      <c r="AE1" s="270" t="inlineStr">
+      <c r="J1" s="483" t="n"/>
+      <c r="K1" s="483" t="n"/>
+      <c r="L1" s="483" t="n"/>
+      <c r="M1" s="483" t="n"/>
+      <c r="N1" s="483" t="n"/>
+      <c r="O1" s="483" t="n"/>
+      <c r="P1" s="483" t="n"/>
+      <c r="Q1" s="483" t="n"/>
+      <c r="R1" s="483" t="n"/>
+      <c r="S1" s="483" t="n"/>
+      <c r="T1" s="483" t="n"/>
+      <c r="U1" s="483" t="n"/>
+      <c r="V1" s="483" t="n"/>
+      <c r="W1" s="483" t="n"/>
+      <c r="X1" s="483" t="n"/>
+      <c r="Y1" s="483" t="n"/>
+      <c r="Z1" s="483" t="n"/>
+      <c r="AA1" s="483" t="n"/>
+      <c r="AB1" s="483" t="n"/>
+      <c r="AC1" s="483" t="n"/>
+      <c r="AD1" s="483" t="n"/>
+      <c r="AE1" s="397" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="271" t="n"/>
-      <c r="AG1" s="271" t="n"/>
-      <c r="AH1" s="272" t="n"/>
-      <c r="AI1" s="273" t="inlineStr">
+      <c r="AF1" s="484" t="n"/>
+      <c r="AG1" s="484" t="n"/>
+      <c r="AH1" s="485" t="n"/>
+      <c r="AI1" s="400" t="inlineStr">
         <is>
           <t>FRM-209</t>
         </is>
       </c>
-      <c r="AJ1" s="271" t="n"/>
-      <c r="AK1" s="271" t="n"/>
-      <c r="AL1" s="271" t="n"/>
-      <c r="AM1" s="271" t="n"/>
-      <c r="AN1" s="274" t="n"/>
+      <c r="AJ1" s="484" t="n"/>
+      <c r="AK1" s="484" t="n"/>
+      <c r="AL1" s="484" t="n"/>
+      <c r="AM1" s="484" t="n"/>
+      <c r="AN1" s="485" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="I2" s="275" t="n"/>
-      <c r="AE2" s="276" t="inlineStr">
+      <c r="A2" s="486" t="n"/>
+      <c r="I2" s="486" t="n"/>
+      <c r="AE2" s="403" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="277" t="n"/>
-      <c r="AG2" s="277" t="n"/>
-      <c r="AH2" s="278" t="n"/>
-      <c r="AI2" s="279" t="inlineStr">
+      <c r="AF2" s="487" t="n"/>
+      <c r="AG2" s="487" t="n"/>
+      <c r="AH2" s="488" t="n"/>
+      <c r="AI2" s="406" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="277" t="n"/>
-      <c r="AK2" s="277" t="n"/>
-      <c r="AL2" s="277" t="n"/>
-      <c r="AM2" s="277" t="n"/>
-      <c r="AN2" s="280" t="n"/>
+      <c r="AJ2" s="487" t="n"/>
+      <c r="AK2" s="487" t="n"/>
+      <c r="AL2" s="487" t="n"/>
+      <c r="AM2" s="487" t="n"/>
+      <c r="AN2" s="488" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="I3" s="281" t="n"/>
-      <c r="J3" s="277" t="n"/>
-      <c r="K3" s="277" t="n"/>
-      <c r="L3" s="277" t="n"/>
-      <c r="M3" s="277" t="n"/>
-      <c r="N3" s="277" t="n"/>
-      <c r="O3" s="277" t="n"/>
-      <c r="P3" s="277" t="n"/>
-      <c r="Q3" s="277" t="n"/>
-      <c r="R3" s="277" t="n"/>
-      <c r="S3" s="277" t="n"/>
-      <c r="T3" s="277" t="n"/>
-      <c r="U3" s="277" t="n"/>
-      <c r="V3" s="277" t="n"/>
-      <c r="W3" s="277" t="n"/>
-      <c r="X3" s="277" t="n"/>
-      <c r="Y3" s="277" t="n"/>
-      <c r="Z3" s="277" t="n"/>
-      <c r="AA3" s="277" t="n"/>
-      <c r="AB3" s="277" t="n"/>
-      <c r="AC3" s="277" t="n"/>
-      <c r="AD3" s="277" t="n"/>
-      <c r="AE3" s="276" t="inlineStr">
+      <c r="A3" s="486" t="n"/>
+      <c r="I3" s="489" t="n"/>
+      <c r="J3" s="487" t="n"/>
+      <c r="K3" s="487" t="n"/>
+      <c r="L3" s="487" t="n"/>
+      <c r="M3" s="487" t="n"/>
+      <c r="N3" s="487" t="n"/>
+      <c r="O3" s="487" t="n"/>
+      <c r="P3" s="487" t="n"/>
+      <c r="Q3" s="487" t="n"/>
+      <c r="R3" s="487" t="n"/>
+      <c r="S3" s="487" t="n"/>
+      <c r="T3" s="487" t="n"/>
+      <c r="U3" s="487" t="n"/>
+      <c r="V3" s="487" t="n"/>
+      <c r="W3" s="487" t="n"/>
+      <c r="X3" s="487" t="n"/>
+      <c r="Y3" s="487" t="n"/>
+      <c r="Z3" s="487" t="n"/>
+      <c r="AA3" s="487" t="n"/>
+      <c r="AB3" s="487" t="n"/>
+      <c r="AC3" s="487" t="n"/>
+      <c r="AD3" s="487" t="n"/>
+      <c r="AE3" s="403" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="277" t="n"/>
-      <c r="AG3" s="277" t="n"/>
-      <c r="AH3" s="278" t="n"/>
-      <c r="AI3" s="279" t="inlineStr">
+      <c r="AF3" s="487" t="n"/>
+      <c r="AG3" s="487" t="n"/>
+      <c r="AH3" s="488" t="n"/>
+      <c r="AI3" s="406" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="277" t="n"/>
-      <c r="AK3" s="277" t="n"/>
-      <c r="AL3" s="277" t="n"/>
-      <c r="AM3" s="277" t="n"/>
-      <c r="AN3" s="280" t="n"/>
+      <c r="AJ3" s="487" t="n"/>
+      <c r="AK3" s="487" t="n"/>
+      <c r="AL3" s="487" t="n"/>
+      <c r="AM3" s="487" t="n"/>
+      <c r="AN3" s="488" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="A4" s="486" t="n"/>
+      <c r="I4" s="408" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="AE4" s="276" t="inlineStr">
+      <c r="AE4" s="403" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="277" t="n"/>
-      <c r="AG4" s="277" t="n"/>
-      <c r="AH4" s="278" t="n"/>
-      <c r="AI4" s="279" t="inlineStr">
+      <c r="AF4" s="487" t="n"/>
+      <c r="AG4" s="487" t="n"/>
+      <c r="AH4" s="488" t="n"/>
+      <c r="AI4" s="406" t="inlineStr">
         <is>
           <t>Planning / QA / Engineering</t>
         </is>
       </c>
-      <c r="AJ4" s="277" t="n"/>
-      <c r="AK4" s="277" t="n"/>
-      <c r="AL4" s="277" t="n"/>
-      <c r="AM4" s="277" t="n"/>
-      <c r="AN4" s="280" t="n"/>
+      <c r="AJ4" s="487" t="n"/>
+      <c r="AK4" s="487" t="n"/>
+      <c r="AL4" s="487" t="n"/>
+      <c r="AM4" s="487" t="n"/>
+      <c r="AN4" s="488" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="282" t="n"/>
-      <c r="B5" s="283" t="n"/>
-      <c r="C5" s="283" t="n"/>
-      <c r="D5" s="283" t="n"/>
-      <c r="E5" s="283" t="n"/>
-      <c r="F5" s="283" t="n"/>
-      <c r="G5" s="283" t="n"/>
-      <c r="H5" s="283" t="n"/>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="A5" s="489" t="n"/>
+      <c r="B5" s="487" t="n"/>
+      <c r="C5" s="487" t="n"/>
+      <c r="D5" s="487" t="n"/>
+      <c r="E5" s="487" t="n"/>
+      <c r="F5" s="487" t="n"/>
+      <c r="G5" s="487" t="n"/>
+      <c r="H5" s="487" t="n"/>
+      <c r="I5" s="409" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="283" t="n"/>
-      <c r="K5" s="283" t="n"/>
-      <c r="L5" s="283" t="n"/>
-      <c r="M5" s="283" t="n"/>
-      <c r="N5" s="283" t="n"/>
-      <c r="O5" s="283" t="n"/>
-      <c r="P5" s="283" t="n"/>
-      <c r="Q5" s="283" t="n"/>
-      <c r="R5" s="283" t="n"/>
-      <c r="S5" s="283" t="n"/>
-      <c r="T5" s="283" t="n"/>
-      <c r="U5" s="283" t="n"/>
-      <c r="V5" s="283" t="n"/>
-      <c r="W5" s="283" t="n"/>
-      <c r="X5" s="283" t="n"/>
-      <c r="Y5" s="283" t="n"/>
-      <c r="Z5" s="283" t="n"/>
-      <c r="AA5" s="283" t="n"/>
-      <c r="AB5" s="283" t="n"/>
-      <c r="AC5" s="283" t="n"/>
-      <c r="AD5" s="283" t="n"/>
-      <c r="AE5" s="284" t="inlineStr">
+      <c r="J5" s="487" t="n"/>
+      <c r="K5" s="487" t="n"/>
+      <c r="L5" s="487" t="n"/>
+      <c r="M5" s="487" t="n"/>
+      <c r="N5" s="487" t="n"/>
+      <c r="O5" s="487" t="n"/>
+      <c r="P5" s="487" t="n"/>
+      <c r="Q5" s="487" t="n"/>
+      <c r="R5" s="487" t="n"/>
+      <c r="S5" s="487" t="n"/>
+      <c r="T5" s="487" t="n"/>
+      <c r="U5" s="487" t="n"/>
+      <c r="V5" s="487" t="n"/>
+      <c r="W5" s="487" t="n"/>
+      <c r="X5" s="487" t="n"/>
+      <c r="Y5" s="487" t="n"/>
+      <c r="Z5" s="487" t="n"/>
+      <c r="AA5" s="487" t="n"/>
+      <c r="AB5" s="487" t="n"/>
+      <c r="AC5" s="487" t="n"/>
+      <c r="AD5" s="487" t="n"/>
+      <c r="AE5" s="403" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="283" t="n"/>
-      <c r="AG5" s="283" t="n"/>
-      <c r="AH5" s="285" t="n"/>
-      <c r="AI5" s="286" t="inlineStr">
+      <c r="AF5" s="487" t="n"/>
+      <c r="AG5" s="487" t="n"/>
+      <c r="AH5" s="488" t="n"/>
+      <c r="AI5" s="406" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="283" t="n"/>
-      <c r="AK5" s="283" t="n"/>
-      <c r="AL5" s="283" t="n"/>
-      <c r="AM5" s="283" t="n"/>
-      <c r="AN5" s="287" t="n"/>
+      <c r="AJ5" s="487" t="n"/>
+      <c r="AK5" s="487" t="n"/>
+      <c r="AL5" s="487" t="n"/>
+      <c r="AM5" s="487" t="n"/>
+      <c r="AN5" s="488" t="n"/>
     </row>
     <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="25" t="inlineStr"/>
+      <c r="A6" s="410" t="inlineStr"/>
+      <c r="B6" s="482" t="n"/>
+      <c r="C6" s="482" t="n"/>
+      <c r="D6" s="482" t="n"/>
+      <c r="E6" s="482" t="n"/>
+      <c r="F6" s="482" t="n"/>
+      <c r="G6" s="482" t="n"/>
+      <c r="H6" s="482" t="n"/>
+      <c r="I6" s="482" t="n"/>
+      <c r="J6" s="482" t="n"/>
+      <c r="K6" s="482" t="n"/>
+      <c r="L6" s="482" t="n"/>
+      <c r="M6" s="482" t="n"/>
+      <c r="N6" s="482" t="n"/>
+      <c r="O6" s="482" t="n"/>
+      <c r="P6" s="482" t="n"/>
+      <c r="Q6" s="482" t="n"/>
+      <c r="R6" s="482" t="n"/>
+      <c r="S6" s="482" t="n"/>
+      <c r="T6" s="482" t="n"/>
+      <c r="U6" s="482" t="n"/>
+      <c r="V6" s="482" t="n"/>
+      <c r="W6" s="482" t="n"/>
+      <c r="X6" s="482" t="n"/>
+      <c r="Y6" s="482" t="n"/>
+      <c r="Z6" s="482" t="n"/>
+      <c r="AA6" s="482" t="n"/>
+      <c r="AB6" s="482" t="n"/>
+      <c r="AC6" s="482" t="n"/>
+      <c r="AD6" s="482" t="n"/>
+      <c r="AE6" s="482" t="n"/>
+      <c r="AF6" s="482" t="n"/>
+      <c r="AG6" s="482" t="n"/>
+      <c r="AH6" s="482" t="n"/>
+      <c r="AI6" s="482" t="n"/>
+      <c r="AJ6" s="482" t="n"/>
+      <c r="AK6" s="482" t="n"/>
+      <c r="AL6" s="482" t="n"/>
+      <c r="AM6" s="482" t="n"/>
+      <c r="AN6" s="482" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="288" t="inlineStr">
+      <c r="A7" s="411" t="inlineStr">
         <is>
           <t>1.  HIGH-RISK JOB HEADER / REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="289" t="n"/>
-      <c r="C7" s="289" t="n"/>
-      <c r="D7" s="289" t="n"/>
-      <c r="E7" s="289" t="n"/>
-      <c r="F7" s="289" t="n"/>
-      <c r="G7" s="289" t="n"/>
-      <c r="H7" s="289" t="n"/>
-      <c r="I7" s="289" t="n"/>
-      <c r="J7" s="289" t="n"/>
-      <c r="K7" s="289" t="n"/>
-      <c r="L7" s="289" t="n"/>
-      <c r="M7" s="289" t="n"/>
-      <c r="N7" s="289" t="n"/>
-      <c r="O7" s="289" t="n"/>
-      <c r="P7" s="289" t="n"/>
-      <c r="Q7" s="289" t="n"/>
-      <c r="R7" s="289" t="n"/>
-      <c r="S7" s="289" t="n"/>
-      <c r="T7" s="289" t="n"/>
-      <c r="U7" s="289" t="n"/>
-      <c r="V7" s="289" t="n"/>
-      <c r="W7" s="289" t="n"/>
-      <c r="X7" s="289" t="n"/>
-      <c r="Y7" s="289" t="n"/>
-      <c r="Z7" s="289" t="n"/>
-      <c r="AA7" s="289" t="n"/>
-      <c r="AB7" s="289" t="n"/>
-      <c r="AC7" s="289" t="n"/>
-      <c r="AD7" s="289" t="n"/>
-      <c r="AE7" s="289" t="n"/>
-      <c r="AF7" s="289" t="n"/>
-      <c r="AG7" s="289" t="n"/>
-      <c r="AH7" s="289" t="n"/>
-      <c r="AI7" s="289" t="n"/>
-      <c r="AJ7" s="289" t="n"/>
-      <c r="AK7" s="289" t="n"/>
-      <c r="AL7" s="289" t="n"/>
-      <c r="AM7" s="289" t="n"/>
-      <c r="AN7" s="290" t="n"/>
+      <c r="B7" s="484" t="n"/>
+      <c r="C7" s="484" t="n"/>
+      <c r="D7" s="484" t="n"/>
+      <c r="E7" s="484" t="n"/>
+      <c r="F7" s="484" t="n"/>
+      <c r="G7" s="484" t="n"/>
+      <c r="H7" s="484" t="n"/>
+      <c r="I7" s="484" t="n"/>
+      <c r="J7" s="484" t="n"/>
+      <c r="K7" s="484" t="n"/>
+      <c r="L7" s="484" t="n"/>
+      <c r="M7" s="484" t="n"/>
+      <c r="N7" s="484" t="n"/>
+      <c r="O7" s="484" t="n"/>
+      <c r="P7" s="484" t="n"/>
+      <c r="Q7" s="484" t="n"/>
+      <c r="R7" s="484" t="n"/>
+      <c r="S7" s="484" t="n"/>
+      <c r="T7" s="484" t="n"/>
+      <c r="U7" s="484" t="n"/>
+      <c r="V7" s="484" t="n"/>
+      <c r="W7" s="484" t="n"/>
+      <c r="X7" s="484" t="n"/>
+      <c r="Y7" s="484" t="n"/>
+      <c r="Z7" s="484" t="n"/>
+      <c r="AA7" s="484" t="n"/>
+      <c r="AB7" s="484" t="n"/>
+      <c r="AC7" s="484" t="n"/>
+      <c r="AD7" s="484" t="n"/>
+      <c r="AE7" s="484" t="n"/>
+      <c r="AF7" s="484" t="n"/>
+      <c r="AG7" s="484" t="n"/>
+      <c r="AH7" s="484" t="n"/>
+      <c r="AI7" s="484" t="n"/>
+      <c r="AJ7" s="484" t="n"/>
+      <c r="AK7" s="484" t="n"/>
+      <c r="AL7" s="484" t="n"/>
+      <c r="AM7" s="484" t="n"/>
+      <c r="AN7" s="485" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="291" t="inlineStr">
+      <c r="A8" s="412" t="inlineStr">
         <is>
           <t>Readiness Review ID</t>
         </is>
       </c>
-      <c r="B8" s="271" t="n"/>
-      <c r="C8" s="271" t="n"/>
-      <c r="D8" s="271" t="n"/>
-      <c r="E8" s="271" t="n"/>
-      <c r="F8" s="271" t="n"/>
-      <c r="G8" s="272" t="n"/>
-      <c r="H8" s="292" t="inlineStr"/>
-      <c r="I8" s="271" t="n"/>
-      <c r="J8" s="271" t="n"/>
-      <c r="K8" s="271" t="n"/>
-      <c r="L8" s="271" t="n"/>
-      <c r="M8" s="271" t="n"/>
-      <c r="N8" s="271" t="n"/>
-      <c r="O8" s="271" t="n"/>
-      <c r="P8" s="271" t="n"/>
-      <c r="Q8" s="271" t="n"/>
-      <c r="R8" s="271" t="n"/>
-      <c r="S8" s="271" t="n"/>
-      <c r="T8" s="272" t="n"/>
-      <c r="U8" s="293" t="inlineStr">
+      <c r="B8" s="473" t="n"/>
+      <c r="C8" s="473" t="n"/>
+      <c r="D8" s="473" t="n"/>
+      <c r="E8" s="473" t="n"/>
+      <c r="F8" s="473" t="n"/>
+      <c r="G8" s="474" t="n"/>
+      <c r="H8" s="415" t="inlineStr"/>
+      <c r="I8" s="473" t="n"/>
+      <c r="J8" s="473" t="n"/>
+      <c r="K8" s="473" t="n"/>
+      <c r="L8" s="473" t="n"/>
+      <c r="M8" s="473" t="n"/>
+      <c r="N8" s="473" t="n"/>
+      <c r="O8" s="473" t="n"/>
+      <c r="P8" s="473" t="n"/>
+      <c r="Q8" s="473" t="n"/>
+      <c r="R8" s="473" t="n"/>
+      <c r="S8" s="473" t="n"/>
+      <c r="T8" s="474" t="n"/>
+      <c r="U8" s="416" t="inlineStr">
         <is>
           <t>Job / WO</t>
         </is>
       </c>
-      <c r="V8" s="271" t="n"/>
-      <c r="W8" s="271" t="n"/>
-      <c r="X8" s="271" t="n"/>
-      <c r="Y8" s="271" t="n"/>
-      <c r="Z8" s="271" t="n"/>
-      <c r="AA8" s="272" t="n"/>
-      <c r="AB8" s="294" t="inlineStr"/>
-      <c r="AC8" s="271" t="n"/>
-      <c r="AD8" s="271" t="n"/>
-      <c r="AE8" s="271" t="n"/>
-      <c r="AF8" s="271" t="n"/>
-      <c r="AG8" s="271" t="n"/>
-      <c r="AH8" s="271" t="n"/>
-      <c r="AI8" s="271" t="n"/>
-      <c r="AJ8" s="271" t="n"/>
-      <c r="AK8" s="271" t="n"/>
-      <c r="AL8" s="271" t="n"/>
-      <c r="AM8" s="271" t="n"/>
-      <c r="AN8" s="274" t="n"/>
+      <c r="V8" s="473" t="n"/>
+      <c r="W8" s="473" t="n"/>
+      <c r="X8" s="473" t="n"/>
+      <c r="Y8" s="473" t="n"/>
+      <c r="Z8" s="473" t="n"/>
+      <c r="AA8" s="474" t="n"/>
+      <c r="AB8" s="415" t="inlineStr"/>
+      <c r="AC8" s="473" t="n"/>
+      <c r="AD8" s="473" t="n"/>
+      <c r="AE8" s="473" t="n"/>
+      <c r="AF8" s="473" t="n"/>
+      <c r="AG8" s="473" t="n"/>
+      <c r="AH8" s="473" t="n"/>
+      <c r="AI8" s="473" t="n"/>
+      <c r="AJ8" s="473" t="n"/>
+      <c r="AK8" s="473" t="n"/>
+      <c r="AL8" s="473" t="n"/>
+      <c r="AM8" s="473" t="n"/>
+      <c r="AN8" s="474" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="295" t="inlineStr">
+      <c r="A9" s="417" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="B9" s="277" t="n"/>
-      <c r="C9" s="277" t="n"/>
-      <c r="D9" s="277" t="n"/>
-      <c r="E9" s="277" t="n"/>
-      <c r="F9" s="277" t="n"/>
-      <c r="G9" s="278" t="n"/>
-      <c r="H9" s="296" t="inlineStr"/>
-      <c r="I9" s="277" t="n"/>
-      <c r="J9" s="277" t="n"/>
-      <c r="K9" s="277" t="n"/>
-      <c r="L9" s="277" t="n"/>
-      <c r="M9" s="277" t="n"/>
-      <c r="N9" s="277" t="n"/>
-      <c r="O9" s="277" t="n"/>
-      <c r="P9" s="277" t="n"/>
-      <c r="Q9" s="277" t="n"/>
-      <c r="R9" s="277" t="n"/>
-      <c r="S9" s="277" t="n"/>
-      <c r="T9" s="278" t="n"/>
-      <c r="U9" s="297" t="inlineStr">
+      <c r="B9" s="475" t="n"/>
+      <c r="C9" s="475" t="n"/>
+      <c r="D9" s="475" t="n"/>
+      <c r="E9" s="475" t="n"/>
+      <c r="F9" s="475" t="n"/>
+      <c r="G9" s="476" t="n"/>
+      <c r="H9" s="406" t="inlineStr"/>
+      <c r="I9" s="475" t="n"/>
+      <c r="J9" s="475" t="n"/>
+      <c r="K9" s="475" t="n"/>
+      <c r="L9" s="475" t="n"/>
+      <c r="M9" s="475" t="n"/>
+      <c r="N9" s="475" t="n"/>
+      <c r="O9" s="475" t="n"/>
+      <c r="P9" s="475" t="n"/>
+      <c r="Q9" s="475" t="n"/>
+      <c r="R9" s="475" t="n"/>
+      <c r="S9" s="475" t="n"/>
+      <c r="T9" s="476" t="n"/>
+      <c r="U9" s="420" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="V9" s="277" t="n"/>
-      <c r="W9" s="277" t="n"/>
-      <c r="X9" s="277" t="n"/>
-      <c r="Y9" s="277" t="n"/>
-      <c r="Z9" s="277" t="n"/>
-      <c r="AA9" s="278" t="n"/>
-      <c r="AB9" s="279" t="inlineStr"/>
-      <c r="AC9" s="277" t="n"/>
-      <c r="AD9" s="277" t="n"/>
-      <c r="AE9" s="277" t="n"/>
-      <c r="AF9" s="277" t="n"/>
-      <c r="AG9" s="277" t="n"/>
-      <c r="AH9" s="277" t="n"/>
-      <c r="AI9" s="277" t="n"/>
-      <c r="AJ9" s="277" t="n"/>
-      <c r="AK9" s="277" t="n"/>
-      <c r="AL9" s="277" t="n"/>
-      <c r="AM9" s="277" t="n"/>
-      <c r="AN9" s="280" t="n"/>
+      <c r="V9" s="475" t="n"/>
+      <c r="W9" s="475" t="n"/>
+      <c r="X9" s="475" t="n"/>
+      <c r="Y9" s="475" t="n"/>
+      <c r="Z9" s="475" t="n"/>
+      <c r="AA9" s="476" t="n"/>
+      <c r="AB9" s="406" t="inlineStr"/>
+      <c r="AC9" s="475" t="n"/>
+      <c r="AD9" s="475" t="n"/>
+      <c r="AE9" s="475" t="n"/>
+      <c r="AF9" s="475" t="n"/>
+      <c r="AG9" s="475" t="n"/>
+      <c r="AH9" s="475" t="n"/>
+      <c r="AI9" s="475" t="n"/>
+      <c r="AJ9" s="475" t="n"/>
+      <c r="AK9" s="475" t="n"/>
+      <c r="AL9" s="475" t="n"/>
+      <c r="AM9" s="475" t="n"/>
+      <c r="AN9" s="476" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="295" t="inlineStr">
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="417" t="inlineStr">
         <is>
           <t>Due Date / Commit</t>
         </is>
       </c>
-      <c r="B10" s="277" t="n"/>
-      <c r="C10" s="277" t="n"/>
-      <c r="D10" s="277" t="n"/>
-      <c r="E10" s="277" t="n"/>
-      <c r="F10" s="277" t="n"/>
-      <c r="G10" s="278" t="n"/>
-      <c r="H10" s="296" t="inlineStr"/>
-      <c r="I10" s="277" t="n"/>
-      <c r="J10" s="277" t="n"/>
-      <c r="K10" s="277" t="n"/>
-      <c r="L10" s="277" t="n"/>
-      <c r="M10" s="277" t="n"/>
-      <c r="N10" s="277" t="n"/>
-      <c r="O10" s="277" t="n"/>
-      <c r="P10" s="277" t="n"/>
-      <c r="Q10" s="277" t="n"/>
-      <c r="R10" s="277" t="n"/>
-      <c r="S10" s="277" t="n"/>
-      <c r="T10" s="278" t="n"/>
-      <c r="U10" s="297" t="inlineStr">
+      <c r="B10" s="470" t="n"/>
+      <c r="C10" s="470" t="n"/>
+      <c r="D10" s="470" t="n"/>
+      <c r="E10" s="470" t="n"/>
+      <c r="F10" s="470" t="n"/>
+      <c r="G10" s="471" t="n"/>
+      <c r="H10" s="406" t="inlineStr"/>
+      <c r="I10" s="470" t="n"/>
+      <c r="J10" s="470" t="n"/>
+      <c r="K10" s="470" t="n"/>
+      <c r="L10" s="470" t="n"/>
+      <c r="M10" s="470" t="n"/>
+      <c r="N10" s="470" t="n"/>
+      <c r="O10" s="470" t="n"/>
+      <c r="P10" s="470" t="n"/>
+      <c r="Q10" s="470" t="n"/>
+      <c r="R10" s="470" t="n"/>
+      <c r="S10" s="470" t="n"/>
+      <c r="T10" s="471" t="n"/>
+      <c r="U10" s="420" t="inlineStr">
         <is>
           <t>Current Route Step</t>
         </is>
       </c>
-      <c r="V10" s="277" t="n"/>
-      <c r="W10" s="277" t="n"/>
-      <c r="X10" s="277" t="n"/>
-      <c r="Y10" s="277" t="n"/>
-      <c r="Z10" s="277" t="n"/>
-      <c r="AA10" s="278" t="n"/>
-      <c r="AB10" s="279" t="inlineStr"/>
-      <c r="AC10" s="277" t="n"/>
-      <c r="AD10" s="277" t="n"/>
-      <c r="AE10" s="277" t="n"/>
-      <c r="AF10" s="277" t="n"/>
-      <c r="AG10" s="277" t="n"/>
-      <c r="AH10" s="277" t="n"/>
-      <c r="AI10" s="277" t="n"/>
-      <c r="AJ10" s="277" t="n"/>
-      <c r="AK10" s="277" t="n"/>
-      <c r="AL10" s="277" t="n"/>
-      <c r="AM10" s="277" t="n"/>
-      <c r="AN10" s="280" t="n"/>
+      <c r="V10" s="470" t="n"/>
+      <c r="W10" s="470" t="n"/>
+      <c r="X10" s="470" t="n"/>
+      <c r="Y10" s="470" t="n"/>
+      <c r="Z10" s="470" t="n"/>
+      <c r="AA10" s="471" t="n"/>
+      <c r="AB10" s="406" t="inlineStr"/>
+      <c r="AC10" s="470" t="n"/>
+      <c r="AD10" s="470" t="n"/>
+      <c r="AE10" s="470" t="n"/>
+      <c r="AF10" s="470" t="n"/>
+      <c r="AG10" s="470" t="n"/>
+      <c r="AH10" s="470" t="n"/>
+      <c r="AI10" s="470" t="n"/>
+      <c r="AJ10" s="470" t="n"/>
+      <c r="AK10" s="470" t="n"/>
+      <c r="AL10" s="470" t="n"/>
+      <c r="AM10" s="470" t="n"/>
+      <c r="AN10" s="471" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="295" t="inlineStr">
+      <c r="A11" s="417" t="inlineStr">
         <is>
           <t>Top Risk Class</t>
         </is>
       </c>
-      <c r="B11" s="277" t="n"/>
-      <c r="C11" s="277" t="n"/>
-      <c r="D11" s="277" t="n"/>
-      <c r="E11" s="277" t="n"/>
-      <c r="F11" s="277" t="n"/>
-      <c r="G11" s="278" t="n"/>
-      <c r="H11" s="296" t="inlineStr"/>
-      <c r="I11" s="277" t="n"/>
-      <c r="J11" s="277" t="n"/>
-      <c r="K11" s="277" t="n"/>
-      <c r="L11" s="277" t="n"/>
-      <c r="M11" s="277" t="n"/>
-      <c r="N11" s="277" t="n"/>
-      <c r="O11" s="277" t="n"/>
-      <c r="P11" s="277" t="n"/>
-      <c r="Q11" s="277" t="n"/>
-      <c r="R11" s="277" t="n"/>
-      <c r="S11" s="277" t="n"/>
-      <c r="T11" s="278" t="n"/>
-      <c r="U11" s="297" t="inlineStr">
+      <c r="B11" s="475" t="n"/>
+      <c r="C11" s="475" t="n"/>
+      <c r="D11" s="475" t="n"/>
+      <c r="E11" s="475" t="n"/>
+      <c r="F11" s="475" t="n"/>
+      <c r="G11" s="476" t="n"/>
+      <c r="H11" s="406" t="inlineStr"/>
+      <c r="I11" s="475" t="n"/>
+      <c r="J11" s="475" t="n"/>
+      <c r="K11" s="475" t="n"/>
+      <c r="L11" s="475" t="n"/>
+      <c r="M11" s="475" t="n"/>
+      <c r="N11" s="475" t="n"/>
+      <c r="O11" s="475" t="n"/>
+      <c r="P11" s="475" t="n"/>
+      <c r="Q11" s="475" t="n"/>
+      <c r="R11" s="475" t="n"/>
+      <c r="S11" s="475" t="n"/>
+      <c r="T11" s="476" t="n"/>
+      <c r="U11" s="420" t="inlineStr">
         <is>
           <t>Commercial / Ops Owner</t>
         </is>
       </c>
-      <c r="V11" s="277" t="n"/>
-      <c r="W11" s="277" t="n"/>
-      <c r="X11" s="277" t="n"/>
-      <c r="Y11" s="277" t="n"/>
-      <c r="Z11" s="277" t="n"/>
-      <c r="AA11" s="278" t="n"/>
-      <c r="AB11" s="279" t="inlineStr"/>
-      <c r="AC11" s="277" t="n"/>
-      <c r="AD11" s="277" t="n"/>
-      <c r="AE11" s="277" t="n"/>
-      <c r="AF11" s="277" t="n"/>
-      <c r="AG11" s="277" t="n"/>
-      <c r="AH11" s="277" t="n"/>
-      <c r="AI11" s="277" t="n"/>
-      <c r="AJ11" s="277" t="n"/>
-      <c r="AK11" s="277" t="n"/>
-      <c r="AL11" s="277" t="n"/>
-      <c r="AM11" s="277" t="n"/>
-      <c r="AN11" s="280" t="n"/>
+      <c r="V11" s="475" t="n"/>
+      <c r="W11" s="475" t="n"/>
+      <c r="X11" s="475" t="n"/>
+      <c r="Y11" s="475" t="n"/>
+      <c r="Z11" s="475" t="n"/>
+      <c r="AA11" s="476" t="n"/>
+      <c r="AB11" s="406" t="inlineStr"/>
+      <c r="AC11" s="475" t="n"/>
+      <c r="AD11" s="475" t="n"/>
+      <c r="AE11" s="475" t="n"/>
+      <c r="AF11" s="475" t="n"/>
+      <c r="AG11" s="475" t="n"/>
+      <c r="AH11" s="475" t="n"/>
+      <c r="AI11" s="475" t="n"/>
+      <c r="AJ11" s="475" t="n"/>
+      <c r="AK11" s="475" t="n"/>
+      <c r="AL11" s="475" t="n"/>
+      <c r="AM11" s="475" t="n"/>
+      <c r="AN11" s="476" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="298" t="inlineStr">
+      <c r="A12" s="417" t="inlineStr">
         <is>
           <t>Evidence Folder</t>
         </is>
       </c>
-      <c r="B12" s="283" t="n"/>
-      <c r="C12" s="283" t="n"/>
-      <c r="D12" s="283" t="n"/>
-      <c r="E12" s="283" t="n"/>
-      <c r="F12" s="283" t="n"/>
-      <c r="G12" s="285" t="n"/>
-      <c r="H12" s="299" t="inlineStr"/>
-      <c r="I12" s="283" t="n"/>
-      <c r="J12" s="283" t="n"/>
-      <c r="K12" s="283" t="n"/>
-      <c r="L12" s="283" t="n"/>
-      <c r="M12" s="283" t="n"/>
-      <c r="N12" s="283" t="n"/>
-      <c r="O12" s="283" t="n"/>
-      <c r="P12" s="283" t="n"/>
-      <c r="Q12" s="283" t="n"/>
-      <c r="R12" s="283" t="n"/>
-      <c r="S12" s="283" t="n"/>
-      <c r="T12" s="285" t="n"/>
-      <c r="U12" s="300" t="inlineStr">
+      <c r="B12" s="475" t="n"/>
+      <c r="C12" s="475" t="n"/>
+      <c r="D12" s="475" t="n"/>
+      <c r="E12" s="475" t="n"/>
+      <c r="F12" s="475" t="n"/>
+      <c r="G12" s="476" t="n"/>
+      <c r="H12" s="406" t="inlineStr"/>
+      <c r="I12" s="475" t="n"/>
+      <c r="J12" s="475" t="n"/>
+      <c r="K12" s="475" t="n"/>
+      <c r="L12" s="475" t="n"/>
+      <c r="M12" s="475" t="n"/>
+      <c r="N12" s="475" t="n"/>
+      <c r="O12" s="475" t="n"/>
+      <c r="P12" s="475" t="n"/>
+      <c r="Q12" s="475" t="n"/>
+      <c r="R12" s="475" t="n"/>
+      <c r="S12" s="475" t="n"/>
+      <c r="T12" s="476" t="n"/>
+      <c r="U12" s="420" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="V12" s="283" t="n"/>
-      <c r="W12" s="283" t="n"/>
-      <c r="X12" s="283" t="n"/>
-      <c r="Y12" s="283" t="n"/>
-      <c r="Z12" s="283" t="n"/>
-      <c r="AA12" s="285" t="n"/>
-      <c r="AB12" s="286" t="inlineStr"/>
-      <c r="AC12" s="283" t="n"/>
-      <c r="AD12" s="283" t="n"/>
-      <c r="AE12" s="283" t="n"/>
-      <c r="AF12" s="283" t="n"/>
-      <c r="AG12" s="283" t="n"/>
-      <c r="AH12" s="283" t="n"/>
-      <c r="AI12" s="283" t="n"/>
-      <c r="AJ12" s="283" t="n"/>
-      <c r="AK12" s="283" t="n"/>
-      <c r="AL12" s="283" t="n"/>
-      <c r="AM12" s="283" t="n"/>
-      <c r="AN12" s="287" t="n"/>
+      <c r="V12" s="475" t="n"/>
+      <c r="W12" s="475" t="n"/>
+      <c r="X12" s="475" t="n"/>
+      <c r="Y12" s="475" t="n"/>
+      <c r="Z12" s="475" t="n"/>
+      <c r="AA12" s="476" t="n"/>
+      <c r="AB12" s="406" t="inlineStr"/>
+      <c r="AC12" s="475" t="n"/>
+      <c r="AD12" s="475" t="n"/>
+      <c r="AE12" s="475" t="n"/>
+      <c r="AF12" s="475" t="n"/>
+      <c r="AG12" s="475" t="n"/>
+      <c r="AH12" s="475" t="n"/>
+      <c r="AI12" s="475" t="n"/>
+      <c r="AJ12" s="475" t="n"/>
+      <c r="AK12" s="475" t="n"/>
+      <c r="AL12" s="475" t="n"/>
+      <c r="AM12" s="475" t="n"/>
+      <c r="AN12" s="476" t="n"/>
     </row>
     <row r="13" ht="4" customHeight="1">
-      <c r="A13" s="25" t="n"/>
+      <c r="A13" s="410" t="n"/>
+      <c r="B13" s="482" t="n"/>
+      <c r="C13" s="482" t="n"/>
+      <c r="D13" s="482" t="n"/>
+      <c r="E13" s="482" t="n"/>
+      <c r="F13" s="482" t="n"/>
+      <c r="G13" s="482" t="n"/>
+      <c r="H13" s="482" t="n"/>
+      <c r="I13" s="482" t="n"/>
+      <c r="J13" s="482" t="n"/>
+      <c r="K13" s="482" t="n"/>
+      <c r="L13" s="482" t="n"/>
+      <c r="M13" s="482" t="n"/>
+      <c r="N13" s="482" t="n"/>
+      <c r="O13" s="482" t="n"/>
+      <c r="P13" s="482" t="n"/>
+      <c r="Q13" s="482" t="n"/>
+      <c r="R13" s="482" t="n"/>
+      <c r="S13" s="482" t="n"/>
+      <c r="T13" s="482" t="n"/>
+      <c r="U13" s="482" t="n"/>
+      <c r="V13" s="482" t="n"/>
+      <c r="W13" s="482" t="n"/>
+      <c r="X13" s="482" t="n"/>
+      <c r="Y13" s="482" t="n"/>
+      <c r="Z13" s="482" t="n"/>
+      <c r="AA13" s="482" t="n"/>
+      <c r="AB13" s="482" t="n"/>
+      <c r="AC13" s="482" t="n"/>
+      <c r="AD13" s="482" t="n"/>
+      <c r="AE13" s="482" t="n"/>
+      <c r="AF13" s="482" t="n"/>
+      <c r="AG13" s="482" t="n"/>
+      <c r="AH13" s="482" t="n"/>
+      <c r="AI13" s="482" t="n"/>
+      <c r="AJ13" s="482" t="n"/>
+      <c r="AK13" s="482" t="n"/>
+      <c r="AL13" s="482" t="n"/>
+      <c r="AM13" s="482" t="n"/>
+      <c r="AN13" s="482" t="n"/>
     </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="288" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="411" t="inlineStr">
         <is>
           <t>2.  READINESS DECISION / OPEN RISK CONDITIONS</t>
         </is>
       </c>
-      <c r="B14" s="289" t="n"/>
-      <c r="C14" s="289" t="n"/>
-      <c r="D14" s="289" t="n"/>
-      <c r="E14" s="289" t="n"/>
-      <c r="F14" s="289" t="n"/>
-      <c r="G14" s="289" t="n"/>
-      <c r="H14" s="289" t="n"/>
-      <c r="I14" s="289" t="n"/>
-      <c r="J14" s="289" t="n"/>
-      <c r="K14" s="289" t="n"/>
-      <c r="L14" s="289" t="n"/>
-      <c r="M14" s="289" t="n"/>
-      <c r="N14" s="289" t="n"/>
-      <c r="O14" s="289" t="n"/>
-      <c r="P14" s="289" t="n"/>
-      <c r="Q14" s="289" t="n"/>
-      <c r="R14" s="289" t="n"/>
-      <c r="S14" s="289" t="n"/>
-      <c r="T14" s="289" t="n"/>
-      <c r="U14" s="289" t="n"/>
-      <c r="V14" s="289" t="n"/>
-      <c r="W14" s="289" t="n"/>
-      <c r="X14" s="289" t="n"/>
-      <c r="Y14" s="289" t="n"/>
-      <c r="Z14" s="289" t="n"/>
-      <c r="AA14" s="289" t="n"/>
-      <c r="AB14" s="289" t="n"/>
-      <c r="AC14" s="289" t="n"/>
-      <c r="AD14" s="289" t="n"/>
-      <c r="AE14" s="289" t="n"/>
-      <c r="AF14" s="289" t="n"/>
-      <c r="AG14" s="289" t="n"/>
-      <c r="AH14" s="289" t="n"/>
-      <c r="AI14" s="289" t="n"/>
-      <c r="AJ14" s="289" t="n"/>
-      <c r="AK14" s="289" t="n"/>
-      <c r="AL14" s="289" t="n"/>
-      <c r="AM14" s="289" t="n"/>
-      <c r="AN14" s="290" t="n"/>
+      <c r="B14" s="473" t="n"/>
+      <c r="C14" s="473" t="n"/>
+      <c r="D14" s="473" t="n"/>
+      <c r="E14" s="473" t="n"/>
+      <c r="F14" s="473" t="n"/>
+      <c r="G14" s="473" t="n"/>
+      <c r="H14" s="473" t="n"/>
+      <c r="I14" s="473" t="n"/>
+      <c r="J14" s="473" t="n"/>
+      <c r="K14" s="473" t="n"/>
+      <c r="L14" s="473" t="n"/>
+      <c r="M14" s="473" t="n"/>
+      <c r="N14" s="473" t="n"/>
+      <c r="O14" s="473" t="n"/>
+      <c r="P14" s="473" t="n"/>
+      <c r="Q14" s="473" t="n"/>
+      <c r="R14" s="473" t="n"/>
+      <c r="S14" s="473" t="n"/>
+      <c r="T14" s="473" t="n"/>
+      <c r="U14" s="473" t="n"/>
+      <c r="V14" s="473" t="n"/>
+      <c r="W14" s="473" t="n"/>
+      <c r="X14" s="473" t="n"/>
+      <c r="Y14" s="473" t="n"/>
+      <c r="Z14" s="473" t="n"/>
+      <c r="AA14" s="473" t="n"/>
+      <c r="AB14" s="473" t="n"/>
+      <c r="AC14" s="473" t="n"/>
+      <c r="AD14" s="473" t="n"/>
+      <c r="AE14" s="473" t="n"/>
+      <c r="AF14" s="473" t="n"/>
+      <c r="AG14" s="473" t="n"/>
+      <c r="AH14" s="473" t="n"/>
+      <c r="AI14" s="473" t="n"/>
+      <c r="AJ14" s="473" t="n"/>
+      <c r="AK14" s="473" t="n"/>
+      <c r="AL14" s="473" t="n"/>
+      <c r="AM14" s="473" t="n"/>
+      <c r="AN14" s="474" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="291" t="inlineStr">
+      <c r="A15" s="412" t="inlineStr">
         <is>
           <t>Gate Name / Trigger</t>
         </is>
       </c>
-      <c r="B15" s="271" t="n"/>
-      <c r="C15" s="271" t="n"/>
-      <c r="D15" s="271" t="n"/>
-      <c r="E15" s="271" t="n"/>
-      <c r="F15" s="271" t="n"/>
-      <c r="G15" s="272" t="n"/>
-      <c r="H15" s="292" t="inlineStr">
+      <c r="B15" s="467" t="n"/>
+      <c r="C15" s="467" t="n"/>
+      <c r="D15" s="467" t="n"/>
+      <c r="E15" s="467" t="n"/>
+      <c r="F15" s="467" t="n"/>
+      <c r="G15" s="468" t="n"/>
+      <c r="H15" s="415" t="inlineStr">
         <is>
           <t>High-risk job release review</t>
         </is>
       </c>
-      <c r="I15" s="271" t="n"/>
-      <c r="J15" s="271" t="n"/>
-      <c r="K15" s="271" t="n"/>
-      <c r="L15" s="271" t="n"/>
-      <c r="M15" s="271" t="n"/>
-      <c r="N15" s="271" t="n"/>
-      <c r="O15" s="271" t="n"/>
-      <c r="P15" s="271" t="n"/>
-      <c r="Q15" s="271" t="n"/>
-      <c r="R15" s="271" t="n"/>
-      <c r="S15" s="271" t="n"/>
-      <c r="T15" s="272" t="n"/>
-      <c r="U15" s="293" t="inlineStr">
+      <c r="I15" s="467" t="n"/>
+      <c r="J15" s="467" t="n"/>
+      <c r="K15" s="467" t="n"/>
+      <c r="L15" s="467" t="n"/>
+      <c r="M15" s="467" t="n"/>
+      <c r="N15" s="467" t="n"/>
+      <c r="O15" s="467" t="n"/>
+      <c r="P15" s="467" t="n"/>
+      <c r="Q15" s="467" t="n"/>
+      <c r="R15" s="467" t="n"/>
+      <c r="S15" s="467" t="n"/>
+      <c r="T15" s="468" t="n"/>
+      <c r="U15" s="416" t="inlineStr">
         <is>
           <t>Gate Conclusion</t>
         </is>
       </c>
-      <c r="V15" s="271" t="n"/>
-      <c r="W15" s="271" t="n"/>
-      <c r="X15" s="271" t="n"/>
-      <c r="Y15" s="271" t="n"/>
-      <c r="Z15" s="271" t="n"/>
-      <c r="AA15" s="272" t="n"/>
-      <c r="AB15" s="294">
+      <c r="V15" s="467" t="n"/>
+      <c r="W15" s="467" t="n"/>
+      <c r="X15" s="467" t="n"/>
+      <c r="Y15" s="467" t="n"/>
+      <c r="Z15" s="467" t="n"/>
+      <c r="AA15" s="468" t="n"/>
+      <c r="AB15" s="415">
         <f>IF(COUNTA(AF22:AF31)=0,"",IF(COUNTIF(AF22:AF31,"FAIL")+COUNTIF(AF22:AF31,"HOLD")&gt;0,"HOLD",IF(COUNTIF(AF22:AF31,"PASS")=COUNTA(AF22:AF31),"APPROVED","CONDITIONAL")))</f>
         <v/>
       </c>
-      <c r="AC15" s="271" t="n"/>
-      <c r="AD15" s="271" t="n"/>
-      <c r="AE15" s="271" t="n"/>
-      <c r="AF15" s="271" t="n"/>
-      <c r="AG15" s="271" t="n"/>
-      <c r="AH15" s="271" t="n"/>
-      <c r="AI15" s="271" t="n"/>
-      <c r="AJ15" s="271" t="n"/>
-      <c r="AK15" s="271" t="n"/>
-      <c r="AL15" s="271" t="n"/>
-      <c r="AM15" s="271" t="n"/>
-      <c r="AN15" s="274" t="n"/>
+      <c r="AC15" s="467" t="n"/>
+      <c r="AD15" s="467" t="n"/>
+      <c r="AE15" s="467" t="n"/>
+      <c r="AF15" s="467" t="n"/>
+      <c r="AG15" s="467" t="n"/>
+      <c r="AH15" s="467" t="n"/>
+      <c r="AI15" s="467" t="n"/>
+      <c r="AJ15" s="467" t="n"/>
+      <c r="AK15" s="467" t="n"/>
+      <c r="AL15" s="467" t="n"/>
+      <c r="AM15" s="467" t="n"/>
+      <c r="AN15" s="468" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="295" t="inlineStr">
+      <c r="A16" s="417" t="inlineStr">
         <is>
           <t>Open Risk / Hold Reason</t>
         </is>
       </c>
-      <c r="B16" s="277" t="n"/>
-      <c r="C16" s="277" t="n"/>
-      <c r="D16" s="277" t="n"/>
-      <c r="E16" s="277" t="n"/>
-      <c r="F16" s="277" t="n"/>
-      <c r="G16" s="278" t="n"/>
-      <c r="H16" s="296" t="inlineStr"/>
-      <c r="I16" s="277" t="n"/>
-      <c r="J16" s="277" t="n"/>
-      <c r="K16" s="277" t="n"/>
-      <c r="L16" s="277" t="n"/>
-      <c r="M16" s="277" t="n"/>
-      <c r="N16" s="277" t="n"/>
-      <c r="O16" s="277" t="n"/>
-      <c r="P16" s="277" t="n"/>
-      <c r="Q16" s="277" t="n"/>
-      <c r="R16" s="277" t="n"/>
-      <c r="S16" s="277" t="n"/>
-      <c r="T16" s="278" t="n"/>
-      <c r="U16" s="297" t="inlineStr">
+      <c r="B16" s="475" t="n"/>
+      <c r="C16" s="475" t="n"/>
+      <c r="D16" s="475" t="n"/>
+      <c r="E16" s="475" t="n"/>
+      <c r="F16" s="475" t="n"/>
+      <c r="G16" s="476" t="n"/>
+      <c r="H16" s="406" t="inlineStr"/>
+      <c r="I16" s="475" t="n"/>
+      <c r="J16" s="475" t="n"/>
+      <c r="K16" s="475" t="n"/>
+      <c r="L16" s="475" t="n"/>
+      <c r="M16" s="475" t="n"/>
+      <c r="N16" s="475" t="n"/>
+      <c r="O16" s="475" t="n"/>
+      <c r="P16" s="475" t="n"/>
+      <c r="Q16" s="475" t="n"/>
+      <c r="R16" s="475" t="n"/>
+      <c r="S16" s="475" t="n"/>
+      <c r="T16" s="476" t="n"/>
+      <c r="U16" s="420" t="inlineStr">
         <is>
           <t>Next Step</t>
         </is>
       </c>
-      <c r="V16" s="277" t="n"/>
-      <c r="W16" s="277" t="n"/>
-      <c r="X16" s="277" t="n"/>
-      <c r="Y16" s="277" t="n"/>
-      <c r="Z16" s="277" t="n"/>
-      <c r="AA16" s="278" t="n"/>
-      <c r="AB16" s="279" t="inlineStr"/>
-      <c r="AC16" s="277" t="n"/>
-      <c r="AD16" s="277" t="n"/>
-      <c r="AE16" s="277" t="n"/>
-      <c r="AF16" s="277" t="n"/>
-      <c r="AG16" s="277" t="n"/>
-      <c r="AH16" s="277" t="n"/>
-      <c r="AI16" s="277" t="n"/>
-      <c r="AJ16" s="277" t="n"/>
-      <c r="AK16" s="277" t="n"/>
-      <c r="AL16" s="277" t="n"/>
-      <c r="AM16" s="277" t="n"/>
-      <c r="AN16" s="280" t="n"/>
+      <c r="V16" s="475" t="n"/>
+      <c r="W16" s="475" t="n"/>
+      <c r="X16" s="475" t="n"/>
+      <c r="Y16" s="475" t="n"/>
+      <c r="Z16" s="475" t="n"/>
+      <c r="AA16" s="476" t="n"/>
+      <c r="AB16" s="406" t="inlineStr"/>
+      <c r="AC16" s="475" t="n"/>
+      <c r="AD16" s="475" t="n"/>
+      <c r="AE16" s="475" t="n"/>
+      <c r="AF16" s="475" t="n"/>
+      <c r="AG16" s="475" t="n"/>
+      <c r="AH16" s="475" t="n"/>
+      <c r="AI16" s="475" t="n"/>
+      <c r="AJ16" s="475" t="n"/>
+      <c r="AK16" s="475" t="n"/>
+      <c r="AL16" s="475" t="n"/>
+      <c r="AM16" s="475" t="n"/>
+      <c r="AN16" s="476" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="295" t="inlineStr">
+      <c r="A17" s="417" t="inlineStr">
         <is>
           <t>Action Owner</t>
         </is>
       </c>
-      <c r="B17" s="277" t="n"/>
-      <c r="C17" s="277" t="n"/>
-      <c r="D17" s="277" t="n"/>
-      <c r="E17" s="277" t="n"/>
-      <c r="F17" s="277" t="n"/>
-      <c r="G17" s="278" t="n"/>
-      <c r="H17" s="296" t="inlineStr"/>
-      <c r="I17" s="277" t="n"/>
-      <c r="J17" s="277" t="n"/>
-      <c r="K17" s="277" t="n"/>
-      <c r="L17" s="277" t="n"/>
-      <c r="M17" s="277" t="n"/>
-      <c r="N17" s="277" t="n"/>
-      <c r="O17" s="277" t="n"/>
-      <c r="P17" s="277" t="n"/>
-      <c r="Q17" s="277" t="n"/>
-      <c r="R17" s="277" t="n"/>
-      <c r="S17" s="277" t="n"/>
-      <c r="T17" s="278" t="n"/>
-      <c r="U17" s="297" t="inlineStr">
+      <c r="B17" s="475" t="n"/>
+      <c r="C17" s="475" t="n"/>
+      <c r="D17" s="475" t="n"/>
+      <c r="E17" s="475" t="n"/>
+      <c r="F17" s="475" t="n"/>
+      <c r="G17" s="476" t="n"/>
+      <c r="H17" s="406" t="inlineStr"/>
+      <c r="I17" s="475" t="n"/>
+      <c r="J17" s="475" t="n"/>
+      <c r="K17" s="475" t="n"/>
+      <c r="L17" s="475" t="n"/>
+      <c r="M17" s="475" t="n"/>
+      <c r="N17" s="475" t="n"/>
+      <c r="O17" s="475" t="n"/>
+      <c r="P17" s="475" t="n"/>
+      <c r="Q17" s="475" t="n"/>
+      <c r="R17" s="475" t="n"/>
+      <c r="S17" s="475" t="n"/>
+      <c r="T17" s="476" t="n"/>
+      <c r="U17" s="420" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="V17" s="277" t="n"/>
-      <c r="W17" s="277" t="n"/>
-      <c r="X17" s="277" t="n"/>
-      <c r="Y17" s="277" t="n"/>
-      <c r="Z17" s="277" t="n"/>
-      <c r="AA17" s="278" t="n"/>
-      <c r="AB17" s="279" t="inlineStr"/>
-      <c r="AC17" s="277" t="n"/>
-      <c r="AD17" s="277" t="n"/>
-      <c r="AE17" s="277" t="n"/>
-      <c r="AF17" s="277" t="n"/>
-      <c r="AG17" s="277" t="n"/>
-      <c r="AH17" s="277" t="n"/>
-      <c r="AI17" s="277" t="n"/>
-      <c r="AJ17" s="277" t="n"/>
-      <c r="AK17" s="277" t="n"/>
-      <c r="AL17" s="277" t="n"/>
-      <c r="AM17" s="277" t="n"/>
-      <c r="AN17" s="280" t="n"/>
+      <c r="V17" s="475" t="n"/>
+      <c r="W17" s="475" t="n"/>
+      <c r="X17" s="475" t="n"/>
+      <c r="Y17" s="475" t="n"/>
+      <c r="Z17" s="475" t="n"/>
+      <c r="AA17" s="476" t="n"/>
+      <c r="AB17" s="406" t="inlineStr"/>
+      <c r="AC17" s="475" t="n"/>
+      <c r="AD17" s="475" t="n"/>
+      <c r="AE17" s="475" t="n"/>
+      <c r="AF17" s="475" t="n"/>
+      <c r="AG17" s="475" t="n"/>
+      <c r="AH17" s="475" t="n"/>
+      <c r="AI17" s="475" t="n"/>
+      <c r="AJ17" s="475" t="n"/>
+      <c r="AK17" s="475" t="n"/>
+      <c r="AL17" s="475" t="n"/>
+      <c r="AM17" s="475" t="n"/>
+      <c r="AN17" s="476" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="298" t="inlineStr">
+      <c r="A18" s="417" t="inlineStr">
         <is>
           <t>Escalation if Overdue</t>
         </is>
       </c>
-      <c r="B18" s="283" t="n"/>
-      <c r="C18" s="283" t="n"/>
-      <c r="D18" s="283" t="n"/>
-      <c r="E18" s="283" t="n"/>
-      <c r="F18" s="283" t="n"/>
-      <c r="G18" s="285" t="n"/>
-      <c r="H18" s="299" t="inlineStr"/>
-      <c r="I18" s="283" t="n"/>
-      <c r="J18" s="283" t="n"/>
-      <c r="K18" s="283" t="n"/>
-      <c r="L18" s="283" t="n"/>
-      <c r="M18" s="283" t="n"/>
-      <c r="N18" s="283" t="n"/>
-      <c r="O18" s="283" t="n"/>
-      <c r="P18" s="283" t="n"/>
-      <c r="Q18" s="283" t="n"/>
-      <c r="R18" s="283" t="n"/>
-      <c r="S18" s="283" t="n"/>
-      <c r="T18" s="285" t="n"/>
-      <c r="U18" s="300" t="inlineStr">
+      <c r="B18" s="475" t="n"/>
+      <c r="C18" s="475" t="n"/>
+      <c r="D18" s="475" t="n"/>
+      <c r="E18" s="475" t="n"/>
+      <c r="F18" s="475" t="n"/>
+      <c r="G18" s="476" t="n"/>
+      <c r="H18" s="406" t="inlineStr"/>
+      <c r="I18" s="475" t="n"/>
+      <c r="J18" s="475" t="n"/>
+      <c r="K18" s="475" t="n"/>
+      <c r="L18" s="475" t="n"/>
+      <c r="M18" s="475" t="n"/>
+      <c r="N18" s="475" t="n"/>
+      <c r="O18" s="475" t="n"/>
+      <c r="P18" s="475" t="n"/>
+      <c r="Q18" s="475" t="n"/>
+      <c r="R18" s="475" t="n"/>
+      <c r="S18" s="475" t="n"/>
+      <c r="T18" s="476" t="n"/>
+      <c r="U18" s="420" t="inlineStr">
         <is>
           <t>Gate Status</t>
         </is>
       </c>
-      <c r="V18" s="283" t="n"/>
-      <c r="W18" s="283" t="n"/>
-      <c r="X18" s="283" t="n"/>
-      <c r="Y18" s="283" t="n"/>
-      <c r="Z18" s="283" t="n"/>
-      <c r="AA18" s="285" t="n"/>
-      <c r="AB18" s="286">
+      <c r="V18" s="475" t="n"/>
+      <c r="W18" s="475" t="n"/>
+      <c r="X18" s="475" t="n"/>
+      <c r="Y18" s="475" t="n"/>
+      <c r="Z18" s="475" t="n"/>
+      <c r="AA18" s="476" t="n"/>
+      <c r="AB18" s="406">
         <f>IF(COUNTA(AF22:AF31)=0,"",IF(COUNTIF(AF22:AF31,"FAIL")+COUNTIF(AF22:AF31,"HOLD")&gt;0,"OPEN","CLOSED"))</f>
         <v/>
       </c>
-      <c r="AC18" s="283" t="n"/>
-      <c r="AD18" s="283" t="n"/>
-      <c r="AE18" s="283" t="n"/>
-      <c r="AF18" s="283" t="n"/>
-      <c r="AG18" s="283" t="n"/>
-      <c r="AH18" s="283" t="n"/>
-      <c r="AI18" s="283" t="n"/>
-      <c r="AJ18" s="283" t="n"/>
-      <c r="AK18" s="283" t="n"/>
-      <c r="AL18" s="283" t="n"/>
-      <c r="AM18" s="283" t="n"/>
-      <c r="AN18" s="287" t="n"/>
+      <c r="AC18" s="475" t="n"/>
+      <c r="AD18" s="475" t="n"/>
+      <c r="AE18" s="475" t="n"/>
+      <c r="AF18" s="475" t="n"/>
+      <c r="AG18" s="475" t="n"/>
+      <c r="AH18" s="475" t="n"/>
+      <c r="AI18" s="475" t="n"/>
+      <c r="AJ18" s="475" t="n"/>
+      <c r="AK18" s="475" t="n"/>
+      <c r="AL18" s="475" t="n"/>
+      <c r="AM18" s="475" t="n"/>
+      <c r="AN18" s="476" t="n"/>
     </row>
     <row r="19" ht="4" customHeight="1">
-      <c r="A19" s="25" t="n"/>
+      <c r="A19" s="410" t="n"/>
+      <c r="B19" s="482" t="n"/>
+      <c r="C19" s="482" t="n"/>
+      <c r="D19" s="482" t="n"/>
+      <c r="E19" s="482" t="n"/>
+      <c r="F19" s="482" t="n"/>
+      <c r="G19" s="482" t="n"/>
+      <c r="H19" s="482" t="n"/>
+      <c r="I19" s="482" t="n"/>
+      <c r="J19" s="482" t="n"/>
+      <c r="K19" s="482" t="n"/>
+      <c r="L19" s="482" t="n"/>
+      <c r="M19" s="482" t="n"/>
+      <c r="N19" s="482" t="n"/>
+      <c r="O19" s="482" t="n"/>
+      <c r="P19" s="482" t="n"/>
+      <c r="Q19" s="482" t="n"/>
+      <c r="R19" s="482" t="n"/>
+      <c r="S19" s="482" t="n"/>
+      <c r="T19" s="482" t="n"/>
+      <c r="U19" s="482" t="n"/>
+      <c r="V19" s="482" t="n"/>
+      <c r="W19" s="482" t="n"/>
+      <c r="X19" s="482" t="n"/>
+      <c r="Y19" s="482" t="n"/>
+      <c r="Z19" s="482" t="n"/>
+      <c r="AA19" s="482" t="n"/>
+      <c r="AB19" s="482" t="n"/>
+      <c r="AC19" s="482" t="n"/>
+      <c r="AD19" s="482" t="n"/>
+      <c r="AE19" s="482" t="n"/>
+      <c r="AF19" s="482" t="n"/>
+      <c r="AG19" s="482" t="n"/>
+      <c r="AH19" s="482" t="n"/>
+      <c r="AI19" s="482" t="n"/>
+      <c r="AJ19" s="482" t="n"/>
+      <c r="AK19" s="482" t="n"/>
+      <c r="AL19" s="482" t="n"/>
+      <c r="AM19" s="482" t="n"/>
+      <c r="AN19" s="482" t="n"/>
     </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="288" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="411" t="inlineStr">
         <is>
           <t>3.  READINESS CRITERIA / RISK CHECK</t>
         </is>
       </c>
-      <c r="B20" s="289" t="n"/>
-      <c r="C20" s="289" t="n"/>
-      <c r="D20" s="289" t="n"/>
-      <c r="E20" s="289" t="n"/>
-      <c r="F20" s="289" t="n"/>
-      <c r="G20" s="289" t="n"/>
-      <c r="H20" s="289" t="n"/>
-      <c r="I20" s="289" t="n"/>
-      <c r="J20" s="289" t="n"/>
-      <c r="K20" s="289" t="n"/>
-      <c r="L20" s="289" t="n"/>
-      <c r="M20" s="289" t="n"/>
-      <c r="N20" s="289" t="n"/>
-      <c r="O20" s="289" t="n"/>
-      <c r="P20" s="289" t="n"/>
-      <c r="Q20" s="289" t="n"/>
-      <c r="R20" s="289" t="n"/>
-      <c r="S20" s="289" t="n"/>
-      <c r="T20" s="289" t="n"/>
-      <c r="U20" s="289" t="n"/>
-      <c r="V20" s="289" t="n"/>
-      <c r="W20" s="289" t="n"/>
-      <c r="X20" s="289" t="n"/>
-      <c r="Y20" s="289" t="n"/>
-      <c r="Z20" s="289" t="n"/>
-      <c r="AA20" s="289" t="n"/>
-      <c r="AB20" s="289" t="n"/>
-      <c r="AC20" s="289" t="n"/>
-      <c r="AD20" s="289" t="n"/>
-      <c r="AE20" s="289" t="n"/>
-      <c r="AF20" s="289" t="n"/>
-      <c r="AG20" s="289" t="n"/>
-      <c r="AH20" s="289" t="n"/>
-      <c r="AI20" s="289" t="n"/>
-      <c r="AJ20" s="289" t="n"/>
-      <c r="AK20" s="289" t="n"/>
-      <c r="AL20" s="289" t="n"/>
-      <c r="AM20" s="289" t="n"/>
-      <c r="AN20" s="290" t="n"/>
+      <c r="B20" s="473" t="n"/>
+      <c r="C20" s="473" t="n"/>
+      <c r="D20" s="473" t="n"/>
+      <c r="E20" s="473" t="n"/>
+      <c r="F20" s="473" t="n"/>
+      <c r="G20" s="473" t="n"/>
+      <c r="H20" s="473" t="n"/>
+      <c r="I20" s="473" t="n"/>
+      <c r="J20" s="473" t="n"/>
+      <c r="K20" s="473" t="n"/>
+      <c r="L20" s="473" t="n"/>
+      <c r="M20" s="473" t="n"/>
+      <c r="N20" s="473" t="n"/>
+      <c r="O20" s="473" t="n"/>
+      <c r="P20" s="473" t="n"/>
+      <c r="Q20" s="473" t="n"/>
+      <c r="R20" s="473" t="n"/>
+      <c r="S20" s="473" t="n"/>
+      <c r="T20" s="473" t="n"/>
+      <c r="U20" s="473" t="n"/>
+      <c r="V20" s="473" t="n"/>
+      <c r="W20" s="473" t="n"/>
+      <c r="X20" s="473" t="n"/>
+      <c r="Y20" s="473" t="n"/>
+      <c r="Z20" s="473" t="n"/>
+      <c r="AA20" s="473" t="n"/>
+      <c r="AB20" s="473" t="n"/>
+      <c r="AC20" s="473" t="n"/>
+      <c r="AD20" s="473" t="n"/>
+      <c r="AE20" s="473" t="n"/>
+      <c r="AF20" s="473" t="n"/>
+      <c r="AG20" s="473" t="n"/>
+      <c r="AH20" s="473" t="n"/>
+      <c r="AI20" s="473" t="n"/>
+      <c r="AJ20" s="473" t="n"/>
+      <c r="AK20" s="473" t="n"/>
+      <c r="AL20" s="473" t="n"/>
+      <c r="AM20" s="473" t="n"/>
+      <c r="AN20" s="474" t="n"/>
     </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="301" t="inlineStr">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="421" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B21" s="272" t="n"/>
-      <c r="C21" s="302" t="inlineStr">
+      <c r="B21" s="474" t="n"/>
+      <c r="C21" s="422" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="D21" s="271" t="n"/>
-      <c r="E21" s="272" t="n"/>
-      <c r="F21" s="302" t="inlineStr">
+      <c r="D21" s="473" t="n"/>
+      <c r="E21" s="474" t="n"/>
+      <c r="F21" s="422" t="inlineStr">
         <is>
           <t>Readiness / Risk Item</t>
         </is>
       </c>
-      <c r="G21" s="271" t="n"/>
-      <c r="H21" s="271" t="n"/>
-      <c r="I21" s="271" t="n"/>
-      <c r="J21" s="271" t="n"/>
-      <c r="K21" s="271" t="n"/>
-      <c r="L21" s="271" t="n"/>
-      <c r="M21" s="271" t="n"/>
-      <c r="N21" s="271" t="n"/>
-      <c r="O21" s="271" t="n"/>
-      <c r="P21" s="271" t="n"/>
-      <c r="Q21" s="271" t="n"/>
-      <c r="R21" s="271" t="n"/>
-      <c r="S21" s="272" t="n"/>
-      <c r="T21" s="302" t="inlineStr">
+      <c r="G21" s="473" t="n"/>
+      <c r="H21" s="473" t="n"/>
+      <c r="I21" s="473" t="n"/>
+      <c r="J21" s="473" t="n"/>
+      <c r="K21" s="473" t="n"/>
+      <c r="L21" s="473" t="n"/>
+      <c r="M21" s="473" t="n"/>
+      <c r="N21" s="473" t="n"/>
+      <c r="O21" s="473" t="n"/>
+      <c r="P21" s="473" t="n"/>
+      <c r="Q21" s="473" t="n"/>
+      <c r="R21" s="473" t="n"/>
+      <c r="S21" s="474" t="n"/>
+      <c r="T21" s="422" t="inlineStr">
         <is>
           <t>Acceptance / Control Rule</t>
         </is>
       </c>
-      <c r="U21" s="271" t="n"/>
-      <c r="V21" s="271" t="n"/>
-      <c r="W21" s="271" t="n"/>
-      <c r="X21" s="271" t="n"/>
-      <c r="Y21" s="271" t="n"/>
-      <c r="Z21" s="271" t="n"/>
-      <c r="AA21" s="271" t="n"/>
-      <c r="AB21" s="271" t="n"/>
-      <c r="AC21" s="271" t="n"/>
-      <c r="AD21" s="271" t="n"/>
-      <c r="AE21" s="272" t="n"/>
-      <c r="AF21" s="302" t="inlineStr">
+      <c r="U21" s="473" t="n"/>
+      <c r="V21" s="473" t="n"/>
+      <c r="W21" s="473" t="n"/>
+      <c r="X21" s="473" t="n"/>
+      <c r="Y21" s="473" t="n"/>
+      <c r="Z21" s="473" t="n"/>
+      <c r="AA21" s="473" t="n"/>
+      <c r="AB21" s="473" t="n"/>
+      <c r="AC21" s="473" t="n"/>
+      <c r="AD21" s="473" t="n"/>
+      <c r="AE21" s="474" t="n"/>
+      <c r="AF21" s="422" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG21" s="271" t="n"/>
-      <c r="AH21" s="271" t="n"/>
-      <c r="AI21" s="272" t="n"/>
-      <c r="AJ21" s="302" t="inlineStr">
+      <c r="AG21" s="473" t="n"/>
+      <c r="AH21" s="473" t="n"/>
+      <c r="AI21" s="474" t="n"/>
+      <c r="AJ21" s="422" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK21" s="271" t="n"/>
-      <c r="AL21" s="272" t="n"/>
-      <c r="AM21" s="303" t="inlineStr">
+      <c r="AK21" s="473" t="n"/>
+      <c r="AL21" s="474" t="n"/>
+      <c r="AM21" s="422" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="AN21" s="274" t="n"/>
+      <c r="AN21" s="474" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="304" t="n">
+      <c r="A22" s="423" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="328" t="n"/>
-      <c r="C22" s="305" t="inlineStr">
+      <c r="B22" s="474" t="n"/>
+      <c r="C22" s="424" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D22" s="277" t="n"/>
-      <c r="E22" s="278" t="n"/>
-      <c r="F22" s="306" t="inlineStr">
+      <c r="D22" s="475" t="n"/>
+      <c r="E22" s="476" t="n"/>
+      <c r="F22" s="425" t="inlineStr">
         <is>
           <t>Released baseline package is locked.</t>
         </is>
       </c>
-      <c r="G22" s="277" t="n"/>
-      <c r="H22" s="277" t="n"/>
-      <c r="I22" s="277" t="n"/>
-      <c r="J22" s="277" t="n"/>
-      <c r="K22" s="277" t="n"/>
-      <c r="L22" s="277" t="n"/>
-      <c r="M22" s="277" t="n"/>
-      <c r="N22" s="277" t="n"/>
-      <c r="O22" s="277" t="n"/>
-      <c r="P22" s="277" t="n"/>
-      <c r="Q22" s="277" t="n"/>
-      <c r="R22" s="277" t="n"/>
-      <c r="S22" s="278" t="n"/>
-      <c r="T22" s="307" t="inlineStr">
+      <c r="G22" s="475" t="n"/>
+      <c r="H22" s="475" t="n"/>
+      <c r="I22" s="475" t="n"/>
+      <c r="J22" s="475" t="n"/>
+      <c r="K22" s="475" t="n"/>
+      <c r="L22" s="475" t="n"/>
+      <c r="M22" s="475" t="n"/>
+      <c r="N22" s="475" t="n"/>
+      <c r="O22" s="475" t="n"/>
+      <c r="P22" s="475" t="n"/>
+      <c r="Q22" s="475" t="n"/>
+      <c r="R22" s="475" t="n"/>
+      <c r="S22" s="476" t="n"/>
+      <c r="T22" s="426" t="inlineStr">
         <is>
           <t>FRM-306 or released package reference is current.</t>
         </is>
       </c>
-      <c r="U22" s="277" t="n"/>
-      <c r="V22" s="277" t="n"/>
-      <c r="W22" s="277" t="n"/>
-      <c r="X22" s="277" t="n"/>
-      <c r="Y22" s="277" t="n"/>
-      <c r="Z22" s="277" t="n"/>
-      <c r="AA22" s="277" t="n"/>
-      <c r="AB22" s="277" t="n"/>
-      <c r="AC22" s="277" t="n"/>
-      <c r="AD22" s="277" t="n"/>
-      <c r="AE22" s="278" t="n"/>
-      <c r="AF22" s="308" t="n"/>
-      <c r="AG22" s="329" t="n"/>
-      <c r="AH22" s="329" t="n"/>
-      <c r="AI22" s="328" t="n"/>
-      <c r="AJ22" s="308" t="n"/>
-      <c r="AK22" s="329" t="n"/>
-      <c r="AL22" s="328" t="n"/>
-      <c r="AM22" s="308" t="n"/>
-      <c r="AN22" s="328" t="n"/>
+      <c r="U22" s="475" t="n"/>
+      <c r="V22" s="475" t="n"/>
+      <c r="W22" s="475" t="n"/>
+      <c r="X22" s="475" t="n"/>
+      <c r="Y22" s="475" t="n"/>
+      <c r="Z22" s="475" t="n"/>
+      <c r="AA22" s="475" t="n"/>
+      <c r="AB22" s="475" t="n"/>
+      <c r="AC22" s="475" t="n"/>
+      <c r="AD22" s="475" t="n"/>
+      <c r="AE22" s="476" t="n"/>
+      <c r="AF22" s="427" t="n"/>
+      <c r="AG22" s="473" t="n"/>
+      <c r="AH22" s="473" t="n"/>
+      <c r="AI22" s="474" t="n"/>
+      <c r="AJ22" s="427" t="n"/>
+      <c r="AK22" s="473" t="n"/>
+      <c r="AL22" s="474" t="n"/>
+      <c r="AM22" s="427" t="n"/>
+      <c r="AN22" s="474" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="304" t="n">
+      <c r="A23" s="423" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="328" t="n"/>
-      <c r="C23" s="305" t="inlineStr">
+      <c r="B23" s="474" t="n"/>
+      <c r="C23" s="424" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D23" s="277" t="n"/>
-      <c r="E23" s="278" t="n"/>
-      <c r="F23" s="309" t="inlineStr">
+      <c r="D23" s="475" t="n"/>
+      <c r="E23" s="476" t="n"/>
+      <c r="F23" s="428" t="inlineStr">
         <is>
           <t>Customer / quality package is identified.</t>
         </is>
       </c>
-      <c r="G23" s="277" t="n"/>
-      <c r="H23" s="277" t="n"/>
-      <c r="I23" s="277" t="n"/>
-      <c r="J23" s="277" t="n"/>
-      <c r="K23" s="277" t="n"/>
-      <c r="L23" s="277" t="n"/>
-      <c r="M23" s="277" t="n"/>
-      <c r="N23" s="277" t="n"/>
-      <c r="O23" s="277" t="n"/>
-      <c r="P23" s="277" t="n"/>
-      <c r="Q23" s="277" t="n"/>
-      <c r="R23" s="277" t="n"/>
-      <c r="S23" s="278" t="n"/>
-      <c r="T23" s="307" t="inlineStr">
+      <c r="G23" s="475" t="n"/>
+      <c r="H23" s="475" t="n"/>
+      <c r="I23" s="475" t="n"/>
+      <c r="J23" s="475" t="n"/>
+      <c r="K23" s="475" t="n"/>
+      <c r="L23" s="475" t="n"/>
+      <c r="M23" s="475" t="n"/>
+      <c r="N23" s="475" t="n"/>
+      <c r="O23" s="475" t="n"/>
+      <c r="P23" s="475" t="n"/>
+      <c r="Q23" s="475" t="n"/>
+      <c r="R23" s="475" t="n"/>
+      <c r="S23" s="476" t="n"/>
+      <c r="T23" s="426" t="inlineStr">
         <is>
           <t>CSR / cert / packaging rules are visible.</t>
         </is>
       </c>
-      <c r="U23" s="277" t="n"/>
-      <c r="V23" s="277" t="n"/>
-      <c r="W23" s="277" t="n"/>
-      <c r="X23" s="277" t="n"/>
-      <c r="Y23" s="277" t="n"/>
-      <c r="Z23" s="277" t="n"/>
-      <c r="AA23" s="277" t="n"/>
-      <c r="AB23" s="277" t="n"/>
-      <c r="AC23" s="277" t="n"/>
-      <c r="AD23" s="277" t="n"/>
-      <c r="AE23" s="278" t="n"/>
-      <c r="AF23" s="308" t="n"/>
-      <c r="AG23" s="329" t="n"/>
-      <c r="AH23" s="329" t="n"/>
-      <c r="AI23" s="328" t="n"/>
-      <c r="AJ23" s="308" t="n"/>
-      <c r="AK23" s="329" t="n"/>
-      <c r="AL23" s="328" t="n"/>
-      <c r="AM23" s="308" t="n"/>
-      <c r="AN23" s="328" t="n"/>
+      <c r="U23" s="475" t="n"/>
+      <c r="V23" s="475" t="n"/>
+      <c r="W23" s="475" t="n"/>
+      <c r="X23" s="475" t="n"/>
+      <c r="Y23" s="475" t="n"/>
+      <c r="Z23" s="475" t="n"/>
+      <c r="AA23" s="475" t="n"/>
+      <c r="AB23" s="475" t="n"/>
+      <c r="AC23" s="475" t="n"/>
+      <c r="AD23" s="475" t="n"/>
+      <c r="AE23" s="476" t="n"/>
+      <c r="AF23" s="427" t="n"/>
+      <c r="AG23" s="473" t="n"/>
+      <c r="AH23" s="473" t="n"/>
+      <c r="AI23" s="474" t="n"/>
+      <c r="AJ23" s="427" t="n"/>
+      <c r="AK23" s="473" t="n"/>
+      <c r="AL23" s="474" t="n"/>
+      <c r="AM23" s="427" t="n"/>
+      <c r="AN23" s="474" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="304" t="n">
+      <c r="A24" s="423" t="n">
         <v>3</v>
       </c>
-      <c r="B24" s="328" t="n"/>
-      <c r="C24" s="305" t="inlineStr">
+      <c r="B24" s="474" t="n"/>
+      <c r="C24" s="424" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D24" s="277" t="n"/>
-      <c r="E24" s="278" t="n"/>
-      <c r="F24" s="306" t="inlineStr">
+      <c r="D24" s="475" t="n"/>
+      <c r="E24" s="476" t="n"/>
+      <c r="F24" s="425" t="inlineStr">
         <is>
           <t>Material / outsource path is feasible.</t>
         </is>
       </c>
-      <c r="G24" s="277" t="n"/>
-      <c r="H24" s="277" t="n"/>
-      <c r="I24" s="277" t="n"/>
-      <c r="J24" s="277" t="n"/>
-      <c r="K24" s="277" t="n"/>
-      <c r="L24" s="277" t="n"/>
-      <c r="M24" s="277" t="n"/>
-      <c r="N24" s="277" t="n"/>
-      <c r="O24" s="277" t="n"/>
-      <c r="P24" s="277" t="n"/>
-      <c r="Q24" s="277" t="n"/>
-      <c r="R24" s="277" t="n"/>
-      <c r="S24" s="278" t="n"/>
-      <c r="T24" s="307" t="inlineStr">
+      <c r="G24" s="475" t="n"/>
+      <c r="H24" s="475" t="n"/>
+      <c r="I24" s="475" t="n"/>
+      <c r="J24" s="475" t="n"/>
+      <c r="K24" s="475" t="n"/>
+      <c r="L24" s="475" t="n"/>
+      <c r="M24" s="475" t="n"/>
+      <c r="N24" s="475" t="n"/>
+      <c r="O24" s="475" t="n"/>
+      <c r="P24" s="475" t="n"/>
+      <c r="Q24" s="475" t="n"/>
+      <c r="R24" s="475" t="n"/>
+      <c r="S24" s="476" t="n"/>
+      <c r="T24" s="426" t="inlineStr">
         <is>
           <t>Critical source path is not assumed.</t>
         </is>
       </c>
-      <c r="U24" s="277" t="n"/>
-      <c r="V24" s="277" t="n"/>
-      <c r="W24" s="277" t="n"/>
-      <c r="X24" s="277" t="n"/>
-      <c r="Y24" s="277" t="n"/>
-      <c r="Z24" s="277" t="n"/>
-      <c r="AA24" s="277" t="n"/>
-      <c r="AB24" s="277" t="n"/>
-      <c r="AC24" s="277" t="n"/>
-      <c r="AD24" s="277" t="n"/>
-      <c r="AE24" s="278" t="n"/>
-      <c r="AF24" s="308" t="n"/>
-      <c r="AG24" s="329" t="n"/>
-      <c r="AH24" s="329" t="n"/>
-      <c r="AI24" s="328" t="n"/>
-      <c r="AJ24" s="308" t="n"/>
-      <c r="AK24" s="329" t="n"/>
-      <c r="AL24" s="328" t="n"/>
-      <c r="AM24" s="308" t="n"/>
-      <c r="AN24" s="328" t="n"/>
+      <c r="U24" s="475" t="n"/>
+      <c r="V24" s="475" t="n"/>
+      <c r="W24" s="475" t="n"/>
+      <c r="X24" s="475" t="n"/>
+      <c r="Y24" s="475" t="n"/>
+      <c r="Z24" s="475" t="n"/>
+      <c r="AA24" s="475" t="n"/>
+      <c r="AB24" s="475" t="n"/>
+      <c r="AC24" s="475" t="n"/>
+      <c r="AD24" s="475" t="n"/>
+      <c r="AE24" s="476" t="n"/>
+      <c r="AF24" s="427" t="n"/>
+      <c r="AG24" s="473" t="n"/>
+      <c r="AH24" s="473" t="n"/>
+      <c r="AI24" s="474" t="n"/>
+      <c r="AJ24" s="427" t="n"/>
+      <c r="AK24" s="473" t="n"/>
+      <c r="AL24" s="474" t="n"/>
+      <c r="AM24" s="427" t="n"/>
+      <c r="AN24" s="474" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="304" t="n">
+      <c r="A25" s="423" t="n">
         <v>4</v>
       </c>
-      <c r="B25" s="328" t="n"/>
-      <c r="C25" s="305" t="inlineStr">
+      <c r="B25" s="474" t="n"/>
+      <c r="C25" s="424" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D25" s="277" t="n"/>
-      <c r="E25" s="278" t="n"/>
-      <c r="F25" s="309" t="inlineStr">
+      <c r="D25" s="475" t="n"/>
+      <c r="E25" s="476" t="n"/>
+      <c r="F25" s="428" t="inlineStr">
         <is>
           <t>Machine / tooling / gage readiness exists.</t>
         </is>
       </c>
-      <c r="G25" s="277" t="n"/>
-      <c r="H25" s="277" t="n"/>
-      <c r="I25" s="277" t="n"/>
-      <c r="J25" s="277" t="n"/>
-      <c r="K25" s="277" t="n"/>
-      <c r="L25" s="277" t="n"/>
-      <c r="M25" s="277" t="n"/>
-      <c r="N25" s="277" t="n"/>
-      <c r="O25" s="277" t="n"/>
-      <c r="P25" s="277" t="n"/>
-      <c r="Q25" s="277" t="n"/>
-      <c r="R25" s="277" t="n"/>
-      <c r="S25" s="278" t="n"/>
-      <c r="T25" s="307" t="inlineStr">
+      <c r="G25" s="475" t="n"/>
+      <c r="H25" s="475" t="n"/>
+      <c r="I25" s="475" t="n"/>
+      <c r="J25" s="475" t="n"/>
+      <c r="K25" s="475" t="n"/>
+      <c r="L25" s="475" t="n"/>
+      <c r="M25" s="475" t="n"/>
+      <c r="N25" s="475" t="n"/>
+      <c r="O25" s="475" t="n"/>
+      <c r="P25" s="475" t="n"/>
+      <c r="Q25" s="475" t="n"/>
+      <c r="R25" s="475" t="n"/>
+      <c r="S25" s="476" t="n"/>
+      <c r="T25" s="426" t="inlineStr">
         <is>
           <t>Capability and readiness path are visible.</t>
         </is>
       </c>
-      <c r="U25" s="277" t="n"/>
-      <c r="V25" s="277" t="n"/>
-      <c r="W25" s="277" t="n"/>
-      <c r="X25" s="277" t="n"/>
-      <c r="Y25" s="277" t="n"/>
-      <c r="Z25" s="277" t="n"/>
-      <c r="AA25" s="277" t="n"/>
-      <c r="AB25" s="277" t="n"/>
-      <c r="AC25" s="277" t="n"/>
-      <c r="AD25" s="277" t="n"/>
-      <c r="AE25" s="278" t="n"/>
-      <c r="AF25" s="308" t="n"/>
-      <c r="AG25" s="329" t="n"/>
-      <c r="AH25" s="329" t="n"/>
-      <c r="AI25" s="328" t="n"/>
-      <c r="AJ25" s="308" t="n"/>
-      <c r="AK25" s="329" t="n"/>
-      <c r="AL25" s="328" t="n"/>
-      <c r="AM25" s="308" t="n"/>
-      <c r="AN25" s="328" t="n"/>
+      <c r="U25" s="475" t="n"/>
+      <c r="V25" s="475" t="n"/>
+      <c r="W25" s="475" t="n"/>
+      <c r="X25" s="475" t="n"/>
+      <c r="Y25" s="475" t="n"/>
+      <c r="Z25" s="475" t="n"/>
+      <c r="AA25" s="475" t="n"/>
+      <c r="AB25" s="475" t="n"/>
+      <c r="AC25" s="475" t="n"/>
+      <c r="AD25" s="475" t="n"/>
+      <c r="AE25" s="476" t="n"/>
+      <c r="AF25" s="427" t="n"/>
+      <c r="AG25" s="473" t="n"/>
+      <c r="AH25" s="473" t="n"/>
+      <c r="AI25" s="474" t="n"/>
+      <c r="AJ25" s="427" t="n"/>
+      <c r="AK25" s="473" t="n"/>
+      <c r="AL25" s="474" t="n"/>
+      <c r="AM25" s="427" t="n"/>
+      <c r="AN25" s="474" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="304" t="n">
+      <c r="A26" s="423" t="n">
         <v>5</v>
       </c>
-      <c r="B26" s="328" t="n"/>
-      <c r="C26" s="305" t="inlineStr">
+      <c r="B26" s="474" t="n"/>
+      <c r="C26" s="424" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D26" s="277" t="n"/>
-      <c r="E26" s="278" t="n"/>
-      <c r="F26" s="306" t="inlineStr">
+      <c r="D26" s="475" t="n"/>
+      <c r="E26" s="476" t="n"/>
+      <c r="F26" s="425" t="inlineStr">
         <is>
           <t>First-piece / FAI strategy is defined.</t>
         </is>
       </c>
-      <c r="G26" s="277" t="n"/>
-      <c r="H26" s="277" t="n"/>
-      <c r="I26" s="277" t="n"/>
-      <c r="J26" s="277" t="n"/>
-      <c r="K26" s="277" t="n"/>
-      <c r="L26" s="277" t="n"/>
-      <c r="M26" s="277" t="n"/>
-      <c r="N26" s="277" t="n"/>
-      <c r="O26" s="277" t="n"/>
-      <c r="P26" s="277" t="n"/>
-      <c r="Q26" s="277" t="n"/>
-      <c r="R26" s="277" t="n"/>
-      <c r="S26" s="278" t="n"/>
-      <c r="T26" s="307" t="inlineStr">
+      <c r="G26" s="475" t="n"/>
+      <c r="H26" s="475" t="n"/>
+      <c r="I26" s="475" t="n"/>
+      <c r="J26" s="475" t="n"/>
+      <c r="K26" s="475" t="n"/>
+      <c r="L26" s="475" t="n"/>
+      <c r="M26" s="475" t="n"/>
+      <c r="N26" s="475" t="n"/>
+      <c r="O26" s="475" t="n"/>
+      <c r="P26" s="475" t="n"/>
+      <c r="Q26" s="475" t="n"/>
+      <c r="R26" s="475" t="n"/>
+      <c r="S26" s="476" t="n"/>
+      <c r="T26" s="426" t="inlineStr">
         <is>
           <t>QA gate logic and owner are visible.</t>
         </is>
       </c>
-      <c r="U26" s="277" t="n"/>
-      <c r="V26" s="277" t="n"/>
-      <c r="W26" s="277" t="n"/>
-      <c r="X26" s="277" t="n"/>
-      <c r="Y26" s="277" t="n"/>
-      <c r="Z26" s="277" t="n"/>
-      <c r="AA26" s="277" t="n"/>
-      <c r="AB26" s="277" t="n"/>
-      <c r="AC26" s="277" t="n"/>
-      <c r="AD26" s="277" t="n"/>
-      <c r="AE26" s="278" t="n"/>
-      <c r="AF26" s="308" t="n"/>
-      <c r="AG26" s="329" t="n"/>
-      <c r="AH26" s="329" t="n"/>
-      <c r="AI26" s="328" t="n"/>
-      <c r="AJ26" s="308" t="n"/>
-      <c r="AK26" s="329" t="n"/>
-      <c r="AL26" s="328" t="n"/>
-      <c r="AM26" s="308" t="n"/>
-      <c r="AN26" s="328" t="n"/>
+      <c r="U26" s="475" t="n"/>
+      <c r="V26" s="475" t="n"/>
+      <c r="W26" s="475" t="n"/>
+      <c r="X26" s="475" t="n"/>
+      <c r="Y26" s="475" t="n"/>
+      <c r="Z26" s="475" t="n"/>
+      <c r="AA26" s="475" t="n"/>
+      <c r="AB26" s="475" t="n"/>
+      <c r="AC26" s="475" t="n"/>
+      <c r="AD26" s="475" t="n"/>
+      <c r="AE26" s="476" t="n"/>
+      <c r="AF26" s="427" t="n"/>
+      <c r="AG26" s="473" t="n"/>
+      <c r="AH26" s="473" t="n"/>
+      <c r="AI26" s="474" t="n"/>
+      <c r="AJ26" s="427" t="n"/>
+      <c r="AK26" s="473" t="n"/>
+      <c r="AL26" s="474" t="n"/>
+      <c r="AM26" s="427" t="n"/>
+      <c r="AN26" s="474" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="304" t="n">
+      <c r="A27" s="423" t="n">
         <v>6</v>
       </c>
-      <c r="B27" s="328" t="n"/>
-      <c r="C27" s="305" t="inlineStr">
+      <c r="B27" s="474" t="n"/>
+      <c r="C27" s="424" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D27" s="277" t="n"/>
-      <c r="E27" s="278" t="n"/>
-      <c r="F27" s="309" t="inlineStr">
+      <c r="D27" s="475" t="n"/>
+      <c r="E27" s="476" t="n"/>
+      <c r="F27" s="428" t="inlineStr">
         <is>
           <t>Delivery / ship logic is feasible.</t>
         </is>
       </c>
-      <c r="G27" s="277" t="n"/>
-      <c r="H27" s="277" t="n"/>
-      <c r="I27" s="277" t="n"/>
-      <c r="J27" s="277" t="n"/>
-      <c r="K27" s="277" t="n"/>
-      <c r="L27" s="277" t="n"/>
-      <c r="M27" s="277" t="n"/>
-      <c r="N27" s="277" t="n"/>
-      <c r="O27" s="277" t="n"/>
-      <c r="P27" s="277" t="n"/>
-      <c r="Q27" s="277" t="n"/>
-      <c r="R27" s="277" t="n"/>
-      <c r="S27" s="278" t="n"/>
-      <c r="T27" s="307" t="inlineStr">
+      <c r="G27" s="475" t="n"/>
+      <c r="H27" s="475" t="n"/>
+      <c r="I27" s="475" t="n"/>
+      <c r="J27" s="475" t="n"/>
+      <c r="K27" s="475" t="n"/>
+      <c r="L27" s="475" t="n"/>
+      <c r="M27" s="475" t="n"/>
+      <c r="N27" s="475" t="n"/>
+      <c r="O27" s="475" t="n"/>
+      <c r="P27" s="475" t="n"/>
+      <c r="Q27" s="475" t="n"/>
+      <c r="R27" s="475" t="n"/>
+      <c r="S27" s="476" t="n"/>
+      <c r="T27" s="426" t="inlineStr">
         <is>
           <t>Commitment and ship impact are realistic.</t>
         </is>
       </c>
-      <c r="U27" s="277" t="n"/>
-      <c r="V27" s="277" t="n"/>
-      <c r="W27" s="277" t="n"/>
-      <c r="X27" s="277" t="n"/>
-      <c r="Y27" s="277" t="n"/>
-      <c r="Z27" s="277" t="n"/>
-      <c r="AA27" s="277" t="n"/>
-      <c r="AB27" s="277" t="n"/>
-      <c r="AC27" s="277" t="n"/>
-      <c r="AD27" s="277" t="n"/>
-      <c r="AE27" s="278" t="n"/>
-      <c r="AF27" s="308" t="n"/>
-      <c r="AG27" s="329" t="n"/>
-      <c r="AH27" s="329" t="n"/>
-      <c r="AI27" s="328" t="n"/>
-      <c r="AJ27" s="308" t="n"/>
-      <c r="AK27" s="329" t="n"/>
-      <c r="AL27" s="328" t="n"/>
-      <c r="AM27" s="308" t="n"/>
-      <c r="AN27" s="328" t="n"/>
+      <c r="U27" s="475" t="n"/>
+      <c r="V27" s="475" t="n"/>
+      <c r="W27" s="475" t="n"/>
+      <c r="X27" s="475" t="n"/>
+      <c r="Y27" s="475" t="n"/>
+      <c r="Z27" s="475" t="n"/>
+      <c r="AA27" s="475" t="n"/>
+      <c r="AB27" s="475" t="n"/>
+      <c r="AC27" s="475" t="n"/>
+      <c r="AD27" s="475" t="n"/>
+      <c r="AE27" s="476" t="n"/>
+      <c r="AF27" s="427" t="n"/>
+      <c r="AG27" s="473" t="n"/>
+      <c r="AH27" s="473" t="n"/>
+      <c r="AI27" s="474" t="n"/>
+      <c r="AJ27" s="427" t="n"/>
+      <c r="AK27" s="473" t="n"/>
+      <c r="AL27" s="474" t="n"/>
+      <c r="AM27" s="427" t="n"/>
+      <c r="AN27" s="474" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="304" t="n">
+      <c r="A28" s="423" t="n">
         <v>7</v>
       </c>
-      <c r="B28" s="328" t="n"/>
-      <c r="C28" s="305" t="inlineStr">
+      <c r="B28" s="474" t="n"/>
+      <c r="C28" s="424" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D28" s="277" t="n"/>
-      <c r="E28" s="278" t="n"/>
-      <c r="F28" s="306" t="inlineStr">
+      <c r="D28" s="475" t="n"/>
+      <c r="E28" s="476" t="n"/>
+      <c r="F28" s="425" t="inlineStr">
         <is>
           <t>Top abnormal / failure mode is explicit.</t>
         </is>
       </c>
-      <c r="G28" s="277" t="n"/>
-      <c r="H28" s="277" t="n"/>
-      <c r="I28" s="277" t="n"/>
-      <c r="J28" s="277" t="n"/>
-      <c r="K28" s="277" t="n"/>
-      <c r="L28" s="277" t="n"/>
-      <c r="M28" s="277" t="n"/>
-      <c r="N28" s="277" t="n"/>
-      <c r="O28" s="277" t="n"/>
-      <c r="P28" s="277" t="n"/>
-      <c r="Q28" s="277" t="n"/>
-      <c r="R28" s="277" t="n"/>
-      <c r="S28" s="278" t="n"/>
-      <c r="T28" s="307" t="inlineStr">
+      <c r="G28" s="475" t="n"/>
+      <c r="H28" s="475" t="n"/>
+      <c r="I28" s="475" t="n"/>
+      <c r="J28" s="475" t="n"/>
+      <c r="K28" s="475" t="n"/>
+      <c r="L28" s="475" t="n"/>
+      <c r="M28" s="475" t="n"/>
+      <c r="N28" s="475" t="n"/>
+      <c r="O28" s="475" t="n"/>
+      <c r="P28" s="475" t="n"/>
+      <c r="Q28" s="475" t="n"/>
+      <c r="R28" s="475" t="n"/>
+      <c r="S28" s="476" t="n"/>
+      <c r="T28" s="426" t="inlineStr">
         <is>
           <t>Most severe risk is named, not hidden.</t>
         </is>
       </c>
-      <c r="U28" s="277" t="n"/>
-      <c r="V28" s="277" t="n"/>
-      <c r="W28" s="277" t="n"/>
-      <c r="X28" s="277" t="n"/>
-      <c r="Y28" s="277" t="n"/>
-      <c r="Z28" s="277" t="n"/>
-      <c r="AA28" s="277" t="n"/>
-      <c r="AB28" s="277" t="n"/>
-      <c r="AC28" s="277" t="n"/>
-      <c r="AD28" s="277" t="n"/>
-      <c r="AE28" s="278" t="n"/>
-      <c r="AF28" s="308" t="n"/>
-      <c r="AG28" s="329" t="n"/>
-      <c r="AH28" s="329" t="n"/>
-      <c r="AI28" s="328" t="n"/>
-      <c r="AJ28" s="308" t="n"/>
-      <c r="AK28" s="329" t="n"/>
-      <c r="AL28" s="328" t="n"/>
-      <c r="AM28" s="308" t="n"/>
-      <c r="AN28" s="328" t="n"/>
+      <c r="U28" s="475" t="n"/>
+      <c r="V28" s="475" t="n"/>
+      <c r="W28" s="475" t="n"/>
+      <c r="X28" s="475" t="n"/>
+      <c r="Y28" s="475" t="n"/>
+      <c r="Z28" s="475" t="n"/>
+      <c r="AA28" s="475" t="n"/>
+      <c r="AB28" s="475" t="n"/>
+      <c r="AC28" s="475" t="n"/>
+      <c r="AD28" s="475" t="n"/>
+      <c r="AE28" s="476" t="n"/>
+      <c r="AF28" s="427" t="n"/>
+      <c r="AG28" s="473" t="n"/>
+      <c r="AH28" s="473" t="n"/>
+      <c r="AI28" s="474" t="n"/>
+      <c r="AJ28" s="427" t="n"/>
+      <c r="AK28" s="473" t="n"/>
+      <c r="AL28" s="474" t="n"/>
+      <c r="AM28" s="427" t="n"/>
+      <c r="AN28" s="474" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="304" t="n">
+      <c r="A29" s="423" t="n">
         <v>8</v>
       </c>
-      <c r="B29" s="328" t="n"/>
-      <c r="C29" s="305" t="inlineStr">
+      <c r="B29" s="474" t="n"/>
+      <c r="C29" s="424" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D29" s="277" t="n"/>
-      <c r="E29" s="278" t="n"/>
-      <c r="F29" s="309" t="inlineStr">
+      <c r="D29" s="475" t="n"/>
+      <c r="E29" s="476" t="n"/>
+      <c r="F29" s="428" t="inlineStr">
         <is>
           <t>Containment / contingency exists.</t>
         </is>
       </c>
-      <c r="G29" s="277" t="n"/>
-      <c r="H29" s="277" t="n"/>
-      <c r="I29" s="277" t="n"/>
-      <c r="J29" s="277" t="n"/>
-      <c r="K29" s="277" t="n"/>
-      <c r="L29" s="277" t="n"/>
-      <c r="M29" s="277" t="n"/>
-      <c r="N29" s="277" t="n"/>
-      <c r="O29" s="277" t="n"/>
-      <c r="P29" s="277" t="n"/>
-      <c r="Q29" s="277" t="n"/>
-      <c r="R29" s="277" t="n"/>
-      <c r="S29" s="278" t="n"/>
-      <c r="T29" s="307" t="inlineStr">
+      <c r="G29" s="475" t="n"/>
+      <c r="H29" s="475" t="n"/>
+      <c r="I29" s="475" t="n"/>
+      <c r="J29" s="475" t="n"/>
+      <c r="K29" s="475" t="n"/>
+      <c r="L29" s="475" t="n"/>
+      <c r="M29" s="475" t="n"/>
+      <c r="N29" s="475" t="n"/>
+      <c r="O29" s="475" t="n"/>
+      <c r="P29" s="475" t="n"/>
+      <c r="Q29" s="475" t="n"/>
+      <c r="R29" s="475" t="n"/>
+      <c r="S29" s="476" t="n"/>
+      <c r="T29" s="426" t="inlineStr">
         <is>
           <t>Recovery path exists if primary plan fails.</t>
         </is>
       </c>
-      <c r="U29" s="277" t="n"/>
-      <c r="V29" s="277" t="n"/>
-      <c r="W29" s="277" t="n"/>
-      <c r="X29" s="277" t="n"/>
-      <c r="Y29" s="277" t="n"/>
-      <c r="Z29" s="277" t="n"/>
-      <c r="AA29" s="277" t="n"/>
-      <c r="AB29" s="277" t="n"/>
-      <c r="AC29" s="277" t="n"/>
-      <c r="AD29" s="277" t="n"/>
-      <c r="AE29" s="278" t="n"/>
-      <c r="AF29" s="308" t="n"/>
-      <c r="AG29" s="329" t="n"/>
-      <c r="AH29" s="329" t="n"/>
-      <c r="AI29" s="328" t="n"/>
-      <c r="AJ29" s="308" t="n"/>
-      <c r="AK29" s="329" t="n"/>
-      <c r="AL29" s="328" t="n"/>
-      <c r="AM29" s="308" t="n"/>
-      <c r="AN29" s="328" t="n"/>
+      <c r="U29" s="475" t="n"/>
+      <c r="V29" s="475" t="n"/>
+      <c r="W29" s="475" t="n"/>
+      <c r="X29" s="475" t="n"/>
+      <c r="Y29" s="475" t="n"/>
+      <c r="Z29" s="475" t="n"/>
+      <c r="AA29" s="475" t="n"/>
+      <c r="AB29" s="475" t="n"/>
+      <c r="AC29" s="475" t="n"/>
+      <c r="AD29" s="475" t="n"/>
+      <c r="AE29" s="476" t="n"/>
+      <c r="AF29" s="427" t="n"/>
+      <c r="AG29" s="473" t="n"/>
+      <c r="AH29" s="473" t="n"/>
+      <c r="AI29" s="474" t="n"/>
+      <c r="AJ29" s="427" t="n"/>
+      <c r="AK29" s="473" t="n"/>
+      <c r="AL29" s="474" t="n"/>
+      <c r="AM29" s="427" t="n"/>
+      <c r="AN29" s="474" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="304" t="n">
+      <c r="A30" s="423" t="n">
         <v>9</v>
       </c>
-      <c r="B30" s="328" t="n"/>
-      <c r="C30" s="305" t="inlineStr">
+      <c r="B30" s="474" t="n"/>
+      <c r="C30" s="424" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D30" s="277" t="n"/>
-      <c r="E30" s="278" t="n"/>
-      <c r="F30" s="306" t="inlineStr">
+      <c r="D30" s="475" t="n"/>
+      <c r="E30" s="476" t="n"/>
+      <c r="F30" s="425" t="inlineStr">
         <is>
           <t>Conditional-release authority is explicit.</t>
         </is>
       </c>
-      <c r="G30" s="277" t="n"/>
-      <c r="H30" s="277" t="n"/>
-      <c r="I30" s="277" t="n"/>
-      <c r="J30" s="277" t="n"/>
-      <c r="K30" s="277" t="n"/>
-      <c r="L30" s="277" t="n"/>
-      <c r="M30" s="277" t="n"/>
-      <c r="N30" s="277" t="n"/>
-      <c r="O30" s="277" t="n"/>
-      <c r="P30" s="277" t="n"/>
-      <c r="Q30" s="277" t="n"/>
-      <c r="R30" s="277" t="n"/>
-      <c r="S30" s="278" t="n"/>
-      <c r="T30" s="307" t="inlineStr">
+      <c r="G30" s="475" t="n"/>
+      <c r="H30" s="475" t="n"/>
+      <c r="I30" s="475" t="n"/>
+      <c r="J30" s="475" t="n"/>
+      <c r="K30" s="475" t="n"/>
+      <c r="L30" s="475" t="n"/>
+      <c r="M30" s="475" t="n"/>
+      <c r="N30" s="475" t="n"/>
+      <c r="O30" s="475" t="n"/>
+      <c r="P30" s="475" t="n"/>
+      <c r="Q30" s="475" t="n"/>
+      <c r="R30" s="475" t="n"/>
+      <c r="S30" s="476" t="n"/>
+      <c r="T30" s="426" t="inlineStr">
         <is>
           <t>No conditional release without named owner.</t>
         </is>
       </c>
-      <c r="U30" s="277" t="n"/>
-      <c r="V30" s="277" t="n"/>
-      <c r="W30" s="277" t="n"/>
-      <c r="X30" s="277" t="n"/>
-      <c r="Y30" s="277" t="n"/>
-      <c r="Z30" s="277" t="n"/>
-      <c r="AA30" s="277" t="n"/>
-      <c r="AB30" s="277" t="n"/>
-      <c r="AC30" s="277" t="n"/>
-      <c r="AD30" s="277" t="n"/>
-      <c r="AE30" s="278" t="n"/>
-      <c r="AF30" s="308" t="n"/>
-      <c r="AG30" s="329" t="n"/>
-      <c r="AH30" s="329" t="n"/>
-      <c r="AI30" s="328" t="n"/>
-      <c r="AJ30" s="308" t="n"/>
-      <c r="AK30" s="329" t="n"/>
-      <c r="AL30" s="328" t="n"/>
-      <c r="AM30" s="308" t="n"/>
-      <c r="AN30" s="328" t="n"/>
+      <c r="U30" s="475" t="n"/>
+      <c r="V30" s="475" t="n"/>
+      <c r="W30" s="475" t="n"/>
+      <c r="X30" s="475" t="n"/>
+      <c r="Y30" s="475" t="n"/>
+      <c r="Z30" s="475" t="n"/>
+      <c r="AA30" s="475" t="n"/>
+      <c r="AB30" s="475" t="n"/>
+      <c r="AC30" s="475" t="n"/>
+      <c r="AD30" s="475" t="n"/>
+      <c r="AE30" s="476" t="n"/>
+      <c r="AF30" s="427" t="n"/>
+      <c r="AG30" s="473" t="n"/>
+      <c r="AH30" s="473" t="n"/>
+      <c r="AI30" s="474" t="n"/>
+      <c r="AJ30" s="427" t="n"/>
+      <c r="AK30" s="473" t="n"/>
+      <c r="AL30" s="474" t="n"/>
+      <c r="AM30" s="427" t="n"/>
+      <c r="AN30" s="474" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="304" t="n">
+      <c r="A31" s="423" t="n">
         <v>10</v>
       </c>
-      <c r="B31" s="328" t="n"/>
-      <c r="C31" s="310" t="inlineStr">
+      <c r="B31" s="474" t="n"/>
+      <c r="C31" s="424" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D31" s="283" t="n"/>
-      <c r="E31" s="285" t="n"/>
-      <c r="F31" s="311" t="inlineStr">
+      <c r="D31" s="475" t="n"/>
+      <c r="E31" s="476" t="n"/>
+      <c r="F31" s="428" t="inlineStr">
         <is>
           <t>Evidence path and dossier traceability exist.</t>
         </is>
       </c>
-      <c r="G31" s="283" t="n"/>
-      <c r="H31" s="283" t="n"/>
-      <c r="I31" s="283" t="n"/>
-      <c r="J31" s="283" t="n"/>
-      <c r="K31" s="283" t="n"/>
-      <c r="L31" s="283" t="n"/>
-      <c r="M31" s="283" t="n"/>
-      <c r="N31" s="283" t="n"/>
-      <c r="O31" s="283" t="n"/>
-      <c r="P31" s="283" t="n"/>
-      <c r="Q31" s="283" t="n"/>
-      <c r="R31" s="283" t="n"/>
-      <c r="S31" s="285" t="n"/>
-      <c r="T31" s="312" t="inlineStr">
+      <c r="G31" s="475" t="n"/>
+      <c r="H31" s="475" t="n"/>
+      <c r="I31" s="475" t="n"/>
+      <c r="J31" s="475" t="n"/>
+      <c r="K31" s="475" t="n"/>
+      <c r="L31" s="475" t="n"/>
+      <c r="M31" s="475" t="n"/>
+      <c r="N31" s="475" t="n"/>
+      <c r="O31" s="475" t="n"/>
+      <c r="P31" s="475" t="n"/>
+      <c r="Q31" s="475" t="n"/>
+      <c r="R31" s="475" t="n"/>
+      <c r="S31" s="476" t="n"/>
+      <c r="T31" s="426" t="inlineStr">
         <is>
           <t>Decision can be reconstructed later.</t>
         </is>
       </c>
-      <c r="U31" s="283" t="n"/>
-      <c r="V31" s="283" t="n"/>
-      <c r="W31" s="283" t="n"/>
-      <c r="X31" s="283" t="n"/>
-      <c r="Y31" s="283" t="n"/>
-      <c r="Z31" s="283" t="n"/>
-      <c r="AA31" s="283" t="n"/>
-      <c r="AB31" s="283" t="n"/>
-      <c r="AC31" s="283" t="n"/>
-      <c r="AD31" s="283" t="n"/>
-      <c r="AE31" s="285" t="n"/>
-      <c r="AF31" s="308" t="n"/>
-      <c r="AG31" s="329" t="n"/>
-      <c r="AH31" s="329" t="n"/>
-      <c r="AI31" s="328" t="n"/>
-      <c r="AJ31" s="308" t="n"/>
-      <c r="AK31" s="329" t="n"/>
-      <c r="AL31" s="328" t="n"/>
-      <c r="AM31" s="308" t="n"/>
-      <c r="AN31" s="328" t="n"/>
+      <c r="U31" s="475" t="n"/>
+      <c r="V31" s="475" t="n"/>
+      <c r="W31" s="475" t="n"/>
+      <c r="X31" s="475" t="n"/>
+      <c r="Y31" s="475" t="n"/>
+      <c r="Z31" s="475" t="n"/>
+      <c r="AA31" s="475" t="n"/>
+      <c r="AB31" s="475" t="n"/>
+      <c r="AC31" s="475" t="n"/>
+      <c r="AD31" s="475" t="n"/>
+      <c r="AE31" s="476" t="n"/>
+      <c r="AF31" s="427" t="n"/>
+      <c r="AG31" s="473" t="n"/>
+      <c r="AH31" s="473" t="n"/>
+      <c r="AI31" s="474" t="n"/>
+      <c r="AJ31" s="427" t="n"/>
+      <c r="AK31" s="473" t="n"/>
+      <c r="AL31" s="474" t="n"/>
+      <c r="AM31" s="427" t="n"/>
+      <c r="AN31" s="474" t="n"/>
     </row>
     <row r="32" ht="4" customHeight="1">
-      <c r="A32" s="25" t="n"/>
+      <c r="A32" s="410" t="n"/>
+      <c r="B32" s="482" t="n"/>
+      <c r="C32" s="482" t="n"/>
+      <c r="D32" s="482" t="n"/>
+      <c r="E32" s="482" t="n"/>
+      <c r="F32" s="482" t="n"/>
+      <c r="G32" s="482" t="n"/>
+      <c r="H32" s="482" t="n"/>
+      <c r="I32" s="482" t="n"/>
+      <c r="J32" s="482" t="n"/>
+      <c r="K32" s="482" t="n"/>
+      <c r="L32" s="482" t="n"/>
+      <c r="M32" s="482" t="n"/>
+      <c r="N32" s="482" t="n"/>
+      <c r="O32" s="482" t="n"/>
+      <c r="P32" s="482" t="n"/>
+      <c r="Q32" s="482" t="n"/>
+      <c r="R32" s="482" t="n"/>
+      <c r="S32" s="482" t="n"/>
+      <c r="T32" s="482" t="n"/>
+      <c r="U32" s="482" t="n"/>
+      <c r="V32" s="482" t="n"/>
+      <c r="W32" s="482" t="n"/>
+      <c r="X32" s="482" t="n"/>
+      <c r="Y32" s="482" t="n"/>
+      <c r="Z32" s="482" t="n"/>
+      <c r="AA32" s="482" t="n"/>
+      <c r="AB32" s="482" t="n"/>
+      <c r="AC32" s="482" t="n"/>
+      <c r="AD32" s="482" t="n"/>
+      <c r="AE32" s="482" t="n"/>
+      <c r="AF32" s="482" t="n"/>
+      <c r="AG32" s="482" t="n"/>
+      <c r="AH32" s="482" t="n"/>
+      <c r="AI32" s="482" t="n"/>
+      <c r="AJ32" s="482" t="n"/>
+      <c r="AK32" s="482" t="n"/>
+      <c r="AL32" s="482" t="n"/>
+      <c r="AM32" s="482" t="n"/>
+      <c r="AN32" s="482" t="n"/>
     </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="288" t="inlineStr">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="411" t="inlineStr">
         <is>
           <t>4.  OPEN RISK ACTIONS / CONTAINMENT</t>
         </is>
       </c>
-      <c r="B33" s="289" t="n"/>
-      <c r="C33" s="289" t="n"/>
-      <c r="D33" s="289" t="n"/>
-      <c r="E33" s="289" t="n"/>
-      <c r="F33" s="289" t="n"/>
-      <c r="G33" s="289" t="n"/>
-      <c r="H33" s="289" t="n"/>
-      <c r="I33" s="289" t="n"/>
-      <c r="J33" s="289" t="n"/>
-      <c r="K33" s="289" t="n"/>
-      <c r="L33" s="289" t="n"/>
-      <c r="M33" s="289" t="n"/>
-      <c r="N33" s="289" t="n"/>
-      <c r="O33" s="289" t="n"/>
-      <c r="P33" s="289" t="n"/>
-      <c r="Q33" s="289" t="n"/>
-      <c r="R33" s="289" t="n"/>
-      <c r="S33" s="289" t="n"/>
-      <c r="T33" s="289" t="n"/>
-      <c r="U33" s="289" t="n"/>
-      <c r="V33" s="289" t="n"/>
-      <c r="W33" s="289" t="n"/>
-      <c r="X33" s="289" t="n"/>
-      <c r="Y33" s="289" t="n"/>
-      <c r="Z33" s="289" t="n"/>
-      <c r="AA33" s="289" t="n"/>
-      <c r="AB33" s="289" t="n"/>
-      <c r="AC33" s="289" t="n"/>
-      <c r="AD33" s="289" t="n"/>
-      <c r="AE33" s="289" t="n"/>
-      <c r="AF33" s="289" t="n"/>
-      <c r="AG33" s="289" t="n"/>
-      <c r="AH33" s="289" t="n"/>
-      <c r="AI33" s="289" t="n"/>
-      <c r="AJ33" s="289" t="n"/>
-      <c r="AK33" s="289" t="n"/>
-      <c r="AL33" s="289" t="n"/>
-      <c r="AM33" s="289" t="n"/>
-      <c r="AN33" s="290" t="n"/>
+      <c r="B33" s="473" t="n"/>
+      <c r="C33" s="473" t="n"/>
+      <c r="D33" s="473" t="n"/>
+      <c r="E33" s="473" t="n"/>
+      <c r="F33" s="473" t="n"/>
+      <c r="G33" s="473" t="n"/>
+      <c r="H33" s="473" t="n"/>
+      <c r="I33" s="473" t="n"/>
+      <c r="J33" s="473" t="n"/>
+      <c r="K33" s="473" t="n"/>
+      <c r="L33" s="473" t="n"/>
+      <c r="M33" s="473" t="n"/>
+      <c r="N33" s="473" t="n"/>
+      <c r="O33" s="473" t="n"/>
+      <c r="P33" s="473" t="n"/>
+      <c r="Q33" s="473" t="n"/>
+      <c r="R33" s="473" t="n"/>
+      <c r="S33" s="473" t="n"/>
+      <c r="T33" s="473" t="n"/>
+      <c r="U33" s="473" t="n"/>
+      <c r="V33" s="473" t="n"/>
+      <c r="W33" s="473" t="n"/>
+      <c r="X33" s="473" t="n"/>
+      <c r="Y33" s="473" t="n"/>
+      <c r="Z33" s="473" t="n"/>
+      <c r="AA33" s="473" t="n"/>
+      <c r="AB33" s="473" t="n"/>
+      <c r="AC33" s="473" t="n"/>
+      <c r="AD33" s="473" t="n"/>
+      <c r="AE33" s="473" t="n"/>
+      <c r="AF33" s="473" t="n"/>
+      <c r="AG33" s="473" t="n"/>
+      <c r="AH33" s="473" t="n"/>
+      <c r="AI33" s="473" t="n"/>
+      <c r="AJ33" s="473" t="n"/>
+      <c r="AK33" s="473" t="n"/>
+      <c r="AL33" s="473" t="n"/>
+      <c r="AM33" s="473" t="n"/>
+      <c r="AN33" s="474" t="n"/>
     </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="301" t="inlineStr">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="421" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B34" s="272" t="n"/>
-      <c r="C34" s="302" t="inlineStr">
+      <c r="B34" s="474" t="n"/>
+      <c r="C34" s="422" t="inlineStr">
         <is>
           <t>Risk / Readiness Gap</t>
         </is>
       </c>
-      <c r="D34" s="271" t="n"/>
-      <c r="E34" s="271" t="n"/>
-      <c r="F34" s="271" t="n"/>
-      <c r="G34" s="271" t="n"/>
-      <c r="H34" s="271" t="n"/>
-      <c r="I34" s="271" t="n"/>
-      <c r="J34" s="271" t="n"/>
-      <c r="K34" s="271" t="n"/>
-      <c r="L34" s="272" t="n"/>
-      <c r="M34" s="302" t="inlineStr">
+      <c r="D34" s="473" t="n"/>
+      <c r="E34" s="473" t="n"/>
+      <c r="F34" s="473" t="n"/>
+      <c r="G34" s="473" t="n"/>
+      <c r="H34" s="473" t="n"/>
+      <c r="I34" s="473" t="n"/>
+      <c r="J34" s="473" t="n"/>
+      <c r="K34" s="473" t="n"/>
+      <c r="L34" s="474" t="n"/>
+      <c r="M34" s="422" t="inlineStr">
         <is>
           <t>Required Containment / Action</t>
         </is>
       </c>
-      <c r="N34" s="271" t="n"/>
-      <c r="O34" s="271" t="n"/>
-      <c r="P34" s="271" t="n"/>
-      <c r="Q34" s="271" t="n"/>
-      <c r="R34" s="271" t="n"/>
-      <c r="S34" s="271" t="n"/>
-      <c r="T34" s="271" t="n"/>
-      <c r="U34" s="271" t="n"/>
-      <c r="V34" s="271" t="n"/>
-      <c r="W34" s="271" t="n"/>
-      <c r="X34" s="272" t="n"/>
-      <c r="Y34" s="302" t="inlineStr">
+      <c r="N34" s="473" t="n"/>
+      <c r="O34" s="473" t="n"/>
+      <c r="P34" s="473" t="n"/>
+      <c r="Q34" s="473" t="n"/>
+      <c r="R34" s="473" t="n"/>
+      <c r="S34" s="473" t="n"/>
+      <c r="T34" s="473" t="n"/>
+      <c r="U34" s="473" t="n"/>
+      <c r="V34" s="473" t="n"/>
+      <c r="W34" s="473" t="n"/>
+      <c r="X34" s="474" t="n"/>
+      <c r="Y34" s="422" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="Z34" s="271" t="n"/>
-      <c r="AA34" s="271" t="n"/>
-      <c r="AB34" s="271" t="n"/>
-      <c r="AC34" s="272" t="n"/>
-      <c r="AD34" s="302" t="inlineStr">
+      <c r="Z34" s="473" t="n"/>
+      <c r="AA34" s="473" t="n"/>
+      <c r="AB34" s="473" t="n"/>
+      <c r="AC34" s="474" t="n"/>
+      <c r="AD34" s="422" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="AE34" s="271" t="n"/>
-      <c r="AF34" s="271" t="n"/>
-      <c r="AG34" s="271" t="n"/>
-      <c r="AH34" s="272" t="n"/>
-      <c r="AI34" s="302" t="inlineStr">
+      <c r="AE34" s="473" t="n"/>
+      <c r="AF34" s="473" t="n"/>
+      <c r="AG34" s="473" t="n"/>
+      <c r="AH34" s="474" t="n"/>
+      <c r="AI34" s="422" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AJ34" s="271" t="n"/>
-      <c r="AK34" s="272" t="n"/>
-      <c r="AL34" s="303" t="inlineStr">
+      <c r="AJ34" s="473" t="n"/>
+      <c r="AK34" s="474" t="n"/>
+      <c r="AL34" s="422" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="AM34" s="271" t="n"/>
-      <c r="AN34" s="274" t="n"/>
+      <c r="AM34" s="473" t="n"/>
+      <c r="AN34" s="474" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="313" t="n">
+      <c r="A35" s="429" t="n">
         <v>1</v>
       </c>
-      <c r="B35" s="278" t="n"/>
-      <c r="C35" s="308" t="n"/>
-      <c r="D35" s="329" t="n"/>
-      <c r="E35" s="329" t="n"/>
-      <c r="F35" s="329" t="n"/>
-      <c r="G35" s="329" t="n"/>
-      <c r="H35" s="329" t="n"/>
-      <c r="I35" s="329" t="n"/>
-      <c r="J35" s="329" t="n"/>
-      <c r="K35" s="329" t="n"/>
-      <c r="L35" s="328" t="n"/>
-      <c r="M35" s="308" t="n"/>
-      <c r="N35" s="329" t="n"/>
-      <c r="O35" s="329" t="n"/>
-      <c r="P35" s="329" t="n"/>
-      <c r="Q35" s="329" t="n"/>
-      <c r="R35" s="329" t="n"/>
-      <c r="S35" s="329" t="n"/>
-      <c r="T35" s="329" t="n"/>
-      <c r="U35" s="329" t="n"/>
-      <c r="V35" s="329" t="n"/>
-      <c r="W35" s="329" t="n"/>
-      <c r="X35" s="328" t="n"/>
-      <c r="Y35" s="308" t="n"/>
-      <c r="Z35" s="329" t="n"/>
-      <c r="AA35" s="329" t="n"/>
-      <c r="AB35" s="329" t="n"/>
-      <c r="AC35" s="328" t="n"/>
-      <c r="AD35" s="308" t="n"/>
-      <c r="AE35" s="329" t="n"/>
-      <c r="AF35" s="329" t="n"/>
-      <c r="AG35" s="329" t="n"/>
-      <c r="AH35" s="328" t="n"/>
-      <c r="AI35" s="308" t="n"/>
-      <c r="AJ35" s="329" t="n"/>
-      <c r="AK35" s="328" t="n"/>
-      <c r="AL35" s="308" t="n"/>
-      <c r="AM35" s="329" t="n"/>
-      <c r="AN35" s="328" t="n"/>
+      <c r="B35" s="476" t="n"/>
+      <c r="C35" s="427" t="n"/>
+      <c r="D35" s="473" t="n"/>
+      <c r="E35" s="473" t="n"/>
+      <c r="F35" s="473" t="n"/>
+      <c r="G35" s="473" t="n"/>
+      <c r="H35" s="473" t="n"/>
+      <c r="I35" s="473" t="n"/>
+      <c r="J35" s="473" t="n"/>
+      <c r="K35" s="473" t="n"/>
+      <c r="L35" s="474" t="n"/>
+      <c r="M35" s="427" t="n"/>
+      <c r="N35" s="473" t="n"/>
+      <c r="O35" s="473" t="n"/>
+      <c r="P35" s="473" t="n"/>
+      <c r="Q35" s="473" t="n"/>
+      <c r="R35" s="473" t="n"/>
+      <c r="S35" s="473" t="n"/>
+      <c r="T35" s="473" t="n"/>
+      <c r="U35" s="473" t="n"/>
+      <c r="V35" s="473" t="n"/>
+      <c r="W35" s="473" t="n"/>
+      <c r="X35" s="474" t="n"/>
+      <c r="Y35" s="427" t="n"/>
+      <c r="Z35" s="473" t="n"/>
+      <c r="AA35" s="473" t="n"/>
+      <c r="AB35" s="473" t="n"/>
+      <c r="AC35" s="474" t="n"/>
+      <c r="AD35" s="427" t="n"/>
+      <c r="AE35" s="473" t="n"/>
+      <c r="AF35" s="473" t="n"/>
+      <c r="AG35" s="473" t="n"/>
+      <c r="AH35" s="474" t="n"/>
+      <c r="AI35" s="427" t="n"/>
+      <c r="AJ35" s="473" t="n"/>
+      <c r="AK35" s="474" t="n"/>
+      <c r="AL35" s="427" t="n"/>
+      <c r="AM35" s="473" t="n"/>
+      <c r="AN35" s="474" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="313" t="n">
+      <c r="A36" s="429" t="n">
         <v>2</v>
       </c>
-      <c r="B36" s="278" t="n"/>
-      <c r="C36" s="308" t="n"/>
-      <c r="D36" s="329" t="n"/>
-      <c r="E36" s="329" t="n"/>
-      <c r="F36" s="329" t="n"/>
-      <c r="G36" s="329" t="n"/>
-      <c r="H36" s="329" t="n"/>
-      <c r="I36" s="329" t="n"/>
-      <c r="J36" s="329" t="n"/>
-      <c r="K36" s="329" t="n"/>
-      <c r="L36" s="328" t="n"/>
-      <c r="M36" s="308" t="n"/>
-      <c r="N36" s="329" t="n"/>
-      <c r="O36" s="329" t="n"/>
-      <c r="P36" s="329" t="n"/>
-      <c r="Q36" s="329" t="n"/>
-      <c r="R36" s="329" t="n"/>
-      <c r="S36" s="329" t="n"/>
-      <c r="T36" s="329" t="n"/>
-      <c r="U36" s="329" t="n"/>
-      <c r="V36" s="329" t="n"/>
-      <c r="W36" s="329" t="n"/>
-      <c r="X36" s="328" t="n"/>
-      <c r="Y36" s="308" t="n"/>
-      <c r="Z36" s="329" t="n"/>
-      <c r="AA36" s="329" t="n"/>
-      <c r="AB36" s="329" t="n"/>
-      <c r="AC36" s="328" t="n"/>
-      <c r="AD36" s="308" t="n"/>
-      <c r="AE36" s="329" t="n"/>
-      <c r="AF36" s="329" t="n"/>
-      <c r="AG36" s="329" t="n"/>
-      <c r="AH36" s="328" t="n"/>
-      <c r="AI36" s="308" t="n"/>
-      <c r="AJ36" s="329" t="n"/>
-      <c r="AK36" s="328" t="n"/>
-      <c r="AL36" s="308" t="n"/>
-      <c r="AM36" s="329" t="n"/>
-      <c r="AN36" s="328" t="n"/>
+      <c r="B36" s="476" t="n"/>
+      <c r="C36" s="427" t="n"/>
+      <c r="D36" s="473" t="n"/>
+      <c r="E36" s="473" t="n"/>
+      <c r="F36" s="473" t="n"/>
+      <c r="G36" s="473" t="n"/>
+      <c r="H36" s="473" t="n"/>
+      <c r="I36" s="473" t="n"/>
+      <c r="J36" s="473" t="n"/>
+      <c r="K36" s="473" t="n"/>
+      <c r="L36" s="474" t="n"/>
+      <c r="M36" s="427" t="n"/>
+      <c r="N36" s="473" t="n"/>
+      <c r="O36" s="473" t="n"/>
+      <c r="P36" s="473" t="n"/>
+      <c r="Q36" s="473" t="n"/>
+      <c r="R36" s="473" t="n"/>
+      <c r="S36" s="473" t="n"/>
+      <c r="T36" s="473" t="n"/>
+      <c r="U36" s="473" t="n"/>
+      <c r="V36" s="473" t="n"/>
+      <c r="W36" s="473" t="n"/>
+      <c r="X36" s="474" t="n"/>
+      <c r="Y36" s="427" t="n"/>
+      <c r="Z36" s="473" t="n"/>
+      <c r="AA36" s="473" t="n"/>
+      <c r="AB36" s="473" t="n"/>
+      <c r="AC36" s="474" t="n"/>
+      <c r="AD36" s="427" t="n"/>
+      <c r="AE36" s="473" t="n"/>
+      <c r="AF36" s="473" t="n"/>
+      <c r="AG36" s="473" t="n"/>
+      <c r="AH36" s="474" t="n"/>
+      <c r="AI36" s="427" t="n"/>
+      <c r="AJ36" s="473" t="n"/>
+      <c r="AK36" s="474" t="n"/>
+      <c r="AL36" s="427" t="n"/>
+      <c r="AM36" s="473" t="n"/>
+      <c r="AN36" s="474" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="313" t="n">
+      <c r="A37" s="429" t="n">
         <v>3</v>
       </c>
-      <c r="B37" s="278" t="n"/>
-      <c r="C37" s="308" t="n"/>
-      <c r="D37" s="329" t="n"/>
-      <c r="E37" s="329" t="n"/>
-      <c r="F37" s="329" t="n"/>
-      <c r="G37" s="329" t="n"/>
-      <c r="H37" s="329" t="n"/>
-      <c r="I37" s="329" t="n"/>
-      <c r="J37" s="329" t="n"/>
-      <c r="K37" s="329" t="n"/>
-      <c r="L37" s="328" t="n"/>
-      <c r="M37" s="308" t="n"/>
-      <c r="N37" s="329" t="n"/>
-      <c r="O37" s="329" t="n"/>
-      <c r="P37" s="329" t="n"/>
-      <c r="Q37" s="329" t="n"/>
-      <c r="R37" s="329" t="n"/>
-      <c r="S37" s="329" t="n"/>
-      <c r="T37" s="329" t="n"/>
-      <c r="U37" s="329" t="n"/>
-      <c r="V37" s="329" t="n"/>
-      <c r="W37" s="329" t="n"/>
-      <c r="X37" s="328" t="n"/>
-      <c r="Y37" s="308" t="n"/>
-      <c r="Z37" s="329" t="n"/>
-      <c r="AA37" s="329" t="n"/>
-      <c r="AB37" s="329" t="n"/>
-      <c r="AC37" s="328" t="n"/>
-      <c r="AD37" s="308" t="n"/>
-      <c r="AE37" s="329" t="n"/>
-      <c r="AF37" s="329" t="n"/>
-      <c r="AG37" s="329" t="n"/>
-      <c r="AH37" s="328" t="n"/>
-      <c r="AI37" s="308" t="n"/>
-      <c r="AJ37" s="329" t="n"/>
-      <c r="AK37" s="328" t="n"/>
-      <c r="AL37" s="308" t="n"/>
-      <c r="AM37" s="329" t="n"/>
-      <c r="AN37" s="328" t="n"/>
+      <c r="B37" s="476" t="n"/>
+      <c r="C37" s="427" t="n"/>
+      <c r="D37" s="473" t="n"/>
+      <c r="E37" s="473" t="n"/>
+      <c r="F37" s="473" t="n"/>
+      <c r="G37" s="473" t="n"/>
+      <c r="H37" s="473" t="n"/>
+      <c r="I37" s="473" t="n"/>
+      <c r="J37" s="473" t="n"/>
+      <c r="K37" s="473" t="n"/>
+      <c r="L37" s="474" t="n"/>
+      <c r="M37" s="427" t="n"/>
+      <c r="N37" s="473" t="n"/>
+      <c r="O37" s="473" t="n"/>
+      <c r="P37" s="473" t="n"/>
+      <c r="Q37" s="473" t="n"/>
+      <c r="R37" s="473" t="n"/>
+      <c r="S37" s="473" t="n"/>
+      <c r="T37" s="473" t="n"/>
+      <c r="U37" s="473" t="n"/>
+      <c r="V37" s="473" t="n"/>
+      <c r="W37" s="473" t="n"/>
+      <c r="X37" s="474" t="n"/>
+      <c r="Y37" s="427" t="n"/>
+      <c r="Z37" s="473" t="n"/>
+      <c r="AA37" s="473" t="n"/>
+      <c r="AB37" s="473" t="n"/>
+      <c r="AC37" s="474" t="n"/>
+      <c r="AD37" s="427" t="n"/>
+      <c r="AE37" s="473" t="n"/>
+      <c r="AF37" s="473" t="n"/>
+      <c r="AG37" s="473" t="n"/>
+      <c r="AH37" s="474" t="n"/>
+      <c r="AI37" s="427" t="n"/>
+      <c r="AJ37" s="473" t="n"/>
+      <c r="AK37" s="474" t="n"/>
+      <c r="AL37" s="427" t="n"/>
+      <c r="AM37" s="473" t="n"/>
+      <c r="AN37" s="474" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="313" t="n">
+      <c r="A38" s="429" t="n">
         <v>4</v>
       </c>
-      <c r="B38" s="278" t="n"/>
-      <c r="C38" s="308" t="n"/>
-      <c r="D38" s="329" t="n"/>
-      <c r="E38" s="329" t="n"/>
-      <c r="F38" s="329" t="n"/>
-      <c r="G38" s="329" t="n"/>
-      <c r="H38" s="329" t="n"/>
-      <c r="I38" s="329" t="n"/>
-      <c r="J38" s="329" t="n"/>
-      <c r="K38" s="329" t="n"/>
-      <c r="L38" s="328" t="n"/>
-      <c r="M38" s="308" t="n"/>
-      <c r="N38" s="329" t="n"/>
-      <c r="O38" s="329" t="n"/>
-      <c r="P38" s="329" t="n"/>
-      <c r="Q38" s="329" t="n"/>
-      <c r="R38" s="329" t="n"/>
-      <c r="S38" s="329" t="n"/>
-      <c r="T38" s="329" t="n"/>
-      <c r="U38" s="329" t="n"/>
-      <c r="V38" s="329" t="n"/>
-      <c r="W38" s="329" t="n"/>
-      <c r="X38" s="328" t="n"/>
-      <c r="Y38" s="308" t="n"/>
-      <c r="Z38" s="329" t="n"/>
-      <c r="AA38" s="329" t="n"/>
-      <c r="AB38" s="329" t="n"/>
-      <c r="AC38" s="328" t="n"/>
-      <c r="AD38" s="308" t="n"/>
-      <c r="AE38" s="329" t="n"/>
-      <c r="AF38" s="329" t="n"/>
-      <c r="AG38" s="329" t="n"/>
-      <c r="AH38" s="328" t="n"/>
-      <c r="AI38" s="308" t="n"/>
-      <c r="AJ38" s="329" t="n"/>
-      <c r="AK38" s="328" t="n"/>
-      <c r="AL38" s="308" t="n"/>
-      <c r="AM38" s="329" t="n"/>
-      <c r="AN38" s="328" t="n"/>
+      <c r="B38" s="476" t="n"/>
+      <c r="C38" s="427" t="n"/>
+      <c r="D38" s="473" t="n"/>
+      <c r="E38" s="473" t="n"/>
+      <c r="F38" s="473" t="n"/>
+      <c r="G38" s="473" t="n"/>
+      <c r="H38" s="473" t="n"/>
+      <c r="I38" s="473" t="n"/>
+      <c r="J38" s="473" t="n"/>
+      <c r="K38" s="473" t="n"/>
+      <c r="L38" s="474" t="n"/>
+      <c r="M38" s="427" t="n"/>
+      <c r="N38" s="473" t="n"/>
+      <c r="O38" s="473" t="n"/>
+      <c r="P38" s="473" t="n"/>
+      <c r="Q38" s="473" t="n"/>
+      <c r="R38" s="473" t="n"/>
+      <c r="S38" s="473" t="n"/>
+      <c r="T38" s="473" t="n"/>
+      <c r="U38" s="473" t="n"/>
+      <c r="V38" s="473" t="n"/>
+      <c r="W38" s="473" t="n"/>
+      <c r="X38" s="474" t="n"/>
+      <c r="Y38" s="427" t="n"/>
+      <c r="Z38" s="473" t="n"/>
+      <c r="AA38" s="473" t="n"/>
+      <c r="AB38" s="473" t="n"/>
+      <c r="AC38" s="474" t="n"/>
+      <c r="AD38" s="427" t="n"/>
+      <c r="AE38" s="473" t="n"/>
+      <c r="AF38" s="473" t="n"/>
+      <c r="AG38" s="473" t="n"/>
+      <c r="AH38" s="474" t="n"/>
+      <c r="AI38" s="427" t="n"/>
+      <c r="AJ38" s="473" t="n"/>
+      <c r="AK38" s="474" t="n"/>
+      <c r="AL38" s="427" t="n"/>
+      <c r="AM38" s="473" t="n"/>
+      <c r="AN38" s="474" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="314" t="n">
+      <c r="A39" s="429" t="n">
         <v>5</v>
       </c>
-      <c r="B39" s="285" t="n"/>
-      <c r="C39" s="308" t="n"/>
-      <c r="D39" s="329" t="n"/>
-      <c r="E39" s="329" t="n"/>
-      <c r="F39" s="329" t="n"/>
-      <c r="G39" s="329" t="n"/>
-      <c r="H39" s="329" t="n"/>
-      <c r="I39" s="329" t="n"/>
-      <c r="J39" s="329" t="n"/>
-      <c r="K39" s="329" t="n"/>
-      <c r="L39" s="328" t="n"/>
-      <c r="M39" s="308" t="n"/>
-      <c r="N39" s="329" t="n"/>
-      <c r="O39" s="329" t="n"/>
-      <c r="P39" s="329" t="n"/>
-      <c r="Q39" s="329" t="n"/>
-      <c r="R39" s="329" t="n"/>
-      <c r="S39" s="329" t="n"/>
-      <c r="T39" s="329" t="n"/>
-      <c r="U39" s="329" t="n"/>
-      <c r="V39" s="329" t="n"/>
-      <c r="W39" s="329" t="n"/>
-      <c r="X39" s="328" t="n"/>
-      <c r="Y39" s="308" t="n"/>
-      <c r="Z39" s="329" t="n"/>
-      <c r="AA39" s="329" t="n"/>
-      <c r="AB39" s="329" t="n"/>
-      <c r="AC39" s="328" t="n"/>
-      <c r="AD39" s="308" t="n"/>
-      <c r="AE39" s="329" t="n"/>
-      <c r="AF39" s="329" t="n"/>
-      <c r="AG39" s="329" t="n"/>
-      <c r="AH39" s="328" t="n"/>
-      <c r="AI39" s="308" t="n"/>
-      <c r="AJ39" s="329" t="n"/>
-      <c r="AK39" s="328" t="n"/>
-      <c r="AL39" s="308" t="n"/>
-      <c r="AM39" s="329" t="n"/>
-      <c r="AN39" s="328" t="n"/>
+      <c r="B39" s="476" t="n"/>
+      <c r="C39" s="427" t="n"/>
+      <c r="D39" s="473" t="n"/>
+      <c r="E39" s="473" t="n"/>
+      <c r="F39" s="473" t="n"/>
+      <c r="G39" s="473" t="n"/>
+      <c r="H39" s="473" t="n"/>
+      <c r="I39" s="473" t="n"/>
+      <c r="J39" s="473" t="n"/>
+      <c r="K39" s="473" t="n"/>
+      <c r="L39" s="474" t="n"/>
+      <c r="M39" s="427" t="n"/>
+      <c r="N39" s="473" t="n"/>
+      <c r="O39" s="473" t="n"/>
+      <c r="P39" s="473" t="n"/>
+      <c r="Q39" s="473" t="n"/>
+      <c r="R39" s="473" t="n"/>
+      <c r="S39" s="473" t="n"/>
+      <c r="T39" s="473" t="n"/>
+      <c r="U39" s="473" t="n"/>
+      <c r="V39" s="473" t="n"/>
+      <c r="W39" s="473" t="n"/>
+      <c r="X39" s="474" t="n"/>
+      <c r="Y39" s="427" t="n"/>
+      <c r="Z39" s="473" t="n"/>
+      <c r="AA39" s="473" t="n"/>
+      <c r="AB39" s="473" t="n"/>
+      <c r="AC39" s="474" t="n"/>
+      <c r="AD39" s="427" t="n"/>
+      <c r="AE39" s="473" t="n"/>
+      <c r="AF39" s="473" t="n"/>
+      <c r="AG39" s="473" t="n"/>
+      <c r="AH39" s="474" t="n"/>
+      <c r="AI39" s="427" t="n"/>
+      <c r="AJ39" s="473" t="n"/>
+      <c r="AK39" s="474" t="n"/>
+      <c r="AL39" s="427" t="n"/>
+      <c r="AM39" s="473" t="n"/>
+      <c r="AN39" s="474" t="n"/>
     </row>
     <row r="40" ht="4" customHeight="1">
-      <c r="A40" s="25" t="n"/>
+      <c r="A40" s="410" t="n"/>
+      <c r="B40" s="482" t="n"/>
+      <c r="C40" s="482" t="n"/>
+      <c r="D40" s="482" t="n"/>
+      <c r="E40" s="482" t="n"/>
+      <c r="F40" s="482" t="n"/>
+      <c r="G40" s="482" t="n"/>
+      <c r="H40" s="482" t="n"/>
+      <c r="I40" s="482" t="n"/>
+      <c r="J40" s="482" t="n"/>
+      <c r="K40" s="482" t="n"/>
+      <c r="L40" s="482" t="n"/>
+      <c r="M40" s="482" t="n"/>
+      <c r="N40" s="482" t="n"/>
+      <c r="O40" s="482" t="n"/>
+      <c r="P40" s="482" t="n"/>
+      <c r="Q40" s="482" t="n"/>
+      <c r="R40" s="482" t="n"/>
+      <c r="S40" s="482" t="n"/>
+      <c r="T40" s="482" t="n"/>
+      <c r="U40" s="482" t="n"/>
+      <c r="V40" s="482" t="n"/>
+      <c r="W40" s="482" t="n"/>
+      <c r="X40" s="482" t="n"/>
+      <c r="Y40" s="482" t="n"/>
+      <c r="Z40" s="482" t="n"/>
+      <c r="AA40" s="482" t="n"/>
+      <c r="AB40" s="482" t="n"/>
+      <c r="AC40" s="482" t="n"/>
+      <c r="AD40" s="482" t="n"/>
+      <c r="AE40" s="482" t="n"/>
+      <c r="AF40" s="482" t="n"/>
+      <c r="AG40" s="482" t="n"/>
+      <c r="AH40" s="482" t="n"/>
+      <c r="AI40" s="482" t="n"/>
+      <c r="AJ40" s="482" t="n"/>
+      <c r="AK40" s="482" t="n"/>
+      <c r="AL40" s="482" t="n"/>
+      <c r="AM40" s="482" t="n"/>
+      <c r="AN40" s="482" t="n"/>
     </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="288" t="inlineStr">
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="411" t="inlineStr">
         <is>
           <t>5.  APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B41" s="289" t="n"/>
-      <c r="C41" s="289" t="n"/>
-      <c r="D41" s="289" t="n"/>
-      <c r="E41" s="289" t="n"/>
-      <c r="F41" s="289" t="n"/>
-      <c r="G41" s="289" t="n"/>
-      <c r="H41" s="289" t="n"/>
-      <c r="I41" s="289" t="n"/>
-      <c r="J41" s="289" t="n"/>
-      <c r="K41" s="289" t="n"/>
-      <c r="L41" s="289" t="n"/>
-      <c r="M41" s="289" t="n"/>
-      <c r="N41" s="289" t="n"/>
-      <c r="O41" s="289" t="n"/>
-      <c r="P41" s="289" t="n"/>
-      <c r="Q41" s="289" t="n"/>
-      <c r="R41" s="289" t="n"/>
-      <c r="S41" s="289" t="n"/>
-      <c r="T41" s="289" t="n"/>
-      <c r="U41" s="289" t="n"/>
-      <c r="V41" s="289" t="n"/>
-      <c r="W41" s="289" t="n"/>
-      <c r="X41" s="289" t="n"/>
-      <c r="Y41" s="289" t="n"/>
-      <c r="Z41" s="289" t="n"/>
-      <c r="AA41" s="289" t="n"/>
-      <c r="AB41" s="289" t="n"/>
-      <c r="AC41" s="289" t="n"/>
-      <c r="AD41" s="289" t="n"/>
-      <c r="AE41" s="289" t="n"/>
-      <c r="AF41" s="289" t="n"/>
-      <c r="AG41" s="289" t="n"/>
-      <c r="AH41" s="289" t="n"/>
-      <c r="AI41" s="289" t="n"/>
-      <c r="AJ41" s="289" t="n"/>
-      <c r="AK41" s="289" t="n"/>
-      <c r="AL41" s="289" t="n"/>
-      <c r="AM41" s="289" t="n"/>
-      <c r="AN41" s="290" t="n"/>
+      <c r="B41" s="473" t="n"/>
+      <c r="C41" s="473" t="n"/>
+      <c r="D41" s="473" t="n"/>
+      <c r="E41" s="473" t="n"/>
+      <c r="F41" s="473" t="n"/>
+      <c r="G41" s="473" t="n"/>
+      <c r="H41" s="473" t="n"/>
+      <c r="I41" s="473" t="n"/>
+      <c r="J41" s="473" t="n"/>
+      <c r="K41" s="473" t="n"/>
+      <c r="L41" s="473" t="n"/>
+      <c r="M41" s="473" t="n"/>
+      <c r="N41" s="473" t="n"/>
+      <c r="O41" s="473" t="n"/>
+      <c r="P41" s="473" t="n"/>
+      <c r="Q41" s="473" t="n"/>
+      <c r="R41" s="473" t="n"/>
+      <c r="S41" s="473" t="n"/>
+      <c r="T41" s="473" t="n"/>
+      <c r="U41" s="473" t="n"/>
+      <c r="V41" s="473" t="n"/>
+      <c r="W41" s="473" t="n"/>
+      <c r="X41" s="473" t="n"/>
+      <c r="Y41" s="473" t="n"/>
+      <c r="Z41" s="473" t="n"/>
+      <c r="AA41" s="473" t="n"/>
+      <c r="AB41" s="473" t="n"/>
+      <c r="AC41" s="473" t="n"/>
+      <c r="AD41" s="473" t="n"/>
+      <c r="AE41" s="473" t="n"/>
+      <c r="AF41" s="473" t="n"/>
+      <c r="AG41" s="473" t="n"/>
+      <c r="AH41" s="473" t="n"/>
+      <c r="AI41" s="473" t="n"/>
+      <c r="AJ41" s="473" t="n"/>
+      <c r="AK41" s="473" t="n"/>
+      <c r="AL41" s="473" t="n"/>
+      <c r="AM41" s="473" t="n"/>
+      <c r="AN41" s="474" t="n"/>
     </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="315" t="inlineStr">
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="430" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B42" s="289" t="n"/>
-      <c r="C42" s="289" t="n"/>
-      <c r="D42" s="289" t="n"/>
-      <c r="E42" s="289" t="n"/>
-      <c r="F42" s="289" t="n"/>
-      <c r="G42" s="289" t="n"/>
-      <c r="H42" s="289" t="n"/>
-      <c r="I42" s="289" t="n"/>
-      <c r="J42" s="289" t="n"/>
-      <c r="K42" s="289" t="n"/>
-      <c r="L42" s="289" t="n"/>
-      <c r="M42" s="289" t="n"/>
-      <c r="N42" s="316" t="inlineStr">
+      <c r="B42" s="467" t="n"/>
+      <c r="C42" s="467" t="n"/>
+      <c r="D42" s="467" t="n"/>
+      <c r="E42" s="467" t="n"/>
+      <c r="F42" s="467" t="n"/>
+      <c r="G42" s="467" t="n"/>
+      <c r="H42" s="467" t="n"/>
+      <c r="I42" s="467" t="n"/>
+      <c r="J42" s="467" t="n"/>
+      <c r="K42" s="467" t="n"/>
+      <c r="L42" s="467" t="n"/>
+      <c r="M42" s="467" t="n"/>
+      <c r="N42" s="431" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="O42" s="289" t="n"/>
-      <c r="P42" s="289" t="n"/>
-      <c r="Q42" s="289" t="n"/>
-      <c r="R42" s="289" t="n"/>
-      <c r="S42" s="289" t="n"/>
-      <c r="T42" s="289" t="n"/>
-      <c r="U42" s="289" t="n"/>
-      <c r="V42" s="289" t="n"/>
-      <c r="W42" s="289" t="n"/>
-      <c r="X42" s="289" t="n"/>
-      <c r="Y42" s="289" t="n"/>
-      <c r="Z42" s="289" t="n"/>
-      <c r="AA42" s="317" t="inlineStr">
+      <c r="O42" s="467" t="n"/>
+      <c r="P42" s="467" t="n"/>
+      <c r="Q42" s="467" t="n"/>
+      <c r="R42" s="467" t="n"/>
+      <c r="S42" s="467" t="n"/>
+      <c r="T42" s="467" t="n"/>
+      <c r="U42" s="467" t="n"/>
+      <c r="V42" s="467" t="n"/>
+      <c r="W42" s="467" t="n"/>
+      <c r="X42" s="467" t="n"/>
+      <c r="Y42" s="467" t="n"/>
+      <c r="Z42" s="467" t="n"/>
+      <c r="AA42" s="432" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AB42" s="289" t="n"/>
-      <c r="AC42" s="289" t="n"/>
-      <c r="AD42" s="289" t="n"/>
-      <c r="AE42" s="289" t="n"/>
-      <c r="AF42" s="289" t="n"/>
-      <c r="AG42" s="289" t="n"/>
-      <c r="AH42" s="289" t="n"/>
-      <c r="AI42" s="289" t="n"/>
-      <c r="AJ42" s="289" t="n"/>
-      <c r="AK42" s="289" t="n"/>
-      <c r="AL42" s="289" t="n"/>
-      <c r="AM42" s="289" t="n"/>
-      <c r="AN42" s="290" t="n"/>
+      <c r="AB42" s="467" t="n"/>
+      <c r="AC42" s="467" t="n"/>
+      <c r="AD42" s="467" t="n"/>
+      <c r="AE42" s="467" t="n"/>
+      <c r="AF42" s="467" t="n"/>
+      <c r="AG42" s="467" t="n"/>
+      <c r="AH42" s="467" t="n"/>
+      <c r="AI42" s="467" t="n"/>
+      <c r="AJ42" s="467" t="n"/>
+      <c r="AK42" s="467" t="n"/>
+      <c r="AL42" s="467" t="n"/>
+      <c r="AM42" s="467" t="n"/>
+      <c r="AN42" s="468" t="n"/>
     </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="318" t="inlineStr">
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="433" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="B43" s="268" t="n"/>
-      <c r="C43" s="268" t="n"/>
-      <c r="D43" s="268" t="n"/>
-      <c r="E43" s="268" t="n"/>
-      <c r="F43" s="268" t="n"/>
-      <c r="G43" s="268" t="n"/>
-      <c r="H43" s="268" t="n"/>
-      <c r="I43" s="268" t="n"/>
-      <c r="J43" s="268" t="n"/>
-      <c r="K43" s="268" t="n"/>
-      <c r="L43" s="268" t="n"/>
-      <c r="M43" s="319" t="n"/>
-      <c r="N43" s="318" t="inlineStr">
+      <c r="B43" s="466" t="n"/>
+      <c r="C43" s="466" t="n"/>
+      <c r="D43" s="466" t="n"/>
+      <c r="E43" s="466" t="n"/>
+      <c r="F43" s="466" t="n"/>
+      <c r="G43" s="466" t="n"/>
+      <c r="H43" s="466" t="n"/>
+      <c r="I43" s="466" t="n"/>
+      <c r="J43" s="466" t="n"/>
+      <c r="K43" s="466" t="n"/>
+      <c r="L43" s="466" t="n"/>
+      <c r="M43" s="477" t="n"/>
+      <c r="N43" s="433" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="O43" s="268" t="n"/>
-      <c r="P43" s="268" t="n"/>
-      <c r="Q43" s="268" t="n"/>
-      <c r="R43" s="268" t="n"/>
-      <c r="S43" s="268" t="n"/>
-      <c r="T43" s="268" t="n"/>
-      <c r="U43" s="268" t="n"/>
-      <c r="V43" s="268" t="n"/>
-      <c r="W43" s="268" t="n"/>
-      <c r="X43" s="268" t="n"/>
-      <c r="Y43" s="268" t="n"/>
-      <c r="Z43" s="319" t="n"/>
-      <c r="AA43" s="318" t="inlineStr">
+      <c r="O43" s="466" t="n"/>
+      <c r="P43" s="466" t="n"/>
+      <c r="Q43" s="466" t="n"/>
+      <c r="R43" s="466" t="n"/>
+      <c r="S43" s="466" t="n"/>
+      <c r="T43" s="466" t="n"/>
+      <c r="U43" s="466" t="n"/>
+      <c r="V43" s="466" t="n"/>
+      <c r="W43" s="466" t="n"/>
+      <c r="X43" s="466" t="n"/>
+      <c r="Y43" s="466" t="n"/>
+      <c r="Z43" s="477" t="n"/>
+      <c r="AA43" s="433" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="AB43" s="268" t="n"/>
-      <c r="AC43" s="268" t="n"/>
-      <c r="AD43" s="268" t="n"/>
-      <c r="AE43" s="268" t="n"/>
-      <c r="AF43" s="268" t="n"/>
-      <c r="AG43" s="268" t="n"/>
-      <c r="AH43" s="268" t="n"/>
-      <c r="AI43" s="268" t="n"/>
-      <c r="AJ43" s="268" t="n"/>
-      <c r="AK43" s="268" t="n"/>
-      <c r="AL43" s="268" t="n"/>
-      <c r="AM43" s="268" t="n"/>
-      <c r="AN43" s="319" t="n"/>
+      <c r="AB43" s="466" t="n"/>
+      <c r="AC43" s="466" t="n"/>
+      <c r="AD43" s="466" t="n"/>
+      <c r="AE43" s="466" t="n"/>
+      <c r="AF43" s="466" t="n"/>
+      <c r="AG43" s="466" t="n"/>
+      <c r="AH43" s="466" t="n"/>
+      <c r="AI43" s="466" t="n"/>
+      <c r="AJ43" s="466" t="n"/>
+      <c r="AK43" s="466" t="n"/>
+      <c r="AL43" s="466" t="n"/>
+      <c r="AM43" s="466" t="n"/>
+      <c r="AN43" s="477" t="n"/>
     </row>
-    <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="275" t="n"/>
-      <c r="M44" s="320" t="n"/>
-      <c r="N44" s="275" t="n"/>
-      <c r="Z44" s="320" t="n"/>
-      <c r="AA44" s="275" t="n"/>
-      <c r="AN44" s="320" t="n"/>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="478" t="n"/>
+      <c r="B44" s="436" t="n"/>
+      <c r="C44" s="436" t="n"/>
+      <c r="D44" s="436" t="n"/>
+      <c r="E44" s="436" t="n"/>
+      <c r="F44" s="436" t="n"/>
+      <c r="G44" s="436" t="n"/>
+      <c r="H44" s="436" t="n"/>
+      <c r="I44" s="436" t="n"/>
+      <c r="J44" s="436" t="n"/>
+      <c r="K44" s="436" t="n"/>
+      <c r="L44" s="436" t="n"/>
+      <c r="M44" s="479" t="n"/>
+      <c r="N44" s="478" t="n"/>
+      <c r="O44" s="436" t="n"/>
+      <c r="P44" s="436" t="n"/>
+      <c r="Q44" s="436" t="n"/>
+      <c r="R44" s="436" t="n"/>
+      <c r="S44" s="436" t="n"/>
+      <c r="T44" s="436" t="n"/>
+      <c r="U44" s="436" t="n"/>
+      <c r="V44" s="436" t="n"/>
+      <c r="W44" s="436" t="n"/>
+      <c r="X44" s="436" t="n"/>
+      <c r="Y44" s="436" t="n"/>
+      <c r="Z44" s="479" t="n"/>
+      <c r="AA44" s="478" t="n"/>
+      <c r="AB44" s="436" t="n"/>
+      <c r="AC44" s="436" t="n"/>
+      <c r="AD44" s="436" t="n"/>
+      <c r="AE44" s="436" t="n"/>
+      <c r="AF44" s="436" t="n"/>
+      <c r="AG44" s="436" t="n"/>
+      <c r="AH44" s="436" t="n"/>
+      <c r="AI44" s="436" t="n"/>
+      <c r="AJ44" s="436" t="n"/>
+      <c r="AK44" s="436" t="n"/>
+      <c r="AL44" s="436" t="n"/>
+      <c r="AM44" s="436" t="n"/>
+      <c r="AN44" s="479" t="n"/>
     </row>
-    <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="282" t="n"/>
-      <c r="B45" s="283" t="n"/>
-      <c r="C45" s="283" t="n"/>
-      <c r="D45" s="283" t="n"/>
-      <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="n"/>
-      <c r="I45" s="283" t="n"/>
-      <c r="J45" s="283" t="n"/>
-      <c r="K45" s="283" t="n"/>
-      <c r="L45" s="283" t="n"/>
-      <c r="M45" s="287" t="n"/>
-      <c r="N45" s="282" t="n"/>
-      <c r="O45" s="283" t="n"/>
-      <c r="P45" s="283" t="n"/>
-      <c r="Q45" s="283" t="n"/>
-      <c r="R45" s="283" t="n"/>
-      <c r="S45" s="283" t="n"/>
-      <c r="T45" s="283" t="n"/>
-      <c r="U45" s="283" t="n"/>
-      <c r="V45" s="283" t="n"/>
-      <c r="W45" s="283" t="n"/>
-      <c r="X45" s="283" t="n"/>
-      <c r="Y45" s="283" t="n"/>
-      <c r="Z45" s="287" t="n"/>
-      <c r="AA45" s="282" t="n"/>
-      <c r="AB45" s="283" t="n"/>
-      <c r="AC45" s="283" t="n"/>
-      <c r="AD45" s="283" t="n"/>
-      <c r="AE45" s="283" t="n"/>
-      <c r="AF45" s="283" t="n"/>
-      <c r="AG45" s="283" t="n"/>
-      <c r="AH45" s="283" t="n"/>
-      <c r="AI45" s="283" t="n"/>
-      <c r="AJ45" s="283" t="n"/>
-      <c r="AK45" s="283" t="n"/>
-      <c r="AL45" s="283" t="n"/>
-      <c r="AM45" s="283" t="n"/>
-      <c r="AN45" s="287" t="n"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="480" t="n"/>
+      <c r="B45" s="475" t="n"/>
+      <c r="C45" s="475" t="n"/>
+      <c r="D45" s="475" t="n"/>
+      <c r="E45" s="475" t="n"/>
+      <c r="F45" s="475" t="n"/>
+      <c r="G45" s="475" t="n"/>
+      <c r="H45" s="475" t="n"/>
+      <c r="I45" s="475" t="n"/>
+      <c r="J45" s="475" t="n"/>
+      <c r="K45" s="475" t="n"/>
+      <c r="L45" s="475" t="n"/>
+      <c r="M45" s="476" t="n"/>
+      <c r="N45" s="480" t="n"/>
+      <c r="O45" s="475" t="n"/>
+      <c r="P45" s="475" t="n"/>
+      <c r="Q45" s="475" t="n"/>
+      <c r="R45" s="475" t="n"/>
+      <c r="S45" s="475" t="n"/>
+      <c r="T45" s="475" t="n"/>
+      <c r="U45" s="475" t="n"/>
+      <c r="V45" s="475" t="n"/>
+      <c r="W45" s="475" t="n"/>
+      <c r="X45" s="475" t="n"/>
+      <c r="Y45" s="475" t="n"/>
+      <c r="Z45" s="476" t="n"/>
+      <c r="AA45" s="480" t="n"/>
+      <c r="AB45" s="475" t="n"/>
+      <c r="AC45" s="475" t="n"/>
+      <c r="AD45" s="475" t="n"/>
+      <c r="AE45" s="475" t="n"/>
+      <c r="AF45" s="475" t="n"/>
+      <c r="AG45" s="475" t="n"/>
+      <c r="AH45" s="475" t="n"/>
+      <c r="AI45" s="475" t="n"/>
+      <c r="AJ45" s="475" t="n"/>
+      <c r="AK45" s="475" t="n"/>
+      <c r="AL45" s="475" t="n"/>
+      <c r="AM45" s="475" t="n"/>
+      <c r="AN45" s="476" t="n"/>
     </row>
     <row r="46" ht="4" customHeight="1">
-      <c r="A46" s="25" t="n"/>
+      <c r="A46" s="410" t="n"/>
+      <c r="B46" s="482" t="n"/>
+      <c r="C46" s="482" t="n"/>
+      <c r="D46" s="482" t="n"/>
+      <c r="E46" s="482" t="n"/>
+      <c r="F46" s="482" t="n"/>
+      <c r="G46" s="482" t="n"/>
+      <c r="H46" s="482" t="n"/>
+      <c r="I46" s="482" t="n"/>
+      <c r="J46" s="482" t="n"/>
+      <c r="K46" s="482" t="n"/>
+      <c r="L46" s="482" t="n"/>
+      <c r="M46" s="482" t="n"/>
+      <c r="N46" s="482" t="n"/>
+      <c r="O46" s="482" t="n"/>
+      <c r="P46" s="482" t="n"/>
+      <c r="Q46" s="482" t="n"/>
+      <c r="R46" s="482" t="n"/>
+      <c r="S46" s="482" t="n"/>
+      <c r="T46" s="482" t="n"/>
+      <c r="U46" s="482" t="n"/>
+      <c r="V46" s="482" t="n"/>
+      <c r="W46" s="482" t="n"/>
+      <c r="X46" s="482" t="n"/>
+      <c r="Y46" s="482" t="n"/>
+      <c r="Z46" s="482" t="n"/>
+      <c r="AA46" s="482" t="n"/>
+      <c r="AB46" s="482" t="n"/>
+      <c r="AC46" s="482" t="n"/>
+      <c r="AD46" s="482" t="n"/>
+      <c r="AE46" s="482" t="n"/>
+      <c r="AF46" s="482" t="n"/>
+      <c r="AG46" s="482" t="n"/>
+      <c r="AH46" s="482" t="n"/>
+      <c r="AI46" s="482" t="n"/>
+      <c r="AJ46" s="482" t="n"/>
+      <c r="AK46" s="482" t="n"/>
+      <c r="AL46" s="482" t="n"/>
+      <c r="AM46" s="482" t="n"/>
+      <c r="AN46" s="482" t="n"/>
     </row>
-    <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="321" t="inlineStr">
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="439" t="inlineStr">
         <is>
           <t>NOTICE  —  Enter data only in designated white input cells. Do not add, delete or resize columns/rows. File naming: FRM-209_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="289" t="n"/>
-      <c r="C47" s="289" t="n"/>
-      <c r="D47" s="289" t="n"/>
-      <c r="E47" s="289" t="n"/>
-      <c r="F47" s="289" t="n"/>
-      <c r="G47" s="289" t="n"/>
-      <c r="H47" s="289" t="n"/>
-      <c r="I47" s="289" t="n"/>
-      <c r="J47" s="289" t="n"/>
-      <c r="K47" s="289" t="n"/>
-      <c r="L47" s="289" t="n"/>
-      <c r="M47" s="289" t="n"/>
-      <c r="N47" s="289" t="n"/>
-      <c r="O47" s="289" t="n"/>
-      <c r="P47" s="289" t="n"/>
-      <c r="Q47" s="289" t="n"/>
-      <c r="R47" s="289" t="n"/>
-      <c r="S47" s="289" t="n"/>
-      <c r="T47" s="289" t="n"/>
-      <c r="U47" s="289" t="n"/>
-      <c r="V47" s="289" t="n"/>
-      <c r="W47" s="289" t="n"/>
-      <c r="X47" s="289" t="n"/>
-      <c r="Y47" s="289" t="n"/>
-      <c r="Z47" s="289" t="n"/>
-      <c r="AA47" s="289" t="n"/>
-      <c r="AB47" s="289" t="n"/>
-      <c r="AC47" s="289" t="n"/>
-      <c r="AD47" s="289" t="n"/>
-      <c r="AE47" s="289" t="n"/>
-      <c r="AF47" s="289" t="n"/>
-      <c r="AG47" s="289" t="n"/>
-      <c r="AH47" s="289" t="n"/>
-      <c r="AI47" s="289" t="n"/>
-      <c r="AJ47" s="289" t="n"/>
-      <c r="AK47" s="289" t="n"/>
-      <c r="AL47" s="289" t="n"/>
-      <c r="AM47" s="289" t="n"/>
-      <c r="AN47" s="290" t="n"/>
+      <c r="B47" s="473" t="n"/>
+      <c r="C47" s="473" t="n"/>
+      <c r="D47" s="473" t="n"/>
+      <c r="E47" s="473" t="n"/>
+      <c r="F47" s="473" t="n"/>
+      <c r="G47" s="473" t="n"/>
+      <c r="H47" s="473" t="n"/>
+      <c r="I47" s="473" t="n"/>
+      <c r="J47" s="473" t="n"/>
+      <c r="K47" s="473" t="n"/>
+      <c r="L47" s="473" t="n"/>
+      <c r="M47" s="473" t="n"/>
+      <c r="N47" s="473" t="n"/>
+      <c r="O47" s="473" t="n"/>
+      <c r="P47" s="473" t="n"/>
+      <c r="Q47" s="473" t="n"/>
+      <c r="R47" s="473" t="n"/>
+      <c r="S47" s="473" t="n"/>
+      <c r="T47" s="473" t="n"/>
+      <c r="U47" s="473" t="n"/>
+      <c r="V47" s="473" t="n"/>
+      <c r="W47" s="473" t="n"/>
+      <c r="X47" s="473" t="n"/>
+      <c r="Y47" s="473" t="n"/>
+      <c r="Z47" s="473" t="n"/>
+      <c r="AA47" s="473" t="n"/>
+      <c r="AB47" s="473" t="n"/>
+      <c r="AC47" s="473" t="n"/>
+      <c r="AD47" s="473" t="n"/>
+      <c r="AE47" s="473" t="n"/>
+      <c r="AF47" s="473" t="n"/>
+      <c r="AG47" s="473" t="n"/>
+      <c r="AH47" s="473" t="n"/>
+      <c r="AI47" s="473" t="n"/>
+      <c r="AJ47" s="473" t="n"/>
+      <c r="AK47" s="473" t="n"/>
+      <c r="AL47" s="473" t="n"/>
+      <c r="AM47" s="473" t="n"/>
+      <c r="AN47" s="474" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="1"/>
     <row r="49" hidden="1" outlineLevel="1"/>
@@ -7753,7 +8433,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -7764,139 +8443,432 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col hidden="1" width="20" customWidth="1" min="5" max="16384"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col hidden="1" width="2.33" customWidth="1" min="5" max="16384"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="402" t="inlineStr">
         <is>
           <t>VAL_RESULT_CORE</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="402" t="inlineStr">
         <is>
           <t>VAL_DECISION_GATE_CORE</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="402" t="inlineStr">
         <is>
           <t>VAL_STATUS_CORE</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="402" t="inlineStr">
         <is>
           <t>VAL_RISK_LEVEL_CORE</t>
         </is>
       </c>
+      <c r="E1" s="402" t="n"/>
+      <c r="F1" s="402" t="n"/>
+      <c r="G1" s="402" t="n"/>
+      <c r="H1" s="402" t="n"/>
+      <c r="I1" s="402" t="n"/>
+      <c r="J1" s="402" t="n"/>
+      <c r="K1" s="402" t="n"/>
+      <c r="L1" s="402" t="n"/>
+      <c r="M1" s="402" t="n"/>
+      <c r="N1" s="402" t="n"/>
+      <c r="O1" s="402" t="n"/>
+      <c r="P1" s="402" t="n"/>
+      <c r="Q1" s="402" t="n"/>
+      <c r="R1" s="402" t="n"/>
+      <c r="S1" s="402" t="n"/>
+      <c r="T1" s="402" t="n"/>
+      <c r="U1" s="402" t="n"/>
+      <c r="V1" s="402" t="n"/>
+      <c r="W1" s="402" t="n"/>
+      <c r="X1" s="402" t="n"/>
+      <c r="Y1" s="402" t="n"/>
+      <c r="Z1" s="402" t="n"/>
+      <c r="AA1" s="402" t="n"/>
+      <c r="AB1" s="402" t="n"/>
+      <c r="AC1" s="402" t="n"/>
+      <c r="AD1" s="402" t="n"/>
+      <c r="AE1" s="402" t="n"/>
+      <c r="AF1" s="402" t="n"/>
+      <c r="AG1" s="402" t="n"/>
+      <c r="AH1" s="402" t="n"/>
+      <c r="AI1" s="402" t="n"/>
+      <c r="AJ1" s="402" t="n"/>
+      <c r="AK1" s="402" t="n"/>
+      <c r="AL1" s="402" t="n"/>
+      <c r="AM1" s="402" t="n"/>
+      <c r="AN1" s="402" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="402" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="402" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="402" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="402" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
+      <c r="E2" s="402" t="n"/>
+      <c r="F2" s="402" t="n"/>
+      <c r="G2" s="402" t="n"/>
+      <c r="H2" s="402" t="n"/>
+      <c r="I2" s="402" t="n"/>
+      <c r="J2" s="402" t="n"/>
+      <c r="K2" s="402" t="n"/>
+      <c r="L2" s="402" t="n"/>
+      <c r="M2" s="402" t="n"/>
+      <c r="N2" s="402" t="n"/>
+      <c r="O2" s="402" t="n"/>
+      <c r="P2" s="402" t="n"/>
+      <c r="Q2" s="402" t="n"/>
+      <c r="R2" s="402" t="n"/>
+      <c r="S2" s="402" t="n"/>
+      <c r="T2" s="402" t="n"/>
+      <c r="U2" s="402" t="n"/>
+      <c r="V2" s="402" t="n"/>
+      <c r="W2" s="402" t="n"/>
+      <c r="X2" s="402" t="n"/>
+      <c r="Y2" s="402" t="n"/>
+      <c r="Z2" s="402" t="n"/>
+      <c r="AA2" s="402" t="n"/>
+      <c r="AB2" s="402" t="n"/>
+      <c r="AC2" s="402" t="n"/>
+      <c r="AD2" s="402" t="n"/>
+      <c r="AE2" s="402" t="n"/>
+      <c r="AF2" s="402" t="n"/>
+      <c r="AG2" s="402" t="n"/>
+      <c r="AH2" s="402" t="n"/>
+      <c r="AI2" s="402" t="n"/>
+      <c r="AJ2" s="402" t="n"/>
+      <c r="AK2" s="402" t="n"/>
+      <c r="AL2" s="402" t="n"/>
+      <c r="AM2" s="402" t="n"/>
+      <c r="AN2" s="402" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="402" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="402" t="inlineStr">
         <is>
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="402" t="inlineStr">
         <is>
           <t>IN PROGRESS</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="402" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="E3" s="402" t="n"/>
+      <c r="F3" s="402" t="n"/>
+      <c r="G3" s="402" t="n"/>
+      <c r="H3" s="402" t="n"/>
+      <c r="I3" s="402" t="n"/>
+      <c r="J3" s="402" t="n"/>
+      <c r="K3" s="402" t="n"/>
+      <c r="L3" s="402" t="n"/>
+      <c r="M3" s="402" t="n"/>
+      <c r="N3" s="402" t="n"/>
+      <c r="O3" s="402" t="n"/>
+      <c r="P3" s="402" t="n"/>
+      <c r="Q3" s="402" t="n"/>
+      <c r="R3" s="402" t="n"/>
+      <c r="S3" s="402" t="n"/>
+      <c r="T3" s="402" t="n"/>
+      <c r="U3" s="402" t="n"/>
+      <c r="V3" s="402" t="n"/>
+      <c r="W3" s="402" t="n"/>
+      <c r="X3" s="402" t="n"/>
+      <c r="Y3" s="402" t="n"/>
+      <c r="Z3" s="402" t="n"/>
+      <c r="AA3" s="402" t="n"/>
+      <c r="AB3" s="402" t="n"/>
+      <c r="AC3" s="402" t="n"/>
+      <c r="AD3" s="402" t="n"/>
+      <c r="AE3" s="402" t="n"/>
+      <c r="AF3" s="402" t="n"/>
+      <c r="AG3" s="402" t="n"/>
+      <c r="AH3" s="402" t="n"/>
+      <c r="AI3" s="402" t="n"/>
+      <c r="AJ3" s="402" t="n"/>
+      <c r="AK3" s="402" t="n"/>
+      <c r="AL3" s="402" t="n"/>
+      <c r="AM3" s="402" t="n"/>
+      <c r="AN3" s="402" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="402" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="402" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="402" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="402" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
+      <c r="E4" s="402" t="n"/>
+      <c r="F4" s="402" t="n"/>
+      <c r="G4" s="402" t="n"/>
+      <c r="H4" s="402" t="n"/>
+      <c r="I4" s="402" t="n"/>
+      <c r="J4" s="402" t="n"/>
+      <c r="K4" s="402" t="n"/>
+      <c r="L4" s="402" t="n"/>
+      <c r="M4" s="402" t="n"/>
+      <c r="N4" s="402" t="n"/>
+      <c r="O4" s="402" t="n"/>
+      <c r="P4" s="402" t="n"/>
+      <c r="Q4" s="402" t="n"/>
+      <c r="R4" s="402" t="n"/>
+      <c r="S4" s="402" t="n"/>
+      <c r="T4" s="402" t="n"/>
+      <c r="U4" s="402" t="n"/>
+      <c r="V4" s="402" t="n"/>
+      <c r="W4" s="402" t="n"/>
+      <c r="X4" s="402" t="n"/>
+      <c r="Y4" s="402" t="n"/>
+      <c r="Z4" s="402" t="n"/>
+      <c r="AA4" s="402" t="n"/>
+      <c r="AB4" s="402" t="n"/>
+      <c r="AC4" s="402" t="n"/>
+      <c r="AD4" s="402" t="n"/>
+      <c r="AE4" s="402" t="n"/>
+      <c r="AF4" s="402" t="n"/>
+      <c r="AG4" s="402" t="n"/>
+      <c r="AH4" s="402" t="n"/>
+      <c r="AI4" s="402" t="n"/>
+      <c r="AJ4" s="402" t="n"/>
+      <c r="AK4" s="402" t="n"/>
+      <c r="AL4" s="402" t="n"/>
+      <c r="AM4" s="402" t="n"/>
+      <c r="AN4" s="402" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="402" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="402" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="402" t="inlineStr">
         <is>
           <t>MONITORING</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="402" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="E5" s="402" t="n"/>
+      <c r="F5" s="402" t="n"/>
+      <c r="G5" s="402" t="n"/>
+      <c r="H5" s="402" t="n"/>
+      <c r="I5" s="402" t="n"/>
+      <c r="J5" s="402" t="n"/>
+      <c r="K5" s="402" t="n"/>
+      <c r="L5" s="402" t="n"/>
+      <c r="M5" s="402" t="n"/>
+      <c r="N5" s="402" t="n"/>
+      <c r="O5" s="402" t="n"/>
+      <c r="P5" s="402" t="n"/>
+      <c r="Q5" s="402" t="n"/>
+      <c r="R5" s="402" t="n"/>
+      <c r="S5" s="402" t="n"/>
+      <c r="T5" s="402" t="n"/>
+      <c r="U5" s="402" t="n"/>
+      <c r="V5" s="402" t="n"/>
+      <c r="W5" s="402" t="n"/>
+      <c r="X5" s="402" t="n"/>
+      <c r="Y5" s="402" t="n"/>
+      <c r="Z5" s="402" t="n"/>
+      <c r="AA5" s="402" t="n"/>
+      <c r="AB5" s="402" t="n"/>
+      <c r="AC5" s="402" t="n"/>
+      <c r="AD5" s="402" t="n"/>
+      <c r="AE5" s="402" t="n"/>
+      <c r="AF5" s="402" t="n"/>
+      <c r="AG5" s="402" t="n"/>
+      <c r="AH5" s="402" t="n"/>
+      <c r="AI5" s="402" t="n"/>
+      <c r="AJ5" s="402" t="n"/>
+      <c r="AK5" s="402" t="n"/>
+      <c r="AL5" s="402" t="n"/>
+      <c r="AM5" s="402" t="n"/>
+      <c r="AN5" s="402" t="n"/>
     </row>
     <row r="6">
-      <c r="C6" t="inlineStr">
+      <c r="A6" s="402" t="n"/>
+      <c r="B6" s="402" t="n"/>
+      <c r="C6" s="402" t="inlineStr">
         <is>
           <t>SUPERSEDED</t>
         </is>
       </c>
+      <c r="D6" s="402" t="n"/>
+      <c r="E6" s="402" t="n"/>
+      <c r="F6" s="402" t="n"/>
+      <c r="G6" s="402" t="n"/>
+      <c r="H6" s="402" t="n"/>
+      <c r="I6" s="402" t="n"/>
+      <c r="J6" s="402" t="n"/>
+      <c r="K6" s="402" t="n"/>
+      <c r="L6" s="402" t="n"/>
+      <c r="M6" s="402" t="n"/>
+      <c r="N6" s="402" t="n"/>
+      <c r="O6" s="402" t="n"/>
+      <c r="P6" s="402" t="n"/>
+      <c r="Q6" s="402" t="n"/>
+      <c r="R6" s="402" t="n"/>
+      <c r="S6" s="402" t="n"/>
+      <c r="T6" s="402" t="n"/>
+      <c r="U6" s="402" t="n"/>
+      <c r="V6" s="402" t="n"/>
+      <c r="W6" s="402" t="n"/>
+      <c r="X6" s="402" t="n"/>
+      <c r="Y6" s="402" t="n"/>
+      <c r="Z6" s="402" t="n"/>
+      <c r="AA6" s="402" t="n"/>
+      <c r="AB6" s="402" t="n"/>
+      <c r="AC6" s="402" t="n"/>
+      <c r="AD6" s="402" t="n"/>
+      <c r="AE6" s="402" t="n"/>
+      <c r="AF6" s="402" t="n"/>
+      <c r="AG6" s="402" t="n"/>
+      <c r="AH6" s="402" t="n"/>
+      <c r="AI6" s="402" t="n"/>
+      <c r="AJ6" s="402" t="n"/>
+      <c r="AK6" s="402" t="n"/>
+      <c r="AL6" s="402" t="n"/>
+      <c r="AM6" s="402" t="n"/>
+      <c r="AN6" s="402" t="n"/>
     </row>
     <row r="7">
-      <c r="C7" t="inlineStr">
+      <c r="A7" s="402" t="n"/>
+      <c r="B7" s="402" t="n"/>
+      <c r="C7" s="402" t="inlineStr">
         <is>
           <t>VOID</t>
         </is>
       </c>
+      <c r="D7" s="402" t="n"/>
+      <c r="E7" s="402" t="n"/>
+      <c r="F7" s="402" t="n"/>
+      <c r="G7" s="402" t="n"/>
+      <c r="H7" s="402" t="n"/>
+      <c r="I7" s="402" t="n"/>
+      <c r="J7" s="402" t="n"/>
+      <c r="K7" s="402" t="n"/>
+      <c r="L7" s="402" t="n"/>
+      <c r="M7" s="402" t="n"/>
+      <c r="N7" s="402" t="n"/>
+      <c r="O7" s="402" t="n"/>
+      <c r="P7" s="402" t="n"/>
+      <c r="Q7" s="402" t="n"/>
+      <c r="R7" s="402" t="n"/>
+      <c r="S7" s="402" t="n"/>
+      <c r="T7" s="402" t="n"/>
+      <c r="U7" s="402" t="n"/>
+      <c r="V7" s="402" t="n"/>
+      <c r="W7" s="402" t="n"/>
+      <c r="X7" s="402" t="n"/>
+      <c r="Y7" s="402" t="n"/>
+      <c r="Z7" s="402" t="n"/>
+      <c r="AA7" s="402" t="n"/>
+      <c r="AB7" s="402" t="n"/>
+      <c r="AC7" s="402" t="n"/>
+      <c r="AD7" s="402" t="n"/>
+      <c r="AE7" s="402" t="n"/>
+      <c r="AF7" s="402" t="n"/>
+      <c r="AG7" s="402" t="n"/>
+      <c r="AH7" s="402" t="n"/>
+      <c r="AI7" s="402" t="n"/>
+      <c r="AJ7" s="402" t="n"/>
+      <c r="AK7" s="402" t="n"/>
+      <c r="AL7" s="402" t="n"/>
+      <c r="AM7" s="402" t="n"/>
+      <c r="AN7" s="402" t="n"/>
     </row>
     <row r="8" hidden="1"/>
     <row r="9" hidden="1"/>
@@ -8092,7 +9064,8 @@
     <row r="199" hidden="1"/>
     <row r="200" hidden="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -8102,113 +9075,374 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col hidden="1" width="13" customWidth="1" min="5" max="16384"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col hidden="1" width="2.33" customWidth="1" min="5" max="16384"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="402" t="inlineStr">
         <is>
           <t>REF_CUSTOMER_MASTER</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="402" t="inlineStr">
         <is>
           <t>REF_PART_REV_MASTER</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="402" t="inlineStr">
         <is>
           <t>REF_JOB_WO_MASTER</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="402" t="inlineStr">
         <is>
           <t>REF_OWNER_PERSON_MASTER</t>
         </is>
       </c>
+      <c r="E1" s="402" t="n"/>
+      <c r="F1" s="402" t="n"/>
+      <c r="G1" s="402" t="n"/>
+      <c r="H1" s="402" t="n"/>
+      <c r="I1" s="402" t="n"/>
+      <c r="J1" s="402" t="n"/>
+      <c r="K1" s="402" t="n"/>
+      <c r="L1" s="402" t="n"/>
+      <c r="M1" s="402" t="n"/>
+      <c r="N1" s="402" t="n"/>
+      <c r="O1" s="402" t="n"/>
+      <c r="P1" s="402" t="n"/>
+      <c r="Q1" s="402" t="n"/>
+      <c r="R1" s="402" t="n"/>
+      <c r="S1" s="402" t="n"/>
+      <c r="T1" s="402" t="n"/>
+      <c r="U1" s="402" t="n"/>
+      <c r="V1" s="402" t="n"/>
+      <c r="W1" s="402" t="n"/>
+      <c r="X1" s="402" t="n"/>
+      <c r="Y1" s="402" t="n"/>
+      <c r="Z1" s="402" t="n"/>
+      <c r="AA1" s="402" t="n"/>
+      <c r="AB1" s="402" t="n"/>
+      <c r="AC1" s="402" t="n"/>
+      <c r="AD1" s="402" t="n"/>
+      <c r="AE1" s="402" t="n"/>
+      <c r="AF1" s="402" t="n"/>
+      <c r="AG1" s="402" t="n"/>
+      <c r="AH1" s="402" t="n"/>
+      <c r="AI1" s="402" t="n"/>
+      <c r="AJ1" s="402" t="n"/>
+      <c r="AK1" s="402" t="n"/>
+      <c r="AL1" s="402" t="n"/>
+      <c r="AM1" s="402" t="n"/>
+      <c r="AN1" s="402" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="402" t="inlineStr">
         <is>
           <t>CUST-001 Alpha Semi</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="402" t="inlineStr">
         <is>
           <t>PN-1001 / Rev.A</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="402" t="inlineStr">
         <is>
           <t>JOB-240001</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="402" t="inlineStr">
         <is>
           <t>Planning Lead</t>
         </is>
       </c>
+      <c r="E2" s="402" t="n"/>
+      <c r="F2" s="402" t="n"/>
+      <c r="G2" s="402" t="n"/>
+      <c r="H2" s="402" t="n"/>
+      <c r="I2" s="402" t="n"/>
+      <c r="J2" s="402" t="n"/>
+      <c r="K2" s="402" t="n"/>
+      <c r="L2" s="402" t="n"/>
+      <c r="M2" s="402" t="n"/>
+      <c r="N2" s="402" t="n"/>
+      <c r="O2" s="402" t="n"/>
+      <c r="P2" s="402" t="n"/>
+      <c r="Q2" s="402" t="n"/>
+      <c r="R2" s="402" t="n"/>
+      <c r="S2" s="402" t="n"/>
+      <c r="T2" s="402" t="n"/>
+      <c r="U2" s="402" t="n"/>
+      <c r="V2" s="402" t="n"/>
+      <c r="W2" s="402" t="n"/>
+      <c r="X2" s="402" t="n"/>
+      <c r="Y2" s="402" t="n"/>
+      <c r="Z2" s="402" t="n"/>
+      <c r="AA2" s="402" t="n"/>
+      <c r="AB2" s="402" t="n"/>
+      <c r="AC2" s="402" t="n"/>
+      <c r="AD2" s="402" t="n"/>
+      <c r="AE2" s="402" t="n"/>
+      <c r="AF2" s="402" t="n"/>
+      <c r="AG2" s="402" t="n"/>
+      <c r="AH2" s="402" t="n"/>
+      <c r="AI2" s="402" t="n"/>
+      <c r="AJ2" s="402" t="n"/>
+      <c r="AK2" s="402" t="n"/>
+      <c r="AL2" s="402" t="n"/>
+      <c r="AM2" s="402" t="n"/>
+      <c r="AN2" s="402" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="402" t="inlineStr">
         <is>
           <t>CUST-002 NovaFab</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="402" t="inlineStr">
         <is>
           <t>PN-1002 / Rev.B</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="402" t="inlineStr">
         <is>
           <t>JOB-240002</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="402" t="inlineStr">
         <is>
           <t>Production Supervisor</t>
         </is>
       </c>
+      <c r="E3" s="402" t="n"/>
+      <c r="F3" s="402" t="n"/>
+      <c r="G3" s="402" t="n"/>
+      <c r="H3" s="402" t="n"/>
+      <c r="I3" s="402" t="n"/>
+      <c r="J3" s="402" t="n"/>
+      <c r="K3" s="402" t="n"/>
+      <c r="L3" s="402" t="n"/>
+      <c r="M3" s="402" t="n"/>
+      <c r="N3" s="402" t="n"/>
+      <c r="O3" s="402" t="n"/>
+      <c r="P3" s="402" t="n"/>
+      <c r="Q3" s="402" t="n"/>
+      <c r="R3" s="402" t="n"/>
+      <c r="S3" s="402" t="n"/>
+      <c r="T3" s="402" t="n"/>
+      <c r="U3" s="402" t="n"/>
+      <c r="V3" s="402" t="n"/>
+      <c r="W3" s="402" t="n"/>
+      <c r="X3" s="402" t="n"/>
+      <c r="Y3" s="402" t="n"/>
+      <c r="Z3" s="402" t="n"/>
+      <c r="AA3" s="402" t="n"/>
+      <c r="AB3" s="402" t="n"/>
+      <c r="AC3" s="402" t="n"/>
+      <c r="AD3" s="402" t="n"/>
+      <c r="AE3" s="402" t="n"/>
+      <c r="AF3" s="402" t="n"/>
+      <c r="AG3" s="402" t="n"/>
+      <c r="AH3" s="402" t="n"/>
+      <c r="AI3" s="402" t="n"/>
+      <c r="AJ3" s="402" t="n"/>
+      <c r="AK3" s="402" t="n"/>
+      <c r="AL3" s="402" t="n"/>
+      <c r="AM3" s="402" t="n"/>
+      <c r="AN3" s="402" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="402" t="inlineStr">
         <is>
           <t>CUST-003 Orion Tech</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="402" t="inlineStr">
         <is>
           <t>PN-1003 / Rev.C</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="402" t="inlineStr">
         <is>
           <t>JOB-240003</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="402" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
+      <c r="E4" s="402" t="n"/>
+      <c r="F4" s="402" t="n"/>
+      <c r="G4" s="402" t="n"/>
+      <c r="H4" s="402" t="n"/>
+      <c r="I4" s="402" t="n"/>
+      <c r="J4" s="402" t="n"/>
+      <c r="K4" s="402" t="n"/>
+      <c r="L4" s="402" t="n"/>
+      <c r="M4" s="402" t="n"/>
+      <c r="N4" s="402" t="n"/>
+      <c r="O4" s="402" t="n"/>
+      <c r="P4" s="402" t="n"/>
+      <c r="Q4" s="402" t="n"/>
+      <c r="R4" s="402" t="n"/>
+      <c r="S4" s="402" t="n"/>
+      <c r="T4" s="402" t="n"/>
+      <c r="U4" s="402" t="n"/>
+      <c r="V4" s="402" t="n"/>
+      <c r="W4" s="402" t="n"/>
+      <c r="X4" s="402" t="n"/>
+      <c r="Y4" s="402" t="n"/>
+      <c r="Z4" s="402" t="n"/>
+      <c r="AA4" s="402" t="n"/>
+      <c r="AB4" s="402" t="n"/>
+      <c r="AC4" s="402" t="n"/>
+      <c r="AD4" s="402" t="n"/>
+      <c r="AE4" s="402" t="n"/>
+      <c r="AF4" s="402" t="n"/>
+      <c r="AG4" s="402" t="n"/>
+      <c r="AH4" s="402" t="n"/>
+      <c r="AI4" s="402" t="n"/>
+      <c r="AJ4" s="402" t="n"/>
+      <c r="AK4" s="402" t="n"/>
+      <c r="AL4" s="402" t="n"/>
+      <c r="AM4" s="402" t="n"/>
+      <c r="AN4" s="402" t="n"/>
     </row>
     <row r="5">
-      <c r="D5" t="inlineStr">
+      <c r="A5" s="402" t="n"/>
+      <c r="B5" s="402" t="n"/>
+      <c r="C5" s="402" t="n"/>
+      <c r="D5" s="402" t="inlineStr">
         <is>
           <t>Engineering Lead</t>
         </is>
       </c>
+      <c r="E5" s="402" t="n"/>
+      <c r="F5" s="402" t="n"/>
+      <c r="G5" s="402" t="n"/>
+      <c r="H5" s="402" t="n"/>
+      <c r="I5" s="402" t="n"/>
+      <c r="J5" s="402" t="n"/>
+      <c r="K5" s="402" t="n"/>
+      <c r="L5" s="402" t="n"/>
+      <c r="M5" s="402" t="n"/>
+      <c r="N5" s="402" t="n"/>
+      <c r="O5" s="402" t="n"/>
+      <c r="P5" s="402" t="n"/>
+      <c r="Q5" s="402" t="n"/>
+      <c r="R5" s="402" t="n"/>
+      <c r="S5" s="402" t="n"/>
+      <c r="T5" s="402" t="n"/>
+      <c r="U5" s="402" t="n"/>
+      <c r="V5" s="402" t="n"/>
+      <c r="W5" s="402" t="n"/>
+      <c r="X5" s="402" t="n"/>
+      <c r="Y5" s="402" t="n"/>
+      <c r="Z5" s="402" t="n"/>
+      <c r="AA5" s="402" t="n"/>
+      <c r="AB5" s="402" t="n"/>
+      <c r="AC5" s="402" t="n"/>
+      <c r="AD5" s="402" t="n"/>
+      <c r="AE5" s="402" t="n"/>
+      <c r="AF5" s="402" t="n"/>
+      <c r="AG5" s="402" t="n"/>
+      <c r="AH5" s="402" t="n"/>
+      <c r="AI5" s="402" t="n"/>
+      <c r="AJ5" s="402" t="n"/>
+      <c r="AK5" s="402" t="n"/>
+      <c r="AL5" s="402" t="n"/>
+      <c r="AM5" s="402" t="n"/>
+      <c r="AN5" s="402" t="n"/>
     </row>
     <row r="6">
-      <c r="D6" t="inlineStr">
+      <c r="A6" s="402" t="n"/>
+      <c r="B6" s="402" t="n"/>
+      <c r="C6" s="402" t="n"/>
+      <c r="D6" s="402" t="inlineStr">
         <is>
           <t>Setup Technician</t>
         </is>
       </c>
+      <c r="E6" s="402" t="n"/>
+      <c r="F6" s="402" t="n"/>
+      <c r="G6" s="402" t="n"/>
+      <c r="H6" s="402" t="n"/>
+      <c r="I6" s="402" t="n"/>
+      <c r="J6" s="402" t="n"/>
+      <c r="K6" s="402" t="n"/>
+      <c r="L6" s="402" t="n"/>
+      <c r="M6" s="402" t="n"/>
+      <c r="N6" s="402" t="n"/>
+      <c r="O6" s="402" t="n"/>
+      <c r="P6" s="402" t="n"/>
+      <c r="Q6" s="402" t="n"/>
+      <c r="R6" s="402" t="n"/>
+      <c r="S6" s="402" t="n"/>
+      <c r="T6" s="402" t="n"/>
+      <c r="U6" s="402" t="n"/>
+      <c r="V6" s="402" t="n"/>
+      <c r="W6" s="402" t="n"/>
+      <c r="X6" s="402" t="n"/>
+      <c r="Y6" s="402" t="n"/>
+      <c r="Z6" s="402" t="n"/>
+      <c r="AA6" s="402" t="n"/>
+      <c r="AB6" s="402" t="n"/>
+      <c r="AC6" s="402" t="n"/>
+      <c r="AD6" s="402" t="n"/>
+      <c r="AE6" s="402" t="n"/>
+      <c r="AF6" s="402" t="n"/>
+      <c r="AG6" s="402" t="n"/>
+      <c r="AH6" s="402" t="n"/>
+      <c r="AI6" s="402" t="n"/>
+      <c r="AJ6" s="402" t="n"/>
+      <c r="AK6" s="402" t="n"/>
+      <c r="AL6" s="402" t="n"/>
+      <c r="AM6" s="402" t="n"/>
+      <c r="AN6" s="402" t="n"/>
     </row>
     <row r="7" hidden="1"/>
     <row r="8" hidden="1"/>
@@ -8405,7 +9639,8 @@
     <row r="199" hidden="1"/>
     <row r="200" hidden="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -8415,513 +9650,1421 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:AN28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="13.53" customWidth="1" min="2" max="2"/>
-    <col width="16.23" customWidth="1" min="3" max="3"/>
-    <col width="16.23" customWidth="1" min="4" max="4"/>
-    <col width="8.119999999999999" customWidth="1" min="5" max="5"/>
-    <col width="8.789999999999999" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="8.119999999999999" customWidth="1" min="8" max="8"/>
-    <col width="10.82" customWidth="1" min="9" max="9"/>
-    <col hidden="1" outlineLevel="1" width="13" customWidth="1" min="10" max="16384"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col hidden="1" outlineLevel="1" width="2.33" customWidth="1" min="10" max="16384"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="386" t="n"/>
-      <c r="B1" s="319" t="n"/>
-      <c r="C1" s="387" t="inlineStr">
+      <c r="A1" s="440" t="n"/>
+      <c r="B1" s="490" t="n"/>
+      <c r="C1" s="441" t="inlineStr">
         <is>
           <t>RISKS / ACTIONS REGISTER</t>
         </is>
       </c>
-      <c r="D1" s="268" t="n"/>
-      <c r="E1" s="268" t="n"/>
-      <c r="F1" s="268" t="n"/>
-      <c r="G1" s="319" t="n"/>
-      <c r="H1" s="337" t="inlineStr">
+      <c r="D1" s="483" t="n"/>
+      <c r="E1" s="483" t="n"/>
+      <c r="F1" s="483" t="n"/>
+      <c r="G1" s="490" t="n"/>
+      <c r="H1" s="442" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="I1" s="338" t="inlineStr">
+      <c r="I1" s="443" t="inlineStr">
         <is>
           <t>FRM-209</t>
         </is>
       </c>
+      <c r="J1" s="402" t="n"/>
+      <c r="K1" s="402" t="n"/>
+      <c r="L1" s="402" t="n"/>
+      <c r="M1" s="402" t="n"/>
+      <c r="N1" s="402" t="n"/>
+      <c r="O1" s="402" t="n"/>
+      <c r="P1" s="402" t="n"/>
+      <c r="Q1" s="402" t="n"/>
+      <c r="R1" s="402" t="n"/>
+      <c r="S1" s="402" t="n"/>
+      <c r="T1" s="402" t="n"/>
+      <c r="U1" s="402" t="n"/>
+      <c r="V1" s="402" t="n"/>
+      <c r="W1" s="402" t="n"/>
+      <c r="X1" s="402" t="n"/>
+      <c r="Y1" s="402" t="n"/>
+      <c r="Z1" s="402" t="n"/>
+      <c r="AA1" s="402" t="n"/>
+      <c r="AB1" s="402" t="n"/>
+      <c r="AC1" s="402" t="n"/>
+      <c r="AD1" s="402" t="n"/>
+      <c r="AE1" s="402" t="n"/>
+      <c r="AF1" s="402" t="n"/>
+      <c r="AG1" s="402" t="n"/>
+      <c r="AH1" s="402" t="n"/>
+      <c r="AI1" s="402" t="n"/>
+      <c r="AJ1" s="402" t="n"/>
+      <c r="AK1" s="402" t="n"/>
+      <c r="AL1" s="402" t="n"/>
+      <c r="AM1" s="402" t="n"/>
+      <c r="AN1" s="402" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="B2" s="320" t="n"/>
-      <c r="C2" s="275" t="n"/>
-      <c r="G2" s="320" t="n"/>
-      <c r="H2" s="344" t="inlineStr">
+      <c r="A2" s="486" t="n"/>
+      <c r="B2" s="491" t="n"/>
+      <c r="C2" s="486" t="n"/>
+      <c r="G2" s="491" t="n"/>
+      <c r="H2" s="442" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="I2" s="345" t="inlineStr">
+      <c r="I2" s="443" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
+      <c r="J2" s="402" t="n"/>
+      <c r="K2" s="402" t="n"/>
+      <c r="L2" s="402" t="n"/>
+      <c r="M2" s="402" t="n"/>
+      <c r="N2" s="402" t="n"/>
+      <c r="O2" s="402" t="n"/>
+      <c r="P2" s="402" t="n"/>
+      <c r="Q2" s="402" t="n"/>
+      <c r="R2" s="402" t="n"/>
+      <c r="S2" s="402" t="n"/>
+      <c r="T2" s="402" t="n"/>
+      <c r="U2" s="402" t="n"/>
+      <c r="V2" s="402" t="n"/>
+      <c r="W2" s="402" t="n"/>
+      <c r="X2" s="402" t="n"/>
+      <c r="Y2" s="402" t="n"/>
+      <c r="Z2" s="402" t="n"/>
+      <c r="AA2" s="402" t="n"/>
+      <c r="AB2" s="402" t="n"/>
+      <c r="AC2" s="402" t="n"/>
+      <c r="AD2" s="402" t="n"/>
+      <c r="AE2" s="402" t="n"/>
+      <c r="AF2" s="402" t="n"/>
+      <c r="AG2" s="402" t="n"/>
+      <c r="AH2" s="402" t="n"/>
+      <c r="AI2" s="402" t="n"/>
+      <c r="AJ2" s="402" t="n"/>
+      <c r="AK2" s="402" t="n"/>
+      <c r="AL2" s="402" t="n"/>
+      <c r="AM2" s="402" t="n"/>
+      <c r="AN2" s="402" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="B3" s="320" t="n"/>
-      <c r="C3" s="282" t="n"/>
-      <c r="D3" s="283" t="n"/>
-      <c r="E3" s="283" t="n"/>
-      <c r="F3" s="283" t="n"/>
-      <c r="G3" s="287" t="n"/>
-      <c r="H3" s="344" t="inlineStr">
+      <c r="A3" s="486" t="n"/>
+      <c r="B3" s="491" t="n"/>
+      <c r="C3" s="489" t="n"/>
+      <c r="D3" s="487" t="n"/>
+      <c r="E3" s="487" t="n"/>
+      <c r="F3" s="487" t="n"/>
+      <c r="G3" s="488" t="n"/>
+      <c r="H3" s="442" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="I3" s="345" t="inlineStr">
+      <c r="I3" s="443" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
+      <c r="J3" s="402" t="n"/>
+      <c r="K3" s="402" t="n"/>
+      <c r="L3" s="402" t="n"/>
+      <c r="M3" s="402" t="n"/>
+      <c r="N3" s="402" t="n"/>
+      <c r="O3" s="402" t="n"/>
+      <c r="P3" s="402" t="n"/>
+      <c r="Q3" s="402" t="n"/>
+      <c r="R3" s="402" t="n"/>
+      <c r="S3" s="402" t="n"/>
+      <c r="T3" s="402" t="n"/>
+      <c r="U3" s="402" t="n"/>
+      <c r="V3" s="402" t="n"/>
+      <c r="W3" s="402" t="n"/>
+      <c r="X3" s="402" t="n"/>
+      <c r="Y3" s="402" t="n"/>
+      <c r="Z3" s="402" t="n"/>
+      <c r="AA3" s="402" t="n"/>
+      <c r="AB3" s="402" t="n"/>
+      <c r="AC3" s="402" t="n"/>
+      <c r="AD3" s="402" t="n"/>
+      <c r="AE3" s="402" t="n"/>
+      <c r="AF3" s="402" t="n"/>
+      <c r="AG3" s="402" t="n"/>
+      <c r="AH3" s="402" t="n"/>
+      <c r="AI3" s="402" t="n"/>
+      <c r="AJ3" s="402" t="n"/>
+      <c r="AK3" s="402" t="n"/>
+      <c r="AL3" s="402" t="n"/>
+      <c r="AM3" s="402" t="n"/>
+      <c r="AN3" s="402" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="B4" s="320" t="n"/>
-      <c r="C4" s="388" t="inlineStr">
+      <c r="A4" s="486" t="n"/>
+      <c r="B4" s="491" t="n"/>
+      <c r="C4" s="445" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="289" t="n"/>
-      <c r="E4" s="289" t="n"/>
-      <c r="F4" s="289" t="n"/>
-      <c r="G4" s="290" t="n"/>
-      <c r="H4" s="344" t="inlineStr">
+      <c r="D4" s="484" t="n"/>
+      <c r="E4" s="484" t="n"/>
+      <c r="F4" s="484" t="n"/>
+      <c r="G4" s="485" t="n"/>
+      <c r="H4" s="442" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="I4" s="345" t="inlineStr"/>
+      <c r="I4" s="443" t="inlineStr"/>
+      <c r="J4" s="402" t="n"/>
+      <c r="K4" s="402" t="n"/>
+      <c r="L4" s="402" t="n"/>
+      <c r="M4" s="402" t="n"/>
+      <c r="N4" s="402" t="n"/>
+      <c r="O4" s="402" t="n"/>
+      <c r="P4" s="402" t="n"/>
+      <c r="Q4" s="402" t="n"/>
+      <c r="R4" s="402" t="n"/>
+      <c r="S4" s="402" t="n"/>
+      <c r="T4" s="402" t="n"/>
+      <c r="U4" s="402" t="n"/>
+      <c r="V4" s="402" t="n"/>
+      <c r="W4" s="402" t="n"/>
+      <c r="X4" s="402" t="n"/>
+      <c r="Y4" s="402" t="n"/>
+      <c r="Z4" s="402" t="n"/>
+      <c r="AA4" s="402" t="n"/>
+      <c r="AB4" s="402" t="n"/>
+      <c r="AC4" s="402" t="n"/>
+      <c r="AD4" s="402" t="n"/>
+      <c r="AE4" s="402" t="n"/>
+      <c r="AF4" s="402" t="n"/>
+      <c r="AG4" s="402" t="n"/>
+      <c r="AH4" s="402" t="n"/>
+      <c r="AI4" s="402" t="n"/>
+      <c r="AJ4" s="402" t="n"/>
+      <c r="AK4" s="402" t="n"/>
+      <c r="AL4" s="402" t="n"/>
+      <c r="AM4" s="402" t="n"/>
+      <c r="AN4" s="402" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="282" t="n"/>
-      <c r="B5" s="287" t="n"/>
-      <c r="C5" s="389" t="inlineStr">
+      <c r="A5" s="489" t="n"/>
+      <c r="B5" s="488" t="n"/>
+      <c r="C5" s="446" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="289" t="n"/>
-      <c r="E5" s="289" t="n"/>
-      <c r="F5" s="289" t="n"/>
-      <c r="G5" s="290" t="n"/>
-      <c r="H5" s="357" t="inlineStr">
+      <c r="D5" s="484" t="n"/>
+      <c r="E5" s="484" t="n"/>
+      <c r="F5" s="484" t="n"/>
+      <c r="G5" s="485" t="n"/>
+      <c r="H5" s="447" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="I5" s="358" t="inlineStr"/>
+      <c r="I5" s="448" t="inlineStr"/>
+      <c r="J5" s="402" t="n"/>
+      <c r="K5" s="402" t="n"/>
+      <c r="L5" s="402" t="n"/>
+      <c r="M5" s="402" t="n"/>
+      <c r="N5" s="402" t="n"/>
+      <c r="O5" s="402" t="n"/>
+      <c r="P5" s="402" t="n"/>
+      <c r="Q5" s="402" t="n"/>
+      <c r="R5" s="402" t="n"/>
+      <c r="S5" s="402" t="n"/>
+      <c r="T5" s="402" t="n"/>
+      <c r="U5" s="402" t="n"/>
+      <c r="V5" s="402" t="n"/>
+      <c r="W5" s="402" t="n"/>
+      <c r="X5" s="402" t="n"/>
+      <c r="Y5" s="402" t="n"/>
+      <c r="Z5" s="402" t="n"/>
+      <c r="AA5" s="402" t="n"/>
+      <c r="AB5" s="402" t="n"/>
+      <c r="AC5" s="402" t="n"/>
+      <c r="AD5" s="402" t="n"/>
+      <c r="AE5" s="402" t="n"/>
+      <c r="AF5" s="402" t="n"/>
+      <c r="AG5" s="402" t="n"/>
+      <c r="AH5" s="402" t="n"/>
+      <c r="AI5" s="402" t="n"/>
+      <c r="AJ5" s="402" t="n"/>
+      <c r="AK5" s="402" t="n"/>
+      <c r="AL5" s="402" t="n"/>
+      <c r="AM5" s="402" t="n"/>
+      <c r="AN5" s="402" t="n"/>
     </row>
     <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="386" t="n"/>
-      <c r="B6" s="289" t="n"/>
-      <c r="C6" s="289" t="n"/>
-      <c r="D6" s="289" t="n"/>
-      <c r="E6" s="289" t="n"/>
-      <c r="F6" s="289" t="n"/>
-      <c r="G6" s="289" t="n"/>
-      <c r="H6" s="289" t="n"/>
-      <c r="I6" s="290" t="n"/>
+      <c r="A6" s="449" t="n"/>
+      <c r="B6" s="482" t="n"/>
+      <c r="C6" s="482" t="n"/>
+      <c r="D6" s="482" t="n"/>
+      <c r="E6" s="482" t="n"/>
+      <c r="F6" s="482" t="n"/>
+      <c r="G6" s="482" t="n"/>
+      <c r="H6" s="482" t="n"/>
+      <c r="I6" s="482" t="n"/>
+      <c r="J6" s="410" t="n"/>
+      <c r="K6" s="410" t="n"/>
+      <c r="L6" s="410" t="n"/>
+      <c r="M6" s="410" t="n"/>
+      <c r="N6" s="410" t="n"/>
+      <c r="O6" s="410" t="n"/>
+      <c r="P6" s="410" t="n"/>
+      <c r="Q6" s="410" t="n"/>
+      <c r="R6" s="410" t="n"/>
+      <c r="S6" s="410" t="n"/>
+      <c r="T6" s="410" t="n"/>
+      <c r="U6" s="410" t="n"/>
+      <c r="V6" s="410" t="n"/>
+      <c r="W6" s="410" t="n"/>
+      <c r="X6" s="410" t="n"/>
+      <c r="Y6" s="410" t="n"/>
+      <c r="Z6" s="410" t="n"/>
+      <c r="AA6" s="410" t="n"/>
+      <c r="AB6" s="410" t="n"/>
+      <c r="AC6" s="410" t="n"/>
+      <c r="AD6" s="410" t="n"/>
+      <c r="AE6" s="410" t="n"/>
+      <c r="AF6" s="410" t="n"/>
+      <c r="AG6" s="410" t="n"/>
+      <c r="AH6" s="410" t="n"/>
+      <c r="AI6" s="410" t="n"/>
+      <c r="AJ6" s="410" t="n"/>
+      <c r="AK6" s="410" t="n"/>
+      <c r="AL6" s="410" t="n"/>
+      <c r="AM6" s="410" t="n"/>
+      <c r="AN6" s="410" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="390" t="inlineStr">
+      <c r="A7" s="450" t="inlineStr">
         <is>
           <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
         </is>
       </c>
-      <c r="B7" s="289" t="n"/>
-      <c r="C7" s="289" t="n"/>
-      <c r="D7" s="289" t="n"/>
-      <c r="E7" s="289" t="n"/>
-      <c r="F7" s="289" t="n"/>
-      <c r="G7" s="289" t="n"/>
-      <c r="H7" s="289" t="n"/>
-      <c r="I7" s="290" t="n"/>
+      <c r="B7" s="484" t="n"/>
+      <c r="C7" s="484" t="n"/>
+      <c r="D7" s="484" t="n"/>
+      <c r="E7" s="484" t="n"/>
+      <c r="F7" s="484" t="n"/>
+      <c r="G7" s="484" t="n"/>
+      <c r="H7" s="484" t="n"/>
+      <c r="I7" s="485" t="n"/>
+      <c r="J7" s="402" t="n"/>
+      <c r="K7" s="402" t="n"/>
+      <c r="L7" s="402" t="n"/>
+      <c r="M7" s="402" t="n"/>
+      <c r="N7" s="402" t="n"/>
+      <c r="O7" s="402" t="n"/>
+      <c r="P7" s="402" t="n"/>
+      <c r="Q7" s="402" t="n"/>
+      <c r="R7" s="402" t="n"/>
+      <c r="S7" s="402" t="n"/>
+      <c r="T7" s="402" t="n"/>
+      <c r="U7" s="402" t="n"/>
+      <c r="V7" s="402" t="n"/>
+      <c r="W7" s="402" t="n"/>
+      <c r="X7" s="402" t="n"/>
+      <c r="Y7" s="402" t="n"/>
+      <c r="Z7" s="402" t="n"/>
+      <c r="AA7" s="402" t="n"/>
+      <c r="AB7" s="402" t="n"/>
+      <c r="AC7" s="402" t="n"/>
+      <c r="AD7" s="402" t="n"/>
+      <c r="AE7" s="402" t="n"/>
+      <c r="AF7" s="402" t="n"/>
+      <c r="AG7" s="402" t="n"/>
+      <c r="AH7" s="402" t="n"/>
+      <c r="AI7" s="402" t="n"/>
+      <c r="AJ7" s="402" t="n"/>
+      <c r="AK7" s="402" t="n"/>
+      <c r="AL7" s="402" t="n"/>
+      <c r="AM7" s="402" t="n"/>
+      <c r="AN7" s="402" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="391" t="inlineStr">
+      <c r="A8" s="447" t="inlineStr">
         <is>
           <t>Parent Form</t>
         </is>
       </c>
-      <c r="B8" s="290" t="n"/>
-      <c r="C8" s="392" t="inlineStr">
+      <c r="B8" s="474" t="n"/>
+      <c r="C8" s="448" t="inlineStr">
         <is>
           <t>FRM-209 · HIGH-RISK JOB READINESS REVIEW</t>
         </is>
       </c>
-      <c r="D8" s="289" t="n"/>
-      <c r="E8" s="290" t="n"/>
-      <c r="F8" s="391" t="inlineStr">
+      <c r="D8" s="473" t="n"/>
+      <c r="E8" s="474" t="n"/>
+      <c r="F8" s="447" t="inlineStr">
         <is>
           <t>Support Tab</t>
         </is>
       </c>
-      <c r="G8" s="290" t="n"/>
-      <c r="H8" s="392" t="inlineStr">
+      <c r="G8" s="474" t="n"/>
+      <c r="H8" s="448" t="inlineStr">
         <is>
           <t>RISKS_ACTIONS</t>
         </is>
       </c>
-      <c r="I8" s="290" t="n"/>
+      <c r="I8" s="474" t="n"/>
+      <c r="J8" s="436" t="n"/>
+      <c r="K8" s="436" t="n"/>
+      <c r="L8" s="436" t="n"/>
+      <c r="M8" s="436" t="n"/>
+      <c r="N8" s="436" t="n"/>
+      <c r="O8" s="436" t="n"/>
+      <c r="P8" s="436" t="n"/>
+      <c r="Q8" s="436" t="n"/>
+      <c r="R8" s="436" t="n"/>
+      <c r="S8" s="436" t="n"/>
+      <c r="T8" s="436" t="n"/>
+      <c r="U8" s="436" t="n"/>
+      <c r="V8" s="436" t="n"/>
+      <c r="W8" s="436" t="n"/>
+      <c r="X8" s="436" t="n"/>
+      <c r="Y8" s="436" t="n"/>
+      <c r="Z8" s="436" t="n"/>
+      <c r="AA8" s="436" t="n"/>
+      <c r="AB8" s="436" t="n"/>
+      <c r="AC8" s="436" t="n"/>
+      <c r="AD8" s="436" t="n"/>
+      <c r="AE8" s="436" t="n"/>
+      <c r="AF8" s="436" t="n"/>
+      <c r="AG8" s="436" t="n"/>
+      <c r="AH8" s="436" t="n"/>
+      <c r="AI8" s="436" t="n"/>
+      <c r="AJ8" s="436" t="n"/>
+      <c r="AK8" s="436" t="n"/>
+      <c r="AL8" s="436" t="n"/>
+      <c r="AM8" s="436" t="n"/>
+      <c r="AN8" s="436" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="391" t="inlineStr">
+      <c r="A9" s="447" t="inlineStr">
         <is>
           <t>Tab Purpose</t>
         </is>
       </c>
-      <c r="B9" s="290" t="n"/>
-      <c r="C9" s="392" t="inlineStr">
+      <c r="B9" s="474" t="n"/>
+      <c r="C9" s="448" t="inlineStr">
         <is>
           <t>One line per material, capacity, quality or customer-risk condition.</t>
         </is>
       </c>
-      <c r="D9" s="289" t="n"/>
-      <c r="E9" s="290" t="n"/>
-      <c r="F9" s="391" t="inlineStr">
+      <c r="D9" s="473" t="n"/>
+      <c r="E9" s="474" t="n"/>
+      <c r="F9" s="447" t="inlineStr">
         <is>
           <t>Working Owner</t>
         </is>
       </c>
-      <c r="G9" s="290" t="n"/>
-      <c r="H9" s="392" t="inlineStr"/>
-      <c r="I9" s="290" t="n"/>
+      <c r="G9" s="474" t="n"/>
+      <c r="H9" s="448" t="inlineStr"/>
+      <c r="I9" s="474" t="n"/>
+      <c r="J9" s="436" t="n"/>
+      <c r="K9" s="436" t="n"/>
+      <c r="L9" s="436" t="n"/>
+      <c r="M9" s="436" t="n"/>
+      <c r="N9" s="436" t="n"/>
+      <c r="O9" s="436" t="n"/>
+      <c r="P9" s="436" t="n"/>
+      <c r="Q9" s="436" t="n"/>
+      <c r="R9" s="436" t="n"/>
+      <c r="S9" s="436" t="n"/>
+      <c r="T9" s="436" t="n"/>
+      <c r="U9" s="436" t="n"/>
+      <c r="V9" s="436" t="n"/>
+      <c r="W9" s="436" t="n"/>
+      <c r="X9" s="436" t="n"/>
+      <c r="Y9" s="436" t="n"/>
+      <c r="Z9" s="436" t="n"/>
+      <c r="AA9" s="436" t="n"/>
+      <c r="AB9" s="436" t="n"/>
+      <c r="AC9" s="436" t="n"/>
+      <c r="AD9" s="436" t="n"/>
+      <c r="AE9" s="436" t="n"/>
+      <c r="AF9" s="436" t="n"/>
+      <c r="AG9" s="436" t="n"/>
+      <c r="AH9" s="436" t="n"/>
+      <c r="AI9" s="436" t="n"/>
+      <c r="AJ9" s="436" t="n"/>
+      <c r="AK9" s="436" t="n"/>
+      <c r="AL9" s="436" t="n"/>
+      <c r="AM9" s="436" t="n"/>
+      <c r="AN9" s="436" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="391" t="inlineStr">
+      <c r="A10" s="447" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B10" s="290" t="n"/>
-      <c r="C10" s="392" t="inlineStr">
+      <c r="B10" s="474" t="n"/>
+      <c r="C10" s="448" t="inlineStr">
         <is>
           <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
         </is>
       </c>
-      <c r="D10" s="289" t="n"/>
-      <c r="E10" s="290" t="n"/>
-      <c r="F10" s="391" t="inlineStr">
+      <c r="D10" s="473" t="n"/>
+      <c r="E10" s="474" t="n"/>
+      <c r="F10" s="447" t="inlineStr">
         <is>
           <t>Reviewed By</t>
         </is>
       </c>
-      <c r="G10" s="290" t="n"/>
-      <c r="H10" s="392" t="inlineStr"/>
-      <c r="I10" s="290" t="n"/>
+      <c r="G10" s="474" t="n"/>
+      <c r="H10" s="448" t="inlineStr"/>
+      <c r="I10" s="474" t="n"/>
+      <c r="J10" s="436" t="n"/>
+      <c r="K10" s="436" t="n"/>
+      <c r="L10" s="436" t="n"/>
+      <c r="M10" s="436" t="n"/>
+      <c r="N10" s="436" t="n"/>
+      <c r="O10" s="436" t="n"/>
+      <c r="P10" s="436" t="n"/>
+      <c r="Q10" s="436" t="n"/>
+      <c r="R10" s="436" t="n"/>
+      <c r="S10" s="436" t="n"/>
+      <c r="T10" s="436" t="n"/>
+      <c r="U10" s="436" t="n"/>
+      <c r="V10" s="436" t="n"/>
+      <c r="W10" s="436" t="n"/>
+      <c r="X10" s="436" t="n"/>
+      <c r="Y10" s="436" t="n"/>
+      <c r="Z10" s="436" t="n"/>
+      <c r="AA10" s="436" t="n"/>
+      <c r="AB10" s="436" t="n"/>
+      <c r="AC10" s="436" t="n"/>
+      <c r="AD10" s="436" t="n"/>
+      <c r="AE10" s="436" t="n"/>
+      <c r="AF10" s="436" t="n"/>
+      <c r="AG10" s="436" t="n"/>
+      <c r="AH10" s="436" t="n"/>
+      <c r="AI10" s="436" t="n"/>
+      <c r="AJ10" s="436" t="n"/>
+      <c r="AK10" s="436" t="n"/>
+      <c r="AL10" s="436" t="n"/>
+      <c r="AM10" s="436" t="n"/>
+      <c r="AN10" s="436" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="391" t="inlineStr">
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="447" t="inlineStr">
         <is>
           <t>Update Trigger</t>
         </is>
       </c>
-      <c r="B11" s="290" t="n"/>
-      <c r="C11" s="392" t="inlineStr">
+      <c r="B11" s="468" t="n"/>
+      <c r="C11" s="448" t="inlineStr">
         <is>
           <t>Update when the linked review, evidence or follow-up status changes.</t>
         </is>
       </c>
-      <c r="D11" s="289" t="n"/>
-      <c r="E11" s="290" t="n"/>
-      <c r="F11" s="391" t="inlineStr">
+      <c r="D11" s="467" t="n"/>
+      <c r="E11" s="468" t="n"/>
+      <c r="F11" s="447" t="inlineStr">
         <is>
           <t>Data Structure</t>
         </is>
       </c>
-      <c r="G11" s="290" t="n"/>
-      <c r="H11" s="392" t="inlineStr">
+      <c r="G11" s="468" t="n"/>
+      <c r="H11" s="448" t="inlineStr">
         <is>
           <t>Structured Excel Table with filters and print-title rows.</t>
         </is>
       </c>
-      <c r="I11" s="290" t="n"/>
+      <c r="I11" s="468" t="n"/>
+      <c r="J11" s="402" t="n"/>
+      <c r="K11" s="402" t="n"/>
+      <c r="L11" s="402" t="n"/>
+      <c r="M11" s="402" t="n"/>
+      <c r="N11" s="402" t="n"/>
+      <c r="O11" s="402" t="n"/>
+      <c r="P11" s="402" t="n"/>
+      <c r="Q11" s="402" t="n"/>
+      <c r="R11" s="402" t="n"/>
+      <c r="S11" s="402" t="n"/>
+      <c r="T11" s="402" t="n"/>
+      <c r="U11" s="402" t="n"/>
+      <c r="V11" s="402" t="n"/>
+      <c r="W11" s="402" t="n"/>
+      <c r="X11" s="402" t="n"/>
+      <c r="Y11" s="402" t="n"/>
+      <c r="Z11" s="402" t="n"/>
+      <c r="AA11" s="402" t="n"/>
+      <c r="AB11" s="402" t="n"/>
+      <c r="AC11" s="402" t="n"/>
+      <c r="AD11" s="402" t="n"/>
+      <c r="AE11" s="402" t="n"/>
+      <c r="AF11" s="402" t="n"/>
+      <c r="AG11" s="402" t="n"/>
+      <c r="AH11" s="402" t="n"/>
+      <c r="AI11" s="402" t="n"/>
+      <c r="AJ11" s="402" t="n"/>
+      <c r="AK11" s="402" t="n"/>
+      <c r="AL11" s="402" t="n"/>
+      <c r="AM11" s="402" t="n"/>
+      <c r="AN11" s="402" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="391" t="inlineStr">
+      <c r="A12" s="447" t="inlineStr">
         <is>
           <t>Retention Rule</t>
         </is>
       </c>
-      <c r="B12" s="290" t="n"/>
-      <c r="C12" s="392" t="inlineStr">
+      <c r="B12" s="474" t="n"/>
+      <c r="C12" s="448" t="inlineStr">
         <is>
           <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
         </is>
       </c>
-      <c r="D12" s="289" t="n"/>
-      <c r="E12" s="290" t="n"/>
-      <c r="F12" s="391" t="inlineStr">
+      <c r="D12" s="473" t="n"/>
+      <c r="E12" s="474" t="n"/>
+      <c r="F12" s="447" t="inlineStr">
         <is>
           <t>Controlled Status</t>
         </is>
       </c>
-      <c r="G12" s="290" t="n"/>
-      <c r="H12" s="392" t="inlineStr">
+      <c r="G12" s="474" t="n"/>
+      <c r="H12" s="448" t="inlineStr">
         <is>
           <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
         </is>
       </c>
-      <c r="I12" s="290" t="n"/>
+      <c r="I12" s="474" t="n"/>
+      <c r="J12" s="436" t="n"/>
+      <c r="K12" s="436" t="n"/>
+      <c r="L12" s="436" t="n"/>
+      <c r="M12" s="436" t="n"/>
+      <c r="N12" s="436" t="n"/>
+      <c r="O12" s="436" t="n"/>
+      <c r="P12" s="436" t="n"/>
+      <c r="Q12" s="436" t="n"/>
+      <c r="R12" s="436" t="n"/>
+      <c r="S12" s="436" t="n"/>
+      <c r="T12" s="436" t="n"/>
+      <c r="U12" s="436" t="n"/>
+      <c r="V12" s="436" t="n"/>
+      <c r="W12" s="436" t="n"/>
+      <c r="X12" s="436" t="n"/>
+      <c r="Y12" s="436" t="n"/>
+      <c r="Z12" s="436" t="n"/>
+      <c r="AA12" s="436" t="n"/>
+      <c r="AB12" s="436" t="n"/>
+      <c r="AC12" s="436" t="n"/>
+      <c r="AD12" s="436" t="n"/>
+      <c r="AE12" s="436" t="n"/>
+      <c r="AF12" s="436" t="n"/>
+      <c r="AG12" s="436" t="n"/>
+      <c r="AH12" s="436" t="n"/>
+      <c r="AI12" s="436" t="n"/>
+      <c r="AJ12" s="436" t="n"/>
+      <c r="AK12" s="436" t="n"/>
+      <c r="AL12" s="436" t="n"/>
+      <c r="AM12" s="436" t="n"/>
+      <c r="AN12" s="436" t="n"/>
     </row>
     <row r="13" ht="4" customHeight="1">
-      <c r="A13" s="386" t="n"/>
-      <c r="B13" s="289" t="n"/>
-      <c r="C13" s="289" t="n"/>
-      <c r="D13" s="289" t="n"/>
-      <c r="E13" s="289" t="n"/>
-      <c r="F13" s="289" t="n"/>
-      <c r="G13" s="289" t="n"/>
-      <c r="H13" s="289" t="n"/>
-      <c r="I13" s="290" t="n"/>
+      <c r="A13" s="449" t="n"/>
+      <c r="B13" s="482" t="n"/>
+      <c r="C13" s="482" t="n"/>
+      <c r="D13" s="482" t="n"/>
+      <c r="E13" s="482" t="n"/>
+      <c r="F13" s="482" t="n"/>
+      <c r="G13" s="482" t="n"/>
+      <c r="H13" s="482" t="n"/>
+      <c r="I13" s="482" t="n"/>
+      <c r="J13" s="410" t="n"/>
+      <c r="K13" s="410" t="n"/>
+      <c r="L13" s="410" t="n"/>
+      <c r="M13" s="410" t="n"/>
+      <c r="N13" s="410" t="n"/>
+      <c r="O13" s="410" t="n"/>
+      <c r="P13" s="410" t="n"/>
+      <c r="Q13" s="410" t="n"/>
+      <c r="R13" s="410" t="n"/>
+      <c r="S13" s="410" t="n"/>
+      <c r="T13" s="410" t="n"/>
+      <c r="U13" s="410" t="n"/>
+      <c r="V13" s="410" t="n"/>
+      <c r="W13" s="410" t="n"/>
+      <c r="X13" s="410" t="n"/>
+      <c r="Y13" s="410" t="n"/>
+      <c r="Z13" s="410" t="n"/>
+      <c r="AA13" s="410" t="n"/>
+      <c r="AB13" s="410" t="n"/>
+      <c r="AC13" s="410" t="n"/>
+      <c r="AD13" s="410" t="n"/>
+      <c r="AE13" s="410" t="n"/>
+      <c r="AF13" s="410" t="n"/>
+      <c r="AG13" s="410" t="n"/>
+      <c r="AH13" s="410" t="n"/>
+      <c r="AI13" s="410" t="n"/>
+      <c r="AJ13" s="410" t="n"/>
+      <c r="AK13" s="410" t="n"/>
+      <c r="AL13" s="410" t="n"/>
+      <c r="AM13" s="410" t="n"/>
+      <c r="AN13" s="410" t="n"/>
     </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="390" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="450" t="inlineStr">
         <is>
           <t>2.  WORKING TABLE / DETAIL LINES</t>
         </is>
       </c>
-      <c r="B14" s="289" t="n"/>
-      <c r="C14" s="289" t="n"/>
-      <c r="D14" s="289" t="n"/>
-      <c r="E14" s="289" t="n"/>
-      <c r="F14" s="289" t="n"/>
-      <c r="G14" s="289" t="n"/>
-      <c r="H14" s="289" t="n"/>
-      <c r="I14" s="290" t="n"/>
+      <c r="B14" s="473" t="n"/>
+      <c r="C14" s="473" t="n"/>
+      <c r="D14" s="473" t="n"/>
+      <c r="E14" s="473" t="n"/>
+      <c r="F14" s="473" t="n"/>
+      <c r="G14" s="473" t="n"/>
+      <c r="H14" s="473" t="n"/>
+      <c r="I14" s="474" t="n"/>
+      <c r="J14" s="436" t="n"/>
+      <c r="K14" s="436" t="n"/>
+      <c r="L14" s="436" t="n"/>
+      <c r="M14" s="436" t="n"/>
+      <c r="N14" s="436" t="n"/>
+      <c r="O14" s="436" t="n"/>
+      <c r="P14" s="436" t="n"/>
+      <c r="Q14" s="436" t="n"/>
+      <c r="R14" s="436" t="n"/>
+      <c r="S14" s="436" t="n"/>
+      <c r="T14" s="436" t="n"/>
+      <c r="U14" s="436" t="n"/>
+      <c r="V14" s="436" t="n"/>
+      <c r="W14" s="436" t="n"/>
+      <c r="X14" s="436" t="n"/>
+      <c r="Y14" s="436" t="n"/>
+      <c r="Z14" s="436" t="n"/>
+      <c r="AA14" s="436" t="n"/>
+      <c r="AB14" s="436" t="n"/>
+      <c r="AC14" s="436" t="n"/>
+      <c r="AD14" s="436" t="n"/>
+      <c r="AE14" s="436" t="n"/>
+      <c r="AF14" s="436" t="n"/>
+      <c r="AG14" s="436" t="n"/>
+      <c r="AH14" s="436" t="n"/>
+      <c r="AI14" s="436" t="n"/>
+      <c r="AJ14" s="436" t="n"/>
+      <c r="AK14" s="436" t="n"/>
+      <c r="AL14" s="436" t="n"/>
+      <c r="AM14" s="436" t="n"/>
+      <c r="AN14" s="436" t="n"/>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="393" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="451" t="inlineStr">
         <is>
           <t>One line per material, capacity, quality or customer-risk condition.</t>
         </is>
       </c>
-      <c r="B15" s="289" t="n"/>
-      <c r="C15" s="289" t="n"/>
-      <c r="D15" s="289" t="n"/>
-      <c r="E15" s="289" t="n"/>
-      <c r="F15" s="289" t="n"/>
-      <c r="G15" s="289" t="n"/>
-      <c r="H15" s="289" t="n"/>
-      <c r="I15" s="290" t="n"/>
+      <c r="B15" s="473" t="n"/>
+      <c r="C15" s="473" t="n"/>
+      <c r="D15" s="473" t="n"/>
+      <c r="E15" s="473" t="n"/>
+      <c r="F15" s="473" t="n"/>
+      <c r="G15" s="473" t="n"/>
+      <c r="H15" s="473" t="n"/>
+      <c r="I15" s="474" t="n"/>
+      <c r="J15" s="436" t="n"/>
+      <c r="K15" s="436" t="n"/>
+      <c r="L15" s="436" t="n"/>
+      <c r="M15" s="436" t="n"/>
+      <c r="N15" s="436" t="n"/>
+      <c r="O15" s="436" t="n"/>
+      <c r="P15" s="436" t="n"/>
+      <c r="Q15" s="436" t="n"/>
+      <c r="R15" s="436" t="n"/>
+      <c r="S15" s="436" t="n"/>
+      <c r="T15" s="436" t="n"/>
+      <c r="U15" s="436" t="n"/>
+      <c r="V15" s="436" t="n"/>
+      <c r="W15" s="436" t="n"/>
+      <c r="X15" s="436" t="n"/>
+      <c r="Y15" s="436" t="n"/>
+      <c r="Z15" s="436" t="n"/>
+      <c r="AA15" s="436" t="n"/>
+      <c r="AB15" s="436" t="n"/>
+      <c r="AC15" s="436" t="n"/>
+      <c r="AD15" s="436" t="n"/>
+      <c r="AE15" s="436" t="n"/>
+      <c r="AF15" s="436" t="n"/>
+      <c r="AG15" s="436" t="n"/>
+      <c r="AH15" s="436" t="n"/>
+      <c r="AI15" s="436" t="n"/>
+      <c r="AJ15" s="436" t="n"/>
+      <c r="AK15" s="436" t="n"/>
+      <c r="AL15" s="436" t="n"/>
+      <c r="AM15" s="436" t="n"/>
+      <c r="AN15" s="436" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="373" t="inlineStr">
+      <c r="A16" s="452" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B16" s="374" t="inlineStr">
+      <c r="B16" s="452" t="inlineStr">
         <is>
           <t>Risk / Readiness Gap</t>
         </is>
       </c>
-      <c r="C16" s="374" t="inlineStr">
+      <c r="C16" s="452" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="D16" s="374" t="inlineStr">
+      <c r="D16" s="452" t="inlineStr">
         <is>
           <t>Containment / Action</t>
         </is>
       </c>
-      <c r="E16" s="374" t="inlineStr">
+      <c r="E16" s="452" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F16" s="374" t="inlineStr">
+      <c r="F16" s="452" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="G16" s="374" t="inlineStr">
+      <c r="G16" s="452" t="inlineStr">
         <is>
           <t>Escalation</t>
         </is>
       </c>
-      <c r="H16" s="374" t="inlineStr">
+      <c r="H16" s="452" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I16" s="375" t="inlineStr">
+      <c r="I16" s="421" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
+      <c r="J16" s="436" t="n"/>
+      <c r="K16" s="436" t="n"/>
+      <c r="L16" s="436" t="n"/>
+      <c r="M16" s="436" t="n"/>
+      <c r="N16" s="436" t="n"/>
+      <c r="O16" s="436" t="n"/>
+      <c r="P16" s="436" t="n"/>
+      <c r="Q16" s="436" t="n"/>
+      <c r="R16" s="436" t="n"/>
+      <c r="S16" s="436" t="n"/>
+      <c r="T16" s="436" t="n"/>
+      <c r="U16" s="436" t="n"/>
+      <c r="V16" s="436" t="n"/>
+      <c r="W16" s="436" t="n"/>
+      <c r="X16" s="436" t="n"/>
+      <c r="Y16" s="436" t="n"/>
+      <c r="Z16" s="436" t="n"/>
+      <c r="AA16" s="436" t="n"/>
+      <c r="AB16" s="436" t="n"/>
+      <c r="AC16" s="436" t="n"/>
+      <c r="AD16" s="436" t="n"/>
+      <c r="AE16" s="436" t="n"/>
+      <c r="AF16" s="436" t="n"/>
+      <c r="AG16" s="436" t="n"/>
+      <c r="AH16" s="436" t="n"/>
+      <c r="AI16" s="436" t="n"/>
+      <c r="AJ16" s="436" t="n"/>
+      <c r="AK16" s="436" t="n"/>
+      <c r="AL16" s="436" t="n"/>
+      <c r="AM16" s="436" t="n"/>
+      <c r="AN16" s="436" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="376">
+      <c r="A17" s="453">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B17" s="377" t="n"/>
-      <c r="C17" s="377" t="n"/>
-      <c r="D17" s="377" t="n"/>
-      <c r="E17" s="377" t="n"/>
-      <c r="F17" s="378" t="n"/>
-      <c r="G17" s="377" t="n"/>
-      <c r="H17" s="377" t="n"/>
-      <c r="I17" s="345" t="n"/>
+      <c r="B17" s="454" t="n"/>
+      <c r="C17" s="454" t="n"/>
+      <c r="D17" s="454" t="n"/>
+      <c r="E17" s="454" t="n"/>
+      <c r="F17" s="455" t="n"/>
+      <c r="G17" s="454" t="n"/>
+      <c r="H17" s="454" t="n"/>
+      <c r="I17" s="443" t="n"/>
+      <c r="J17" s="436" t="n"/>
+      <c r="K17" s="436" t="n"/>
+      <c r="L17" s="436" t="n"/>
+      <c r="M17" s="436" t="n"/>
+      <c r="N17" s="436" t="n"/>
+      <c r="O17" s="436" t="n"/>
+      <c r="P17" s="436" t="n"/>
+      <c r="Q17" s="436" t="n"/>
+      <c r="R17" s="436" t="n"/>
+      <c r="S17" s="436" t="n"/>
+      <c r="T17" s="436" t="n"/>
+      <c r="U17" s="436" t="n"/>
+      <c r="V17" s="436" t="n"/>
+      <c r="W17" s="436" t="n"/>
+      <c r="X17" s="436" t="n"/>
+      <c r="Y17" s="436" t="n"/>
+      <c r="Z17" s="436" t="n"/>
+      <c r="AA17" s="436" t="n"/>
+      <c r="AB17" s="436" t="n"/>
+      <c r="AC17" s="436" t="n"/>
+      <c r="AD17" s="436" t="n"/>
+      <c r="AE17" s="436" t="n"/>
+      <c r="AF17" s="436" t="n"/>
+      <c r="AG17" s="436" t="n"/>
+      <c r="AH17" s="436" t="n"/>
+      <c r="AI17" s="436" t="n"/>
+      <c r="AJ17" s="436" t="n"/>
+      <c r="AK17" s="436" t="n"/>
+      <c r="AL17" s="436" t="n"/>
+      <c r="AM17" s="436" t="n"/>
+      <c r="AN17" s="436" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="376">
+      <c r="A18" s="453">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B18" s="379" t="n"/>
-      <c r="C18" s="379" t="n"/>
-      <c r="D18" s="379" t="n"/>
-      <c r="E18" s="379" t="n"/>
-      <c r="F18" s="380" t="n"/>
-      <c r="G18" s="379" t="n"/>
-      <c r="H18" s="379" t="n"/>
-      <c r="I18" s="381" t="n"/>
+      <c r="B18" s="456" t="n"/>
+      <c r="C18" s="456" t="n"/>
+      <c r="D18" s="456" t="n"/>
+      <c r="E18" s="456" t="n"/>
+      <c r="F18" s="457" t="n"/>
+      <c r="G18" s="456" t="n"/>
+      <c r="H18" s="456" t="n"/>
+      <c r="I18" s="458" t="n"/>
+      <c r="J18" s="436" t="n"/>
+      <c r="K18" s="436" t="n"/>
+      <c r="L18" s="436" t="n"/>
+      <c r="M18" s="436" t="n"/>
+      <c r="N18" s="436" t="n"/>
+      <c r="O18" s="436" t="n"/>
+      <c r="P18" s="436" t="n"/>
+      <c r="Q18" s="436" t="n"/>
+      <c r="R18" s="436" t="n"/>
+      <c r="S18" s="436" t="n"/>
+      <c r="T18" s="436" t="n"/>
+      <c r="U18" s="436" t="n"/>
+      <c r="V18" s="436" t="n"/>
+      <c r="W18" s="436" t="n"/>
+      <c r="X18" s="436" t="n"/>
+      <c r="Y18" s="436" t="n"/>
+      <c r="Z18" s="436" t="n"/>
+      <c r="AA18" s="436" t="n"/>
+      <c r="AB18" s="436" t="n"/>
+      <c r="AC18" s="436" t="n"/>
+      <c r="AD18" s="436" t="n"/>
+      <c r="AE18" s="436" t="n"/>
+      <c r="AF18" s="436" t="n"/>
+      <c r="AG18" s="436" t="n"/>
+      <c r="AH18" s="436" t="n"/>
+      <c r="AI18" s="436" t="n"/>
+      <c r="AJ18" s="436" t="n"/>
+      <c r="AK18" s="436" t="n"/>
+      <c r="AL18" s="436" t="n"/>
+      <c r="AM18" s="436" t="n"/>
+      <c r="AN18" s="436" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="376">
+      <c r="A19" s="453">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B19" s="377" t="n"/>
-      <c r="C19" s="377" t="n"/>
-      <c r="D19" s="377" t="n"/>
-      <c r="E19" s="377" t="n"/>
-      <c r="F19" s="378" t="n"/>
-      <c r="G19" s="377" t="n"/>
-      <c r="H19" s="377" t="n"/>
-      <c r="I19" s="345" t="n"/>
+      <c r="B19" s="454" t="n"/>
+      <c r="C19" s="454" t="n"/>
+      <c r="D19" s="454" t="n"/>
+      <c r="E19" s="454" t="n"/>
+      <c r="F19" s="455" t="n"/>
+      <c r="G19" s="454" t="n"/>
+      <c r="H19" s="454" t="n"/>
+      <c r="I19" s="443" t="n"/>
+      <c r="J19" s="436" t="n"/>
+      <c r="K19" s="436" t="n"/>
+      <c r="L19" s="436" t="n"/>
+      <c r="M19" s="436" t="n"/>
+      <c r="N19" s="436" t="n"/>
+      <c r="O19" s="436" t="n"/>
+      <c r="P19" s="436" t="n"/>
+      <c r="Q19" s="436" t="n"/>
+      <c r="R19" s="436" t="n"/>
+      <c r="S19" s="436" t="n"/>
+      <c r="T19" s="436" t="n"/>
+      <c r="U19" s="436" t="n"/>
+      <c r="V19" s="436" t="n"/>
+      <c r="W19" s="436" t="n"/>
+      <c r="X19" s="436" t="n"/>
+      <c r="Y19" s="436" t="n"/>
+      <c r="Z19" s="436" t="n"/>
+      <c r="AA19" s="436" t="n"/>
+      <c r="AB19" s="436" t="n"/>
+      <c r="AC19" s="436" t="n"/>
+      <c r="AD19" s="436" t="n"/>
+      <c r="AE19" s="436" t="n"/>
+      <c r="AF19" s="436" t="n"/>
+      <c r="AG19" s="436" t="n"/>
+      <c r="AH19" s="436" t="n"/>
+      <c r="AI19" s="436" t="n"/>
+      <c r="AJ19" s="436" t="n"/>
+      <c r="AK19" s="436" t="n"/>
+      <c r="AL19" s="436" t="n"/>
+      <c r="AM19" s="436" t="n"/>
+      <c r="AN19" s="436" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="376">
+      <c r="A20" s="453">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B20" s="379" t="n"/>
-      <c r="C20" s="379" t="n"/>
-      <c r="D20" s="379" t="n"/>
-      <c r="E20" s="379" t="n"/>
-      <c r="F20" s="380" t="n"/>
-      <c r="G20" s="379" t="n"/>
-      <c r="H20" s="379" t="n"/>
-      <c r="I20" s="381" t="n"/>
+      <c r="B20" s="456" t="n"/>
+      <c r="C20" s="456" t="n"/>
+      <c r="D20" s="456" t="n"/>
+      <c r="E20" s="456" t="n"/>
+      <c r="F20" s="457" t="n"/>
+      <c r="G20" s="456" t="n"/>
+      <c r="H20" s="456" t="n"/>
+      <c r="I20" s="458" t="n"/>
+      <c r="J20" s="436" t="n"/>
+      <c r="K20" s="436" t="n"/>
+      <c r="L20" s="436" t="n"/>
+      <c r="M20" s="436" t="n"/>
+      <c r="N20" s="436" t="n"/>
+      <c r="O20" s="436" t="n"/>
+      <c r="P20" s="436" t="n"/>
+      <c r="Q20" s="436" t="n"/>
+      <c r="R20" s="436" t="n"/>
+      <c r="S20" s="436" t="n"/>
+      <c r="T20" s="436" t="n"/>
+      <c r="U20" s="436" t="n"/>
+      <c r="V20" s="436" t="n"/>
+      <c r="W20" s="436" t="n"/>
+      <c r="X20" s="436" t="n"/>
+      <c r="Y20" s="436" t="n"/>
+      <c r="Z20" s="436" t="n"/>
+      <c r="AA20" s="436" t="n"/>
+      <c r="AB20" s="436" t="n"/>
+      <c r="AC20" s="436" t="n"/>
+      <c r="AD20" s="436" t="n"/>
+      <c r="AE20" s="436" t="n"/>
+      <c r="AF20" s="436" t="n"/>
+      <c r="AG20" s="436" t="n"/>
+      <c r="AH20" s="436" t="n"/>
+      <c r="AI20" s="436" t="n"/>
+      <c r="AJ20" s="436" t="n"/>
+      <c r="AK20" s="436" t="n"/>
+      <c r="AL20" s="436" t="n"/>
+      <c r="AM20" s="436" t="n"/>
+      <c r="AN20" s="436" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="376">
+      <c r="A21" s="453">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B21" s="377" t="n"/>
-      <c r="C21" s="377" t="n"/>
-      <c r="D21" s="377" t="n"/>
-      <c r="E21" s="377" t="n"/>
-      <c r="F21" s="378" t="n"/>
-      <c r="G21" s="377" t="n"/>
-      <c r="H21" s="377" t="n"/>
-      <c r="I21" s="345" t="n"/>
+      <c r="B21" s="454" t="n"/>
+      <c r="C21" s="454" t="n"/>
+      <c r="D21" s="454" t="n"/>
+      <c r="E21" s="454" t="n"/>
+      <c r="F21" s="455" t="n"/>
+      <c r="G21" s="454" t="n"/>
+      <c r="H21" s="454" t="n"/>
+      <c r="I21" s="443" t="n"/>
+      <c r="J21" s="436" t="n"/>
+      <c r="K21" s="436" t="n"/>
+      <c r="L21" s="436" t="n"/>
+      <c r="M21" s="436" t="n"/>
+      <c r="N21" s="436" t="n"/>
+      <c r="O21" s="436" t="n"/>
+      <c r="P21" s="436" t="n"/>
+      <c r="Q21" s="436" t="n"/>
+      <c r="R21" s="436" t="n"/>
+      <c r="S21" s="436" t="n"/>
+      <c r="T21" s="436" t="n"/>
+      <c r="U21" s="436" t="n"/>
+      <c r="V21" s="436" t="n"/>
+      <c r="W21" s="436" t="n"/>
+      <c r="X21" s="436" t="n"/>
+      <c r="Y21" s="436" t="n"/>
+      <c r="Z21" s="436" t="n"/>
+      <c r="AA21" s="436" t="n"/>
+      <c r="AB21" s="436" t="n"/>
+      <c r="AC21" s="436" t="n"/>
+      <c r="AD21" s="436" t="n"/>
+      <c r="AE21" s="436" t="n"/>
+      <c r="AF21" s="436" t="n"/>
+      <c r="AG21" s="436" t="n"/>
+      <c r="AH21" s="436" t="n"/>
+      <c r="AI21" s="436" t="n"/>
+      <c r="AJ21" s="436" t="n"/>
+      <c r="AK21" s="436" t="n"/>
+      <c r="AL21" s="436" t="n"/>
+      <c r="AM21" s="436" t="n"/>
+      <c r="AN21" s="436" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="376">
+      <c r="A22" s="453">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B22" s="379" t="n"/>
-      <c r="C22" s="379" t="n"/>
-      <c r="D22" s="379" t="n"/>
-      <c r="E22" s="379" t="n"/>
-      <c r="F22" s="380" t="n"/>
-      <c r="G22" s="379" t="n"/>
-      <c r="H22" s="379" t="n"/>
-      <c r="I22" s="381" t="n"/>
+      <c r="B22" s="456" t="n"/>
+      <c r="C22" s="456" t="n"/>
+      <c r="D22" s="456" t="n"/>
+      <c r="E22" s="456" t="n"/>
+      <c r="F22" s="457" t="n"/>
+      <c r="G22" s="456" t="n"/>
+      <c r="H22" s="456" t="n"/>
+      <c r="I22" s="458" t="n"/>
+      <c r="J22" s="436" t="n"/>
+      <c r="K22" s="436" t="n"/>
+      <c r="L22" s="436" t="n"/>
+      <c r="M22" s="436" t="n"/>
+      <c r="N22" s="436" t="n"/>
+      <c r="O22" s="436" t="n"/>
+      <c r="P22" s="436" t="n"/>
+      <c r="Q22" s="436" t="n"/>
+      <c r="R22" s="436" t="n"/>
+      <c r="S22" s="436" t="n"/>
+      <c r="T22" s="436" t="n"/>
+      <c r="U22" s="436" t="n"/>
+      <c r="V22" s="436" t="n"/>
+      <c r="W22" s="436" t="n"/>
+      <c r="X22" s="436" t="n"/>
+      <c r="Y22" s="436" t="n"/>
+      <c r="Z22" s="436" t="n"/>
+      <c r="AA22" s="436" t="n"/>
+      <c r="AB22" s="436" t="n"/>
+      <c r="AC22" s="436" t="n"/>
+      <c r="AD22" s="436" t="n"/>
+      <c r="AE22" s="436" t="n"/>
+      <c r="AF22" s="436" t="n"/>
+      <c r="AG22" s="436" t="n"/>
+      <c r="AH22" s="436" t="n"/>
+      <c r="AI22" s="436" t="n"/>
+      <c r="AJ22" s="436" t="n"/>
+      <c r="AK22" s="436" t="n"/>
+      <c r="AL22" s="436" t="n"/>
+      <c r="AM22" s="436" t="n"/>
+      <c r="AN22" s="436" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="376">
+      <c r="A23" s="453">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B23" s="377" t="n"/>
-      <c r="C23" s="377" t="n"/>
-      <c r="D23" s="377" t="n"/>
-      <c r="E23" s="377" t="n"/>
-      <c r="F23" s="378" t="n"/>
-      <c r="G23" s="377" t="n"/>
-      <c r="H23" s="377" t="n"/>
-      <c r="I23" s="345" t="n"/>
+      <c r="B23" s="454" t="n"/>
+      <c r="C23" s="454" t="n"/>
+      <c r="D23" s="454" t="n"/>
+      <c r="E23" s="454" t="n"/>
+      <c r="F23" s="455" t="n"/>
+      <c r="G23" s="454" t="n"/>
+      <c r="H23" s="454" t="n"/>
+      <c r="I23" s="443" t="n"/>
+      <c r="J23" s="436" t="n"/>
+      <c r="K23" s="436" t="n"/>
+      <c r="L23" s="436" t="n"/>
+      <c r="M23" s="436" t="n"/>
+      <c r="N23" s="436" t="n"/>
+      <c r="O23" s="436" t="n"/>
+      <c r="P23" s="436" t="n"/>
+      <c r="Q23" s="436" t="n"/>
+      <c r="R23" s="436" t="n"/>
+      <c r="S23" s="436" t="n"/>
+      <c r="T23" s="436" t="n"/>
+      <c r="U23" s="436" t="n"/>
+      <c r="V23" s="436" t="n"/>
+      <c r="W23" s="436" t="n"/>
+      <c r="X23" s="436" t="n"/>
+      <c r="Y23" s="436" t="n"/>
+      <c r="Z23" s="436" t="n"/>
+      <c r="AA23" s="436" t="n"/>
+      <c r="AB23" s="436" t="n"/>
+      <c r="AC23" s="436" t="n"/>
+      <c r="AD23" s="436" t="n"/>
+      <c r="AE23" s="436" t="n"/>
+      <c r="AF23" s="436" t="n"/>
+      <c r="AG23" s="436" t="n"/>
+      <c r="AH23" s="436" t="n"/>
+      <c r="AI23" s="436" t="n"/>
+      <c r="AJ23" s="436" t="n"/>
+      <c r="AK23" s="436" t="n"/>
+      <c r="AL23" s="436" t="n"/>
+      <c r="AM23" s="436" t="n"/>
+      <c r="AN23" s="436" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="376">
+      <c r="A24" s="453">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B24" s="379" t="n"/>
-      <c r="C24" s="379" t="n"/>
-      <c r="D24" s="379" t="n"/>
-      <c r="E24" s="379" t="n"/>
-      <c r="F24" s="380" t="n"/>
-      <c r="G24" s="379" t="n"/>
-      <c r="H24" s="379" t="n"/>
-      <c r="I24" s="381" t="n"/>
+      <c r="B24" s="456" t="n"/>
+      <c r="C24" s="456" t="n"/>
+      <c r="D24" s="456" t="n"/>
+      <c r="E24" s="456" t="n"/>
+      <c r="F24" s="457" t="n"/>
+      <c r="G24" s="456" t="n"/>
+      <c r="H24" s="456" t="n"/>
+      <c r="I24" s="458" t="n"/>
+      <c r="J24" s="436" t="n"/>
+      <c r="K24" s="436" t="n"/>
+      <c r="L24" s="436" t="n"/>
+      <c r="M24" s="436" t="n"/>
+      <c r="N24" s="436" t="n"/>
+      <c r="O24" s="436" t="n"/>
+      <c r="P24" s="436" t="n"/>
+      <c r="Q24" s="436" t="n"/>
+      <c r="R24" s="436" t="n"/>
+      <c r="S24" s="436" t="n"/>
+      <c r="T24" s="436" t="n"/>
+      <c r="U24" s="436" t="n"/>
+      <c r="V24" s="436" t="n"/>
+      <c r="W24" s="436" t="n"/>
+      <c r="X24" s="436" t="n"/>
+      <c r="Y24" s="436" t="n"/>
+      <c r="Z24" s="436" t="n"/>
+      <c r="AA24" s="436" t="n"/>
+      <c r="AB24" s="436" t="n"/>
+      <c r="AC24" s="436" t="n"/>
+      <c r="AD24" s="436" t="n"/>
+      <c r="AE24" s="436" t="n"/>
+      <c r="AF24" s="436" t="n"/>
+      <c r="AG24" s="436" t="n"/>
+      <c r="AH24" s="436" t="n"/>
+      <c r="AI24" s="436" t="n"/>
+      <c r="AJ24" s="436" t="n"/>
+      <c r="AK24" s="436" t="n"/>
+      <c r="AL24" s="436" t="n"/>
+      <c r="AM24" s="436" t="n"/>
+      <c r="AN24" s="436" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="376">
+      <c r="A25" s="453">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B25" s="377" t="n"/>
-      <c r="C25" s="377" t="n"/>
-      <c r="D25" s="377" t="n"/>
-      <c r="E25" s="377" t="n"/>
-      <c r="F25" s="378" t="n"/>
-      <c r="G25" s="377" t="n"/>
-      <c r="H25" s="377" t="n"/>
-      <c r="I25" s="345" t="n"/>
+      <c r="B25" s="454" t="n"/>
+      <c r="C25" s="454" t="n"/>
+      <c r="D25" s="454" t="n"/>
+      <c r="E25" s="454" t="n"/>
+      <c r="F25" s="455" t="n"/>
+      <c r="G25" s="454" t="n"/>
+      <c r="H25" s="454" t="n"/>
+      <c r="I25" s="443" t="n"/>
+      <c r="J25" s="436" t="n"/>
+      <c r="K25" s="436" t="n"/>
+      <c r="L25" s="436" t="n"/>
+      <c r="M25" s="436" t="n"/>
+      <c r="N25" s="436" t="n"/>
+      <c r="O25" s="436" t="n"/>
+      <c r="P25" s="436" t="n"/>
+      <c r="Q25" s="436" t="n"/>
+      <c r="R25" s="436" t="n"/>
+      <c r="S25" s="436" t="n"/>
+      <c r="T25" s="436" t="n"/>
+      <c r="U25" s="436" t="n"/>
+      <c r="V25" s="436" t="n"/>
+      <c r="W25" s="436" t="n"/>
+      <c r="X25" s="436" t="n"/>
+      <c r="Y25" s="436" t="n"/>
+      <c r="Z25" s="436" t="n"/>
+      <c r="AA25" s="436" t="n"/>
+      <c r="AB25" s="436" t="n"/>
+      <c r="AC25" s="436" t="n"/>
+      <c r="AD25" s="436" t="n"/>
+      <c r="AE25" s="436" t="n"/>
+      <c r="AF25" s="436" t="n"/>
+      <c r="AG25" s="436" t="n"/>
+      <c r="AH25" s="436" t="n"/>
+      <c r="AI25" s="436" t="n"/>
+      <c r="AJ25" s="436" t="n"/>
+      <c r="AK25" s="436" t="n"/>
+      <c r="AL25" s="436" t="n"/>
+      <c r="AM25" s="436" t="n"/>
+      <c r="AN25" s="436" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="382">
+      <c r="A26" s="459">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B26" s="383" t="n"/>
-      <c r="C26" s="383" t="n"/>
-      <c r="D26" s="383" t="n"/>
-      <c r="E26" s="383" t="n"/>
-      <c r="F26" s="384" t="n"/>
-      <c r="G26" s="383" t="n"/>
-      <c r="H26" s="383" t="n"/>
-      <c r="I26" s="385" t="n"/>
+      <c r="B26" s="460" t="n"/>
+      <c r="C26" s="460" t="n"/>
+      <c r="D26" s="460" t="n"/>
+      <c r="E26" s="460" t="n"/>
+      <c r="F26" s="461" t="n"/>
+      <c r="G26" s="460" t="n"/>
+      <c r="H26" s="460" t="n"/>
+      <c r="I26" s="462" t="n"/>
+      <c r="J26" s="436" t="n"/>
+      <c r="K26" s="436" t="n"/>
+      <c r="L26" s="436" t="n"/>
+      <c r="M26" s="436" t="n"/>
+      <c r="N26" s="436" t="n"/>
+      <c r="O26" s="436" t="n"/>
+      <c r="P26" s="436" t="n"/>
+      <c r="Q26" s="436" t="n"/>
+      <c r="R26" s="436" t="n"/>
+      <c r="S26" s="436" t="n"/>
+      <c r="T26" s="436" t="n"/>
+      <c r="U26" s="436" t="n"/>
+      <c r="V26" s="436" t="n"/>
+      <c r="W26" s="436" t="n"/>
+      <c r="X26" s="436" t="n"/>
+      <c r="Y26" s="436" t="n"/>
+      <c r="Z26" s="436" t="n"/>
+      <c r="AA26" s="436" t="n"/>
+      <c r="AB26" s="436" t="n"/>
+      <c r="AC26" s="436" t="n"/>
+      <c r="AD26" s="436" t="n"/>
+      <c r="AE26" s="436" t="n"/>
+      <c r="AF26" s="436" t="n"/>
+      <c r="AG26" s="436" t="n"/>
+      <c r="AH26" s="436" t="n"/>
+      <c r="AI26" s="436" t="n"/>
+      <c r="AJ26" s="436" t="n"/>
+      <c r="AK26" s="436" t="n"/>
+      <c r="AL26" s="436" t="n"/>
+      <c r="AM26" s="436" t="n"/>
+      <c r="AN26" s="436" t="n"/>
     </row>
-    <row r="27"/>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="393" t="inlineStr">
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="436" t="n"/>
+      <c r="B27" s="436" t="n"/>
+      <c r="C27" s="436" t="n"/>
+      <c r="D27" s="436" t="n"/>
+      <c r="E27" s="436" t="n"/>
+      <c r="F27" s="436" t="n"/>
+      <c r="G27" s="436" t="n"/>
+      <c r="H27" s="436" t="n"/>
+      <c r="I27" s="436" t="n"/>
+      <c r="J27" s="436" t="n"/>
+      <c r="K27" s="436" t="n"/>
+      <c r="L27" s="436" t="n"/>
+      <c r="M27" s="436" t="n"/>
+      <c r="N27" s="436" t="n"/>
+      <c r="O27" s="436" t="n"/>
+      <c r="P27" s="436" t="n"/>
+      <c r="Q27" s="436" t="n"/>
+      <c r="R27" s="436" t="n"/>
+      <c r="S27" s="436" t="n"/>
+      <c r="T27" s="436" t="n"/>
+      <c r="U27" s="436" t="n"/>
+      <c r="V27" s="436" t="n"/>
+      <c r="W27" s="436" t="n"/>
+      <c r="X27" s="436" t="n"/>
+      <c r="Y27" s="436" t="n"/>
+      <c r="Z27" s="436" t="n"/>
+      <c r="AA27" s="436" t="n"/>
+      <c r="AB27" s="436" t="n"/>
+      <c r="AC27" s="436" t="n"/>
+      <c r="AD27" s="436" t="n"/>
+      <c r="AE27" s="436" t="n"/>
+      <c r="AF27" s="436" t="n"/>
+      <c r="AG27" s="436" t="n"/>
+      <c r="AH27" s="436" t="n"/>
+      <c r="AI27" s="436" t="n"/>
+      <c r="AJ27" s="436" t="n"/>
+      <c r="AK27" s="436" t="n"/>
+      <c r="AL27" s="436" t="n"/>
+      <c r="AM27" s="436" t="n"/>
+      <c r="AN27" s="436" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="451" t="inlineStr">
         <is>
           <t>NOTICE  —  One line per material, capacity, quality or customer-risk condition.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B28" s="289" t="n"/>
-      <c r="C28" s="289" t="n"/>
-      <c r="D28" s="289" t="n"/>
-      <c r="E28" s="289" t="n"/>
-      <c r="F28" s="289" t="n"/>
-      <c r="G28" s="289" t="n"/>
-      <c r="H28" s="289" t="n"/>
-      <c r="I28" s="290" t="n"/>
+      <c r="B28" s="467" t="n"/>
+      <c r="C28" s="467" t="n"/>
+      <c r="D28" s="467" t="n"/>
+      <c r="E28" s="467" t="n"/>
+      <c r="F28" s="467" t="n"/>
+      <c r="G28" s="467" t="n"/>
+      <c r="H28" s="467" t="n"/>
+      <c r="I28" s="468" t="n"/>
+      <c r="J28" s="402" t="n"/>
+      <c r="K28" s="402" t="n"/>
+      <c r="L28" s="402" t="n"/>
+      <c r="M28" s="402" t="n"/>
+      <c r="N28" s="402" t="n"/>
+      <c r="O28" s="402" t="n"/>
+      <c r="P28" s="402" t="n"/>
+      <c r="Q28" s="402" t="n"/>
+      <c r="R28" s="402" t="n"/>
+      <c r="S28" s="402" t="n"/>
+      <c r="T28" s="402" t="n"/>
+      <c r="U28" s="402" t="n"/>
+      <c r="V28" s="402" t="n"/>
+      <c r="W28" s="402" t="n"/>
+      <c r="X28" s="402" t="n"/>
+      <c r="Y28" s="402" t="n"/>
+      <c r="Z28" s="402" t="n"/>
+      <c r="AA28" s="402" t="n"/>
+      <c r="AB28" s="402" t="n"/>
+      <c r="AC28" s="402" t="n"/>
+      <c r="AD28" s="402" t="n"/>
+      <c r="AE28" s="402" t="n"/>
+      <c r="AF28" s="402" t="n"/>
+      <c r="AG28" s="402" t="n"/>
+      <c r="AH28" s="402" t="n"/>
+      <c r="AI28" s="402" t="n"/>
+      <c r="AJ28" s="402" t="n"/>
+      <c r="AK28" s="402" t="n"/>
+      <c r="AL28" s="402" t="n"/>
+      <c r="AM28" s="402" t="n"/>
+      <c r="AN28" s="402" t="n"/>
     </row>
     <row r="29" hidden="1" outlineLevel="1"/>
     <row r="30" hidden="1" outlineLevel="1"/>
@@ -9147,9 +11290,8 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9160,31 +11302,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col hidden="1" width="13" customWidth="1" min="8" max="16384"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col hidden="1" width="2.33" customWidth="1" min="8" max="16384"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="322" t="inlineStr">
+      <c r="A1" s="463" t="inlineStr">
         <is>
           <t>REF LINKS</t>
         </is>
       </c>
-      <c r="B1" s="330" t="n"/>
-      <c r="C1" s="330" t="n"/>
-      <c r="D1" s="330" t="n"/>
-      <c r="E1" s="330" t="n"/>
-      <c r="F1" s="330" t="n"/>
-      <c r="G1" s="331" t="n"/>
+      <c r="B1" s="484" t="n"/>
+      <c r="C1" s="484" t="n"/>
+      <c r="D1" s="484" t="n"/>
+      <c r="E1" s="484" t="n"/>
+      <c r="F1" s="484" t="n"/>
+      <c r="G1" s="485" t="n"/>
+      <c r="H1" s="402" t="n"/>
+      <c r="I1" s="402" t="n"/>
+      <c r="J1" s="402" t="n"/>
+      <c r="K1" s="402" t="n"/>
+      <c r="L1" s="402" t="n"/>
+      <c r="M1" s="402" t="n"/>
+      <c r="N1" s="402" t="n"/>
+      <c r="O1" s="402" t="n"/>
+      <c r="P1" s="402" t="n"/>
+      <c r="Q1" s="402" t="n"/>
+      <c r="R1" s="402" t="n"/>
+      <c r="S1" s="402" t="n"/>
+      <c r="T1" s="402" t="n"/>
+      <c r="U1" s="402" t="n"/>
+      <c r="V1" s="402" t="n"/>
+      <c r="W1" s="402" t="n"/>
+      <c r="X1" s="402" t="n"/>
+      <c r="Y1" s="402" t="n"/>
+      <c r="Z1" s="402" t="n"/>
+      <c r="AA1" s="402" t="n"/>
+      <c r="AB1" s="402" t="n"/>
+      <c r="AC1" s="402" t="n"/>
+      <c r="AD1" s="402" t="n"/>
+      <c r="AE1" s="402" t="n"/>
+      <c r="AF1" s="402" t="n"/>
+      <c r="AG1" s="402" t="n"/>
+      <c r="AH1" s="402" t="n"/>
+      <c r="AI1" s="402" t="n"/>
+      <c r="AJ1" s="402" t="n"/>
+      <c r="AK1" s="402" t="n"/>
+      <c r="AL1" s="402" t="n"/>
+      <c r="AM1" s="402" t="n"/>
+      <c r="AN1" s="402" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="323" t="inlineStr">
@@ -9192,115 +11399,445 @@
           <t>Reference release package, planner snapshot and dossier evidence only.</t>
         </is>
       </c>
+      <c r="H2" s="402" t="n"/>
+      <c r="I2" s="402" t="n"/>
+      <c r="J2" s="402" t="n"/>
+      <c r="K2" s="402" t="n"/>
+      <c r="L2" s="402" t="n"/>
+      <c r="M2" s="402" t="n"/>
+      <c r="N2" s="402" t="n"/>
+      <c r="O2" s="402" t="n"/>
+      <c r="P2" s="402" t="n"/>
+      <c r="Q2" s="402" t="n"/>
+      <c r="R2" s="402" t="n"/>
+      <c r="S2" s="402" t="n"/>
+      <c r="T2" s="402" t="n"/>
+      <c r="U2" s="402" t="n"/>
+      <c r="V2" s="402" t="n"/>
+      <c r="W2" s="402" t="n"/>
+      <c r="X2" s="402" t="n"/>
+      <c r="Y2" s="402" t="n"/>
+      <c r="Z2" s="402" t="n"/>
+      <c r="AA2" s="402" t="n"/>
+      <c r="AB2" s="402" t="n"/>
+      <c r="AC2" s="402" t="n"/>
+      <c r="AD2" s="402" t="n"/>
+      <c r="AE2" s="402" t="n"/>
+      <c r="AF2" s="402" t="n"/>
+      <c r="AG2" s="402" t="n"/>
+      <c r="AH2" s="402" t="n"/>
+      <c r="AI2" s="402" t="n"/>
+      <c r="AJ2" s="402" t="n"/>
+      <c r="AK2" s="402" t="n"/>
+      <c r="AL2" s="402" t="n"/>
+      <c r="AM2" s="402" t="n"/>
+      <c r="AN2" s="402" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="324" t="inlineStr">
+      <c r="A3" s="464" t="inlineStr">
         <is>
           <t>Ref Type</t>
         </is>
       </c>
-      <c r="B3" s="324" t="inlineStr">
+      <c r="B3" s="464" t="inlineStr">
         <is>
           <t>Document / Record</t>
         </is>
       </c>
-      <c r="C3" s="324" t="inlineStr">
+      <c r="C3" s="464" t="inlineStr">
         <is>
           <t>System of Record</t>
         </is>
       </c>
-      <c r="D3" s="324" t="inlineStr">
+      <c r="D3" s="464" t="inlineStr">
         <is>
           <t>Unique Ref</t>
         </is>
       </c>
-      <c r="E3" s="324" t="inlineStr">
+      <c r="E3" s="464" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F3" s="324" t="inlineStr">
+      <c r="F3" s="464" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G3" s="324" t="inlineStr">
+      <c r="G3" s="464" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
+      <c r="H3" s="402" t="n"/>
+      <c r="I3" s="402" t="n"/>
+      <c r="J3" s="402" t="n"/>
+      <c r="K3" s="402" t="n"/>
+      <c r="L3" s="402" t="n"/>
+      <c r="M3" s="402" t="n"/>
+      <c r="N3" s="402" t="n"/>
+      <c r="O3" s="402" t="n"/>
+      <c r="P3" s="402" t="n"/>
+      <c r="Q3" s="402" t="n"/>
+      <c r="R3" s="402" t="n"/>
+      <c r="S3" s="402" t="n"/>
+      <c r="T3" s="402" t="n"/>
+      <c r="U3" s="402" t="n"/>
+      <c r="V3" s="402" t="n"/>
+      <c r="W3" s="402" t="n"/>
+      <c r="X3" s="402" t="n"/>
+      <c r="Y3" s="402" t="n"/>
+      <c r="Z3" s="402" t="n"/>
+      <c r="AA3" s="402" t="n"/>
+      <c r="AB3" s="402" t="n"/>
+      <c r="AC3" s="402" t="n"/>
+      <c r="AD3" s="402" t="n"/>
+      <c r="AE3" s="402" t="n"/>
+      <c r="AF3" s="402" t="n"/>
+      <c r="AG3" s="402" t="n"/>
+      <c r="AH3" s="402" t="n"/>
+      <c r="AI3" s="402" t="n"/>
+      <c r="AJ3" s="402" t="n"/>
+      <c r="AK3" s="402" t="n"/>
+      <c r="AL3" s="402" t="n"/>
+      <c r="AM3" s="402" t="n"/>
+      <c r="AN3" s="402" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="308" t="n"/>
-      <c r="B4" s="308" t="n"/>
-      <c r="C4" s="308" t="n"/>
-      <c r="D4" s="308" t="n"/>
-      <c r="E4" s="308" t="n"/>
-      <c r="F4" s="308" t="n"/>
-      <c r="G4" s="308" t="n"/>
+      <c r="A4" s="427" t="n"/>
+      <c r="B4" s="427" t="n"/>
+      <c r="C4" s="427" t="n"/>
+      <c r="D4" s="427" t="n"/>
+      <c r="E4" s="427" t="n"/>
+      <c r="F4" s="427" t="n"/>
+      <c r="G4" s="427" t="n"/>
+      <c r="H4" s="402" t="n"/>
+      <c r="I4" s="402" t="n"/>
+      <c r="J4" s="402" t="n"/>
+      <c r="K4" s="402" t="n"/>
+      <c r="L4" s="402" t="n"/>
+      <c r="M4" s="402" t="n"/>
+      <c r="N4" s="402" t="n"/>
+      <c r="O4" s="402" t="n"/>
+      <c r="P4" s="402" t="n"/>
+      <c r="Q4" s="402" t="n"/>
+      <c r="R4" s="402" t="n"/>
+      <c r="S4" s="402" t="n"/>
+      <c r="T4" s="402" t="n"/>
+      <c r="U4" s="402" t="n"/>
+      <c r="V4" s="402" t="n"/>
+      <c r="W4" s="402" t="n"/>
+      <c r="X4" s="402" t="n"/>
+      <c r="Y4" s="402" t="n"/>
+      <c r="Z4" s="402" t="n"/>
+      <c r="AA4" s="402" t="n"/>
+      <c r="AB4" s="402" t="n"/>
+      <c r="AC4" s="402" t="n"/>
+      <c r="AD4" s="402" t="n"/>
+      <c r="AE4" s="402" t="n"/>
+      <c r="AF4" s="402" t="n"/>
+      <c r="AG4" s="402" t="n"/>
+      <c r="AH4" s="402" t="n"/>
+      <c r="AI4" s="402" t="n"/>
+      <c r="AJ4" s="402" t="n"/>
+      <c r="AK4" s="402" t="n"/>
+      <c r="AL4" s="402" t="n"/>
+      <c r="AM4" s="402" t="n"/>
+      <c r="AN4" s="402" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="327" t="n"/>
-      <c r="B5" s="327" t="n"/>
-      <c r="C5" s="327" t="n"/>
-      <c r="D5" s="327" t="n"/>
-      <c r="E5" s="327" t="n"/>
-      <c r="F5" s="327" t="n"/>
-      <c r="G5" s="327" t="n"/>
+      <c r="A5" s="465" t="n"/>
+      <c r="B5" s="465" t="n"/>
+      <c r="C5" s="465" t="n"/>
+      <c r="D5" s="465" t="n"/>
+      <c r="E5" s="465" t="n"/>
+      <c r="F5" s="465" t="n"/>
+      <c r="G5" s="465" t="n"/>
+      <c r="H5" s="402" t="n"/>
+      <c r="I5" s="402" t="n"/>
+      <c r="J5" s="402" t="n"/>
+      <c r="K5" s="402" t="n"/>
+      <c r="L5" s="402" t="n"/>
+      <c r="M5" s="402" t="n"/>
+      <c r="N5" s="402" t="n"/>
+      <c r="O5" s="402" t="n"/>
+      <c r="P5" s="402" t="n"/>
+      <c r="Q5" s="402" t="n"/>
+      <c r="R5" s="402" t="n"/>
+      <c r="S5" s="402" t="n"/>
+      <c r="T5" s="402" t="n"/>
+      <c r="U5" s="402" t="n"/>
+      <c r="V5" s="402" t="n"/>
+      <c r="W5" s="402" t="n"/>
+      <c r="X5" s="402" t="n"/>
+      <c r="Y5" s="402" t="n"/>
+      <c r="Z5" s="402" t="n"/>
+      <c r="AA5" s="402" t="n"/>
+      <c r="AB5" s="402" t="n"/>
+      <c r="AC5" s="402" t="n"/>
+      <c r="AD5" s="402" t="n"/>
+      <c r="AE5" s="402" t="n"/>
+      <c r="AF5" s="402" t="n"/>
+      <c r="AG5" s="402" t="n"/>
+      <c r="AH5" s="402" t="n"/>
+      <c r="AI5" s="402" t="n"/>
+      <c r="AJ5" s="402" t="n"/>
+      <c r="AK5" s="402" t="n"/>
+      <c r="AL5" s="402" t="n"/>
+      <c r="AM5" s="402" t="n"/>
+      <c r="AN5" s="402" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="308" t="n"/>
-      <c r="B6" s="308" t="n"/>
-      <c r="C6" s="308" t="n"/>
-      <c r="D6" s="308" t="n"/>
-      <c r="E6" s="308" t="n"/>
-      <c r="F6" s="308" t="n"/>
-      <c r="G6" s="308" t="n"/>
+      <c r="A6" s="427" t="n"/>
+      <c r="B6" s="427" t="n"/>
+      <c r="C6" s="427" t="n"/>
+      <c r="D6" s="427" t="n"/>
+      <c r="E6" s="427" t="n"/>
+      <c r="F6" s="427" t="n"/>
+      <c r="G6" s="427" t="n"/>
+      <c r="H6" s="402" t="n"/>
+      <c r="I6" s="402" t="n"/>
+      <c r="J6" s="402" t="n"/>
+      <c r="K6" s="402" t="n"/>
+      <c r="L6" s="402" t="n"/>
+      <c r="M6" s="402" t="n"/>
+      <c r="N6" s="402" t="n"/>
+      <c r="O6" s="402" t="n"/>
+      <c r="P6" s="402" t="n"/>
+      <c r="Q6" s="402" t="n"/>
+      <c r="R6" s="402" t="n"/>
+      <c r="S6" s="402" t="n"/>
+      <c r="T6" s="402" t="n"/>
+      <c r="U6" s="402" t="n"/>
+      <c r="V6" s="402" t="n"/>
+      <c r="W6" s="402" t="n"/>
+      <c r="X6" s="402" t="n"/>
+      <c r="Y6" s="402" t="n"/>
+      <c r="Z6" s="402" t="n"/>
+      <c r="AA6" s="402" t="n"/>
+      <c r="AB6" s="402" t="n"/>
+      <c r="AC6" s="402" t="n"/>
+      <c r="AD6" s="402" t="n"/>
+      <c r="AE6" s="402" t="n"/>
+      <c r="AF6" s="402" t="n"/>
+      <c r="AG6" s="402" t="n"/>
+      <c r="AH6" s="402" t="n"/>
+      <c r="AI6" s="402" t="n"/>
+      <c r="AJ6" s="402" t="n"/>
+      <c r="AK6" s="402" t="n"/>
+      <c r="AL6" s="402" t="n"/>
+      <c r="AM6" s="402" t="n"/>
+      <c r="AN6" s="402" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="327" t="n"/>
-      <c r="B7" s="327" t="n"/>
-      <c r="C7" s="327" t="n"/>
-      <c r="D7" s="327" t="n"/>
-      <c r="E7" s="327" t="n"/>
-      <c r="F7" s="327" t="n"/>
-      <c r="G7" s="327" t="n"/>
+      <c r="A7" s="465" t="n"/>
+      <c r="B7" s="465" t="n"/>
+      <c r="C7" s="465" t="n"/>
+      <c r="D7" s="465" t="n"/>
+      <c r="E7" s="465" t="n"/>
+      <c r="F7" s="465" t="n"/>
+      <c r="G7" s="465" t="n"/>
+      <c r="H7" s="402" t="n"/>
+      <c r="I7" s="402" t="n"/>
+      <c r="J7" s="402" t="n"/>
+      <c r="K7" s="402" t="n"/>
+      <c r="L7" s="402" t="n"/>
+      <c r="M7" s="402" t="n"/>
+      <c r="N7" s="402" t="n"/>
+      <c r="O7" s="402" t="n"/>
+      <c r="P7" s="402" t="n"/>
+      <c r="Q7" s="402" t="n"/>
+      <c r="R7" s="402" t="n"/>
+      <c r="S7" s="402" t="n"/>
+      <c r="T7" s="402" t="n"/>
+      <c r="U7" s="402" t="n"/>
+      <c r="V7" s="402" t="n"/>
+      <c r="W7" s="402" t="n"/>
+      <c r="X7" s="402" t="n"/>
+      <c r="Y7" s="402" t="n"/>
+      <c r="Z7" s="402" t="n"/>
+      <c r="AA7" s="402" t="n"/>
+      <c r="AB7" s="402" t="n"/>
+      <c r="AC7" s="402" t="n"/>
+      <c r="AD7" s="402" t="n"/>
+      <c r="AE7" s="402" t="n"/>
+      <c r="AF7" s="402" t="n"/>
+      <c r="AG7" s="402" t="n"/>
+      <c r="AH7" s="402" t="n"/>
+      <c r="AI7" s="402" t="n"/>
+      <c r="AJ7" s="402" t="n"/>
+      <c r="AK7" s="402" t="n"/>
+      <c r="AL7" s="402" t="n"/>
+      <c r="AM7" s="402" t="n"/>
+      <c r="AN7" s="402" t="n"/>
     </row>
-    <row r="8">
-      <c r="A8" s="308" t="n"/>
-      <c r="B8" s="308" t="n"/>
-      <c r="C8" s="308" t="n"/>
-      <c r="D8" s="308" t="n"/>
-      <c r="E8" s="308" t="n"/>
-      <c r="F8" s="308" t="n"/>
-      <c r="G8" s="308" t="n"/>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="427" t="n"/>
+      <c r="B8" s="427" t="n"/>
+      <c r="C8" s="427" t="n"/>
+      <c r="D8" s="427" t="n"/>
+      <c r="E8" s="427" t="n"/>
+      <c r="F8" s="427" t="n"/>
+      <c r="G8" s="427" t="n"/>
+      <c r="H8" s="436" t="n"/>
+      <c r="I8" s="436" t="n"/>
+      <c r="J8" s="436" t="n"/>
+      <c r="K8" s="436" t="n"/>
+      <c r="L8" s="436" t="n"/>
+      <c r="M8" s="436" t="n"/>
+      <c r="N8" s="436" t="n"/>
+      <c r="O8" s="436" t="n"/>
+      <c r="P8" s="436" t="n"/>
+      <c r="Q8" s="436" t="n"/>
+      <c r="R8" s="436" t="n"/>
+      <c r="S8" s="436" t="n"/>
+      <c r="T8" s="436" t="n"/>
+      <c r="U8" s="436" t="n"/>
+      <c r="V8" s="436" t="n"/>
+      <c r="W8" s="436" t="n"/>
+      <c r="X8" s="436" t="n"/>
+      <c r="Y8" s="436" t="n"/>
+      <c r="Z8" s="436" t="n"/>
+      <c r="AA8" s="436" t="n"/>
+      <c r="AB8" s="436" t="n"/>
+      <c r="AC8" s="436" t="n"/>
+      <c r="AD8" s="436" t="n"/>
+      <c r="AE8" s="436" t="n"/>
+      <c r="AF8" s="436" t="n"/>
+      <c r="AG8" s="436" t="n"/>
+      <c r="AH8" s="436" t="n"/>
+      <c r="AI8" s="436" t="n"/>
+      <c r="AJ8" s="436" t="n"/>
+      <c r="AK8" s="436" t="n"/>
+      <c r="AL8" s="436" t="n"/>
+      <c r="AM8" s="436" t="n"/>
+      <c r="AN8" s="436" t="n"/>
     </row>
-    <row r="9">
-      <c r="A9" s="327" t="n"/>
-      <c r="B9" s="327" t="n"/>
-      <c r="C9" s="327" t="n"/>
-      <c r="D9" s="327" t="n"/>
-      <c r="E9" s="327" t="n"/>
-      <c r="F9" s="327" t="n"/>
-      <c r="G9" s="327" t="n"/>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="465" t="n"/>
+      <c r="B9" s="465" t="n"/>
+      <c r="C9" s="465" t="n"/>
+      <c r="D9" s="465" t="n"/>
+      <c r="E9" s="465" t="n"/>
+      <c r="F9" s="465" t="n"/>
+      <c r="G9" s="465" t="n"/>
+      <c r="H9" s="436" t="n"/>
+      <c r="I9" s="436" t="n"/>
+      <c r="J9" s="436" t="n"/>
+      <c r="K9" s="436" t="n"/>
+      <c r="L9" s="436" t="n"/>
+      <c r="M9" s="436" t="n"/>
+      <c r="N9" s="436" t="n"/>
+      <c r="O9" s="436" t="n"/>
+      <c r="P9" s="436" t="n"/>
+      <c r="Q9" s="436" t="n"/>
+      <c r="R9" s="436" t="n"/>
+      <c r="S9" s="436" t="n"/>
+      <c r="T9" s="436" t="n"/>
+      <c r="U9" s="436" t="n"/>
+      <c r="V9" s="436" t="n"/>
+      <c r="W9" s="436" t="n"/>
+      <c r="X9" s="436" t="n"/>
+      <c r="Y9" s="436" t="n"/>
+      <c r="Z9" s="436" t="n"/>
+      <c r="AA9" s="436" t="n"/>
+      <c r="AB9" s="436" t="n"/>
+      <c r="AC9" s="436" t="n"/>
+      <c r="AD9" s="436" t="n"/>
+      <c r="AE9" s="436" t="n"/>
+      <c r="AF9" s="436" t="n"/>
+      <c r="AG9" s="436" t="n"/>
+      <c r="AH9" s="436" t="n"/>
+      <c r="AI9" s="436" t="n"/>
+      <c r="AJ9" s="436" t="n"/>
+      <c r="AK9" s="436" t="n"/>
+      <c r="AL9" s="436" t="n"/>
+      <c r="AM9" s="436" t="n"/>
+      <c r="AN9" s="436" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="308" t="n"/>
-      <c r="B10" s="308" t="n"/>
-      <c r="C10" s="308" t="n"/>
-      <c r="D10" s="308" t="n"/>
-      <c r="E10" s="308" t="n"/>
-      <c r="F10" s="308" t="n"/>
-      <c r="G10" s="308" t="n"/>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="427" t="n"/>
+      <c r="B10" s="427" t="n"/>
+      <c r="C10" s="427" t="n"/>
+      <c r="D10" s="427" t="n"/>
+      <c r="E10" s="427" t="n"/>
+      <c r="F10" s="427" t="n"/>
+      <c r="G10" s="427" t="n"/>
+      <c r="H10" s="436" t="n"/>
+      <c r="I10" s="436" t="n"/>
+      <c r="J10" s="436" t="n"/>
+      <c r="K10" s="436" t="n"/>
+      <c r="L10" s="436" t="n"/>
+      <c r="M10" s="436" t="n"/>
+      <c r="N10" s="436" t="n"/>
+      <c r="O10" s="436" t="n"/>
+      <c r="P10" s="436" t="n"/>
+      <c r="Q10" s="436" t="n"/>
+      <c r="R10" s="436" t="n"/>
+      <c r="S10" s="436" t="n"/>
+      <c r="T10" s="436" t="n"/>
+      <c r="U10" s="436" t="n"/>
+      <c r="V10" s="436" t="n"/>
+      <c r="W10" s="436" t="n"/>
+      <c r="X10" s="436" t="n"/>
+      <c r="Y10" s="436" t="n"/>
+      <c r="Z10" s="436" t="n"/>
+      <c r="AA10" s="436" t="n"/>
+      <c r="AB10" s="436" t="n"/>
+      <c r="AC10" s="436" t="n"/>
+      <c r="AD10" s="436" t="n"/>
+      <c r="AE10" s="436" t="n"/>
+      <c r="AF10" s="436" t="n"/>
+      <c r="AG10" s="436" t="n"/>
+      <c r="AH10" s="436" t="n"/>
+      <c r="AI10" s="436" t="n"/>
+      <c r="AJ10" s="436" t="n"/>
+      <c r="AK10" s="436" t="n"/>
+      <c r="AL10" s="436" t="n"/>
+      <c r="AM10" s="436" t="n"/>
+      <c r="AN10" s="436" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="327" t="n"/>
-      <c r="B11" s="327" t="n"/>
-      <c r="C11" s="327" t="n"/>
-      <c r="D11" s="327" t="n"/>
-      <c r="E11" s="327" t="n"/>
-      <c r="F11" s="327" t="n"/>
-      <c r="G11" s="327" t="n"/>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="465" t="n"/>
+      <c r="B11" s="465" t="n"/>
+      <c r="C11" s="465" t="n"/>
+      <c r="D11" s="465" t="n"/>
+      <c r="E11" s="465" t="n"/>
+      <c r="F11" s="465" t="n"/>
+      <c r="G11" s="465" t="n"/>
+      <c r="H11" s="436" t="n"/>
+      <c r="I11" s="436" t="n"/>
+      <c r="J11" s="436" t="n"/>
+      <c r="K11" s="436" t="n"/>
+      <c r="L11" s="436" t="n"/>
+      <c r="M11" s="436" t="n"/>
+      <c r="N11" s="436" t="n"/>
+      <c r="O11" s="436" t="n"/>
+      <c r="P11" s="436" t="n"/>
+      <c r="Q11" s="436" t="n"/>
+      <c r="R11" s="436" t="n"/>
+      <c r="S11" s="436" t="n"/>
+      <c r="T11" s="436" t="n"/>
+      <c r="U11" s="436" t="n"/>
+      <c r="V11" s="436" t="n"/>
+      <c r="W11" s="436" t="n"/>
+      <c r="X11" s="436" t="n"/>
+      <c r="Y11" s="436" t="n"/>
+      <c r="Z11" s="436" t="n"/>
+      <c r="AA11" s="436" t="n"/>
+      <c r="AB11" s="436" t="n"/>
+      <c r="AC11" s="436" t="n"/>
+      <c r="AD11" s="436" t="n"/>
+      <c r="AE11" s="436" t="n"/>
+      <c r="AF11" s="436" t="n"/>
+      <c r="AG11" s="436" t="n"/>
+      <c r="AH11" s="436" t="n"/>
+      <c r="AI11" s="436" t="n"/>
+      <c r="AJ11" s="436" t="n"/>
+      <c r="AK11" s="436" t="n"/>
+      <c r="AL11" s="436" t="n"/>
+      <c r="AM11" s="436" t="n"/>
+      <c r="AN11" s="436" t="n"/>
     </row>
     <row r="12" hidden="1"/>
     <row r="13" hidden="1"/>

--- a/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
@@ -33,7 +33,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="84">
+  <fonts count="89">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -509,8 +509,35 @@
       <color theme="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001565C0"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007A8FA6"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00BBCCCC"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="52">
+  <fills count="57">
     <fill>
       <patternFill/>
     </fill>
@@ -767,8 +794,33 @@
         <fgColor rgb="00F7F9FC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002C9CD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F0F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001565C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F7FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000C2D48"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="314">
+  <borders count="341">
     <border>
       <left/>
       <right/>
@@ -4145,12 +4197,298 @@
         <color rgb="00C5D9E8"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="492">
+  <cellXfs count="630">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5311,6 +5649,376 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="313" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="306" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="308" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="314" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="315" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="316" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="53" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="53" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="53" borderId="317" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="320" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="53" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="53" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="53" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="323" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="324" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="325" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="53" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="53" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="53" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="52" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="54" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="54" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="54" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="335" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="337" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="339" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="327" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="330" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="56" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="56" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="56" borderId="340" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="56" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="47" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="55" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="47" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="8" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="55" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="47" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="8" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="55" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="338" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="326" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="329" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="334" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="52" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="337" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="339" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="55" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="55" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="55" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="316" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="320" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="325" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="51" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="51" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="51" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="51" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -5404,6 +6112,96 @@
     </comment>
   </commentList>
 </comments>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5665,543 +6463,606 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="394" t="inlineStr"/>
-      <c r="B1" s="483" t="n"/>
-      <c r="C1" s="483" t="n"/>
-      <c r="D1" s="483" t="n"/>
-      <c r="E1" s="483" t="n"/>
-      <c r="F1" s="483" t="n"/>
-      <c r="G1" s="483" t="n"/>
-      <c r="H1" s="483" t="n"/>
-      <c r="I1" s="396" t="inlineStr">
+      <c r="A1" s="492" t="inlineStr"/>
+      <c r="B1" s="493" t="n"/>
+      <c r="C1" s="493" t="n"/>
+      <c r="D1" s="493" t="n"/>
+      <c r="E1" s="493" t="n"/>
+      <c r="F1" s="493" t="n"/>
+      <c r="G1" s="493" t="n"/>
+      <c r="H1" s="494" t="n"/>
+      <c r="I1" s="495" t="inlineStr">
         <is>
           <t>HIGH-RISK JOB READINESS REVIEW</t>
         </is>
       </c>
-      <c r="J1" s="483" t="n"/>
-      <c r="K1" s="483" t="n"/>
-      <c r="L1" s="483" t="n"/>
-      <c r="M1" s="483" t="n"/>
-      <c r="N1" s="483" t="n"/>
-      <c r="O1" s="483" t="n"/>
-      <c r="P1" s="483" t="n"/>
-      <c r="Q1" s="483" t="n"/>
-      <c r="R1" s="483" t="n"/>
-      <c r="S1" s="483" t="n"/>
-      <c r="T1" s="483" t="n"/>
-      <c r="U1" s="483" t="n"/>
-      <c r="V1" s="483" t="n"/>
-      <c r="W1" s="483" t="n"/>
-      <c r="X1" s="483" t="n"/>
-      <c r="Y1" s="483" t="n"/>
-      <c r="Z1" s="483" t="n"/>
-      <c r="AA1" s="483" t="n"/>
-      <c r="AB1" s="483" t="n"/>
-      <c r="AC1" s="483" t="n"/>
-      <c r="AD1" s="483" t="n"/>
-      <c r="AE1" s="397" t="inlineStr">
+      <c r="J1" s="496" t="n"/>
+      <c r="K1" s="496" t="n"/>
+      <c r="L1" s="496" t="n"/>
+      <c r="M1" s="496" t="n"/>
+      <c r="N1" s="496" t="n"/>
+      <c r="O1" s="496" t="n"/>
+      <c r="P1" s="496" t="n"/>
+      <c r="Q1" s="496" t="n"/>
+      <c r="R1" s="496" t="n"/>
+      <c r="S1" s="496" t="n"/>
+      <c r="T1" s="496" t="n"/>
+      <c r="U1" s="496" t="n"/>
+      <c r="V1" s="496" t="n"/>
+      <c r="W1" s="496" t="n"/>
+      <c r="X1" s="496" t="n"/>
+      <c r="Y1" s="496" t="n"/>
+      <c r="Z1" s="496" t="n"/>
+      <c r="AA1" s="496" t="n"/>
+      <c r="AB1" s="496" t="n"/>
+      <c r="AC1" s="496" t="n"/>
+      <c r="AD1" s="497" t="n"/>
+      <c r="AE1" s="498" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="484" t="n"/>
-      <c r="AG1" s="484" t="n"/>
-      <c r="AH1" s="485" t="n"/>
-      <c r="AI1" s="400" t="inlineStr">
+      <c r="AF1" s="499" t="n"/>
+      <c r="AG1" s="499" t="n"/>
+      <c r="AH1" s="500" t="n"/>
+      <c r="AI1" s="501" t="inlineStr">
         <is>
           <t>FRM-209</t>
         </is>
       </c>
-      <c r="AJ1" s="484" t="n"/>
-      <c r="AK1" s="484" t="n"/>
-      <c r="AL1" s="484" t="n"/>
-      <c r="AM1" s="484" t="n"/>
-      <c r="AN1" s="485" t="n"/>
+      <c r="AJ1" s="502" t="n"/>
+      <c r="AK1" s="502" t="n"/>
+      <c r="AL1" s="502" t="n"/>
+      <c r="AM1" s="502" t="n"/>
+      <c r="AN1" s="503" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="486" t="n"/>
-      <c r="I2" s="486" t="n"/>
-      <c r="AE2" s="403" t="inlineStr">
+      <c r="A2" s="504" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="505" t="n"/>
+      <c r="I2" s="506" t="n"/>
+      <c r="J2" s="507" t="n"/>
+      <c r="K2" s="507" t="n"/>
+      <c r="L2" s="507" t="n"/>
+      <c r="M2" s="507" t="n"/>
+      <c r="N2" s="507" t="n"/>
+      <c r="O2" s="507" t="n"/>
+      <c r="P2" s="507" t="n"/>
+      <c r="Q2" s="507" t="n"/>
+      <c r="R2" s="507" t="n"/>
+      <c r="S2" s="507" t="n"/>
+      <c r="T2" s="507" t="n"/>
+      <c r="U2" s="507" t="n"/>
+      <c r="V2" s="507" t="n"/>
+      <c r="W2" s="507" t="n"/>
+      <c r="X2" s="507" t="n"/>
+      <c r="Y2" s="507" t="n"/>
+      <c r="Z2" s="507" t="n"/>
+      <c r="AA2" s="507" t="n"/>
+      <c r="AB2" s="507" t="n"/>
+      <c r="AC2" s="507" t="n"/>
+      <c r="AD2" s="508" t="n"/>
+      <c r="AE2" s="509" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="487" t="n"/>
-      <c r="AG2" s="487" t="n"/>
-      <c r="AH2" s="488" t="n"/>
-      <c r="AI2" s="406" t="inlineStr">
+      <c r="AF2" s="510" t="n"/>
+      <c r="AG2" s="510" t="n"/>
+      <c r="AH2" s="511" t="n"/>
+      <c r="AI2" s="512" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="487" t="n"/>
-      <c r="AK2" s="487" t="n"/>
-      <c r="AL2" s="487" t="n"/>
-      <c r="AM2" s="487" t="n"/>
-      <c r="AN2" s="488" t="n"/>
+      <c r="AJ2" s="513" t="n"/>
+      <c r="AK2" s="513" t="n"/>
+      <c r="AL2" s="513" t="n"/>
+      <c r="AM2" s="513" t="n"/>
+      <c r="AN2" s="514" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="486" t="n"/>
-      <c r="I3" s="489" t="n"/>
-      <c r="J3" s="487" t="n"/>
-      <c r="K3" s="487" t="n"/>
-      <c r="L3" s="487" t="n"/>
-      <c r="M3" s="487" t="n"/>
-      <c r="N3" s="487" t="n"/>
-      <c r="O3" s="487" t="n"/>
-      <c r="P3" s="487" t="n"/>
-      <c r="Q3" s="487" t="n"/>
-      <c r="R3" s="487" t="n"/>
-      <c r="S3" s="487" t="n"/>
-      <c r="T3" s="487" t="n"/>
-      <c r="U3" s="487" t="n"/>
-      <c r="V3" s="487" t="n"/>
-      <c r="W3" s="487" t="n"/>
-      <c r="X3" s="487" t="n"/>
-      <c r="Y3" s="487" t="n"/>
-      <c r="Z3" s="487" t="n"/>
-      <c r="AA3" s="487" t="n"/>
-      <c r="AB3" s="487" t="n"/>
-      <c r="AC3" s="487" t="n"/>
-      <c r="AD3" s="487" t="n"/>
-      <c r="AE3" s="403" t="inlineStr">
+      <c r="A3" s="504" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="505" t="n"/>
+      <c r="I3" s="506" t="n"/>
+      <c r="J3" s="507" t="n"/>
+      <c r="K3" s="507" t="n"/>
+      <c r="L3" s="507" t="n"/>
+      <c r="M3" s="507" t="n"/>
+      <c r="N3" s="507" t="n"/>
+      <c r="O3" s="507" t="n"/>
+      <c r="P3" s="507" t="n"/>
+      <c r="Q3" s="507" t="n"/>
+      <c r="R3" s="507" t="n"/>
+      <c r="S3" s="507" t="n"/>
+      <c r="T3" s="507" t="n"/>
+      <c r="U3" s="507" t="n"/>
+      <c r="V3" s="507" t="n"/>
+      <c r="W3" s="507" t="n"/>
+      <c r="X3" s="507" t="n"/>
+      <c r="Y3" s="507" t="n"/>
+      <c r="Z3" s="507" t="n"/>
+      <c r="AA3" s="507" t="n"/>
+      <c r="AB3" s="507" t="n"/>
+      <c r="AC3" s="507" t="n"/>
+      <c r="AD3" s="508" t="n"/>
+      <c r="AE3" s="509" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="487" t="n"/>
-      <c r="AG3" s="487" t="n"/>
-      <c r="AH3" s="488" t="n"/>
-      <c r="AI3" s="406" t="inlineStr">
+      <c r="AF3" s="510" t="n"/>
+      <c r="AG3" s="510" t="n"/>
+      <c r="AH3" s="511" t="n"/>
+      <c r="AI3" s="512" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="487" t="n"/>
-      <c r="AK3" s="487" t="n"/>
-      <c r="AL3" s="487" t="n"/>
-      <c r="AM3" s="487" t="n"/>
-      <c r="AN3" s="488" t="n"/>
+      <c r="AJ3" s="513" t="n"/>
+      <c r="AK3" s="513" t="n"/>
+      <c r="AL3" s="513" t="n"/>
+      <c r="AM3" s="513" t="n"/>
+      <c r="AN3" s="514" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="486" t="n"/>
-      <c r="I4" s="408" t="inlineStr">
+      <c r="A4" s="504" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="505" t="n"/>
+      <c r="I4" s="515" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="AE4" s="403" t="inlineStr">
+      <c r="J4" s="516" t="n"/>
+      <c r="K4" s="516" t="n"/>
+      <c r="L4" s="516" t="n"/>
+      <c r="M4" s="516" t="n"/>
+      <c r="N4" s="516" t="n"/>
+      <c r="O4" s="516" t="n"/>
+      <c r="P4" s="516" t="n"/>
+      <c r="Q4" s="516" t="n"/>
+      <c r="R4" s="516" t="n"/>
+      <c r="S4" s="516" t="n"/>
+      <c r="T4" s="516" t="n"/>
+      <c r="U4" s="516" t="n"/>
+      <c r="V4" s="516" t="n"/>
+      <c r="W4" s="516" t="n"/>
+      <c r="X4" s="516" t="n"/>
+      <c r="Y4" s="516" t="n"/>
+      <c r="Z4" s="516" t="n"/>
+      <c r="AA4" s="516" t="n"/>
+      <c r="AB4" s="516" t="n"/>
+      <c r="AC4" s="516" t="n"/>
+      <c r="AD4" s="517" t="n"/>
+      <c r="AE4" s="509" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="487" t="n"/>
-      <c r="AG4" s="487" t="n"/>
-      <c r="AH4" s="488" t="n"/>
-      <c r="AI4" s="406" t="inlineStr">
+      <c r="AF4" s="510" t="n"/>
+      <c r="AG4" s="510" t="n"/>
+      <c r="AH4" s="511" t="n"/>
+      <c r="AI4" s="512" t="inlineStr">
         <is>
           <t>Planning / QA / Engineering</t>
         </is>
       </c>
-      <c r="AJ4" s="487" t="n"/>
-      <c r="AK4" s="487" t="n"/>
-      <c r="AL4" s="487" t="n"/>
-      <c r="AM4" s="487" t="n"/>
-      <c r="AN4" s="488" t="n"/>
+      <c r="AJ4" s="513" t="n"/>
+      <c r="AK4" s="513" t="n"/>
+      <c r="AL4" s="513" t="n"/>
+      <c r="AM4" s="513" t="n"/>
+      <c r="AN4" s="514" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="489" t="n"/>
-      <c r="B5" s="487" t="n"/>
-      <c r="C5" s="487" t="n"/>
-      <c r="D5" s="487" t="n"/>
-      <c r="E5" s="487" t="n"/>
-      <c r="F5" s="487" t="n"/>
-      <c r="G5" s="487" t="n"/>
-      <c r="H5" s="487" t="n"/>
-      <c r="I5" s="409" t="inlineStr">
+      <c r="A5" s="518" t="n"/>
+      <c r="B5" s="519" t="n"/>
+      <c r="C5" s="519" t="n"/>
+      <c r="D5" s="519" t="n"/>
+      <c r="E5" s="519" t="n"/>
+      <c r="F5" s="519" t="n"/>
+      <c r="G5" s="519" t="n"/>
+      <c r="H5" s="520" t="n"/>
+      <c r="I5" s="521" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="487" t="n"/>
-      <c r="K5" s="487" t="n"/>
-      <c r="L5" s="487" t="n"/>
-      <c r="M5" s="487" t="n"/>
-      <c r="N5" s="487" t="n"/>
-      <c r="O5" s="487" t="n"/>
-      <c r="P5" s="487" t="n"/>
-      <c r="Q5" s="487" t="n"/>
-      <c r="R5" s="487" t="n"/>
-      <c r="S5" s="487" t="n"/>
-      <c r="T5" s="487" t="n"/>
-      <c r="U5" s="487" t="n"/>
-      <c r="V5" s="487" t="n"/>
-      <c r="W5" s="487" t="n"/>
-      <c r="X5" s="487" t="n"/>
-      <c r="Y5" s="487" t="n"/>
-      <c r="Z5" s="487" t="n"/>
-      <c r="AA5" s="487" t="n"/>
-      <c r="AB5" s="487" t="n"/>
-      <c r="AC5" s="487" t="n"/>
-      <c r="AD5" s="487" t="n"/>
-      <c r="AE5" s="403" t="inlineStr">
+      <c r="J5" s="522" t="n"/>
+      <c r="K5" s="522" t="n"/>
+      <c r="L5" s="522" t="n"/>
+      <c r="M5" s="522" t="n"/>
+      <c r="N5" s="522" t="n"/>
+      <c r="O5" s="522" t="n"/>
+      <c r="P5" s="522" t="n"/>
+      <c r="Q5" s="522" t="n"/>
+      <c r="R5" s="522" t="n"/>
+      <c r="S5" s="522" t="n"/>
+      <c r="T5" s="522" t="n"/>
+      <c r="U5" s="522" t="n"/>
+      <c r="V5" s="522" t="n"/>
+      <c r="W5" s="522" t="n"/>
+      <c r="X5" s="522" t="n"/>
+      <c r="Y5" s="522" t="n"/>
+      <c r="Z5" s="522" t="n"/>
+      <c r="AA5" s="522" t="n"/>
+      <c r="AB5" s="522" t="n"/>
+      <c r="AC5" s="522" t="n"/>
+      <c r="AD5" s="523" t="n"/>
+      <c r="AE5" s="524" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="487" t="n"/>
-      <c r="AG5" s="487" t="n"/>
-      <c r="AH5" s="488" t="n"/>
-      <c r="AI5" s="406" t="inlineStr">
+      <c r="AF5" s="525" t="n"/>
+      <c r="AG5" s="525" t="n"/>
+      <c r="AH5" s="526" t="n"/>
+      <c r="AI5" s="527" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="487" t="n"/>
-      <c r="AK5" s="487" t="n"/>
-      <c r="AL5" s="487" t="n"/>
-      <c r="AM5" s="487" t="n"/>
-      <c r="AN5" s="488" t="n"/>
+      <c r="AJ5" s="528" t="n"/>
+      <c r="AK5" s="528" t="n"/>
+      <c r="AL5" s="528" t="n"/>
+      <c r="AM5" s="528" t="n"/>
+      <c r="AN5" s="529" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="410" t="inlineStr"/>
-      <c r="B6" s="482" t="n"/>
-      <c r="C6" s="482" t="n"/>
-      <c r="D6" s="482" t="n"/>
-      <c r="E6" s="482" t="n"/>
-      <c r="F6" s="482" t="n"/>
-      <c r="G6" s="482" t="n"/>
-      <c r="H6" s="482" t="n"/>
-      <c r="I6" s="482" t="n"/>
-      <c r="J6" s="482" t="n"/>
-      <c r="K6" s="482" t="n"/>
-      <c r="L6" s="482" t="n"/>
-      <c r="M6" s="482" t="n"/>
-      <c r="N6" s="482" t="n"/>
-      <c r="O6" s="482" t="n"/>
-      <c r="P6" s="482" t="n"/>
-      <c r="Q6" s="482" t="n"/>
-      <c r="R6" s="482" t="n"/>
-      <c r="S6" s="482" t="n"/>
-      <c r="T6" s="482" t="n"/>
-      <c r="U6" s="482" t="n"/>
-      <c r="V6" s="482" t="n"/>
-      <c r="W6" s="482" t="n"/>
-      <c r="X6" s="482" t="n"/>
-      <c r="Y6" s="482" t="n"/>
-      <c r="Z6" s="482" t="n"/>
-      <c r="AA6" s="482" t="n"/>
-      <c r="AB6" s="482" t="n"/>
-      <c r="AC6" s="482" t="n"/>
-      <c r="AD6" s="482" t="n"/>
-      <c r="AE6" s="482" t="n"/>
-      <c r="AF6" s="482" t="n"/>
-      <c r="AG6" s="482" t="n"/>
-      <c r="AH6" s="482" t="n"/>
-      <c r="AI6" s="482" t="n"/>
-      <c r="AJ6" s="482" t="n"/>
-      <c r="AK6" s="482" t="n"/>
-      <c r="AL6" s="482" t="n"/>
-      <c r="AM6" s="482" t="n"/>
-      <c r="AN6" s="482" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="530" t="n"/>
+      <c r="B6" s="530" t="n"/>
+      <c r="C6" s="530" t="n"/>
+      <c r="D6" s="530" t="n"/>
+      <c r="E6" s="530" t="n"/>
+      <c r="F6" s="530" t="n"/>
+      <c r="G6" s="530" t="n"/>
+      <c r="H6" s="530" t="n"/>
+      <c r="I6" s="530" t="n"/>
+      <c r="J6" s="530" t="n"/>
+      <c r="K6" s="530" t="n"/>
+      <c r="L6" s="530" t="n"/>
+      <c r="M6" s="530" t="n"/>
+      <c r="N6" s="530" t="n"/>
+      <c r="O6" s="530" t="n"/>
+      <c r="P6" s="530" t="n"/>
+      <c r="Q6" s="530" t="n"/>
+      <c r="R6" s="530" t="n"/>
+      <c r="S6" s="530" t="n"/>
+      <c r="T6" s="530" t="n"/>
+      <c r="U6" s="530" t="n"/>
+      <c r="V6" s="530" t="n"/>
+      <c r="W6" s="530" t="n"/>
+      <c r="X6" s="530" t="n"/>
+      <c r="Y6" s="530" t="n"/>
+      <c r="Z6" s="530" t="n"/>
+      <c r="AA6" s="530" t="n"/>
+      <c r="AB6" s="530" t="n"/>
+      <c r="AC6" s="530" t="n"/>
+      <c r="AD6" s="530" t="n"/>
+      <c r="AE6" s="530" t="n"/>
+      <c r="AF6" s="530" t="n"/>
+      <c r="AG6" s="530" t="n"/>
+      <c r="AH6" s="530" t="n"/>
+      <c r="AI6" s="530" t="n"/>
+      <c r="AJ6" s="530" t="n"/>
+      <c r="AK6" s="530" t="n"/>
+      <c r="AL6" s="530" t="n"/>
+      <c r="AM6" s="530" t="n"/>
+      <c r="AN6" s="530" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="411" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="531" t="inlineStr">
         <is>
           <t>1.  HIGH-RISK JOB HEADER / REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="484" t="n"/>
-      <c r="C7" s="484" t="n"/>
-      <c r="D7" s="484" t="n"/>
-      <c r="E7" s="484" t="n"/>
-      <c r="F7" s="484" t="n"/>
-      <c r="G7" s="484" t="n"/>
-      <c r="H7" s="484" t="n"/>
-      <c r="I7" s="484" t="n"/>
-      <c r="J7" s="484" t="n"/>
-      <c r="K7" s="484" t="n"/>
-      <c r="L7" s="484" t="n"/>
-      <c r="M7" s="484" t="n"/>
-      <c r="N7" s="484" t="n"/>
-      <c r="O7" s="484" t="n"/>
-      <c r="P7" s="484" t="n"/>
-      <c r="Q7" s="484" t="n"/>
-      <c r="R7" s="484" t="n"/>
-      <c r="S7" s="484" t="n"/>
-      <c r="T7" s="484" t="n"/>
-      <c r="U7" s="484" t="n"/>
-      <c r="V7" s="484" t="n"/>
-      <c r="W7" s="484" t="n"/>
-      <c r="X7" s="484" t="n"/>
-      <c r="Y7" s="484" t="n"/>
-      <c r="Z7" s="484" t="n"/>
-      <c r="AA7" s="484" t="n"/>
-      <c r="AB7" s="484" t="n"/>
-      <c r="AC7" s="484" t="n"/>
-      <c r="AD7" s="484" t="n"/>
-      <c r="AE7" s="484" t="n"/>
-      <c r="AF7" s="484" t="n"/>
-      <c r="AG7" s="484" t="n"/>
-      <c r="AH7" s="484" t="n"/>
-      <c r="AI7" s="484" t="n"/>
-      <c r="AJ7" s="484" t="n"/>
-      <c r="AK7" s="484" t="n"/>
-      <c r="AL7" s="484" t="n"/>
-      <c r="AM7" s="484" t="n"/>
-      <c r="AN7" s="485" t="n"/>
+      <c r="B7" s="532" t="n"/>
+      <c r="C7" s="532" t="n"/>
+      <c r="D7" s="532" t="n"/>
+      <c r="E7" s="532" t="n"/>
+      <c r="F7" s="532" t="n"/>
+      <c r="G7" s="532" t="n"/>
+      <c r="H7" s="532" t="n"/>
+      <c r="I7" s="532" t="n"/>
+      <c r="J7" s="532" t="n"/>
+      <c r="K7" s="532" t="n"/>
+      <c r="L7" s="532" t="n"/>
+      <c r="M7" s="532" t="n"/>
+      <c r="N7" s="532" t="n"/>
+      <c r="O7" s="532" t="n"/>
+      <c r="P7" s="532" t="n"/>
+      <c r="Q7" s="532" t="n"/>
+      <c r="R7" s="532" t="n"/>
+      <c r="S7" s="532" t="n"/>
+      <c r="T7" s="532" t="n"/>
+      <c r="U7" s="532" t="n"/>
+      <c r="V7" s="532" t="n"/>
+      <c r="W7" s="532" t="n"/>
+      <c r="X7" s="532" t="n"/>
+      <c r="Y7" s="532" t="n"/>
+      <c r="Z7" s="532" t="n"/>
+      <c r="AA7" s="532" t="n"/>
+      <c r="AB7" s="532" t="n"/>
+      <c r="AC7" s="532" t="n"/>
+      <c r="AD7" s="532" t="n"/>
+      <c r="AE7" s="532" t="n"/>
+      <c r="AF7" s="532" t="n"/>
+      <c r="AG7" s="532" t="n"/>
+      <c r="AH7" s="532" t="n"/>
+      <c r="AI7" s="532" t="n"/>
+      <c r="AJ7" s="532" t="n"/>
+      <c r="AK7" s="532" t="n"/>
+      <c r="AL7" s="532" t="n"/>
+      <c r="AM7" s="532" t="n"/>
+      <c r="AN7" s="533" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="412" t="inlineStr">
+      <c r="A8" s="534" t="inlineStr">
         <is>
           <t>Readiness Review ID</t>
         </is>
       </c>
-      <c r="B8" s="473" t="n"/>
-      <c r="C8" s="473" t="n"/>
-      <c r="D8" s="473" t="n"/>
-      <c r="E8" s="473" t="n"/>
-      <c r="F8" s="473" t="n"/>
-      <c r="G8" s="474" t="n"/>
-      <c r="H8" s="415" t="inlineStr"/>
-      <c r="I8" s="473" t="n"/>
-      <c r="J8" s="473" t="n"/>
-      <c r="K8" s="473" t="n"/>
-      <c r="L8" s="473" t="n"/>
-      <c r="M8" s="473" t="n"/>
-      <c r="N8" s="473" t="n"/>
-      <c r="O8" s="473" t="n"/>
-      <c r="P8" s="473" t="n"/>
-      <c r="Q8" s="473" t="n"/>
-      <c r="R8" s="473" t="n"/>
-      <c r="S8" s="473" t="n"/>
-      <c r="T8" s="474" t="n"/>
-      <c r="U8" s="416" t="inlineStr">
+      <c r="B8" s="535" t="n"/>
+      <c r="C8" s="535" t="n"/>
+      <c r="D8" s="535" t="n"/>
+      <c r="E8" s="535" t="n"/>
+      <c r="F8" s="535" t="n"/>
+      <c r="G8" s="535" t="n"/>
+      <c r="H8" s="536" t="inlineStr"/>
+      <c r="I8" s="535" t="n"/>
+      <c r="J8" s="535" t="n"/>
+      <c r="K8" s="535" t="n"/>
+      <c r="L8" s="535" t="n"/>
+      <c r="M8" s="535" t="n"/>
+      <c r="N8" s="535" t="n"/>
+      <c r="O8" s="535" t="n"/>
+      <c r="P8" s="535" t="n"/>
+      <c r="Q8" s="535" t="n"/>
+      <c r="R8" s="535" t="n"/>
+      <c r="S8" s="535" t="n"/>
+      <c r="T8" s="535" t="n"/>
+      <c r="U8" s="537" t="inlineStr">
         <is>
           <t>Job / WO</t>
         </is>
       </c>
-      <c r="V8" s="473" t="n"/>
-      <c r="W8" s="473" t="n"/>
-      <c r="X8" s="473" t="n"/>
-      <c r="Y8" s="473" t="n"/>
-      <c r="Z8" s="473" t="n"/>
-      <c r="AA8" s="474" t="n"/>
-      <c r="AB8" s="415" t="inlineStr"/>
-      <c r="AC8" s="473" t="n"/>
-      <c r="AD8" s="473" t="n"/>
-      <c r="AE8" s="473" t="n"/>
-      <c r="AF8" s="473" t="n"/>
-      <c r="AG8" s="473" t="n"/>
-      <c r="AH8" s="473" t="n"/>
-      <c r="AI8" s="473" t="n"/>
-      <c r="AJ8" s="473" t="n"/>
-      <c r="AK8" s="473" t="n"/>
-      <c r="AL8" s="473" t="n"/>
-      <c r="AM8" s="473" t="n"/>
-      <c r="AN8" s="474" t="n"/>
+      <c r="V8" s="535" t="n"/>
+      <c r="W8" s="535" t="n"/>
+      <c r="X8" s="535" t="n"/>
+      <c r="Y8" s="535" t="n"/>
+      <c r="Z8" s="535" t="n"/>
+      <c r="AA8" s="535" t="n"/>
+      <c r="AB8" s="536" t="inlineStr"/>
+      <c r="AC8" s="535" t="n"/>
+      <c r="AD8" s="535" t="n"/>
+      <c r="AE8" s="535" t="n"/>
+      <c r="AF8" s="535" t="n"/>
+      <c r="AG8" s="535" t="n"/>
+      <c r="AH8" s="535" t="n"/>
+      <c r="AI8" s="535" t="n"/>
+      <c r="AJ8" s="535" t="n"/>
+      <c r="AK8" s="535" t="n"/>
+      <c r="AL8" s="535" t="n"/>
+      <c r="AM8" s="535" t="n"/>
+      <c r="AN8" s="538" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="417" t="inlineStr">
+      <c r="A9" s="539" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="B9" s="475" t="n"/>
-      <c r="C9" s="475" t="n"/>
-      <c r="D9" s="475" t="n"/>
-      <c r="E9" s="475" t="n"/>
-      <c r="F9" s="475" t="n"/>
-      <c r="G9" s="476" t="n"/>
-      <c r="H9" s="406" t="inlineStr"/>
-      <c r="I9" s="475" t="n"/>
-      <c r="J9" s="475" t="n"/>
-      <c r="K9" s="475" t="n"/>
-      <c r="L9" s="475" t="n"/>
-      <c r="M9" s="475" t="n"/>
-      <c r="N9" s="475" t="n"/>
-      <c r="O9" s="475" t="n"/>
-      <c r="P9" s="475" t="n"/>
-      <c r="Q9" s="475" t="n"/>
-      <c r="R9" s="475" t="n"/>
-      <c r="S9" s="475" t="n"/>
-      <c r="T9" s="476" t="n"/>
-      <c r="U9" s="420" t="inlineStr">
+      <c r="B9" s="398" t="n"/>
+      <c r="C9" s="398" t="n"/>
+      <c r="D9" s="398" t="n"/>
+      <c r="E9" s="398" t="n"/>
+      <c r="F9" s="398" t="n"/>
+      <c r="G9" s="398" t="n"/>
+      <c r="H9" s="540" t="inlineStr"/>
+      <c r="I9" s="398" t="n"/>
+      <c r="J9" s="398" t="n"/>
+      <c r="K9" s="398" t="n"/>
+      <c r="L9" s="398" t="n"/>
+      <c r="M9" s="398" t="n"/>
+      <c r="N9" s="398" t="n"/>
+      <c r="O9" s="398" t="n"/>
+      <c r="P9" s="398" t="n"/>
+      <c r="Q9" s="398" t="n"/>
+      <c r="R9" s="398" t="n"/>
+      <c r="S9" s="398" t="n"/>
+      <c r="T9" s="398" t="n"/>
+      <c r="U9" s="541" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="V9" s="475" t="n"/>
-      <c r="W9" s="475" t="n"/>
-      <c r="X9" s="475" t="n"/>
-      <c r="Y9" s="475" t="n"/>
-      <c r="Z9" s="475" t="n"/>
-      <c r="AA9" s="476" t="n"/>
-      <c r="AB9" s="406" t="inlineStr"/>
-      <c r="AC9" s="475" t="n"/>
-      <c r="AD9" s="475" t="n"/>
-      <c r="AE9" s="475" t="n"/>
-      <c r="AF9" s="475" t="n"/>
-      <c r="AG9" s="475" t="n"/>
-      <c r="AH9" s="475" t="n"/>
-      <c r="AI9" s="475" t="n"/>
-      <c r="AJ9" s="475" t="n"/>
-      <c r="AK9" s="475" t="n"/>
-      <c r="AL9" s="475" t="n"/>
-      <c r="AM9" s="475" t="n"/>
-      <c r="AN9" s="476" t="n"/>
+      <c r="V9" s="398" t="n"/>
+      <c r="W9" s="398" t="n"/>
+      <c r="X9" s="398" t="n"/>
+      <c r="Y9" s="398" t="n"/>
+      <c r="Z9" s="398" t="n"/>
+      <c r="AA9" s="398" t="n"/>
+      <c r="AB9" s="540" t="inlineStr"/>
+      <c r="AC9" s="398" t="n"/>
+      <c r="AD9" s="398" t="n"/>
+      <c r="AE9" s="398" t="n"/>
+      <c r="AF9" s="398" t="n"/>
+      <c r="AG9" s="398" t="n"/>
+      <c r="AH9" s="398" t="n"/>
+      <c r="AI9" s="398" t="n"/>
+      <c r="AJ9" s="398" t="n"/>
+      <c r="AK9" s="398" t="n"/>
+      <c r="AL9" s="398" t="n"/>
+      <c r="AM9" s="398" t="n"/>
+      <c r="AN9" s="542" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="417" t="inlineStr">
+      <c r="A10" s="539" t="inlineStr">
         <is>
           <t>Due Date / Commit</t>
         </is>
       </c>
-      <c r="B10" s="470" t="n"/>
-      <c r="C10" s="470" t="n"/>
-      <c r="D10" s="470" t="n"/>
-      <c r="E10" s="470" t="n"/>
-      <c r="F10" s="470" t="n"/>
-      <c r="G10" s="471" t="n"/>
-      <c r="H10" s="406" t="inlineStr"/>
-      <c r="I10" s="470" t="n"/>
-      <c r="J10" s="470" t="n"/>
-      <c r="K10" s="470" t="n"/>
-      <c r="L10" s="470" t="n"/>
-      <c r="M10" s="470" t="n"/>
-      <c r="N10" s="470" t="n"/>
-      <c r="O10" s="470" t="n"/>
-      <c r="P10" s="470" t="n"/>
-      <c r="Q10" s="470" t="n"/>
-      <c r="R10" s="470" t="n"/>
-      <c r="S10" s="470" t="n"/>
-      <c r="T10" s="471" t="n"/>
-      <c r="U10" s="420" t="inlineStr">
+      <c r="B10" s="398" t="n"/>
+      <c r="C10" s="398" t="n"/>
+      <c r="D10" s="398" t="n"/>
+      <c r="E10" s="398" t="n"/>
+      <c r="F10" s="398" t="n"/>
+      <c r="G10" s="398" t="n"/>
+      <c r="H10" s="540" t="inlineStr"/>
+      <c r="I10" s="398" t="n"/>
+      <c r="J10" s="398" t="n"/>
+      <c r="K10" s="398" t="n"/>
+      <c r="L10" s="398" t="n"/>
+      <c r="M10" s="398" t="n"/>
+      <c r="N10" s="398" t="n"/>
+      <c r="O10" s="398" t="n"/>
+      <c r="P10" s="398" t="n"/>
+      <c r="Q10" s="398" t="n"/>
+      <c r="R10" s="398" t="n"/>
+      <c r="S10" s="398" t="n"/>
+      <c r="T10" s="398" t="n"/>
+      <c r="U10" s="541" t="inlineStr">
         <is>
           <t>Current Route Step</t>
         </is>
       </c>
-      <c r="V10" s="470" t="n"/>
-      <c r="W10" s="470" t="n"/>
-      <c r="X10" s="470" t="n"/>
-      <c r="Y10" s="470" t="n"/>
-      <c r="Z10" s="470" t="n"/>
-      <c r="AA10" s="471" t="n"/>
-      <c r="AB10" s="406" t="inlineStr"/>
-      <c r="AC10" s="470" t="n"/>
-      <c r="AD10" s="470" t="n"/>
-      <c r="AE10" s="470" t="n"/>
-      <c r="AF10" s="470" t="n"/>
-      <c r="AG10" s="470" t="n"/>
-      <c r="AH10" s="470" t="n"/>
-      <c r="AI10" s="470" t="n"/>
-      <c r="AJ10" s="470" t="n"/>
-      <c r="AK10" s="470" t="n"/>
-      <c r="AL10" s="470" t="n"/>
-      <c r="AM10" s="470" t="n"/>
-      <c r="AN10" s="471" t="n"/>
+      <c r="V10" s="398" t="n"/>
+      <c r="W10" s="398" t="n"/>
+      <c r="X10" s="398" t="n"/>
+      <c r="Y10" s="398" t="n"/>
+      <c r="Z10" s="398" t="n"/>
+      <c r="AA10" s="398" t="n"/>
+      <c r="AB10" s="540" t="inlineStr"/>
+      <c r="AC10" s="398" t="n"/>
+      <c r="AD10" s="398" t="n"/>
+      <c r="AE10" s="398" t="n"/>
+      <c r="AF10" s="398" t="n"/>
+      <c r="AG10" s="398" t="n"/>
+      <c r="AH10" s="398" t="n"/>
+      <c r="AI10" s="398" t="n"/>
+      <c r="AJ10" s="398" t="n"/>
+      <c r="AK10" s="398" t="n"/>
+      <c r="AL10" s="398" t="n"/>
+      <c r="AM10" s="398" t="n"/>
+      <c r="AN10" s="542" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="417" t="inlineStr">
+      <c r="A11" s="539" t="inlineStr">
         <is>
           <t>Top Risk Class</t>
         </is>
       </c>
-      <c r="B11" s="475" t="n"/>
-      <c r="C11" s="475" t="n"/>
-      <c r="D11" s="475" t="n"/>
-      <c r="E11" s="475" t="n"/>
-      <c r="F11" s="475" t="n"/>
-      <c r="G11" s="476" t="n"/>
-      <c r="H11" s="406" t="inlineStr"/>
-      <c r="I11" s="475" t="n"/>
-      <c r="J11" s="475" t="n"/>
-      <c r="K11" s="475" t="n"/>
-      <c r="L11" s="475" t="n"/>
-      <c r="M11" s="475" t="n"/>
-      <c r="N11" s="475" t="n"/>
-      <c r="O11" s="475" t="n"/>
-      <c r="P11" s="475" t="n"/>
-      <c r="Q11" s="475" t="n"/>
-      <c r="R11" s="475" t="n"/>
-      <c r="S11" s="475" t="n"/>
-      <c r="T11" s="476" t="n"/>
-      <c r="U11" s="420" t="inlineStr">
+      <c r="B11" s="398" t="n"/>
+      <c r="C11" s="398" t="n"/>
+      <c r="D11" s="398" t="n"/>
+      <c r="E11" s="398" t="n"/>
+      <c r="F11" s="398" t="n"/>
+      <c r="G11" s="398" t="n"/>
+      <c r="H11" s="540" t="inlineStr"/>
+      <c r="I11" s="398" t="n"/>
+      <c r="J11" s="398" t="n"/>
+      <c r="K11" s="398" t="n"/>
+      <c r="L11" s="398" t="n"/>
+      <c r="M11" s="398" t="n"/>
+      <c r="N11" s="398" t="n"/>
+      <c r="O11" s="398" t="n"/>
+      <c r="P11" s="398" t="n"/>
+      <c r="Q11" s="398" t="n"/>
+      <c r="R11" s="398" t="n"/>
+      <c r="S11" s="398" t="n"/>
+      <c r="T11" s="398" t="n"/>
+      <c r="U11" s="541" t="inlineStr">
         <is>
           <t>Commercial / Ops Owner</t>
         </is>
       </c>
-      <c r="V11" s="475" t="n"/>
-      <c r="W11" s="475" t="n"/>
-      <c r="X11" s="475" t="n"/>
-      <c r="Y11" s="475" t="n"/>
-      <c r="Z11" s="475" t="n"/>
-      <c r="AA11" s="476" t="n"/>
-      <c r="AB11" s="406" t="inlineStr"/>
-      <c r="AC11" s="475" t="n"/>
-      <c r="AD11" s="475" t="n"/>
-      <c r="AE11" s="475" t="n"/>
-      <c r="AF11" s="475" t="n"/>
-      <c r="AG11" s="475" t="n"/>
-      <c r="AH11" s="475" t="n"/>
-      <c r="AI11" s="475" t="n"/>
-      <c r="AJ11" s="475" t="n"/>
-      <c r="AK11" s="475" t="n"/>
-      <c r="AL11" s="475" t="n"/>
-      <c r="AM11" s="475" t="n"/>
-      <c r="AN11" s="476" t="n"/>
+      <c r="V11" s="398" t="n"/>
+      <c r="W11" s="398" t="n"/>
+      <c r="X11" s="398" t="n"/>
+      <c r="Y11" s="398" t="n"/>
+      <c r="Z11" s="398" t="n"/>
+      <c r="AA11" s="398" t="n"/>
+      <c r="AB11" s="540" t="inlineStr"/>
+      <c r="AC11" s="398" t="n"/>
+      <c r="AD11" s="398" t="n"/>
+      <c r="AE11" s="398" t="n"/>
+      <c r="AF11" s="398" t="n"/>
+      <c r="AG11" s="398" t="n"/>
+      <c r="AH11" s="398" t="n"/>
+      <c r="AI11" s="398" t="n"/>
+      <c r="AJ11" s="398" t="n"/>
+      <c r="AK11" s="398" t="n"/>
+      <c r="AL11" s="398" t="n"/>
+      <c r="AM11" s="398" t="n"/>
+      <c r="AN11" s="542" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="417" t="inlineStr">
+      <c r="A12" s="543" t="inlineStr">
         <is>
           <t>Evidence Folder</t>
         </is>
       </c>
-      <c r="B12" s="475" t="n"/>
-      <c r="C12" s="475" t="n"/>
-      <c r="D12" s="475" t="n"/>
-      <c r="E12" s="475" t="n"/>
-      <c r="F12" s="475" t="n"/>
-      <c r="G12" s="476" t="n"/>
-      <c r="H12" s="406" t="inlineStr"/>
-      <c r="I12" s="475" t="n"/>
-      <c r="J12" s="475" t="n"/>
-      <c r="K12" s="475" t="n"/>
-      <c r="L12" s="475" t="n"/>
-      <c r="M12" s="475" t="n"/>
-      <c r="N12" s="475" t="n"/>
-      <c r="O12" s="475" t="n"/>
-      <c r="P12" s="475" t="n"/>
-      <c r="Q12" s="475" t="n"/>
-      <c r="R12" s="475" t="n"/>
-      <c r="S12" s="475" t="n"/>
-      <c r="T12" s="476" t="n"/>
-      <c r="U12" s="420" t="inlineStr">
+      <c r="B12" s="544" t="n"/>
+      <c r="C12" s="544" t="n"/>
+      <c r="D12" s="544" t="n"/>
+      <c r="E12" s="544" t="n"/>
+      <c r="F12" s="544" t="n"/>
+      <c r="G12" s="544" t="n"/>
+      <c r="H12" s="545" t="inlineStr"/>
+      <c r="I12" s="544" t="n"/>
+      <c r="J12" s="544" t="n"/>
+      <c r="K12" s="544" t="n"/>
+      <c r="L12" s="544" t="n"/>
+      <c r="M12" s="544" t="n"/>
+      <c r="N12" s="544" t="n"/>
+      <c r="O12" s="544" t="n"/>
+      <c r="P12" s="544" t="n"/>
+      <c r="Q12" s="544" t="n"/>
+      <c r="R12" s="544" t="n"/>
+      <c r="S12" s="544" t="n"/>
+      <c r="T12" s="544" t="n"/>
+      <c r="U12" s="546" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="V12" s="475" t="n"/>
-      <c r="W12" s="475" t="n"/>
-      <c r="X12" s="475" t="n"/>
-      <c r="Y12" s="475" t="n"/>
-      <c r="Z12" s="475" t="n"/>
-      <c r="AA12" s="476" t="n"/>
-      <c r="AB12" s="406" t="inlineStr"/>
-      <c r="AC12" s="475" t="n"/>
-      <c r="AD12" s="475" t="n"/>
-      <c r="AE12" s="475" t="n"/>
-      <c r="AF12" s="475" t="n"/>
-      <c r="AG12" s="475" t="n"/>
-      <c r="AH12" s="475" t="n"/>
-      <c r="AI12" s="475" t="n"/>
-      <c r="AJ12" s="475" t="n"/>
-      <c r="AK12" s="475" t="n"/>
-      <c r="AL12" s="475" t="n"/>
-      <c r="AM12" s="475" t="n"/>
-      <c r="AN12" s="476" t="n"/>
+      <c r="V12" s="544" t="n"/>
+      <c r="W12" s="544" t="n"/>
+      <c r="X12" s="544" t="n"/>
+      <c r="Y12" s="544" t="n"/>
+      <c r="Z12" s="544" t="n"/>
+      <c r="AA12" s="544" t="n"/>
+      <c r="AB12" s="545" t="inlineStr"/>
+      <c r="AC12" s="544" t="n"/>
+      <c r="AD12" s="544" t="n"/>
+      <c r="AE12" s="544" t="n"/>
+      <c r="AF12" s="544" t="n"/>
+      <c r="AG12" s="544" t="n"/>
+      <c r="AH12" s="544" t="n"/>
+      <c r="AI12" s="544" t="n"/>
+      <c r="AJ12" s="544" t="n"/>
+      <c r="AK12" s="544" t="n"/>
+      <c r="AL12" s="544" t="n"/>
+      <c r="AM12" s="544" t="n"/>
+      <c r="AN12" s="547" t="n"/>
     </row>
-    <row r="13" ht="4" customHeight="1">
+    <row r="13" ht="3" customHeight="1">
       <c r="A13" s="410" t="n"/>
       <c r="B13" s="482" t="n"/>
       <c r="C13" s="482" t="n"/>
@@ -6243,263 +7104,263 @@
       <c r="AM13" s="482" t="n"/>
       <c r="AN13" s="482" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="411" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="531" t="inlineStr">
         <is>
           <t>2.  READINESS DECISION / OPEN RISK CONDITIONS</t>
         </is>
       </c>
-      <c r="B14" s="473" t="n"/>
-      <c r="C14" s="473" t="n"/>
-      <c r="D14" s="473" t="n"/>
-      <c r="E14" s="473" t="n"/>
-      <c r="F14" s="473" t="n"/>
-      <c r="G14" s="473" t="n"/>
-      <c r="H14" s="473" t="n"/>
-      <c r="I14" s="473" t="n"/>
-      <c r="J14" s="473" t="n"/>
-      <c r="K14" s="473" t="n"/>
-      <c r="L14" s="473" t="n"/>
-      <c r="M14" s="473" t="n"/>
-      <c r="N14" s="473" t="n"/>
-      <c r="O14" s="473" t="n"/>
-      <c r="P14" s="473" t="n"/>
-      <c r="Q14" s="473" t="n"/>
-      <c r="R14" s="473" t="n"/>
-      <c r="S14" s="473" t="n"/>
-      <c r="T14" s="473" t="n"/>
-      <c r="U14" s="473" t="n"/>
-      <c r="V14" s="473" t="n"/>
-      <c r="W14" s="473" t="n"/>
-      <c r="X14" s="473" t="n"/>
-      <c r="Y14" s="473" t="n"/>
-      <c r="Z14" s="473" t="n"/>
-      <c r="AA14" s="473" t="n"/>
-      <c r="AB14" s="473" t="n"/>
-      <c r="AC14" s="473" t="n"/>
-      <c r="AD14" s="473" t="n"/>
-      <c r="AE14" s="473" t="n"/>
-      <c r="AF14" s="473" t="n"/>
-      <c r="AG14" s="473" t="n"/>
-      <c r="AH14" s="473" t="n"/>
-      <c r="AI14" s="473" t="n"/>
-      <c r="AJ14" s="473" t="n"/>
-      <c r="AK14" s="473" t="n"/>
-      <c r="AL14" s="473" t="n"/>
-      <c r="AM14" s="473" t="n"/>
-      <c r="AN14" s="474" t="n"/>
+      <c r="B14" s="532" t="n"/>
+      <c r="C14" s="532" t="n"/>
+      <c r="D14" s="532" t="n"/>
+      <c r="E14" s="532" t="n"/>
+      <c r="F14" s="532" t="n"/>
+      <c r="G14" s="532" t="n"/>
+      <c r="H14" s="532" t="n"/>
+      <c r="I14" s="532" t="n"/>
+      <c r="J14" s="532" t="n"/>
+      <c r="K14" s="532" t="n"/>
+      <c r="L14" s="532" t="n"/>
+      <c r="M14" s="532" t="n"/>
+      <c r="N14" s="532" t="n"/>
+      <c r="O14" s="532" t="n"/>
+      <c r="P14" s="532" t="n"/>
+      <c r="Q14" s="532" t="n"/>
+      <c r="R14" s="532" t="n"/>
+      <c r="S14" s="532" t="n"/>
+      <c r="T14" s="532" t="n"/>
+      <c r="U14" s="532" t="n"/>
+      <c r="V14" s="532" t="n"/>
+      <c r="W14" s="532" t="n"/>
+      <c r="X14" s="532" t="n"/>
+      <c r="Y14" s="532" t="n"/>
+      <c r="Z14" s="532" t="n"/>
+      <c r="AA14" s="532" t="n"/>
+      <c r="AB14" s="532" t="n"/>
+      <c r="AC14" s="532" t="n"/>
+      <c r="AD14" s="532" t="n"/>
+      <c r="AE14" s="532" t="n"/>
+      <c r="AF14" s="532" t="n"/>
+      <c r="AG14" s="532" t="n"/>
+      <c r="AH14" s="532" t="n"/>
+      <c r="AI14" s="532" t="n"/>
+      <c r="AJ14" s="532" t="n"/>
+      <c r="AK14" s="532" t="n"/>
+      <c r="AL14" s="532" t="n"/>
+      <c r="AM14" s="532" t="n"/>
+      <c r="AN14" s="533" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="412" t="inlineStr">
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="534" t="inlineStr">
         <is>
           <t>Gate Name / Trigger</t>
         </is>
       </c>
-      <c r="B15" s="467" t="n"/>
-      <c r="C15" s="467" t="n"/>
-      <c r="D15" s="467" t="n"/>
-      <c r="E15" s="467" t="n"/>
-      <c r="F15" s="467" t="n"/>
-      <c r="G15" s="468" t="n"/>
-      <c r="H15" s="415" t="inlineStr">
+      <c r="B15" s="535" t="n"/>
+      <c r="C15" s="535" t="n"/>
+      <c r="D15" s="535" t="n"/>
+      <c r="E15" s="535" t="n"/>
+      <c r="F15" s="535" t="n"/>
+      <c r="G15" s="535" t="n"/>
+      <c r="H15" s="536" t="inlineStr">
         <is>
           <t>High-risk job release review</t>
         </is>
       </c>
-      <c r="I15" s="467" t="n"/>
-      <c r="J15" s="467" t="n"/>
-      <c r="K15" s="467" t="n"/>
-      <c r="L15" s="467" t="n"/>
-      <c r="M15" s="467" t="n"/>
-      <c r="N15" s="467" t="n"/>
-      <c r="O15" s="467" t="n"/>
-      <c r="P15" s="467" t="n"/>
-      <c r="Q15" s="467" t="n"/>
-      <c r="R15" s="467" t="n"/>
-      <c r="S15" s="467" t="n"/>
-      <c r="T15" s="468" t="n"/>
-      <c r="U15" s="416" t="inlineStr">
+      <c r="I15" s="535" t="n"/>
+      <c r="J15" s="535" t="n"/>
+      <c r="K15" s="535" t="n"/>
+      <c r="L15" s="535" t="n"/>
+      <c r="M15" s="535" t="n"/>
+      <c r="N15" s="535" t="n"/>
+      <c r="O15" s="535" t="n"/>
+      <c r="P15" s="535" t="n"/>
+      <c r="Q15" s="535" t="n"/>
+      <c r="R15" s="535" t="n"/>
+      <c r="S15" s="535" t="n"/>
+      <c r="T15" s="535" t="n"/>
+      <c r="U15" s="537" t="inlineStr">
         <is>
           <t>Gate Conclusion</t>
         </is>
       </c>
-      <c r="V15" s="467" t="n"/>
-      <c r="W15" s="467" t="n"/>
-      <c r="X15" s="467" t="n"/>
-      <c r="Y15" s="467" t="n"/>
-      <c r="Z15" s="467" t="n"/>
-      <c r="AA15" s="468" t="n"/>
-      <c r="AB15" s="415">
+      <c r="V15" s="535" t="n"/>
+      <c r="W15" s="535" t="n"/>
+      <c r="X15" s="535" t="n"/>
+      <c r="Y15" s="535" t="n"/>
+      <c r="Z15" s="535" t="n"/>
+      <c r="AA15" s="535" t="n"/>
+      <c r="AB15" s="536">
         <f>IF(COUNTA(AF22:AF31)=0,"",IF(COUNTIF(AF22:AF31,"FAIL")+COUNTIF(AF22:AF31,"HOLD")&gt;0,"HOLD",IF(COUNTIF(AF22:AF31,"PASS")=COUNTA(AF22:AF31),"APPROVED","CONDITIONAL")))</f>
         <v/>
       </c>
-      <c r="AC15" s="467" t="n"/>
-      <c r="AD15" s="467" t="n"/>
-      <c r="AE15" s="467" t="n"/>
-      <c r="AF15" s="467" t="n"/>
-      <c r="AG15" s="467" t="n"/>
-      <c r="AH15" s="467" t="n"/>
-      <c r="AI15" s="467" t="n"/>
-      <c r="AJ15" s="467" t="n"/>
-      <c r="AK15" s="467" t="n"/>
-      <c r="AL15" s="467" t="n"/>
-      <c r="AM15" s="467" t="n"/>
-      <c r="AN15" s="468" t="n"/>
+      <c r="AC15" s="535" t="n"/>
+      <c r="AD15" s="535" t="n"/>
+      <c r="AE15" s="535" t="n"/>
+      <c r="AF15" s="535" t="n"/>
+      <c r="AG15" s="535" t="n"/>
+      <c r="AH15" s="535" t="n"/>
+      <c r="AI15" s="535" t="n"/>
+      <c r="AJ15" s="535" t="n"/>
+      <c r="AK15" s="535" t="n"/>
+      <c r="AL15" s="535" t="n"/>
+      <c r="AM15" s="535" t="n"/>
+      <c r="AN15" s="538" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="417" t="inlineStr">
+      <c r="A16" s="539" t="inlineStr">
         <is>
           <t>Open Risk / Hold Reason</t>
         </is>
       </c>
-      <c r="B16" s="475" t="n"/>
-      <c r="C16" s="475" t="n"/>
-      <c r="D16" s="475" t="n"/>
-      <c r="E16" s="475" t="n"/>
-      <c r="F16" s="475" t="n"/>
-      <c r="G16" s="476" t="n"/>
-      <c r="H16" s="406" t="inlineStr"/>
-      <c r="I16" s="475" t="n"/>
-      <c r="J16" s="475" t="n"/>
-      <c r="K16" s="475" t="n"/>
-      <c r="L16" s="475" t="n"/>
-      <c r="M16" s="475" t="n"/>
-      <c r="N16" s="475" t="n"/>
-      <c r="O16" s="475" t="n"/>
-      <c r="P16" s="475" t="n"/>
-      <c r="Q16" s="475" t="n"/>
-      <c r="R16" s="475" t="n"/>
-      <c r="S16" s="475" t="n"/>
-      <c r="T16" s="476" t="n"/>
-      <c r="U16" s="420" t="inlineStr">
+      <c r="B16" s="398" t="n"/>
+      <c r="C16" s="398" t="n"/>
+      <c r="D16" s="398" t="n"/>
+      <c r="E16" s="398" t="n"/>
+      <c r="F16" s="398" t="n"/>
+      <c r="G16" s="398" t="n"/>
+      <c r="H16" s="540" t="inlineStr"/>
+      <c r="I16" s="398" t="n"/>
+      <c r="J16" s="398" t="n"/>
+      <c r="K16" s="398" t="n"/>
+      <c r="L16" s="398" t="n"/>
+      <c r="M16" s="398" t="n"/>
+      <c r="N16" s="398" t="n"/>
+      <c r="O16" s="398" t="n"/>
+      <c r="P16" s="398" t="n"/>
+      <c r="Q16" s="398" t="n"/>
+      <c r="R16" s="398" t="n"/>
+      <c r="S16" s="398" t="n"/>
+      <c r="T16" s="398" t="n"/>
+      <c r="U16" s="541" t="inlineStr">
         <is>
           <t>Next Step</t>
         </is>
       </c>
-      <c r="V16" s="475" t="n"/>
-      <c r="W16" s="475" t="n"/>
-      <c r="X16" s="475" t="n"/>
-      <c r="Y16" s="475" t="n"/>
-      <c r="Z16" s="475" t="n"/>
-      <c r="AA16" s="476" t="n"/>
-      <c r="AB16" s="406" t="inlineStr"/>
-      <c r="AC16" s="475" t="n"/>
-      <c r="AD16" s="475" t="n"/>
-      <c r="AE16" s="475" t="n"/>
-      <c r="AF16" s="475" t="n"/>
-      <c r="AG16" s="475" t="n"/>
-      <c r="AH16" s="475" t="n"/>
-      <c r="AI16" s="475" t="n"/>
-      <c r="AJ16" s="475" t="n"/>
-      <c r="AK16" s="475" t="n"/>
-      <c r="AL16" s="475" t="n"/>
-      <c r="AM16" s="475" t="n"/>
-      <c r="AN16" s="476" t="n"/>
+      <c r="V16" s="398" t="n"/>
+      <c r="W16" s="398" t="n"/>
+      <c r="X16" s="398" t="n"/>
+      <c r="Y16" s="398" t="n"/>
+      <c r="Z16" s="398" t="n"/>
+      <c r="AA16" s="398" t="n"/>
+      <c r="AB16" s="540" t="inlineStr"/>
+      <c r="AC16" s="398" t="n"/>
+      <c r="AD16" s="398" t="n"/>
+      <c r="AE16" s="398" t="n"/>
+      <c r="AF16" s="398" t="n"/>
+      <c r="AG16" s="398" t="n"/>
+      <c r="AH16" s="398" t="n"/>
+      <c r="AI16" s="398" t="n"/>
+      <c r="AJ16" s="398" t="n"/>
+      <c r="AK16" s="398" t="n"/>
+      <c r="AL16" s="398" t="n"/>
+      <c r="AM16" s="398" t="n"/>
+      <c r="AN16" s="542" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="417" t="inlineStr">
+      <c r="A17" s="539" t="inlineStr">
         <is>
           <t>Action Owner</t>
         </is>
       </c>
-      <c r="B17" s="475" t="n"/>
-      <c r="C17" s="475" t="n"/>
-      <c r="D17" s="475" t="n"/>
-      <c r="E17" s="475" t="n"/>
-      <c r="F17" s="475" t="n"/>
-      <c r="G17" s="476" t="n"/>
-      <c r="H17" s="406" t="inlineStr"/>
-      <c r="I17" s="475" t="n"/>
-      <c r="J17" s="475" t="n"/>
-      <c r="K17" s="475" t="n"/>
-      <c r="L17" s="475" t="n"/>
-      <c r="M17" s="475" t="n"/>
-      <c r="N17" s="475" t="n"/>
-      <c r="O17" s="475" t="n"/>
-      <c r="P17" s="475" t="n"/>
-      <c r="Q17" s="475" t="n"/>
-      <c r="R17" s="475" t="n"/>
-      <c r="S17" s="475" t="n"/>
-      <c r="T17" s="476" t="n"/>
-      <c r="U17" s="420" t="inlineStr">
+      <c r="B17" s="398" t="n"/>
+      <c r="C17" s="398" t="n"/>
+      <c r="D17" s="398" t="n"/>
+      <c r="E17" s="398" t="n"/>
+      <c r="F17" s="398" t="n"/>
+      <c r="G17" s="398" t="n"/>
+      <c r="H17" s="540" t="inlineStr"/>
+      <c r="I17" s="398" t="n"/>
+      <c r="J17" s="398" t="n"/>
+      <c r="K17" s="398" t="n"/>
+      <c r="L17" s="398" t="n"/>
+      <c r="M17" s="398" t="n"/>
+      <c r="N17" s="398" t="n"/>
+      <c r="O17" s="398" t="n"/>
+      <c r="P17" s="398" t="n"/>
+      <c r="Q17" s="398" t="n"/>
+      <c r="R17" s="398" t="n"/>
+      <c r="S17" s="398" t="n"/>
+      <c r="T17" s="398" t="n"/>
+      <c r="U17" s="541" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="V17" s="475" t="n"/>
-      <c r="W17" s="475" t="n"/>
-      <c r="X17" s="475" t="n"/>
-      <c r="Y17" s="475" t="n"/>
-      <c r="Z17" s="475" t="n"/>
-      <c r="AA17" s="476" t="n"/>
-      <c r="AB17" s="406" t="inlineStr"/>
-      <c r="AC17" s="475" t="n"/>
-      <c r="AD17" s="475" t="n"/>
-      <c r="AE17" s="475" t="n"/>
-      <c r="AF17" s="475" t="n"/>
-      <c r="AG17" s="475" t="n"/>
-      <c r="AH17" s="475" t="n"/>
-      <c r="AI17" s="475" t="n"/>
-      <c r="AJ17" s="475" t="n"/>
-      <c r="AK17" s="475" t="n"/>
-      <c r="AL17" s="475" t="n"/>
-      <c r="AM17" s="475" t="n"/>
-      <c r="AN17" s="476" t="n"/>
+      <c r="V17" s="398" t="n"/>
+      <c r="W17" s="398" t="n"/>
+      <c r="X17" s="398" t="n"/>
+      <c r="Y17" s="398" t="n"/>
+      <c r="Z17" s="398" t="n"/>
+      <c r="AA17" s="398" t="n"/>
+      <c r="AB17" s="540" t="inlineStr"/>
+      <c r="AC17" s="398" t="n"/>
+      <c r="AD17" s="398" t="n"/>
+      <c r="AE17" s="398" t="n"/>
+      <c r="AF17" s="398" t="n"/>
+      <c r="AG17" s="398" t="n"/>
+      <c r="AH17" s="398" t="n"/>
+      <c r="AI17" s="398" t="n"/>
+      <c r="AJ17" s="398" t="n"/>
+      <c r="AK17" s="398" t="n"/>
+      <c r="AL17" s="398" t="n"/>
+      <c r="AM17" s="398" t="n"/>
+      <c r="AN17" s="542" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="417" t="inlineStr">
+      <c r="A18" s="543" t="inlineStr">
         <is>
           <t>Escalation if Overdue</t>
         </is>
       </c>
-      <c r="B18" s="475" t="n"/>
-      <c r="C18" s="475" t="n"/>
-      <c r="D18" s="475" t="n"/>
-      <c r="E18" s="475" t="n"/>
-      <c r="F18" s="475" t="n"/>
-      <c r="G18" s="476" t="n"/>
-      <c r="H18" s="406" t="inlineStr"/>
-      <c r="I18" s="475" t="n"/>
-      <c r="J18" s="475" t="n"/>
-      <c r="K18" s="475" t="n"/>
-      <c r="L18" s="475" t="n"/>
-      <c r="M18" s="475" t="n"/>
-      <c r="N18" s="475" t="n"/>
-      <c r="O18" s="475" t="n"/>
-      <c r="P18" s="475" t="n"/>
-      <c r="Q18" s="475" t="n"/>
-      <c r="R18" s="475" t="n"/>
-      <c r="S18" s="475" t="n"/>
-      <c r="T18" s="476" t="n"/>
-      <c r="U18" s="420" t="inlineStr">
+      <c r="B18" s="544" t="n"/>
+      <c r="C18" s="544" t="n"/>
+      <c r="D18" s="544" t="n"/>
+      <c r="E18" s="544" t="n"/>
+      <c r="F18" s="544" t="n"/>
+      <c r="G18" s="544" t="n"/>
+      <c r="H18" s="545" t="inlineStr"/>
+      <c r="I18" s="544" t="n"/>
+      <c r="J18" s="544" t="n"/>
+      <c r="K18" s="544" t="n"/>
+      <c r="L18" s="544" t="n"/>
+      <c r="M18" s="544" t="n"/>
+      <c r="N18" s="544" t="n"/>
+      <c r="O18" s="544" t="n"/>
+      <c r="P18" s="544" t="n"/>
+      <c r="Q18" s="544" t="n"/>
+      <c r="R18" s="544" t="n"/>
+      <c r="S18" s="544" t="n"/>
+      <c r="T18" s="544" t="n"/>
+      <c r="U18" s="546" t="inlineStr">
         <is>
           <t>Gate Status</t>
         </is>
       </c>
-      <c r="V18" s="475" t="n"/>
-      <c r="W18" s="475" t="n"/>
-      <c r="X18" s="475" t="n"/>
-      <c r="Y18" s="475" t="n"/>
-      <c r="Z18" s="475" t="n"/>
-      <c r="AA18" s="476" t="n"/>
-      <c r="AB18" s="406">
+      <c r="V18" s="544" t="n"/>
+      <c r="W18" s="544" t="n"/>
+      <c r="X18" s="544" t="n"/>
+      <c r="Y18" s="544" t="n"/>
+      <c r="Z18" s="544" t="n"/>
+      <c r="AA18" s="544" t="n"/>
+      <c r="AB18" s="545">
         <f>IF(COUNTA(AF22:AF31)=0,"",IF(COUNTIF(AF22:AF31,"FAIL")+COUNTIF(AF22:AF31,"HOLD")&gt;0,"OPEN","CLOSED"))</f>
         <v/>
       </c>
-      <c r="AC18" s="475" t="n"/>
-      <c r="AD18" s="475" t="n"/>
-      <c r="AE18" s="475" t="n"/>
-      <c r="AF18" s="475" t="n"/>
-      <c r="AG18" s="475" t="n"/>
-      <c r="AH18" s="475" t="n"/>
-      <c r="AI18" s="475" t="n"/>
-      <c r="AJ18" s="475" t="n"/>
-      <c r="AK18" s="475" t="n"/>
-      <c r="AL18" s="475" t="n"/>
-      <c r="AM18" s="475" t="n"/>
-      <c r="AN18" s="476" t="n"/>
+      <c r="AC18" s="544" t="n"/>
+      <c r="AD18" s="544" t="n"/>
+      <c r="AE18" s="544" t="n"/>
+      <c r="AF18" s="544" t="n"/>
+      <c r="AG18" s="544" t="n"/>
+      <c r="AH18" s="544" t="n"/>
+      <c r="AI18" s="544" t="n"/>
+      <c r="AJ18" s="544" t="n"/>
+      <c r="AK18" s="544" t="n"/>
+      <c r="AL18" s="544" t="n"/>
+      <c r="AM18" s="544" t="n"/>
+      <c r="AN18" s="547" t="n"/>
     </row>
-    <row r="19" ht="4" customHeight="1">
+    <row r="19" ht="3" customHeight="1">
       <c r="A19" s="410" t="n"/>
       <c r="B19" s="482" t="n"/>
       <c r="C19" s="482" t="n"/>
@@ -6541,683 +7402,683 @@
       <c r="AM19" s="482" t="n"/>
       <c r="AN19" s="482" t="n"/>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="411" t="inlineStr">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="531" t="inlineStr">
         <is>
           <t>3.  READINESS CRITERIA / RISK CHECK</t>
         </is>
       </c>
-      <c r="B20" s="473" t="n"/>
-      <c r="C20" s="473" t="n"/>
-      <c r="D20" s="473" t="n"/>
-      <c r="E20" s="473" t="n"/>
-      <c r="F20" s="473" t="n"/>
-      <c r="G20" s="473" t="n"/>
-      <c r="H20" s="473" t="n"/>
-      <c r="I20" s="473" t="n"/>
-      <c r="J20" s="473" t="n"/>
-      <c r="K20" s="473" t="n"/>
-      <c r="L20" s="473" t="n"/>
-      <c r="M20" s="473" t="n"/>
-      <c r="N20" s="473" t="n"/>
-      <c r="O20" s="473" t="n"/>
-      <c r="P20" s="473" t="n"/>
-      <c r="Q20" s="473" t="n"/>
-      <c r="R20" s="473" t="n"/>
-      <c r="S20" s="473" t="n"/>
-      <c r="T20" s="473" t="n"/>
-      <c r="U20" s="473" t="n"/>
-      <c r="V20" s="473" t="n"/>
-      <c r="W20" s="473" t="n"/>
-      <c r="X20" s="473" t="n"/>
-      <c r="Y20" s="473" t="n"/>
-      <c r="Z20" s="473" t="n"/>
-      <c r="AA20" s="473" t="n"/>
-      <c r="AB20" s="473" t="n"/>
-      <c r="AC20" s="473" t="n"/>
-      <c r="AD20" s="473" t="n"/>
-      <c r="AE20" s="473" t="n"/>
-      <c r="AF20" s="473" t="n"/>
-      <c r="AG20" s="473" t="n"/>
-      <c r="AH20" s="473" t="n"/>
-      <c r="AI20" s="473" t="n"/>
-      <c r="AJ20" s="473" t="n"/>
-      <c r="AK20" s="473" t="n"/>
-      <c r="AL20" s="473" t="n"/>
-      <c r="AM20" s="473" t="n"/>
-      <c r="AN20" s="474" t="n"/>
+      <c r="B20" s="532" t="n"/>
+      <c r="C20" s="532" t="n"/>
+      <c r="D20" s="532" t="n"/>
+      <c r="E20" s="532" t="n"/>
+      <c r="F20" s="532" t="n"/>
+      <c r="G20" s="532" t="n"/>
+      <c r="H20" s="532" t="n"/>
+      <c r="I20" s="532" t="n"/>
+      <c r="J20" s="532" t="n"/>
+      <c r="K20" s="532" t="n"/>
+      <c r="L20" s="532" t="n"/>
+      <c r="M20" s="532" t="n"/>
+      <c r="N20" s="532" t="n"/>
+      <c r="O20" s="532" t="n"/>
+      <c r="P20" s="532" t="n"/>
+      <c r="Q20" s="532" t="n"/>
+      <c r="R20" s="532" t="n"/>
+      <c r="S20" s="532" t="n"/>
+      <c r="T20" s="532" t="n"/>
+      <c r="U20" s="532" t="n"/>
+      <c r="V20" s="532" t="n"/>
+      <c r="W20" s="532" t="n"/>
+      <c r="X20" s="532" t="n"/>
+      <c r="Y20" s="532" t="n"/>
+      <c r="Z20" s="532" t="n"/>
+      <c r="AA20" s="532" t="n"/>
+      <c r="AB20" s="532" t="n"/>
+      <c r="AC20" s="532" t="n"/>
+      <c r="AD20" s="532" t="n"/>
+      <c r="AE20" s="532" t="n"/>
+      <c r="AF20" s="532" t="n"/>
+      <c r="AG20" s="532" t="n"/>
+      <c r="AH20" s="532" t="n"/>
+      <c r="AI20" s="532" t="n"/>
+      <c r="AJ20" s="532" t="n"/>
+      <c r="AK20" s="532" t="n"/>
+      <c r="AL20" s="532" t="n"/>
+      <c r="AM20" s="532" t="n"/>
+      <c r="AN20" s="533" t="n"/>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="421" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="548" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B21" s="474" t="n"/>
-      <c r="C21" s="422" t="inlineStr">
+      <c r="B21" s="549" t="n"/>
+      <c r="C21" s="550" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="D21" s="473" t="n"/>
-      <c r="E21" s="474" t="n"/>
-      <c r="F21" s="422" t="inlineStr">
+      <c r="D21" s="549" t="n"/>
+      <c r="E21" s="549" t="n"/>
+      <c r="F21" s="550" t="inlineStr">
         <is>
           <t>Readiness / Risk Item</t>
         </is>
       </c>
-      <c r="G21" s="473" t="n"/>
-      <c r="H21" s="473" t="n"/>
-      <c r="I21" s="473" t="n"/>
-      <c r="J21" s="473" t="n"/>
-      <c r="K21" s="473" t="n"/>
-      <c r="L21" s="473" t="n"/>
-      <c r="M21" s="473" t="n"/>
-      <c r="N21" s="473" t="n"/>
-      <c r="O21" s="473" t="n"/>
-      <c r="P21" s="473" t="n"/>
-      <c r="Q21" s="473" t="n"/>
-      <c r="R21" s="473" t="n"/>
-      <c r="S21" s="474" t="n"/>
-      <c r="T21" s="422" t="inlineStr">
+      <c r="G21" s="549" t="n"/>
+      <c r="H21" s="549" t="n"/>
+      <c r="I21" s="549" t="n"/>
+      <c r="J21" s="549" t="n"/>
+      <c r="K21" s="549" t="n"/>
+      <c r="L21" s="549" t="n"/>
+      <c r="M21" s="549" t="n"/>
+      <c r="N21" s="549" t="n"/>
+      <c r="O21" s="549" t="n"/>
+      <c r="P21" s="549" t="n"/>
+      <c r="Q21" s="549" t="n"/>
+      <c r="R21" s="549" t="n"/>
+      <c r="S21" s="549" t="n"/>
+      <c r="T21" s="550" t="inlineStr">
         <is>
           <t>Acceptance / Control Rule</t>
         </is>
       </c>
-      <c r="U21" s="473" t="n"/>
-      <c r="V21" s="473" t="n"/>
-      <c r="W21" s="473" t="n"/>
-      <c r="X21" s="473" t="n"/>
-      <c r="Y21" s="473" t="n"/>
-      <c r="Z21" s="473" t="n"/>
-      <c r="AA21" s="473" t="n"/>
-      <c r="AB21" s="473" t="n"/>
-      <c r="AC21" s="473" t="n"/>
-      <c r="AD21" s="473" t="n"/>
-      <c r="AE21" s="474" t="n"/>
-      <c r="AF21" s="422" t="inlineStr">
+      <c r="U21" s="549" t="n"/>
+      <c r="V21" s="549" t="n"/>
+      <c r="W21" s="549" t="n"/>
+      <c r="X21" s="549" t="n"/>
+      <c r="Y21" s="549" t="n"/>
+      <c r="Z21" s="549" t="n"/>
+      <c r="AA21" s="549" t="n"/>
+      <c r="AB21" s="549" t="n"/>
+      <c r="AC21" s="549" t="n"/>
+      <c r="AD21" s="549" t="n"/>
+      <c r="AE21" s="549" t="n"/>
+      <c r="AF21" s="550" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG21" s="473" t="n"/>
-      <c r="AH21" s="473" t="n"/>
-      <c r="AI21" s="474" t="n"/>
-      <c r="AJ21" s="422" t="inlineStr">
+      <c r="AG21" s="549" t="n"/>
+      <c r="AH21" s="549" t="n"/>
+      <c r="AI21" s="549" t="n"/>
+      <c r="AJ21" s="550" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK21" s="473" t="n"/>
-      <c r="AL21" s="474" t="n"/>
-      <c r="AM21" s="422" t="inlineStr">
+      <c r="AK21" s="549" t="n"/>
+      <c r="AL21" s="549" t="n"/>
+      <c r="AM21" s="550" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="AN21" s="474" t="n"/>
+      <c r="AN21" s="551" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="423" t="n">
+      <c r="A22" s="552" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="474" t="n"/>
-      <c r="C22" s="424" t="inlineStr">
+      <c r="B22" s="535" t="n"/>
+      <c r="C22" s="553" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D22" s="475" t="n"/>
-      <c r="E22" s="476" t="n"/>
-      <c r="F22" s="425" t="inlineStr">
+      <c r="D22" s="535" t="n"/>
+      <c r="E22" s="535" t="n"/>
+      <c r="F22" s="554" t="inlineStr">
         <is>
           <t>Released baseline package is locked.</t>
         </is>
       </c>
-      <c r="G22" s="475" t="n"/>
-      <c r="H22" s="475" t="n"/>
-      <c r="I22" s="475" t="n"/>
-      <c r="J22" s="475" t="n"/>
-      <c r="K22" s="475" t="n"/>
-      <c r="L22" s="475" t="n"/>
-      <c r="M22" s="475" t="n"/>
-      <c r="N22" s="475" t="n"/>
-      <c r="O22" s="475" t="n"/>
-      <c r="P22" s="475" t="n"/>
-      <c r="Q22" s="475" t="n"/>
-      <c r="R22" s="475" t="n"/>
-      <c r="S22" s="476" t="n"/>
-      <c r="T22" s="426" t="inlineStr">
+      <c r="G22" s="535" t="n"/>
+      <c r="H22" s="535" t="n"/>
+      <c r="I22" s="535" t="n"/>
+      <c r="J22" s="535" t="n"/>
+      <c r="K22" s="535" t="n"/>
+      <c r="L22" s="535" t="n"/>
+      <c r="M22" s="535" t="n"/>
+      <c r="N22" s="535" t="n"/>
+      <c r="O22" s="535" t="n"/>
+      <c r="P22" s="535" t="n"/>
+      <c r="Q22" s="535" t="n"/>
+      <c r="R22" s="535" t="n"/>
+      <c r="S22" s="535" t="n"/>
+      <c r="T22" s="555" t="inlineStr">
         <is>
           <t>FRM-306 or released package reference is current.</t>
         </is>
       </c>
-      <c r="U22" s="475" t="n"/>
-      <c r="V22" s="475" t="n"/>
-      <c r="W22" s="475" t="n"/>
-      <c r="X22" s="475" t="n"/>
-      <c r="Y22" s="475" t="n"/>
-      <c r="Z22" s="475" t="n"/>
-      <c r="AA22" s="475" t="n"/>
-      <c r="AB22" s="475" t="n"/>
-      <c r="AC22" s="475" t="n"/>
-      <c r="AD22" s="475" t="n"/>
-      <c r="AE22" s="476" t="n"/>
-      <c r="AF22" s="427" t="n"/>
-      <c r="AG22" s="473" t="n"/>
-      <c r="AH22" s="473" t="n"/>
-      <c r="AI22" s="474" t="n"/>
-      <c r="AJ22" s="427" t="n"/>
-      <c r="AK22" s="473" t="n"/>
-      <c r="AL22" s="474" t="n"/>
-      <c r="AM22" s="427" t="n"/>
-      <c r="AN22" s="474" t="n"/>
+      <c r="U22" s="535" t="n"/>
+      <c r="V22" s="535" t="n"/>
+      <c r="W22" s="535" t="n"/>
+      <c r="X22" s="535" t="n"/>
+      <c r="Y22" s="535" t="n"/>
+      <c r="Z22" s="535" t="n"/>
+      <c r="AA22" s="535" t="n"/>
+      <c r="AB22" s="535" t="n"/>
+      <c r="AC22" s="535" t="n"/>
+      <c r="AD22" s="535" t="n"/>
+      <c r="AE22" s="535" t="n"/>
+      <c r="AF22" s="554" t="n"/>
+      <c r="AG22" s="535" t="n"/>
+      <c r="AH22" s="535" t="n"/>
+      <c r="AI22" s="535" t="n"/>
+      <c r="AJ22" s="554" t="n"/>
+      <c r="AK22" s="535" t="n"/>
+      <c r="AL22" s="535" t="n"/>
+      <c r="AM22" s="554" t="n"/>
+      <c r="AN22" s="538" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="423" t="n">
+      <c r="A23" s="556" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="474" t="n"/>
-      <c r="C23" s="424" t="inlineStr">
+      <c r="B23" s="398" t="n"/>
+      <c r="C23" s="557" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D23" s="475" t="n"/>
-      <c r="E23" s="476" t="n"/>
-      <c r="F23" s="428" t="inlineStr">
+      <c r="D23" s="398" t="n"/>
+      <c r="E23" s="398" t="n"/>
+      <c r="F23" s="558" t="inlineStr">
         <is>
           <t>Customer / quality package is identified.</t>
         </is>
       </c>
-      <c r="G23" s="475" t="n"/>
-      <c r="H23" s="475" t="n"/>
-      <c r="I23" s="475" t="n"/>
-      <c r="J23" s="475" t="n"/>
-      <c r="K23" s="475" t="n"/>
-      <c r="L23" s="475" t="n"/>
-      <c r="M23" s="475" t="n"/>
-      <c r="N23" s="475" t="n"/>
-      <c r="O23" s="475" t="n"/>
-      <c r="P23" s="475" t="n"/>
-      <c r="Q23" s="475" t="n"/>
-      <c r="R23" s="475" t="n"/>
-      <c r="S23" s="476" t="n"/>
-      <c r="T23" s="426" t="inlineStr">
+      <c r="G23" s="398" t="n"/>
+      <c r="H23" s="398" t="n"/>
+      <c r="I23" s="398" t="n"/>
+      <c r="J23" s="398" t="n"/>
+      <c r="K23" s="398" t="n"/>
+      <c r="L23" s="398" t="n"/>
+      <c r="M23" s="398" t="n"/>
+      <c r="N23" s="398" t="n"/>
+      <c r="O23" s="398" t="n"/>
+      <c r="P23" s="398" t="n"/>
+      <c r="Q23" s="398" t="n"/>
+      <c r="R23" s="398" t="n"/>
+      <c r="S23" s="398" t="n"/>
+      <c r="T23" s="559" t="inlineStr">
         <is>
           <t>CSR / cert / packaging rules are visible.</t>
         </is>
       </c>
-      <c r="U23" s="475" t="n"/>
-      <c r="V23" s="475" t="n"/>
-      <c r="W23" s="475" t="n"/>
-      <c r="X23" s="475" t="n"/>
-      <c r="Y23" s="475" t="n"/>
-      <c r="Z23" s="475" t="n"/>
-      <c r="AA23" s="475" t="n"/>
-      <c r="AB23" s="475" t="n"/>
-      <c r="AC23" s="475" t="n"/>
-      <c r="AD23" s="475" t="n"/>
-      <c r="AE23" s="476" t="n"/>
-      <c r="AF23" s="427" t="n"/>
-      <c r="AG23" s="473" t="n"/>
-      <c r="AH23" s="473" t="n"/>
-      <c r="AI23" s="474" t="n"/>
-      <c r="AJ23" s="427" t="n"/>
-      <c r="AK23" s="473" t="n"/>
-      <c r="AL23" s="474" t="n"/>
-      <c r="AM23" s="427" t="n"/>
-      <c r="AN23" s="474" t="n"/>
+      <c r="U23" s="398" t="n"/>
+      <c r="V23" s="398" t="n"/>
+      <c r="W23" s="398" t="n"/>
+      <c r="X23" s="398" t="n"/>
+      <c r="Y23" s="398" t="n"/>
+      <c r="Z23" s="398" t="n"/>
+      <c r="AA23" s="398" t="n"/>
+      <c r="AB23" s="398" t="n"/>
+      <c r="AC23" s="398" t="n"/>
+      <c r="AD23" s="398" t="n"/>
+      <c r="AE23" s="398" t="n"/>
+      <c r="AF23" s="560" t="n"/>
+      <c r="AG23" s="398" t="n"/>
+      <c r="AH23" s="398" t="n"/>
+      <c r="AI23" s="398" t="n"/>
+      <c r="AJ23" s="560" t="n"/>
+      <c r="AK23" s="398" t="n"/>
+      <c r="AL23" s="398" t="n"/>
+      <c r="AM23" s="560" t="n"/>
+      <c r="AN23" s="542" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="423" t="n">
+      <c r="A24" s="556" t="n">
         <v>3</v>
       </c>
-      <c r="B24" s="474" t="n"/>
-      <c r="C24" s="424" t="inlineStr">
+      <c r="B24" s="398" t="n"/>
+      <c r="C24" s="557" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D24" s="475" t="n"/>
-      <c r="E24" s="476" t="n"/>
-      <c r="F24" s="425" t="inlineStr">
+      <c r="D24" s="398" t="n"/>
+      <c r="E24" s="398" t="n"/>
+      <c r="F24" s="560" t="inlineStr">
         <is>
           <t>Material / outsource path is feasible.</t>
         </is>
       </c>
-      <c r="G24" s="475" t="n"/>
-      <c r="H24" s="475" t="n"/>
-      <c r="I24" s="475" t="n"/>
-      <c r="J24" s="475" t="n"/>
-      <c r="K24" s="475" t="n"/>
-      <c r="L24" s="475" t="n"/>
-      <c r="M24" s="475" t="n"/>
-      <c r="N24" s="475" t="n"/>
-      <c r="O24" s="475" t="n"/>
-      <c r="P24" s="475" t="n"/>
-      <c r="Q24" s="475" t="n"/>
-      <c r="R24" s="475" t="n"/>
-      <c r="S24" s="476" t="n"/>
-      <c r="T24" s="426" t="inlineStr">
+      <c r="G24" s="398" t="n"/>
+      <c r="H24" s="398" t="n"/>
+      <c r="I24" s="398" t="n"/>
+      <c r="J24" s="398" t="n"/>
+      <c r="K24" s="398" t="n"/>
+      <c r="L24" s="398" t="n"/>
+      <c r="M24" s="398" t="n"/>
+      <c r="N24" s="398" t="n"/>
+      <c r="O24" s="398" t="n"/>
+      <c r="P24" s="398" t="n"/>
+      <c r="Q24" s="398" t="n"/>
+      <c r="R24" s="398" t="n"/>
+      <c r="S24" s="398" t="n"/>
+      <c r="T24" s="559" t="inlineStr">
         <is>
           <t>Critical source path is not assumed.</t>
         </is>
       </c>
-      <c r="U24" s="475" t="n"/>
-      <c r="V24" s="475" t="n"/>
-      <c r="W24" s="475" t="n"/>
-      <c r="X24" s="475" t="n"/>
-      <c r="Y24" s="475" t="n"/>
-      <c r="Z24" s="475" t="n"/>
-      <c r="AA24" s="475" t="n"/>
-      <c r="AB24" s="475" t="n"/>
-      <c r="AC24" s="475" t="n"/>
-      <c r="AD24" s="475" t="n"/>
-      <c r="AE24" s="476" t="n"/>
-      <c r="AF24" s="427" t="n"/>
-      <c r="AG24" s="473" t="n"/>
-      <c r="AH24" s="473" t="n"/>
-      <c r="AI24" s="474" t="n"/>
-      <c r="AJ24" s="427" t="n"/>
-      <c r="AK24" s="473" t="n"/>
-      <c r="AL24" s="474" t="n"/>
-      <c r="AM24" s="427" t="n"/>
-      <c r="AN24" s="474" t="n"/>
+      <c r="U24" s="398" t="n"/>
+      <c r="V24" s="398" t="n"/>
+      <c r="W24" s="398" t="n"/>
+      <c r="X24" s="398" t="n"/>
+      <c r="Y24" s="398" t="n"/>
+      <c r="Z24" s="398" t="n"/>
+      <c r="AA24" s="398" t="n"/>
+      <c r="AB24" s="398" t="n"/>
+      <c r="AC24" s="398" t="n"/>
+      <c r="AD24" s="398" t="n"/>
+      <c r="AE24" s="398" t="n"/>
+      <c r="AF24" s="560" t="n"/>
+      <c r="AG24" s="398" t="n"/>
+      <c r="AH24" s="398" t="n"/>
+      <c r="AI24" s="398" t="n"/>
+      <c r="AJ24" s="560" t="n"/>
+      <c r="AK24" s="398" t="n"/>
+      <c r="AL24" s="398" t="n"/>
+      <c r="AM24" s="560" t="n"/>
+      <c r="AN24" s="542" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="423" t="n">
+      <c r="A25" s="556" t="n">
         <v>4</v>
       </c>
-      <c r="B25" s="474" t="n"/>
-      <c r="C25" s="424" t="inlineStr">
+      <c r="B25" s="398" t="n"/>
+      <c r="C25" s="557" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D25" s="475" t="n"/>
-      <c r="E25" s="476" t="n"/>
-      <c r="F25" s="428" t="inlineStr">
+      <c r="D25" s="398" t="n"/>
+      <c r="E25" s="398" t="n"/>
+      <c r="F25" s="558" t="inlineStr">
         <is>
           <t>Machine / tooling / gage readiness exists.</t>
         </is>
       </c>
-      <c r="G25" s="475" t="n"/>
-      <c r="H25" s="475" t="n"/>
-      <c r="I25" s="475" t="n"/>
-      <c r="J25" s="475" t="n"/>
-      <c r="K25" s="475" t="n"/>
-      <c r="L25" s="475" t="n"/>
-      <c r="M25" s="475" t="n"/>
-      <c r="N25" s="475" t="n"/>
-      <c r="O25" s="475" t="n"/>
-      <c r="P25" s="475" t="n"/>
-      <c r="Q25" s="475" t="n"/>
-      <c r="R25" s="475" t="n"/>
-      <c r="S25" s="476" t="n"/>
-      <c r="T25" s="426" t="inlineStr">
+      <c r="G25" s="398" t="n"/>
+      <c r="H25" s="398" t="n"/>
+      <c r="I25" s="398" t="n"/>
+      <c r="J25" s="398" t="n"/>
+      <c r="K25" s="398" t="n"/>
+      <c r="L25" s="398" t="n"/>
+      <c r="M25" s="398" t="n"/>
+      <c r="N25" s="398" t="n"/>
+      <c r="O25" s="398" t="n"/>
+      <c r="P25" s="398" t="n"/>
+      <c r="Q25" s="398" t="n"/>
+      <c r="R25" s="398" t="n"/>
+      <c r="S25" s="398" t="n"/>
+      <c r="T25" s="559" t="inlineStr">
         <is>
           <t>Capability and readiness path are visible.</t>
         </is>
       </c>
-      <c r="U25" s="475" t="n"/>
-      <c r="V25" s="475" t="n"/>
-      <c r="W25" s="475" t="n"/>
-      <c r="X25" s="475" t="n"/>
-      <c r="Y25" s="475" t="n"/>
-      <c r="Z25" s="475" t="n"/>
-      <c r="AA25" s="475" t="n"/>
-      <c r="AB25" s="475" t="n"/>
-      <c r="AC25" s="475" t="n"/>
-      <c r="AD25" s="475" t="n"/>
-      <c r="AE25" s="476" t="n"/>
-      <c r="AF25" s="427" t="n"/>
-      <c r="AG25" s="473" t="n"/>
-      <c r="AH25" s="473" t="n"/>
-      <c r="AI25" s="474" t="n"/>
-      <c r="AJ25" s="427" t="n"/>
-      <c r="AK25" s="473" t="n"/>
-      <c r="AL25" s="474" t="n"/>
-      <c r="AM25" s="427" t="n"/>
-      <c r="AN25" s="474" t="n"/>
+      <c r="U25" s="398" t="n"/>
+      <c r="V25" s="398" t="n"/>
+      <c r="W25" s="398" t="n"/>
+      <c r="X25" s="398" t="n"/>
+      <c r="Y25" s="398" t="n"/>
+      <c r="Z25" s="398" t="n"/>
+      <c r="AA25" s="398" t="n"/>
+      <c r="AB25" s="398" t="n"/>
+      <c r="AC25" s="398" t="n"/>
+      <c r="AD25" s="398" t="n"/>
+      <c r="AE25" s="398" t="n"/>
+      <c r="AF25" s="560" t="n"/>
+      <c r="AG25" s="398" t="n"/>
+      <c r="AH25" s="398" t="n"/>
+      <c r="AI25" s="398" t="n"/>
+      <c r="AJ25" s="560" t="n"/>
+      <c r="AK25" s="398" t="n"/>
+      <c r="AL25" s="398" t="n"/>
+      <c r="AM25" s="560" t="n"/>
+      <c r="AN25" s="542" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="423" t="n">
+      <c r="A26" s="556" t="n">
         <v>5</v>
       </c>
-      <c r="B26" s="474" t="n"/>
-      <c r="C26" s="424" t="inlineStr">
+      <c r="B26" s="398" t="n"/>
+      <c r="C26" s="557" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D26" s="475" t="n"/>
-      <c r="E26" s="476" t="n"/>
-      <c r="F26" s="425" t="inlineStr">
+      <c r="D26" s="398" t="n"/>
+      <c r="E26" s="398" t="n"/>
+      <c r="F26" s="560" t="inlineStr">
         <is>
           <t>First-piece / FAI strategy is defined.</t>
         </is>
       </c>
-      <c r="G26" s="475" t="n"/>
-      <c r="H26" s="475" t="n"/>
-      <c r="I26" s="475" t="n"/>
-      <c r="J26" s="475" t="n"/>
-      <c r="K26" s="475" t="n"/>
-      <c r="L26" s="475" t="n"/>
-      <c r="M26" s="475" t="n"/>
-      <c r="N26" s="475" t="n"/>
-      <c r="O26" s="475" t="n"/>
-      <c r="P26" s="475" t="n"/>
-      <c r="Q26" s="475" t="n"/>
-      <c r="R26" s="475" t="n"/>
-      <c r="S26" s="476" t="n"/>
-      <c r="T26" s="426" t="inlineStr">
+      <c r="G26" s="398" t="n"/>
+      <c r="H26" s="398" t="n"/>
+      <c r="I26" s="398" t="n"/>
+      <c r="J26" s="398" t="n"/>
+      <c r="K26" s="398" t="n"/>
+      <c r="L26" s="398" t="n"/>
+      <c r="M26" s="398" t="n"/>
+      <c r="N26" s="398" t="n"/>
+      <c r="O26" s="398" t="n"/>
+      <c r="P26" s="398" t="n"/>
+      <c r="Q26" s="398" t="n"/>
+      <c r="R26" s="398" t="n"/>
+      <c r="S26" s="398" t="n"/>
+      <c r="T26" s="559" t="inlineStr">
         <is>
           <t>QA gate logic and owner are visible.</t>
         </is>
       </c>
-      <c r="U26" s="475" t="n"/>
-      <c r="V26" s="475" t="n"/>
-      <c r="W26" s="475" t="n"/>
-      <c r="X26" s="475" t="n"/>
-      <c r="Y26" s="475" t="n"/>
-      <c r="Z26" s="475" t="n"/>
-      <c r="AA26" s="475" t="n"/>
-      <c r="AB26" s="475" t="n"/>
-      <c r="AC26" s="475" t="n"/>
-      <c r="AD26" s="475" t="n"/>
-      <c r="AE26" s="476" t="n"/>
-      <c r="AF26" s="427" t="n"/>
-      <c r="AG26" s="473" t="n"/>
-      <c r="AH26" s="473" t="n"/>
-      <c r="AI26" s="474" t="n"/>
-      <c r="AJ26" s="427" t="n"/>
-      <c r="AK26" s="473" t="n"/>
-      <c r="AL26" s="474" t="n"/>
-      <c r="AM26" s="427" t="n"/>
-      <c r="AN26" s="474" t="n"/>
+      <c r="U26" s="398" t="n"/>
+      <c r="V26" s="398" t="n"/>
+      <c r="W26" s="398" t="n"/>
+      <c r="X26" s="398" t="n"/>
+      <c r="Y26" s="398" t="n"/>
+      <c r="Z26" s="398" t="n"/>
+      <c r="AA26" s="398" t="n"/>
+      <c r="AB26" s="398" t="n"/>
+      <c r="AC26" s="398" t="n"/>
+      <c r="AD26" s="398" t="n"/>
+      <c r="AE26" s="398" t="n"/>
+      <c r="AF26" s="560" t="n"/>
+      <c r="AG26" s="398" t="n"/>
+      <c r="AH26" s="398" t="n"/>
+      <c r="AI26" s="398" t="n"/>
+      <c r="AJ26" s="560" t="n"/>
+      <c r="AK26" s="398" t="n"/>
+      <c r="AL26" s="398" t="n"/>
+      <c r="AM26" s="560" t="n"/>
+      <c r="AN26" s="542" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="423" t="n">
+      <c r="A27" s="556" t="n">
         <v>6</v>
       </c>
-      <c r="B27" s="474" t="n"/>
-      <c r="C27" s="424" t="inlineStr">
+      <c r="B27" s="398" t="n"/>
+      <c r="C27" s="557" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D27" s="475" t="n"/>
-      <c r="E27" s="476" t="n"/>
-      <c r="F27" s="428" t="inlineStr">
+      <c r="D27" s="398" t="n"/>
+      <c r="E27" s="398" t="n"/>
+      <c r="F27" s="558" t="inlineStr">
         <is>
           <t>Delivery / ship logic is feasible.</t>
         </is>
       </c>
-      <c r="G27" s="475" t="n"/>
-      <c r="H27" s="475" t="n"/>
-      <c r="I27" s="475" t="n"/>
-      <c r="J27" s="475" t="n"/>
-      <c r="K27" s="475" t="n"/>
-      <c r="L27" s="475" t="n"/>
-      <c r="M27" s="475" t="n"/>
-      <c r="N27" s="475" t="n"/>
-      <c r="O27" s="475" t="n"/>
-      <c r="P27" s="475" t="n"/>
-      <c r="Q27" s="475" t="n"/>
-      <c r="R27" s="475" t="n"/>
-      <c r="S27" s="476" t="n"/>
-      <c r="T27" s="426" t="inlineStr">
+      <c r="G27" s="398" t="n"/>
+      <c r="H27" s="398" t="n"/>
+      <c r="I27" s="398" t="n"/>
+      <c r="J27" s="398" t="n"/>
+      <c r="K27" s="398" t="n"/>
+      <c r="L27" s="398" t="n"/>
+      <c r="M27" s="398" t="n"/>
+      <c r="N27" s="398" t="n"/>
+      <c r="O27" s="398" t="n"/>
+      <c r="P27" s="398" t="n"/>
+      <c r="Q27" s="398" t="n"/>
+      <c r="R27" s="398" t="n"/>
+      <c r="S27" s="398" t="n"/>
+      <c r="T27" s="559" t="inlineStr">
         <is>
           <t>Commitment and ship impact are realistic.</t>
         </is>
       </c>
-      <c r="U27" s="475" t="n"/>
-      <c r="V27" s="475" t="n"/>
-      <c r="W27" s="475" t="n"/>
-      <c r="X27" s="475" t="n"/>
-      <c r="Y27" s="475" t="n"/>
-      <c r="Z27" s="475" t="n"/>
-      <c r="AA27" s="475" t="n"/>
-      <c r="AB27" s="475" t="n"/>
-      <c r="AC27" s="475" t="n"/>
-      <c r="AD27" s="475" t="n"/>
-      <c r="AE27" s="476" t="n"/>
-      <c r="AF27" s="427" t="n"/>
-      <c r="AG27" s="473" t="n"/>
-      <c r="AH27" s="473" t="n"/>
-      <c r="AI27" s="474" t="n"/>
-      <c r="AJ27" s="427" t="n"/>
-      <c r="AK27" s="473" t="n"/>
-      <c r="AL27" s="474" t="n"/>
-      <c r="AM27" s="427" t="n"/>
-      <c r="AN27" s="474" t="n"/>
+      <c r="U27" s="398" t="n"/>
+      <c r="V27" s="398" t="n"/>
+      <c r="W27" s="398" t="n"/>
+      <c r="X27" s="398" t="n"/>
+      <c r="Y27" s="398" t="n"/>
+      <c r="Z27" s="398" t="n"/>
+      <c r="AA27" s="398" t="n"/>
+      <c r="AB27" s="398" t="n"/>
+      <c r="AC27" s="398" t="n"/>
+      <c r="AD27" s="398" t="n"/>
+      <c r="AE27" s="398" t="n"/>
+      <c r="AF27" s="560" t="n"/>
+      <c r="AG27" s="398" t="n"/>
+      <c r="AH27" s="398" t="n"/>
+      <c r="AI27" s="398" t="n"/>
+      <c r="AJ27" s="560" t="n"/>
+      <c r="AK27" s="398" t="n"/>
+      <c r="AL27" s="398" t="n"/>
+      <c r="AM27" s="560" t="n"/>
+      <c r="AN27" s="542" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="423" t="n">
+      <c r="A28" s="556" t="n">
         <v>7</v>
       </c>
-      <c r="B28" s="474" t="n"/>
-      <c r="C28" s="424" t="inlineStr">
+      <c r="B28" s="398" t="n"/>
+      <c r="C28" s="557" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D28" s="475" t="n"/>
-      <c r="E28" s="476" t="n"/>
-      <c r="F28" s="425" t="inlineStr">
+      <c r="D28" s="398" t="n"/>
+      <c r="E28" s="398" t="n"/>
+      <c r="F28" s="560" t="inlineStr">
         <is>
           <t>Top abnormal / failure mode is explicit.</t>
         </is>
       </c>
-      <c r="G28" s="475" t="n"/>
-      <c r="H28" s="475" t="n"/>
-      <c r="I28" s="475" t="n"/>
-      <c r="J28" s="475" t="n"/>
-      <c r="K28" s="475" t="n"/>
-      <c r="L28" s="475" t="n"/>
-      <c r="M28" s="475" t="n"/>
-      <c r="N28" s="475" t="n"/>
-      <c r="O28" s="475" t="n"/>
-      <c r="P28" s="475" t="n"/>
-      <c r="Q28" s="475" t="n"/>
-      <c r="R28" s="475" t="n"/>
-      <c r="S28" s="476" t="n"/>
-      <c r="T28" s="426" t="inlineStr">
+      <c r="G28" s="398" t="n"/>
+      <c r="H28" s="398" t="n"/>
+      <c r="I28" s="398" t="n"/>
+      <c r="J28" s="398" t="n"/>
+      <c r="K28" s="398" t="n"/>
+      <c r="L28" s="398" t="n"/>
+      <c r="M28" s="398" t="n"/>
+      <c r="N28" s="398" t="n"/>
+      <c r="O28" s="398" t="n"/>
+      <c r="P28" s="398" t="n"/>
+      <c r="Q28" s="398" t="n"/>
+      <c r="R28" s="398" t="n"/>
+      <c r="S28" s="398" t="n"/>
+      <c r="T28" s="559" t="inlineStr">
         <is>
           <t>Most severe risk is named, not hidden.</t>
         </is>
       </c>
-      <c r="U28" s="475" t="n"/>
-      <c r="V28" s="475" t="n"/>
-      <c r="W28" s="475" t="n"/>
-      <c r="X28" s="475" t="n"/>
-      <c r="Y28" s="475" t="n"/>
-      <c r="Z28" s="475" t="n"/>
-      <c r="AA28" s="475" t="n"/>
-      <c r="AB28" s="475" t="n"/>
-      <c r="AC28" s="475" t="n"/>
-      <c r="AD28" s="475" t="n"/>
-      <c r="AE28" s="476" t="n"/>
-      <c r="AF28" s="427" t="n"/>
-      <c r="AG28" s="473" t="n"/>
-      <c r="AH28" s="473" t="n"/>
-      <c r="AI28" s="474" t="n"/>
-      <c r="AJ28" s="427" t="n"/>
-      <c r="AK28" s="473" t="n"/>
-      <c r="AL28" s="474" t="n"/>
-      <c r="AM28" s="427" t="n"/>
-      <c r="AN28" s="474" t="n"/>
+      <c r="U28" s="398" t="n"/>
+      <c r="V28" s="398" t="n"/>
+      <c r="W28" s="398" t="n"/>
+      <c r="X28" s="398" t="n"/>
+      <c r="Y28" s="398" t="n"/>
+      <c r="Z28" s="398" t="n"/>
+      <c r="AA28" s="398" t="n"/>
+      <c r="AB28" s="398" t="n"/>
+      <c r="AC28" s="398" t="n"/>
+      <c r="AD28" s="398" t="n"/>
+      <c r="AE28" s="398" t="n"/>
+      <c r="AF28" s="560" t="n"/>
+      <c r="AG28" s="398" t="n"/>
+      <c r="AH28" s="398" t="n"/>
+      <c r="AI28" s="398" t="n"/>
+      <c r="AJ28" s="560" t="n"/>
+      <c r="AK28" s="398" t="n"/>
+      <c r="AL28" s="398" t="n"/>
+      <c r="AM28" s="560" t="n"/>
+      <c r="AN28" s="542" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="423" t="n">
+      <c r="A29" s="556" t="n">
         <v>8</v>
       </c>
-      <c r="B29" s="474" t="n"/>
-      <c r="C29" s="424" t="inlineStr">
+      <c r="B29" s="398" t="n"/>
+      <c r="C29" s="557" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D29" s="475" t="n"/>
-      <c r="E29" s="476" t="n"/>
-      <c r="F29" s="428" t="inlineStr">
+      <c r="D29" s="398" t="n"/>
+      <c r="E29" s="398" t="n"/>
+      <c r="F29" s="558" t="inlineStr">
         <is>
           <t>Containment / contingency exists.</t>
         </is>
       </c>
-      <c r="G29" s="475" t="n"/>
-      <c r="H29" s="475" t="n"/>
-      <c r="I29" s="475" t="n"/>
-      <c r="J29" s="475" t="n"/>
-      <c r="K29" s="475" t="n"/>
-      <c r="L29" s="475" t="n"/>
-      <c r="M29" s="475" t="n"/>
-      <c r="N29" s="475" t="n"/>
-      <c r="O29" s="475" t="n"/>
-      <c r="P29" s="475" t="n"/>
-      <c r="Q29" s="475" t="n"/>
-      <c r="R29" s="475" t="n"/>
-      <c r="S29" s="476" t="n"/>
-      <c r="T29" s="426" t="inlineStr">
+      <c r="G29" s="398" t="n"/>
+      <c r="H29" s="398" t="n"/>
+      <c r="I29" s="398" t="n"/>
+      <c r="J29" s="398" t="n"/>
+      <c r="K29" s="398" t="n"/>
+      <c r="L29" s="398" t="n"/>
+      <c r="M29" s="398" t="n"/>
+      <c r="N29" s="398" t="n"/>
+      <c r="O29" s="398" t="n"/>
+      <c r="P29" s="398" t="n"/>
+      <c r="Q29" s="398" t="n"/>
+      <c r="R29" s="398" t="n"/>
+      <c r="S29" s="398" t="n"/>
+      <c r="T29" s="559" t="inlineStr">
         <is>
           <t>Recovery path exists if primary plan fails.</t>
         </is>
       </c>
-      <c r="U29" s="475" t="n"/>
-      <c r="V29" s="475" t="n"/>
-      <c r="W29" s="475" t="n"/>
-      <c r="X29" s="475" t="n"/>
-      <c r="Y29" s="475" t="n"/>
-      <c r="Z29" s="475" t="n"/>
-      <c r="AA29" s="475" t="n"/>
-      <c r="AB29" s="475" t="n"/>
-      <c r="AC29" s="475" t="n"/>
-      <c r="AD29" s="475" t="n"/>
-      <c r="AE29" s="476" t="n"/>
-      <c r="AF29" s="427" t="n"/>
-      <c r="AG29" s="473" t="n"/>
-      <c r="AH29" s="473" t="n"/>
-      <c r="AI29" s="474" t="n"/>
-      <c r="AJ29" s="427" t="n"/>
-      <c r="AK29" s="473" t="n"/>
-      <c r="AL29" s="474" t="n"/>
-      <c r="AM29" s="427" t="n"/>
-      <c r="AN29" s="474" t="n"/>
+      <c r="U29" s="398" t="n"/>
+      <c r="V29" s="398" t="n"/>
+      <c r="W29" s="398" t="n"/>
+      <c r="X29" s="398" t="n"/>
+      <c r="Y29" s="398" t="n"/>
+      <c r="Z29" s="398" t="n"/>
+      <c r="AA29" s="398" t="n"/>
+      <c r="AB29" s="398" t="n"/>
+      <c r="AC29" s="398" t="n"/>
+      <c r="AD29" s="398" t="n"/>
+      <c r="AE29" s="398" t="n"/>
+      <c r="AF29" s="560" t="n"/>
+      <c r="AG29" s="398" t="n"/>
+      <c r="AH29" s="398" t="n"/>
+      <c r="AI29" s="398" t="n"/>
+      <c r="AJ29" s="560" t="n"/>
+      <c r="AK29" s="398" t="n"/>
+      <c r="AL29" s="398" t="n"/>
+      <c r="AM29" s="560" t="n"/>
+      <c r="AN29" s="542" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="423" t="n">
+      <c r="A30" s="556" t="n">
         <v>9</v>
       </c>
-      <c r="B30" s="474" t="n"/>
-      <c r="C30" s="424" t="inlineStr">
+      <c r="B30" s="398" t="n"/>
+      <c r="C30" s="557" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D30" s="475" t="n"/>
-      <c r="E30" s="476" t="n"/>
-      <c r="F30" s="425" t="inlineStr">
+      <c r="D30" s="398" t="n"/>
+      <c r="E30" s="398" t="n"/>
+      <c r="F30" s="560" t="inlineStr">
         <is>
           <t>Conditional-release authority is explicit.</t>
         </is>
       </c>
-      <c r="G30" s="475" t="n"/>
-      <c r="H30" s="475" t="n"/>
-      <c r="I30" s="475" t="n"/>
-      <c r="J30" s="475" t="n"/>
-      <c r="K30" s="475" t="n"/>
-      <c r="L30" s="475" t="n"/>
-      <c r="M30" s="475" t="n"/>
-      <c r="N30" s="475" t="n"/>
-      <c r="O30" s="475" t="n"/>
-      <c r="P30" s="475" t="n"/>
-      <c r="Q30" s="475" t="n"/>
-      <c r="R30" s="475" t="n"/>
-      <c r="S30" s="476" t="n"/>
-      <c r="T30" s="426" t="inlineStr">
+      <c r="G30" s="398" t="n"/>
+      <c r="H30" s="398" t="n"/>
+      <c r="I30" s="398" t="n"/>
+      <c r="J30" s="398" t="n"/>
+      <c r="K30" s="398" t="n"/>
+      <c r="L30" s="398" t="n"/>
+      <c r="M30" s="398" t="n"/>
+      <c r="N30" s="398" t="n"/>
+      <c r="O30" s="398" t="n"/>
+      <c r="P30" s="398" t="n"/>
+      <c r="Q30" s="398" t="n"/>
+      <c r="R30" s="398" t="n"/>
+      <c r="S30" s="398" t="n"/>
+      <c r="T30" s="559" t="inlineStr">
         <is>
           <t>No conditional release without named owner.</t>
         </is>
       </c>
-      <c r="U30" s="475" t="n"/>
-      <c r="V30" s="475" t="n"/>
-      <c r="W30" s="475" t="n"/>
-      <c r="X30" s="475" t="n"/>
-      <c r="Y30" s="475" t="n"/>
-      <c r="Z30" s="475" t="n"/>
-      <c r="AA30" s="475" t="n"/>
-      <c r="AB30" s="475" t="n"/>
-      <c r="AC30" s="475" t="n"/>
-      <c r="AD30" s="475" t="n"/>
-      <c r="AE30" s="476" t="n"/>
-      <c r="AF30" s="427" t="n"/>
-      <c r="AG30" s="473" t="n"/>
-      <c r="AH30" s="473" t="n"/>
-      <c r="AI30" s="474" t="n"/>
-      <c r="AJ30" s="427" t="n"/>
-      <c r="AK30" s="473" t="n"/>
-      <c r="AL30" s="474" t="n"/>
-      <c r="AM30" s="427" t="n"/>
-      <c r="AN30" s="474" t="n"/>
+      <c r="U30" s="398" t="n"/>
+      <c r="V30" s="398" t="n"/>
+      <c r="W30" s="398" t="n"/>
+      <c r="X30" s="398" t="n"/>
+      <c r="Y30" s="398" t="n"/>
+      <c r="Z30" s="398" t="n"/>
+      <c r="AA30" s="398" t="n"/>
+      <c r="AB30" s="398" t="n"/>
+      <c r="AC30" s="398" t="n"/>
+      <c r="AD30" s="398" t="n"/>
+      <c r="AE30" s="398" t="n"/>
+      <c r="AF30" s="560" t="n"/>
+      <c r="AG30" s="398" t="n"/>
+      <c r="AH30" s="398" t="n"/>
+      <c r="AI30" s="398" t="n"/>
+      <c r="AJ30" s="560" t="n"/>
+      <c r="AK30" s="398" t="n"/>
+      <c r="AL30" s="398" t="n"/>
+      <c r="AM30" s="560" t="n"/>
+      <c r="AN30" s="542" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="423" t="n">
+      <c r="A31" s="561" t="n">
         <v>10</v>
       </c>
-      <c r="B31" s="474" t="n"/>
-      <c r="C31" s="424" t="inlineStr">
+      <c r="B31" s="544" t="n"/>
+      <c r="C31" s="562" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D31" s="475" t="n"/>
-      <c r="E31" s="476" t="n"/>
-      <c r="F31" s="428" t="inlineStr">
+      <c r="D31" s="544" t="n"/>
+      <c r="E31" s="544" t="n"/>
+      <c r="F31" s="563" t="inlineStr">
         <is>
           <t>Evidence path and dossier traceability exist.</t>
         </is>
       </c>
-      <c r="G31" s="475" t="n"/>
-      <c r="H31" s="475" t="n"/>
-      <c r="I31" s="475" t="n"/>
-      <c r="J31" s="475" t="n"/>
-      <c r="K31" s="475" t="n"/>
-      <c r="L31" s="475" t="n"/>
-      <c r="M31" s="475" t="n"/>
-      <c r="N31" s="475" t="n"/>
-      <c r="O31" s="475" t="n"/>
-      <c r="P31" s="475" t="n"/>
-      <c r="Q31" s="475" t="n"/>
-      <c r="R31" s="475" t="n"/>
-      <c r="S31" s="476" t="n"/>
-      <c r="T31" s="426" t="inlineStr">
+      <c r="G31" s="544" t="n"/>
+      <c r="H31" s="544" t="n"/>
+      <c r="I31" s="544" t="n"/>
+      <c r="J31" s="544" t="n"/>
+      <c r="K31" s="544" t="n"/>
+      <c r="L31" s="544" t="n"/>
+      <c r="M31" s="544" t="n"/>
+      <c r="N31" s="544" t="n"/>
+      <c r="O31" s="544" t="n"/>
+      <c r="P31" s="544" t="n"/>
+      <c r="Q31" s="544" t="n"/>
+      <c r="R31" s="544" t="n"/>
+      <c r="S31" s="544" t="n"/>
+      <c r="T31" s="564" t="inlineStr">
         <is>
           <t>Decision can be reconstructed later.</t>
         </is>
       </c>
-      <c r="U31" s="475" t="n"/>
-      <c r="V31" s="475" t="n"/>
-      <c r="W31" s="475" t="n"/>
-      <c r="X31" s="475" t="n"/>
-      <c r="Y31" s="475" t="n"/>
-      <c r="Z31" s="475" t="n"/>
-      <c r="AA31" s="475" t="n"/>
-      <c r="AB31" s="475" t="n"/>
-      <c r="AC31" s="475" t="n"/>
-      <c r="AD31" s="475" t="n"/>
-      <c r="AE31" s="476" t="n"/>
-      <c r="AF31" s="427" t="n"/>
-      <c r="AG31" s="473" t="n"/>
-      <c r="AH31" s="473" t="n"/>
-      <c r="AI31" s="474" t="n"/>
-      <c r="AJ31" s="427" t="n"/>
-      <c r="AK31" s="473" t="n"/>
-      <c r="AL31" s="474" t="n"/>
-      <c r="AM31" s="427" t="n"/>
-      <c r="AN31" s="474" t="n"/>
+      <c r="U31" s="544" t="n"/>
+      <c r="V31" s="544" t="n"/>
+      <c r="W31" s="544" t="n"/>
+      <c r="X31" s="544" t="n"/>
+      <c r="Y31" s="544" t="n"/>
+      <c r="Z31" s="544" t="n"/>
+      <c r="AA31" s="544" t="n"/>
+      <c r="AB31" s="544" t="n"/>
+      <c r="AC31" s="544" t="n"/>
+      <c r="AD31" s="544" t="n"/>
+      <c r="AE31" s="544" t="n"/>
+      <c r="AF31" s="565" t="n"/>
+      <c r="AG31" s="544" t="n"/>
+      <c r="AH31" s="544" t="n"/>
+      <c r="AI31" s="544" t="n"/>
+      <c r="AJ31" s="565" t="n"/>
+      <c r="AK31" s="544" t="n"/>
+      <c r="AL31" s="544" t="n"/>
+      <c r="AM31" s="565" t="n"/>
+      <c r="AN31" s="547" t="n"/>
     </row>
-    <row r="32" ht="4" customHeight="1">
+    <row r="32" ht="3" customHeight="1">
       <c r="A32" s="410" t="n"/>
       <c r="B32" s="482" t="n"/>
       <c r="C32" s="482" t="n"/>
@@ -7259,343 +8120,343 @@
       <c r="AM32" s="482" t="n"/>
       <c r="AN32" s="482" t="n"/>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="411" t="inlineStr">
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="531" t="inlineStr">
         <is>
           <t>4.  OPEN RISK ACTIONS / CONTAINMENT</t>
         </is>
       </c>
-      <c r="B33" s="473" t="n"/>
-      <c r="C33" s="473" t="n"/>
-      <c r="D33" s="473" t="n"/>
-      <c r="E33" s="473" t="n"/>
-      <c r="F33" s="473" t="n"/>
-      <c r="G33" s="473" t="n"/>
-      <c r="H33" s="473" t="n"/>
-      <c r="I33" s="473" t="n"/>
-      <c r="J33" s="473" t="n"/>
-      <c r="K33" s="473" t="n"/>
-      <c r="L33" s="473" t="n"/>
-      <c r="M33" s="473" t="n"/>
-      <c r="N33" s="473" t="n"/>
-      <c r="O33" s="473" t="n"/>
-      <c r="P33" s="473" t="n"/>
-      <c r="Q33" s="473" t="n"/>
-      <c r="R33" s="473" t="n"/>
-      <c r="S33" s="473" t="n"/>
-      <c r="T33" s="473" t="n"/>
-      <c r="U33" s="473" t="n"/>
-      <c r="V33" s="473" t="n"/>
-      <c r="W33" s="473" t="n"/>
-      <c r="X33" s="473" t="n"/>
-      <c r="Y33" s="473" t="n"/>
-      <c r="Z33" s="473" t="n"/>
-      <c r="AA33" s="473" t="n"/>
-      <c r="AB33" s="473" t="n"/>
-      <c r="AC33" s="473" t="n"/>
-      <c r="AD33" s="473" t="n"/>
-      <c r="AE33" s="473" t="n"/>
-      <c r="AF33" s="473" t="n"/>
-      <c r="AG33" s="473" t="n"/>
-      <c r="AH33" s="473" t="n"/>
-      <c r="AI33" s="473" t="n"/>
-      <c r="AJ33" s="473" t="n"/>
-      <c r="AK33" s="473" t="n"/>
-      <c r="AL33" s="473" t="n"/>
-      <c r="AM33" s="473" t="n"/>
-      <c r="AN33" s="474" t="n"/>
+      <c r="B33" s="532" t="n"/>
+      <c r="C33" s="532" t="n"/>
+      <c r="D33" s="532" t="n"/>
+      <c r="E33" s="532" t="n"/>
+      <c r="F33" s="532" t="n"/>
+      <c r="G33" s="532" t="n"/>
+      <c r="H33" s="532" t="n"/>
+      <c r="I33" s="532" t="n"/>
+      <c r="J33" s="532" t="n"/>
+      <c r="K33" s="532" t="n"/>
+      <c r="L33" s="532" t="n"/>
+      <c r="M33" s="532" t="n"/>
+      <c r="N33" s="532" t="n"/>
+      <c r="O33" s="532" t="n"/>
+      <c r="P33" s="532" t="n"/>
+      <c r="Q33" s="532" t="n"/>
+      <c r="R33" s="532" t="n"/>
+      <c r="S33" s="532" t="n"/>
+      <c r="T33" s="532" t="n"/>
+      <c r="U33" s="532" t="n"/>
+      <c r="V33" s="532" t="n"/>
+      <c r="W33" s="532" t="n"/>
+      <c r="X33" s="532" t="n"/>
+      <c r="Y33" s="532" t="n"/>
+      <c r="Z33" s="532" t="n"/>
+      <c r="AA33" s="532" t="n"/>
+      <c r="AB33" s="532" t="n"/>
+      <c r="AC33" s="532" t="n"/>
+      <c r="AD33" s="532" t="n"/>
+      <c r="AE33" s="532" t="n"/>
+      <c r="AF33" s="532" t="n"/>
+      <c r="AG33" s="532" t="n"/>
+      <c r="AH33" s="532" t="n"/>
+      <c r="AI33" s="532" t="n"/>
+      <c r="AJ33" s="532" t="n"/>
+      <c r="AK33" s="532" t="n"/>
+      <c r="AL33" s="532" t="n"/>
+      <c r="AM33" s="532" t="n"/>
+      <c r="AN33" s="533" t="n"/>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="421" t="inlineStr">
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="548" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B34" s="474" t="n"/>
-      <c r="C34" s="422" t="inlineStr">
+      <c r="B34" s="549" t="n"/>
+      <c r="C34" s="550" t="inlineStr">
         <is>
           <t>Risk / Readiness Gap</t>
         </is>
       </c>
-      <c r="D34" s="473" t="n"/>
-      <c r="E34" s="473" t="n"/>
-      <c r="F34" s="473" t="n"/>
-      <c r="G34" s="473" t="n"/>
-      <c r="H34" s="473" t="n"/>
-      <c r="I34" s="473" t="n"/>
-      <c r="J34" s="473" t="n"/>
-      <c r="K34" s="473" t="n"/>
-      <c r="L34" s="474" t="n"/>
-      <c r="M34" s="422" t="inlineStr">
+      <c r="D34" s="549" t="n"/>
+      <c r="E34" s="549" t="n"/>
+      <c r="F34" s="549" t="n"/>
+      <c r="G34" s="549" t="n"/>
+      <c r="H34" s="549" t="n"/>
+      <c r="I34" s="549" t="n"/>
+      <c r="J34" s="549" t="n"/>
+      <c r="K34" s="549" t="n"/>
+      <c r="L34" s="549" t="n"/>
+      <c r="M34" s="550" t="inlineStr">
         <is>
           <t>Required Containment / Action</t>
         </is>
       </c>
-      <c r="N34" s="473" t="n"/>
-      <c r="O34" s="473" t="n"/>
-      <c r="P34" s="473" t="n"/>
-      <c r="Q34" s="473" t="n"/>
-      <c r="R34" s="473" t="n"/>
-      <c r="S34" s="473" t="n"/>
-      <c r="T34" s="473" t="n"/>
-      <c r="U34" s="473" t="n"/>
-      <c r="V34" s="473" t="n"/>
-      <c r="W34" s="473" t="n"/>
-      <c r="X34" s="474" t="n"/>
-      <c r="Y34" s="422" t="inlineStr">
+      <c r="N34" s="549" t="n"/>
+      <c r="O34" s="549" t="n"/>
+      <c r="P34" s="549" t="n"/>
+      <c r="Q34" s="549" t="n"/>
+      <c r="R34" s="549" t="n"/>
+      <c r="S34" s="549" t="n"/>
+      <c r="T34" s="549" t="n"/>
+      <c r="U34" s="549" t="n"/>
+      <c r="V34" s="549" t="n"/>
+      <c r="W34" s="549" t="n"/>
+      <c r="X34" s="549" t="n"/>
+      <c r="Y34" s="550" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="Z34" s="473" t="n"/>
-      <c r="AA34" s="473" t="n"/>
-      <c r="AB34" s="473" t="n"/>
-      <c r="AC34" s="474" t="n"/>
-      <c r="AD34" s="422" t="inlineStr">
+      <c r="Z34" s="549" t="n"/>
+      <c r="AA34" s="549" t="n"/>
+      <c r="AB34" s="549" t="n"/>
+      <c r="AC34" s="549" t="n"/>
+      <c r="AD34" s="550" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="AE34" s="473" t="n"/>
-      <c r="AF34" s="473" t="n"/>
-      <c r="AG34" s="473" t="n"/>
-      <c r="AH34" s="474" t="n"/>
-      <c r="AI34" s="422" t="inlineStr">
+      <c r="AE34" s="549" t="n"/>
+      <c r="AF34" s="549" t="n"/>
+      <c r="AG34" s="549" t="n"/>
+      <c r="AH34" s="549" t="n"/>
+      <c r="AI34" s="550" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AJ34" s="473" t="n"/>
-      <c r="AK34" s="474" t="n"/>
-      <c r="AL34" s="422" t="inlineStr">
+      <c r="AJ34" s="549" t="n"/>
+      <c r="AK34" s="549" t="n"/>
+      <c r="AL34" s="550" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="AM34" s="473" t="n"/>
-      <c r="AN34" s="474" t="n"/>
+      <c r="AM34" s="549" t="n"/>
+      <c r="AN34" s="551" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="429" t="n">
+      <c r="A35" s="566" t="n">
         <v>1</v>
       </c>
-      <c r="B35" s="476" t="n"/>
-      <c r="C35" s="427" t="n"/>
-      <c r="D35" s="473" t="n"/>
-      <c r="E35" s="473" t="n"/>
-      <c r="F35" s="473" t="n"/>
-      <c r="G35" s="473" t="n"/>
-      <c r="H35" s="473" t="n"/>
-      <c r="I35" s="473" t="n"/>
-      <c r="J35" s="473" t="n"/>
-      <c r="K35" s="473" t="n"/>
-      <c r="L35" s="474" t="n"/>
-      <c r="M35" s="427" t="n"/>
-      <c r="N35" s="473" t="n"/>
-      <c r="O35" s="473" t="n"/>
-      <c r="P35" s="473" t="n"/>
-      <c r="Q35" s="473" t="n"/>
-      <c r="R35" s="473" t="n"/>
-      <c r="S35" s="473" t="n"/>
-      <c r="T35" s="473" t="n"/>
-      <c r="U35" s="473" t="n"/>
-      <c r="V35" s="473" t="n"/>
-      <c r="W35" s="473" t="n"/>
-      <c r="X35" s="474" t="n"/>
-      <c r="Y35" s="427" t="n"/>
-      <c r="Z35" s="473" t="n"/>
-      <c r="AA35" s="473" t="n"/>
-      <c r="AB35" s="473" t="n"/>
-      <c r="AC35" s="474" t="n"/>
-      <c r="AD35" s="427" t="n"/>
-      <c r="AE35" s="473" t="n"/>
-      <c r="AF35" s="473" t="n"/>
-      <c r="AG35" s="473" t="n"/>
-      <c r="AH35" s="474" t="n"/>
-      <c r="AI35" s="427" t="n"/>
-      <c r="AJ35" s="473" t="n"/>
-      <c r="AK35" s="474" t="n"/>
-      <c r="AL35" s="427" t="n"/>
-      <c r="AM35" s="473" t="n"/>
-      <c r="AN35" s="474" t="n"/>
+      <c r="B35" s="535" t="n"/>
+      <c r="C35" s="554" t="n"/>
+      <c r="D35" s="535" t="n"/>
+      <c r="E35" s="535" t="n"/>
+      <c r="F35" s="535" t="n"/>
+      <c r="G35" s="535" t="n"/>
+      <c r="H35" s="535" t="n"/>
+      <c r="I35" s="535" t="n"/>
+      <c r="J35" s="535" t="n"/>
+      <c r="K35" s="535" t="n"/>
+      <c r="L35" s="535" t="n"/>
+      <c r="M35" s="554" t="n"/>
+      <c r="N35" s="535" t="n"/>
+      <c r="O35" s="535" t="n"/>
+      <c r="P35" s="535" t="n"/>
+      <c r="Q35" s="535" t="n"/>
+      <c r="R35" s="535" t="n"/>
+      <c r="S35" s="535" t="n"/>
+      <c r="T35" s="535" t="n"/>
+      <c r="U35" s="535" t="n"/>
+      <c r="V35" s="535" t="n"/>
+      <c r="W35" s="535" t="n"/>
+      <c r="X35" s="535" t="n"/>
+      <c r="Y35" s="554" t="n"/>
+      <c r="Z35" s="535" t="n"/>
+      <c r="AA35" s="535" t="n"/>
+      <c r="AB35" s="535" t="n"/>
+      <c r="AC35" s="535" t="n"/>
+      <c r="AD35" s="554" t="n"/>
+      <c r="AE35" s="535" t="n"/>
+      <c r="AF35" s="535" t="n"/>
+      <c r="AG35" s="535" t="n"/>
+      <c r="AH35" s="535" t="n"/>
+      <c r="AI35" s="554" t="n"/>
+      <c r="AJ35" s="535" t="n"/>
+      <c r="AK35" s="535" t="n"/>
+      <c r="AL35" s="554" t="n"/>
+      <c r="AM35" s="535" t="n"/>
+      <c r="AN35" s="538" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="429" t="n">
+      <c r="A36" s="567" t="n">
         <v>2</v>
       </c>
-      <c r="B36" s="476" t="n"/>
-      <c r="C36" s="427" t="n"/>
-      <c r="D36" s="473" t="n"/>
-      <c r="E36" s="473" t="n"/>
-      <c r="F36" s="473" t="n"/>
-      <c r="G36" s="473" t="n"/>
-      <c r="H36" s="473" t="n"/>
-      <c r="I36" s="473" t="n"/>
-      <c r="J36" s="473" t="n"/>
-      <c r="K36" s="473" t="n"/>
-      <c r="L36" s="474" t="n"/>
-      <c r="M36" s="427" t="n"/>
-      <c r="N36" s="473" t="n"/>
-      <c r="O36" s="473" t="n"/>
-      <c r="P36" s="473" t="n"/>
-      <c r="Q36" s="473" t="n"/>
-      <c r="R36" s="473" t="n"/>
-      <c r="S36" s="473" t="n"/>
-      <c r="T36" s="473" t="n"/>
-      <c r="U36" s="473" t="n"/>
-      <c r="V36" s="473" t="n"/>
-      <c r="W36" s="473" t="n"/>
-      <c r="X36" s="474" t="n"/>
-      <c r="Y36" s="427" t="n"/>
-      <c r="Z36" s="473" t="n"/>
-      <c r="AA36" s="473" t="n"/>
-      <c r="AB36" s="473" t="n"/>
-      <c r="AC36" s="474" t="n"/>
-      <c r="AD36" s="427" t="n"/>
-      <c r="AE36" s="473" t="n"/>
-      <c r="AF36" s="473" t="n"/>
-      <c r="AG36" s="473" t="n"/>
-      <c r="AH36" s="474" t="n"/>
-      <c r="AI36" s="427" t="n"/>
-      <c r="AJ36" s="473" t="n"/>
-      <c r="AK36" s="474" t="n"/>
-      <c r="AL36" s="427" t="n"/>
-      <c r="AM36" s="473" t="n"/>
-      <c r="AN36" s="474" t="n"/>
+      <c r="B36" s="398" t="n"/>
+      <c r="C36" s="560" t="n"/>
+      <c r="D36" s="398" t="n"/>
+      <c r="E36" s="398" t="n"/>
+      <c r="F36" s="398" t="n"/>
+      <c r="G36" s="398" t="n"/>
+      <c r="H36" s="398" t="n"/>
+      <c r="I36" s="398" t="n"/>
+      <c r="J36" s="398" t="n"/>
+      <c r="K36" s="398" t="n"/>
+      <c r="L36" s="398" t="n"/>
+      <c r="M36" s="560" t="n"/>
+      <c r="N36" s="398" t="n"/>
+      <c r="O36" s="398" t="n"/>
+      <c r="P36" s="398" t="n"/>
+      <c r="Q36" s="398" t="n"/>
+      <c r="R36" s="398" t="n"/>
+      <c r="S36" s="398" t="n"/>
+      <c r="T36" s="398" t="n"/>
+      <c r="U36" s="398" t="n"/>
+      <c r="V36" s="398" t="n"/>
+      <c r="W36" s="398" t="n"/>
+      <c r="X36" s="398" t="n"/>
+      <c r="Y36" s="560" t="n"/>
+      <c r="Z36" s="398" t="n"/>
+      <c r="AA36" s="398" t="n"/>
+      <c r="AB36" s="398" t="n"/>
+      <c r="AC36" s="398" t="n"/>
+      <c r="AD36" s="560" t="n"/>
+      <c r="AE36" s="398" t="n"/>
+      <c r="AF36" s="398" t="n"/>
+      <c r="AG36" s="398" t="n"/>
+      <c r="AH36" s="398" t="n"/>
+      <c r="AI36" s="560" t="n"/>
+      <c r="AJ36" s="398" t="n"/>
+      <c r="AK36" s="398" t="n"/>
+      <c r="AL36" s="560" t="n"/>
+      <c r="AM36" s="398" t="n"/>
+      <c r="AN36" s="542" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="429" t="n">
+      <c r="A37" s="567" t="n">
         <v>3</v>
       </c>
-      <c r="B37" s="476" t="n"/>
-      <c r="C37" s="427" t="n"/>
-      <c r="D37" s="473" t="n"/>
-      <c r="E37" s="473" t="n"/>
-      <c r="F37" s="473" t="n"/>
-      <c r="G37" s="473" t="n"/>
-      <c r="H37" s="473" t="n"/>
-      <c r="I37" s="473" t="n"/>
-      <c r="J37" s="473" t="n"/>
-      <c r="K37" s="473" t="n"/>
-      <c r="L37" s="474" t="n"/>
-      <c r="M37" s="427" t="n"/>
-      <c r="N37" s="473" t="n"/>
-      <c r="O37" s="473" t="n"/>
-      <c r="P37" s="473" t="n"/>
-      <c r="Q37" s="473" t="n"/>
-      <c r="R37" s="473" t="n"/>
-      <c r="S37" s="473" t="n"/>
-      <c r="T37" s="473" t="n"/>
-      <c r="U37" s="473" t="n"/>
-      <c r="V37" s="473" t="n"/>
-      <c r="W37" s="473" t="n"/>
-      <c r="X37" s="474" t="n"/>
-      <c r="Y37" s="427" t="n"/>
-      <c r="Z37" s="473" t="n"/>
-      <c r="AA37" s="473" t="n"/>
-      <c r="AB37" s="473" t="n"/>
-      <c r="AC37" s="474" t="n"/>
-      <c r="AD37" s="427" t="n"/>
-      <c r="AE37" s="473" t="n"/>
-      <c r="AF37" s="473" t="n"/>
-      <c r="AG37" s="473" t="n"/>
-      <c r="AH37" s="474" t="n"/>
-      <c r="AI37" s="427" t="n"/>
-      <c r="AJ37" s="473" t="n"/>
-      <c r="AK37" s="474" t="n"/>
-      <c r="AL37" s="427" t="n"/>
-      <c r="AM37" s="473" t="n"/>
-      <c r="AN37" s="474" t="n"/>
+      <c r="B37" s="398" t="n"/>
+      <c r="C37" s="560" t="n"/>
+      <c r="D37" s="398" t="n"/>
+      <c r="E37" s="398" t="n"/>
+      <c r="F37" s="398" t="n"/>
+      <c r="G37" s="398" t="n"/>
+      <c r="H37" s="398" t="n"/>
+      <c r="I37" s="398" t="n"/>
+      <c r="J37" s="398" t="n"/>
+      <c r="K37" s="398" t="n"/>
+      <c r="L37" s="398" t="n"/>
+      <c r="M37" s="560" t="n"/>
+      <c r="N37" s="398" t="n"/>
+      <c r="O37" s="398" t="n"/>
+      <c r="P37" s="398" t="n"/>
+      <c r="Q37" s="398" t="n"/>
+      <c r="R37" s="398" t="n"/>
+      <c r="S37" s="398" t="n"/>
+      <c r="T37" s="398" t="n"/>
+      <c r="U37" s="398" t="n"/>
+      <c r="V37" s="398" t="n"/>
+      <c r="W37" s="398" t="n"/>
+      <c r="X37" s="398" t="n"/>
+      <c r="Y37" s="560" t="n"/>
+      <c r="Z37" s="398" t="n"/>
+      <c r="AA37" s="398" t="n"/>
+      <c r="AB37" s="398" t="n"/>
+      <c r="AC37" s="398" t="n"/>
+      <c r="AD37" s="560" t="n"/>
+      <c r="AE37" s="398" t="n"/>
+      <c r="AF37" s="398" t="n"/>
+      <c r="AG37" s="398" t="n"/>
+      <c r="AH37" s="398" t="n"/>
+      <c r="AI37" s="560" t="n"/>
+      <c r="AJ37" s="398" t="n"/>
+      <c r="AK37" s="398" t="n"/>
+      <c r="AL37" s="560" t="n"/>
+      <c r="AM37" s="398" t="n"/>
+      <c r="AN37" s="542" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="429" t="n">
+      <c r="A38" s="567" t="n">
         <v>4</v>
       </c>
-      <c r="B38" s="476" t="n"/>
-      <c r="C38" s="427" t="n"/>
-      <c r="D38" s="473" t="n"/>
-      <c r="E38" s="473" t="n"/>
-      <c r="F38" s="473" t="n"/>
-      <c r="G38" s="473" t="n"/>
-      <c r="H38" s="473" t="n"/>
-      <c r="I38" s="473" t="n"/>
-      <c r="J38" s="473" t="n"/>
-      <c r="K38" s="473" t="n"/>
-      <c r="L38" s="474" t="n"/>
-      <c r="M38" s="427" t="n"/>
-      <c r="N38" s="473" t="n"/>
-      <c r="O38" s="473" t="n"/>
-      <c r="P38" s="473" t="n"/>
-      <c r="Q38" s="473" t="n"/>
-      <c r="R38" s="473" t="n"/>
-      <c r="S38" s="473" t="n"/>
-      <c r="T38" s="473" t="n"/>
-      <c r="U38" s="473" t="n"/>
-      <c r="V38" s="473" t="n"/>
-      <c r="W38" s="473" t="n"/>
-      <c r="X38" s="474" t="n"/>
-      <c r="Y38" s="427" t="n"/>
-      <c r="Z38" s="473" t="n"/>
-      <c r="AA38" s="473" t="n"/>
-      <c r="AB38" s="473" t="n"/>
-      <c r="AC38" s="474" t="n"/>
-      <c r="AD38" s="427" t="n"/>
-      <c r="AE38" s="473" t="n"/>
-      <c r="AF38" s="473" t="n"/>
-      <c r="AG38" s="473" t="n"/>
-      <c r="AH38" s="474" t="n"/>
-      <c r="AI38" s="427" t="n"/>
-      <c r="AJ38" s="473" t="n"/>
-      <c r="AK38" s="474" t="n"/>
-      <c r="AL38" s="427" t="n"/>
-      <c r="AM38" s="473" t="n"/>
-      <c r="AN38" s="474" t="n"/>
+      <c r="B38" s="398" t="n"/>
+      <c r="C38" s="560" t="n"/>
+      <c r="D38" s="398" t="n"/>
+      <c r="E38" s="398" t="n"/>
+      <c r="F38" s="398" t="n"/>
+      <c r="G38" s="398" t="n"/>
+      <c r="H38" s="398" t="n"/>
+      <c r="I38" s="398" t="n"/>
+      <c r="J38" s="398" t="n"/>
+      <c r="K38" s="398" t="n"/>
+      <c r="L38" s="398" t="n"/>
+      <c r="M38" s="560" t="n"/>
+      <c r="N38" s="398" t="n"/>
+      <c r="O38" s="398" t="n"/>
+      <c r="P38" s="398" t="n"/>
+      <c r="Q38" s="398" t="n"/>
+      <c r="R38" s="398" t="n"/>
+      <c r="S38" s="398" t="n"/>
+      <c r="T38" s="398" t="n"/>
+      <c r="U38" s="398" t="n"/>
+      <c r="V38" s="398" t="n"/>
+      <c r="W38" s="398" t="n"/>
+      <c r="X38" s="398" t="n"/>
+      <c r="Y38" s="560" t="n"/>
+      <c r="Z38" s="398" t="n"/>
+      <c r="AA38" s="398" t="n"/>
+      <c r="AB38" s="398" t="n"/>
+      <c r="AC38" s="398" t="n"/>
+      <c r="AD38" s="560" t="n"/>
+      <c r="AE38" s="398" t="n"/>
+      <c r="AF38" s="398" t="n"/>
+      <c r="AG38" s="398" t="n"/>
+      <c r="AH38" s="398" t="n"/>
+      <c r="AI38" s="560" t="n"/>
+      <c r="AJ38" s="398" t="n"/>
+      <c r="AK38" s="398" t="n"/>
+      <c r="AL38" s="560" t="n"/>
+      <c r="AM38" s="398" t="n"/>
+      <c r="AN38" s="542" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="429" t="n">
+      <c r="A39" s="568" t="n">
         <v>5</v>
       </c>
-      <c r="B39" s="476" t="n"/>
-      <c r="C39" s="427" t="n"/>
-      <c r="D39" s="473" t="n"/>
-      <c r="E39" s="473" t="n"/>
-      <c r="F39" s="473" t="n"/>
-      <c r="G39" s="473" t="n"/>
-      <c r="H39" s="473" t="n"/>
-      <c r="I39" s="473" t="n"/>
-      <c r="J39" s="473" t="n"/>
-      <c r="K39" s="473" t="n"/>
-      <c r="L39" s="474" t="n"/>
-      <c r="M39" s="427" t="n"/>
-      <c r="N39" s="473" t="n"/>
-      <c r="O39" s="473" t="n"/>
-      <c r="P39" s="473" t="n"/>
-      <c r="Q39" s="473" t="n"/>
-      <c r="R39" s="473" t="n"/>
-      <c r="S39" s="473" t="n"/>
-      <c r="T39" s="473" t="n"/>
-      <c r="U39" s="473" t="n"/>
-      <c r="V39" s="473" t="n"/>
-      <c r="W39" s="473" t="n"/>
-      <c r="X39" s="474" t="n"/>
-      <c r="Y39" s="427" t="n"/>
-      <c r="Z39" s="473" t="n"/>
-      <c r="AA39" s="473" t="n"/>
-      <c r="AB39" s="473" t="n"/>
-      <c r="AC39" s="474" t="n"/>
-      <c r="AD39" s="427" t="n"/>
-      <c r="AE39" s="473" t="n"/>
-      <c r="AF39" s="473" t="n"/>
-      <c r="AG39" s="473" t="n"/>
-      <c r="AH39" s="474" t="n"/>
-      <c r="AI39" s="427" t="n"/>
-      <c r="AJ39" s="473" t="n"/>
-      <c r="AK39" s="474" t="n"/>
-      <c r="AL39" s="427" t="n"/>
-      <c r="AM39" s="473" t="n"/>
-      <c r="AN39" s="474" t="n"/>
+      <c r="B39" s="544" t="n"/>
+      <c r="C39" s="565" t="n"/>
+      <c r="D39" s="544" t="n"/>
+      <c r="E39" s="544" t="n"/>
+      <c r="F39" s="544" t="n"/>
+      <c r="G39" s="544" t="n"/>
+      <c r="H39" s="544" t="n"/>
+      <c r="I39" s="544" t="n"/>
+      <c r="J39" s="544" t="n"/>
+      <c r="K39" s="544" t="n"/>
+      <c r="L39" s="544" t="n"/>
+      <c r="M39" s="565" t="n"/>
+      <c r="N39" s="544" t="n"/>
+      <c r="O39" s="544" t="n"/>
+      <c r="P39" s="544" t="n"/>
+      <c r="Q39" s="544" t="n"/>
+      <c r="R39" s="544" t="n"/>
+      <c r="S39" s="544" t="n"/>
+      <c r="T39" s="544" t="n"/>
+      <c r="U39" s="544" t="n"/>
+      <c r="V39" s="544" t="n"/>
+      <c r="W39" s="544" t="n"/>
+      <c r="X39" s="544" t="n"/>
+      <c r="Y39" s="565" t="n"/>
+      <c r="Z39" s="544" t="n"/>
+      <c r="AA39" s="544" t="n"/>
+      <c r="AB39" s="544" t="n"/>
+      <c r="AC39" s="544" t="n"/>
+      <c r="AD39" s="565" t="n"/>
+      <c r="AE39" s="544" t="n"/>
+      <c r="AF39" s="544" t="n"/>
+      <c r="AG39" s="544" t="n"/>
+      <c r="AH39" s="544" t="n"/>
+      <c r="AI39" s="565" t="n"/>
+      <c r="AJ39" s="544" t="n"/>
+      <c r="AK39" s="544" t="n"/>
+      <c r="AL39" s="565" t="n"/>
+      <c r="AM39" s="544" t="n"/>
+      <c r="AN39" s="547" t="n"/>
     </row>
-    <row r="40" ht="4" customHeight="1">
+    <row r="40" ht="3" customHeight="1">
       <c r="A40" s="410" t="n"/>
       <c r="B40" s="482" t="n"/>
       <c r="C40" s="482" t="n"/>
@@ -7637,245 +8498,245 @@
       <c r="AM40" s="482" t="n"/>
       <c r="AN40" s="482" t="n"/>
     </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="411" t="inlineStr">
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="531" t="inlineStr">
         <is>
           <t>5.  APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B41" s="473" t="n"/>
-      <c r="C41" s="473" t="n"/>
-      <c r="D41" s="473" t="n"/>
-      <c r="E41" s="473" t="n"/>
-      <c r="F41" s="473" t="n"/>
-      <c r="G41" s="473" t="n"/>
-      <c r="H41" s="473" t="n"/>
-      <c r="I41" s="473" t="n"/>
-      <c r="J41" s="473" t="n"/>
-      <c r="K41" s="473" t="n"/>
-      <c r="L41" s="473" t="n"/>
-      <c r="M41" s="473" t="n"/>
-      <c r="N41" s="473" t="n"/>
-      <c r="O41" s="473" t="n"/>
-      <c r="P41" s="473" t="n"/>
-      <c r="Q41" s="473" t="n"/>
-      <c r="R41" s="473" t="n"/>
-      <c r="S41" s="473" t="n"/>
-      <c r="T41" s="473" t="n"/>
-      <c r="U41" s="473" t="n"/>
-      <c r="V41" s="473" t="n"/>
-      <c r="W41" s="473" t="n"/>
-      <c r="X41" s="473" t="n"/>
-      <c r="Y41" s="473" t="n"/>
-      <c r="Z41" s="473" t="n"/>
-      <c r="AA41" s="473" t="n"/>
-      <c r="AB41" s="473" t="n"/>
-      <c r="AC41" s="473" t="n"/>
-      <c r="AD41" s="473" t="n"/>
-      <c r="AE41" s="473" t="n"/>
-      <c r="AF41" s="473" t="n"/>
-      <c r="AG41" s="473" t="n"/>
-      <c r="AH41" s="473" t="n"/>
-      <c r="AI41" s="473" t="n"/>
-      <c r="AJ41" s="473" t="n"/>
-      <c r="AK41" s="473" t="n"/>
-      <c r="AL41" s="473" t="n"/>
-      <c r="AM41" s="473" t="n"/>
-      <c r="AN41" s="474" t="n"/>
+      <c r="B41" s="532" t="n"/>
+      <c r="C41" s="532" t="n"/>
+      <c r="D41" s="532" t="n"/>
+      <c r="E41" s="532" t="n"/>
+      <c r="F41" s="532" t="n"/>
+      <c r="G41" s="532" t="n"/>
+      <c r="H41" s="532" t="n"/>
+      <c r="I41" s="532" t="n"/>
+      <c r="J41" s="532" t="n"/>
+      <c r="K41" s="532" t="n"/>
+      <c r="L41" s="532" t="n"/>
+      <c r="M41" s="532" t="n"/>
+      <c r="N41" s="532" t="n"/>
+      <c r="O41" s="532" t="n"/>
+      <c r="P41" s="532" t="n"/>
+      <c r="Q41" s="532" t="n"/>
+      <c r="R41" s="532" t="n"/>
+      <c r="S41" s="532" t="n"/>
+      <c r="T41" s="532" t="n"/>
+      <c r="U41" s="532" t="n"/>
+      <c r="V41" s="532" t="n"/>
+      <c r="W41" s="532" t="n"/>
+      <c r="X41" s="532" t="n"/>
+      <c r="Y41" s="532" t="n"/>
+      <c r="Z41" s="532" t="n"/>
+      <c r="AA41" s="532" t="n"/>
+      <c r="AB41" s="532" t="n"/>
+      <c r="AC41" s="532" t="n"/>
+      <c r="AD41" s="532" t="n"/>
+      <c r="AE41" s="532" t="n"/>
+      <c r="AF41" s="532" t="n"/>
+      <c r="AG41" s="532" t="n"/>
+      <c r="AH41" s="532" t="n"/>
+      <c r="AI41" s="532" t="n"/>
+      <c r="AJ41" s="532" t="n"/>
+      <c r="AK41" s="532" t="n"/>
+      <c r="AL41" s="532" t="n"/>
+      <c r="AM41" s="532" t="n"/>
+      <c r="AN41" s="533" t="n"/>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="430" t="inlineStr">
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="552" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B42" s="467" t="n"/>
-      <c r="C42" s="467" t="n"/>
-      <c r="D42" s="467" t="n"/>
-      <c r="E42" s="467" t="n"/>
-      <c r="F42" s="467" t="n"/>
-      <c r="G42" s="467" t="n"/>
-      <c r="H42" s="467" t="n"/>
-      <c r="I42" s="467" t="n"/>
-      <c r="J42" s="467" t="n"/>
-      <c r="K42" s="467" t="n"/>
-      <c r="L42" s="467" t="n"/>
-      <c r="M42" s="467" t="n"/>
-      <c r="N42" s="431" t="inlineStr">
+      <c r="B42" s="535" t="n"/>
+      <c r="C42" s="535" t="n"/>
+      <c r="D42" s="535" t="n"/>
+      <c r="E42" s="535" t="n"/>
+      <c r="F42" s="535" t="n"/>
+      <c r="G42" s="535" t="n"/>
+      <c r="H42" s="535" t="n"/>
+      <c r="I42" s="535" t="n"/>
+      <c r="J42" s="535" t="n"/>
+      <c r="K42" s="535" t="n"/>
+      <c r="L42" s="535" t="n"/>
+      <c r="M42" s="535" t="n"/>
+      <c r="N42" s="569" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="O42" s="467" t="n"/>
-      <c r="P42" s="467" t="n"/>
-      <c r="Q42" s="467" t="n"/>
-      <c r="R42" s="467" t="n"/>
-      <c r="S42" s="467" t="n"/>
-      <c r="T42" s="467" t="n"/>
-      <c r="U42" s="467" t="n"/>
-      <c r="V42" s="467" t="n"/>
-      <c r="W42" s="467" t="n"/>
-      <c r="X42" s="467" t="n"/>
-      <c r="Y42" s="467" t="n"/>
-      <c r="Z42" s="467" t="n"/>
-      <c r="AA42" s="432" t="inlineStr">
+      <c r="O42" s="535" t="n"/>
+      <c r="P42" s="535" t="n"/>
+      <c r="Q42" s="535" t="n"/>
+      <c r="R42" s="535" t="n"/>
+      <c r="S42" s="535" t="n"/>
+      <c r="T42" s="535" t="n"/>
+      <c r="U42" s="535" t="n"/>
+      <c r="V42" s="535" t="n"/>
+      <c r="W42" s="535" t="n"/>
+      <c r="X42" s="535" t="n"/>
+      <c r="Y42" s="535" t="n"/>
+      <c r="Z42" s="535" t="n"/>
+      <c r="AA42" s="569" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AB42" s="467" t="n"/>
-      <c r="AC42" s="467" t="n"/>
-      <c r="AD42" s="467" t="n"/>
-      <c r="AE42" s="467" t="n"/>
-      <c r="AF42" s="467" t="n"/>
-      <c r="AG42" s="467" t="n"/>
-      <c r="AH42" s="467" t="n"/>
-      <c r="AI42" s="467" t="n"/>
-      <c r="AJ42" s="467" t="n"/>
-      <c r="AK42" s="467" t="n"/>
-      <c r="AL42" s="467" t="n"/>
-      <c r="AM42" s="467" t="n"/>
-      <c r="AN42" s="468" t="n"/>
+      <c r="AB42" s="535" t="n"/>
+      <c r="AC42" s="535" t="n"/>
+      <c r="AD42" s="535" t="n"/>
+      <c r="AE42" s="535" t="n"/>
+      <c r="AF42" s="535" t="n"/>
+      <c r="AG42" s="535" t="n"/>
+      <c r="AH42" s="535" t="n"/>
+      <c r="AI42" s="535" t="n"/>
+      <c r="AJ42" s="535" t="n"/>
+      <c r="AK42" s="535" t="n"/>
+      <c r="AL42" s="535" t="n"/>
+      <c r="AM42" s="535" t="n"/>
+      <c r="AN42" s="538" t="n"/>
     </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="433" t="inlineStr">
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="570" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="B43" s="466" t="n"/>
-      <c r="C43" s="466" t="n"/>
-      <c r="D43" s="466" t="n"/>
-      <c r="E43" s="466" t="n"/>
-      <c r="F43" s="466" t="n"/>
-      <c r="G43" s="466" t="n"/>
-      <c r="H43" s="466" t="n"/>
-      <c r="I43" s="466" t="n"/>
-      <c r="J43" s="466" t="n"/>
-      <c r="K43" s="466" t="n"/>
-      <c r="L43" s="466" t="n"/>
-      <c r="M43" s="477" t="n"/>
-      <c r="N43" s="433" t="inlineStr">
+      <c r="B43" s="398" t="n"/>
+      <c r="C43" s="398" t="n"/>
+      <c r="D43" s="398" t="n"/>
+      <c r="E43" s="398" t="n"/>
+      <c r="F43" s="398" t="n"/>
+      <c r="G43" s="398" t="n"/>
+      <c r="H43" s="398" t="n"/>
+      <c r="I43" s="398" t="n"/>
+      <c r="J43" s="398" t="n"/>
+      <c r="K43" s="398" t="n"/>
+      <c r="L43" s="398" t="n"/>
+      <c r="M43" s="398" t="n"/>
+      <c r="N43" s="571" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="O43" s="466" t="n"/>
-      <c r="P43" s="466" t="n"/>
-      <c r="Q43" s="466" t="n"/>
-      <c r="R43" s="466" t="n"/>
-      <c r="S43" s="466" t="n"/>
-      <c r="T43" s="466" t="n"/>
-      <c r="U43" s="466" t="n"/>
-      <c r="V43" s="466" t="n"/>
-      <c r="W43" s="466" t="n"/>
-      <c r="X43" s="466" t="n"/>
-      <c r="Y43" s="466" t="n"/>
-      <c r="Z43" s="477" t="n"/>
-      <c r="AA43" s="433" t="inlineStr">
+      <c r="O43" s="398" t="n"/>
+      <c r="P43" s="398" t="n"/>
+      <c r="Q43" s="398" t="n"/>
+      <c r="R43" s="398" t="n"/>
+      <c r="S43" s="398" t="n"/>
+      <c r="T43" s="398" t="n"/>
+      <c r="U43" s="398" t="n"/>
+      <c r="V43" s="398" t="n"/>
+      <c r="W43" s="398" t="n"/>
+      <c r="X43" s="398" t="n"/>
+      <c r="Y43" s="398" t="n"/>
+      <c r="Z43" s="398" t="n"/>
+      <c r="AA43" s="571" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="AB43" s="466" t="n"/>
-      <c r="AC43" s="466" t="n"/>
-      <c r="AD43" s="466" t="n"/>
-      <c r="AE43" s="466" t="n"/>
-      <c r="AF43" s="466" t="n"/>
-      <c r="AG43" s="466" t="n"/>
-      <c r="AH43" s="466" t="n"/>
-      <c r="AI43" s="466" t="n"/>
-      <c r="AJ43" s="466" t="n"/>
-      <c r="AK43" s="466" t="n"/>
-      <c r="AL43" s="466" t="n"/>
-      <c r="AM43" s="466" t="n"/>
-      <c r="AN43" s="477" t="n"/>
+      <c r="AB43" s="398" t="n"/>
+      <c r="AC43" s="398" t="n"/>
+      <c r="AD43" s="398" t="n"/>
+      <c r="AE43" s="398" t="n"/>
+      <c r="AF43" s="398" t="n"/>
+      <c r="AG43" s="398" t="n"/>
+      <c r="AH43" s="398" t="n"/>
+      <c r="AI43" s="398" t="n"/>
+      <c r="AJ43" s="398" t="n"/>
+      <c r="AK43" s="398" t="n"/>
+      <c r="AL43" s="398" t="n"/>
+      <c r="AM43" s="398" t="n"/>
+      <c r="AN43" s="542" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="478" t="n"/>
-      <c r="B44" s="436" t="n"/>
-      <c r="C44" s="436" t="n"/>
-      <c r="D44" s="436" t="n"/>
-      <c r="E44" s="436" t="n"/>
-      <c r="F44" s="436" t="n"/>
-      <c r="G44" s="436" t="n"/>
-      <c r="H44" s="436" t="n"/>
-      <c r="I44" s="436" t="n"/>
-      <c r="J44" s="436" t="n"/>
-      <c r="K44" s="436" t="n"/>
-      <c r="L44" s="436" t="n"/>
-      <c r="M44" s="479" t="n"/>
-      <c r="N44" s="478" t="n"/>
-      <c r="O44" s="436" t="n"/>
-      <c r="P44" s="436" t="n"/>
-      <c r="Q44" s="436" t="n"/>
-      <c r="R44" s="436" t="n"/>
-      <c r="S44" s="436" t="n"/>
-      <c r="T44" s="436" t="n"/>
-      <c r="U44" s="436" t="n"/>
-      <c r="V44" s="436" t="n"/>
-      <c r="W44" s="436" t="n"/>
-      <c r="X44" s="436" t="n"/>
-      <c r="Y44" s="436" t="n"/>
-      <c r="Z44" s="479" t="n"/>
-      <c r="AA44" s="478" t="n"/>
-      <c r="AB44" s="436" t="n"/>
-      <c r="AC44" s="436" t="n"/>
-      <c r="AD44" s="436" t="n"/>
-      <c r="AE44" s="436" t="n"/>
-      <c r="AF44" s="436" t="n"/>
-      <c r="AG44" s="436" t="n"/>
-      <c r="AH44" s="436" t="n"/>
-      <c r="AI44" s="436" t="n"/>
-      <c r="AJ44" s="436" t="n"/>
-      <c r="AK44" s="436" t="n"/>
-      <c r="AL44" s="436" t="n"/>
-      <c r="AM44" s="436" t="n"/>
-      <c r="AN44" s="479" t="n"/>
+      <c r="A44" s="572" t="n"/>
+      <c r="B44" s="398" t="n"/>
+      <c r="C44" s="398" t="n"/>
+      <c r="D44" s="398" t="n"/>
+      <c r="E44" s="398" t="n"/>
+      <c r="F44" s="398" t="n"/>
+      <c r="G44" s="398" t="n"/>
+      <c r="H44" s="398" t="n"/>
+      <c r="I44" s="398" t="n"/>
+      <c r="J44" s="398" t="n"/>
+      <c r="K44" s="398" t="n"/>
+      <c r="L44" s="398" t="n"/>
+      <c r="M44" s="398" t="n"/>
+      <c r="N44" s="573" t="n"/>
+      <c r="O44" s="398" t="n"/>
+      <c r="P44" s="398" t="n"/>
+      <c r="Q44" s="398" t="n"/>
+      <c r="R44" s="398" t="n"/>
+      <c r="S44" s="398" t="n"/>
+      <c r="T44" s="398" t="n"/>
+      <c r="U44" s="398" t="n"/>
+      <c r="V44" s="398" t="n"/>
+      <c r="W44" s="398" t="n"/>
+      <c r="X44" s="398" t="n"/>
+      <c r="Y44" s="398" t="n"/>
+      <c r="Z44" s="398" t="n"/>
+      <c r="AA44" s="573" t="n"/>
+      <c r="AB44" s="398" t="n"/>
+      <c r="AC44" s="398" t="n"/>
+      <c r="AD44" s="398" t="n"/>
+      <c r="AE44" s="398" t="n"/>
+      <c r="AF44" s="398" t="n"/>
+      <c r="AG44" s="398" t="n"/>
+      <c r="AH44" s="398" t="n"/>
+      <c r="AI44" s="398" t="n"/>
+      <c r="AJ44" s="398" t="n"/>
+      <c r="AK44" s="398" t="n"/>
+      <c r="AL44" s="398" t="n"/>
+      <c r="AM44" s="398" t="n"/>
+      <c r="AN44" s="542" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="480" t="n"/>
-      <c r="B45" s="475" t="n"/>
-      <c r="C45" s="475" t="n"/>
-      <c r="D45" s="475" t="n"/>
-      <c r="E45" s="475" t="n"/>
-      <c r="F45" s="475" t="n"/>
-      <c r="G45" s="475" t="n"/>
-      <c r="H45" s="475" t="n"/>
-      <c r="I45" s="475" t="n"/>
-      <c r="J45" s="475" t="n"/>
-      <c r="K45" s="475" t="n"/>
-      <c r="L45" s="475" t="n"/>
-      <c r="M45" s="476" t="n"/>
-      <c r="N45" s="480" t="n"/>
-      <c r="O45" s="475" t="n"/>
-      <c r="P45" s="475" t="n"/>
-      <c r="Q45" s="475" t="n"/>
-      <c r="R45" s="475" t="n"/>
-      <c r="S45" s="475" t="n"/>
-      <c r="T45" s="475" t="n"/>
-      <c r="U45" s="475" t="n"/>
-      <c r="V45" s="475" t="n"/>
-      <c r="W45" s="475" t="n"/>
-      <c r="X45" s="475" t="n"/>
-      <c r="Y45" s="475" t="n"/>
-      <c r="Z45" s="476" t="n"/>
-      <c r="AA45" s="480" t="n"/>
-      <c r="AB45" s="475" t="n"/>
-      <c r="AC45" s="475" t="n"/>
-      <c r="AD45" s="475" t="n"/>
-      <c r="AE45" s="475" t="n"/>
-      <c r="AF45" s="475" t="n"/>
-      <c r="AG45" s="475" t="n"/>
-      <c r="AH45" s="475" t="n"/>
-      <c r="AI45" s="475" t="n"/>
-      <c r="AJ45" s="475" t="n"/>
-      <c r="AK45" s="475" t="n"/>
-      <c r="AL45" s="475" t="n"/>
-      <c r="AM45" s="475" t="n"/>
-      <c r="AN45" s="476" t="n"/>
+      <c r="A45" s="574" t="n"/>
+      <c r="B45" s="544" t="n"/>
+      <c r="C45" s="544" t="n"/>
+      <c r="D45" s="544" t="n"/>
+      <c r="E45" s="544" t="n"/>
+      <c r="F45" s="544" t="n"/>
+      <c r="G45" s="544" t="n"/>
+      <c r="H45" s="544" t="n"/>
+      <c r="I45" s="544" t="n"/>
+      <c r="J45" s="544" t="n"/>
+      <c r="K45" s="544" t="n"/>
+      <c r="L45" s="544" t="n"/>
+      <c r="M45" s="544" t="n"/>
+      <c r="N45" s="575" t="n"/>
+      <c r="O45" s="544" t="n"/>
+      <c r="P45" s="544" t="n"/>
+      <c r="Q45" s="544" t="n"/>
+      <c r="R45" s="544" t="n"/>
+      <c r="S45" s="544" t="n"/>
+      <c r="T45" s="544" t="n"/>
+      <c r="U45" s="544" t="n"/>
+      <c r="V45" s="544" t="n"/>
+      <c r="W45" s="544" t="n"/>
+      <c r="X45" s="544" t="n"/>
+      <c r="Y45" s="544" t="n"/>
+      <c r="Z45" s="544" t="n"/>
+      <c r="AA45" s="575" t="n"/>
+      <c r="AB45" s="544" t="n"/>
+      <c r="AC45" s="544" t="n"/>
+      <c r="AD45" s="544" t="n"/>
+      <c r="AE45" s="544" t="n"/>
+      <c r="AF45" s="544" t="n"/>
+      <c r="AG45" s="544" t="n"/>
+      <c r="AH45" s="544" t="n"/>
+      <c r="AI45" s="544" t="n"/>
+      <c r="AJ45" s="544" t="n"/>
+      <c r="AK45" s="544" t="n"/>
+      <c r="AL45" s="544" t="n"/>
+      <c r="AM45" s="544" t="n"/>
+      <c r="AN45" s="547" t="n"/>
     </row>
-    <row r="46" ht="4" customHeight="1">
+    <row r="46" ht="3" customHeight="1">
       <c r="A46" s="410" t="n"/>
       <c r="B46" s="482" t="n"/>
       <c r="C46" s="482" t="n"/>
@@ -7917,51 +8778,51 @@
       <c r="AM46" s="482" t="n"/>
       <c r="AN46" s="482" t="n"/>
     </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="439" t="inlineStr">
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="531" t="inlineStr">
         <is>
           <t>NOTICE  —  Enter data only in designated white input cells. Do not add, delete or resize columns/rows. File naming: FRM-209_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="473" t="n"/>
-      <c r="C47" s="473" t="n"/>
-      <c r="D47" s="473" t="n"/>
-      <c r="E47" s="473" t="n"/>
-      <c r="F47" s="473" t="n"/>
-      <c r="G47" s="473" t="n"/>
-      <c r="H47" s="473" t="n"/>
-      <c r="I47" s="473" t="n"/>
-      <c r="J47" s="473" t="n"/>
-      <c r="K47" s="473" t="n"/>
-      <c r="L47" s="473" t="n"/>
-      <c r="M47" s="473" t="n"/>
-      <c r="N47" s="473" t="n"/>
-      <c r="O47" s="473" t="n"/>
-      <c r="P47" s="473" t="n"/>
-      <c r="Q47" s="473" t="n"/>
-      <c r="R47" s="473" t="n"/>
-      <c r="S47" s="473" t="n"/>
-      <c r="T47" s="473" t="n"/>
-      <c r="U47" s="473" t="n"/>
-      <c r="V47" s="473" t="n"/>
-      <c r="W47" s="473" t="n"/>
-      <c r="X47" s="473" t="n"/>
-      <c r="Y47" s="473" t="n"/>
-      <c r="Z47" s="473" t="n"/>
-      <c r="AA47" s="473" t="n"/>
-      <c r="AB47" s="473" t="n"/>
-      <c r="AC47" s="473" t="n"/>
-      <c r="AD47" s="473" t="n"/>
-      <c r="AE47" s="473" t="n"/>
-      <c r="AF47" s="473" t="n"/>
-      <c r="AG47" s="473" t="n"/>
-      <c r="AH47" s="473" t="n"/>
-      <c r="AI47" s="473" t="n"/>
-      <c r="AJ47" s="473" t="n"/>
-      <c r="AK47" s="473" t="n"/>
-      <c r="AL47" s="473" t="n"/>
-      <c r="AM47" s="473" t="n"/>
-      <c r="AN47" s="474" t="n"/>
+      <c r="B47" s="532" t="n"/>
+      <c r="C47" s="532" t="n"/>
+      <c r="D47" s="532" t="n"/>
+      <c r="E47" s="532" t="n"/>
+      <c r="F47" s="532" t="n"/>
+      <c r="G47" s="532" t="n"/>
+      <c r="H47" s="532" t="n"/>
+      <c r="I47" s="532" t="n"/>
+      <c r="J47" s="532" t="n"/>
+      <c r="K47" s="532" t="n"/>
+      <c r="L47" s="532" t="n"/>
+      <c r="M47" s="532" t="n"/>
+      <c r="N47" s="532" t="n"/>
+      <c r="O47" s="532" t="n"/>
+      <c r="P47" s="532" t="n"/>
+      <c r="Q47" s="532" t="n"/>
+      <c r="R47" s="532" t="n"/>
+      <c r="S47" s="532" t="n"/>
+      <c r="T47" s="532" t="n"/>
+      <c r="U47" s="532" t="n"/>
+      <c r="V47" s="532" t="n"/>
+      <c r="W47" s="532" t="n"/>
+      <c r="X47" s="532" t="n"/>
+      <c r="Y47" s="532" t="n"/>
+      <c r="Z47" s="532" t="n"/>
+      <c r="AA47" s="532" t="n"/>
+      <c r="AB47" s="532" t="n"/>
+      <c r="AC47" s="532" t="n"/>
+      <c r="AD47" s="532" t="n"/>
+      <c r="AE47" s="532" t="n"/>
+      <c r="AF47" s="532" t="n"/>
+      <c r="AG47" s="532" t="n"/>
+      <c r="AH47" s="532" t="n"/>
+      <c r="AI47" s="532" t="n"/>
+      <c r="AJ47" s="532" t="n"/>
+      <c r="AK47" s="532" t="n"/>
+      <c r="AL47" s="532" t="n"/>
+      <c r="AM47" s="532" t="n"/>
+      <c r="AN47" s="533" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="1"/>
     <row r="49" hidden="1" outlineLevel="1"/>
@@ -8117,7 +8978,7 @@
     <row r="199" hidden="1" outlineLevel="1"/>
     <row r="200" hidden="1" outlineLevel="1"/>
   </sheetData>
-  <mergeCells count="187">
+  <mergeCells count="181">
     <mergeCell ref="AM26:AN26"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="AF23:AI23"/>
@@ -8126,7 +8987,6 @@
     <mergeCell ref="AB17:AN17"/>
     <mergeCell ref="AM29:AN29"/>
     <mergeCell ref="AM23:AN23"/>
-    <mergeCell ref="A32:AN32"/>
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="A14:AN14"/>
     <mergeCell ref="I4:AD4"/>
@@ -8145,7 +9005,6 @@
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="T31:AE31"/>
-    <mergeCell ref="A40:AN40"/>
     <mergeCell ref="AJ29:AL29"/>
     <mergeCell ref="AD36:AH36"/>
     <mergeCell ref="T28:AE28"/>
@@ -8157,7 +9016,6 @@
     <mergeCell ref="F28:S28"/>
     <mergeCell ref="T30:AE30"/>
     <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A6:AN6"/>
     <mergeCell ref="AJ21:AL21"/>
     <mergeCell ref="AM25:AN25"/>
     <mergeCell ref="AI34:AK34"/>
@@ -8198,7 +9056,6 @@
     <mergeCell ref="H8:T8"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="AJ26:AL26"/>
-    <mergeCell ref="A13:AN13"/>
     <mergeCell ref="AF24:AI24"/>
     <mergeCell ref="AI3:AN3"/>
     <mergeCell ref="AL35:AN35"/>
@@ -8242,7 +9099,6 @@
     <mergeCell ref="AA43:AN45"/>
     <mergeCell ref="Y35:AC35"/>
     <mergeCell ref="F24:S24"/>
-    <mergeCell ref="A19:AN19"/>
     <mergeCell ref="T23:AE23"/>
     <mergeCell ref="A1:H5"/>
     <mergeCell ref="F26:S26"/>
@@ -8268,7 +9124,6 @@
     <mergeCell ref="AM21:AN21"/>
     <mergeCell ref="N43:Z45"/>
     <mergeCell ref="AL36:AN36"/>
-    <mergeCell ref="A46:AN46"/>
     <mergeCell ref="H11:T11"/>
     <mergeCell ref="AM27:AN27"/>
     <mergeCell ref="AB11:AN11"/>
@@ -8433,6 +9288,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -9121,328 +9977,328 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="402" t="inlineStr">
+      <c r="A1" s="576" t="inlineStr">
         <is>
           <t>REF_CUSTOMER_MASTER</t>
         </is>
       </c>
-      <c r="B1" s="402" t="inlineStr">
+      <c r="B1" s="535" t="inlineStr">
         <is>
           <t>REF_PART_REV_MASTER</t>
         </is>
       </c>
-      <c r="C1" s="402" t="inlineStr">
+      <c r="C1" s="535" t="inlineStr">
         <is>
           <t>REF_JOB_WO_MASTER</t>
         </is>
       </c>
-      <c r="D1" s="402" t="inlineStr">
+      <c r="D1" s="535" t="inlineStr">
         <is>
           <t>REF_OWNER_PERSON_MASTER</t>
         </is>
       </c>
-      <c r="E1" s="402" t="n"/>
-      <c r="F1" s="402" t="n"/>
-      <c r="G1" s="402" t="n"/>
-      <c r="H1" s="402" t="n"/>
-      <c r="I1" s="402" t="n"/>
-      <c r="J1" s="402" t="n"/>
-      <c r="K1" s="402" t="n"/>
-      <c r="L1" s="402" t="n"/>
-      <c r="M1" s="402" t="n"/>
-      <c r="N1" s="402" t="n"/>
-      <c r="O1" s="402" t="n"/>
-      <c r="P1" s="402" t="n"/>
-      <c r="Q1" s="402" t="n"/>
-      <c r="R1" s="402" t="n"/>
-      <c r="S1" s="402" t="n"/>
-      <c r="T1" s="402" t="n"/>
-      <c r="U1" s="402" t="n"/>
-      <c r="V1" s="402" t="n"/>
-      <c r="W1" s="402" t="n"/>
-      <c r="X1" s="402" t="n"/>
-      <c r="Y1" s="402" t="n"/>
-      <c r="Z1" s="402" t="n"/>
-      <c r="AA1" s="402" t="n"/>
-      <c r="AB1" s="402" t="n"/>
-      <c r="AC1" s="402" t="n"/>
-      <c r="AD1" s="402" t="n"/>
-      <c r="AE1" s="402" t="n"/>
-      <c r="AF1" s="402" t="n"/>
-      <c r="AG1" s="402" t="n"/>
-      <c r="AH1" s="402" t="n"/>
-      <c r="AI1" s="402" t="n"/>
-      <c r="AJ1" s="402" t="n"/>
-      <c r="AK1" s="402" t="n"/>
-      <c r="AL1" s="402" t="n"/>
-      <c r="AM1" s="402" t="n"/>
-      <c r="AN1" s="402" t="n"/>
+      <c r="E1" s="535" t="n"/>
+      <c r="F1" s="535" t="n"/>
+      <c r="G1" s="535" t="n"/>
+      <c r="H1" s="535" t="n"/>
+      <c r="I1" s="535" t="n"/>
+      <c r="J1" s="535" t="n"/>
+      <c r="K1" s="535" t="n"/>
+      <c r="L1" s="535" t="n"/>
+      <c r="M1" s="535" t="n"/>
+      <c r="N1" s="535" t="n"/>
+      <c r="O1" s="535" t="n"/>
+      <c r="P1" s="535" t="n"/>
+      <c r="Q1" s="535" t="n"/>
+      <c r="R1" s="535" t="n"/>
+      <c r="S1" s="535" t="n"/>
+      <c r="T1" s="535" t="n"/>
+      <c r="U1" s="535" t="n"/>
+      <c r="V1" s="535" t="n"/>
+      <c r="W1" s="535" t="n"/>
+      <c r="X1" s="535" t="n"/>
+      <c r="Y1" s="535" t="n"/>
+      <c r="Z1" s="535" t="n"/>
+      <c r="AA1" s="535" t="n"/>
+      <c r="AB1" s="535" t="n"/>
+      <c r="AC1" s="535" t="n"/>
+      <c r="AD1" s="535" t="n"/>
+      <c r="AE1" s="535" t="n"/>
+      <c r="AF1" s="535" t="n"/>
+      <c r="AG1" s="535" t="n"/>
+      <c r="AH1" s="535" t="n"/>
+      <c r="AI1" s="535" t="n"/>
+      <c r="AJ1" s="535" t="n"/>
+      <c r="AK1" s="535" t="n"/>
+      <c r="AL1" s="535" t="n"/>
+      <c r="AM1" s="535" t="n"/>
+      <c r="AN1" s="538" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="402" t="inlineStr">
+      <c r="A2" s="572" t="inlineStr">
         <is>
           <t>CUST-001 Alpha Semi</t>
         </is>
       </c>
-      <c r="B2" s="402" t="inlineStr">
+      <c r="B2" s="398" t="inlineStr">
         <is>
           <t>PN-1001 / Rev.A</t>
         </is>
       </c>
-      <c r="C2" s="402" t="inlineStr">
+      <c r="C2" s="398" t="inlineStr">
         <is>
           <t>JOB-240001</t>
         </is>
       </c>
-      <c r="D2" s="402" t="inlineStr">
+      <c r="D2" s="398" t="inlineStr">
         <is>
           <t>Planning Lead</t>
         </is>
       </c>
-      <c r="E2" s="402" t="n"/>
-      <c r="F2" s="402" t="n"/>
-      <c r="G2" s="402" t="n"/>
-      <c r="H2" s="402" t="n"/>
-      <c r="I2" s="402" t="n"/>
-      <c r="J2" s="402" t="n"/>
-      <c r="K2" s="402" t="n"/>
-      <c r="L2" s="402" t="n"/>
-      <c r="M2" s="402" t="n"/>
-      <c r="N2" s="402" t="n"/>
-      <c r="O2" s="402" t="n"/>
-      <c r="P2" s="402" t="n"/>
-      <c r="Q2" s="402" t="n"/>
-      <c r="R2" s="402" t="n"/>
-      <c r="S2" s="402" t="n"/>
-      <c r="T2" s="402" t="n"/>
-      <c r="U2" s="402" t="n"/>
-      <c r="V2" s="402" t="n"/>
-      <c r="W2" s="402" t="n"/>
-      <c r="X2" s="402" t="n"/>
-      <c r="Y2" s="402" t="n"/>
-      <c r="Z2" s="402" t="n"/>
-      <c r="AA2" s="402" t="n"/>
-      <c r="AB2" s="402" t="n"/>
-      <c r="AC2" s="402" t="n"/>
-      <c r="AD2" s="402" t="n"/>
-      <c r="AE2" s="402" t="n"/>
-      <c r="AF2" s="402" t="n"/>
-      <c r="AG2" s="402" t="n"/>
-      <c r="AH2" s="402" t="n"/>
-      <c r="AI2" s="402" t="n"/>
-      <c r="AJ2" s="402" t="n"/>
-      <c r="AK2" s="402" t="n"/>
-      <c r="AL2" s="402" t="n"/>
-      <c r="AM2" s="402" t="n"/>
-      <c r="AN2" s="402" t="n"/>
+      <c r="E2" s="398" t="n"/>
+      <c r="F2" s="398" t="n"/>
+      <c r="G2" s="398" t="n"/>
+      <c r="H2" s="398" t="n"/>
+      <c r="I2" s="398" t="n"/>
+      <c r="J2" s="398" t="n"/>
+      <c r="K2" s="398" t="n"/>
+      <c r="L2" s="398" t="n"/>
+      <c r="M2" s="398" t="n"/>
+      <c r="N2" s="398" t="n"/>
+      <c r="O2" s="398" t="n"/>
+      <c r="P2" s="398" t="n"/>
+      <c r="Q2" s="398" t="n"/>
+      <c r="R2" s="398" t="n"/>
+      <c r="S2" s="398" t="n"/>
+      <c r="T2" s="398" t="n"/>
+      <c r="U2" s="398" t="n"/>
+      <c r="V2" s="398" t="n"/>
+      <c r="W2" s="398" t="n"/>
+      <c r="X2" s="398" t="n"/>
+      <c r="Y2" s="398" t="n"/>
+      <c r="Z2" s="398" t="n"/>
+      <c r="AA2" s="398" t="n"/>
+      <c r="AB2" s="398" t="n"/>
+      <c r="AC2" s="398" t="n"/>
+      <c r="AD2" s="398" t="n"/>
+      <c r="AE2" s="398" t="n"/>
+      <c r="AF2" s="398" t="n"/>
+      <c r="AG2" s="398" t="n"/>
+      <c r="AH2" s="398" t="n"/>
+      <c r="AI2" s="398" t="n"/>
+      <c r="AJ2" s="398" t="n"/>
+      <c r="AK2" s="398" t="n"/>
+      <c r="AL2" s="398" t="n"/>
+      <c r="AM2" s="398" t="n"/>
+      <c r="AN2" s="542" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="402" t="inlineStr">
+      <c r="A3" s="572" t="inlineStr">
         <is>
           <t>CUST-002 NovaFab</t>
         </is>
       </c>
-      <c r="B3" s="402" t="inlineStr">
+      <c r="B3" s="398" t="inlineStr">
         <is>
           <t>PN-1002 / Rev.B</t>
         </is>
       </c>
-      <c r="C3" s="402" t="inlineStr">
+      <c r="C3" s="398" t="inlineStr">
         <is>
           <t>JOB-240002</t>
         </is>
       </c>
-      <c r="D3" s="402" t="inlineStr">
+      <c r="D3" s="398" t="inlineStr">
         <is>
           <t>Production Supervisor</t>
         </is>
       </c>
-      <c r="E3" s="402" t="n"/>
-      <c r="F3" s="402" t="n"/>
-      <c r="G3" s="402" t="n"/>
-      <c r="H3" s="402" t="n"/>
-      <c r="I3" s="402" t="n"/>
-      <c r="J3" s="402" t="n"/>
-      <c r="K3" s="402" t="n"/>
-      <c r="L3" s="402" t="n"/>
-      <c r="M3" s="402" t="n"/>
-      <c r="N3" s="402" t="n"/>
-      <c r="O3" s="402" t="n"/>
-      <c r="P3" s="402" t="n"/>
-      <c r="Q3" s="402" t="n"/>
-      <c r="R3" s="402" t="n"/>
-      <c r="S3" s="402" t="n"/>
-      <c r="T3" s="402" t="n"/>
-      <c r="U3" s="402" t="n"/>
-      <c r="V3" s="402" t="n"/>
-      <c r="W3" s="402" t="n"/>
-      <c r="X3" s="402" t="n"/>
-      <c r="Y3" s="402" t="n"/>
-      <c r="Z3" s="402" t="n"/>
-      <c r="AA3" s="402" t="n"/>
-      <c r="AB3" s="402" t="n"/>
-      <c r="AC3" s="402" t="n"/>
-      <c r="AD3" s="402" t="n"/>
-      <c r="AE3" s="402" t="n"/>
-      <c r="AF3" s="402" t="n"/>
-      <c r="AG3" s="402" t="n"/>
-      <c r="AH3" s="402" t="n"/>
-      <c r="AI3" s="402" t="n"/>
-      <c r="AJ3" s="402" t="n"/>
-      <c r="AK3" s="402" t="n"/>
-      <c r="AL3" s="402" t="n"/>
-      <c r="AM3" s="402" t="n"/>
-      <c r="AN3" s="402" t="n"/>
+      <c r="E3" s="398" t="n"/>
+      <c r="F3" s="398" t="n"/>
+      <c r="G3" s="398" t="n"/>
+      <c r="H3" s="398" t="n"/>
+      <c r="I3" s="398" t="n"/>
+      <c r="J3" s="398" t="n"/>
+      <c r="K3" s="398" t="n"/>
+      <c r="L3" s="398" t="n"/>
+      <c r="M3" s="398" t="n"/>
+      <c r="N3" s="398" t="n"/>
+      <c r="O3" s="398" t="n"/>
+      <c r="P3" s="398" t="n"/>
+      <c r="Q3" s="398" t="n"/>
+      <c r="R3" s="398" t="n"/>
+      <c r="S3" s="398" t="n"/>
+      <c r="T3" s="398" t="n"/>
+      <c r="U3" s="398" t="n"/>
+      <c r="V3" s="398" t="n"/>
+      <c r="W3" s="398" t="n"/>
+      <c r="X3" s="398" t="n"/>
+      <c r="Y3" s="398" t="n"/>
+      <c r="Z3" s="398" t="n"/>
+      <c r="AA3" s="398" t="n"/>
+      <c r="AB3" s="398" t="n"/>
+      <c r="AC3" s="398" t="n"/>
+      <c r="AD3" s="398" t="n"/>
+      <c r="AE3" s="398" t="n"/>
+      <c r="AF3" s="398" t="n"/>
+      <c r="AG3" s="398" t="n"/>
+      <c r="AH3" s="398" t="n"/>
+      <c r="AI3" s="398" t="n"/>
+      <c r="AJ3" s="398" t="n"/>
+      <c r="AK3" s="398" t="n"/>
+      <c r="AL3" s="398" t="n"/>
+      <c r="AM3" s="398" t="n"/>
+      <c r="AN3" s="542" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="402" t="inlineStr">
+      <c r="A4" s="572" t="inlineStr">
         <is>
           <t>CUST-003 Orion Tech</t>
         </is>
       </c>
-      <c r="B4" s="402" t="inlineStr">
+      <c r="B4" s="398" t="inlineStr">
         <is>
           <t>PN-1003 / Rev.C</t>
         </is>
       </c>
-      <c r="C4" s="402" t="inlineStr">
+      <c r="C4" s="398" t="inlineStr">
         <is>
           <t>JOB-240003</t>
         </is>
       </c>
-      <c r="D4" s="402" t="inlineStr">
+      <c r="D4" s="398" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="E4" s="402" t="n"/>
-      <c r="F4" s="402" t="n"/>
-      <c r="G4" s="402" t="n"/>
-      <c r="H4" s="402" t="n"/>
-      <c r="I4" s="402" t="n"/>
-      <c r="J4" s="402" t="n"/>
-      <c r="K4" s="402" t="n"/>
-      <c r="L4" s="402" t="n"/>
-      <c r="M4" s="402" t="n"/>
-      <c r="N4" s="402" t="n"/>
-      <c r="O4" s="402" t="n"/>
-      <c r="P4" s="402" t="n"/>
-      <c r="Q4" s="402" t="n"/>
-      <c r="R4" s="402" t="n"/>
-      <c r="S4" s="402" t="n"/>
-      <c r="T4" s="402" t="n"/>
-      <c r="U4" s="402" t="n"/>
-      <c r="V4" s="402" t="n"/>
-      <c r="W4" s="402" t="n"/>
-      <c r="X4" s="402" t="n"/>
-      <c r="Y4" s="402" t="n"/>
-      <c r="Z4" s="402" t="n"/>
-      <c r="AA4" s="402" t="n"/>
-      <c r="AB4" s="402" t="n"/>
-      <c r="AC4" s="402" t="n"/>
-      <c r="AD4" s="402" t="n"/>
-      <c r="AE4" s="402" t="n"/>
-      <c r="AF4" s="402" t="n"/>
-      <c r="AG4" s="402" t="n"/>
-      <c r="AH4" s="402" t="n"/>
-      <c r="AI4" s="402" t="n"/>
-      <c r="AJ4" s="402" t="n"/>
-      <c r="AK4" s="402" t="n"/>
-      <c r="AL4" s="402" t="n"/>
-      <c r="AM4" s="402" t="n"/>
-      <c r="AN4" s="402" t="n"/>
+      <c r="E4" s="398" t="n"/>
+      <c r="F4" s="398" t="n"/>
+      <c r="G4" s="398" t="n"/>
+      <c r="H4" s="398" t="n"/>
+      <c r="I4" s="398" t="n"/>
+      <c r="J4" s="398" t="n"/>
+      <c r="K4" s="398" t="n"/>
+      <c r="L4" s="398" t="n"/>
+      <c r="M4" s="398" t="n"/>
+      <c r="N4" s="398" t="n"/>
+      <c r="O4" s="398" t="n"/>
+      <c r="P4" s="398" t="n"/>
+      <c r="Q4" s="398" t="n"/>
+      <c r="R4" s="398" t="n"/>
+      <c r="S4" s="398" t="n"/>
+      <c r="T4" s="398" t="n"/>
+      <c r="U4" s="398" t="n"/>
+      <c r="V4" s="398" t="n"/>
+      <c r="W4" s="398" t="n"/>
+      <c r="X4" s="398" t="n"/>
+      <c r="Y4" s="398" t="n"/>
+      <c r="Z4" s="398" t="n"/>
+      <c r="AA4" s="398" t="n"/>
+      <c r="AB4" s="398" t="n"/>
+      <c r="AC4" s="398" t="n"/>
+      <c r="AD4" s="398" t="n"/>
+      <c r="AE4" s="398" t="n"/>
+      <c r="AF4" s="398" t="n"/>
+      <c r="AG4" s="398" t="n"/>
+      <c r="AH4" s="398" t="n"/>
+      <c r="AI4" s="398" t="n"/>
+      <c r="AJ4" s="398" t="n"/>
+      <c r="AK4" s="398" t="n"/>
+      <c r="AL4" s="398" t="n"/>
+      <c r="AM4" s="398" t="n"/>
+      <c r="AN4" s="542" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="402" t="n"/>
-      <c r="B5" s="402" t="n"/>
-      <c r="C5" s="402" t="n"/>
-      <c r="D5" s="402" t="inlineStr">
+      <c r="A5" s="572" t="n"/>
+      <c r="B5" s="398" t="n"/>
+      <c r="C5" s="398" t="n"/>
+      <c r="D5" s="398" t="inlineStr">
         <is>
           <t>Engineering Lead</t>
         </is>
       </c>
-      <c r="E5" s="402" t="n"/>
-      <c r="F5" s="402" t="n"/>
-      <c r="G5" s="402" t="n"/>
-      <c r="H5" s="402" t="n"/>
-      <c r="I5" s="402" t="n"/>
-      <c r="J5" s="402" t="n"/>
-      <c r="K5" s="402" t="n"/>
-      <c r="L5" s="402" t="n"/>
-      <c r="M5" s="402" t="n"/>
-      <c r="N5" s="402" t="n"/>
-      <c r="O5" s="402" t="n"/>
-      <c r="P5" s="402" t="n"/>
-      <c r="Q5" s="402" t="n"/>
-      <c r="R5" s="402" t="n"/>
-      <c r="S5" s="402" t="n"/>
-      <c r="T5" s="402" t="n"/>
-      <c r="U5" s="402" t="n"/>
-      <c r="V5" s="402" t="n"/>
-      <c r="W5" s="402" t="n"/>
-      <c r="X5" s="402" t="n"/>
-      <c r="Y5" s="402" t="n"/>
-      <c r="Z5" s="402" t="n"/>
-      <c r="AA5" s="402" t="n"/>
-      <c r="AB5" s="402" t="n"/>
-      <c r="AC5" s="402" t="n"/>
-      <c r="AD5" s="402" t="n"/>
-      <c r="AE5" s="402" t="n"/>
-      <c r="AF5" s="402" t="n"/>
-      <c r="AG5" s="402" t="n"/>
-      <c r="AH5" s="402" t="n"/>
-      <c r="AI5" s="402" t="n"/>
-      <c r="AJ5" s="402" t="n"/>
-      <c r="AK5" s="402" t="n"/>
-      <c r="AL5" s="402" t="n"/>
-      <c r="AM5" s="402" t="n"/>
-      <c r="AN5" s="402" t="n"/>
+      <c r="E5" s="398" t="n"/>
+      <c r="F5" s="398" t="n"/>
+      <c r="G5" s="398" t="n"/>
+      <c r="H5" s="398" t="n"/>
+      <c r="I5" s="398" t="n"/>
+      <c r="J5" s="398" t="n"/>
+      <c r="K5" s="398" t="n"/>
+      <c r="L5" s="398" t="n"/>
+      <c r="M5" s="398" t="n"/>
+      <c r="N5" s="398" t="n"/>
+      <c r="O5" s="398" t="n"/>
+      <c r="P5" s="398" t="n"/>
+      <c r="Q5" s="398" t="n"/>
+      <c r="R5" s="398" t="n"/>
+      <c r="S5" s="398" t="n"/>
+      <c r="T5" s="398" t="n"/>
+      <c r="U5" s="398" t="n"/>
+      <c r="V5" s="398" t="n"/>
+      <c r="W5" s="398" t="n"/>
+      <c r="X5" s="398" t="n"/>
+      <c r="Y5" s="398" t="n"/>
+      <c r="Z5" s="398" t="n"/>
+      <c r="AA5" s="398" t="n"/>
+      <c r="AB5" s="398" t="n"/>
+      <c r="AC5" s="398" t="n"/>
+      <c r="AD5" s="398" t="n"/>
+      <c r="AE5" s="398" t="n"/>
+      <c r="AF5" s="398" t="n"/>
+      <c r="AG5" s="398" t="n"/>
+      <c r="AH5" s="398" t="n"/>
+      <c r="AI5" s="398" t="n"/>
+      <c r="AJ5" s="398" t="n"/>
+      <c r="AK5" s="398" t="n"/>
+      <c r="AL5" s="398" t="n"/>
+      <c r="AM5" s="398" t="n"/>
+      <c r="AN5" s="542" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="402" t="n"/>
-      <c r="B6" s="402" t="n"/>
-      <c r="C6" s="402" t="n"/>
-      <c r="D6" s="402" t="inlineStr">
+      <c r="A6" s="574" t="n"/>
+      <c r="B6" s="544" t="n"/>
+      <c r="C6" s="544" t="n"/>
+      <c r="D6" s="544" t="inlineStr">
         <is>
           <t>Setup Technician</t>
         </is>
       </c>
-      <c r="E6" s="402" t="n"/>
-      <c r="F6" s="402" t="n"/>
-      <c r="G6" s="402" t="n"/>
-      <c r="H6" s="402" t="n"/>
-      <c r="I6" s="402" t="n"/>
-      <c r="J6" s="402" t="n"/>
-      <c r="K6" s="402" t="n"/>
-      <c r="L6" s="402" t="n"/>
-      <c r="M6" s="402" t="n"/>
-      <c r="N6" s="402" t="n"/>
-      <c r="O6" s="402" t="n"/>
-      <c r="P6" s="402" t="n"/>
-      <c r="Q6" s="402" t="n"/>
-      <c r="R6" s="402" t="n"/>
-      <c r="S6" s="402" t="n"/>
-      <c r="T6" s="402" t="n"/>
-      <c r="U6" s="402" t="n"/>
-      <c r="V6" s="402" t="n"/>
-      <c r="W6" s="402" t="n"/>
-      <c r="X6" s="402" t="n"/>
-      <c r="Y6" s="402" t="n"/>
-      <c r="Z6" s="402" t="n"/>
-      <c r="AA6" s="402" t="n"/>
-      <c r="AB6" s="402" t="n"/>
-      <c r="AC6" s="402" t="n"/>
-      <c r="AD6" s="402" t="n"/>
-      <c r="AE6" s="402" t="n"/>
-      <c r="AF6" s="402" t="n"/>
-      <c r="AG6" s="402" t="n"/>
-      <c r="AH6" s="402" t="n"/>
-      <c r="AI6" s="402" t="n"/>
-      <c r="AJ6" s="402" t="n"/>
-      <c r="AK6" s="402" t="n"/>
-      <c r="AL6" s="402" t="n"/>
-      <c r="AM6" s="402" t="n"/>
-      <c r="AN6" s="402" t="n"/>
+      <c r="E6" s="544" t="n"/>
+      <c r="F6" s="544" t="n"/>
+      <c r="G6" s="544" t="n"/>
+      <c r="H6" s="544" t="n"/>
+      <c r="I6" s="544" t="n"/>
+      <c r="J6" s="544" t="n"/>
+      <c r="K6" s="544" t="n"/>
+      <c r="L6" s="544" t="n"/>
+      <c r="M6" s="544" t="n"/>
+      <c r="N6" s="544" t="n"/>
+      <c r="O6" s="544" t="n"/>
+      <c r="P6" s="544" t="n"/>
+      <c r="Q6" s="544" t="n"/>
+      <c r="R6" s="544" t="n"/>
+      <c r="S6" s="544" t="n"/>
+      <c r="T6" s="544" t="n"/>
+      <c r="U6" s="544" t="n"/>
+      <c r="V6" s="544" t="n"/>
+      <c r="W6" s="544" t="n"/>
+      <c r="X6" s="544" t="n"/>
+      <c r="Y6" s="544" t="n"/>
+      <c r="Z6" s="544" t="n"/>
+      <c r="AA6" s="544" t="n"/>
+      <c r="AB6" s="544" t="n"/>
+      <c r="AC6" s="544" t="n"/>
+      <c r="AD6" s="544" t="n"/>
+      <c r="AE6" s="544" t="n"/>
+      <c r="AF6" s="544" t="n"/>
+      <c r="AG6" s="544" t="n"/>
+      <c r="AH6" s="544" t="n"/>
+      <c r="AI6" s="544" t="n"/>
+      <c r="AJ6" s="544" t="n"/>
+      <c r="AK6" s="544" t="n"/>
+      <c r="AL6" s="544" t="n"/>
+      <c r="AM6" s="544" t="n"/>
+      <c r="AN6" s="547" t="n"/>
     </row>
     <row r="7" hidden="1"/>
     <row r="8" hidden="1"/>
@@ -9696,627 +10552,630 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="440" t="n"/>
-      <c r="B1" s="490" t="n"/>
-      <c r="C1" s="441" t="inlineStr">
+      <c r="A1" s="577" t="n"/>
+      <c r="B1" s="493" t="n"/>
+      <c r="C1" s="578" t="inlineStr">
         <is>
           <t>RISKS / ACTIONS REGISTER</t>
         </is>
       </c>
-      <c r="D1" s="483" t="n"/>
-      <c r="E1" s="483" t="n"/>
-      <c r="F1" s="483" t="n"/>
-      <c r="G1" s="490" t="n"/>
-      <c r="H1" s="442" t="inlineStr">
+      <c r="D1" s="493" t="n"/>
+      <c r="E1" s="493" t="n"/>
+      <c r="F1" s="493" t="n"/>
+      <c r="G1" s="493" t="n"/>
+      <c r="H1" s="579" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="I1" s="443" t="inlineStr">
+      <c r="I1" s="495" t="inlineStr">
         <is>
           <t>FRM-209</t>
         </is>
       </c>
-      <c r="J1" s="402" t="n"/>
-      <c r="K1" s="402" t="n"/>
-      <c r="L1" s="402" t="n"/>
-      <c r="M1" s="402" t="n"/>
-      <c r="N1" s="402" t="n"/>
-      <c r="O1" s="402" t="n"/>
-      <c r="P1" s="402" t="n"/>
-      <c r="Q1" s="402" t="n"/>
-      <c r="R1" s="402" t="n"/>
-      <c r="S1" s="402" t="n"/>
-      <c r="T1" s="402" t="n"/>
-      <c r="U1" s="402" t="n"/>
-      <c r="V1" s="402" t="n"/>
-      <c r="W1" s="402" t="n"/>
-      <c r="X1" s="402" t="n"/>
-      <c r="Y1" s="402" t="n"/>
-      <c r="Z1" s="402" t="n"/>
-      <c r="AA1" s="402" t="n"/>
-      <c r="AB1" s="402" t="n"/>
-      <c r="AC1" s="402" t="n"/>
-      <c r="AD1" s="402" t="n"/>
-      <c r="AE1" s="402" t="n"/>
-      <c r="AF1" s="402" t="n"/>
-      <c r="AG1" s="402" t="n"/>
-      <c r="AH1" s="402" t="n"/>
-      <c r="AI1" s="402" t="n"/>
-      <c r="AJ1" s="402" t="n"/>
-      <c r="AK1" s="402" t="n"/>
-      <c r="AL1" s="402" t="n"/>
-      <c r="AM1" s="402" t="n"/>
-      <c r="AN1" s="402" t="n"/>
+      <c r="J1" s="496" t="n"/>
+      <c r="K1" s="496" t="n"/>
+      <c r="L1" s="496" t="n"/>
+      <c r="M1" s="496" t="n"/>
+      <c r="N1" s="496" t="n"/>
+      <c r="O1" s="496" t="n"/>
+      <c r="P1" s="496" t="n"/>
+      <c r="Q1" s="496" t="n"/>
+      <c r="R1" s="496" t="n"/>
+      <c r="S1" s="496" t="n"/>
+      <c r="T1" s="496" t="n"/>
+      <c r="U1" s="496" t="n"/>
+      <c r="V1" s="496" t="n"/>
+      <c r="W1" s="496" t="n"/>
+      <c r="X1" s="496" t="n"/>
+      <c r="Y1" s="496" t="n"/>
+      <c r="Z1" s="496" t="n"/>
+      <c r="AA1" s="496" t="n"/>
+      <c r="AB1" s="496" t="n"/>
+      <c r="AC1" s="496" t="n"/>
+      <c r="AD1" s="497" t="n"/>
+      <c r="AE1" s="498" t="n"/>
+      <c r="AF1" s="499" t="n"/>
+      <c r="AG1" s="499" t="n"/>
+      <c r="AH1" s="500" t="n"/>
+      <c r="AI1" s="501" t="n"/>
+      <c r="AJ1" s="502" t="n"/>
+      <c r="AK1" s="502" t="n"/>
+      <c r="AL1" s="502" t="n"/>
+      <c r="AM1" s="502" t="n"/>
+      <c r="AN1" s="503" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="486" t="n"/>
-      <c r="B2" s="491" t="n"/>
-      <c r="C2" s="486" t="n"/>
-      <c r="G2" s="491" t="n"/>
-      <c r="H2" s="442" t="inlineStr">
+      <c r="A2" s="504" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="580" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="I2" s="443" t="inlineStr">
+      <c r="I2" s="506" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="J2" s="402" t="n"/>
-      <c r="K2" s="402" t="n"/>
-      <c r="L2" s="402" t="n"/>
-      <c r="M2" s="402" t="n"/>
-      <c r="N2" s="402" t="n"/>
-      <c r="O2" s="402" t="n"/>
-      <c r="P2" s="402" t="n"/>
-      <c r="Q2" s="402" t="n"/>
-      <c r="R2" s="402" t="n"/>
-      <c r="S2" s="402" t="n"/>
-      <c r="T2" s="402" t="n"/>
-      <c r="U2" s="402" t="n"/>
-      <c r="V2" s="402" t="n"/>
-      <c r="W2" s="402" t="n"/>
-      <c r="X2" s="402" t="n"/>
-      <c r="Y2" s="402" t="n"/>
-      <c r="Z2" s="402" t="n"/>
-      <c r="AA2" s="402" t="n"/>
-      <c r="AB2" s="402" t="n"/>
-      <c r="AC2" s="402" t="n"/>
-      <c r="AD2" s="402" t="n"/>
-      <c r="AE2" s="402" t="n"/>
-      <c r="AF2" s="402" t="n"/>
-      <c r="AG2" s="402" t="n"/>
-      <c r="AH2" s="402" t="n"/>
-      <c r="AI2" s="402" t="n"/>
-      <c r="AJ2" s="402" t="n"/>
-      <c r="AK2" s="402" t="n"/>
-      <c r="AL2" s="402" t="n"/>
-      <c r="AM2" s="402" t="n"/>
-      <c r="AN2" s="402" t="n"/>
+      <c r="J2" s="507" t="n"/>
+      <c r="K2" s="507" t="n"/>
+      <c r="L2" s="507" t="n"/>
+      <c r="M2" s="507" t="n"/>
+      <c r="N2" s="507" t="n"/>
+      <c r="O2" s="507" t="n"/>
+      <c r="P2" s="507" t="n"/>
+      <c r="Q2" s="507" t="n"/>
+      <c r="R2" s="507" t="n"/>
+      <c r="S2" s="507" t="n"/>
+      <c r="T2" s="507" t="n"/>
+      <c r="U2" s="507" t="n"/>
+      <c r="V2" s="507" t="n"/>
+      <c r="W2" s="507" t="n"/>
+      <c r="X2" s="507" t="n"/>
+      <c r="Y2" s="507" t="n"/>
+      <c r="Z2" s="507" t="n"/>
+      <c r="AA2" s="507" t="n"/>
+      <c r="AB2" s="507" t="n"/>
+      <c r="AC2" s="507" t="n"/>
+      <c r="AD2" s="508" t="n"/>
+      <c r="AE2" s="509" t="n"/>
+      <c r="AF2" s="510" t="n"/>
+      <c r="AG2" s="510" t="n"/>
+      <c r="AH2" s="511" t="n"/>
+      <c r="AI2" s="512" t="n"/>
+      <c r="AJ2" s="513" t="n"/>
+      <c r="AK2" s="513" t="n"/>
+      <c r="AL2" s="513" t="n"/>
+      <c r="AM2" s="513" t="n"/>
+      <c r="AN2" s="514" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="486" t="n"/>
-      <c r="B3" s="491" t="n"/>
-      <c r="C3" s="489" t="n"/>
-      <c r="D3" s="487" t="n"/>
-      <c r="E3" s="487" t="n"/>
-      <c r="F3" s="487" t="n"/>
-      <c r="G3" s="488" t="n"/>
-      <c r="H3" s="442" t="inlineStr">
+      <c r="A3" s="504" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="580" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="I3" s="443" t="inlineStr">
+      <c r="I3" s="506" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J3" s="402" t="n"/>
-      <c r="K3" s="402" t="n"/>
-      <c r="L3" s="402" t="n"/>
-      <c r="M3" s="402" t="n"/>
-      <c r="N3" s="402" t="n"/>
-      <c r="O3" s="402" t="n"/>
-      <c r="P3" s="402" t="n"/>
-      <c r="Q3" s="402" t="n"/>
-      <c r="R3" s="402" t="n"/>
-      <c r="S3" s="402" t="n"/>
-      <c r="T3" s="402" t="n"/>
-      <c r="U3" s="402" t="n"/>
-      <c r="V3" s="402" t="n"/>
-      <c r="W3" s="402" t="n"/>
-      <c r="X3" s="402" t="n"/>
-      <c r="Y3" s="402" t="n"/>
-      <c r="Z3" s="402" t="n"/>
-      <c r="AA3" s="402" t="n"/>
-      <c r="AB3" s="402" t="n"/>
-      <c r="AC3" s="402" t="n"/>
-      <c r="AD3" s="402" t="n"/>
-      <c r="AE3" s="402" t="n"/>
-      <c r="AF3" s="402" t="n"/>
-      <c r="AG3" s="402" t="n"/>
-      <c r="AH3" s="402" t="n"/>
-      <c r="AI3" s="402" t="n"/>
-      <c r="AJ3" s="402" t="n"/>
-      <c r="AK3" s="402" t="n"/>
-      <c r="AL3" s="402" t="n"/>
-      <c r="AM3" s="402" t="n"/>
-      <c r="AN3" s="402" t="n"/>
+      <c r="J3" s="507" t="n"/>
+      <c r="K3" s="507" t="n"/>
+      <c r="L3" s="507" t="n"/>
+      <c r="M3" s="507" t="n"/>
+      <c r="N3" s="507" t="n"/>
+      <c r="O3" s="507" t="n"/>
+      <c r="P3" s="507" t="n"/>
+      <c r="Q3" s="507" t="n"/>
+      <c r="R3" s="507" t="n"/>
+      <c r="S3" s="507" t="n"/>
+      <c r="T3" s="507" t="n"/>
+      <c r="U3" s="507" t="n"/>
+      <c r="V3" s="507" t="n"/>
+      <c r="W3" s="507" t="n"/>
+      <c r="X3" s="507" t="n"/>
+      <c r="Y3" s="507" t="n"/>
+      <c r="Z3" s="507" t="n"/>
+      <c r="AA3" s="507" t="n"/>
+      <c r="AB3" s="507" t="n"/>
+      <c r="AC3" s="507" t="n"/>
+      <c r="AD3" s="508" t="n"/>
+      <c r="AE3" s="509" t="n"/>
+      <c r="AF3" s="510" t="n"/>
+      <c r="AG3" s="510" t="n"/>
+      <c r="AH3" s="511" t="n"/>
+      <c r="AI3" s="512" t="n"/>
+      <c r="AJ3" s="513" t="n"/>
+      <c r="AK3" s="513" t="n"/>
+      <c r="AL3" s="513" t="n"/>
+      <c r="AM3" s="513" t="n"/>
+      <c r="AN3" s="514" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="486" t="n"/>
-      <c r="B4" s="491" t="n"/>
-      <c r="C4" s="445" t="inlineStr">
+      <c r="A4" s="504" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="581" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="484" t="n"/>
-      <c r="E4" s="484" t="n"/>
-      <c r="F4" s="484" t="n"/>
-      <c r="G4" s="485" t="n"/>
-      <c r="H4" s="442" t="inlineStr">
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="580" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="I4" s="443" t="inlineStr"/>
-      <c r="J4" s="402" t="n"/>
-      <c r="K4" s="402" t="n"/>
-      <c r="L4" s="402" t="n"/>
-      <c r="M4" s="402" t="n"/>
-      <c r="N4" s="402" t="n"/>
-      <c r="O4" s="402" t="n"/>
-      <c r="P4" s="402" t="n"/>
-      <c r="Q4" s="402" t="n"/>
-      <c r="R4" s="402" t="n"/>
-      <c r="S4" s="402" t="n"/>
-      <c r="T4" s="402" t="n"/>
-      <c r="U4" s="402" t="n"/>
-      <c r="V4" s="402" t="n"/>
-      <c r="W4" s="402" t="n"/>
-      <c r="X4" s="402" t="n"/>
-      <c r="Y4" s="402" t="n"/>
-      <c r="Z4" s="402" t="n"/>
-      <c r="AA4" s="402" t="n"/>
-      <c r="AB4" s="402" t="n"/>
-      <c r="AC4" s="402" t="n"/>
-      <c r="AD4" s="402" t="n"/>
-      <c r="AE4" s="402" t="n"/>
-      <c r="AF4" s="402" t="n"/>
-      <c r="AG4" s="402" t="n"/>
-      <c r="AH4" s="402" t="n"/>
-      <c r="AI4" s="402" t="n"/>
-      <c r="AJ4" s="402" t="n"/>
-      <c r="AK4" s="402" t="n"/>
-      <c r="AL4" s="402" t="n"/>
-      <c r="AM4" s="402" t="n"/>
-      <c r="AN4" s="402" t="n"/>
+      <c r="I4" s="515" t="inlineStr"/>
+      <c r="J4" s="516" t="n"/>
+      <c r="K4" s="516" t="n"/>
+      <c r="L4" s="516" t="n"/>
+      <c r="M4" s="516" t="n"/>
+      <c r="N4" s="516" t="n"/>
+      <c r="O4" s="516" t="n"/>
+      <c r="P4" s="516" t="n"/>
+      <c r="Q4" s="516" t="n"/>
+      <c r="R4" s="516" t="n"/>
+      <c r="S4" s="516" t="n"/>
+      <c r="T4" s="516" t="n"/>
+      <c r="U4" s="516" t="n"/>
+      <c r="V4" s="516" t="n"/>
+      <c r="W4" s="516" t="n"/>
+      <c r="X4" s="516" t="n"/>
+      <c r="Y4" s="516" t="n"/>
+      <c r="Z4" s="516" t="n"/>
+      <c r="AA4" s="516" t="n"/>
+      <c r="AB4" s="516" t="n"/>
+      <c r="AC4" s="516" t="n"/>
+      <c r="AD4" s="517" t="n"/>
+      <c r="AE4" s="509" t="n"/>
+      <c r="AF4" s="510" t="n"/>
+      <c r="AG4" s="510" t="n"/>
+      <c r="AH4" s="511" t="n"/>
+      <c r="AI4" s="512" t="n"/>
+      <c r="AJ4" s="513" t="n"/>
+      <c r="AK4" s="513" t="n"/>
+      <c r="AL4" s="513" t="n"/>
+      <c r="AM4" s="513" t="n"/>
+      <c r="AN4" s="514" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="489" t="n"/>
-      <c r="B5" s="488" t="n"/>
-      <c r="C5" s="446" t="inlineStr">
+      <c r="A5" s="518" t="n"/>
+      <c r="B5" s="519" t="n"/>
+      <c r="C5" s="582" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="484" t="n"/>
-      <c r="E5" s="484" t="n"/>
-      <c r="F5" s="484" t="n"/>
-      <c r="G5" s="485" t="n"/>
-      <c r="H5" s="447" t="inlineStr">
+      <c r="D5" s="519" t="n"/>
+      <c r="E5" s="519" t="n"/>
+      <c r="F5" s="519" t="n"/>
+      <c r="G5" s="519" t="n"/>
+      <c r="H5" s="583" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="I5" s="448" t="inlineStr"/>
-      <c r="J5" s="402" t="n"/>
-      <c r="K5" s="402" t="n"/>
-      <c r="L5" s="402" t="n"/>
-      <c r="M5" s="402" t="n"/>
-      <c r="N5" s="402" t="n"/>
-      <c r="O5" s="402" t="n"/>
-      <c r="P5" s="402" t="n"/>
-      <c r="Q5" s="402" t="n"/>
-      <c r="R5" s="402" t="n"/>
-      <c r="S5" s="402" t="n"/>
-      <c r="T5" s="402" t="n"/>
-      <c r="U5" s="402" t="n"/>
-      <c r="V5" s="402" t="n"/>
-      <c r="W5" s="402" t="n"/>
-      <c r="X5" s="402" t="n"/>
-      <c r="Y5" s="402" t="n"/>
-      <c r="Z5" s="402" t="n"/>
-      <c r="AA5" s="402" t="n"/>
-      <c r="AB5" s="402" t="n"/>
-      <c r="AC5" s="402" t="n"/>
-      <c r="AD5" s="402" t="n"/>
-      <c r="AE5" s="402" t="n"/>
-      <c r="AF5" s="402" t="n"/>
-      <c r="AG5" s="402" t="n"/>
-      <c r="AH5" s="402" t="n"/>
-      <c r="AI5" s="402" t="n"/>
-      <c r="AJ5" s="402" t="n"/>
-      <c r="AK5" s="402" t="n"/>
-      <c r="AL5" s="402" t="n"/>
-      <c r="AM5" s="402" t="n"/>
-      <c r="AN5" s="402" t="n"/>
+      <c r="I5" s="521" t="inlineStr"/>
+      <c r="J5" s="522" t="n"/>
+      <c r="K5" s="522" t="n"/>
+      <c r="L5" s="522" t="n"/>
+      <c r="M5" s="522" t="n"/>
+      <c r="N5" s="522" t="n"/>
+      <c r="O5" s="522" t="n"/>
+      <c r="P5" s="522" t="n"/>
+      <c r="Q5" s="522" t="n"/>
+      <c r="R5" s="522" t="n"/>
+      <c r="S5" s="522" t="n"/>
+      <c r="T5" s="522" t="n"/>
+      <c r="U5" s="522" t="n"/>
+      <c r="V5" s="522" t="n"/>
+      <c r="W5" s="522" t="n"/>
+      <c r="X5" s="522" t="n"/>
+      <c r="Y5" s="522" t="n"/>
+      <c r="Z5" s="522" t="n"/>
+      <c r="AA5" s="522" t="n"/>
+      <c r="AB5" s="522" t="n"/>
+      <c r="AC5" s="522" t="n"/>
+      <c r="AD5" s="523" t="n"/>
+      <c r="AE5" s="524" t="n"/>
+      <c r="AF5" s="525" t="n"/>
+      <c r="AG5" s="525" t="n"/>
+      <c r="AH5" s="526" t="n"/>
+      <c r="AI5" s="527" t="n"/>
+      <c r="AJ5" s="528" t="n"/>
+      <c r="AK5" s="528" t="n"/>
+      <c r="AL5" s="528" t="n"/>
+      <c r="AM5" s="528" t="n"/>
+      <c r="AN5" s="529" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="449" t="n"/>
-      <c r="B6" s="482" t="n"/>
-      <c r="C6" s="482" t="n"/>
-      <c r="D6" s="482" t="n"/>
-      <c r="E6" s="482" t="n"/>
-      <c r="F6" s="482" t="n"/>
-      <c r="G6" s="482" t="n"/>
-      <c r="H6" s="482" t="n"/>
-      <c r="I6" s="482" t="n"/>
-      <c r="J6" s="410" t="n"/>
-      <c r="K6" s="410" t="n"/>
-      <c r="L6" s="410" t="n"/>
-      <c r="M6" s="410" t="n"/>
-      <c r="N6" s="410" t="n"/>
-      <c r="O6" s="410" t="n"/>
-      <c r="P6" s="410" t="n"/>
-      <c r="Q6" s="410" t="n"/>
-      <c r="R6" s="410" t="n"/>
-      <c r="S6" s="410" t="n"/>
-      <c r="T6" s="410" t="n"/>
-      <c r="U6" s="410" t="n"/>
-      <c r="V6" s="410" t="n"/>
-      <c r="W6" s="410" t="n"/>
-      <c r="X6" s="410" t="n"/>
-      <c r="Y6" s="410" t="n"/>
-      <c r="Z6" s="410" t="n"/>
-      <c r="AA6" s="410" t="n"/>
-      <c r="AB6" s="410" t="n"/>
-      <c r="AC6" s="410" t="n"/>
-      <c r="AD6" s="410" t="n"/>
-      <c r="AE6" s="410" t="n"/>
-      <c r="AF6" s="410" t="n"/>
-      <c r="AG6" s="410" t="n"/>
-      <c r="AH6" s="410" t="n"/>
-      <c r="AI6" s="410" t="n"/>
-      <c r="AJ6" s="410" t="n"/>
-      <c r="AK6" s="410" t="n"/>
-      <c r="AL6" s="410" t="n"/>
-      <c r="AM6" s="410" t="n"/>
-      <c r="AN6" s="410" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="584" t="n"/>
+      <c r="B6" s="530" t="n"/>
+      <c r="C6" s="530" t="n"/>
+      <c r="D6" s="530" t="n"/>
+      <c r="E6" s="530" t="n"/>
+      <c r="F6" s="530" t="n"/>
+      <c r="G6" s="530" t="n"/>
+      <c r="H6" s="530" t="n"/>
+      <c r="I6" s="530" t="n"/>
+      <c r="J6" s="530" t="n"/>
+      <c r="K6" s="530" t="n"/>
+      <c r="L6" s="530" t="n"/>
+      <c r="M6" s="530" t="n"/>
+      <c r="N6" s="530" t="n"/>
+      <c r="O6" s="530" t="n"/>
+      <c r="P6" s="530" t="n"/>
+      <c r="Q6" s="530" t="n"/>
+      <c r="R6" s="530" t="n"/>
+      <c r="S6" s="530" t="n"/>
+      <c r="T6" s="530" t="n"/>
+      <c r="U6" s="530" t="n"/>
+      <c r="V6" s="530" t="n"/>
+      <c r="W6" s="530" t="n"/>
+      <c r="X6" s="530" t="n"/>
+      <c r="Y6" s="530" t="n"/>
+      <c r="Z6" s="530" t="n"/>
+      <c r="AA6" s="530" t="n"/>
+      <c r="AB6" s="530" t="n"/>
+      <c r="AC6" s="530" t="n"/>
+      <c r="AD6" s="530" t="n"/>
+      <c r="AE6" s="530" t="n"/>
+      <c r="AF6" s="530" t="n"/>
+      <c r="AG6" s="530" t="n"/>
+      <c r="AH6" s="530" t="n"/>
+      <c r="AI6" s="530" t="n"/>
+      <c r="AJ6" s="530" t="n"/>
+      <c r="AK6" s="530" t="n"/>
+      <c r="AL6" s="530" t="n"/>
+      <c r="AM6" s="530" t="n"/>
+      <c r="AN6" s="530" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="450" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="531" t="inlineStr">
         <is>
           <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
         </is>
       </c>
-      <c r="B7" s="484" t="n"/>
-      <c r="C7" s="484" t="n"/>
-      <c r="D7" s="484" t="n"/>
-      <c r="E7" s="484" t="n"/>
-      <c r="F7" s="484" t="n"/>
-      <c r="G7" s="484" t="n"/>
-      <c r="H7" s="484" t="n"/>
-      <c r="I7" s="485" t="n"/>
-      <c r="J7" s="402" t="n"/>
-      <c r="K7" s="402" t="n"/>
-      <c r="L7" s="402" t="n"/>
-      <c r="M7" s="402" t="n"/>
-      <c r="N7" s="402" t="n"/>
-      <c r="O7" s="402" t="n"/>
-      <c r="P7" s="402" t="n"/>
-      <c r="Q7" s="402" t="n"/>
-      <c r="R7" s="402" t="n"/>
-      <c r="S7" s="402" t="n"/>
-      <c r="T7" s="402" t="n"/>
-      <c r="U7" s="402" t="n"/>
-      <c r="V7" s="402" t="n"/>
-      <c r="W7" s="402" t="n"/>
-      <c r="X7" s="402" t="n"/>
-      <c r="Y7" s="402" t="n"/>
-      <c r="Z7" s="402" t="n"/>
-      <c r="AA7" s="402" t="n"/>
-      <c r="AB7" s="402" t="n"/>
-      <c r="AC7" s="402" t="n"/>
-      <c r="AD7" s="402" t="n"/>
-      <c r="AE7" s="402" t="n"/>
-      <c r="AF7" s="402" t="n"/>
-      <c r="AG7" s="402" t="n"/>
-      <c r="AH7" s="402" t="n"/>
-      <c r="AI7" s="402" t="n"/>
-      <c r="AJ7" s="402" t="n"/>
-      <c r="AK7" s="402" t="n"/>
-      <c r="AL7" s="402" t="n"/>
-      <c r="AM7" s="402" t="n"/>
-      <c r="AN7" s="402" t="n"/>
+      <c r="B7" s="532" t="n"/>
+      <c r="C7" s="532" t="n"/>
+      <c r="D7" s="532" t="n"/>
+      <c r="E7" s="532" t="n"/>
+      <c r="F7" s="532" t="n"/>
+      <c r="G7" s="532" t="n"/>
+      <c r="H7" s="532" t="n"/>
+      <c r="I7" s="532" t="n"/>
+      <c r="J7" s="532" t="n"/>
+      <c r="K7" s="532" t="n"/>
+      <c r="L7" s="532" t="n"/>
+      <c r="M7" s="532" t="n"/>
+      <c r="N7" s="532" t="n"/>
+      <c r="O7" s="532" t="n"/>
+      <c r="P7" s="532" t="n"/>
+      <c r="Q7" s="532" t="n"/>
+      <c r="R7" s="532" t="n"/>
+      <c r="S7" s="532" t="n"/>
+      <c r="T7" s="532" t="n"/>
+      <c r="U7" s="532" t="n"/>
+      <c r="V7" s="532" t="n"/>
+      <c r="W7" s="532" t="n"/>
+      <c r="X7" s="532" t="n"/>
+      <c r="Y7" s="532" t="n"/>
+      <c r="Z7" s="532" t="n"/>
+      <c r="AA7" s="532" t="n"/>
+      <c r="AB7" s="532" t="n"/>
+      <c r="AC7" s="532" t="n"/>
+      <c r="AD7" s="532" t="n"/>
+      <c r="AE7" s="532" t="n"/>
+      <c r="AF7" s="532" t="n"/>
+      <c r="AG7" s="532" t="n"/>
+      <c r="AH7" s="532" t="n"/>
+      <c r="AI7" s="532" t="n"/>
+      <c r="AJ7" s="532" t="n"/>
+      <c r="AK7" s="532" t="n"/>
+      <c r="AL7" s="532" t="n"/>
+      <c r="AM7" s="532" t="n"/>
+      <c r="AN7" s="533" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="447" t="inlineStr">
+      <c r="A8" s="585" t="inlineStr">
         <is>
           <t>Parent Form</t>
         </is>
       </c>
-      <c r="B8" s="474" t="n"/>
-      <c r="C8" s="448" t="inlineStr">
+      <c r="B8" s="535" t="n"/>
+      <c r="C8" s="586" t="inlineStr">
         <is>
           <t>FRM-209 · HIGH-RISK JOB READINESS REVIEW</t>
         </is>
       </c>
-      <c r="D8" s="473" t="n"/>
-      <c r="E8" s="474" t="n"/>
-      <c r="F8" s="447" t="inlineStr">
+      <c r="D8" s="535" t="n"/>
+      <c r="E8" s="535" t="n"/>
+      <c r="F8" s="587" t="inlineStr">
         <is>
           <t>Support Tab</t>
         </is>
       </c>
-      <c r="G8" s="474" t="n"/>
-      <c r="H8" s="448" t="inlineStr">
+      <c r="G8" s="535" t="n"/>
+      <c r="H8" s="586" t="inlineStr">
         <is>
           <t>RISKS_ACTIONS</t>
         </is>
       </c>
-      <c r="I8" s="474" t="n"/>
-      <c r="J8" s="436" t="n"/>
-      <c r="K8" s="436" t="n"/>
-      <c r="L8" s="436" t="n"/>
-      <c r="M8" s="436" t="n"/>
-      <c r="N8" s="436" t="n"/>
-      <c r="O8" s="436" t="n"/>
-      <c r="P8" s="436" t="n"/>
-      <c r="Q8" s="436" t="n"/>
-      <c r="R8" s="436" t="n"/>
-      <c r="S8" s="436" t="n"/>
-      <c r="T8" s="436" t="n"/>
-      <c r="U8" s="436" t="n"/>
-      <c r="V8" s="436" t="n"/>
-      <c r="W8" s="436" t="n"/>
-      <c r="X8" s="436" t="n"/>
-      <c r="Y8" s="436" t="n"/>
-      <c r="Z8" s="436" t="n"/>
-      <c r="AA8" s="436" t="n"/>
-      <c r="AB8" s="436" t="n"/>
-      <c r="AC8" s="436" t="n"/>
-      <c r="AD8" s="436" t="n"/>
-      <c r="AE8" s="436" t="n"/>
-      <c r="AF8" s="436" t="n"/>
-      <c r="AG8" s="436" t="n"/>
-      <c r="AH8" s="436" t="n"/>
-      <c r="AI8" s="436" t="n"/>
-      <c r="AJ8" s="436" t="n"/>
-      <c r="AK8" s="436" t="n"/>
-      <c r="AL8" s="436" t="n"/>
-      <c r="AM8" s="436" t="n"/>
-      <c r="AN8" s="436" t="n"/>
+      <c r="I8" s="535" t="n"/>
+      <c r="J8" s="588" t="n"/>
+      <c r="K8" s="589" t="n"/>
+      <c r="L8" s="589" t="n"/>
+      <c r="M8" s="589" t="n"/>
+      <c r="N8" s="589" t="n"/>
+      <c r="O8" s="589" t="n"/>
+      <c r="P8" s="589" t="n"/>
+      <c r="Q8" s="589" t="n"/>
+      <c r="R8" s="589" t="n"/>
+      <c r="S8" s="589" t="n"/>
+      <c r="T8" s="589" t="n"/>
+      <c r="U8" s="589" t="n"/>
+      <c r="V8" s="589" t="n"/>
+      <c r="W8" s="589" t="n"/>
+      <c r="X8" s="589" t="n"/>
+      <c r="Y8" s="589" t="n"/>
+      <c r="Z8" s="589" t="n"/>
+      <c r="AA8" s="589" t="n"/>
+      <c r="AB8" s="589" t="n"/>
+      <c r="AC8" s="589" t="n"/>
+      <c r="AD8" s="589" t="n"/>
+      <c r="AE8" s="589" t="n"/>
+      <c r="AF8" s="589" t="n"/>
+      <c r="AG8" s="589" t="n"/>
+      <c r="AH8" s="589" t="n"/>
+      <c r="AI8" s="589" t="n"/>
+      <c r="AJ8" s="589" t="n"/>
+      <c r="AK8" s="589" t="n"/>
+      <c r="AL8" s="589" t="n"/>
+      <c r="AM8" s="589" t="n"/>
+      <c r="AN8" s="590" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="447" t="inlineStr">
+      <c r="A9" s="591" t="inlineStr">
         <is>
           <t>Tab Purpose</t>
         </is>
       </c>
-      <c r="B9" s="474" t="n"/>
-      <c r="C9" s="448" t="inlineStr">
+      <c r="B9" s="398" t="n"/>
+      <c r="C9" s="592" t="inlineStr">
         <is>
           <t>One line per material, capacity, quality or customer-risk condition.</t>
         </is>
       </c>
-      <c r="D9" s="473" t="n"/>
-      <c r="E9" s="474" t="n"/>
-      <c r="F9" s="447" t="inlineStr">
+      <c r="D9" s="398" t="n"/>
+      <c r="E9" s="398" t="n"/>
+      <c r="F9" s="593" t="inlineStr">
         <is>
           <t>Working Owner</t>
         </is>
       </c>
-      <c r="G9" s="474" t="n"/>
-      <c r="H9" s="448" t="inlineStr"/>
-      <c r="I9" s="474" t="n"/>
-      <c r="J9" s="436" t="n"/>
-      <c r="K9" s="436" t="n"/>
-      <c r="L9" s="436" t="n"/>
-      <c r="M9" s="436" t="n"/>
-      <c r="N9" s="436" t="n"/>
-      <c r="O9" s="436" t="n"/>
-      <c r="P9" s="436" t="n"/>
-      <c r="Q9" s="436" t="n"/>
-      <c r="R9" s="436" t="n"/>
-      <c r="S9" s="436" t="n"/>
-      <c r="T9" s="436" t="n"/>
-      <c r="U9" s="436" t="n"/>
-      <c r="V9" s="436" t="n"/>
-      <c r="W9" s="436" t="n"/>
-      <c r="X9" s="436" t="n"/>
-      <c r="Y9" s="436" t="n"/>
-      <c r="Z9" s="436" t="n"/>
-      <c r="AA9" s="436" t="n"/>
-      <c r="AB9" s="436" t="n"/>
-      <c r="AC9" s="436" t="n"/>
-      <c r="AD9" s="436" t="n"/>
-      <c r="AE9" s="436" t="n"/>
-      <c r="AF9" s="436" t="n"/>
-      <c r="AG9" s="436" t="n"/>
-      <c r="AH9" s="436" t="n"/>
-      <c r="AI9" s="436" t="n"/>
-      <c r="AJ9" s="436" t="n"/>
-      <c r="AK9" s="436" t="n"/>
-      <c r="AL9" s="436" t="n"/>
-      <c r="AM9" s="436" t="n"/>
-      <c r="AN9" s="436" t="n"/>
+      <c r="G9" s="398" t="n"/>
+      <c r="H9" s="592" t="inlineStr"/>
+      <c r="I9" s="398" t="n"/>
+      <c r="J9" s="594" t="n"/>
+      <c r="K9" s="413" t="n"/>
+      <c r="L9" s="413" t="n"/>
+      <c r="M9" s="413" t="n"/>
+      <c r="N9" s="413" t="n"/>
+      <c r="O9" s="413" t="n"/>
+      <c r="P9" s="413" t="n"/>
+      <c r="Q9" s="413" t="n"/>
+      <c r="R9" s="413" t="n"/>
+      <c r="S9" s="413" t="n"/>
+      <c r="T9" s="413" t="n"/>
+      <c r="U9" s="413" t="n"/>
+      <c r="V9" s="413" t="n"/>
+      <c r="W9" s="413" t="n"/>
+      <c r="X9" s="413" t="n"/>
+      <c r="Y9" s="413" t="n"/>
+      <c r="Z9" s="413" t="n"/>
+      <c r="AA9" s="413" t="n"/>
+      <c r="AB9" s="413" t="n"/>
+      <c r="AC9" s="413" t="n"/>
+      <c r="AD9" s="413" t="n"/>
+      <c r="AE9" s="413" t="n"/>
+      <c r="AF9" s="413" t="n"/>
+      <c r="AG9" s="413" t="n"/>
+      <c r="AH9" s="413" t="n"/>
+      <c r="AI9" s="413" t="n"/>
+      <c r="AJ9" s="413" t="n"/>
+      <c r="AK9" s="413" t="n"/>
+      <c r="AL9" s="413" t="n"/>
+      <c r="AM9" s="413" t="n"/>
+      <c r="AN9" s="595" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="447" t="inlineStr">
+      <c r="A10" s="591" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B10" s="474" t="n"/>
-      <c r="C10" s="448" t="inlineStr">
+      <c r="B10" s="398" t="n"/>
+      <c r="C10" s="592" t="inlineStr">
         <is>
           <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
         </is>
       </c>
-      <c r="D10" s="473" t="n"/>
-      <c r="E10" s="474" t="n"/>
-      <c r="F10" s="447" t="inlineStr">
+      <c r="D10" s="398" t="n"/>
+      <c r="E10" s="398" t="n"/>
+      <c r="F10" s="593" t="inlineStr">
         <is>
           <t>Reviewed By</t>
         </is>
       </c>
-      <c r="G10" s="474" t="n"/>
-      <c r="H10" s="448" t="inlineStr"/>
-      <c r="I10" s="474" t="n"/>
-      <c r="J10" s="436" t="n"/>
-      <c r="K10" s="436" t="n"/>
-      <c r="L10" s="436" t="n"/>
-      <c r="M10" s="436" t="n"/>
-      <c r="N10" s="436" t="n"/>
-      <c r="O10" s="436" t="n"/>
-      <c r="P10" s="436" t="n"/>
-      <c r="Q10" s="436" t="n"/>
-      <c r="R10" s="436" t="n"/>
-      <c r="S10" s="436" t="n"/>
-      <c r="T10" s="436" t="n"/>
-      <c r="U10" s="436" t="n"/>
-      <c r="V10" s="436" t="n"/>
-      <c r="W10" s="436" t="n"/>
-      <c r="X10" s="436" t="n"/>
-      <c r="Y10" s="436" t="n"/>
-      <c r="Z10" s="436" t="n"/>
-      <c r="AA10" s="436" t="n"/>
-      <c r="AB10" s="436" t="n"/>
-      <c r="AC10" s="436" t="n"/>
-      <c r="AD10" s="436" t="n"/>
-      <c r="AE10" s="436" t="n"/>
-      <c r="AF10" s="436" t="n"/>
-      <c r="AG10" s="436" t="n"/>
-      <c r="AH10" s="436" t="n"/>
-      <c r="AI10" s="436" t="n"/>
-      <c r="AJ10" s="436" t="n"/>
-      <c r="AK10" s="436" t="n"/>
-      <c r="AL10" s="436" t="n"/>
-      <c r="AM10" s="436" t="n"/>
-      <c r="AN10" s="436" t="n"/>
+      <c r="G10" s="398" t="n"/>
+      <c r="H10" s="592" t="inlineStr"/>
+      <c r="I10" s="398" t="n"/>
+      <c r="J10" s="594" t="n"/>
+      <c r="K10" s="413" t="n"/>
+      <c r="L10" s="413" t="n"/>
+      <c r="M10" s="413" t="n"/>
+      <c r="N10" s="413" t="n"/>
+      <c r="O10" s="413" t="n"/>
+      <c r="P10" s="413" t="n"/>
+      <c r="Q10" s="413" t="n"/>
+      <c r="R10" s="413" t="n"/>
+      <c r="S10" s="413" t="n"/>
+      <c r="T10" s="413" t="n"/>
+      <c r="U10" s="413" t="n"/>
+      <c r="V10" s="413" t="n"/>
+      <c r="W10" s="413" t="n"/>
+      <c r="X10" s="413" t="n"/>
+      <c r="Y10" s="413" t="n"/>
+      <c r="Z10" s="413" t="n"/>
+      <c r="AA10" s="413" t="n"/>
+      <c r="AB10" s="413" t="n"/>
+      <c r="AC10" s="413" t="n"/>
+      <c r="AD10" s="413" t="n"/>
+      <c r="AE10" s="413" t="n"/>
+      <c r="AF10" s="413" t="n"/>
+      <c r="AG10" s="413" t="n"/>
+      <c r="AH10" s="413" t="n"/>
+      <c r="AI10" s="413" t="n"/>
+      <c r="AJ10" s="413" t="n"/>
+      <c r="AK10" s="413" t="n"/>
+      <c r="AL10" s="413" t="n"/>
+      <c r="AM10" s="413" t="n"/>
+      <c r="AN10" s="595" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="447" t="inlineStr">
+      <c r="A11" s="591" t="inlineStr">
         <is>
           <t>Update Trigger</t>
         </is>
       </c>
-      <c r="B11" s="468" t="n"/>
-      <c r="C11" s="448" t="inlineStr">
+      <c r="B11" s="398" t="n"/>
+      <c r="C11" s="592" t="inlineStr">
         <is>
           <t>Update when the linked review, evidence or follow-up status changes.</t>
         </is>
       </c>
-      <c r="D11" s="467" t="n"/>
-      <c r="E11" s="468" t="n"/>
-      <c r="F11" s="447" t="inlineStr">
+      <c r="D11" s="398" t="n"/>
+      <c r="E11" s="398" t="n"/>
+      <c r="F11" s="593" t="inlineStr">
         <is>
           <t>Data Structure</t>
         </is>
       </c>
-      <c r="G11" s="468" t="n"/>
-      <c r="H11" s="448" t="inlineStr">
+      <c r="G11" s="398" t="n"/>
+      <c r="H11" s="592" t="inlineStr">
         <is>
           <t>Structured Excel Table with filters and print-title rows.</t>
         </is>
       </c>
-      <c r="I11" s="468" t="n"/>
-      <c r="J11" s="402" t="n"/>
-      <c r="K11" s="402" t="n"/>
-      <c r="L11" s="402" t="n"/>
-      <c r="M11" s="402" t="n"/>
-      <c r="N11" s="402" t="n"/>
-      <c r="O11" s="402" t="n"/>
-      <c r="P11" s="402" t="n"/>
-      <c r="Q11" s="402" t="n"/>
-      <c r="R11" s="402" t="n"/>
-      <c r="S11" s="402" t="n"/>
-      <c r="T11" s="402" t="n"/>
-      <c r="U11" s="402" t="n"/>
-      <c r="V11" s="402" t="n"/>
-      <c r="W11" s="402" t="n"/>
-      <c r="X11" s="402" t="n"/>
-      <c r="Y11" s="402" t="n"/>
-      <c r="Z11" s="402" t="n"/>
-      <c r="AA11" s="402" t="n"/>
-      <c r="AB11" s="402" t="n"/>
-      <c r="AC11" s="402" t="n"/>
-      <c r="AD11" s="402" t="n"/>
-      <c r="AE11" s="402" t="n"/>
-      <c r="AF11" s="402" t="n"/>
-      <c r="AG11" s="402" t="n"/>
-      <c r="AH11" s="402" t="n"/>
-      <c r="AI11" s="402" t="n"/>
-      <c r="AJ11" s="402" t="n"/>
-      <c r="AK11" s="402" t="n"/>
-      <c r="AL11" s="402" t="n"/>
-      <c r="AM11" s="402" t="n"/>
-      <c r="AN11" s="402" t="n"/>
+      <c r="I11" s="398" t="n"/>
+      <c r="J11" s="573" t="n"/>
+      <c r="K11" s="398" t="n"/>
+      <c r="L11" s="398" t="n"/>
+      <c r="M11" s="398" t="n"/>
+      <c r="N11" s="398" t="n"/>
+      <c r="O11" s="398" t="n"/>
+      <c r="P11" s="398" t="n"/>
+      <c r="Q11" s="398" t="n"/>
+      <c r="R11" s="398" t="n"/>
+      <c r="S11" s="398" t="n"/>
+      <c r="T11" s="398" t="n"/>
+      <c r="U11" s="398" t="n"/>
+      <c r="V11" s="398" t="n"/>
+      <c r="W11" s="398" t="n"/>
+      <c r="X11" s="398" t="n"/>
+      <c r="Y11" s="398" t="n"/>
+      <c r="Z11" s="398" t="n"/>
+      <c r="AA11" s="398" t="n"/>
+      <c r="AB11" s="398" t="n"/>
+      <c r="AC11" s="398" t="n"/>
+      <c r="AD11" s="398" t="n"/>
+      <c r="AE11" s="398" t="n"/>
+      <c r="AF11" s="398" t="n"/>
+      <c r="AG11" s="398" t="n"/>
+      <c r="AH11" s="398" t="n"/>
+      <c r="AI11" s="398" t="n"/>
+      <c r="AJ11" s="398" t="n"/>
+      <c r="AK11" s="398" t="n"/>
+      <c r="AL11" s="398" t="n"/>
+      <c r="AM11" s="398" t="n"/>
+      <c r="AN11" s="542" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="447" t="inlineStr">
+      <c r="A12" s="596" t="inlineStr">
         <is>
           <t>Retention Rule</t>
         </is>
       </c>
-      <c r="B12" s="474" t="n"/>
-      <c r="C12" s="448" t="inlineStr">
+      <c r="B12" s="544" t="n"/>
+      <c r="C12" s="597" t="inlineStr">
         <is>
           <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
         </is>
       </c>
-      <c r="D12" s="473" t="n"/>
-      <c r="E12" s="474" t="n"/>
-      <c r="F12" s="447" t="inlineStr">
+      <c r="D12" s="544" t="n"/>
+      <c r="E12" s="544" t="n"/>
+      <c r="F12" s="598" t="inlineStr">
         <is>
           <t>Controlled Status</t>
         </is>
       </c>
-      <c r="G12" s="474" t="n"/>
-      <c r="H12" s="448" t="inlineStr">
+      <c r="G12" s="544" t="n"/>
+      <c r="H12" s="597" t="inlineStr">
         <is>
           <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
         </is>
       </c>
-      <c r="I12" s="474" t="n"/>
-      <c r="J12" s="436" t="n"/>
-      <c r="K12" s="436" t="n"/>
-      <c r="L12" s="436" t="n"/>
-      <c r="M12" s="436" t="n"/>
-      <c r="N12" s="436" t="n"/>
-      <c r="O12" s="436" t="n"/>
-      <c r="P12" s="436" t="n"/>
-      <c r="Q12" s="436" t="n"/>
-      <c r="R12" s="436" t="n"/>
-      <c r="S12" s="436" t="n"/>
-      <c r="T12" s="436" t="n"/>
-      <c r="U12" s="436" t="n"/>
-      <c r="V12" s="436" t="n"/>
-      <c r="W12" s="436" t="n"/>
-      <c r="X12" s="436" t="n"/>
-      <c r="Y12" s="436" t="n"/>
-      <c r="Z12" s="436" t="n"/>
-      <c r="AA12" s="436" t="n"/>
-      <c r="AB12" s="436" t="n"/>
-      <c r="AC12" s="436" t="n"/>
-      <c r="AD12" s="436" t="n"/>
-      <c r="AE12" s="436" t="n"/>
-      <c r="AF12" s="436" t="n"/>
-      <c r="AG12" s="436" t="n"/>
-      <c r="AH12" s="436" t="n"/>
-      <c r="AI12" s="436" t="n"/>
-      <c r="AJ12" s="436" t="n"/>
-      <c r="AK12" s="436" t="n"/>
-      <c r="AL12" s="436" t="n"/>
-      <c r="AM12" s="436" t="n"/>
-      <c r="AN12" s="436" t="n"/>
+      <c r="I12" s="544" t="n"/>
+      <c r="J12" s="599" t="n"/>
+      <c r="K12" s="600" t="n"/>
+      <c r="L12" s="600" t="n"/>
+      <c r="M12" s="600" t="n"/>
+      <c r="N12" s="600" t="n"/>
+      <c r="O12" s="600" t="n"/>
+      <c r="P12" s="600" t="n"/>
+      <c r="Q12" s="600" t="n"/>
+      <c r="R12" s="600" t="n"/>
+      <c r="S12" s="600" t="n"/>
+      <c r="T12" s="600" t="n"/>
+      <c r="U12" s="600" t="n"/>
+      <c r="V12" s="600" t="n"/>
+      <c r="W12" s="600" t="n"/>
+      <c r="X12" s="600" t="n"/>
+      <c r="Y12" s="600" t="n"/>
+      <c r="Z12" s="600" t="n"/>
+      <c r="AA12" s="600" t="n"/>
+      <c r="AB12" s="600" t="n"/>
+      <c r="AC12" s="600" t="n"/>
+      <c r="AD12" s="600" t="n"/>
+      <c r="AE12" s="600" t="n"/>
+      <c r="AF12" s="600" t="n"/>
+      <c r="AG12" s="600" t="n"/>
+      <c r="AH12" s="600" t="n"/>
+      <c r="AI12" s="600" t="n"/>
+      <c r="AJ12" s="600" t="n"/>
+      <c r="AK12" s="600" t="n"/>
+      <c r="AL12" s="600" t="n"/>
+      <c r="AM12" s="600" t="n"/>
+      <c r="AN12" s="601" t="n"/>
     </row>
-    <row r="13" ht="4" customHeight="1">
+    <row r="13" ht="3" customHeight="1">
       <c r="A13" s="449" t="n"/>
       <c r="B13" s="482" t="n"/>
       <c r="C13" s="482" t="n"/>
@@ -10358,713 +11217,713 @@
       <c r="AM13" s="410" t="n"/>
       <c r="AN13" s="410" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="450" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="531" t="inlineStr">
         <is>
           <t>2.  WORKING TABLE / DETAIL LINES</t>
         </is>
       </c>
-      <c r="B14" s="473" t="n"/>
-      <c r="C14" s="473" t="n"/>
-      <c r="D14" s="473" t="n"/>
-      <c r="E14" s="473" t="n"/>
-      <c r="F14" s="473" t="n"/>
-      <c r="G14" s="473" t="n"/>
-      <c r="H14" s="473" t="n"/>
-      <c r="I14" s="474" t="n"/>
-      <c r="J14" s="436" t="n"/>
-      <c r="K14" s="436" t="n"/>
-      <c r="L14" s="436" t="n"/>
-      <c r="M14" s="436" t="n"/>
-      <c r="N14" s="436" t="n"/>
-      <c r="O14" s="436" t="n"/>
-      <c r="P14" s="436" t="n"/>
-      <c r="Q14" s="436" t="n"/>
-      <c r="R14" s="436" t="n"/>
-      <c r="S14" s="436" t="n"/>
-      <c r="T14" s="436" t="n"/>
-      <c r="U14" s="436" t="n"/>
-      <c r="V14" s="436" t="n"/>
-      <c r="W14" s="436" t="n"/>
-      <c r="X14" s="436" t="n"/>
-      <c r="Y14" s="436" t="n"/>
-      <c r="Z14" s="436" t="n"/>
-      <c r="AA14" s="436" t="n"/>
-      <c r="AB14" s="436" t="n"/>
-      <c r="AC14" s="436" t="n"/>
-      <c r="AD14" s="436" t="n"/>
-      <c r="AE14" s="436" t="n"/>
-      <c r="AF14" s="436" t="n"/>
-      <c r="AG14" s="436" t="n"/>
-      <c r="AH14" s="436" t="n"/>
-      <c r="AI14" s="436" t="n"/>
-      <c r="AJ14" s="436" t="n"/>
-      <c r="AK14" s="436" t="n"/>
-      <c r="AL14" s="436" t="n"/>
-      <c r="AM14" s="436" t="n"/>
-      <c r="AN14" s="436" t="n"/>
+      <c r="B14" s="532" t="n"/>
+      <c r="C14" s="532" t="n"/>
+      <c r="D14" s="532" t="n"/>
+      <c r="E14" s="532" t="n"/>
+      <c r="F14" s="532" t="n"/>
+      <c r="G14" s="532" t="n"/>
+      <c r="H14" s="532" t="n"/>
+      <c r="I14" s="532" t="n"/>
+      <c r="J14" s="532" t="n"/>
+      <c r="K14" s="532" t="n"/>
+      <c r="L14" s="532" t="n"/>
+      <c r="M14" s="532" t="n"/>
+      <c r="N14" s="532" t="n"/>
+      <c r="O14" s="532" t="n"/>
+      <c r="P14" s="532" t="n"/>
+      <c r="Q14" s="532" t="n"/>
+      <c r="R14" s="532" t="n"/>
+      <c r="S14" s="532" t="n"/>
+      <c r="T14" s="532" t="n"/>
+      <c r="U14" s="532" t="n"/>
+      <c r="V14" s="532" t="n"/>
+      <c r="W14" s="532" t="n"/>
+      <c r="X14" s="532" t="n"/>
+      <c r="Y14" s="532" t="n"/>
+      <c r="Z14" s="532" t="n"/>
+      <c r="AA14" s="532" t="n"/>
+      <c r="AB14" s="532" t="n"/>
+      <c r="AC14" s="532" t="n"/>
+      <c r="AD14" s="532" t="n"/>
+      <c r="AE14" s="532" t="n"/>
+      <c r="AF14" s="532" t="n"/>
+      <c r="AG14" s="532" t="n"/>
+      <c r="AH14" s="532" t="n"/>
+      <c r="AI14" s="532" t="n"/>
+      <c r="AJ14" s="532" t="n"/>
+      <c r="AK14" s="532" t="n"/>
+      <c r="AL14" s="532" t="n"/>
+      <c r="AM14" s="532" t="n"/>
+      <c r="AN14" s="533" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="451" t="inlineStr">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="531" t="inlineStr">
         <is>
           <t>One line per material, capacity, quality or customer-risk condition.</t>
         </is>
       </c>
-      <c r="B15" s="473" t="n"/>
-      <c r="C15" s="473" t="n"/>
-      <c r="D15" s="473" t="n"/>
-      <c r="E15" s="473" t="n"/>
-      <c r="F15" s="473" t="n"/>
-      <c r="G15" s="473" t="n"/>
-      <c r="H15" s="473" t="n"/>
-      <c r="I15" s="474" t="n"/>
-      <c r="J15" s="436" t="n"/>
-      <c r="K15" s="436" t="n"/>
-      <c r="L15" s="436" t="n"/>
-      <c r="M15" s="436" t="n"/>
-      <c r="N15" s="436" t="n"/>
-      <c r="O15" s="436" t="n"/>
-      <c r="P15" s="436" t="n"/>
-      <c r="Q15" s="436" t="n"/>
-      <c r="R15" s="436" t="n"/>
-      <c r="S15" s="436" t="n"/>
-      <c r="T15" s="436" t="n"/>
-      <c r="U15" s="436" t="n"/>
-      <c r="V15" s="436" t="n"/>
-      <c r="W15" s="436" t="n"/>
-      <c r="X15" s="436" t="n"/>
-      <c r="Y15" s="436" t="n"/>
-      <c r="Z15" s="436" t="n"/>
-      <c r="AA15" s="436" t="n"/>
-      <c r="AB15" s="436" t="n"/>
-      <c r="AC15" s="436" t="n"/>
-      <c r="AD15" s="436" t="n"/>
-      <c r="AE15" s="436" t="n"/>
-      <c r="AF15" s="436" t="n"/>
-      <c r="AG15" s="436" t="n"/>
-      <c r="AH15" s="436" t="n"/>
-      <c r="AI15" s="436" t="n"/>
-      <c r="AJ15" s="436" t="n"/>
-      <c r="AK15" s="436" t="n"/>
-      <c r="AL15" s="436" t="n"/>
-      <c r="AM15" s="436" t="n"/>
-      <c r="AN15" s="436" t="n"/>
+      <c r="B15" s="532" t="n"/>
+      <c r="C15" s="532" t="n"/>
+      <c r="D15" s="532" t="n"/>
+      <c r="E15" s="532" t="n"/>
+      <c r="F15" s="532" t="n"/>
+      <c r="G15" s="532" t="n"/>
+      <c r="H15" s="532" t="n"/>
+      <c r="I15" s="532" t="n"/>
+      <c r="J15" s="532" t="n"/>
+      <c r="K15" s="532" t="n"/>
+      <c r="L15" s="532" t="n"/>
+      <c r="M15" s="532" t="n"/>
+      <c r="N15" s="532" t="n"/>
+      <c r="O15" s="532" t="n"/>
+      <c r="P15" s="532" t="n"/>
+      <c r="Q15" s="532" t="n"/>
+      <c r="R15" s="532" t="n"/>
+      <c r="S15" s="532" t="n"/>
+      <c r="T15" s="532" t="n"/>
+      <c r="U15" s="532" t="n"/>
+      <c r="V15" s="532" t="n"/>
+      <c r="W15" s="532" t="n"/>
+      <c r="X15" s="532" t="n"/>
+      <c r="Y15" s="532" t="n"/>
+      <c r="Z15" s="532" t="n"/>
+      <c r="AA15" s="532" t="n"/>
+      <c r="AB15" s="532" t="n"/>
+      <c r="AC15" s="532" t="n"/>
+      <c r="AD15" s="532" t="n"/>
+      <c r="AE15" s="532" t="n"/>
+      <c r="AF15" s="532" t="n"/>
+      <c r="AG15" s="532" t="n"/>
+      <c r="AH15" s="532" t="n"/>
+      <c r="AI15" s="532" t="n"/>
+      <c r="AJ15" s="532" t="n"/>
+      <c r="AK15" s="532" t="n"/>
+      <c r="AL15" s="532" t="n"/>
+      <c r="AM15" s="532" t="n"/>
+      <c r="AN15" s="533" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="452" t="inlineStr">
+      <c r="A16" s="548" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B16" s="452" t="inlineStr">
+      <c r="B16" s="549" t="inlineStr">
         <is>
           <t>Risk / Readiness Gap</t>
         </is>
       </c>
-      <c r="C16" s="452" t="inlineStr">
+      <c r="C16" s="549" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="D16" s="452" t="inlineStr">
+      <c r="D16" s="549" t="inlineStr">
         <is>
           <t>Containment / Action</t>
         </is>
       </c>
-      <c r="E16" s="452" t="inlineStr">
+      <c r="E16" s="549" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F16" s="452" t="inlineStr">
+      <c r="F16" s="549" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="G16" s="452" t="inlineStr">
+      <c r="G16" s="549" t="inlineStr">
         <is>
           <t>Escalation</t>
         </is>
       </c>
-      <c r="H16" s="452" t="inlineStr">
+      <c r="H16" s="549" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I16" s="421" t="inlineStr">
+      <c r="I16" s="549" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="J16" s="436" t="n"/>
-      <c r="K16" s="436" t="n"/>
-      <c r="L16" s="436" t="n"/>
-      <c r="M16" s="436" t="n"/>
-      <c r="N16" s="436" t="n"/>
-      <c r="O16" s="436" t="n"/>
-      <c r="P16" s="436" t="n"/>
-      <c r="Q16" s="436" t="n"/>
-      <c r="R16" s="436" t="n"/>
-      <c r="S16" s="436" t="n"/>
-      <c r="T16" s="436" t="n"/>
-      <c r="U16" s="436" t="n"/>
-      <c r="V16" s="436" t="n"/>
-      <c r="W16" s="436" t="n"/>
-      <c r="X16" s="436" t="n"/>
-      <c r="Y16" s="436" t="n"/>
-      <c r="Z16" s="436" t="n"/>
-      <c r="AA16" s="436" t="n"/>
-      <c r="AB16" s="436" t="n"/>
-      <c r="AC16" s="436" t="n"/>
-      <c r="AD16" s="436" t="n"/>
-      <c r="AE16" s="436" t="n"/>
-      <c r="AF16" s="436" t="n"/>
-      <c r="AG16" s="436" t="n"/>
-      <c r="AH16" s="436" t="n"/>
-      <c r="AI16" s="436" t="n"/>
-      <c r="AJ16" s="436" t="n"/>
-      <c r="AK16" s="436" t="n"/>
-      <c r="AL16" s="436" t="n"/>
-      <c r="AM16" s="436" t="n"/>
-      <c r="AN16" s="436" t="n"/>
+      <c r="J16" s="549" t="n"/>
+      <c r="K16" s="549" t="n"/>
+      <c r="L16" s="549" t="n"/>
+      <c r="M16" s="549" t="n"/>
+      <c r="N16" s="549" t="n"/>
+      <c r="O16" s="549" t="n"/>
+      <c r="P16" s="549" t="n"/>
+      <c r="Q16" s="549" t="n"/>
+      <c r="R16" s="549" t="n"/>
+      <c r="S16" s="549" t="n"/>
+      <c r="T16" s="549" t="n"/>
+      <c r="U16" s="549" t="n"/>
+      <c r="V16" s="549" t="n"/>
+      <c r="W16" s="549" t="n"/>
+      <c r="X16" s="549" t="n"/>
+      <c r="Y16" s="549" t="n"/>
+      <c r="Z16" s="549" t="n"/>
+      <c r="AA16" s="549" t="n"/>
+      <c r="AB16" s="549" t="n"/>
+      <c r="AC16" s="549" t="n"/>
+      <c r="AD16" s="549" t="n"/>
+      <c r="AE16" s="549" t="n"/>
+      <c r="AF16" s="549" t="n"/>
+      <c r="AG16" s="549" t="n"/>
+      <c r="AH16" s="549" t="n"/>
+      <c r="AI16" s="549" t="n"/>
+      <c r="AJ16" s="549" t="n"/>
+      <c r="AK16" s="549" t="n"/>
+      <c r="AL16" s="549" t="n"/>
+      <c r="AM16" s="549" t="n"/>
+      <c r="AN16" s="551" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="453">
+      <c r="A17" s="602">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B17" s="454" t="n"/>
-      <c r="C17" s="454" t="n"/>
-      <c r="D17" s="454" t="n"/>
-      <c r="E17" s="454" t="n"/>
-      <c r="F17" s="455" t="n"/>
-      <c r="G17" s="454" t="n"/>
-      <c r="H17" s="454" t="n"/>
-      <c r="I17" s="443" t="n"/>
-      <c r="J17" s="436" t="n"/>
-      <c r="K17" s="436" t="n"/>
-      <c r="L17" s="436" t="n"/>
-      <c r="M17" s="436" t="n"/>
-      <c r="N17" s="436" t="n"/>
-      <c r="O17" s="436" t="n"/>
-      <c r="P17" s="436" t="n"/>
-      <c r="Q17" s="436" t="n"/>
-      <c r="R17" s="436" t="n"/>
-      <c r="S17" s="436" t="n"/>
-      <c r="T17" s="436" t="n"/>
-      <c r="U17" s="436" t="n"/>
-      <c r="V17" s="436" t="n"/>
-      <c r="W17" s="436" t="n"/>
-      <c r="X17" s="436" t="n"/>
-      <c r="Y17" s="436" t="n"/>
-      <c r="Z17" s="436" t="n"/>
-      <c r="AA17" s="436" t="n"/>
-      <c r="AB17" s="436" t="n"/>
-      <c r="AC17" s="436" t="n"/>
-      <c r="AD17" s="436" t="n"/>
-      <c r="AE17" s="436" t="n"/>
-      <c r="AF17" s="436" t="n"/>
-      <c r="AG17" s="436" t="n"/>
-      <c r="AH17" s="436" t="n"/>
-      <c r="AI17" s="436" t="n"/>
-      <c r="AJ17" s="436" t="n"/>
-      <c r="AK17" s="436" t="n"/>
-      <c r="AL17" s="436" t="n"/>
-      <c r="AM17" s="436" t="n"/>
-      <c r="AN17" s="436" t="n"/>
+      <c r="B17" s="586" t="n"/>
+      <c r="C17" s="603" t="n"/>
+      <c r="D17" s="603" t="n"/>
+      <c r="E17" s="603" t="n"/>
+      <c r="F17" s="604" t="n"/>
+      <c r="G17" s="603" t="n"/>
+      <c r="H17" s="603" t="n"/>
+      <c r="I17" s="603" t="n"/>
+      <c r="J17" s="589" t="n"/>
+      <c r="K17" s="589" t="n"/>
+      <c r="L17" s="589" t="n"/>
+      <c r="M17" s="589" t="n"/>
+      <c r="N17" s="589" t="n"/>
+      <c r="O17" s="589" t="n"/>
+      <c r="P17" s="589" t="n"/>
+      <c r="Q17" s="589" t="n"/>
+      <c r="R17" s="589" t="n"/>
+      <c r="S17" s="589" t="n"/>
+      <c r="T17" s="589" t="n"/>
+      <c r="U17" s="589" t="n"/>
+      <c r="V17" s="589" t="n"/>
+      <c r="W17" s="589" t="n"/>
+      <c r="X17" s="589" t="n"/>
+      <c r="Y17" s="589" t="n"/>
+      <c r="Z17" s="589" t="n"/>
+      <c r="AA17" s="589" t="n"/>
+      <c r="AB17" s="589" t="n"/>
+      <c r="AC17" s="589" t="n"/>
+      <c r="AD17" s="589" t="n"/>
+      <c r="AE17" s="589" t="n"/>
+      <c r="AF17" s="589" t="n"/>
+      <c r="AG17" s="589" t="n"/>
+      <c r="AH17" s="589" t="n"/>
+      <c r="AI17" s="589" t="n"/>
+      <c r="AJ17" s="589" t="n"/>
+      <c r="AK17" s="589" t="n"/>
+      <c r="AL17" s="589" t="n"/>
+      <c r="AM17" s="589" t="n"/>
+      <c r="AN17" s="590" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="453">
+      <c r="A18" s="605">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B18" s="456" t="n"/>
-      <c r="C18" s="456" t="n"/>
-      <c r="D18" s="456" t="n"/>
-      <c r="E18" s="456" t="n"/>
-      <c r="F18" s="457" t="n"/>
-      <c r="G18" s="456" t="n"/>
-      <c r="H18" s="456" t="n"/>
-      <c r="I18" s="458" t="n"/>
-      <c r="J18" s="436" t="n"/>
-      <c r="K18" s="436" t="n"/>
-      <c r="L18" s="436" t="n"/>
-      <c r="M18" s="436" t="n"/>
-      <c r="N18" s="436" t="n"/>
-      <c r="O18" s="436" t="n"/>
-      <c r="P18" s="436" t="n"/>
-      <c r="Q18" s="436" t="n"/>
-      <c r="R18" s="436" t="n"/>
-      <c r="S18" s="436" t="n"/>
-      <c r="T18" s="436" t="n"/>
-      <c r="U18" s="436" t="n"/>
-      <c r="V18" s="436" t="n"/>
-      <c r="W18" s="436" t="n"/>
-      <c r="X18" s="436" t="n"/>
-      <c r="Y18" s="436" t="n"/>
-      <c r="Z18" s="436" t="n"/>
-      <c r="AA18" s="436" t="n"/>
-      <c r="AB18" s="436" t="n"/>
-      <c r="AC18" s="436" t="n"/>
-      <c r="AD18" s="436" t="n"/>
-      <c r="AE18" s="436" t="n"/>
-      <c r="AF18" s="436" t="n"/>
-      <c r="AG18" s="436" t="n"/>
-      <c r="AH18" s="436" t="n"/>
-      <c r="AI18" s="436" t="n"/>
-      <c r="AJ18" s="436" t="n"/>
-      <c r="AK18" s="436" t="n"/>
-      <c r="AL18" s="436" t="n"/>
-      <c r="AM18" s="436" t="n"/>
-      <c r="AN18" s="436" t="n"/>
+      <c r="B18" s="460" t="n"/>
+      <c r="C18" s="606" t="n"/>
+      <c r="D18" s="606" t="n"/>
+      <c r="E18" s="606" t="n"/>
+      <c r="F18" s="607" t="n"/>
+      <c r="G18" s="606" t="n"/>
+      <c r="H18" s="606" t="n"/>
+      <c r="I18" s="606" t="n"/>
+      <c r="J18" s="413" t="n"/>
+      <c r="K18" s="413" t="n"/>
+      <c r="L18" s="413" t="n"/>
+      <c r="M18" s="413" t="n"/>
+      <c r="N18" s="413" t="n"/>
+      <c r="O18" s="413" t="n"/>
+      <c r="P18" s="413" t="n"/>
+      <c r="Q18" s="413" t="n"/>
+      <c r="R18" s="413" t="n"/>
+      <c r="S18" s="413" t="n"/>
+      <c r="T18" s="413" t="n"/>
+      <c r="U18" s="413" t="n"/>
+      <c r="V18" s="413" t="n"/>
+      <c r="W18" s="413" t="n"/>
+      <c r="X18" s="413" t="n"/>
+      <c r="Y18" s="413" t="n"/>
+      <c r="Z18" s="413" t="n"/>
+      <c r="AA18" s="413" t="n"/>
+      <c r="AB18" s="413" t="n"/>
+      <c r="AC18" s="413" t="n"/>
+      <c r="AD18" s="413" t="n"/>
+      <c r="AE18" s="413" t="n"/>
+      <c r="AF18" s="413" t="n"/>
+      <c r="AG18" s="413" t="n"/>
+      <c r="AH18" s="413" t="n"/>
+      <c r="AI18" s="413" t="n"/>
+      <c r="AJ18" s="413" t="n"/>
+      <c r="AK18" s="413" t="n"/>
+      <c r="AL18" s="413" t="n"/>
+      <c r="AM18" s="413" t="n"/>
+      <c r="AN18" s="595" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="453">
+      <c r="A19" s="605">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B19" s="454" t="n"/>
-      <c r="C19" s="454" t="n"/>
-      <c r="D19" s="454" t="n"/>
-      <c r="E19" s="454" t="n"/>
-      <c r="F19" s="455" t="n"/>
-      <c r="G19" s="454" t="n"/>
-      <c r="H19" s="454" t="n"/>
-      <c r="I19" s="443" t="n"/>
-      <c r="J19" s="436" t="n"/>
-      <c r="K19" s="436" t="n"/>
-      <c r="L19" s="436" t="n"/>
-      <c r="M19" s="436" t="n"/>
-      <c r="N19" s="436" t="n"/>
-      <c r="O19" s="436" t="n"/>
-      <c r="P19" s="436" t="n"/>
-      <c r="Q19" s="436" t="n"/>
-      <c r="R19" s="436" t="n"/>
-      <c r="S19" s="436" t="n"/>
-      <c r="T19" s="436" t="n"/>
-      <c r="U19" s="436" t="n"/>
-      <c r="V19" s="436" t="n"/>
-      <c r="W19" s="436" t="n"/>
-      <c r="X19" s="436" t="n"/>
-      <c r="Y19" s="436" t="n"/>
-      <c r="Z19" s="436" t="n"/>
-      <c r="AA19" s="436" t="n"/>
-      <c r="AB19" s="436" t="n"/>
-      <c r="AC19" s="436" t="n"/>
-      <c r="AD19" s="436" t="n"/>
-      <c r="AE19" s="436" t="n"/>
-      <c r="AF19" s="436" t="n"/>
-      <c r="AG19" s="436" t="n"/>
-      <c r="AH19" s="436" t="n"/>
-      <c r="AI19" s="436" t="n"/>
-      <c r="AJ19" s="436" t="n"/>
-      <c r="AK19" s="436" t="n"/>
-      <c r="AL19" s="436" t="n"/>
-      <c r="AM19" s="436" t="n"/>
-      <c r="AN19" s="436" t="n"/>
+      <c r="B19" s="592" t="n"/>
+      <c r="C19" s="608" t="n"/>
+      <c r="D19" s="608" t="n"/>
+      <c r="E19" s="608" t="n"/>
+      <c r="F19" s="609" t="n"/>
+      <c r="G19" s="608" t="n"/>
+      <c r="H19" s="608" t="n"/>
+      <c r="I19" s="608" t="n"/>
+      <c r="J19" s="413" t="n"/>
+      <c r="K19" s="413" t="n"/>
+      <c r="L19" s="413" t="n"/>
+      <c r="M19" s="413" t="n"/>
+      <c r="N19" s="413" t="n"/>
+      <c r="O19" s="413" t="n"/>
+      <c r="P19" s="413" t="n"/>
+      <c r="Q19" s="413" t="n"/>
+      <c r="R19" s="413" t="n"/>
+      <c r="S19" s="413" t="n"/>
+      <c r="T19" s="413" t="n"/>
+      <c r="U19" s="413" t="n"/>
+      <c r="V19" s="413" t="n"/>
+      <c r="W19" s="413" t="n"/>
+      <c r="X19" s="413" t="n"/>
+      <c r="Y19" s="413" t="n"/>
+      <c r="Z19" s="413" t="n"/>
+      <c r="AA19" s="413" t="n"/>
+      <c r="AB19" s="413" t="n"/>
+      <c r="AC19" s="413" t="n"/>
+      <c r="AD19" s="413" t="n"/>
+      <c r="AE19" s="413" t="n"/>
+      <c r="AF19" s="413" t="n"/>
+      <c r="AG19" s="413" t="n"/>
+      <c r="AH19" s="413" t="n"/>
+      <c r="AI19" s="413" t="n"/>
+      <c r="AJ19" s="413" t="n"/>
+      <c r="AK19" s="413" t="n"/>
+      <c r="AL19" s="413" t="n"/>
+      <c r="AM19" s="413" t="n"/>
+      <c r="AN19" s="595" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="453">
+      <c r="A20" s="605">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B20" s="456" t="n"/>
-      <c r="C20" s="456" t="n"/>
-      <c r="D20" s="456" t="n"/>
-      <c r="E20" s="456" t="n"/>
-      <c r="F20" s="457" t="n"/>
-      <c r="G20" s="456" t="n"/>
-      <c r="H20" s="456" t="n"/>
-      <c r="I20" s="458" t="n"/>
-      <c r="J20" s="436" t="n"/>
-      <c r="K20" s="436" t="n"/>
-      <c r="L20" s="436" t="n"/>
-      <c r="M20" s="436" t="n"/>
-      <c r="N20" s="436" t="n"/>
-      <c r="O20" s="436" t="n"/>
-      <c r="P20" s="436" t="n"/>
-      <c r="Q20" s="436" t="n"/>
-      <c r="R20" s="436" t="n"/>
-      <c r="S20" s="436" t="n"/>
-      <c r="T20" s="436" t="n"/>
-      <c r="U20" s="436" t="n"/>
-      <c r="V20" s="436" t="n"/>
-      <c r="W20" s="436" t="n"/>
-      <c r="X20" s="436" t="n"/>
-      <c r="Y20" s="436" t="n"/>
-      <c r="Z20" s="436" t="n"/>
-      <c r="AA20" s="436" t="n"/>
-      <c r="AB20" s="436" t="n"/>
-      <c r="AC20" s="436" t="n"/>
-      <c r="AD20" s="436" t="n"/>
-      <c r="AE20" s="436" t="n"/>
-      <c r="AF20" s="436" t="n"/>
-      <c r="AG20" s="436" t="n"/>
-      <c r="AH20" s="436" t="n"/>
-      <c r="AI20" s="436" t="n"/>
-      <c r="AJ20" s="436" t="n"/>
-      <c r="AK20" s="436" t="n"/>
-      <c r="AL20" s="436" t="n"/>
-      <c r="AM20" s="436" t="n"/>
-      <c r="AN20" s="436" t="n"/>
+      <c r="B20" s="460" t="n"/>
+      <c r="C20" s="606" t="n"/>
+      <c r="D20" s="606" t="n"/>
+      <c r="E20" s="606" t="n"/>
+      <c r="F20" s="607" t="n"/>
+      <c r="G20" s="606" t="n"/>
+      <c r="H20" s="606" t="n"/>
+      <c r="I20" s="606" t="n"/>
+      <c r="J20" s="413" t="n"/>
+      <c r="K20" s="413" t="n"/>
+      <c r="L20" s="413" t="n"/>
+      <c r="M20" s="413" t="n"/>
+      <c r="N20" s="413" t="n"/>
+      <c r="O20" s="413" t="n"/>
+      <c r="P20" s="413" t="n"/>
+      <c r="Q20" s="413" t="n"/>
+      <c r="R20" s="413" t="n"/>
+      <c r="S20" s="413" t="n"/>
+      <c r="T20" s="413" t="n"/>
+      <c r="U20" s="413" t="n"/>
+      <c r="V20" s="413" t="n"/>
+      <c r="W20" s="413" t="n"/>
+      <c r="X20" s="413" t="n"/>
+      <c r="Y20" s="413" t="n"/>
+      <c r="Z20" s="413" t="n"/>
+      <c r="AA20" s="413" t="n"/>
+      <c r="AB20" s="413" t="n"/>
+      <c r="AC20" s="413" t="n"/>
+      <c r="AD20" s="413" t="n"/>
+      <c r="AE20" s="413" t="n"/>
+      <c r="AF20" s="413" t="n"/>
+      <c r="AG20" s="413" t="n"/>
+      <c r="AH20" s="413" t="n"/>
+      <c r="AI20" s="413" t="n"/>
+      <c r="AJ20" s="413" t="n"/>
+      <c r="AK20" s="413" t="n"/>
+      <c r="AL20" s="413" t="n"/>
+      <c r="AM20" s="413" t="n"/>
+      <c r="AN20" s="595" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="453">
+      <c r="A21" s="605">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B21" s="454" t="n"/>
-      <c r="C21" s="454" t="n"/>
-      <c r="D21" s="454" t="n"/>
-      <c r="E21" s="454" t="n"/>
-      <c r="F21" s="455" t="n"/>
-      <c r="G21" s="454" t="n"/>
-      <c r="H21" s="454" t="n"/>
-      <c r="I21" s="443" t="n"/>
-      <c r="J21" s="436" t="n"/>
-      <c r="K21" s="436" t="n"/>
-      <c r="L21" s="436" t="n"/>
-      <c r="M21" s="436" t="n"/>
-      <c r="N21" s="436" t="n"/>
-      <c r="O21" s="436" t="n"/>
-      <c r="P21" s="436" t="n"/>
-      <c r="Q21" s="436" t="n"/>
-      <c r="R21" s="436" t="n"/>
-      <c r="S21" s="436" t="n"/>
-      <c r="T21" s="436" t="n"/>
-      <c r="U21" s="436" t="n"/>
-      <c r="V21" s="436" t="n"/>
-      <c r="W21" s="436" t="n"/>
-      <c r="X21" s="436" t="n"/>
-      <c r="Y21" s="436" t="n"/>
-      <c r="Z21" s="436" t="n"/>
-      <c r="AA21" s="436" t="n"/>
-      <c r="AB21" s="436" t="n"/>
-      <c r="AC21" s="436" t="n"/>
-      <c r="AD21" s="436" t="n"/>
-      <c r="AE21" s="436" t="n"/>
-      <c r="AF21" s="436" t="n"/>
-      <c r="AG21" s="436" t="n"/>
-      <c r="AH21" s="436" t="n"/>
-      <c r="AI21" s="436" t="n"/>
-      <c r="AJ21" s="436" t="n"/>
-      <c r="AK21" s="436" t="n"/>
-      <c r="AL21" s="436" t="n"/>
-      <c r="AM21" s="436" t="n"/>
-      <c r="AN21" s="436" t="n"/>
+      <c r="B21" s="592" t="n"/>
+      <c r="C21" s="608" t="n"/>
+      <c r="D21" s="608" t="n"/>
+      <c r="E21" s="608" t="n"/>
+      <c r="F21" s="609" t="n"/>
+      <c r="G21" s="608" t="n"/>
+      <c r="H21" s="608" t="n"/>
+      <c r="I21" s="608" t="n"/>
+      <c r="J21" s="413" t="n"/>
+      <c r="K21" s="413" t="n"/>
+      <c r="L21" s="413" t="n"/>
+      <c r="M21" s="413" t="n"/>
+      <c r="N21" s="413" t="n"/>
+      <c r="O21" s="413" t="n"/>
+      <c r="P21" s="413" t="n"/>
+      <c r="Q21" s="413" t="n"/>
+      <c r="R21" s="413" t="n"/>
+      <c r="S21" s="413" t="n"/>
+      <c r="T21" s="413" t="n"/>
+      <c r="U21" s="413" t="n"/>
+      <c r="V21" s="413" t="n"/>
+      <c r="W21" s="413" t="n"/>
+      <c r="X21" s="413" t="n"/>
+      <c r="Y21" s="413" t="n"/>
+      <c r="Z21" s="413" t="n"/>
+      <c r="AA21" s="413" t="n"/>
+      <c r="AB21" s="413" t="n"/>
+      <c r="AC21" s="413" t="n"/>
+      <c r="AD21" s="413" t="n"/>
+      <c r="AE21" s="413" t="n"/>
+      <c r="AF21" s="413" t="n"/>
+      <c r="AG21" s="413" t="n"/>
+      <c r="AH21" s="413" t="n"/>
+      <c r="AI21" s="413" t="n"/>
+      <c r="AJ21" s="413" t="n"/>
+      <c r="AK21" s="413" t="n"/>
+      <c r="AL21" s="413" t="n"/>
+      <c r="AM21" s="413" t="n"/>
+      <c r="AN21" s="595" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="453">
+      <c r="A22" s="605">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B22" s="456" t="n"/>
-      <c r="C22" s="456" t="n"/>
-      <c r="D22" s="456" t="n"/>
-      <c r="E22" s="456" t="n"/>
-      <c r="F22" s="457" t="n"/>
-      <c r="G22" s="456" t="n"/>
-      <c r="H22" s="456" t="n"/>
-      <c r="I22" s="458" t="n"/>
-      <c r="J22" s="436" t="n"/>
-      <c r="K22" s="436" t="n"/>
-      <c r="L22" s="436" t="n"/>
-      <c r="M22" s="436" t="n"/>
-      <c r="N22" s="436" t="n"/>
-      <c r="O22" s="436" t="n"/>
-      <c r="P22" s="436" t="n"/>
-      <c r="Q22" s="436" t="n"/>
-      <c r="R22" s="436" t="n"/>
-      <c r="S22" s="436" t="n"/>
-      <c r="T22" s="436" t="n"/>
-      <c r="U22" s="436" t="n"/>
-      <c r="V22" s="436" t="n"/>
-      <c r="W22" s="436" t="n"/>
-      <c r="X22" s="436" t="n"/>
-      <c r="Y22" s="436" t="n"/>
-      <c r="Z22" s="436" t="n"/>
-      <c r="AA22" s="436" t="n"/>
-      <c r="AB22" s="436" t="n"/>
-      <c r="AC22" s="436" t="n"/>
-      <c r="AD22" s="436" t="n"/>
-      <c r="AE22" s="436" t="n"/>
-      <c r="AF22" s="436" t="n"/>
-      <c r="AG22" s="436" t="n"/>
-      <c r="AH22" s="436" t="n"/>
-      <c r="AI22" s="436" t="n"/>
-      <c r="AJ22" s="436" t="n"/>
-      <c r="AK22" s="436" t="n"/>
-      <c r="AL22" s="436" t="n"/>
-      <c r="AM22" s="436" t="n"/>
-      <c r="AN22" s="436" t="n"/>
+      <c r="B22" s="460" t="n"/>
+      <c r="C22" s="606" t="n"/>
+      <c r="D22" s="606" t="n"/>
+      <c r="E22" s="606" t="n"/>
+      <c r="F22" s="607" t="n"/>
+      <c r="G22" s="606" t="n"/>
+      <c r="H22" s="606" t="n"/>
+      <c r="I22" s="606" t="n"/>
+      <c r="J22" s="413" t="n"/>
+      <c r="K22" s="413" t="n"/>
+      <c r="L22" s="413" t="n"/>
+      <c r="M22" s="413" t="n"/>
+      <c r="N22" s="413" t="n"/>
+      <c r="O22" s="413" t="n"/>
+      <c r="P22" s="413" t="n"/>
+      <c r="Q22" s="413" t="n"/>
+      <c r="R22" s="413" t="n"/>
+      <c r="S22" s="413" t="n"/>
+      <c r="T22" s="413" t="n"/>
+      <c r="U22" s="413" t="n"/>
+      <c r="V22" s="413" t="n"/>
+      <c r="W22" s="413" t="n"/>
+      <c r="X22" s="413" t="n"/>
+      <c r="Y22" s="413" t="n"/>
+      <c r="Z22" s="413" t="n"/>
+      <c r="AA22" s="413" t="n"/>
+      <c r="AB22" s="413" t="n"/>
+      <c r="AC22" s="413" t="n"/>
+      <c r="AD22" s="413" t="n"/>
+      <c r="AE22" s="413" t="n"/>
+      <c r="AF22" s="413" t="n"/>
+      <c r="AG22" s="413" t="n"/>
+      <c r="AH22" s="413" t="n"/>
+      <c r="AI22" s="413" t="n"/>
+      <c r="AJ22" s="413" t="n"/>
+      <c r="AK22" s="413" t="n"/>
+      <c r="AL22" s="413" t="n"/>
+      <c r="AM22" s="413" t="n"/>
+      <c r="AN22" s="595" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="453">
+      <c r="A23" s="605">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B23" s="454" t="n"/>
-      <c r="C23" s="454" t="n"/>
-      <c r="D23" s="454" t="n"/>
-      <c r="E23" s="454" t="n"/>
-      <c r="F23" s="455" t="n"/>
-      <c r="G23" s="454" t="n"/>
-      <c r="H23" s="454" t="n"/>
-      <c r="I23" s="443" t="n"/>
-      <c r="J23" s="436" t="n"/>
-      <c r="K23" s="436" t="n"/>
-      <c r="L23" s="436" t="n"/>
-      <c r="M23" s="436" t="n"/>
-      <c r="N23" s="436" t="n"/>
-      <c r="O23" s="436" t="n"/>
-      <c r="P23" s="436" t="n"/>
-      <c r="Q23" s="436" t="n"/>
-      <c r="R23" s="436" t="n"/>
-      <c r="S23" s="436" t="n"/>
-      <c r="T23" s="436" t="n"/>
-      <c r="U23" s="436" t="n"/>
-      <c r="V23" s="436" t="n"/>
-      <c r="W23" s="436" t="n"/>
-      <c r="X23" s="436" t="n"/>
-      <c r="Y23" s="436" t="n"/>
-      <c r="Z23" s="436" t="n"/>
-      <c r="AA23" s="436" t="n"/>
-      <c r="AB23" s="436" t="n"/>
-      <c r="AC23" s="436" t="n"/>
-      <c r="AD23" s="436" t="n"/>
-      <c r="AE23" s="436" t="n"/>
-      <c r="AF23" s="436" t="n"/>
-      <c r="AG23" s="436" t="n"/>
-      <c r="AH23" s="436" t="n"/>
-      <c r="AI23" s="436" t="n"/>
-      <c r="AJ23" s="436" t="n"/>
-      <c r="AK23" s="436" t="n"/>
-      <c r="AL23" s="436" t="n"/>
-      <c r="AM23" s="436" t="n"/>
-      <c r="AN23" s="436" t="n"/>
+      <c r="B23" s="592" t="n"/>
+      <c r="C23" s="608" t="n"/>
+      <c r="D23" s="608" t="n"/>
+      <c r="E23" s="608" t="n"/>
+      <c r="F23" s="609" t="n"/>
+      <c r="G23" s="608" t="n"/>
+      <c r="H23" s="608" t="n"/>
+      <c r="I23" s="608" t="n"/>
+      <c r="J23" s="413" t="n"/>
+      <c r="K23" s="413" t="n"/>
+      <c r="L23" s="413" t="n"/>
+      <c r="M23" s="413" t="n"/>
+      <c r="N23" s="413" t="n"/>
+      <c r="O23" s="413" t="n"/>
+      <c r="P23" s="413" t="n"/>
+      <c r="Q23" s="413" t="n"/>
+      <c r="R23" s="413" t="n"/>
+      <c r="S23" s="413" t="n"/>
+      <c r="T23" s="413" t="n"/>
+      <c r="U23" s="413" t="n"/>
+      <c r="V23" s="413" t="n"/>
+      <c r="W23" s="413" t="n"/>
+      <c r="X23" s="413" t="n"/>
+      <c r="Y23" s="413" t="n"/>
+      <c r="Z23" s="413" t="n"/>
+      <c r="AA23" s="413" t="n"/>
+      <c r="AB23" s="413" t="n"/>
+      <c r="AC23" s="413" t="n"/>
+      <c r="AD23" s="413" t="n"/>
+      <c r="AE23" s="413" t="n"/>
+      <c r="AF23" s="413" t="n"/>
+      <c r="AG23" s="413" t="n"/>
+      <c r="AH23" s="413" t="n"/>
+      <c r="AI23" s="413" t="n"/>
+      <c r="AJ23" s="413" t="n"/>
+      <c r="AK23" s="413" t="n"/>
+      <c r="AL23" s="413" t="n"/>
+      <c r="AM23" s="413" t="n"/>
+      <c r="AN23" s="595" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="453">
+      <c r="A24" s="605">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B24" s="456" t="n"/>
-      <c r="C24" s="456" t="n"/>
-      <c r="D24" s="456" t="n"/>
-      <c r="E24" s="456" t="n"/>
-      <c r="F24" s="457" t="n"/>
-      <c r="G24" s="456" t="n"/>
-      <c r="H24" s="456" t="n"/>
-      <c r="I24" s="458" t="n"/>
-      <c r="J24" s="436" t="n"/>
-      <c r="K24" s="436" t="n"/>
-      <c r="L24" s="436" t="n"/>
-      <c r="M24" s="436" t="n"/>
-      <c r="N24" s="436" t="n"/>
-      <c r="O24" s="436" t="n"/>
-      <c r="P24" s="436" t="n"/>
-      <c r="Q24" s="436" t="n"/>
-      <c r="R24" s="436" t="n"/>
-      <c r="S24" s="436" t="n"/>
-      <c r="T24" s="436" t="n"/>
-      <c r="U24" s="436" t="n"/>
-      <c r="V24" s="436" t="n"/>
-      <c r="W24" s="436" t="n"/>
-      <c r="X24" s="436" t="n"/>
-      <c r="Y24" s="436" t="n"/>
-      <c r="Z24" s="436" t="n"/>
-      <c r="AA24" s="436" t="n"/>
-      <c r="AB24" s="436" t="n"/>
-      <c r="AC24" s="436" t="n"/>
-      <c r="AD24" s="436" t="n"/>
-      <c r="AE24" s="436" t="n"/>
-      <c r="AF24" s="436" t="n"/>
-      <c r="AG24" s="436" t="n"/>
-      <c r="AH24" s="436" t="n"/>
-      <c r="AI24" s="436" t="n"/>
-      <c r="AJ24" s="436" t="n"/>
-      <c r="AK24" s="436" t="n"/>
-      <c r="AL24" s="436" t="n"/>
-      <c r="AM24" s="436" t="n"/>
-      <c r="AN24" s="436" t="n"/>
+      <c r="B24" s="460" t="n"/>
+      <c r="C24" s="606" t="n"/>
+      <c r="D24" s="606" t="n"/>
+      <c r="E24" s="606" t="n"/>
+      <c r="F24" s="607" t="n"/>
+      <c r="G24" s="606" t="n"/>
+      <c r="H24" s="606" t="n"/>
+      <c r="I24" s="606" t="n"/>
+      <c r="J24" s="413" t="n"/>
+      <c r="K24" s="413" t="n"/>
+      <c r="L24" s="413" t="n"/>
+      <c r="M24" s="413" t="n"/>
+      <c r="N24" s="413" t="n"/>
+      <c r="O24" s="413" t="n"/>
+      <c r="P24" s="413" t="n"/>
+      <c r="Q24" s="413" t="n"/>
+      <c r="R24" s="413" t="n"/>
+      <c r="S24" s="413" t="n"/>
+      <c r="T24" s="413" t="n"/>
+      <c r="U24" s="413" t="n"/>
+      <c r="V24" s="413" t="n"/>
+      <c r="W24" s="413" t="n"/>
+      <c r="X24" s="413" t="n"/>
+      <c r="Y24" s="413" t="n"/>
+      <c r="Z24" s="413" t="n"/>
+      <c r="AA24" s="413" t="n"/>
+      <c r="AB24" s="413" t="n"/>
+      <c r="AC24" s="413" t="n"/>
+      <c r="AD24" s="413" t="n"/>
+      <c r="AE24" s="413" t="n"/>
+      <c r="AF24" s="413" t="n"/>
+      <c r="AG24" s="413" t="n"/>
+      <c r="AH24" s="413" t="n"/>
+      <c r="AI24" s="413" t="n"/>
+      <c r="AJ24" s="413" t="n"/>
+      <c r="AK24" s="413" t="n"/>
+      <c r="AL24" s="413" t="n"/>
+      <c r="AM24" s="413" t="n"/>
+      <c r="AN24" s="595" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="453">
+      <c r="A25" s="605">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B25" s="454" t="n"/>
-      <c r="C25" s="454" t="n"/>
-      <c r="D25" s="454" t="n"/>
-      <c r="E25" s="454" t="n"/>
-      <c r="F25" s="455" t="n"/>
-      <c r="G25" s="454" t="n"/>
-      <c r="H25" s="454" t="n"/>
-      <c r="I25" s="443" t="n"/>
-      <c r="J25" s="436" t="n"/>
-      <c r="K25" s="436" t="n"/>
-      <c r="L25" s="436" t="n"/>
-      <c r="M25" s="436" t="n"/>
-      <c r="N25" s="436" t="n"/>
-      <c r="O25" s="436" t="n"/>
-      <c r="P25" s="436" t="n"/>
-      <c r="Q25" s="436" t="n"/>
-      <c r="R25" s="436" t="n"/>
-      <c r="S25" s="436" t="n"/>
-      <c r="T25" s="436" t="n"/>
-      <c r="U25" s="436" t="n"/>
-      <c r="V25" s="436" t="n"/>
-      <c r="W25" s="436" t="n"/>
-      <c r="X25" s="436" t="n"/>
-      <c r="Y25" s="436" t="n"/>
-      <c r="Z25" s="436" t="n"/>
-      <c r="AA25" s="436" t="n"/>
-      <c r="AB25" s="436" t="n"/>
-      <c r="AC25" s="436" t="n"/>
-      <c r="AD25" s="436" t="n"/>
-      <c r="AE25" s="436" t="n"/>
-      <c r="AF25" s="436" t="n"/>
-      <c r="AG25" s="436" t="n"/>
-      <c r="AH25" s="436" t="n"/>
-      <c r="AI25" s="436" t="n"/>
-      <c r="AJ25" s="436" t="n"/>
-      <c r="AK25" s="436" t="n"/>
-      <c r="AL25" s="436" t="n"/>
-      <c r="AM25" s="436" t="n"/>
-      <c r="AN25" s="436" t="n"/>
+      <c r="B25" s="592" t="n"/>
+      <c r="C25" s="608" t="n"/>
+      <c r="D25" s="608" t="n"/>
+      <c r="E25" s="608" t="n"/>
+      <c r="F25" s="609" t="n"/>
+      <c r="G25" s="608" t="n"/>
+      <c r="H25" s="608" t="n"/>
+      <c r="I25" s="608" t="n"/>
+      <c r="J25" s="413" t="n"/>
+      <c r="K25" s="413" t="n"/>
+      <c r="L25" s="413" t="n"/>
+      <c r="M25" s="413" t="n"/>
+      <c r="N25" s="413" t="n"/>
+      <c r="O25" s="413" t="n"/>
+      <c r="P25" s="413" t="n"/>
+      <c r="Q25" s="413" t="n"/>
+      <c r="R25" s="413" t="n"/>
+      <c r="S25" s="413" t="n"/>
+      <c r="T25" s="413" t="n"/>
+      <c r="U25" s="413" t="n"/>
+      <c r="V25" s="413" t="n"/>
+      <c r="W25" s="413" t="n"/>
+      <c r="X25" s="413" t="n"/>
+      <c r="Y25" s="413" t="n"/>
+      <c r="Z25" s="413" t="n"/>
+      <c r="AA25" s="413" t="n"/>
+      <c r="AB25" s="413" t="n"/>
+      <c r="AC25" s="413" t="n"/>
+      <c r="AD25" s="413" t="n"/>
+      <c r="AE25" s="413" t="n"/>
+      <c r="AF25" s="413" t="n"/>
+      <c r="AG25" s="413" t="n"/>
+      <c r="AH25" s="413" t="n"/>
+      <c r="AI25" s="413" t="n"/>
+      <c r="AJ25" s="413" t="n"/>
+      <c r="AK25" s="413" t="n"/>
+      <c r="AL25" s="413" t="n"/>
+      <c r="AM25" s="413" t="n"/>
+      <c r="AN25" s="595" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="459">
+      <c r="A26" s="605">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
       <c r="B26" s="460" t="n"/>
-      <c r="C26" s="460" t="n"/>
-      <c r="D26" s="460" t="n"/>
-      <c r="E26" s="460" t="n"/>
-      <c r="F26" s="461" t="n"/>
-      <c r="G26" s="460" t="n"/>
-      <c r="H26" s="460" t="n"/>
-      <c r="I26" s="462" t="n"/>
-      <c r="J26" s="436" t="n"/>
-      <c r="K26" s="436" t="n"/>
-      <c r="L26" s="436" t="n"/>
-      <c r="M26" s="436" t="n"/>
-      <c r="N26" s="436" t="n"/>
-      <c r="O26" s="436" t="n"/>
-      <c r="P26" s="436" t="n"/>
-      <c r="Q26" s="436" t="n"/>
-      <c r="R26" s="436" t="n"/>
-      <c r="S26" s="436" t="n"/>
-      <c r="T26" s="436" t="n"/>
-      <c r="U26" s="436" t="n"/>
-      <c r="V26" s="436" t="n"/>
-      <c r="W26" s="436" t="n"/>
-      <c r="X26" s="436" t="n"/>
-      <c r="Y26" s="436" t="n"/>
-      <c r="Z26" s="436" t="n"/>
-      <c r="AA26" s="436" t="n"/>
-      <c r="AB26" s="436" t="n"/>
-      <c r="AC26" s="436" t="n"/>
-      <c r="AD26" s="436" t="n"/>
-      <c r="AE26" s="436" t="n"/>
-      <c r="AF26" s="436" t="n"/>
-      <c r="AG26" s="436" t="n"/>
-      <c r="AH26" s="436" t="n"/>
-      <c r="AI26" s="436" t="n"/>
-      <c r="AJ26" s="436" t="n"/>
-      <c r="AK26" s="436" t="n"/>
-      <c r="AL26" s="436" t="n"/>
-      <c r="AM26" s="436" t="n"/>
-      <c r="AN26" s="436" t="n"/>
+      <c r="C26" s="606" t="n"/>
+      <c r="D26" s="606" t="n"/>
+      <c r="E26" s="606" t="n"/>
+      <c r="F26" s="607" t="n"/>
+      <c r="G26" s="606" t="n"/>
+      <c r="H26" s="606" t="n"/>
+      <c r="I26" s="606" t="n"/>
+      <c r="J26" s="413" t="n"/>
+      <c r="K26" s="413" t="n"/>
+      <c r="L26" s="413" t="n"/>
+      <c r="M26" s="413" t="n"/>
+      <c r="N26" s="413" t="n"/>
+      <c r="O26" s="413" t="n"/>
+      <c r="P26" s="413" t="n"/>
+      <c r="Q26" s="413" t="n"/>
+      <c r="R26" s="413" t="n"/>
+      <c r="S26" s="413" t="n"/>
+      <c r="T26" s="413" t="n"/>
+      <c r="U26" s="413" t="n"/>
+      <c r="V26" s="413" t="n"/>
+      <c r="W26" s="413" t="n"/>
+      <c r="X26" s="413" t="n"/>
+      <c r="Y26" s="413" t="n"/>
+      <c r="Z26" s="413" t="n"/>
+      <c r="AA26" s="413" t="n"/>
+      <c r="AB26" s="413" t="n"/>
+      <c r="AC26" s="413" t="n"/>
+      <c r="AD26" s="413" t="n"/>
+      <c r="AE26" s="413" t="n"/>
+      <c r="AF26" s="413" t="n"/>
+      <c r="AG26" s="413" t="n"/>
+      <c r="AH26" s="413" t="n"/>
+      <c r="AI26" s="413" t="n"/>
+      <c r="AJ26" s="413" t="n"/>
+      <c r="AK26" s="413" t="n"/>
+      <c r="AL26" s="413" t="n"/>
+      <c r="AM26" s="413" t="n"/>
+      <c r="AN26" s="595" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="436" t="n"/>
-      <c r="B27" s="436" t="n"/>
-      <c r="C27" s="436" t="n"/>
-      <c r="D27" s="436" t="n"/>
-      <c r="E27" s="436" t="n"/>
-      <c r="F27" s="436" t="n"/>
-      <c r="G27" s="436" t="n"/>
-      <c r="H27" s="436" t="n"/>
-      <c r="I27" s="436" t="n"/>
-      <c r="J27" s="436" t="n"/>
-      <c r="K27" s="436" t="n"/>
-      <c r="L27" s="436" t="n"/>
-      <c r="M27" s="436" t="n"/>
-      <c r="N27" s="436" t="n"/>
-      <c r="O27" s="436" t="n"/>
-      <c r="P27" s="436" t="n"/>
-      <c r="Q27" s="436" t="n"/>
-      <c r="R27" s="436" t="n"/>
-      <c r="S27" s="436" t="n"/>
-      <c r="T27" s="436" t="n"/>
-      <c r="U27" s="436" t="n"/>
-      <c r="V27" s="436" t="n"/>
-      <c r="W27" s="436" t="n"/>
-      <c r="X27" s="436" t="n"/>
-      <c r="Y27" s="436" t="n"/>
-      <c r="Z27" s="436" t="n"/>
-      <c r="AA27" s="436" t="n"/>
-      <c r="AB27" s="436" t="n"/>
-      <c r="AC27" s="436" t="n"/>
-      <c r="AD27" s="436" t="n"/>
-      <c r="AE27" s="436" t="n"/>
-      <c r="AF27" s="436" t="n"/>
-      <c r="AG27" s="436" t="n"/>
-      <c r="AH27" s="436" t="n"/>
-      <c r="AI27" s="436" t="n"/>
-      <c r="AJ27" s="436" t="n"/>
-      <c r="AK27" s="436" t="n"/>
-      <c r="AL27" s="436" t="n"/>
-      <c r="AM27" s="436" t="n"/>
-      <c r="AN27" s="436" t="n"/>
+      <c r="A27" s="610" t="n"/>
+      <c r="B27" s="599" t="n"/>
+      <c r="C27" s="600" t="n"/>
+      <c r="D27" s="600" t="n"/>
+      <c r="E27" s="600" t="n"/>
+      <c r="F27" s="600" t="n"/>
+      <c r="G27" s="600" t="n"/>
+      <c r="H27" s="600" t="n"/>
+      <c r="I27" s="600" t="n"/>
+      <c r="J27" s="600" t="n"/>
+      <c r="K27" s="600" t="n"/>
+      <c r="L27" s="600" t="n"/>
+      <c r="M27" s="600" t="n"/>
+      <c r="N27" s="600" t="n"/>
+      <c r="O27" s="600" t="n"/>
+      <c r="P27" s="600" t="n"/>
+      <c r="Q27" s="600" t="n"/>
+      <c r="R27" s="600" t="n"/>
+      <c r="S27" s="600" t="n"/>
+      <c r="T27" s="600" t="n"/>
+      <c r="U27" s="600" t="n"/>
+      <c r="V27" s="600" t="n"/>
+      <c r="W27" s="600" t="n"/>
+      <c r="X27" s="600" t="n"/>
+      <c r="Y27" s="600" t="n"/>
+      <c r="Z27" s="600" t="n"/>
+      <c r="AA27" s="600" t="n"/>
+      <c r="AB27" s="600" t="n"/>
+      <c r="AC27" s="600" t="n"/>
+      <c r="AD27" s="600" t="n"/>
+      <c r="AE27" s="600" t="n"/>
+      <c r="AF27" s="600" t="n"/>
+      <c r="AG27" s="600" t="n"/>
+      <c r="AH27" s="600" t="n"/>
+      <c r="AI27" s="600" t="n"/>
+      <c r="AJ27" s="600" t="n"/>
+      <c r="AK27" s="600" t="n"/>
+      <c r="AL27" s="600" t="n"/>
+      <c r="AM27" s="600" t="n"/>
+      <c r="AN27" s="601" t="n"/>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="451" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="531" t="inlineStr">
         <is>
           <t>NOTICE  —  One line per material, capacity, quality or customer-risk condition.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B28" s="467" t="n"/>
-      <c r="C28" s="467" t="n"/>
-      <c r="D28" s="467" t="n"/>
-      <c r="E28" s="467" t="n"/>
-      <c r="F28" s="467" t="n"/>
-      <c r="G28" s="467" t="n"/>
-      <c r="H28" s="467" t="n"/>
-      <c r="I28" s="468" t="n"/>
-      <c r="J28" s="402" t="n"/>
-      <c r="K28" s="402" t="n"/>
-      <c r="L28" s="402" t="n"/>
-      <c r="M28" s="402" t="n"/>
-      <c r="N28" s="402" t="n"/>
-      <c r="O28" s="402" t="n"/>
-      <c r="P28" s="402" t="n"/>
-      <c r="Q28" s="402" t="n"/>
-      <c r="R28" s="402" t="n"/>
-      <c r="S28" s="402" t="n"/>
-      <c r="T28" s="402" t="n"/>
-      <c r="U28" s="402" t="n"/>
-      <c r="V28" s="402" t="n"/>
-      <c r="W28" s="402" t="n"/>
-      <c r="X28" s="402" t="n"/>
-      <c r="Y28" s="402" t="n"/>
-      <c r="Z28" s="402" t="n"/>
-      <c r="AA28" s="402" t="n"/>
-      <c r="AB28" s="402" t="n"/>
-      <c r="AC28" s="402" t="n"/>
-      <c r="AD28" s="402" t="n"/>
-      <c r="AE28" s="402" t="n"/>
-      <c r="AF28" s="402" t="n"/>
-      <c r="AG28" s="402" t="n"/>
-      <c r="AH28" s="402" t="n"/>
-      <c r="AI28" s="402" t="n"/>
-      <c r="AJ28" s="402" t="n"/>
-      <c r="AK28" s="402" t="n"/>
-      <c r="AL28" s="402" t="n"/>
-      <c r="AM28" s="402" t="n"/>
-      <c r="AN28" s="402" t="n"/>
+      <c r="B28" s="532" t="n"/>
+      <c r="C28" s="532" t="n"/>
+      <c r="D28" s="532" t="n"/>
+      <c r="E28" s="532" t="n"/>
+      <c r="F28" s="532" t="n"/>
+      <c r="G28" s="532" t="n"/>
+      <c r="H28" s="532" t="n"/>
+      <c r="I28" s="532" t="n"/>
+      <c r="J28" s="532" t="n"/>
+      <c r="K28" s="532" t="n"/>
+      <c r="L28" s="532" t="n"/>
+      <c r="M28" s="532" t="n"/>
+      <c r="N28" s="532" t="n"/>
+      <c r="O28" s="532" t="n"/>
+      <c r="P28" s="532" t="n"/>
+      <c r="Q28" s="532" t="n"/>
+      <c r="R28" s="532" t="n"/>
+      <c r="S28" s="532" t="n"/>
+      <c r="T28" s="532" t="n"/>
+      <c r="U28" s="532" t="n"/>
+      <c r="V28" s="532" t="n"/>
+      <c r="W28" s="532" t="n"/>
+      <c r="X28" s="532" t="n"/>
+      <c r="Y28" s="532" t="n"/>
+      <c r="Z28" s="532" t="n"/>
+      <c r="AA28" s="532" t="n"/>
+      <c r="AB28" s="532" t="n"/>
+      <c r="AC28" s="532" t="n"/>
+      <c r="AD28" s="532" t="n"/>
+      <c r="AE28" s="532" t="n"/>
+      <c r="AF28" s="532" t="n"/>
+      <c r="AG28" s="532" t="n"/>
+      <c r="AH28" s="532" t="n"/>
+      <c r="AI28" s="532" t="n"/>
+      <c r="AJ28" s="532" t="n"/>
+      <c r="AK28" s="532" t="n"/>
+      <c r="AL28" s="532" t="n"/>
+      <c r="AM28" s="532" t="n"/>
+      <c r="AN28" s="533" t="n"/>
     </row>
     <row r="29" hidden="1" outlineLevel="1"/>
     <row r="30" hidden="1" outlineLevel="1"/>
@@ -11239,7 +12098,7 @@
     <row r="199" hidden="1" outlineLevel="1"/>
     <row r="200" hidden="1" outlineLevel="1"/>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="28">
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="F10:G10"/>
@@ -11260,13 +12119,11 @@
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="C1:G3"/>
     <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="H12:I12"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A6:I6"/>
     <mergeCell ref="H8:I8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C10:E10"/>
@@ -11290,8 +12147,9 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -11347,497 +12205,503 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="463" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="611" t="inlineStr">
         <is>
           <t>REF LINKS</t>
         </is>
       </c>
-      <c r="B1" s="484" t="n"/>
-      <c r="C1" s="484" t="n"/>
-      <c r="D1" s="484" t="n"/>
-      <c r="E1" s="484" t="n"/>
-      <c r="F1" s="484" t="n"/>
-      <c r="G1" s="485" t="n"/>
-      <c r="H1" s="402" t="n"/>
-      <c r="I1" s="402" t="n"/>
-      <c r="J1" s="402" t="n"/>
-      <c r="K1" s="402" t="n"/>
-      <c r="L1" s="402" t="n"/>
-      <c r="M1" s="402" t="n"/>
-      <c r="N1" s="402" t="n"/>
-      <c r="O1" s="402" t="n"/>
-      <c r="P1" s="402" t="n"/>
-      <c r="Q1" s="402" t="n"/>
-      <c r="R1" s="402" t="n"/>
-      <c r="S1" s="402" t="n"/>
-      <c r="T1" s="402" t="n"/>
-      <c r="U1" s="402" t="n"/>
-      <c r="V1" s="402" t="n"/>
-      <c r="W1" s="402" t="n"/>
-      <c r="X1" s="402" t="n"/>
-      <c r="Y1" s="402" t="n"/>
-      <c r="Z1" s="402" t="n"/>
-      <c r="AA1" s="402" t="n"/>
-      <c r="AB1" s="402" t="n"/>
-      <c r="AC1" s="402" t="n"/>
-      <c r="AD1" s="402" t="n"/>
-      <c r="AE1" s="402" t="n"/>
-      <c r="AF1" s="402" t="n"/>
-      <c r="AG1" s="402" t="n"/>
-      <c r="AH1" s="402" t="n"/>
-      <c r="AI1" s="402" t="n"/>
-      <c r="AJ1" s="402" t="n"/>
-      <c r="AK1" s="402" t="n"/>
-      <c r="AL1" s="402" t="n"/>
-      <c r="AM1" s="402" t="n"/>
-      <c r="AN1" s="402" t="n"/>
+      <c r="B1" s="493" t="n"/>
+      <c r="C1" s="493" t="n"/>
+      <c r="D1" s="493" t="n"/>
+      <c r="E1" s="493" t="n"/>
+      <c r="F1" s="493" t="n"/>
+      <c r="G1" s="493" t="n"/>
+      <c r="H1" s="612" t="n"/>
+      <c r="I1" s="495" t="n"/>
+      <c r="J1" s="496" t="n"/>
+      <c r="K1" s="496" t="n"/>
+      <c r="L1" s="496" t="n"/>
+      <c r="M1" s="496" t="n"/>
+      <c r="N1" s="496" t="n"/>
+      <c r="O1" s="496" t="n"/>
+      <c r="P1" s="496" t="n"/>
+      <c r="Q1" s="496" t="n"/>
+      <c r="R1" s="496" t="n"/>
+      <c r="S1" s="496" t="n"/>
+      <c r="T1" s="496" t="n"/>
+      <c r="U1" s="496" t="n"/>
+      <c r="V1" s="496" t="n"/>
+      <c r="W1" s="496" t="n"/>
+      <c r="X1" s="496" t="n"/>
+      <c r="Y1" s="496" t="n"/>
+      <c r="Z1" s="496" t="n"/>
+      <c r="AA1" s="496" t="n"/>
+      <c r="AB1" s="496" t="n"/>
+      <c r="AC1" s="496" t="n"/>
+      <c r="AD1" s="497" t="n"/>
+      <c r="AE1" s="498" t="n"/>
+      <c r="AF1" s="499" t="n"/>
+      <c r="AG1" s="499" t="n"/>
+      <c r="AH1" s="500" t="n"/>
+      <c r="AI1" s="501" t="n"/>
+      <c r="AJ1" s="502" t="n"/>
+      <c r="AK1" s="502" t="n"/>
+      <c r="AL1" s="502" t="n"/>
+      <c r="AM1" s="502" t="n"/>
+      <c r="AN1" s="503" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" s="323" t="inlineStr">
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="613" t="inlineStr">
         <is>
           <t>Reference release package, planner snapshot and dossier evidence only.</t>
         </is>
       </c>
-      <c r="H2" s="402" t="n"/>
-      <c r="I2" s="402" t="n"/>
-      <c r="J2" s="402" t="n"/>
-      <c r="K2" s="402" t="n"/>
-      <c r="L2" s="402" t="n"/>
-      <c r="M2" s="402" t="n"/>
-      <c r="N2" s="402" t="n"/>
-      <c r="O2" s="402" t="n"/>
-      <c r="P2" s="402" t="n"/>
-      <c r="Q2" s="402" t="n"/>
-      <c r="R2" s="402" t="n"/>
-      <c r="S2" s="402" t="n"/>
-      <c r="T2" s="402" t="n"/>
-      <c r="U2" s="402" t="n"/>
-      <c r="V2" s="402" t="n"/>
-      <c r="W2" s="402" t="n"/>
-      <c r="X2" s="402" t="n"/>
-      <c r="Y2" s="402" t="n"/>
-      <c r="Z2" s="402" t="n"/>
-      <c r="AA2" s="402" t="n"/>
-      <c r="AB2" s="402" t="n"/>
-      <c r="AC2" s="402" t="n"/>
-      <c r="AD2" s="402" t="n"/>
-      <c r="AE2" s="402" t="n"/>
-      <c r="AF2" s="402" t="n"/>
-      <c r="AG2" s="402" t="n"/>
-      <c r="AH2" s="402" t="n"/>
-      <c r="AI2" s="402" t="n"/>
-      <c r="AJ2" s="402" t="n"/>
-      <c r="AK2" s="402" t="n"/>
-      <c r="AL2" s="402" t="n"/>
-      <c r="AM2" s="402" t="n"/>
-      <c r="AN2" s="402" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="614" t="n"/>
+      <c r="I2" s="506" t="n"/>
+      <c r="J2" s="507" t="n"/>
+      <c r="K2" s="507" t="n"/>
+      <c r="L2" s="507" t="n"/>
+      <c r="M2" s="507" t="n"/>
+      <c r="N2" s="507" t="n"/>
+      <c r="O2" s="507" t="n"/>
+      <c r="P2" s="507" t="n"/>
+      <c r="Q2" s="507" t="n"/>
+      <c r="R2" s="507" t="n"/>
+      <c r="S2" s="507" t="n"/>
+      <c r="T2" s="507" t="n"/>
+      <c r="U2" s="507" t="n"/>
+      <c r="V2" s="507" t="n"/>
+      <c r="W2" s="507" t="n"/>
+      <c r="X2" s="507" t="n"/>
+      <c r="Y2" s="507" t="n"/>
+      <c r="Z2" s="507" t="n"/>
+      <c r="AA2" s="507" t="n"/>
+      <c r="AB2" s="507" t="n"/>
+      <c r="AC2" s="507" t="n"/>
+      <c r="AD2" s="508" t="n"/>
+      <c r="AE2" s="509" t="n"/>
+      <c r="AF2" s="510" t="n"/>
+      <c r="AG2" s="510" t="n"/>
+      <c r="AH2" s="511" t="n"/>
+      <c r="AI2" s="512" t="n"/>
+      <c r="AJ2" s="513" t="n"/>
+      <c r="AK2" s="513" t="n"/>
+      <c r="AL2" s="513" t="n"/>
+      <c r="AM2" s="513" t="n"/>
+      <c r="AN2" s="514" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="464" t="inlineStr">
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="615" t="inlineStr">
         <is>
           <t>Ref Type</t>
         </is>
       </c>
-      <c r="B3" s="464" t="inlineStr">
+      <c r="B3" s="616" t="inlineStr">
         <is>
           <t>Document / Record</t>
         </is>
       </c>
-      <c r="C3" s="464" t="inlineStr">
+      <c r="C3" s="616" t="inlineStr">
         <is>
           <t>System of Record</t>
         </is>
       </c>
-      <c r="D3" s="464" t="inlineStr">
+      <c r="D3" s="616" t="inlineStr">
         <is>
           <t>Unique Ref</t>
         </is>
       </c>
-      <c r="E3" s="464" t="inlineStr">
+      <c r="E3" s="616" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F3" s="464" t="inlineStr">
+      <c r="F3" s="616" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G3" s="464" t="inlineStr">
+      <c r="G3" s="616" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="H3" s="402" t="n"/>
-      <c r="I3" s="402" t="n"/>
-      <c r="J3" s="402" t="n"/>
-      <c r="K3" s="402" t="n"/>
-      <c r="L3" s="402" t="n"/>
-      <c r="M3" s="402" t="n"/>
-      <c r="N3" s="402" t="n"/>
-      <c r="O3" s="402" t="n"/>
-      <c r="P3" s="402" t="n"/>
-      <c r="Q3" s="402" t="n"/>
-      <c r="R3" s="402" t="n"/>
-      <c r="S3" s="402" t="n"/>
-      <c r="T3" s="402" t="n"/>
-      <c r="U3" s="402" t="n"/>
-      <c r="V3" s="402" t="n"/>
-      <c r="W3" s="402" t="n"/>
-      <c r="X3" s="402" t="n"/>
-      <c r="Y3" s="402" t="n"/>
-      <c r="Z3" s="402" t="n"/>
-      <c r="AA3" s="402" t="n"/>
-      <c r="AB3" s="402" t="n"/>
-      <c r="AC3" s="402" t="n"/>
-      <c r="AD3" s="402" t="n"/>
-      <c r="AE3" s="402" t="n"/>
-      <c r="AF3" s="402" t="n"/>
-      <c r="AG3" s="402" t="n"/>
-      <c r="AH3" s="402" t="n"/>
-      <c r="AI3" s="402" t="n"/>
-      <c r="AJ3" s="402" t="n"/>
-      <c r="AK3" s="402" t="n"/>
-      <c r="AL3" s="402" t="n"/>
-      <c r="AM3" s="402" t="n"/>
-      <c r="AN3" s="402" t="n"/>
+      <c r="H3" s="614" t="n"/>
+      <c r="I3" s="506" t="n"/>
+      <c r="J3" s="507" t="n"/>
+      <c r="K3" s="507" t="n"/>
+      <c r="L3" s="507" t="n"/>
+      <c r="M3" s="507" t="n"/>
+      <c r="N3" s="507" t="n"/>
+      <c r="O3" s="507" t="n"/>
+      <c r="P3" s="507" t="n"/>
+      <c r="Q3" s="507" t="n"/>
+      <c r="R3" s="507" t="n"/>
+      <c r="S3" s="507" t="n"/>
+      <c r="T3" s="507" t="n"/>
+      <c r="U3" s="507" t="n"/>
+      <c r="V3" s="507" t="n"/>
+      <c r="W3" s="507" t="n"/>
+      <c r="X3" s="507" t="n"/>
+      <c r="Y3" s="507" t="n"/>
+      <c r="Z3" s="507" t="n"/>
+      <c r="AA3" s="507" t="n"/>
+      <c r="AB3" s="507" t="n"/>
+      <c r="AC3" s="507" t="n"/>
+      <c r="AD3" s="508" t="n"/>
+      <c r="AE3" s="509" t="n"/>
+      <c r="AF3" s="510" t="n"/>
+      <c r="AG3" s="510" t="n"/>
+      <c r="AH3" s="511" t="n"/>
+      <c r="AI3" s="512" t="n"/>
+      <c r="AJ3" s="513" t="n"/>
+      <c r="AK3" s="513" t="n"/>
+      <c r="AL3" s="513" t="n"/>
+      <c r="AM3" s="513" t="n"/>
+      <c r="AN3" s="514" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="427" t="n"/>
-      <c r="B4" s="427" t="n"/>
-      <c r="C4" s="427" t="n"/>
-      <c r="D4" s="427" t="n"/>
-      <c r="E4" s="427" t="n"/>
-      <c r="F4" s="427" t="n"/>
-      <c r="G4" s="427" t="n"/>
-      <c r="H4" s="402" t="n"/>
-      <c r="I4" s="402" t="n"/>
-      <c r="J4" s="402" t="n"/>
-      <c r="K4" s="402" t="n"/>
-      <c r="L4" s="402" t="n"/>
-      <c r="M4" s="402" t="n"/>
-      <c r="N4" s="402" t="n"/>
-      <c r="O4" s="402" t="n"/>
-      <c r="P4" s="402" t="n"/>
-      <c r="Q4" s="402" t="n"/>
-      <c r="R4" s="402" t="n"/>
-      <c r="S4" s="402" t="n"/>
-      <c r="T4" s="402" t="n"/>
-      <c r="U4" s="402" t="n"/>
-      <c r="V4" s="402" t="n"/>
-      <c r="W4" s="402" t="n"/>
-      <c r="X4" s="402" t="n"/>
-      <c r="Y4" s="402" t="n"/>
-      <c r="Z4" s="402" t="n"/>
-      <c r="AA4" s="402" t="n"/>
-      <c r="AB4" s="402" t="n"/>
-      <c r="AC4" s="402" t="n"/>
-      <c r="AD4" s="402" t="n"/>
-      <c r="AE4" s="402" t="n"/>
-      <c r="AF4" s="402" t="n"/>
-      <c r="AG4" s="402" t="n"/>
-      <c r="AH4" s="402" t="n"/>
-      <c r="AI4" s="402" t="n"/>
-      <c r="AJ4" s="402" t="n"/>
-      <c r="AK4" s="402" t="n"/>
-      <c r="AL4" s="402" t="n"/>
-      <c r="AM4" s="402" t="n"/>
-      <c r="AN4" s="402" t="n"/>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="617" t="n"/>
+      <c r="B4" s="618" t="n"/>
+      <c r="C4" s="618" t="n"/>
+      <c r="D4" s="618" t="n"/>
+      <c r="E4" s="618" t="n"/>
+      <c r="F4" s="618" t="n"/>
+      <c r="G4" s="618" t="n"/>
+      <c r="H4" s="614" t="n"/>
+      <c r="I4" s="515" t="n"/>
+      <c r="J4" s="516" t="n"/>
+      <c r="K4" s="516" t="n"/>
+      <c r="L4" s="516" t="n"/>
+      <c r="M4" s="516" t="n"/>
+      <c r="N4" s="516" t="n"/>
+      <c r="O4" s="516" t="n"/>
+      <c r="P4" s="516" t="n"/>
+      <c r="Q4" s="516" t="n"/>
+      <c r="R4" s="516" t="n"/>
+      <c r="S4" s="516" t="n"/>
+      <c r="T4" s="516" t="n"/>
+      <c r="U4" s="516" t="n"/>
+      <c r="V4" s="516" t="n"/>
+      <c r="W4" s="516" t="n"/>
+      <c r="X4" s="516" t="n"/>
+      <c r="Y4" s="516" t="n"/>
+      <c r="Z4" s="516" t="n"/>
+      <c r="AA4" s="516" t="n"/>
+      <c r="AB4" s="516" t="n"/>
+      <c r="AC4" s="516" t="n"/>
+      <c r="AD4" s="517" t="n"/>
+      <c r="AE4" s="509" t="n"/>
+      <c r="AF4" s="510" t="n"/>
+      <c r="AG4" s="510" t="n"/>
+      <c r="AH4" s="511" t="n"/>
+      <c r="AI4" s="512" t="n"/>
+      <c r="AJ4" s="513" t="n"/>
+      <c r="AK4" s="513" t="n"/>
+      <c r="AL4" s="513" t="n"/>
+      <c r="AM4" s="513" t="n"/>
+      <c r="AN4" s="514" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="465" t="n"/>
-      <c r="B5" s="465" t="n"/>
-      <c r="C5" s="465" t="n"/>
-      <c r="D5" s="465" t="n"/>
-      <c r="E5" s="465" t="n"/>
-      <c r="F5" s="465" t="n"/>
-      <c r="G5" s="465" t="n"/>
-      <c r="H5" s="402" t="n"/>
-      <c r="I5" s="402" t="n"/>
-      <c r="J5" s="402" t="n"/>
-      <c r="K5" s="402" t="n"/>
-      <c r="L5" s="402" t="n"/>
-      <c r="M5" s="402" t="n"/>
-      <c r="N5" s="402" t="n"/>
-      <c r="O5" s="402" t="n"/>
-      <c r="P5" s="402" t="n"/>
-      <c r="Q5" s="402" t="n"/>
-      <c r="R5" s="402" t="n"/>
-      <c r="S5" s="402" t="n"/>
-      <c r="T5" s="402" t="n"/>
-      <c r="U5" s="402" t="n"/>
-      <c r="V5" s="402" t="n"/>
-      <c r="W5" s="402" t="n"/>
-      <c r="X5" s="402" t="n"/>
-      <c r="Y5" s="402" t="n"/>
-      <c r="Z5" s="402" t="n"/>
-      <c r="AA5" s="402" t="n"/>
-      <c r="AB5" s="402" t="n"/>
-      <c r="AC5" s="402" t="n"/>
-      <c r="AD5" s="402" t="n"/>
-      <c r="AE5" s="402" t="n"/>
-      <c r="AF5" s="402" t="n"/>
-      <c r="AG5" s="402" t="n"/>
-      <c r="AH5" s="402" t="n"/>
-      <c r="AI5" s="402" t="n"/>
-      <c r="AJ5" s="402" t="n"/>
-      <c r="AK5" s="402" t="n"/>
-      <c r="AL5" s="402" t="n"/>
-      <c r="AM5" s="402" t="n"/>
-      <c r="AN5" s="402" t="n"/>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="619" t="n"/>
+      <c r="B5" s="620" t="n"/>
+      <c r="C5" s="620" t="n"/>
+      <c r="D5" s="620" t="n"/>
+      <c r="E5" s="620" t="n"/>
+      <c r="F5" s="620" t="n"/>
+      <c r="G5" s="620" t="n"/>
+      <c r="H5" s="621" t="n"/>
+      <c r="I5" s="521" t="n"/>
+      <c r="J5" s="522" t="n"/>
+      <c r="K5" s="522" t="n"/>
+      <c r="L5" s="522" t="n"/>
+      <c r="M5" s="522" t="n"/>
+      <c r="N5" s="522" t="n"/>
+      <c r="O5" s="522" t="n"/>
+      <c r="P5" s="522" t="n"/>
+      <c r="Q5" s="522" t="n"/>
+      <c r="R5" s="522" t="n"/>
+      <c r="S5" s="522" t="n"/>
+      <c r="T5" s="522" t="n"/>
+      <c r="U5" s="522" t="n"/>
+      <c r="V5" s="522" t="n"/>
+      <c r="W5" s="522" t="n"/>
+      <c r="X5" s="522" t="n"/>
+      <c r="Y5" s="522" t="n"/>
+      <c r="Z5" s="522" t="n"/>
+      <c r="AA5" s="522" t="n"/>
+      <c r="AB5" s="522" t="n"/>
+      <c r="AC5" s="522" t="n"/>
+      <c r="AD5" s="523" t="n"/>
+      <c r="AE5" s="524" t="n"/>
+      <c r="AF5" s="525" t="n"/>
+      <c r="AG5" s="525" t="n"/>
+      <c r="AH5" s="526" t="n"/>
+      <c r="AI5" s="527" t="n"/>
+      <c r="AJ5" s="528" t="n"/>
+      <c r="AK5" s="528" t="n"/>
+      <c r="AL5" s="528" t="n"/>
+      <c r="AM5" s="528" t="n"/>
+      <c r="AN5" s="529" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="427" t="n"/>
-      <c r="B6" s="427" t="n"/>
-      <c r="C6" s="427" t="n"/>
-      <c r="D6" s="427" t="n"/>
-      <c r="E6" s="427" t="n"/>
-      <c r="F6" s="427" t="n"/>
-      <c r="G6" s="427" t="n"/>
-      <c r="H6" s="402" t="n"/>
-      <c r="I6" s="402" t="n"/>
-      <c r="J6" s="402" t="n"/>
-      <c r="K6" s="402" t="n"/>
-      <c r="L6" s="402" t="n"/>
-      <c r="M6" s="402" t="n"/>
-      <c r="N6" s="402" t="n"/>
-      <c r="O6" s="402" t="n"/>
-      <c r="P6" s="402" t="n"/>
-      <c r="Q6" s="402" t="n"/>
-      <c r="R6" s="402" t="n"/>
-      <c r="S6" s="402" t="n"/>
-      <c r="T6" s="402" t="n"/>
-      <c r="U6" s="402" t="n"/>
-      <c r="V6" s="402" t="n"/>
-      <c r="W6" s="402" t="n"/>
-      <c r="X6" s="402" t="n"/>
-      <c r="Y6" s="402" t="n"/>
-      <c r="Z6" s="402" t="n"/>
-      <c r="AA6" s="402" t="n"/>
-      <c r="AB6" s="402" t="n"/>
-      <c r="AC6" s="402" t="n"/>
-      <c r="AD6" s="402" t="n"/>
-      <c r="AE6" s="402" t="n"/>
-      <c r="AF6" s="402" t="n"/>
-      <c r="AG6" s="402" t="n"/>
-      <c r="AH6" s="402" t="n"/>
-      <c r="AI6" s="402" t="n"/>
-      <c r="AJ6" s="402" t="n"/>
-      <c r="AK6" s="402" t="n"/>
-      <c r="AL6" s="402" t="n"/>
-      <c r="AM6" s="402" t="n"/>
-      <c r="AN6" s="402" t="n"/>
+      <c r="A6" s="622" t="n"/>
+      <c r="B6" s="623" t="n"/>
+      <c r="C6" s="623" t="n"/>
+      <c r="D6" s="623" t="n"/>
+      <c r="E6" s="623" t="n"/>
+      <c r="F6" s="623" t="n"/>
+      <c r="G6" s="623" t="n"/>
+      <c r="H6" s="535" t="n"/>
+      <c r="I6" s="535" t="n"/>
+      <c r="J6" s="535" t="n"/>
+      <c r="K6" s="535" t="n"/>
+      <c r="L6" s="535" t="n"/>
+      <c r="M6" s="535" t="n"/>
+      <c r="N6" s="535" t="n"/>
+      <c r="O6" s="535" t="n"/>
+      <c r="P6" s="535" t="n"/>
+      <c r="Q6" s="535" t="n"/>
+      <c r="R6" s="535" t="n"/>
+      <c r="S6" s="535" t="n"/>
+      <c r="T6" s="535" t="n"/>
+      <c r="U6" s="535" t="n"/>
+      <c r="V6" s="535" t="n"/>
+      <c r="W6" s="535" t="n"/>
+      <c r="X6" s="535" t="n"/>
+      <c r="Y6" s="535" t="n"/>
+      <c r="Z6" s="535" t="n"/>
+      <c r="AA6" s="535" t="n"/>
+      <c r="AB6" s="535" t="n"/>
+      <c r="AC6" s="535" t="n"/>
+      <c r="AD6" s="535" t="n"/>
+      <c r="AE6" s="535" t="n"/>
+      <c r="AF6" s="535" t="n"/>
+      <c r="AG6" s="535" t="n"/>
+      <c r="AH6" s="535" t="n"/>
+      <c r="AI6" s="535" t="n"/>
+      <c r="AJ6" s="535" t="n"/>
+      <c r="AK6" s="535" t="n"/>
+      <c r="AL6" s="535" t="n"/>
+      <c r="AM6" s="535" t="n"/>
+      <c r="AN6" s="538" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="465" t="n"/>
-      <c r="B7" s="465" t="n"/>
-      <c r="C7" s="465" t="n"/>
-      <c r="D7" s="465" t="n"/>
-      <c r="E7" s="465" t="n"/>
-      <c r="F7" s="465" t="n"/>
-      <c r="G7" s="465" t="n"/>
-      <c r="H7" s="402" t="n"/>
-      <c r="I7" s="402" t="n"/>
-      <c r="J7" s="402" t="n"/>
-      <c r="K7" s="402" t="n"/>
-      <c r="L7" s="402" t="n"/>
-      <c r="M7" s="402" t="n"/>
-      <c r="N7" s="402" t="n"/>
-      <c r="O7" s="402" t="n"/>
-      <c r="P7" s="402" t="n"/>
-      <c r="Q7" s="402" t="n"/>
-      <c r="R7" s="402" t="n"/>
-      <c r="S7" s="402" t="n"/>
-      <c r="T7" s="402" t="n"/>
-      <c r="U7" s="402" t="n"/>
-      <c r="V7" s="402" t="n"/>
-      <c r="W7" s="402" t="n"/>
-      <c r="X7" s="402" t="n"/>
-      <c r="Y7" s="402" t="n"/>
-      <c r="Z7" s="402" t="n"/>
-      <c r="AA7" s="402" t="n"/>
-      <c r="AB7" s="402" t="n"/>
-      <c r="AC7" s="402" t="n"/>
-      <c r="AD7" s="402" t="n"/>
-      <c r="AE7" s="402" t="n"/>
-      <c r="AF7" s="402" t="n"/>
-      <c r="AG7" s="402" t="n"/>
-      <c r="AH7" s="402" t="n"/>
-      <c r="AI7" s="402" t="n"/>
-      <c r="AJ7" s="402" t="n"/>
-      <c r="AK7" s="402" t="n"/>
-      <c r="AL7" s="402" t="n"/>
-      <c r="AM7" s="402" t="n"/>
-      <c r="AN7" s="402" t="n"/>
+      <c r="A7" s="624" t="n"/>
+      <c r="B7" s="625" t="n"/>
+      <c r="C7" s="625" t="n"/>
+      <c r="D7" s="625" t="n"/>
+      <c r="E7" s="625" t="n"/>
+      <c r="F7" s="625" t="n"/>
+      <c r="G7" s="625" t="n"/>
+      <c r="H7" s="398" t="n"/>
+      <c r="I7" s="398" t="n"/>
+      <c r="J7" s="398" t="n"/>
+      <c r="K7" s="398" t="n"/>
+      <c r="L7" s="398" t="n"/>
+      <c r="M7" s="398" t="n"/>
+      <c r="N7" s="398" t="n"/>
+      <c r="O7" s="398" t="n"/>
+      <c r="P7" s="398" t="n"/>
+      <c r="Q7" s="398" t="n"/>
+      <c r="R7" s="398" t="n"/>
+      <c r="S7" s="398" t="n"/>
+      <c r="T7" s="398" t="n"/>
+      <c r="U7" s="398" t="n"/>
+      <c r="V7" s="398" t="n"/>
+      <c r="W7" s="398" t="n"/>
+      <c r="X7" s="398" t="n"/>
+      <c r="Y7" s="398" t="n"/>
+      <c r="Z7" s="398" t="n"/>
+      <c r="AA7" s="398" t="n"/>
+      <c r="AB7" s="398" t="n"/>
+      <c r="AC7" s="398" t="n"/>
+      <c r="AD7" s="398" t="n"/>
+      <c r="AE7" s="398" t="n"/>
+      <c r="AF7" s="398" t="n"/>
+      <c r="AG7" s="398" t="n"/>
+      <c r="AH7" s="398" t="n"/>
+      <c r="AI7" s="398" t="n"/>
+      <c r="AJ7" s="398" t="n"/>
+      <c r="AK7" s="398" t="n"/>
+      <c r="AL7" s="398" t="n"/>
+      <c r="AM7" s="398" t="n"/>
+      <c r="AN7" s="542" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="427" t="n"/>
-      <c r="B8" s="427" t="n"/>
-      <c r="C8" s="427" t="n"/>
-      <c r="D8" s="427" t="n"/>
-      <c r="E8" s="427" t="n"/>
-      <c r="F8" s="427" t="n"/>
-      <c r="G8" s="427" t="n"/>
-      <c r="H8" s="436" t="n"/>
-      <c r="I8" s="436" t="n"/>
-      <c r="J8" s="436" t="n"/>
-      <c r="K8" s="436" t="n"/>
-      <c r="L8" s="436" t="n"/>
-      <c r="M8" s="436" t="n"/>
-      <c r="N8" s="436" t="n"/>
-      <c r="O8" s="436" t="n"/>
-      <c r="P8" s="436" t="n"/>
-      <c r="Q8" s="436" t="n"/>
-      <c r="R8" s="436" t="n"/>
-      <c r="S8" s="436" t="n"/>
-      <c r="T8" s="436" t="n"/>
-      <c r="U8" s="436" t="n"/>
-      <c r="V8" s="436" t="n"/>
-      <c r="W8" s="436" t="n"/>
-      <c r="X8" s="436" t="n"/>
-      <c r="Y8" s="436" t="n"/>
-      <c r="Z8" s="436" t="n"/>
-      <c r="AA8" s="436" t="n"/>
-      <c r="AB8" s="436" t="n"/>
-      <c r="AC8" s="436" t="n"/>
-      <c r="AD8" s="436" t="n"/>
-      <c r="AE8" s="436" t="n"/>
-      <c r="AF8" s="436" t="n"/>
-      <c r="AG8" s="436" t="n"/>
-      <c r="AH8" s="436" t="n"/>
-      <c r="AI8" s="436" t="n"/>
-      <c r="AJ8" s="436" t="n"/>
-      <c r="AK8" s="436" t="n"/>
-      <c r="AL8" s="436" t="n"/>
-      <c r="AM8" s="436" t="n"/>
-      <c r="AN8" s="436" t="n"/>
+      <c r="A8" s="626" t="n"/>
+      <c r="B8" s="627" t="n"/>
+      <c r="C8" s="627" t="n"/>
+      <c r="D8" s="627" t="n"/>
+      <c r="E8" s="627" t="n"/>
+      <c r="F8" s="627" t="n"/>
+      <c r="G8" s="627" t="n"/>
+      <c r="H8" s="413" t="n"/>
+      <c r="I8" s="413" t="n"/>
+      <c r="J8" s="413" t="n"/>
+      <c r="K8" s="413" t="n"/>
+      <c r="L8" s="413" t="n"/>
+      <c r="M8" s="413" t="n"/>
+      <c r="N8" s="413" t="n"/>
+      <c r="O8" s="413" t="n"/>
+      <c r="P8" s="413" t="n"/>
+      <c r="Q8" s="413" t="n"/>
+      <c r="R8" s="413" t="n"/>
+      <c r="S8" s="413" t="n"/>
+      <c r="T8" s="413" t="n"/>
+      <c r="U8" s="413" t="n"/>
+      <c r="V8" s="413" t="n"/>
+      <c r="W8" s="413" t="n"/>
+      <c r="X8" s="413" t="n"/>
+      <c r="Y8" s="413" t="n"/>
+      <c r="Z8" s="413" t="n"/>
+      <c r="AA8" s="413" t="n"/>
+      <c r="AB8" s="413" t="n"/>
+      <c r="AC8" s="413" t="n"/>
+      <c r="AD8" s="413" t="n"/>
+      <c r="AE8" s="413" t="n"/>
+      <c r="AF8" s="413" t="n"/>
+      <c r="AG8" s="413" t="n"/>
+      <c r="AH8" s="413" t="n"/>
+      <c r="AI8" s="413" t="n"/>
+      <c r="AJ8" s="413" t="n"/>
+      <c r="AK8" s="413" t="n"/>
+      <c r="AL8" s="413" t="n"/>
+      <c r="AM8" s="413" t="n"/>
+      <c r="AN8" s="595" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="465" t="n"/>
-      <c r="B9" s="465" t="n"/>
-      <c r="C9" s="465" t="n"/>
-      <c r="D9" s="465" t="n"/>
-      <c r="E9" s="465" t="n"/>
-      <c r="F9" s="465" t="n"/>
-      <c r="G9" s="465" t="n"/>
-      <c r="H9" s="436" t="n"/>
-      <c r="I9" s="436" t="n"/>
-      <c r="J9" s="436" t="n"/>
-      <c r="K9" s="436" t="n"/>
-      <c r="L9" s="436" t="n"/>
-      <c r="M9" s="436" t="n"/>
-      <c r="N9" s="436" t="n"/>
-      <c r="O9" s="436" t="n"/>
-      <c r="P9" s="436" t="n"/>
-      <c r="Q9" s="436" t="n"/>
-      <c r="R9" s="436" t="n"/>
-      <c r="S9" s="436" t="n"/>
-      <c r="T9" s="436" t="n"/>
-      <c r="U9" s="436" t="n"/>
-      <c r="V9" s="436" t="n"/>
-      <c r="W9" s="436" t="n"/>
-      <c r="X9" s="436" t="n"/>
-      <c r="Y9" s="436" t="n"/>
-      <c r="Z9" s="436" t="n"/>
-      <c r="AA9" s="436" t="n"/>
-      <c r="AB9" s="436" t="n"/>
-      <c r="AC9" s="436" t="n"/>
-      <c r="AD9" s="436" t="n"/>
-      <c r="AE9" s="436" t="n"/>
-      <c r="AF9" s="436" t="n"/>
-      <c r="AG9" s="436" t="n"/>
-      <c r="AH9" s="436" t="n"/>
-      <c r="AI9" s="436" t="n"/>
-      <c r="AJ9" s="436" t="n"/>
-      <c r="AK9" s="436" t="n"/>
-      <c r="AL9" s="436" t="n"/>
-      <c r="AM9" s="436" t="n"/>
-      <c r="AN9" s="436" t="n"/>
+      <c r="A9" s="624" t="n"/>
+      <c r="B9" s="625" t="n"/>
+      <c r="C9" s="625" t="n"/>
+      <c r="D9" s="625" t="n"/>
+      <c r="E9" s="625" t="n"/>
+      <c r="F9" s="625" t="n"/>
+      <c r="G9" s="625" t="n"/>
+      <c r="H9" s="413" t="n"/>
+      <c r="I9" s="413" t="n"/>
+      <c r="J9" s="413" t="n"/>
+      <c r="K9" s="413" t="n"/>
+      <c r="L9" s="413" t="n"/>
+      <c r="M9" s="413" t="n"/>
+      <c r="N9" s="413" t="n"/>
+      <c r="O9" s="413" t="n"/>
+      <c r="P9" s="413" t="n"/>
+      <c r="Q9" s="413" t="n"/>
+      <c r="R9" s="413" t="n"/>
+      <c r="S9" s="413" t="n"/>
+      <c r="T9" s="413" t="n"/>
+      <c r="U9" s="413" t="n"/>
+      <c r="V9" s="413" t="n"/>
+      <c r="W9" s="413" t="n"/>
+      <c r="X9" s="413" t="n"/>
+      <c r="Y9" s="413" t="n"/>
+      <c r="Z9" s="413" t="n"/>
+      <c r="AA9" s="413" t="n"/>
+      <c r="AB9" s="413" t="n"/>
+      <c r="AC9" s="413" t="n"/>
+      <c r="AD9" s="413" t="n"/>
+      <c r="AE9" s="413" t="n"/>
+      <c r="AF9" s="413" t="n"/>
+      <c r="AG9" s="413" t="n"/>
+      <c r="AH9" s="413" t="n"/>
+      <c r="AI9" s="413" t="n"/>
+      <c r="AJ9" s="413" t="n"/>
+      <c r="AK9" s="413" t="n"/>
+      <c r="AL9" s="413" t="n"/>
+      <c r="AM9" s="413" t="n"/>
+      <c r="AN9" s="595" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="427" t="n"/>
-      <c r="B10" s="427" t="n"/>
-      <c r="C10" s="427" t="n"/>
-      <c r="D10" s="427" t="n"/>
-      <c r="E10" s="427" t="n"/>
-      <c r="F10" s="427" t="n"/>
-      <c r="G10" s="427" t="n"/>
-      <c r="H10" s="436" t="n"/>
-      <c r="I10" s="436" t="n"/>
-      <c r="J10" s="436" t="n"/>
-      <c r="K10" s="436" t="n"/>
-      <c r="L10" s="436" t="n"/>
-      <c r="M10" s="436" t="n"/>
-      <c r="N10" s="436" t="n"/>
-      <c r="O10" s="436" t="n"/>
-      <c r="P10" s="436" t="n"/>
-      <c r="Q10" s="436" t="n"/>
-      <c r="R10" s="436" t="n"/>
-      <c r="S10" s="436" t="n"/>
-      <c r="T10" s="436" t="n"/>
-      <c r="U10" s="436" t="n"/>
-      <c r="V10" s="436" t="n"/>
-      <c r="W10" s="436" t="n"/>
-      <c r="X10" s="436" t="n"/>
-      <c r="Y10" s="436" t="n"/>
-      <c r="Z10" s="436" t="n"/>
-      <c r="AA10" s="436" t="n"/>
-      <c r="AB10" s="436" t="n"/>
-      <c r="AC10" s="436" t="n"/>
-      <c r="AD10" s="436" t="n"/>
-      <c r="AE10" s="436" t="n"/>
-      <c r="AF10" s="436" t="n"/>
-      <c r="AG10" s="436" t="n"/>
-      <c r="AH10" s="436" t="n"/>
-      <c r="AI10" s="436" t="n"/>
-      <c r="AJ10" s="436" t="n"/>
-      <c r="AK10" s="436" t="n"/>
-      <c r="AL10" s="436" t="n"/>
-      <c r="AM10" s="436" t="n"/>
-      <c r="AN10" s="436" t="n"/>
+      <c r="A10" s="626" t="n"/>
+      <c r="B10" s="627" t="n"/>
+      <c r="C10" s="627" t="n"/>
+      <c r="D10" s="627" t="n"/>
+      <c r="E10" s="627" t="n"/>
+      <c r="F10" s="627" t="n"/>
+      <c r="G10" s="627" t="n"/>
+      <c r="H10" s="413" t="n"/>
+      <c r="I10" s="413" t="n"/>
+      <c r="J10" s="413" t="n"/>
+      <c r="K10" s="413" t="n"/>
+      <c r="L10" s="413" t="n"/>
+      <c r="M10" s="413" t="n"/>
+      <c r="N10" s="413" t="n"/>
+      <c r="O10" s="413" t="n"/>
+      <c r="P10" s="413" t="n"/>
+      <c r="Q10" s="413" t="n"/>
+      <c r="R10" s="413" t="n"/>
+      <c r="S10" s="413" t="n"/>
+      <c r="T10" s="413" t="n"/>
+      <c r="U10" s="413" t="n"/>
+      <c r="V10" s="413" t="n"/>
+      <c r="W10" s="413" t="n"/>
+      <c r="X10" s="413" t="n"/>
+      <c r="Y10" s="413" t="n"/>
+      <c r="Z10" s="413" t="n"/>
+      <c r="AA10" s="413" t="n"/>
+      <c r="AB10" s="413" t="n"/>
+      <c r="AC10" s="413" t="n"/>
+      <c r="AD10" s="413" t="n"/>
+      <c r="AE10" s="413" t="n"/>
+      <c r="AF10" s="413" t="n"/>
+      <c r="AG10" s="413" t="n"/>
+      <c r="AH10" s="413" t="n"/>
+      <c r="AI10" s="413" t="n"/>
+      <c r="AJ10" s="413" t="n"/>
+      <c r="AK10" s="413" t="n"/>
+      <c r="AL10" s="413" t="n"/>
+      <c r="AM10" s="413" t="n"/>
+      <c r="AN10" s="595" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="465" t="n"/>
-      <c r="B11" s="465" t="n"/>
-      <c r="C11" s="465" t="n"/>
-      <c r="D11" s="465" t="n"/>
-      <c r="E11" s="465" t="n"/>
-      <c r="F11" s="465" t="n"/>
-      <c r="G11" s="465" t="n"/>
-      <c r="H11" s="436" t="n"/>
-      <c r="I11" s="436" t="n"/>
-      <c r="J11" s="436" t="n"/>
-      <c r="K11" s="436" t="n"/>
-      <c r="L11" s="436" t="n"/>
-      <c r="M11" s="436" t="n"/>
-      <c r="N11" s="436" t="n"/>
-      <c r="O11" s="436" t="n"/>
-      <c r="P11" s="436" t="n"/>
-      <c r="Q11" s="436" t="n"/>
-      <c r="R11" s="436" t="n"/>
-      <c r="S11" s="436" t="n"/>
-      <c r="T11" s="436" t="n"/>
-      <c r="U11" s="436" t="n"/>
-      <c r="V11" s="436" t="n"/>
-      <c r="W11" s="436" t="n"/>
-      <c r="X11" s="436" t="n"/>
-      <c r="Y11" s="436" t="n"/>
-      <c r="Z11" s="436" t="n"/>
-      <c r="AA11" s="436" t="n"/>
-      <c r="AB11" s="436" t="n"/>
-      <c r="AC11" s="436" t="n"/>
-      <c r="AD11" s="436" t="n"/>
-      <c r="AE11" s="436" t="n"/>
-      <c r="AF11" s="436" t="n"/>
-      <c r="AG11" s="436" t="n"/>
-      <c r="AH11" s="436" t="n"/>
-      <c r="AI11" s="436" t="n"/>
-      <c r="AJ11" s="436" t="n"/>
-      <c r="AK11" s="436" t="n"/>
-      <c r="AL11" s="436" t="n"/>
-      <c r="AM11" s="436" t="n"/>
-      <c r="AN11" s="436" t="n"/>
+      <c r="A11" s="628" t="n"/>
+      <c r="B11" s="629" t="n"/>
+      <c r="C11" s="629" t="n"/>
+      <c r="D11" s="629" t="n"/>
+      <c r="E11" s="629" t="n"/>
+      <c r="F11" s="629" t="n"/>
+      <c r="G11" s="629" t="n"/>
+      <c r="H11" s="600" t="n"/>
+      <c r="I11" s="600" t="n"/>
+      <c r="J11" s="600" t="n"/>
+      <c r="K11" s="600" t="n"/>
+      <c r="L11" s="600" t="n"/>
+      <c r="M11" s="600" t="n"/>
+      <c r="N11" s="600" t="n"/>
+      <c r="O11" s="600" t="n"/>
+      <c r="P11" s="600" t="n"/>
+      <c r="Q11" s="600" t="n"/>
+      <c r="R11" s="600" t="n"/>
+      <c r="S11" s="600" t="n"/>
+      <c r="T11" s="600" t="n"/>
+      <c r="U11" s="600" t="n"/>
+      <c r="V11" s="600" t="n"/>
+      <c r="W11" s="600" t="n"/>
+      <c r="X11" s="600" t="n"/>
+      <c r="Y11" s="600" t="n"/>
+      <c r="Z11" s="600" t="n"/>
+      <c r="AA11" s="600" t="n"/>
+      <c r="AB11" s="600" t="n"/>
+      <c r="AC11" s="600" t="n"/>
+      <c r="AD11" s="600" t="n"/>
+      <c r="AE11" s="600" t="n"/>
+      <c r="AF11" s="600" t="n"/>
+      <c r="AG11" s="600" t="n"/>
+      <c r="AH11" s="600" t="n"/>
+      <c r="AI11" s="600" t="n"/>
+      <c r="AJ11" s="600" t="n"/>
+      <c r="AK11" s="600" t="n"/>
+      <c r="AL11" s="600" t="n"/>
+      <c r="AM11" s="600" t="n"/>
+      <c r="AN11" s="601" t="n"/>
     </row>
     <row r="12" hidden="1"/>
     <row r="13" hidden="1"/>
@@ -12044,8 +12908,9 @@
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
@@ -33,7 +33,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="89">
+  <fonts count="90">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -536,6 +536,12 @@
       <color rgb="00BBCCCC"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001B3A6B"/>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="57">
     <fill>
@@ -820,7 +826,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="341">
+  <borders count="380">
     <border>
       <left/>
       <right/>
@@ -4482,13 +4488,462 @@
       </top>
       <bottom style="medium">
         <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="630">
+  <cellXfs count="719">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6019,6 +6474,247 @@
     <xf numFmtId="0" fontId="78" fillId="51" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="373" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="374" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="375" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="376" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="288" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="377" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="378" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="377" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="379" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="47" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="47" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="47" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="376" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="377" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="377" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="379" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="345" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -6119,11 +6815,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
+      <colOff>253512</colOff>
+      <row>0</row>
+      <rowOff>340740</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="941616" cy="271620"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -6149,11 +6845,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
+      <colOff>63378</colOff>
+      <row>0</row>
+      <rowOff>442597</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="235404" cy="67905"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -6197,6 +6893,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6463,2366 +7162,2366 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="492" t="inlineStr"/>
-      <c r="B1" s="493" t="n"/>
-      <c r="C1" s="493" t="n"/>
-      <c r="D1" s="493" t="n"/>
-      <c r="E1" s="493" t="n"/>
-      <c r="F1" s="493" t="n"/>
-      <c r="G1" s="493" t="n"/>
-      <c r="H1" s="494" t="n"/>
-      <c r="I1" s="495" t="inlineStr">
+      <c r="A1" s="630" t="inlineStr"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="53" t="n"/>
+      <c r="I1" s="631" t="inlineStr">
         <is>
           <t>HIGH-RISK JOB READINESS REVIEW</t>
         </is>
       </c>
-      <c r="J1" s="496" t="n"/>
-      <c r="K1" s="496" t="n"/>
-      <c r="L1" s="496" t="n"/>
-      <c r="M1" s="496" t="n"/>
-      <c r="N1" s="496" t="n"/>
-      <c r="O1" s="496" t="n"/>
-      <c r="P1" s="496" t="n"/>
-      <c r="Q1" s="496" t="n"/>
-      <c r="R1" s="496" t="n"/>
-      <c r="S1" s="496" t="n"/>
-      <c r="T1" s="496" t="n"/>
-      <c r="U1" s="496" t="n"/>
-      <c r="V1" s="496" t="n"/>
-      <c r="W1" s="496" t="n"/>
-      <c r="X1" s="496" t="n"/>
-      <c r="Y1" s="496" t="n"/>
-      <c r="Z1" s="496" t="n"/>
-      <c r="AA1" s="496" t="n"/>
-      <c r="AB1" s="496" t="n"/>
-      <c r="AC1" s="496" t="n"/>
-      <c r="AD1" s="497" t="n"/>
-      <c r="AE1" s="498" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+      <c r="AA1" s="2" t="n"/>
+      <c r="AB1" s="2" t="n"/>
+      <c r="AC1" s="2" t="n"/>
+      <c r="AD1" s="2" t="n"/>
+      <c r="AE1" s="632" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="499" t="n"/>
-      <c r="AG1" s="499" t="n"/>
-      <c r="AH1" s="500" t="n"/>
-      <c r="AI1" s="501" t="inlineStr">
+      <c r="AF1" s="2" t="n"/>
+      <c r="AG1" s="2" t="n"/>
+      <c r="AH1" s="633" t="n"/>
+      <c r="AI1" s="634" t="inlineStr">
         <is>
           <t>FRM-209</t>
         </is>
       </c>
-      <c r="AJ1" s="502" t="n"/>
-      <c r="AK1" s="502" t="n"/>
-      <c r="AL1" s="502" t="n"/>
-      <c r="AM1" s="502" t="n"/>
-      <c r="AN1" s="503" t="n"/>
+      <c r="AJ1" s="2" t="n"/>
+      <c r="AK1" s="2" t="n"/>
+      <c r="AL1" s="2" t="n"/>
+      <c r="AM1" s="2" t="n"/>
+      <c r="AN1" s="53" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="504" t="n"/>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
-      <c r="H2" s="505" t="n"/>
-      <c r="I2" s="506" t="n"/>
-      <c r="J2" s="507" t="n"/>
-      <c r="K2" s="507" t="n"/>
-      <c r="L2" s="507" t="n"/>
-      <c r="M2" s="507" t="n"/>
-      <c r="N2" s="507" t="n"/>
-      <c r="O2" s="507" t="n"/>
-      <c r="P2" s="507" t="n"/>
-      <c r="Q2" s="507" t="n"/>
-      <c r="R2" s="507" t="n"/>
-      <c r="S2" s="507" t="n"/>
-      <c r="T2" s="507" t="n"/>
-      <c r="U2" s="507" t="n"/>
-      <c r="V2" s="507" t="n"/>
-      <c r="W2" s="507" t="n"/>
-      <c r="X2" s="507" t="n"/>
-      <c r="Y2" s="507" t="n"/>
-      <c r="Z2" s="507" t="n"/>
-      <c r="AA2" s="507" t="n"/>
-      <c r="AB2" s="507" t="n"/>
-      <c r="AC2" s="507" t="n"/>
-      <c r="AD2" s="508" t="n"/>
-      <c r="AE2" s="509" t="inlineStr">
+      <c r="A2" s="9" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="54" t="n"/>
+      <c r="I2" s="9" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="10" t="n"/>
+      <c r="AE2" s="635" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="510" t="n"/>
-      <c r="AG2" s="510" t="n"/>
-      <c r="AH2" s="511" t="n"/>
-      <c r="AI2" s="512" t="inlineStr">
+      <c r="AF2" s="636" t="n"/>
+      <c r="AG2" s="636" t="n"/>
+      <c r="AH2" s="637" t="n"/>
+      <c r="AI2" s="638" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="513" t="n"/>
-      <c r="AK2" s="513" t="n"/>
-      <c r="AL2" s="513" t="n"/>
-      <c r="AM2" s="513" t="n"/>
-      <c r="AN2" s="514" t="n"/>
+      <c r="AJ2" s="636" t="n"/>
+      <c r="AK2" s="636" t="n"/>
+      <c r="AL2" s="636" t="n"/>
+      <c r="AM2" s="636" t="n"/>
+      <c r="AN2" s="639" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="504" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="505" t="n"/>
-      <c r="I3" s="506" t="n"/>
-      <c r="J3" s="507" t="n"/>
-      <c r="K3" s="507" t="n"/>
-      <c r="L3" s="507" t="n"/>
-      <c r="M3" s="507" t="n"/>
-      <c r="N3" s="507" t="n"/>
-      <c r="O3" s="507" t="n"/>
-      <c r="P3" s="507" t="n"/>
-      <c r="Q3" s="507" t="n"/>
-      <c r="R3" s="507" t="n"/>
-      <c r="S3" s="507" t="n"/>
-      <c r="T3" s="507" t="n"/>
-      <c r="U3" s="507" t="n"/>
-      <c r="V3" s="507" t="n"/>
-      <c r="W3" s="507" t="n"/>
-      <c r="X3" s="507" t="n"/>
-      <c r="Y3" s="507" t="n"/>
-      <c r="Z3" s="507" t="n"/>
-      <c r="AA3" s="507" t="n"/>
-      <c r="AB3" s="507" t="n"/>
-      <c r="AC3" s="507" t="n"/>
-      <c r="AD3" s="508" t="n"/>
-      <c r="AE3" s="509" t="inlineStr">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="635" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="510" t="n"/>
-      <c r="AG3" s="510" t="n"/>
-      <c r="AH3" s="511" t="n"/>
-      <c r="AI3" s="512" t="inlineStr">
+      <c r="AF3" s="636" t="n"/>
+      <c r="AG3" s="636" t="n"/>
+      <c r="AH3" s="637" t="n"/>
+      <c r="AI3" s="638" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="513" t="n"/>
-      <c r="AK3" s="513" t="n"/>
-      <c r="AL3" s="513" t="n"/>
-      <c r="AM3" s="513" t="n"/>
-      <c r="AN3" s="514" t="n"/>
+      <c r="AJ3" s="636" t="n"/>
+      <c r="AK3" s="636" t="n"/>
+      <c r="AL3" s="636" t="n"/>
+      <c r="AM3" s="636" t="n"/>
+      <c r="AN3" s="639" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="504" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="505" t="n"/>
-      <c r="I4" s="515" t="inlineStr">
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="54" t="n"/>
+      <c r="I4" s="640" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="J4" s="516" t="n"/>
-      <c r="K4" s="516" t="n"/>
-      <c r="L4" s="516" t="n"/>
-      <c r="M4" s="516" t="n"/>
-      <c r="N4" s="516" t="n"/>
-      <c r="O4" s="516" t="n"/>
-      <c r="P4" s="516" t="n"/>
-      <c r="Q4" s="516" t="n"/>
-      <c r="R4" s="516" t="n"/>
-      <c r="S4" s="516" t="n"/>
-      <c r="T4" s="516" t="n"/>
-      <c r="U4" s="516" t="n"/>
-      <c r="V4" s="516" t="n"/>
-      <c r="W4" s="516" t="n"/>
-      <c r="X4" s="516" t="n"/>
-      <c r="Y4" s="516" t="n"/>
-      <c r="Z4" s="516" t="n"/>
-      <c r="AA4" s="516" t="n"/>
-      <c r="AB4" s="516" t="n"/>
-      <c r="AC4" s="516" t="n"/>
-      <c r="AD4" s="517" t="n"/>
-      <c r="AE4" s="509" t="inlineStr">
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="635" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="510" t="n"/>
-      <c r="AG4" s="510" t="n"/>
-      <c r="AH4" s="511" t="n"/>
-      <c r="AI4" s="512" t="inlineStr">
+      <c r="AF4" s="636" t="n"/>
+      <c r="AG4" s="636" t="n"/>
+      <c r="AH4" s="637" t="n"/>
+      <c r="AI4" s="638" t="inlineStr">
         <is>
           <t>Planning / QA / Engineering</t>
         </is>
       </c>
-      <c r="AJ4" s="513" t="n"/>
-      <c r="AK4" s="513" t="n"/>
-      <c r="AL4" s="513" t="n"/>
-      <c r="AM4" s="513" t="n"/>
-      <c r="AN4" s="514" t="n"/>
+      <c r="AJ4" s="636" t="n"/>
+      <c r="AK4" s="636" t="n"/>
+      <c r="AL4" s="636" t="n"/>
+      <c r="AM4" s="636" t="n"/>
+      <c r="AN4" s="639" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="518" t="n"/>
-      <c r="B5" s="519" t="n"/>
-      <c r="C5" s="519" t="n"/>
-      <c r="D5" s="519" t="n"/>
-      <c r="E5" s="519" t="n"/>
-      <c r="F5" s="519" t="n"/>
-      <c r="G5" s="519" t="n"/>
-      <c r="H5" s="520" t="n"/>
-      <c r="I5" s="521" t="inlineStr">
+      <c r="A5" s="18" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="19" t="n"/>
+      <c r="H5" s="24" t="n"/>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="522" t="n"/>
-      <c r="K5" s="522" t="n"/>
-      <c r="L5" s="522" t="n"/>
-      <c r="M5" s="522" t="n"/>
-      <c r="N5" s="522" t="n"/>
-      <c r="O5" s="522" t="n"/>
-      <c r="P5" s="522" t="n"/>
-      <c r="Q5" s="522" t="n"/>
-      <c r="R5" s="522" t="n"/>
-      <c r="S5" s="522" t="n"/>
-      <c r="T5" s="522" t="n"/>
-      <c r="U5" s="522" t="n"/>
-      <c r="V5" s="522" t="n"/>
-      <c r="W5" s="522" t="n"/>
-      <c r="X5" s="522" t="n"/>
-      <c r="Y5" s="522" t="n"/>
-      <c r="Z5" s="522" t="n"/>
-      <c r="AA5" s="522" t="n"/>
-      <c r="AB5" s="522" t="n"/>
-      <c r="AC5" s="522" t="n"/>
-      <c r="AD5" s="523" t="n"/>
-      <c r="AE5" s="524" t="inlineStr">
+      <c r="J5" s="19" t="n"/>
+      <c r="K5" s="19" t="n"/>
+      <c r="L5" s="19" t="n"/>
+      <c r="M5" s="19" t="n"/>
+      <c r="N5" s="19" t="n"/>
+      <c r="O5" s="19" t="n"/>
+      <c r="P5" s="19" t="n"/>
+      <c r="Q5" s="19" t="n"/>
+      <c r="R5" s="19" t="n"/>
+      <c r="S5" s="19" t="n"/>
+      <c r="T5" s="19" t="n"/>
+      <c r="U5" s="19" t="n"/>
+      <c r="V5" s="19" t="n"/>
+      <c r="W5" s="19" t="n"/>
+      <c r="X5" s="19" t="n"/>
+      <c r="Y5" s="19" t="n"/>
+      <c r="Z5" s="19" t="n"/>
+      <c r="AA5" s="19" t="n"/>
+      <c r="AB5" s="19" t="n"/>
+      <c r="AC5" s="19" t="n"/>
+      <c r="AD5" s="19" t="n"/>
+      <c r="AE5" s="641" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="525" t="n"/>
-      <c r="AG5" s="525" t="n"/>
-      <c r="AH5" s="526" t="n"/>
-      <c r="AI5" s="527" t="inlineStr">
+      <c r="AF5" s="642" t="n"/>
+      <c r="AG5" s="642" t="n"/>
+      <c r="AH5" s="643" t="n"/>
+      <c r="AI5" s="644" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="528" t="n"/>
-      <c r="AK5" s="528" t="n"/>
-      <c r="AL5" s="528" t="n"/>
-      <c r="AM5" s="528" t="n"/>
-      <c r="AN5" s="529" t="n"/>
+      <c r="AJ5" s="642" t="n"/>
+      <c r="AK5" s="642" t="n"/>
+      <c r="AL5" s="642" t="n"/>
+      <c r="AM5" s="642" t="n"/>
+      <c r="AN5" s="645" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="530" t="n"/>
-      <c r="B6" s="530" t="n"/>
-      <c r="C6" s="530" t="n"/>
-      <c r="D6" s="530" t="n"/>
-      <c r="E6" s="530" t="n"/>
-      <c r="F6" s="530" t="n"/>
-      <c r="G6" s="530" t="n"/>
-      <c r="H6" s="530" t="n"/>
-      <c r="I6" s="530" t="n"/>
-      <c r="J6" s="530" t="n"/>
-      <c r="K6" s="530" t="n"/>
-      <c r="L6" s="530" t="n"/>
-      <c r="M6" s="530" t="n"/>
-      <c r="N6" s="530" t="n"/>
-      <c r="O6" s="530" t="n"/>
-      <c r="P6" s="530" t="n"/>
-      <c r="Q6" s="530" t="n"/>
-      <c r="R6" s="530" t="n"/>
-      <c r="S6" s="530" t="n"/>
-      <c r="T6" s="530" t="n"/>
-      <c r="U6" s="530" t="n"/>
-      <c r="V6" s="530" t="n"/>
-      <c r="W6" s="530" t="n"/>
-      <c r="X6" s="530" t="n"/>
-      <c r="Y6" s="530" t="n"/>
-      <c r="Z6" s="530" t="n"/>
-      <c r="AA6" s="530" t="n"/>
-      <c r="AB6" s="530" t="n"/>
-      <c r="AC6" s="530" t="n"/>
-      <c r="AD6" s="530" t="n"/>
-      <c r="AE6" s="530" t="n"/>
-      <c r="AF6" s="530" t="n"/>
-      <c r="AG6" s="530" t="n"/>
-      <c r="AH6" s="530" t="n"/>
-      <c r="AI6" s="530" t="n"/>
-      <c r="AJ6" s="530" t="n"/>
-      <c r="AK6" s="530" t="n"/>
-      <c r="AL6" s="530" t="n"/>
-      <c r="AM6" s="530" t="n"/>
-      <c r="AN6" s="530" t="n"/>
+      <c r="A6" s="646" t="n"/>
+      <c r="B6" s="646" t="n"/>
+      <c r="C6" s="646" t="n"/>
+      <c r="D6" s="646" t="n"/>
+      <c r="E6" s="646" t="n"/>
+      <c r="F6" s="646" t="n"/>
+      <c r="G6" s="646" t="n"/>
+      <c r="H6" s="646" t="n"/>
+      <c r="I6" s="646" t="n"/>
+      <c r="J6" s="646" t="n"/>
+      <c r="K6" s="646" t="n"/>
+      <c r="L6" s="646" t="n"/>
+      <c r="M6" s="646" t="n"/>
+      <c r="N6" s="646" t="n"/>
+      <c r="O6" s="646" t="n"/>
+      <c r="P6" s="646" t="n"/>
+      <c r="Q6" s="646" t="n"/>
+      <c r="R6" s="646" t="n"/>
+      <c r="S6" s="646" t="n"/>
+      <c r="T6" s="646" t="n"/>
+      <c r="U6" s="646" t="n"/>
+      <c r="V6" s="646" t="n"/>
+      <c r="W6" s="646" t="n"/>
+      <c r="X6" s="646" t="n"/>
+      <c r="Y6" s="646" t="n"/>
+      <c r="Z6" s="646" t="n"/>
+      <c r="AA6" s="646" t="n"/>
+      <c r="AB6" s="646" t="n"/>
+      <c r="AC6" s="646" t="n"/>
+      <c r="AD6" s="646" t="n"/>
+      <c r="AE6" s="646" t="n"/>
+      <c r="AF6" s="646" t="n"/>
+      <c r="AG6" s="646" t="n"/>
+      <c r="AH6" s="646" t="n"/>
+      <c r="AI6" s="646" t="n"/>
+      <c r="AJ6" s="646" t="n"/>
+      <c r="AK6" s="646" t="n"/>
+      <c r="AL6" s="646" t="n"/>
+      <c r="AM6" s="646" t="n"/>
+      <c r="AN6" s="646" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="531" t="inlineStr">
+      <c r="A7" s="647" t="inlineStr">
         <is>
           <t>1.  HIGH-RISK JOB HEADER / REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="532" t="n"/>
-      <c r="C7" s="532" t="n"/>
-      <c r="D7" s="532" t="n"/>
-      <c r="E7" s="532" t="n"/>
-      <c r="F7" s="532" t="n"/>
-      <c r="G7" s="532" t="n"/>
-      <c r="H7" s="532" t="n"/>
-      <c r="I7" s="532" t="n"/>
-      <c r="J7" s="532" t="n"/>
-      <c r="K7" s="532" t="n"/>
-      <c r="L7" s="532" t="n"/>
-      <c r="M7" s="532" t="n"/>
-      <c r="N7" s="532" t="n"/>
-      <c r="O7" s="532" t="n"/>
-      <c r="P7" s="532" t="n"/>
-      <c r="Q7" s="532" t="n"/>
-      <c r="R7" s="532" t="n"/>
-      <c r="S7" s="532" t="n"/>
-      <c r="T7" s="532" t="n"/>
-      <c r="U7" s="532" t="n"/>
-      <c r="V7" s="532" t="n"/>
-      <c r="W7" s="532" t="n"/>
-      <c r="X7" s="532" t="n"/>
-      <c r="Y7" s="532" t="n"/>
-      <c r="Z7" s="532" t="n"/>
-      <c r="AA7" s="532" t="n"/>
-      <c r="AB7" s="532" t="n"/>
-      <c r="AC7" s="532" t="n"/>
-      <c r="AD7" s="532" t="n"/>
-      <c r="AE7" s="532" t="n"/>
-      <c r="AF7" s="532" t="n"/>
-      <c r="AG7" s="532" t="n"/>
-      <c r="AH7" s="532" t="n"/>
-      <c r="AI7" s="532" t="n"/>
-      <c r="AJ7" s="532" t="n"/>
-      <c r="AK7" s="532" t="n"/>
-      <c r="AL7" s="532" t="n"/>
-      <c r="AM7" s="532" t="n"/>
-      <c r="AN7" s="533" t="n"/>
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="27" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
+      <c r="H7" s="27" t="n"/>
+      <c r="I7" s="27" t="n"/>
+      <c r="J7" s="27" t="n"/>
+      <c r="K7" s="27" t="n"/>
+      <c r="L7" s="27" t="n"/>
+      <c r="M7" s="27" t="n"/>
+      <c r="N7" s="27" t="n"/>
+      <c r="O7" s="27" t="n"/>
+      <c r="P7" s="27" t="n"/>
+      <c r="Q7" s="27" t="n"/>
+      <c r="R7" s="27" t="n"/>
+      <c r="S7" s="27" t="n"/>
+      <c r="T7" s="27" t="n"/>
+      <c r="U7" s="27" t="n"/>
+      <c r="V7" s="27" t="n"/>
+      <c r="W7" s="27" t="n"/>
+      <c r="X7" s="27" t="n"/>
+      <c r="Y7" s="27" t="n"/>
+      <c r="Z7" s="27" t="n"/>
+      <c r="AA7" s="27" t="n"/>
+      <c r="AB7" s="27" t="n"/>
+      <c r="AC7" s="27" t="n"/>
+      <c r="AD7" s="27" t="n"/>
+      <c r="AE7" s="27" t="n"/>
+      <c r="AF7" s="27" t="n"/>
+      <c r="AG7" s="27" t="n"/>
+      <c r="AH7" s="27" t="n"/>
+      <c r="AI7" s="27" t="n"/>
+      <c r="AJ7" s="27" t="n"/>
+      <c r="AK7" s="27" t="n"/>
+      <c r="AL7" s="27" t="n"/>
+      <c r="AM7" s="27" t="n"/>
+      <c r="AN7" s="28" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="534" t="inlineStr">
+      <c r="A8" s="648" t="inlineStr">
         <is>
           <t>Readiness Review ID</t>
         </is>
       </c>
-      <c r="B8" s="535" t="n"/>
-      <c r="C8" s="535" t="n"/>
-      <c r="D8" s="535" t="n"/>
-      <c r="E8" s="535" t="n"/>
-      <c r="F8" s="535" t="n"/>
-      <c r="G8" s="535" t="n"/>
-      <c r="H8" s="536" t="inlineStr"/>
-      <c r="I8" s="535" t="n"/>
-      <c r="J8" s="535" t="n"/>
-      <c r="K8" s="535" t="n"/>
-      <c r="L8" s="535" t="n"/>
-      <c r="M8" s="535" t="n"/>
-      <c r="N8" s="535" t="n"/>
-      <c r="O8" s="535" t="n"/>
-      <c r="P8" s="535" t="n"/>
-      <c r="Q8" s="535" t="n"/>
-      <c r="R8" s="535" t="n"/>
-      <c r="S8" s="535" t="n"/>
-      <c r="T8" s="535" t="n"/>
-      <c r="U8" s="537" t="inlineStr">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="30" t="inlineStr"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="6" t="n"/>
+      <c r="U8" s="649" t="inlineStr">
         <is>
           <t>Job / WO</t>
         </is>
       </c>
-      <c r="V8" s="535" t="n"/>
-      <c r="W8" s="535" t="n"/>
-      <c r="X8" s="535" t="n"/>
-      <c r="Y8" s="535" t="n"/>
-      <c r="Z8" s="535" t="n"/>
-      <c r="AA8" s="535" t="n"/>
-      <c r="AB8" s="536" t="inlineStr"/>
-      <c r="AC8" s="535" t="n"/>
-      <c r="AD8" s="535" t="n"/>
-      <c r="AE8" s="535" t="n"/>
-      <c r="AF8" s="535" t="n"/>
-      <c r="AG8" s="535" t="n"/>
-      <c r="AH8" s="535" t="n"/>
-      <c r="AI8" s="535" t="n"/>
-      <c r="AJ8" s="535" t="n"/>
-      <c r="AK8" s="535" t="n"/>
-      <c r="AL8" s="535" t="n"/>
-      <c r="AM8" s="535" t="n"/>
-      <c r="AN8" s="538" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+      <c r="Y8" s="5" t="n"/>
+      <c r="Z8" s="5" t="n"/>
+      <c r="AA8" s="6" t="n"/>
+      <c r="AB8" s="30" t="inlineStr"/>
+      <c r="AC8" s="5" t="n"/>
+      <c r="AD8" s="5" t="n"/>
+      <c r="AE8" s="5" t="n"/>
+      <c r="AF8" s="5" t="n"/>
+      <c r="AG8" s="5" t="n"/>
+      <c r="AH8" s="5" t="n"/>
+      <c r="AI8" s="5" t="n"/>
+      <c r="AJ8" s="5" t="n"/>
+      <c r="AK8" s="5" t="n"/>
+      <c r="AL8" s="5" t="n"/>
+      <c r="AM8" s="5" t="n"/>
+      <c r="AN8" s="8" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="539" t="inlineStr">
+      <c r="A9" s="650" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="B9" s="398" t="n"/>
-      <c r="C9" s="398" t="n"/>
-      <c r="D9" s="398" t="n"/>
-      <c r="E9" s="398" t="n"/>
-      <c r="F9" s="398" t="n"/>
-      <c r="G9" s="398" t="n"/>
-      <c r="H9" s="540" t="inlineStr"/>
-      <c r="I9" s="398" t="n"/>
-      <c r="J9" s="398" t="n"/>
-      <c r="K9" s="398" t="n"/>
-      <c r="L9" s="398" t="n"/>
-      <c r="M9" s="398" t="n"/>
-      <c r="N9" s="398" t="n"/>
-      <c r="O9" s="398" t="n"/>
-      <c r="P9" s="398" t="n"/>
-      <c r="Q9" s="398" t="n"/>
-      <c r="R9" s="398" t="n"/>
-      <c r="S9" s="398" t="n"/>
-      <c r="T9" s="398" t="n"/>
-      <c r="U9" s="541" t="inlineStr">
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="14" t="inlineStr"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="12" t="n"/>
+      <c r="O9" s="12" t="n"/>
+      <c r="P9" s="12" t="n"/>
+      <c r="Q9" s="12" t="n"/>
+      <c r="R9" s="12" t="n"/>
+      <c r="S9" s="12" t="n"/>
+      <c r="T9" s="13" t="n"/>
+      <c r="U9" s="651" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="V9" s="398" t="n"/>
-      <c r="W9" s="398" t="n"/>
-      <c r="X9" s="398" t="n"/>
-      <c r="Y9" s="398" t="n"/>
-      <c r="Z9" s="398" t="n"/>
-      <c r="AA9" s="398" t="n"/>
-      <c r="AB9" s="540" t="inlineStr"/>
-      <c r="AC9" s="398" t="n"/>
-      <c r="AD9" s="398" t="n"/>
-      <c r="AE9" s="398" t="n"/>
-      <c r="AF9" s="398" t="n"/>
-      <c r="AG9" s="398" t="n"/>
-      <c r="AH9" s="398" t="n"/>
-      <c r="AI9" s="398" t="n"/>
-      <c r="AJ9" s="398" t="n"/>
-      <c r="AK9" s="398" t="n"/>
-      <c r="AL9" s="398" t="n"/>
-      <c r="AM9" s="398" t="n"/>
-      <c r="AN9" s="542" t="n"/>
+      <c r="V9" s="12" t="n"/>
+      <c r="W9" s="12" t="n"/>
+      <c r="X9" s="12" t="n"/>
+      <c r="Y9" s="12" t="n"/>
+      <c r="Z9" s="12" t="n"/>
+      <c r="AA9" s="13" t="n"/>
+      <c r="AB9" s="14" t="inlineStr"/>
+      <c r="AC9" s="12" t="n"/>
+      <c r="AD9" s="12" t="n"/>
+      <c r="AE9" s="12" t="n"/>
+      <c r="AF9" s="12" t="n"/>
+      <c r="AG9" s="12" t="n"/>
+      <c r="AH9" s="12" t="n"/>
+      <c r="AI9" s="12" t="n"/>
+      <c r="AJ9" s="12" t="n"/>
+      <c r="AK9" s="12" t="n"/>
+      <c r="AL9" s="12" t="n"/>
+      <c r="AM9" s="12" t="n"/>
+      <c r="AN9" s="15" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="539" t="inlineStr">
+      <c r="A10" s="650" t="inlineStr">
         <is>
           <t>Due Date / Commit</t>
         </is>
       </c>
-      <c r="B10" s="398" t="n"/>
-      <c r="C10" s="398" t="n"/>
-      <c r="D10" s="398" t="n"/>
-      <c r="E10" s="398" t="n"/>
-      <c r="F10" s="398" t="n"/>
-      <c r="G10" s="398" t="n"/>
-      <c r="H10" s="540" t="inlineStr"/>
-      <c r="I10" s="398" t="n"/>
-      <c r="J10" s="398" t="n"/>
-      <c r="K10" s="398" t="n"/>
-      <c r="L10" s="398" t="n"/>
-      <c r="M10" s="398" t="n"/>
-      <c r="N10" s="398" t="n"/>
-      <c r="O10" s="398" t="n"/>
-      <c r="P10" s="398" t="n"/>
-      <c r="Q10" s="398" t="n"/>
-      <c r="R10" s="398" t="n"/>
-      <c r="S10" s="398" t="n"/>
-      <c r="T10" s="398" t="n"/>
-      <c r="U10" s="541" t="inlineStr">
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="14" t="inlineStr"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="12" t="n"/>
+      <c r="M10" s="12" t="n"/>
+      <c r="N10" s="12" t="n"/>
+      <c r="O10" s="12" t="n"/>
+      <c r="P10" s="12" t="n"/>
+      <c r="Q10" s="12" t="n"/>
+      <c r="R10" s="12" t="n"/>
+      <c r="S10" s="12" t="n"/>
+      <c r="T10" s="13" t="n"/>
+      <c r="U10" s="651" t="inlineStr">
         <is>
           <t>Current Route Step</t>
         </is>
       </c>
-      <c r="V10" s="398" t="n"/>
-      <c r="W10" s="398" t="n"/>
-      <c r="X10" s="398" t="n"/>
-      <c r="Y10" s="398" t="n"/>
-      <c r="Z10" s="398" t="n"/>
-      <c r="AA10" s="398" t="n"/>
-      <c r="AB10" s="540" t="inlineStr"/>
-      <c r="AC10" s="398" t="n"/>
-      <c r="AD10" s="398" t="n"/>
-      <c r="AE10" s="398" t="n"/>
-      <c r="AF10" s="398" t="n"/>
-      <c r="AG10" s="398" t="n"/>
-      <c r="AH10" s="398" t="n"/>
-      <c r="AI10" s="398" t="n"/>
-      <c r="AJ10" s="398" t="n"/>
-      <c r="AK10" s="398" t="n"/>
-      <c r="AL10" s="398" t="n"/>
-      <c r="AM10" s="398" t="n"/>
-      <c r="AN10" s="542" t="n"/>
+      <c r="V10" s="12" t="n"/>
+      <c r="W10" s="12" t="n"/>
+      <c r="X10" s="12" t="n"/>
+      <c r="Y10" s="12" t="n"/>
+      <c r="Z10" s="12" t="n"/>
+      <c r="AA10" s="13" t="n"/>
+      <c r="AB10" s="14" t="inlineStr"/>
+      <c r="AC10" s="12" t="n"/>
+      <c r="AD10" s="12" t="n"/>
+      <c r="AE10" s="12" t="n"/>
+      <c r="AF10" s="12" t="n"/>
+      <c r="AG10" s="12" t="n"/>
+      <c r="AH10" s="12" t="n"/>
+      <c r="AI10" s="12" t="n"/>
+      <c r="AJ10" s="12" t="n"/>
+      <c r="AK10" s="12" t="n"/>
+      <c r="AL10" s="12" t="n"/>
+      <c r="AM10" s="12" t="n"/>
+      <c r="AN10" s="15" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="539" t="inlineStr">
+      <c r="A11" s="650" t="inlineStr">
         <is>
           <t>Top Risk Class</t>
         </is>
       </c>
-      <c r="B11" s="398" t="n"/>
-      <c r="C11" s="398" t="n"/>
-      <c r="D11" s="398" t="n"/>
-      <c r="E11" s="398" t="n"/>
-      <c r="F11" s="398" t="n"/>
-      <c r="G11" s="398" t="n"/>
-      <c r="H11" s="540" t="inlineStr"/>
-      <c r="I11" s="398" t="n"/>
-      <c r="J11" s="398" t="n"/>
-      <c r="K11" s="398" t="n"/>
-      <c r="L11" s="398" t="n"/>
-      <c r="M11" s="398" t="n"/>
-      <c r="N11" s="398" t="n"/>
-      <c r="O11" s="398" t="n"/>
-      <c r="P11" s="398" t="n"/>
-      <c r="Q11" s="398" t="n"/>
-      <c r="R11" s="398" t="n"/>
-      <c r="S11" s="398" t="n"/>
-      <c r="T11" s="398" t="n"/>
-      <c r="U11" s="541" t="inlineStr">
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="14" t="inlineStr"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="12" t="n"/>
+      <c r="M11" s="12" t="n"/>
+      <c r="N11" s="12" t="n"/>
+      <c r="O11" s="12" t="n"/>
+      <c r="P11" s="12" t="n"/>
+      <c r="Q11" s="12" t="n"/>
+      <c r="R11" s="12" t="n"/>
+      <c r="S11" s="12" t="n"/>
+      <c r="T11" s="13" t="n"/>
+      <c r="U11" s="651" t="inlineStr">
         <is>
           <t>Commercial / Ops Owner</t>
         </is>
       </c>
-      <c r="V11" s="398" t="n"/>
-      <c r="W11" s="398" t="n"/>
-      <c r="X11" s="398" t="n"/>
-      <c r="Y11" s="398" t="n"/>
-      <c r="Z11" s="398" t="n"/>
-      <c r="AA11" s="398" t="n"/>
-      <c r="AB11" s="540" t="inlineStr"/>
-      <c r="AC11" s="398" t="n"/>
-      <c r="AD11" s="398" t="n"/>
-      <c r="AE11" s="398" t="n"/>
-      <c r="AF11" s="398" t="n"/>
-      <c r="AG11" s="398" t="n"/>
-      <c r="AH11" s="398" t="n"/>
-      <c r="AI11" s="398" t="n"/>
-      <c r="AJ11" s="398" t="n"/>
-      <c r="AK11" s="398" t="n"/>
-      <c r="AL11" s="398" t="n"/>
-      <c r="AM11" s="398" t="n"/>
-      <c r="AN11" s="542" t="n"/>
+      <c r="V11" s="12" t="n"/>
+      <c r="W11" s="12" t="n"/>
+      <c r="X11" s="12" t="n"/>
+      <c r="Y11" s="12" t="n"/>
+      <c r="Z11" s="12" t="n"/>
+      <c r="AA11" s="13" t="n"/>
+      <c r="AB11" s="14" t="inlineStr"/>
+      <c r="AC11" s="12" t="n"/>
+      <c r="AD11" s="12" t="n"/>
+      <c r="AE11" s="12" t="n"/>
+      <c r="AF11" s="12" t="n"/>
+      <c r="AG11" s="12" t="n"/>
+      <c r="AH11" s="12" t="n"/>
+      <c r="AI11" s="12" t="n"/>
+      <c r="AJ11" s="12" t="n"/>
+      <c r="AK11" s="12" t="n"/>
+      <c r="AL11" s="12" t="n"/>
+      <c r="AM11" s="12" t="n"/>
+      <c r="AN11" s="15" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="543" t="inlineStr">
+      <c r="A12" s="652" t="inlineStr">
         <is>
           <t>Evidence Folder</t>
         </is>
       </c>
-      <c r="B12" s="544" t="n"/>
-      <c r="C12" s="544" t="n"/>
-      <c r="D12" s="544" t="n"/>
-      <c r="E12" s="544" t="n"/>
-      <c r="F12" s="544" t="n"/>
-      <c r="G12" s="544" t="n"/>
-      <c r="H12" s="545" t="inlineStr"/>
-      <c r="I12" s="544" t="n"/>
-      <c r="J12" s="544" t="n"/>
-      <c r="K12" s="544" t="n"/>
-      <c r="L12" s="544" t="n"/>
-      <c r="M12" s="544" t="n"/>
-      <c r="N12" s="544" t="n"/>
-      <c r="O12" s="544" t="n"/>
-      <c r="P12" s="544" t="n"/>
-      <c r="Q12" s="544" t="n"/>
-      <c r="R12" s="544" t="n"/>
-      <c r="S12" s="544" t="n"/>
-      <c r="T12" s="544" t="n"/>
-      <c r="U12" s="546" t="inlineStr">
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="23" t="inlineStr"/>
+      <c r="I12" s="19" t="n"/>
+      <c r="J12" s="19" t="n"/>
+      <c r="K12" s="19" t="n"/>
+      <c r="L12" s="19" t="n"/>
+      <c r="M12" s="19" t="n"/>
+      <c r="N12" s="19" t="n"/>
+      <c r="O12" s="19" t="n"/>
+      <c r="P12" s="19" t="n"/>
+      <c r="Q12" s="19" t="n"/>
+      <c r="R12" s="19" t="n"/>
+      <c r="S12" s="19" t="n"/>
+      <c r="T12" s="22" t="n"/>
+      <c r="U12" s="653" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="V12" s="544" t="n"/>
-      <c r="W12" s="544" t="n"/>
-      <c r="X12" s="544" t="n"/>
-      <c r="Y12" s="544" t="n"/>
-      <c r="Z12" s="544" t="n"/>
-      <c r="AA12" s="544" t="n"/>
-      <c r="AB12" s="545" t="inlineStr"/>
-      <c r="AC12" s="544" t="n"/>
-      <c r="AD12" s="544" t="n"/>
-      <c r="AE12" s="544" t="n"/>
-      <c r="AF12" s="544" t="n"/>
-      <c r="AG12" s="544" t="n"/>
-      <c r="AH12" s="544" t="n"/>
-      <c r="AI12" s="544" t="n"/>
-      <c r="AJ12" s="544" t="n"/>
-      <c r="AK12" s="544" t="n"/>
-      <c r="AL12" s="544" t="n"/>
-      <c r="AM12" s="544" t="n"/>
-      <c r="AN12" s="547" t="n"/>
+      <c r="V12" s="19" t="n"/>
+      <c r="W12" s="19" t="n"/>
+      <c r="X12" s="19" t="n"/>
+      <c r="Y12" s="19" t="n"/>
+      <c r="Z12" s="19" t="n"/>
+      <c r="AA12" s="22" t="n"/>
+      <c r="AB12" s="23" t="inlineStr"/>
+      <c r="AC12" s="19" t="n"/>
+      <c r="AD12" s="19" t="n"/>
+      <c r="AE12" s="19" t="n"/>
+      <c r="AF12" s="19" t="n"/>
+      <c r="AG12" s="19" t="n"/>
+      <c r="AH12" s="19" t="n"/>
+      <c r="AI12" s="19" t="n"/>
+      <c r="AJ12" s="19" t="n"/>
+      <c r="AK12" s="19" t="n"/>
+      <c r="AL12" s="19" t="n"/>
+      <c r="AM12" s="19" t="n"/>
+      <c r="AN12" s="24" t="n"/>
     </row>
     <row r="13" ht="3" customHeight="1">
-      <c r="A13" s="410" t="n"/>
-      <c r="B13" s="482" t="n"/>
-      <c r="C13" s="482" t="n"/>
-      <c r="D13" s="482" t="n"/>
-      <c r="E13" s="482" t="n"/>
-      <c r="F13" s="482" t="n"/>
-      <c r="G13" s="482" t="n"/>
-      <c r="H13" s="482" t="n"/>
-      <c r="I13" s="482" t="n"/>
-      <c r="J13" s="482" t="n"/>
-      <c r="K13" s="482" t="n"/>
-      <c r="L13" s="482" t="n"/>
-      <c r="M13" s="482" t="n"/>
-      <c r="N13" s="482" t="n"/>
-      <c r="O13" s="482" t="n"/>
-      <c r="P13" s="482" t="n"/>
-      <c r="Q13" s="482" t="n"/>
-      <c r="R13" s="482" t="n"/>
-      <c r="S13" s="482" t="n"/>
-      <c r="T13" s="482" t="n"/>
-      <c r="U13" s="482" t="n"/>
-      <c r="V13" s="482" t="n"/>
-      <c r="W13" s="482" t="n"/>
-      <c r="X13" s="482" t="n"/>
-      <c r="Y13" s="482" t="n"/>
-      <c r="Z13" s="482" t="n"/>
-      <c r="AA13" s="482" t="n"/>
-      <c r="AB13" s="482" t="n"/>
-      <c r="AC13" s="482" t="n"/>
-      <c r="AD13" s="482" t="n"/>
-      <c r="AE13" s="482" t="n"/>
-      <c r="AF13" s="482" t="n"/>
-      <c r="AG13" s="482" t="n"/>
-      <c r="AH13" s="482" t="n"/>
-      <c r="AI13" s="482" t="n"/>
-      <c r="AJ13" s="482" t="n"/>
-      <c r="AK13" s="482" t="n"/>
-      <c r="AL13" s="482" t="n"/>
-      <c r="AM13" s="482" t="n"/>
-      <c r="AN13" s="482" t="n"/>
+      <c r="A13" s="654" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="10" t="n"/>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="10" t="n"/>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="n"/>
+      <c r="U13" s="10" t="n"/>
+      <c r="V13" s="10" t="n"/>
+      <c r="W13" s="10" t="n"/>
+      <c r="X13" s="10" t="n"/>
+      <c r="Y13" s="10" t="n"/>
+      <c r="Z13" s="10" t="n"/>
+      <c r="AA13" s="10" t="n"/>
+      <c r="AB13" s="10" t="n"/>
+      <c r="AC13" s="10" t="n"/>
+      <c r="AD13" s="10" t="n"/>
+      <c r="AE13" s="10" t="n"/>
+      <c r="AF13" s="10" t="n"/>
+      <c r="AG13" s="10" t="n"/>
+      <c r="AH13" s="10" t="n"/>
+      <c r="AI13" s="10" t="n"/>
+      <c r="AJ13" s="10" t="n"/>
+      <c r="AK13" s="10" t="n"/>
+      <c r="AL13" s="10" t="n"/>
+      <c r="AM13" s="10" t="n"/>
+      <c r="AN13" s="10" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="531" t="inlineStr">
+      <c r="A14" s="647" t="inlineStr">
         <is>
           <t>2.  READINESS DECISION / OPEN RISK CONDITIONS</t>
         </is>
       </c>
-      <c r="B14" s="532" t="n"/>
-      <c r="C14" s="532" t="n"/>
-      <c r="D14" s="532" t="n"/>
-      <c r="E14" s="532" t="n"/>
-      <c r="F14" s="532" t="n"/>
-      <c r="G14" s="532" t="n"/>
-      <c r="H14" s="532" t="n"/>
-      <c r="I14" s="532" t="n"/>
-      <c r="J14" s="532" t="n"/>
-      <c r="K14" s="532" t="n"/>
-      <c r="L14" s="532" t="n"/>
-      <c r="M14" s="532" t="n"/>
-      <c r="N14" s="532" t="n"/>
-      <c r="O14" s="532" t="n"/>
-      <c r="P14" s="532" t="n"/>
-      <c r="Q14" s="532" t="n"/>
-      <c r="R14" s="532" t="n"/>
-      <c r="S14" s="532" t="n"/>
-      <c r="T14" s="532" t="n"/>
-      <c r="U14" s="532" t="n"/>
-      <c r="V14" s="532" t="n"/>
-      <c r="W14" s="532" t="n"/>
-      <c r="X14" s="532" t="n"/>
-      <c r="Y14" s="532" t="n"/>
-      <c r="Z14" s="532" t="n"/>
-      <c r="AA14" s="532" t="n"/>
-      <c r="AB14" s="532" t="n"/>
-      <c r="AC14" s="532" t="n"/>
-      <c r="AD14" s="532" t="n"/>
-      <c r="AE14" s="532" t="n"/>
-      <c r="AF14" s="532" t="n"/>
-      <c r="AG14" s="532" t="n"/>
-      <c r="AH14" s="532" t="n"/>
-      <c r="AI14" s="532" t="n"/>
-      <c r="AJ14" s="532" t="n"/>
-      <c r="AK14" s="532" t="n"/>
-      <c r="AL14" s="532" t="n"/>
-      <c r="AM14" s="532" t="n"/>
-      <c r="AN14" s="533" t="n"/>
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="27" t="n"/>
+      <c r="H14" s="27" t="n"/>
+      <c r="I14" s="27" t="n"/>
+      <c r="J14" s="27" t="n"/>
+      <c r="K14" s="27" t="n"/>
+      <c r="L14" s="27" t="n"/>
+      <c r="M14" s="27" t="n"/>
+      <c r="N14" s="27" t="n"/>
+      <c r="O14" s="27" t="n"/>
+      <c r="P14" s="27" t="n"/>
+      <c r="Q14" s="27" t="n"/>
+      <c r="R14" s="27" t="n"/>
+      <c r="S14" s="27" t="n"/>
+      <c r="T14" s="27" t="n"/>
+      <c r="U14" s="27" t="n"/>
+      <c r="V14" s="27" t="n"/>
+      <c r="W14" s="27" t="n"/>
+      <c r="X14" s="27" t="n"/>
+      <c r="Y14" s="27" t="n"/>
+      <c r="Z14" s="27" t="n"/>
+      <c r="AA14" s="27" t="n"/>
+      <c r="AB14" s="27" t="n"/>
+      <c r="AC14" s="27" t="n"/>
+      <c r="AD14" s="27" t="n"/>
+      <c r="AE14" s="27" t="n"/>
+      <c r="AF14" s="27" t="n"/>
+      <c r="AG14" s="27" t="n"/>
+      <c r="AH14" s="27" t="n"/>
+      <c r="AI14" s="27" t="n"/>
+      <c r="AJ14" s="27" t="n"/>
+      <c r="AK14" s="27" t="n"/>
+      <c r="AL14" s="27" t="n"/>
+      <c r="AM14" s="27" t="n"/>
+      <c r="AN14" s="28" t="n"/>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="534" t="inlineStr">
+      <c r="A15" s="648" t="inlineStr">
         <is>
           <t>Gate Name / Trigger</t>
         </is>
       </c>
-      <c r="B15" s="535" t="n"/>
-      <c r="C15" s="535" t="n"/>
-      <c r="D15" s="535" t="n"/>
-      <c r="E15" s="535" t="n"/>
-      <c r="F15" s="535" t="n"/>
-      <c r="G15" s="535" t="n"/>
-      <c r="H15" s="536" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="30" t="inlineStr">
         <is>
           <t>High-risk job release review</t>
         </is>
       </c>
-      <c r="I15" s="535" t="n"/>
-      <c r="J15" s="535" t="n"/>
-      <c r="K15" s="535" t="n"/>
-      <c r="L15" s="535" t="n"/>
-      <c r="M15" s="535" t="n"/>
-      <c r="N15" s="535" t="n"/>
-      <c r="O15" s="535" t="n"/>
-      <c r="P15" s="535" t="n"/>
-      <c r="Q15" s="535" t="n"/>
-      <c r="R15" s="535" t="n"/>
-      <c r="S15" s="535" t="n"/>
-      <c r="T15" s="535" t="n"/>
-      <c r="U15" s="537" t="inlineStr">
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="6" t="n"/>
+      <c r="U15" s="649" t="inlineStr">
         <is>
           <t>Gate Conclusion</t>
         </is>
       </c>
-      <c r="V15" s="535" t="n"/>
-      <c r="W15" s="535" t="n"/>
-      <c r="X15" s="535" t="n"/>
-      <c r="Y15" s="535" t="n"/>
-      <c r="Z15" s="535" t="n"/>
-      <c r="AA15" s="535" t="n"/>
-      <c r="AB15" s="536">
+      <c r="V15" s="5" t="n"/>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="5" t="n"/>
+      <c r="Y15" s="5" t="n"/>
+      <c r="Z15" s="5" t="n"/>
+      <c r="AA15" s="6" t="n"/>
+      <c r="AB15" s="30">
         <f>IF(COUNTA(AF22:AF31)=0,"",IF(COUNTIF(AF22:AF31,"FAIL")+COUNTIF(AF22:AF31,"HOLD")&gt;0,"HOLD",IF(COUNTIF(AF22:AF31,"PASS")=COUNTA(AF22:AF31),"APPROVED","CONDITIONAL")))</f>
         <v/>
       </c>
-      <c r="AC15" s="535" t="n"/>
-      <c r="AD15" s="535" t="n"/>
-      <c r="AE15" s="535" t="n"/>
-      <c r="AF15" s="535" t="n"/>
-      <c r="AG15" s="535" t="n"/>
-      <c r="AH15" s="535" t="n"/>
-      <c r="AI15" s="535" t="n"/>
-      <c r="AJ15" s="535" t="n"/>
-      <c r="AK15" s="535" t="n"/>
-      <c r="AL15" s="535" t="n"/>
-      <c r="AM15" s="535" t="n"/>
-      <c r="AN15" s="538" t="n"/>
+      <c r="AC15" s="5" t="n"/>
+      <c r="AD15" s="5" t="n"/>
+      <c r="AE15" s="5" t="n"/>
+      <c r="AF15" s="5" t="n"/>
+      <c r="AG15" s="5" t="n"/>
+      <c r="AH15" s="5" t="n"/>
+      <c r="AI15" s="5" t="n"/>
+      <c r="AJ15" s="5" t="n"/>
+      <c r="AK15" s="5" t="n"/>
+      <c r="AL15" s="5" t="n"/>
+      <c r="AM15" s="5" t="n"/>
+      <c r="AN15" s="8" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="539" t="inlineStr">
+      <c r="A16" s="650" t="inlineStr">
         <is>
           <t>Open Risk / Hold Reason</t>
         </is>
       </c>
-      <c r="B16" s="398" t="n"/>
-      <c r="C16" s="398" t="n"/>
-      <c r="D16" s="398" t="n"/>
-      <c r="E16" s="398" t="n"/>
-      <c r="F16" s="398" t="n"/>
-      <c r="G16" s="398" t="n"/>
-      <c r="H16" s="540" t="inlineStr"/>
-      <c r="I16" s="398" t="n"/>
-      <c r="J16" s="398" t="n"/>
-      <c r="K16" s="398" t="n"/>
-      <c r="L16" s="398" t="n"/>
-      <c r="M16" s="398" t="n"/>
-      <c r="N16" s="398" t="n"/>
-      <c r="O16" s="398" t="n"/>
-      <c r="P16" s="398" t="n"/>
-      <c r="Q16" s="398" t="n"/>
-      <c r="R16" s="398" t="n"/>
-      <c r="S16" s="398" t="n"/>
-      <c r="T16" s="398" t="n"/>
-      <c r="U16" s="541" t="inlineStr">
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="14" t="inlineStr"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
+      <c r="M16" s="12" t="n"/>
+      <c r="N16" s="12" t="n"/>
+      <c r="O16" s="12" t="n"/>
+      <c r="P16" s="12" t="n"/>
+      <c r="Q16" s="12" t="n"/>
+      <c r="R16" s="12" t="n"/>
+      <c r="S16" s="12" t="n"/>
+      <c r="T16" s="13" t="n"/>
+      <c r="U16" s="651" t="inlineStr">
         <is>
           <t>Next Step</t>
         </is>
       </c>
-      <c r="V16" s="398" t="n"/>
-      <c r="W16" s="398" t="n"/>
-      <c r="X16" s="398" t="n"/>
-      <c r="Y16" s="398" t="n"/>
-      <c r="Z16" s="398" t="n"/>
-      <c r="AA16" s="398" t="n"/>
-      <c r="AB16" s="540" t="inlineStr"/>
-      <c r="AC16" s="398" t="n"/>
-      <c r="AD16" s="398" t="n"/>
-      <c r="AE16" s="398" t="n"/>
-      <c r="AF16" s="398" t="n"/>
-      <c r="AG16" s="398" t="n"/>
-      <c r="AH16" s="398" t="n"/>
-      <c r="AI16" s="398" t="n"/>
-      <c r="AJ16" s="398" t="n"/>
-      <c r="AK16" s="398" t="n"/>
-      <c r="AL16" s="398" t="n"/>
-      <c r="AM16" s="398" t="n"/>
-      <c r="AN16" s="542" t="n"/>
+      <c r="V16" s="12" t="n"/>
+      <c r="W16" s="12" t="n"/>
+      <c r="X16" s="12" t="n"/>
+      <c r="Y16" s="12" t="n"/>
+      <c r="Z16" s="12" t="n"/>
+      <c r="AA16" s="13" t="n"/>
+      <c r="AB16" s="14" t="inlineStr"/>
+      <c r="AC16" s="12" t="n"/>
+      <c r="AD16" s="12" t="n"/>
+      <c r="AE16" s="12" t="n"/>
+      <c r="AF16" s="12" t="n"/>
+      <c r="AG16" s="12" t="n"/>
+      <c r="AH16" s="12" t="n"/>
+      <c r="AI16" s="12" t="n"/>
+      <c r="AJ16" s="12" t="n"/>
+      <c r="AK16" s="12" t="n"/>
+      <c r="AL16" s="12" t="n"/>
+      <c r="AM16" s="12" t="n"/>
+      <c r="AN16" s="15" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="539" t="inlineStr">
+      <c r="A17" s="650" t="inlineStr">
         <is>
           <t>Action Owner</t>
         </is>
       </c>
-      <c r="B17" s="398" t="n"/>
-      <c r="C17" s="398" t="n"/>
-      <c r="D17" s="398" t="n"/>
-      <c r="E17" s="398" t="n"/>
-      <c r="F17" s="398" t="n"/>
-      <c r="G17" s="398" t="n"/>
-      <c r="H17" s="540" t="inlineStr"/>
-      <c r="I17" s="398" t="n"/>
-      <c r="J17" s="398" t="n"/>
-      <c r="K17" s="398" t="n"/>
-      <c r="L17" s="398" t="n"/>
-      <c r="M17" s="398" t="n"/>
-      <c r="N17" s="398" t="n"/>
-      <c r="O17" s="398" t="n"/>
-      <c r="P17" s="398" t="n"/>
-      <c r="Q17" s="398" t="n"/>
-      <c r="R17" s="398" t="n"/>
-      <c r="S17" s="398" t="n"/>
-      <c r="T17" s="398" t="n"/>
-      <c r="U17" s="541" t="inlineStr">
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="14" t="inlineStr"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="12" t="n"/>
+      <c r="P17" s="12" t="n"/>
+      <c r="Q17" s="12" t="n"/>
+      <c r="R17" s="12" t="n"/>
+      <c r="S17" s="12" t="n"/>
+      <c r="T17" s="13" t="n"/>
+      <c r="U17" s="651" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="V17" s="398" t="n"/>
-      <c r="W17" s="398" t="n"/>
-      <c r="X17" s="398" t="n"/>
-      <c r="Y17" s="398" t="n"/>
-      <c r="Z17" s="398" t="n"/>
-      <c r="AA17" s="398" t="n"/>
-      <c r="AB17" s="540" t="inlineStr"/>
-      <c r="AC17" s="398" t="n"/>
-      <c r="AD17" s="398" t="n"/>
-      <c r="AE17" s="398" t="n"/>
-      <c r="AF17" s="398" t="n"/>
-      <c r="AG17" s="398" t="n"/>
-      <c r="AH17" s="398" t="n"/>
-      <c r="AI17" s="398" t="n"/>
-      <c r="AJ17" s="398" t="n"/>
-      <c r="AK17" s="398" t="n"/>
-      <c r="AL17" s="398" t="n"/>
-      <c r="AM17" s="398" t="n"/>
-      <c r="AN17" s="542" t="n"/>
+      <c r="V17" s="12" t="n"/>
+      <c r="W17" s="12" t="n"/>
+      <c r="X17" s="12" t="n"/>
+      <c r="Y17" s="12" t="n"/>
+      <c r="Z17" s="12" t="n"/>
+      <c r="AA17" s="13" t="n"/>
+      <c r="AB17" s="14" t="inlineStr"/>
+      <c r="AC17" s="12" t="n"/>
+      <c r="AD17" s="12" t="n"/>
+      <c r="AE17" s="12" t="n"/>
+      <c r="AF17" s="12" t="n"/>
+      <c r="AG17" s="12" t="n"/>
+      <c r="AH17" s="12" t="n"/>
+      <c r="AI17" s="12" t="n"/>
+      <c r="AJ17" s="12" t="n"/>
+      <c r="AK17" s="12" t="n"/>
+      <c r="AL17" s="12" t="n"/>
+      <c r="AM17" s="12" t="n"/>
+      <c r="AN17" s="15" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="543" t="inlineStr">
+      <c r="A18" s="652" t="inlineStr">
         <is>
           <t>Escalation if Overdue</t>
         </is>
       </c>
-      <c r="B18" s="544" t="n"/>
-      <c r="C18" s="544" t="n"/>
-      <c r="D18" s="544" t="n"/>
-      <c r="E18" s="544" t="n"/>
-      <c r="F18" s="544" t="n"/>
-      <c r="G18" s="544" t="n"/>
-      <c r="H18" s="545" t="inlineStr"/>
-      <c r="I18" s="544" t="n"/>
-      <c r="J18" s="544" t="n"/>
-      <c r="K18" s="544" t="n"/>
-      <c r="L18" s="544" t="n"/>
-      <c r="M18" s="544" t="n"/>
-      <c r="N18" s="544" t="n"/>
-      <c r="O18" s="544" t="n"/>
-      <c r="P18" s="544" t="n"/>
-      <c r="Q18" s="544" t="n"/>
-      <c r="R18" s="544" t="n"/>
-      <c r="S18" s="544" t="n"/>
-      <c r="T18" s="544" t="n"/>
-      <c r="U18" s="546" t="inlineStr">
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="23" t="inlineStr"/>
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="19" t="n"/>
+      <c r="K18" s="19" t="n"/>
+      <c r="L18" s="19" t="n"/>
+      <c r="M18" s="19" t="n"/>
+      <c r="N18" s="19" t="n"/>
+      <c r="O18" s="19" t="n"/>
+      <c r="P18" s="19" t="n"/>
+      <c r="Q18" s="19" t="n"/>
+      <c r="R18" s="19" t="n"/>
+      <c r="S18" s="19" t="n"/>
+      <c r="T18" s="22" t="n"/>
+      <c r="U18" s="653" t="inlineStr">
         <is>
           <t>Gate Status</t>
         </is>
       </c>
-      <c r="V18" s="544" t="n"/>
-      <c r="W18" s="544" t="n"/>
-      <c r="X18" s="544" t="n"/>
-      <c r="Y18" s="544" t="n"/>
-      <c r="Z18" s="544" t="n"/>
-      <c r="AA18" s="544" t="n"/>
-      <c r="AB18" s="545">
+      <c r="V18" s="19" t="n"/>
+      <c r="W18" s="19" t="n"/>
+      <c r="X18" s="19" t="n"/>
+      <c r="Y18" s="19" t="n"/>
+      <c r="Z18" s="19" t="n"/>
+      <c r="AA18" s="22" t="n"/>
+      <c r="AB18" s="23">
         <f>IF(COUNTA(AF22:AF31)=0,"",IF(COUNTIF(AF22:AF31,"FAIL")+COUNTIF(AF22:AF31,"HOLD")&gt;0,"OPEN","CLOSED"))</f>
         <v/>
       </c>
-      <c r="AC18" s="544" t="n"/>
-      <c r="AD18" s="544" t="n"/>
-      <c r="AE18" s="544" t="n"/>
-      <c r="AF18" s="544" t="n"/>
-      <c r="AG18" s="544" t="n"/>
-      <c r="AH18" s="544" t="n"/>
-      <c r="AI18" s="544" t="n"/>
-      <c r="AJ18" s="544" t="n"/>
-      <c r="AK18" s="544" t="n"/>
-      <c r="AL18" s="544" t="n"/>
-      <c r="AM18" s="544" t="n"/>
-      <c r="AN18" s="547" t="n"/>
+      <c r="AC18" s="19" t="n"/>
+      <c r="AD18" s="19" t="n"/>
+      <c r="AE18" s="19" t="n"/>
+      <c r="AF18" s="19" t="n"/>
+      <c r="AG18" s="19" t="n"/>
+      <c r="AH18" s="19" t="n"/>
+      <c r="AI18" s="19" t="n"/>
+      <c r="AJ18" s="19" t="n"/>
+      <c r="AK18" s="19" t="n"/>
+      <c r="AL18" s="19" t="n"/>
+      <c r="AM18" s="19" t="n"/>
+      <c r="AN18" s="24" t="n"/>
     </row>
     <row r="19" ht="3" customHeight="1">
-      <c r="A19" s="410" t="n"/>
-      <c r="B19" s="482" t="n"/>
-      <c r="C19" s="482" t="n"/>
-      <c r="D19" s="482" t="n"/>
-      <c r="E19" s="482" t="n"/>
-      <c r="F19" s="482" t="n"/>
-      <c r="G19" s="482" t="n"/>
-      <c r="H19" s="482" t="n"/>
-      <c r="I19" s="482" t="n"/>
-      <c r="J19" s="482" t="n"/>
-      <c r="K19" s="482" t="n"/>
-      <c r="L19" s="482" t="n"/>
-      <c r="M19" s="482" t="n"/>
-      <c r="N19" s="482" t="n"/>
-      <c r="O19" s="482" t="n"/>
-      <c r="P19" s="482" t="n"/>
-      <c r="Q19" s="482" t="n"/>
-      <c r="R19" s="482" t="n"/>
-      <c r="S19" s="482" t="n"/>
-      <c r="T19" s="482" t="n"/>
-      <c r="U19" s="482" t="n"/>
-      <c r="V19" s="482" t="n"/>
-      <c r="W19" s="482" t="n"/>
-      <c r="X19" s="482" t="n"/>
-      <c r="Y19" s="482" t="n"/>
-      <c r="Z19" s="482" t="n"/>
-      <c r="AA19" s="482" t="n"/>
-      <c r="AB19" s="482" t="n"/>
-      <c r="AC19" s="482" t="n"/>
-      <c r="AD19" s="482" t="n"/>
-      <c r="AE19" s="482" t="n"/>
-      <c r="AF19" s="482" t="n"/>
-      <c r="AG19" s="482" t="n"/>
-      <c r="AH19" s="482" t="n"/>
-      <c r="AI19" s="482" t="n"/>
-      <c r="AJ19" s="482" t="n"/>
-      <c r="AK19" s="482" t="n"/>
-      <c r="AL19" s="482" t="n"/>
-      <c r="AM19" s="482" t="n"/>
-      <c r="AN19" s="482" t="n"/>
+      <c r="A19" s="654" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="10" t="n"/>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="10" t="n"/>
+      <c r="O19" s="10" t="n"/>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="10" t="n"/>
+      <c r="R19" s="10" t="n"/>
+      <c r="S19" s="10" t="n"/>
+      <c r="T19" s="10" t="n"/>
+      <c r="U19" s="10" t="n"/>
+      <c r="V19" s="10" t="n"/>
+      <c r="W19" s="10" t="n"/>
+      <c r="X19" s="10" t="n"/>
+      <c r="Y19" s="10" t="n"/>
+      <c r="Z19" s="10" t="n"/>
+      <c r="AA19" s="10" t="n"/>
+      <c r="AB19" s="10" t="n"/>
+      <c r="AC19" s="10" t="n"/>
+      <c r="AD19" s="10" t="n"/>
+      <c r="AE19" s="10" t="n"/>
+      <c r="AF19" s="10" t="n"/>
+      <c r="AG19" s="10" t="n"/>
+      <c r="AH19" s="10" t="n"/>
+      <c r="AI19" s="10" t="n"/>
+      <c r="AJ19" s="10" t="n"/>
+      <c r="AK19" s="10" t="n"/>
+      <c r="AL19" s="10" t="n"/>
+      <c r="AM19" s="10" t="n"/>
+      <c r="AN19" s="10" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="531" t="inlineStr">
+      <c r="A20" s="647" t="inlineStr">
         <is>
           <t>3.  READINESS CRITERIA / RISK CHECK</t>
         </is>
       </c>
-      <c r="B20" s="532" t="n"/>
-      <c r="C20" s="532" t="n"/>
-      <c r="D20" s="532" t="n"/>
-      <c r="E20" s="532" t="n"/>
-      <c r="F20" s="532" t="n"/>
-      <c r="G20" s="532" t="n"/>
-      <c r="H20" s="532" t="n"/>
-      <c r="I20" s="532" t="n"/>
-      <c r="J20" s="532" t="n"/>
-      <c r="K20" s="532" t="n"/>
-      <c r="L20" s="532" t="n"/>
-      <c r="M20" s="532" t="n"/>
-      <c r="N20" s="532" t="n"/>
-      <c r="O20" s="532" t="n"/>
-      <c r="P20" s="532" t="n"/>
-      <c r="Q20" s="532" t="n"/>
-      <c r="R20" s="532" t="n"/>
-      <c r="S20" s="532" t="n"/>
-      <c r="T20" s="532" t="n"/>
-      <c r="U20" s="532" t="n"/>
-      <c r="V20" s="532" t="n"/>
-      <c r="W20" s="532" t="n"/>
-      <c r="X20" s="532" t="n"/>
-      <c r="Y20" s="532" t="n"/>
-      <c r="Z20" s="532" t="n"/>
-      <c r="AA20" s="532" t="n"/>
-      <c r="AB20" s="532" t="n"/>
-      <c r="AC20" s="532" t="n"/>
-      <c r="AD20" s="532" t="n"/>
-      <c r="AE20" s="532" t="n"/>
-      <c r="AF20" s="532" t="n"/>
-      <c r="AG20" s="532" t="n"/>
-      <c r="AH20" s="532" t="n"/>
-      <c r="AI20" s="532" t="n"/>
-      <c r="AJ20" s="532" t="n"/>
-      <c r="AK20" s="532" t="n"/>
-      <c r="AL20" s="532" t="n"/>
-      <c r="AM20" s="532" t="n"/>
-      <c r="AN20" s="533" t="n"/>
+      <c r="B20" s="27" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="27" t="n"/>
+      <c r="H20" s="27" t="n"/>
+      <c r="I20" s="27" t="n"/>
+      <c r="J20" s="27" t="n"/>
+      <c r="K20" s="27" t="n"/>
+      <c r="L20" s="27" t="n"/>
+      <c r="M20" s="27" t="n"/>
+      <c r="N20" s="27" t="n"/>
+      <c r="O20" s="27" t="n"/>
+      <c r="P20" s="27" t="n"/>
+      <c r="Q20" s="27" t="n"/>
+      <c r="R20" s="27" t="n"/>
+      <c r="S20" s="27" t="n"/>
+      <c r="T20" s="27" t="n"/>
+      <c r="U20" s="27" t="n"/>
+      <c r="V20" s="27" t="n"/>
+      <c r="W20" s="27" t="n"/>
+      <c r="X20" s="27" t="n"/>
+      <c r="Y20" s="27" t="n"/>
+      <c r="Z20" s="27" t="n"/>
+      <c r="AA20" s="27" t="n"/>
+      <c r="AB20" s="27" t="n"/>
+      <c r="AC20" s="27" t="n"/>
+      <c r="AD20" s="27" t="n"/>
+      <c r="AE20" s="27" t="n"/>
+      <c r="AF20" s="27" t="n"/>
+      <c r="AG20" s="27" t="n"/>
+      <c r="AH20" s="27" t="n"/>
+      <c r="AI20" s="27" t="n"/>
+      <c r="AJ20" s="27" t="n"/>
+      <c r="AK20" s="27" t="n"/>
+      <c r="AL20" s="27" t="n"/>
+      <c r="AM20" s="27" t="n"/>
+      <c r="AN20" s="28" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="548" t="inlineStr">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B21" s="549" t="n"/>
-      <c r="C21" s="550" t="inlineStr">
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="D21" s="549" t="n"/>
-      <c r="E21" s="549" t="n"/>
-      <c r="F21" s="550" t="inlineStr">
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>Readiness / Risk Item</t>
         </is>
       </c>
-      <c r="G21" s="549" t="n"/>
-      <c r="H21" s="549" t="n"/>
-      <c r="I21" s="549" t="n"/>
-      <c r="J21" s="549" t="n"/>
-      <c r="K21" s="549" t="n"/>
-      <c r="L21" s="549" t="n"/>
-      <c r="M21" s="549" t="n"/>
-      <c r="N21" s="549" t="n"/>
-      <c r="O21" s="549" t="n"/>
-      <c r="P21" s="549" t="n"/>
-      <c r="Q21" s="549" t="n"/>
-      <c r="R21" s="549" t="n"/>
-      <c r="S21" s="549" t="n"/>
-      <c r="T21" s="550" t="inlineStr">
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="6" t="n"/>
+      <c r="T21" s="37" t="inlineStr">
         <is>
           <t>Acceptance / Control Rule</t>
         </is>
       </c>
-      <c r="U21" s="549" t="n"/>
-      <c r="V21" s="549" t="n"/>
-      <c r="W21" s="549" t="n"/>
-      <c r="X21" s="549" t="n"/>
-      <c r="Y21" s="549" t="n"/>
-      <c r="Z21" s="549" t="n"/>
-      <c r="AA21" s="549" t="n"/>
-      <c r="AB21" s="549" t="n"/>
-      <c r="AC21" s="549" t="n"/>
-      <c r="AD21" s="549" t="n"/>
-      <c r="AE21" s="549" t="n"/>
-      <c r="AF21" s="550" t="inlineStr">
+      <c r="U21" s="5" t="n"/>
+      <c r="V21" s="5" t="n"/>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+      <c r="Y21" s="5" t="n"/>
+      <c r="Z21" s="5" t="n"/>
+      <c r="AA21" s="5" t="n"/>
+      <c r="AB21" s="5" t="n"/>
+      <c r="AC21" s="5" t="n"/>
+      <c r="AD21" s="5" t="n"/>
+      <c r="AE21" s="6" t="n"/>
+      <c r="AF21" s="37" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG21" s="549" t="n"/>
-      <c r="AH21" s="549" t="n"/>
-      <c r="AI21" s="549" t="n"/>
-      <c r="AJ21" s="550" t="inlineStr">
+      <c r="AG21" s="5" t="n"/>
+      <c r="AH21" s="5" t="n"/>
+      <c r="AI21" s="6" t="n"/>
+      <c r="AJ21" s="37" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK21" s="549" t="n"/>
-      <c r="AL21" s="549" t="n"/>
-      <c r="AM21" s="550" t="inlineStr">
+      <c r="AK21" s="5" t="n"/>
+      <c r="AL21" s="6" t="n"/>
+      <c r="AM21" s="37" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="AN21" s="551" t="n"/>
+      <c r="AN21" s="8" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="552" t="n">
+      <c r="A22" s="655" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="535" t="n"/>
-      <c r="C22" s="553" t="inlineStr">
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="656" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D22" s="535" t="n"/>
-      <c r="E22" s="535" t="n"/>
-      <c r="F22" s="554" t="inlineStr">
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="657" t="inlineStr">
         <is>
           <t>Released baseline package is locked.</t>
         </is>
       </c>
-      <c r="G22" s="535" t="n"/>
-      <c r="H22" s="535" t="n"/>
-      <c r="I22" s="535" t="n"/>
-      <c r="J22" s="535" t="n"/>
-      <c r="K22" s="535" t="n"/>
-      <c r="L22" s="535" t="n"/>
-      <c r="M22" s="535" t="n"/>
-      <c r="N22" s="535" t="n"/>
-      <c r="O22" s="535" t="n"/>
-      <c r="P22" s="535" t="n"/>
-      <c r="Q22" s="535" t="n"/>
-      <c r="R22" s="535" t="n"/>
-      <c r="S22" s="535" t="n"/>
-      <c r="T22" s="555" t="inlineStr">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+      <c r="Q22" s="5" t="n"/>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" s="6" t="n"/>
+      <c r="T22" s="658" t="inlineStr">
         <is>
           <t>FRM-306 or released package reference is current.</t>
         </is>
       </c>
-      <c r="U22" s="535" t="n"/>
-      <c r="V22" s="535" t="n"/>
-      <c r="W22" s="535" t="n"/>
-      <c r="X22" s="535" t="n"/>
-      <c r="Y22" s="535" t="n"/>
-      <c r="Z22" s="535" t="n"/>
-      <c r="AA22" s="535" t="n"/>
-      <c r="AB22" s="535" t="n"/>
-      <c r="AC22" s="535" t="n"/>
-      <c r="AD22" s="535" t="n"/>
-      <c r="AE22" s="535" t="n"/>
-      <c r="AF22" s="554" t="n"/>
-      <c r="AG22" s="535" t="n"/>
-      <c r="AH22" s="535" t="n"/>
-      <c r="AI22" s="535" t="n"/>
-      <c r="AJ22" s="554" t="n"/>
-      <c r="AK22" s="535" t="n"/>
-      <c r="AL22" s="535" t="n"/>
-      <c r="AM22" s="554" t="n"/>
-      <c r="AN22" s="538" t="n"/>
+      <c r="U22" s="5" t="n"/>
+      <c r="V22" s="5" t="n"/>
+      <c r="W22" s="5" t="n"/>
+      <c r="X22" s="5" t="n"/>
+      <c r="Y22" s="5" t="n"/>
+      <c r="Z22" s="5" t="n"/>
+      <c r="AA22" s="5" t="n"/>
+      <c r="AB22" s="5" t="n"/>
+      <c r="AC22" s="5" t="n"/>
+      <c r="AD22" s="5" t="n"/>
+      <c r="AE22" s="6" t="n"/>
+      <c r="AF22" s="657" t="n"/>
+      <c r="AG22" s="5" t="n"/>
+      <c r="AH22" s="5" t="n"/>
+      <c r="AI22" s="6" t="n"/>
+      <c r="AJ22" s="657" t="n"/>
+      <c r="AK22" s="5" t="n"/>
+      <c r="AL22" s="6" t="n"/>
+      <c r="AM22" s="657" t="n"/>
+      <c r="AN22" s="8" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="556" t="n">
+      <c r="A23" s="659" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="398" t="n"/>
-      <c r="C23" s="557" t="inlineStr">
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="660" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D23" s="398" t="n"/>
-      <c r="E23" s="398" t="n"/>
-      <c r="F23" s="558" t="inlineStr">
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="661" t="inlineStr">
         <is>
           <t>Customer / quality package is identified.</t>
         </is>
       </c>
-      <c r="G23" s="398" t="n"/>
-      <c r="H23" s="398" t="n"/>
-      <c r="I23" s="398" t="n"/>
-      <c r="J23" s="398" t="n"/>
-      <c r="K23" s="398" t="n"/>
-      <c r="L23" s="398" t="n"/>
-      <c r="M23" s="398" t="n"/>
-      <c r="N23" s="398" t="n"/>
-      <c r="O23" s="398" t="n"/>
-      <c r="P23" s="398" t="n"/>
-      <c r="Q23" s="398" t="n"/>
-      <c r="R23" s="398" t="n"/>
-      <c r="S23" s="398" t="n"/>
-      <c r="T23" s="559" t="inlineStr">
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="12" t="n"/>
+      <c r="N23" s="12" t="n"/>
+      <c r="O23" s="12" t="n"/>
+      <c r="P23" s="12" t="n"/>
+      <c r="Q23" s="12" t="n"/>
+      <c r="R23" s="12" t="n"/>
+      <c r="S23" s="13" t="n"/>
+      <c r="T23" s="662" t="inlineStr">
         <is>
           <t>CSR / cert / packaging rules are visible.</t>
         </is>
       </c>
-      <c r="U23" s="398" t="n"/>
-      <c r="V23" s="398" t="n"/>
-      <c r="W23" s="398" t="n"/>
-      <c r="X23" s="398" t="n"/>
-      <c r="Y23" s="398" t="n"/>
-      <c r="Z23" s="398" t="n"/>
-      <c r="AA23" s="398" t="n"/>
-      <c r="AB23" s="398" t="n"/>
-      <c r="AC23" s="398" t="n"/>
-      <c r="AD23" s="398" t="n"/>
-      <c r="AE23" s="398" t="n"/>
-      <c r="AF23" s="560" t="n"/>
-      <c r="AG23" s="398" t="n"/>
-      <c r="AH23" s="398" t="n"/>
-      <c r="AI23" s="398" t="n"/>
-      <c r="AJ23" s="560" t="n"/>
-      <c r="AK23" s="398" t="n"/>
-      <c r="AL23" s="398" t="n"/>
-      <c r="AM23" s="560" t="n"/>
-      <c r="AN23" s="542" t="n"/>
+      <c r="U23" s="12" t="n"/>
+      <c r="V23" s="12" t="n"/>
+      <c r="W23" s="12" t="n"/>
+      <c r="X23" s="12" t="n"/>
+      <c r="Y23" s="12" t="n"/>
+      <c r="Z23" s="12" t="n"/>
+      <c r="AA23" s="12" t="n"/>
+      <c r="AB23" s="12" t="n"/>
+      <c r="AC23" s="12" t="n"/>
+      <c r="AD23" s="12" t="n"/>
+      <c r="AE23" s="13" t="n"/>
+      <c r="AF23" s="663" t="n"/>
+      <c r="AG23" s="12" t="n"/>
+      <c r="AH23" s="12" t="n"/>
+      <c r="AI23" s="13" t="n"/>
+      <c r="AJ23" s="663" t="n"/>
+      <c r="AK23" s="12" t="n"/>
+      <c r="AL23" s="13" t="n"/>
+      <c r="AM23" s="663" t="n"/>
+      <c r="AN23" s="15" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="556" t="n">
+      <c r="A24" s="659" t="n">
         <v>3</v>
       </c>
-      <c r="B24" s="398" t="n"/>
-      <c r="C24" s="557" t="inlineStr">
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="660" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D24" s="398" t="n"/>
-      <c r="E24" s="398" t="n"/>
-      <c r="F24" s="560" t="inlineStr">
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="663" t="inlineStr">
         <is>
           <t>Material / outsource path is feasible.</t>
         </is>
       </c>
-      <c r="G24" s="398" t="n"/>
-      <c r="H24" s="398" t="n"/>
-      <c r="I24" s="398" t="n"/>
-      <c r="J24" s="398" t="n"/>
-      <c r="K24" s="398" t="n"/>
-      <c r="L24" s="398" t="n"/>
-      <c r="M24" s="398" t="n"/>
-      <c r="N24" s="398" t="n"/>
-      <c r="O24" s="398" t="n"/>
-      <c r="P24" s="398" t="n"/>
-      <c r="Q24" s="398" t="n"/>
-      <c r="R24" s="398" t="n"/>
-      <c r="S24" s="398" t="n"/>
-      <c r="T24" s="559" t="inlineStr">
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+      <c r="N24" s="12" t="n"/>
+      <c r="O24" s="12" t="n"/>
+      <c r="P24" s="12" t="n"/>
+      <c r="Q24" s="12" t="n"/>
+      <c r="R24" s="12" t="n"/>
+      <c r="S24" s="13" t="n"/>
+      <c r="T24" s="662" t="inlineStr">
         <is>
           <t>Critical source path is not assumed.</t>
         </is>
       </c>
-      <c r="U24" s="398" t="n"/>
-      <c r="V24" s="398" t="n"/>
-      <c r="W24" s="398" t="n"/>
-      <c r="X24" s="398" t="n"/>
-      <c r="Y24" s="398" t="n"/>
-      <c r="Z24" s="398" t="n"/>
-      <c r="AA24" s="398" t="n"/>
-      <c r="AB24" s="398" t="n"/>
-      <c r="AC24" s="398" t="n"/>
-      <c r="AD24" s="398" t="n"/>
-      <c r="AE24" s="398" t="n"/>
-      <c r="AF24" s="560" t="n"/>
-      <c r="AG24" s="398" t="n"/>
-      <c r="AH24" s="398" t="n"/>
-      <c r="AI24" s="398" t="n"/>
-      <c r="AJ24" s="560" t="n"/>
-      <c r="AK24" s="398" t="n"/>
-      <c r="AL24" s="398" t="n"/>
-      <c r="AM24" s="560" t="n"/>
-      <c r="AN24" s="542" t="n"/>
+      <c r="U24" s="12" t="n"/>
+      <c r="V24" s="12" t="n"/>
+      <c r="W24" s="12" t="n"/>
+      <c r="X24" s="12" t="n"/>
+      <c r="Y24" s="12" t="n"/>
+      <c r="Z24" s="12" t="n"/>
+      <c r="AA24" s="12" t="n"/>
+      <c r="AB24" s="12" t="n"/>
+      <c r="AC24" s="12" t="n"/>
+      <c r="AD24" s="12" t="n"/>
+      <c r="AE24" s="13" t="n"/>
+      <c r="AF24" s="663" t="n"/>
+      <c r="AG24" s="12" t="n"/>
+      <c r="AH24" s="12" t="n"/>
+      <c r="AI24" s="13" t="n"/>
+      <c r="AJ24" s="663" t="n"/>
+      <c r="AK24" s="12" t="n"/>
+      <c r="AL24" s="13" t="n"/>
+      <c r="AM24" s="663" t="n"/>
+      <c r="AN24" s="15" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="556" t="n">
+      <c r="A25" s="659" t="n">
         <v>4</v>
       </c>
-      <c r="B25" s="398" t="n"/>
-      <c r="C25" s="557" t="inlineStr">
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="660" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D25" s="398" t="n"/>
-      <c r="E25" s="398" t="n"/>
-      <c r="F25" s="558" t="inlineStr">
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="661" t="inlineStr">
         <is>
           <t>Machine / tooling / gage readiness exists.</t>
         </is>
       </c>
-      <c r="G25" s="398" t="n"/>
-      <c r="H25" s="398" t="n"/>
-      <c r="I25" s="398" t="n"/>
-      <c r="J25" s="398" t="n"/>
-      <c r="K25" s="398" t="n"/>
-      <c r="L25" s="398" t="n"/>
-      <c r="M25" s="398" t="n"/>
-      <c r="N25" s="398" t="n"/>
-      <c r="O25" s="398" t="n"/>
-      <c r="P25" s="398" t="n"/>
-      <c r="Q25" s="398" t="n"/>
-      <c r="R25" s="398" t="n"/>
-      <c r="S25" s="398" t="n"/>
-      <c r="T25" s="559" t="inlineStr">
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
+      <c r="N25" s="12" t="n"/>
+      <c r="O25" s="12" t="n"/>
+      <c r="P25" s="12" t="n"/>
+      <c r="Q25" s="12" t="n"/>
+      <c r="R25" s="12" t="n"/>
+      <c r="S25" s="13" t="n"/>
+      <c r="T25" s="662" t="inlineStr">
         <is>
           <t>Capability and readiness path are visible.</t>
         </is>
       </c>
-      <c r="U25" s="398" t="n"/>
-      <c r="V25" s="398" t="n"/>
-      <c r="W25" s="398" t="n"/>
-      <c r="X25" s="398" t="n"/>
-      <c r="Y25" s="398" t="n"/>
-      <c r="Z25" s="398" t="n"/>
-      <c r="AA25" s="398" t="n"/>
-      <c r="AB25" s="398" t="n"/>
-      <c r="AC25" s="398" t="n"/>
-      <c r="AD25" s="398" t="n"/>
-      <c r="AE25" s="398" t="n"/>
-      <c r="AF25" s="560" t="n"/>
-      <c r="AG25" s="398" t="n"/>
-      <c r="AH25" s="398" t="n"/>
-      <c r="AI25" s="398" t="n"/>
-      <c r="AJ25" s="560" t="n"/>
-      <c r="AK25" s="398" t="n"/>
-      <c r="AL25" s="398" t="n"/>
-      <c r="AM25" s="560" t="n"/>
-      <c r="AN25" s="542" t="n"/>
+      <c r="U25" s="12" t="n"/>
+      <c r="V25" s="12" t="n"/>
+      <c r="W25" s="12" t="n"/>
+      <c r="X25" s="12" t="n"/>
+      <c r="Y25" s="12" t="n"/>
+      <c r="Z25" s="12" t="n"/>
+      <c r="AA25" s="12" t="n"/>
+      <c r="AB25" s="12" t="n"/>
+      <c r="AC25" s="12" t="n"/>
+      <c r="AD25" s="12" t="n"/>
+      <c r="AE25" s="13" t="n"/>
+      <c r="AF25" s="663" t="n"/>
+      <c r="AG25" s="12" t="n"/>
+      <c r="AH25" s="12" t="n"/>
+      <c r="AI25" s="13" t="n"/>
+      <c r="AJ25" s="663" t="n"/>
+      <c r="AK25" s="12" t="n"/>
+      <c r="AL25" s="13" t="n"/>
+      <c r="AM25" s="663" t="n"/>
+      <c r="AN25" s="15" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="556" t="n">
+      <c r="A26" s="659" t="n">
         <v>5</v>
       </c>
-      <c r="B26" s="398" t="n"/>
-      <c r="C26" s="557" t="inlineStr">
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="660" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D26" s="398" t="n"/>
-      <c r="E26" s="398" t="n"/>
-      <c r="F26" s="560" t="inlineStr">
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="663" t="inlineStr">
         <is>
           <t>First-piece / FAI strategy is defined.</t>
         </is>
       </c>
-      <c r="G26" s="398" t="n"/>
-      <c r="H26" s="398" t="n"/>
-      <c r="I26" s="398" t="n"/>
-      <c r="J26" s="398" t="n"/>
-      <c r="K26" s="398" t="n"/>
-      <c r="L26" s="398" t="n"/>
-      <c r="M26" s="398" t="n"/>
-      <c r="N26" s="398" t="n"/>
-      <c r="O26" s="398" t="n"/>
-      <c r="P26" s="398" t="n"/>
-      <c r="Q26" s="398" t="n"/>
-      <c r="R26" s="398" t="n"/>
-      <c r="S26" s="398" t="n"/>
-      <c r="T26" s="559" t="inlineStr">
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
+      <c r="N26" s="12" t="n"/>
+      <c r="O26" s="12" t="n"/>
+      <c r="P26" s="12" t="n"/>
+      <c r="Q26" s="12" t="n"/>
+      <c r="R26" s="12" t="n"/>
+      <c r="S26" s="13" t="n"/>
+      <c r="T26" s="662" t="inlineStr">
         <is>
           <t>QA gate logic and owner are visible.</t>
         </is>
       </c>
-      <c r="U26" s="398" t="n"/>
-      <c r="V26" s="398" t="n"/>
-      <c r="W26" s="398" t="n"/>
-      <c r="X26" s="398" t="n"/>
-      <c r="Y26" s="398" t="n"/>
-      <c r="Z26" s="398" t="n"/>
-      <c r="AA26" s="398" t="n"/>
-      <c r="AB26" s="398" t="n"/>
-      <c r="AC26" s="398" t="n"/>
-      <c r="AD26" s="398" t="n"/>
-      <c r="AE26" s="398" t="n"/>
-      <c r="AF26" s="560" t="n"/>
-      <c r="AG26" s="398" t="n"/>
-      <c r="AH26" s="398" t="n"/>
-      <c r="AI26" s="398" t="n"/>
-      <c r="AJ26" s="560" t="n"/>
-      <c r="AK26" s="398" t="n"/>
-      <c r="AL26" s="398" t="n"/>
-      <c r="AM26" s="560" t="n"/>
-      <c r="AN26" s="542" t="n"/>
+      <c r="U26" s="12" t="n"/>
+      <c r="V26" s="12" t="n"/>
+      <c r="W26" s="12" t="n"/>
+      <c r="X26" s="12" t="n"/>
+      <c r="Y26" s="12" t="n"/>
+      <c r="Z26" s="12" t="n"/>
+      <c r="AA26" s="12" t="n"/>
+      <c r="AB26" s="12" t="n"/>
+      <c r="AC26" s="12" t="n"/>
+      <c r="AD26" s="12" t="n"/>
+      <c r="AE26" s="13" t="n"/>
+      <c r="AF26" s="663" t="n"/>
+      <c r="AG26" s="12" t="n"/>
+      <c r="AH26" s="12" t="n"/>
+      <c r="AI26" s="13" t="n"/>
+      <c r="AJ26" s="663" t="n"/>
+      <c r="AK26" s="12" t="n"/>
+      <c r="AL26" s="13" t="n"/>
+      <c r="AM26" s="663" t="n"/>
+      <c r="AN26" s="15" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="556" t="n">
+      <c r="A27" s="659" t="n">
         <v>6</v>
       </c>
-      <c r="B27" s="398" t="n"/>
-      <c r="C27" s="557" t="inlineStr">
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="660" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D27" s="398" t="n"/>
-      <c r="E27" s="398" t="n"/>
-      <c r="F27" s="558" t="inlineStr">
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="661" t="inlineStr">
         <is>
           <t>Delivery / ship logic is feasible.</t>
         </is>
       </c>
-      <c r="G27" s="398" t="n"/>
-      <c r="H27" s="398" t="n"/>
-      <c r="I27" s="398" t="n"/>
-      <c r="J27" s="398" t="n"/>
-      <c r="K27" s="398" t="n"/>
-      <c r="L27" s="398" t="n"/>
-      <c r="M27" s="398" t="n"/>
-      <c r="N27" s="398" t="n"/>
-      <c r="O27" s="398" t="n"/>
-      <c r="P27" s="398" t="n"/>
-      <c r="Q27" s="398" t="n"/>
-      <c r="R27" s="398" t="n"/>
-      <c r="S27" s="398" t="n"/>
-      <c r="T27" s="559" t="inlineStr">
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+      <c r="N27" s="12" t="n"/>
+      <c r="O27" s="12" t="n"/>
+      <c r="P27" s="12" t="n"/>
+      <c r="Q27" s="12" t="n"/>
+      <c r="R27" s="12" t="n"/>
+      <c r="S27" s="13" t="n"/>
+      <c r="T27" s="662" t="inlineStr">
         <is>
           <t>Commitment and ship impact are realistic.</t>
         </is>
       </c>
-      <c r="U27" s="398" t="n"/>
-      <c r="V27" s="398" t="n"/>
-      <c r="W27" s="398" t="n"/>
-      <c r="X27" s="398" t="n"/>
-      <c r="Y27" s="398" t="n"/>
-      <c r="Z27" s="398" t="n"/>
-      <c r="AA27" s="398" t="n"/>
-      <c r="AB27" s="398" t="n"/>
-      <c r="AC27" s="398" t="n"/>
-      <c r="AD27" s="398" t="n"/>
-      <c r="AE27" s="398" t="n"/>
-      <c r="AF27" s="560" t="n"/>
-      <c r="AG27" s="398" t="n"/>
-      <c r="AH27" s="398" t="n"/>
-      <c r="AI27" s="398" t="n"/>
-      <c r="AJ27" s="560" t="n"/>
-      <c r="AK27" s="398" t="n"/>
-      <c r="AL27" s="398" t="n"/>
-      <c r="AM27" s="560" t="n"/>
-      <c r="AN27" s="542" t="n"/>
+      <c r="U27" s="12" t="n"/>
+      <c r="V27" s="12" t="n"/>
+      <c r="W27" s="12" t="n"/>
+      <c r="X27" s="12" t="n"/>
+      <c r="Y27" s="12" t="n"/>
+      <c r="Z27" s="12" t="n"/>
+      <c r="AA27" s="12" t="n"/>
+      <c r="AB27" s="12" t="n"/>
+      <c r="AC27" s="12" t="n"/>
+      <c r="AD27" s="12" t="n"/>
+      <c r="AE27" s="13" t="n"/>
+      <c r="AF27" s="663" t="n"/>
+      <c r="AG27" s="12" t="n"/>
+      <c r="AH27" s="12" t="n"/>
+      <c r="AI27" s="13" t="n"/>
+      <c r="AJ27" s="663" t="n"/>
+      <c r="AK27" s="12" t="n"/>
+      <c r="AL27" s="13" t="n"/>
+      <c r="AM27" s="663" t="n"/>
+      <c r="AN27" s="15" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="556" t="n">
+      <c r="A28" s="659" t="n">
         <v>7</v>
       </c>
-      <c r="B28" s="398" t="n"/>
-      <c r="C28" s="557" t="inlineStr">
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="660" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D28" s="398" t="n"/>
-      <c r="E28" s="398" t="n"/>
-      <c r="F28" s="560" t="inlineStr">
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="663" t="inlineStr">
         <is>
           <t>Top abnormal / failure mode is explicit.</t>
         </is>
       </c>
-      <c r="G28" s="398" t="n"/>
-      <c r="H28" s="398" t="n"/>
-      <c r="I28" s="398" t="n"/>
-      <c r="J28" s="398" t="n"/>
-      <c r="K28" s="398" t="n"/>
-      <c r="L28" s="398" t="n"/>
-      <c r="M28" s="398" t="n"/>
-      <c r="N28" s="398" t="n"/>
-      <c r="O28" s="398" t="n"/>
-      <c r="P28" s="398" t="n"/>
-      <c r="Q28" s="398" t="n"/>
-      <c r="R28" s="398" t="n"/>
-      <c r="S28" s="398" t="n"/>
-      <c r="T28" s="559" t="inlineStr">
+      <c r="G28" s="12" t="n"/>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="12" t="n"/>
+      <c r="N28" s="12" t="n"/>
+      <c r="O28" s="12" t="n"/>
+      <c r="P28" s="12" t="n"/>
+      <c r="Q28" s="12" t="n"/>
+      <c r="R28" s="12" t="n"/>
+      <c r="S28" s="13" t="n"/>
+      <c r="T28" s="662" t="inlineStr">
         <is>
           <t>Most severe risk is named, not hidden.</t>
         </is>
       </c>
-      <c r="U28" s="398" t="n"/>
-      <c r="V28" s="398" t="n"/>
-      <c r="W28" s="398" t="n"/>
-      <c r="X28" s="398" t="n"/>
-      <c r="Y28" s="398" t="n"/>
-      <c r="Z28" s="398" t="n"/>
-      <c r="AA28" s="398" t="n"/>
-      <c r="AB28" s="398" t="n"/>
-      <c r="AC28" s="398" t="n"/>
-      <c r="AD28" s="398" t="n"/>
-      <c r="AE28" s="398" t="n"/>
-      <c r="AF28" s="560" t="n"/>
-      <c r="AG28" s="398" t="n"/>
-      <c r="AH28" s="398" t="n"/>
-      <c r="AI28" s="398" t="n"/>
-      <c r="AJ28" s="560" t="n"/>
-      <c r="AK28" s="398" t="n"/>
-      <c r="AL28" s="398" t="n"/>
-      <c r="AM28" s="560" t="n"/>
-      <c r="AN28" s="542" t="n"/>
+      <c r="U28" s="12" t="n"/>
+      <c r="V28" s="12" t="n"/>
+      <c r="W28" s="12" t="n"/>
+      <c r="X28" s="12" t="n"/>
+      <c r="Y28" s="12" t="n"/>
+      <c r="Z28" s="12" t="n"/>
+      <c r="AA28" s="12" t="n"/>
+      <c r="AB28" s="12" t="n"/>
+      <c r="AC28" s="12" t="n"/>
+      <c r="AD28" s="12" t="n"/>
+      <c r="AE28" s="13" t="n"/>
+      <c r="AF28" s="663" t="n"/>
+      <c r="AG28" s="12" t="n"/>
+      <c r="AH28" s="12" t="n"/>
+      <c r="AI28" s="13" t="n"/>
+      <c r="AJ28" s="663" t="n"/>
+      <c r="AK28" s="12" t="n"/>
+      <c r="AL28" s="13" t="n"/>
+      <c r="AM28" s="663" t="n"/>
+      <c r="AN28" s="15" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="556" t="n">
+      <c r="A29" s="659" t="n">
         <v>8</v>
       </c>
-      <c r="B29" s="398" t="n"/>
-      <c r="C29" s="557" t="inlineStr">
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="660" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D29" s="398" t="n"/>
-      <c r="E29" s="398" t="n"/>
-      <c r="F29" s="558" t="inlineStr">
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="661" t="inlineStr">
         <is>
           <t>Containment / contingency exists.</t>
         </is>
       </c>
-      <c r="G29" s="398" t="n"/>
-      <c r="H29" s="398" t="n"/>
-      <c r="I29" s="398" t="n"/>
-      <c r="J29" s="398" t="n"/>
-      <c r="K29" s="398" t="n"/>
-      <c r="L29" s="398" t="n"/>
-      <c r="M29" s="398" t="n"/>
-      <c r="N29" s="398" t="n"/>
-      <c r="O29" s="398" t="n"/>
-      <c r="P29" s="398" t="n"/>
-      <c r="Q29" s="398" t="n"/>
-      <c r="R29" s="398" t="n"/>
-      <c r="S29" s="398" t="n"/>
-      <c r="T29" s="559" t="inlineStr">
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="12" t="n"/>
+      <c r="N29" s="12" t="n"/>
+      <c r="O29" s="12" t="n"/>
+      <c r="P29" s="12" t="n"/>
+      <c r="Q29" s="12" t="n"/>
+      <c r="R29" s="12" t="n"/>
+      <c r="S29" s="13" t="n"/>
+      <c r="T29" s="662" t="inlineStr">
         <is>
           <t>Recovery path exists if primary plan fails.</t>
         </is>
       </c>
-      <c r="U29" s="398" t="n"/>
-      <c r="V29" s="398" t="n"/>
-      <c r="W29" s="398" t="n"/>
-      <c r="X29" s="398" t="n"/>
-      <c r="Y29" s="398" t="n"/>
-      <c r="Z29" s="398" t="n"/>
-      <c r="AA29" s="398" t="n"/>
-      <c r="AB29" s="398" t="n"/>
-      <c r="AC29" s="398" t="n"/>
-      <c r="AD29" s="398" t="n"/>
-      <c r="AE29" s="398" t="n"/>
-      <c r="AF29" s="560" t="n"/>
-      <c r="AG29" s="398" t="n"/>
-      <c r="AH29" s="398" t="n"/>
-      <c r="AI29" s="398" t="n"/>
-      <c r="AJ29" s="560" t="n"/>
-      <c r="AK29" s="398" t="n"/>
-      <c r="AL29" s="398" t="n"/>
-      <c r="AM29" s="560" t="n"/>
-      <c r="AN29" s="542" t="n"/>
+      <c r="U29" s="12" t="n"/>
+      <c r="V29" s="12" t="n"/>
+      <c r="W29" s="12" t="n"/>
+      <c r="X29" s="12" t="n"/>
+      <c r="Y29" s="12" t="n"/>
+      <c r="Z29" s="12" t="n"/>
+      <c r="AA29" s="12" t="n"/>
+      <c r="AB29" s="12" t="n"/>
+      <c r="AC29" s="12" t="n"/>
+      <c r="AD29" s="12" t="n"/>
+      <c r="AE29" s="13" t="n"/>
+      <c r="AF29" s="663" t="n"/>
+      <c r="AG29" s="12" t="n"/>
+      <c r="AH29" s="12" t="n"/>
+      <c r="AI29" s="13" t="n"/>
+      <c r="AJ29" s="663" t="n"/>
+      <c r="AK29" s="12" t="n"/>
+      <c r="AL29" s="13" t="n"/>
+      <c r="AM29" s="663" t="n"/>
+      <c r="AN29" s="15" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="556" t="n">
+      <c r="A30" s="659" t="n">
         <v>9</v>
       </c>
-      <c r="B30" s="398" t="n"/>
-      <c r="C30" s="557" t="inlineStr">
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="660" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D30" s="398" t="n"/>
-      <c r="E30" s="398" t="n"/>
-      <c r="F30" s="560" t="inlineStr">
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="663" t="inlineStr">
         <is>
           <t>Conditional-release authority is explicit.</t>
         </is>
       </c>
-      <c r="G30" s="398" t="n"/>
-      <c r="H30" s="398" t="n"/>
-      <c r="I30" s="398" t="n"/>
-      <c r="J30" s="398" t="n"/>
-      <c r="K30" s="398" t="n"/>
-      <c r="L30" s="398" t="n"/>
-      <c r="M30" s="398" t="n"/>
-      <c r="N30" s="398" t="n"/>
-      <c r="O30" s="398" t="n"/>
-      <c r="P30" s="398" t="n"/>
-      <c r="Q30" s="398" t="n"/>
-      <c r="R30" s="398" t="n"/>
-      <c r="S30" s="398" t="n"/>
-      <c r="T30" s="559" t="inlineStr">
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12" t="n"/>
+      <c r="N30" s="12" t="n"/>
+      <c r="O30" s="12" t="n"/>
+      <c r="P30" s="12" t="n"/>
+      <c r="Q30" s="12" t="n"/>
+      <c r="R30" s="12" t="n"/>
+      <c r="S30" s="13" t="n"/>
+      <c r="T30" s="662" t="inlineStr">
         <is>
           <t>No conditional release without named owner.</t>
         </is>
       </c>
-      <c r="U30" s="398" t="n"/>
-      <c r="V30" s="398" t="n"/>
-      <c r="W30" s="398" t="n"/>
-      <c r="X30" s="398" t="n"/>
-      <c r="Y30" s="398" t="n"/>
-      <c r="Z30" s="398" t="n"/>
-      <c r="AA30" s="398" t="n"/>
-      <c r="AB30" s="398" t="n"/>
-      <c r="AC30" s="398" t="n"/>
-      <c r="AD30" s="398" t="n"/>
-      <c r="AE30" s="398" t="n"/>
-      <c r="AF30" s="560" t="n"/>
-      <c r="AG30" s="398" t="n"/>
-      <c r="AH30" s="398" t="n"/>
-      <c r="AI30" s="398" t="n"/>
-      <c r="AJ30" s="560" t="n"/>
-      <c r="AK30" s="398" t="n"/>
-      <c r="AL30" s="398" t="n"/>
-      <c r="AM30" s="560" t="n"/>
-      <c r="AN30" s="542" t="n"/>
+      <c r="U30" s="12" t="n"/>
+      <c r="V30" s="12" t="n"/>
+      <c r="W30" s="12" t="n"/>
+      <c r="X30" s="12" t="n"/>
+      <c r="Y30" s="12" t="n"/>
+      <c r="Z30" s="12" t="n"/>
+      <c r="AA30" s="12" t="n"/>
+      <c r="AB30" s="12" t="n"/>
+      <c r="AC30" s="12" t="n"/>
+      <c r="AD30" s="12" t="n"/>
+      <c r="AE30" s="13" t="n"/>
+      <c r="AF30" s="663" t="n"/>
+      <c r="AG30" s="12" t="n"/>
+      <c r="AH30" s="12" t="n"/>
+      <c r="AI30" s="13" t="n"/>
+      <c r="AJ30" s="663" t="n"/>
+      <c r="AK30" s="12" t="n"/>
+      <c r="AL30" s="13" t="n"/>
+      <c r="AM30" s="663" t="n"/>
+      <c r="AN30" s="15" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="561" t="n">
+      <c r="A31" s="664" t="n">
         <v>10</v>
       </c>
-      <c r="B31" s="544" t="n"/>
-      <c r="C31" s="562" t="inlineStr">
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="665" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D31" s="544" t="n"/>
-      <c r="E31" s="544" t="n"/>
-      <c r="F31" s="563" t="inlineStr">
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="666" t="inlineStr">
         <is>
           <t>Evidence path and dossier traceability exist.</t>
         </is>
       </c>
-      <c r="G31" s="544" t="n"/>
-      <c r="H31" s="544" t="n"/>
-      <c r="I31" s="544" t="n"/>
-      <c r="J31" s="544" t="n"/>
-      <c r="K31" s="544" t="n"/>
-      <c r="L31" s="544" t="n"/>
-      <c r="M31" s="544" t="n"/>
-      <c r="N31" s="544" t="n"/>
-      <c r="O31" s="544" t="n"/>
-      <c r="P31" s="544" t="n"/>
-      <c r="Q31" s="544" t="n"/>
-      <c r="R31" s="544" t="n"/>
-      <c r="S31" s="544" t="n"/>
-      <c r="T31" s="564" t="inlineStr">
+      <c r="G31" s="19" t="n"/>
+      <c r="H31" s="19" t="n"/>
+      <c r="I31" s="19" t="n"/>
+      <c r="J31" s="19" t="n"/>
+      <c r="K31" s="19" t="n"/>
+      <c r="L31" s="19" t="n"/>
+      <c r="M31" s="19" t="n"/>
+      <c r="N31" s="19" t="n"/>
+      <c r="O31" s="19" t="n"/>
+      <c r="P31" s="19" t="n"/>
+      <c r="Q31" s="19" t="n"/>
+      <c r="R31" s="19" t="n"/>
+      <c r="S31" s="22" t="n"/>
+      <c r="T31" s="667" t="inlineStr">
         <is>
           <t>Decision can be reconstructed later.</t>
         </is>
       </c>
-      <c r="U31" s="544" t="n"/>
-      <c r="V31" s="544" t="n"/>
-      <c r="W31" s="544" t="n"/>
-      <c r="X31" s="544" t="n"/>
-      <c r="Y31" s="544" t="n"/>
-      <c r="Z31" s="544" t="n"/>
-      <c r="AA31" s="544" t="n"/>
-      <c r="AB31" s="544" t="n"/>
-      <c r="AC31" s="544" t="n"/>
-      <c r="AD31" s="544" t="n"/>
-      <c r="AE31" s="544" t="n"/>
-      <c r="AF31" s="565" t="n"/>
-      <c r="AG31" s="544" t="n"/>
-      <c r="AH31" s="544" t="n"/>
-      <c r="AI31" s="544" t="n"/>
-      <c r="AJ31" s="565" t="n"/>
-      <c r="AK31" s="544" t="n"/>
-      <c r="AL31" s="544" t="n"/>
-      <c r="AM31" s="565" t="n"/>
-      <c r="AN31" s="547" t="n"/>
+      <c r="U31" s="19" t="n"/>
+      <c r="V31" s="19" t="n"/>
+      <c r="W31" s="19" t="n"/>
+      <c r="X31" s="19" t="n"/>
+      <c r="Y31" s="19" t="n"/>
+      <c r="Z31" s="19" t="n"/>
+      <c r="AA31" s="19" t="n"/>
+      <c r="AB31" s="19" t="n"/>
+      <c r="AC31" s="19" t="n"/>
+      <c r="AD31" s="19" t="n"/>
+      <c r="AE31" s="22" t="n"/>
+      <c r="AF31" s="668" t="n"/>
+      <c r="AG31" s="19" t="n"/>
+      <c r="AH31" s="19" t="n"/>
+      <c r="AI31" s="22" t="n"/>
+      <c r="AJ31" s="668" t="n"/>
+      <c r="AK31" s="19" t="n"/>
+      <c r="AL31" s="22" t="n"/>
+      <c r="AM31" s="668" t="n"/>
+      <c r="AN31" s="24" t="n"/>
     </row>
     <row r="32" ht="3" customHeight="1">
-      <c r="A32" s="410" t="n"/>
-      <c r="B32" s="482" t="n"/>
-      <c r="C32" s="482" t="n"/>
-      <c r="D32" s="482" t="n"/>
-      <c r="E32" s="482" t="n"/>
-      <c r="F32" s="482" t="n"/>
-      <c r="G32" s="482" t="n"/>
-      <c r="H32" s="482" t="n"/>
-      <c r="I32" s="482" t="n"/>
-      <c r="J32" s="482" t="n"/>
-      <c r="K32" s="482" t="n"/>
-      <c r="L32" s="482" t="n"/>
-      <c r="M32" s="482" t="n"/>
-      <c r="N32" s="482" t="n"/>
-      <c r="O32" s="482" t="n"/>
-      <c r="P32" s="482" t="n"/>
-      <c r="Q32" s="482" t="n"/>
-      <c r="R32" s="482" t="n"/>
-      <c r="S32" s="482" t="n"/>
-      <c r="T32" s="482" t="n"/>
-      <c r="U32" s="482" t="n"/>
-      <c r="V32" s="482" t="n"/>
-      <c r="W32" s="482" t="n"/>
-      <c r="X32" s="482" t="n"/>
-      <c r="Y32" s="482" t="n"/>
-      <c r="Z32" s="482" t="n"/>
-      <c r="AA32" s="482" t="n"/>
-      <c r="AB32" s="482" t="n"/>
-      <c r="AC32" s="482" t="n"/>
-      <c r="AD32" s="482" t="n"/>
-      <c r="AE32" s="482" t="n"/>
-      <c r="AF32" s="482" t="n"/>
-      <c r="AG32" s="482" t="n"/>
-      <c r="AH32" s="482" t="n"/>
-      <c r="AI32" s="482" t="n"/>
-      <c r="AJ32" s="482" t="n"/>
-      <c r="AK32" s="482" t="n"/>
-      <c r="AL32" s="482" t="n"/>
-      <c r="AM32" s="482" t="n"/>
-      <c r="AN32" s="482" t="n"/>
+      <c r="A32" s="654" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="10" t="n"/>
+      <c r="L32" s="10" t="n"/>
+      <c r="M32" s="10" t="n"/>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="10" t="n"/>
+      <c r="Q32" s="10" t="n"/>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="10" t="n"/>
+      <c r="T32" s="10" t="n"/>
+      <c r="U32" s="10" t="n"/>
+      <c r="V32" s="10" t="n"/>
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="10" t="n"/>
+      <c r="Y32" s="10" t="n"/>
+      <c r="Z32" s="10" t="n"/>
+      <c r="AA32" s="10" t="n"/>
+      <c r="AB32" s="10" t="n"/>
+      <c r="AC32" s="10" t="n"/>
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="10" t="n"/>
+      <c r="AF32" s="10" t="n"/>
+      <c r="AG32" s="10" t="n"/>
+      <c r="AH32" s="10" t="n"/>
+      <c r="AI32" s="10" t="n"/>
+      <c r="AJ32" s="10" t="n"/>
+      <c r="AK32" s="10" t="n"/>
+      <c r="AL32" s="10" t="n"/>
+      <c r="AM32" s="10" t="n"/>
+      <c r="AN32" s="10" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="531" t="inlineStr">
+      <c r="A33" s="647" t="inlineStr">
         <is>
           <t>4.  OPEN RISK ACTIONS / CONTAINMENT</t>
         </is>
       </c>
-      <c r="B33" s="532" t="n"/>
-      <c r="C33" s="532" t="n"/>
-      <c r="D33" s="532" t="n"/>
-      <c r="E33" s="532" t="n"/>
-      <c r="F33" s="532" t="n"/>
-      <c r="G33" s="532" t="n"/>
-      <c r="H33" s="532" t="n"/>
-      <c r="I33" s="532" t="n"/>
-      <c r="J33" s="532" t="n"/>
-      <c r="K33" s="532" t="n"/>
-      <c r="L33" s="532" t="n"/>
-      <c r="M33" s="532" t="n"/>
-      <c r="N33" s="532" t="n"/>
-      <c r="O33" s="532" t="n"/>
-      <c r="P33" s="532" t="n"/>
-      <c r="Q33" s="532" t="n"/>
-      <c r="R33" s="532" t="n"/>
-      <c r="S33" s="532" t="n"/>
-      <c r="T33" s="532" t="n"/>
-      <c r="U33" s="532" t="n"/>
-      <c r="V33" s="532" t="n"/>
-      <c r="W33" s="532" t="n"/>
-      <c r="X33" s="532" t="n"/>
-      <c r="Y33" s="532" t="n"/>
-      <c r="Z33" s="532" t="n"/>
-      <c r="AA33" s="532" t="n"/>
-      <c r="AB33" s="532" t="n"/>
-      <c r="AC33" s="532" t="n"/>
-      <c r="AD33" s="532" t="n"/>
-      <c r="AE33" s="532" t="n"/>
-      <c r="AF33" s="532" t="n"/>
-      <c r="AG33" s="532" t="n"/>
-      <c r="AH33" s="532" t="n"/>
-      <c r="AI33" s="532" t="n"/>
-      <c r="AJ33" s="532" t="n"/>
-      <c r="AK33" s="532" t="n"/>
-      <c r="AL33" s="532" t="n"/>
-      <c r="AM33" s="532" t="n"/>
-      <c r="AN33" s="533" t="n"/>
+      <c r="B33" s="27" t="n"/>
+      <c r="C33" s="27" t="n"/>
+      <c r="D33" s="27" t="n"/>
+      <c r="E33" s="27" t="n"/>
+      <c r="F33" s="27" t="n"/>
+      <c r="G33" s="27" t="n"/>
+      <c r="H33" s="27" t="n"/>
+      <c r="I33" s="27" t="n"/>
+      <c r="J33" s="27" t="n"/>
+      <c r="K33" s="27" t="n"/>
+      <c r="L33" s="27" t="n"/>
+      <c r="M33" s="27" t="n"/>
+      <c r="N33" s="27" t="n"/>
+      <c r="O33" s="27" t="n"/>
+      <c r="P33" s="27" t="n"/>
+      <c r="Q33" s="27" t="n"/>
+      <c r="R33" s="27" t="n"/>
+      <c r="S33" s="27" t="n"/>
+      <c r="T33" s="27" t="n"/>
+      <c r="U33" s="27" t="n"/>
+      <c r="V33" s="27" t="n"/>
+      <c r="W33" s="27" t="n"/>
+      <c r="X33" s="27" t="n"/>
+      <c r="Y33" s="27" t="n"/>
+      <c r="Z33" s="27" t="n"/>
+      <c r="AA33" s="27" t="n"/>
+      <c r="AB33" s="27" t="n"/>
+      <c r="AC33" s="27" t="n"/>
+      <c r="AD33" s="27" t="n"/>
+      <c r="AE33" s="27" t="n"/>
+      <c r="AF33" s="27" t="n"/>
+      <c r="AG33" s="27" t="n"/>
+      <c r="AH33" s="27" t="n"/>
+      <c r="AI33" s="27" t="n"/>
+      <c r="AJ33" s="27" t="n"/>
+      <c r="AK33" s="27" t="n"/>
+      <c r="AL33" s="27" t="n"/>
+      <c r="AM33" s="27" t="n"/>
+      <c r="AN33" s="28" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="548" t="inlineStr">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B34" s="549" t="n"/>
-      <c r="C34" s="550" t="inlineStr">
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="37" t="inlineStr">
         <is>
           <t>Risk / Readiness Gap</t>
         </is>
       </c>
-      <c r="D34" s="549" t="n"/>
-      <c r="E34" s="549" t="n"/>
-      <c r="F34" s="549" t="n"/>
-      <c r="G34" s="549" t="n"/>
-      <c r="H34" s="549" t="n"/>
-      <c r="I34" s="549" t="n"/>
-      <c r="J34" s="549" t="n"/>
-      <c r="K34" s="549" t="n"/>
-      <c r="L34" s="549" t="n"/>
-      <c r="M34" s="550" t="inlineStr">
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="6" t="n"/>
+      <c r="M34" s="37" t="inlineStr">
         <is>
           <t>Required Containment / Action</t>
         </is>
       </c>
-      <c r="N34" s="549" t="n"/>
-      <c r="O34" s="549" t="n"/>
-      <c r="P34" s="549" t="n"/>
-      <c r="Q34" s="549" t="n"/>
-      <c r="R34" s="549" t="n"/>
-      <c r="S34" s="549" t="n"/>
-      <c r="T34" s="549" t="n"/>
-      <c r="U34" s="549" t="n"/>
-      <c r="V34" s="549" t="n"/>
-      <c r="W34" s="549" t="n"/>
-      <c r="X34" s="549" t="n"/>
-      <c r="Y34" s="550" t="inlineStr">
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
+      <c r="Q34" s="5" t="n"/>
+      <c r="R34" s="5" t="n"/>
+      <c r="S34" s="5" t="n"/>
+      <c r="T34" s="5" t="n"/>
+      <c r="U34" s="5" t="n"/>
+      <c r="V34" s="5" t="n"/>
+      <c r="W34" s="5" t="n"/>
+      <c r="X34" s="6" t="n"/>
+      <c r="Y34" s="37" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="Z34" s="549" t="n"/>
-      <c r="AA34" s="549" t="n"/>
-      <c r="AB34" s="549" t="n"/>
-      <c r="AC34" s="549" t="n"/>
-      <c r="AD34" s="550" t="inlineStr">
+      <c r="Z34" s="5" t="n"/>
+      <c r="AA34" s="5" t="n"/>
+      <c r="AB34" s="5" t="n"/>
+      <c r="AC34" s="6" t="n"/>
+      <c r="AD34" s="37" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="AE34" s="549" t="n"/>
-      <c r="AF34" s="549" t="n"/>
-      <c r="AG34" s="549" t="n"/>
-      <c r="AH34" s="549" t="n"/>
-      <c r="AI34" s="550" t="inlineStr">
+      <c r="AE34" s="5" t="n"/>
+      <c r="AF34" s="5" t="n"/>
+      <c r="AG34" s="5" t="n"/>
+      <c r="AH34" s="6" t="n"/>
+      <c r="AI34" s="37" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AJ34" s="549" t="n"/>
-      <c r="AK34" s="549" t="n"/>
-      <c r="AL34" s="550" t="inlineStr">
+      <c r="AJ34" s="5" t="n"/>
+      <c r="AK34" s="6" t="n"/>
+      <c r="AL34" s="37" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="AM34" s="549" t="n"/>
-      <c r="AN34" s="551" t="n"/>
+      <c r="AM34" s="5" t="n"/>
+      <c r="AN34" s="8" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="566" t="n">
+      <c r="A35" s="669" t="n">
         <v>1</v>
       </c>
-      <c r="B35" s="535" t="n"/>
-      <c r="C35" s="554" t="n"/>
-      <c r="D35" s="535" t="n"/>
-      <c r="E35" s="535" t="n"/>
-      <c r="F35" s="535" t="n"/>
-      <c r="G35" s="535" t="n"/>
-      <c r="H35" s="535" t="n"/>
-      <c r="I35" s="535" t="n"/>
-      <c r="J35" s="535" t="n"/>
-      <c r="K35" s="535" t="n"/>
-      <c r="L35" s="535" t="n"/>
-      <c r="M35" s="554" t="n"/>
-      <c r="N35" s="535" t="n"/>
-      <c r="O35" s="535" t="n"/>
-      <c r="P35" s="535" t="n"/>
-      <c r="Q35" s="535" t="n"/>
-      <c r="R35" s="535" t="n"/>
-      <c r="S35" s="535" t="n"/>
-      <c r="T35" s="535" t="n"/>
-      <c r="U35" s="535" t="n"/>
-      <c r="V35" s="535" t="n"/>
-      <c r="W35" s="535" t="n"/>
-      <c r="X35" s="535" t="n"/>
-      <c r="Y35" s="554" t="n"/>
-      <c r="Z35" s="535" t="n"/>
-      <c r="AA35" s="535" t="n"/>
-      <c r="AB35" s="535" t="n"/>
-      <c r="AC35" s="535" t="n"/>
-      <c r="AD35" s="554" t="n"/>
-      <c r="AE35" s="535" t="n"/>
-      <c r="AF35" s="535" t="n"/>
-      <c r="AG35" s="535" t="n"/>
-      <c r="AH35" s="535" t="n"/>
-      <c r="AI35" s="554" t="n"/>
-      <c r="AJ35" s="535" t="n"/>
-      <c r="AK35" s="535" t="n"/>
-      <c r="AL35" s="554" t="n"/>
-      <c r="AM35" s="535" t="n"/>
-      <c r="AN35" s="538" t="n"/>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="657" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="6" t="n"/>
+      <c r="M35" s="657" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="5" t="n"/>
+      <c r="Q35" s="5" t="n"/>
+      <c r="R35" s="5" t="n"/>
+      <c r="S35" s="5" t="n"/>
+      <c r="T35" s="5" t="n"/>
+      <c r="U35" s="5" t="n"/>
+      <c r="V35" s="5" t="n"/>
+      <c r="W35" s="5" t="n"/>
+      <c r="X35" s="6" t="n"/>
+      <c r="Y35" s="657" t="n"/>
+      <c r="Z35" s="5" t="n"/>
+      <c r="AA35" s="5" t="n"/>
+      <c r="AB35" s="5" t="n"/>
+      <c r="AC35" s="6" t="n"/>
+      <c r="AD35" s="657" t="n"/>
+      <c r="AE35" s="5" t="n"/>
+      <c r="AF35" s="5" t="n"/>
+      <c r="AG35" s="5" t="n"/>
+      <c r="AH35" s="6" t="n"/>
+      <c r="AI35" s="657" t="n"/>
+      <c r="AJ35" s="5" t="n"/>
+      <c r="AK35" s="6" t="n"/>
+      <c r="AL35" s="657" t="n"/>
+      <c r="AM35" s="5" t="n"/>
+      <c r="AN35" s="8" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="567" t="n">
+      <c r="A36" s="670" t="n">
         <v>2</v>
       </c>
-      <c r="B36" s="398" t="n"/>
-      <c r="C36" s="560" t="n"/>
-      <c r="D36" s="398" t="n"/>
-      <c r="E36" s="398" t="n"/>
-      <c r="F36" s="398" t="n"/>
-      <c r="G36" s="398" t="n"/>
-      <c r="H36" s="398" t="n"/>
-      <c r="I36" s="398" t="n"/>
-      <c r="J36" s="398" t="n"/>
-      <c r="K36" s="398" t="n"/>
-      <c r="L36" s="398" t="n"/>
-      <c r="M36" s="560" t="n"/>
-      <c r="N36" s="398" t="n"/>
-      <c r="O36" s="398" t="n"/>
-      <c r="P36" s="398" t="n"/>
-      <c r="Q36" s="398" t="n"/>
-      <c r="R36" s="398" t="n"/>
-      <c r="S36" s="398" t="n"/>
-      <c r="T36" s="398" t="n"/>
-      <c r="U36" s="398" t="n"/>
-      <c r="V36" s="398" t="n"/>
-      <c r="W36" s="398" t="n"/>
-      <c r="X36" s="398" t="n"/>
-      <c r="Y36" s="560" t="n"/>
-      <c r="Z36" s="398" t="n"/>
-      <c r="AA36" s="398" t="n"/>
-      <c r="AB36" s="398" t="n"/>
-      <c r="AC36" s="398" t="n"/>
-      <c r="AD36" s="560" t="n"/>
-      <c r="AE36" s="398" t="n"/>
-      <c r="AF36" s="398" t="n"/>
-      <c r="AG36" s="398" t="n"/>
-      <c r="AH36" s="398" t="n"/>
-      <c r="AI36" s="560" t="n"/>
-      <c r="AJ36" s="398" t="n"/>
-      <c r="AK36" s="398" t="n"/>
-      <c r="AL36" s="560" t="n"/>
-      <c r="AM36" s="398" t="n"/>
-      <c r="AN36" s="542" t="n"/>
+      <c r="B36" s="13" t="n"/>
+      <c r="C36" s="663" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="12" t="n"/>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="13" t="n"/>
+      <c r="M36" s="663" t="n"/>
+      <c r="N36" s="12" t="n"/>
+      <c r="O36" s="12" t="n"/>
+      <c r="P36" s="12" t="n"/>
+      <c r="Q36" s="12" t="n"/>
+      <c r="R36" s="12" t="n"/>
+      <c r="S36" s="12" t="n"/>
+      <c r="T36" s="12" t="n"/>
+      <c r="U36" s="12" t="n"/>
+      <c r="V36" s="12" t="n"/>
+      <c r="W36" s="12" t="n"/>
+      <c r="X36" s="13" t="n"/>
+      <c r="Y36" s="663" t="n"/>
+      <c r="Z36" s="12" t="n"/>
+      <c r="AA36" s="12" t="n"/>
+      <c r="AB36" s="12" t="n"/>
+      <c r="AC36" s="13" t="n"/>
+      <c r="AD36" s="663" t="n"/>
+      <c r="AE36" s="12" t="n"/>
+      <c r="AF36" s="12" t="n"/>
+      <c r="AG36" s="12" t="n"/>
+      <c r="AH36" s="13" t="n"/>
+      <c r="AI36" s="663" t="n"/>
+      <c r="AJ36" s="12" t="n"/>
+      <c r="AK36" s="13" t="n"/>
+      <c r="AL36" s="663" t="n"/>
+      <c r="AM36" s="12" t="n"/>
+      <c r="AN36" s="15" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="567" t="n">
+      <c r="A37" s="670" t="n">
         <v>3</v>
       </c>
-      <c r="B37" s="398" t="n"/>
-      <c r="C37" s="560" t="n"/>
-      <c r="D37" s="398" t="n"/>
-      <c r="E37" s="398" t="n"/>
-      <c r="F37" s="398" t="n"/>
-      <c r="G37" s="398" t="n"/>
-      <c r="H37" s="398" t="n"/>
-      <c r="I37" s="398" t="n"/>
-      <c r="J37" s="398" t="n"/>
-      <c r="K37" s="398" t="n"/>
-      <c r="L37" s="398" t="n"/>
-      <c r="M37" s="560" t="n"/>
-      <c r="N37" s="398" t="n"/>
-      <c r="O37" s="398" t="n"/>
-      <c r="P37" s="398" t="n"/>
-      <c r="Q37" s="398" t="n"/>
-      <c r="R37" s="398" t="n"/>
-      <c r="S37" s="398" t="n"/>
-      <c r="T37" s="398" t="n"/>
-      <c r="U37" s="398" t="n"/>
-      <c r="V37" s="398" t="n"/>
-      <c r="W37" s="398" t="n"/>
-      <c r="X37" s="398" t="n"/>
-      <c r="Y37" s="560" t="n"/>
-      <c r="Z37" s="398" t="n"/>
-      <c r="AA37" s="398" t="n"/>
-      <c r="AB37" s="398" t="n"/>
-      <c r="AC37" s="398" t="n"/>
-      <c r="AD37" s="560" t="n"/>
-      <c r="AE37" s="398" t="n"/>
-      <c r="AF37" s="398" t="n"/>
-      <c r="AG37" s="398" t="n"/>
-      <c r="AH37" s="398" t="n"/>
-      <c r="AI37" s="560" t="n"/>
-      <c r="AJ37" s="398" t="n"/>
-      <c r="AK37" s="398" t="n"/>
-      <c r="AL37" s="560" t="n"/>
-      <c r="AM37" s="398" t="n"/>
-      <c r="AN37" s="542" t="n"/>
+      <c r="B37" s="13" t="n"/>
+      <c r="C37" s="663" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="12" t="n"/>
+      <c r="K37" s="12" t="n"/>
+      <c r="L37" s="13" t="n"/>
+      <c r="M37" s="663" t="n"/>
+      <c r="N37" s="12" t="n"/>
+      <c r="O37" s="12" t="n"/>
+      <c r="P37" s="12" t="n"/>
+      <c r="Q37" s="12" t="n"/>
+      <c r="R37" s="12" t="n"/>
+      <c r="S37" s="12" t="n"/>
+      <c r="T37" s="12" t="n"/>
+      <c r="U37" s="12" t="n"/>
+      <c r="V37" s="12" t="n"/>
+      <c r="W37" s="12" t="n"/>
+      <c r="X37" s="13" t="n"/>
+      <c r="Y37" s="663" t="n"/>
+      <c r="Z37" s="12" t="n"/>
+      <c r="AA37" s="12" t="n"/>
+      <c r="AB37" s="12" t="n"/>
+      <c r="AC37" s="13" t="n"/>
+      <c r="AD37" s="663" t="n"/>
+      <c r="AE37" s="12" t="n"/>
+      <c r="AF37" s="12" t="n"/>
+      <c r="AG37" s="12" t="n"/>
+      <c r="AH37" s="13" t="n"/>
+      <c r="AI37" s="663" t="n"/>
+      <c r="AJ37" s="12" t="n"/>
+      <c r="AK37" s="13" t="n"/>
+      <c r="AL37" s="663" t="n"/>
+      <c r="AM37" s="12" t="n"/>
+      <c r="AN37" s="15" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="567" t="n">
+      <c r="A38" s="670" t="n">
         <v>4</v>
       </c>
-      <c r="B38" s="398" t="n"/>
-      <c r="C38" s="560" t="n"/>
-      <c r="D38" s="398" t="n"/>
-      <c r="E38" s="398" t="n"/>
-      <c r="F38" s="398" t="n"/>
-      <c r="G38" s="398" t="n"/>
-      <c r="H38" s="398" t="n"/>
-      <c r="I38" s="398" t="n"/>
-      <c r="J38" s="398" t="n"/>
-      <c r="K38" s="398" t="n"/>
-      <c r="L38" s="398" t="n"/>
-      <c r="M38" s="560" t="n"/>
-      <c r="N38" s="398" t="n"/>
-      <c r="O38" s="398" t="n"/>
-      <c r="P38" s="398" t="n"/>
-      <c r="Q38" s="398" t="n"/>
-      <c r="R38" s="398" t="n"/>
-      <c r="S38" s="398" t="n"/>
-      <c r="T38" s="398" t="n"/>
-      <c r="U38" s="398" t="n"/>
-      <c r="V38" s="398" t="n"/>
-      <c r="W38" s="398" t="n"/>
-      <c r="X38" s="398" t="n"/>
-      <c r="Y38" s="560" t="n"/>
-      <c r="Z38" s="398" t="n"/>
-      <c r="AA38" s="398" t="n"/>
-      <c r="AB38" s="398" t="n"/>
-      <c r="AC38" s="398" t="n"/>
-      <c r="AD38" s="560" t="n"/>
-      <c r="AE38" s="398" t="n"/>
-      <c r="AF38" s="398" t="n"/>
-      <c r="AG38" s="398" t="n"/>
-      <c r="AH38" s="398" t="n"/>
-      <c r="AI38" s="560" t="n"/>
-      <c r="AJ38" s="398" t="n"/>
-      <c r="AK38" s="398" t="n"/>
-      <c r="AL38" s="560" t="n"/>
-      <c r="AM38" s="398" t="n"/>
-      <c r="AN38" s="542" t="n"/>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="663" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="12" t="n"/>
+      <c r="G38" s="12" t="n"/>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="12" t="n"/>
+      <c r="J38" s="12" t="n"/>
+      <c r="K38" s="12" t="n"/>
+      <c r="L38" s="13" t="n"/>
+      <c r="M38" s="663" t="n"/>
+      <c r="N38" s="12" t="n"/>
+      <c r="O38" s="12" t="n"/>
+      <c r="P38" s="12" t="n"/>
+      <c r="Q38" s="12" t="n"/>
+      <c r="R38" s="12" t="n"/>
+      <c r="S38" s="12" t="n"/>
+      <c r="T38" s="12" t="n"/>
+      <c r="U38" s="12" t="n"/>
+      <c r="V38" s="12" t="n"/>
+      <c r="W38" s="12" t="n"/>
+      <c r="X38" s="13" t="n"/>
+      <c r="Y38" s="663" t="n"/>
+      <c r="Z38" s="12" t="n"/>
+      <c r="AA38" s="12" t="n"/>
+      <c r="AB38" s="12" t="n"/>
+      <c r="AC38" s="13" t="n"/>
+      <c r="AD38" s="663" t="n"/>
+      <c r="AE38" s="12" t="n"/>
+      <c r="AF38" s="12" t="n"/>
+      <c r="AG38" s="12" t="n"/>
+      <c r="AH38" s="13" t="n"/>
+      <c r="AI38" s="663" t="n"/>
+      <c r="AJ38" s="12" t="n"/>
+      <c r="AK38" s="13" t="n"/>
+      <c r="AL38" s="663" t="n"/>
+      <c r="AM38" s="12" t="n"/>
+      <c r="AN38" s="15" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="568" t="n">
+      <c r="A39" s="671" t="n">
         <v>5</v>
       </c>
-      <c r="B39" s="544" t="n"/>
-      <c r="C39" s="565" t="n"/>
-      <c r="D39" s="544" t="n"/>
-      <c r="E39" s="544" t="n"/>
-      <c r="F39" s="544" t="n"/>
-      <c r="G39" s="544" t="n"/>
-      <c r="H39" s="544" t="n"/>
-      <c r="I39" s="544" t="n"/>
-      <c r="J39" s="544" t="n"/>
-      <c r="K39" s="544" t="n"/>
-      <c r="L39" s="544" t="n"/>
-      <c r="M39" s="565" t="n"/>
-      <c r="N39" s="544" t="n"/>
-      <c r="O39" s="544" t="n"/>
-      <c r="P39" s="544" t="n"/>
-      <c r="Q39" s="544" t="n"/>
-      <c r="R39" s="544" t="n"/>
-      <c r="S39" s="544" t="n"/>
-      <c r="T39" s="544" t="n"/>
-      <c r="U39" s="544" t="n"/>
-      <c r="V39" s="544" t="n"/>
-      <c r="W39" s="544" t="n"/>
-      <c r="X39" s="544" t="n"/>
-      <c r="Y39" s="565" t="n"/>
-      <c r="Z39" s="544" t="n"/>
-      <c r="AA39" s="544" t="n"/>
-      <c r="AB39" s="544" t="n"/>
-      <c r="AC39" s="544" t="n"/>
-      <c r="AD39" s="565" t="n"/>
-      <c r="AE39" s="544" t="n"/>
-      <c r="AF39" s="544" t="n"/>
-      <c r="AG39" s="544" t="n"/>
-      <c r="AH39" s="544" t="n"/>
-      <c r="AI39" s="565" t="n"/>
-      <c r="AJ39" s="544" t="n"/>
-      <c r="AK39" s="544" t="n"/>
-      <c r="AL39" s="565" t="n"/>
-      <c r="AM39" s="544" t="n"/>
-      <c r="AN39" s="547" t="n"/>
+      <c r="B39" s="22" t="n"/>
+      <c r="C39" s="668" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="19" t="n"/>
+      <c r="H39" s="19" t="n"/>
+      <c r="I39" s="19" t="n"/>
+      <c r="J39" s="19" t="n"/>
+      <c r="K39" s="19" t="n"/>
+      <c r="L39" s="22" t="n"/>
+      <c r="M39" s="668" t="n"/>
+      <c r="N39" s="19" t="n"/>
+      <c r="O39" s="19" t="n"/>
+      <c r="P39" s="19" t="n"/>
+      <c r="Q39" s="19" t="n"/>
+      <c r="R39" s="19" t="n"/>
+      <c r="S39" s="19" t="n"/>
+      <c r="T39" s="19" t="n"/>
+      <c r="U39" s="19" t="n"/>
+      <c r="V39" s="19" t="n"/>
+      <c r="W39" s="19" t="n"/>
+      <c r="X39" s="22" t="n"/>
+      <c r="Y39" s="668" t="n"/>
+      <c r="Z39" s="19" t="n"/>
+      <c r="AA39" s="19" t="n"/>
+      <c r="AB39" s="19" t="n"/>
+      <c r="AC39" s="22" t="n"/>
+      <c r="AD39" s="668" t="n"/>
+      <c r="AE39" s="19" t="n"/>
+      <c r="AF39" s="19" t="n"/>
+      <c r="AG39" s="19" t="n"/>
+      <c r="AH39" s="22" t="n"/>
+      <c r="AI39" s="668" t="n"/>
+      <c r="AJ39" s="19" t="n"/>
+      <c r="AK39" s="22" t="n"/>
+      <c r="AL39" s="668" t="n"/>
+      <c r="AM39" s="19" t="n"/>
+      <c r="AN39" s="24" t="n"/>
     </row>
     <row r="40" ht="3" customHeight="1">
-      <c r="A40" s="410" t="n"/>
-      <c r="B40" s="482" t="n"/>
-      <c r="C40" s="482" t="n"/>
-      <c r="D40" s="482" t="n"/>
-      <c r="E40" s="482" t="n"/>
-      <c r="F40" s="482" t="n"/>
-      <c r="G40" s="482" t="n"/>
-      <c r="H40" s="482" t="n"/>
-      <c r="I40" s="482" t="n"/>
-      <c r="J40" s="482" t="n"/>
-      <c r="K40" s="482" t="n"/>
-      <c r="L40" s="482" t="n"/>
-      <c r="M40" s="482" t="n"/>
-      <c r="N40" s="482" t="n"/>
-      <c r="O40" s="482" t="n"/>
-      <c r="P40" s="482" t="n"/>
-      <c r="Q40" s="482" t="n"/>
-      <c r="R40" s="482" t="n"/>
-      <c r="S40" s="482" t="n"/>
-      <c r="T40" s="482" t="n"/>
-      <c r="U40" s="482" t="n"/>
-      <c r="V40" s="482" t="n"/>
-      <c r="W40" s="482" t="n"/>
-      <c r="X40" s="482" t="n"/>
-      <c r="Y40" s="482" t="n"/>
-      <c r="Z40" s="482" t="n"/>
-      <c r="AA40" s="482" t="n"/>
-      <c r="AB40" s="482" t="n"/>
-      <c r="AC40" s="482" t="n"/>
-      <c r="AD40" s="482" t="n"/>
-      <c r="AE40" s="482" t="n"/>
-      <c r="AF40" s="482" t="n"/>
-      <c r="AG40" s="482" t="n"/>
-      <c r="AH40" s="482" t="n"/>
-      <c r="AI40" s="482" t="n"/>
-      <c r="AJ40" s="482" t="n"/>
-      <c r="AK40" s="482" t="n"/>
-      <c r="AL40" s="482" t="n"/>
-      <c r="AM40" s="482" t="n"/>
-      <c r="AN40" s="482" t="n"/>
+      <c r="A40" s="654" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="n"/>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="10" t="n"/>
+      <c r="L40" s="10" t="n"/>
+      <c r="M40" s="10" t="n"/>
+      <c r="N40" s="10" t="n"/>
+      <c r="O40" s="10" t="n"/>
+      <c r="P40" s="10" t="n"/>
+      <c r="Q40" s="10" t="n"/>
+      <c r="R40" s="10" t="n"/>
+      <c r="S40" s="10" t="n"/>
+      <c r="T40" s="10" t="n"/>
+      <c r="U40" s="10" t="n"/>
+      <c r="V40" s="10" t="n"/>
+      <c r="W40" s="10" t="n"/>
+      <c r="X40" s="10" t="n"/>
+      <c r="Y40" s="10" t="n"/>
+      <c r="Z40" s="10" t="n"/>
+      <c r="AA40" s="10" t="n"/>
+      <c r="AB40" s="10" t="n"/>
+      <c r="AC40" s="10" t="n"/>
+      <c r="AD40" s="10" t="n"/>
+      <c r="AE40" s="10" t="n"/>
+      <c r="AF40" s="10" t="n"/>
+      <c r="AG40" s="10" t="n"/>
+      <c r="AH40" s="10" t="n"/>
+      <c r="AI40" s="10" t="n"/>
+      <c r="AJ40" s="10" t="n"/>
+      <c r="AK40" s="10" t="n"/>
+      <c r="AL40" s="10" t="n"/>
+      <c r="AM40" s="10" t="n"/>
+      <c r="AN40" s="10" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="531" t="inlineStr">
+      <c r="A41" s="647" t="inlineStr">
         <is>
           <t>5.  APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B41" s="532" t="n"/>
-      <c r="C41" s="532" t="n"/>
-      <c r="D41" s="532" t="n"/>
-      <c r="E41" s="532" t="n"/>
-      <c r="F41" s="532" t="n"/>
-      <c r="G41" s="532" t="n"/>
-      <c r="H41" s="532" t="n"/>
-      <c r="I41" s="532" t="n"/>
-      <c r="J41" s="532" t="n"/>
-      <c r="K41" s="532" t="n"/>
-      <c r="L41" s="532" t="n"/>
-      <c r="M41" s="532" t="n"/>
-      <c r="N41" s="532" t="n"/>
-      <c r="O41" s="532" t="n"/>
-      <c r="P41" s="532" t="n"/>
-      <c r="Q41" s="532" t="n"/>
-      <c r="R41" s="532" t="n"/>
-      <c r="S41" s="532" t="n"/>
-      <c r="T41" s="532" t="n"/>
-      <c r="U41" s="532" t="n"/>
-      <c r="V41" s="532" t="n"/>
-      <c r="W41" s="532" t="n"/>
-      <c r="X41" s="532" t="n"/>
-      <c r="Y41" s="532" t="n"/>
-      <c r="Z41" s="532" t="n"/>
-      <c r="AA41" s="532" t="n"/>
-      <c r="AB41" s="532" t="n"/>
-      <c r="AC41" s="532" t="n"/>
-      <c r="AD41" s="532" t="n"/>
-      <c r="AE41" s="532" t="n"/>
-      <c r="AF41" s="532" t="n"/>
-      <c r="AG41" s="532" t="n"/>
-      <c r="AH41" s="532" t="n"/>
-      <c r="AI41" s="532" t="n"/>
-      <c r="AJ41" s="532" t="n"/>
-      <c r="AK41" s="532" t="n"/>
-      <c r="AL41" s="532" t="n"/>
-      <c r="AM41" s="532" t="n"/>
-      <c r="AN41" s="533" t="n"/>
+      <c r="B41" s="27" t="n"/>
+      <c r="C41" s="27" t="n"/>
+      <c r="D41" s="27" t="n"/>
+      <c r="E41" s="27" t="n"/>
+      <c r="F41" s="27" t="n"/>
+      <c r="G41" s="27" t="n"/>
+      <c r="H41" s="27" t="n"/>
+      <c r="I41" s="27" t="n"/>
+      <c r="J41" s="27" t="n"/>
+      <c r="K41" s="27" t="n"/>
+      <c r="L41" s="27" t="n"/>
+      <c r="M41" s="27" t="n"/>
+      <c r="N41" s="27" t="n"/>
+      <c r="O41" s="27" t="n"/>
+      <c r="P41" s="27" t="n"/>
+      <c r="Q41" s="27" t="n"/>
+      <c r="R41" s="27" t="n"/>
+      <c r="S41" s="27" t="n"/>
+      <c r="T41" s="27" t="n"/>
+      <c r="U41" s="27" t="n"/>
+      <c r="V41" s="27" t="n"/>
+      <c r="W41" s="27" t="n"/>
+      <c r="X41" s="27" t="n"/>
+      <c r="Y41" s="27" t="n"/>
+      <c r="Z41" s="27" t="n"/>
+      <c r="AA41" s="27" t="n"/>
+      <c r="AB41" s="27" t="n"/>
+      <c r="AC41" s="27" t="n"/>
+      <c r="AD41" s="27" t="n"/>
+      <c r="AE41" s="27" t="n"/>
+      <c r="AF41" s="27" t="n"/>
+      <c r="AG41" s="27" t="n"/>
+      <c r="AH41" s="27" t="n"/>
+      <c r="AI41" s="27" t="n"/>
+      <c r="AJ41" s="27" t="n"/>
+      <c r="AK41" s="27" t="n"/>
+      <c r="AL41" s="27" t="n"/>
+      <c r="AM41" s="27" t="n"/>
+      <c r="AN41" s="28" t="n"/>
     </row>
     <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="552" t="inlineStr">
+      <c r="A42" s="655" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B42" s="535" t="n"/>
-      <c r="C42" s="535" t="n"/>
-      <c r="D42" s="535" t="n"/>
-      <c r="E42" s="535" t="n"/>
-      <c r="F42" s="535" t="n"/>
-      <c r="G42" s="535" t="n"/>
-      <c r="H42" s="535" t="n"/>
-      <c r="I42" s="535" t="n"/>
-      <c r="J42" s="535" t="n"/>
-      <c r="K42" s="535" t="n"/>
-      <c r="L42" s="535" t="n"/>
-      <c r="M42" s="535" t="n"/>
-      <c r="N42" s="569" t="inlineStr">
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="6" t="n"/>
+      <c r="N42" s="672" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="O42" s="535" t="n"/>
-      <c r="P42" s="535" t="n"/>
-      <c r="Q42" s="535" t="n"/>
-      <c r="R42" s="535" t="n"/>
-      <c r="S42" s="535" t="n"/>
-      <c r="T42" s="535" t="n"/>
-      <c r="U42" s="535" t="n"/>
-      <c r="V42" s="535" t="n"/>
-      <c r="W42" s="535" t="n"/>
-      <c r="X42" s="535" t="n"/>
-      <c r="Y42" s="535" t="n"/>
-      <c r="Z42" s="535" t="n"/>
-      <c r="AA42" s="569" t="inlineStr">
+      <c r="O42" s="5" t="n"/>
+      <c r="P42" s="5" t="n"/>
+      <c r="Q42" s="5" t="n"/>
+      <c r="R42" s="5" t="n"/>
+      <c r="S42" s="5" t="n"/>
+      <c r="T42" s="5" t="n"/>
+      <c r="U42" s="5" t="n"/>
+      <c r="V42" s="5" t="n"/>
+      <c r="W42" s="5" t="n"/>
+      <c r="X42" s="5" t="n"/>
+      <c r="Y42" s="5" t="n"/>
+      <c r="Z42" s="6" t="n"/>
+      <c r="AA42" s="672" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AB42" s="535" t="n"/>
-      <c r="AC42" s="535" t="n"/>
-      <c r="AD42" s="535" t="n"/>
-      <c r="AE42" s="535" t="n"/>
-      <c r="AF42" s="535" t="n"/>
-      <c r="AG42" s="535" t="n"/>
-      <c r="AH42" s="535" t="n"/>
-      <c r="AI42" s="535" t="n"/>
-      <c r="AJ42" s="535" t="n"/>
-      <c r="AK42" s="535" t="n"/>
-      <c r="AL42" s="535" t="n"/>
-      <c r="AM42" s="535" t="n"/>
-      <c r="AN42" s="538" t="n"/>
+      <c r="AB42" s="5" t="n"/>
+      <c r="AC42" s="5" t="n"/>
+      <c r="AD42" s="5" t="n"/>
+      <c r="AE42" s="5" t="n"/>
+      <c r="AF42" s="5" t="n"/>
+      <c r="AG42" s="5" t="n"/>
+      <c r="AH42" s="5" t="n"/>
+      <c r="AI42" s="5" t="n"/>
+      <c r="AJ42" s="5" t="n"/>
+      <c r="AK42" s="5" t="n"/>
+      <c r="AL42" s="5" t="n"/>
+      <c r="AM42" s="5" t="n"/>
+      <c r="AN42" s="8" t="n"/>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="570" t="inlineStr">
+      <c r="A43" s="673" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="B43" s="398" t="n"/>
-      <c r="C43" s="398" t="n"/>
-      <c r="D43" s="398" t="n"/>
-      <c r="E43" s="398" t="n"/>
-      <c r="F43" s="398" t="n"/>
-      <c r="G43" s="398" t="n"/>
-      <c r="H43" s="398" t="n"/>
-      <c r="I43" s="398" t="n"/>
-      <c r="J43" s="398" t="n"/>
-      <c r="K43" s="398" t="n"/>
-      <c r="L43" s="398" t="n"/>
-      <c r="M43" s="398" t="n"/>
-      <c r="N43" s="571" t="inlineStr">
+      <c r="B43" s="12" t="n"/>
+      <c r="C43" s="12" t="n"/>
+      <c r="D43" s="12" t="n"/>
+      <c r="E43" s="12" t="n"/>
+      <c r="F43" s="12" t="n"/>
+      <c r="G43" s="12" t="n"/>
+      <c r="H43" s="12" t="n"/>
+      <c r="I43" s="12" t="n"/>
+      <c r="J43" s="12" t="n"/>
+      <c r="K43" s="12" t="n"/>
+      <c r="L43" s="12" t="n"/>
+      <c r="M43" s="13" t="n"/>
+      <c r="N43" s="674" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="O43" s="398" t="n"/>
-      <c r="P43" s="398" t="n"/>
-      <c r="Q43" s="398" t="n"/>
-      <c r="R43" s="398" t="n"/>
-      <c r="S43" s="398" t="n"/>
-      <c r="T43" s="398" t="n"/>
-      <c r="U43" s="398" t="n"/>
-      <c r="V43" s="398" t="n"/>
-      <c r="W43" s="398" t="n"/>
-      <c r="X43" s="398" t="n"/>
-      <c r="Y43" s="398" t="n"/>
-      <c r="Z43" s="398" t="n"/>
-      <c r="AA43" s="571" t="inlineStr">
+      <c r="O43" s="12" t="n"/>
+      <c r="P43" s="12" t="n"/>
+      <c r="Q43" s="12" t="n"/>
+      <c r="R43" s="12" t="n"/>
+      <c r="S43" s="12" t="n"/>
+      <c r="T43" s="12" t="n"/>
+      <c r="U43" s="12" t="n"/>
+      <c r="V43" s="12" t="n"/>
+      <c r="W43" s="12" t="n"/>
+      <c r="X43" s="12" t="n"/>
+      <c r="Y43" s="12" t="n"/>
+      <c r="Z43" s="13" t="n"/>
+      <c r="AA43" s="674" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="AB43" s="398" t="n"/>
-      <c r="AC43" s="398" t="n"/>
-      <c r="AD43" s="398" t="n"/>
-      <c r="AE43" s="398" t="n"/>
-      <c r="AF43" s="398" t="n"/>
-      <c r="AG43" s="398" t="n"/>
-      <c r="AH43" s="398" t="n"/>
-      <c r="AI43" s="398" t="n"/>
-      <c r="AJ43" s="398" t="n"/>
-      <c r="AK43" s="398" t="n"/>
-      <c r="AL43" s="398" t="n"/>
-      <c r="AM43" s="398" t="n"/>
-      <c r="AN43" s="542" t="n"/>
+      <c r="AB43" s="12" t="n"/>
+      <c r="AC43" s="12" t="n"/>
+      <c r="AD43" s="12" t="n"/>
+      <c r="AE43" s="12" t="n"/>
+      <c r="AF43" s="12" t="n"/>
+      <c r="AG43" s="12" t="n"/>
+      <c r="AH43" s="12" t="n"/>
+      <c r="AI43" s="12" t="n"/>
+      <c r="AJ43" s="12" t="n"/>
+      <c r="AK43" s="12" t="n"/>
+      <c r="AL43" s="12" t="n"/>
+      <c r="AM43" s="12" t="n"/>
+      <c r="AN43" s="15" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="572" t="n"/>
-      <c r="B44" s="398" t="n"/>
-      <c r="C44" s="398" t="n"/>
-      <c r="D44" s="398" t="n"/>
-      <c r="E44" s="398" t="n"/>
-      <c r="F44" s="398" t="n"/>
-      <c r="G44" s="398" t="n"/>
-      <c r="H44" s="398" t="n"/>
-      <c r="I44" s="398" t="n"/>
-      <c r="J44" s="398" t="n"/>
-      <c r="K44" s="398" t="n"/>
-      <c r="L44" s="398" t="n"/>
-      <c r="M44" s="398" t="n"/>
-      <c r="N44" s="573" t="n"/>
-      <c r="O44" s="398" t="n"/>
-      <c r="P44" s="398" t="n"/>
-      <c r="Q44" s="398" t="n"/>
-      <c r="R44" s="398" t="n"/>
-      <c r="S44" s="398" t="n"/>
-      <c r="T44" s="398" t="n"/>
-      <c r="U44" s="398" t="n"/>
-      <c r="V44" s="398" t="n"/>
-      <c r="W44" s="398" t="n"/>
-      <c r="X44" s="398" t="n"/>
-      <c r="Y44" s="398" t="n"/>
-      <c r="Z44" s="398" t="n"/>
-      <c r="AA44" s="573" t="n"/>
-      <c r="AB44" s="398" t="n"/>
-      <c r="AC44" s="398" t="n"/>
-      <c r="AD44" s="398" t="n"/>
-      <c r="AE44" s="398" t="n"/>
-      <c r="AF44" s="398" t="n"/>
-      <c r="AG44" s="398" t="n"/>
-      <c r="AH44" s="398" t="n"/>
-      <c r="AI44" s="398" t="n"/>
-      <c r="AJ44" s="398" t="n"/>
-      <c r="AK44" s="398" t="n"/>
-      <c r="AL44" s="398" t="n"/>
-      <c r="AM44" s="398" t="n"/>
-      <c r="AN44" s="542" t="n"/>
+      <c r="A44" s="16" t="n"/>
+      <c r="B44" s="12" t="n"/>
+      <c r="C44" s="12" t="n"/>
+      <c r="D44" s="12" t="n"/>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="12" t="n"/>
+      <c r="G44" s="12" t="n"/>
+      <c r="H44" s="12" t="n"/>
+      <c r="I44" s="12" t="n"/>
+      <c r="J44" s="12" t="n"/>
+      <c r="K44" s="12" t="n"/>
+      <c r="L44" s="12" t="n"/>
+      <c r="M44" s="13" t="n"/>
+      <c r="N44" s="12" t="n"/>
+      <c r="O44" s="12" t="n"/>
+      <c r="P44" s="12" t="n"/>
+      <c r="Q44" s="12" t="n"/>
+      <c r="R44" s="12" t="n"/>
+      <c r="S44" s="12" t="n"/>
+      <c r="T44" s="12" t="n"/>
+      <c r="U44" s="12" t="n"/>
+      <c r="V44" s="12" t="n"/>
+      <c r="W44" s="12" t="n"/>
+      <c r="X44" s="12" t="n"/>
+      <c r="Y44" s="12" t="n"/>
+      <c r="Z44" s="13" t="n"/>
+      <c r="AA44" s="12" t="n"/>
+      <c r="AB44" s="12" t="n"/>
+      <c r="AC44" s="12" t="n"/>
+      <c r="AD44" s="12" t="n"/>
+      <c r="AE44" s="12" t="n"/>
+      <c r="AF44" s="12" t="n"/>
+      <c r="AG44" s="12" t="n"/>
+      <c r="AH44" s="12" t="n"/>
+      <c r="AI44" s="12" t="n"/>
+      <c r="AJ44" s="12" t="n"/>
+      <c r="AK44" s="12" t="n"/>
+      <c r="AL44" s="12" t="n"/>
+      <c r="AM44" s="12" t="n"/>
+      <c r="AN44" s="15" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="574" t="n"/>
-      <c r="B45" s="544" t="n"/>
-      <c r="C45" s="544" t="n"/>
-      <c r="D45" s="544" t="n"/>
-      <c r="E45" s="544" t="n"/>
-      <c r="F45" s="544" t="n"/>
-      <c r="G45" s="544" t="n"/>
-      <c r="H45" s="544" t="n"/>
-      <c r="I45" s="544" t="n"/>
-      <c r="J45" s="544" t="n"/>
-      <c r="K45" s="544" t="n"/>
-      <c r="L45" s="544" t="n"/>
-      <c r="M45" s="544" t="n"/>
-      <c r="N45" s="575" t="n"/>
-      <c r="O45" s="544" t="n"/>
-      <c r="P45" s="544" t="n"/>
-      <c r="Q45" s="544" t="n"/>
-      <c r="R45" s="544" t="n"/>
-      <c r="S45" s="544" t="n"/>
-      <c r="T45" s="544" t="n"/>
-      <c r="U45" s="544" t="n"/>
-      <c r="V45" s="544" t="n"/>
-      <c r="W45" s="544" t="n"/>
-      <c r="X45" s="544" t="n"/>
-      <c r="Y45" s="544" t="n"/>
-      <c r="Z45" s="544" t="n"/>
-      <c r="AA45" s="575" t="n"/>
-      <c r="AB45" s="544" t="n"/>
-      <c r="AC45" s="544" t="n"/>
-      <c r="AD45" s="544" t="n"/>
-      <c r="AE45" s="544" t="n"/>
-      <c r="AF45" s="544" t="n"/>
-      <c r="AG45" s="544" t="n"/>
-      <c r="AH45" s="544" t="n"/>
-      <c r="AI45" s="544" t="n"/>
-      <c r="AJ45" s="544" t="n"/>
-      <c r="AK45" s="544" t="n"/>
-      <c r="AL45" s="544" t="n"/>
-      <c r="AM45" s="544" t="n"/>
-      <c r="AN45" s="547" t="n"/>
+      <c r="A45" s="18" t="n"/>
+      <c r="B45" s="19" t="n"/>
+      <c r="C45" s="19" t="n"/>
+      <c r="D45" s="19" t="n"/>
+      <c r="E45" s="19" t="n"/>
+      <c r="F45" s="19" t="n"/>
+      <c r="G45" s="19" t="n"/>
+      <c r="H45" s="19" t="n"/>
+      <c r="I45" s="19" t="n"/>
+      <c r="J45" s="19" t="n"/>
+      <c r="K45" s="19" t="n"/>
+      <c r="L45" s="19" t="n"/>
+      <c r="M45" s="22" t="n"/>
+      <c r="N45" s="19" t="n"/>
+      <c r="O45" s="19" t="n"/>
+      <c r="P45" s="19" t="n"/>
+      <c r="Q45" s="19" t="n"/>
+      <c r="R45" s="19" t="n"/>
+      <c r="S45" s="19" t="n"/>
+      <c r="T45" s="19" t="n"/>
+      <c r="U45" s="19" t="n"/>
+      <c r="V45" s="19" t="n"/>
+      <c r="W45" s="19" t="n"/>
+      <c r="X45" s="19" t="n"/>
+      <c r="Y45" s="19" t="n"/>
+      <c r="Z45" s="22" t="n"/>
+      <c r="AA45" s="19" t="n"/>
+      <c r="AB45" s="19" t="n"/>
+      <c r="AC45" s="19" t="n"/>
+      <c r="AD45" s="19" t="n"/>
+      <c r="AE45" s="19" t="n"/>
+      <c r="AF45" s="19" t="n"/>
+      <c r="AG45" s="19" t="n"/>
+      <c r="AH45" s="19" t="n"/>
+      <c r="AI45" s="19" t="n"/>
+      <c r="AJ45" s="19" t="n"/>
+      <c r="AK45" s="19" t="n"/>
+      <c r="AL45" s="19" t="n"/>
+      <c r="AM45" s="19" t="n"/>
+      <c r="AN45" s="24" t="n"/>
     </row>
     <row r="46" ht="3" customHeight="1">
-      <c r="A46" s="410" t="n"/>
-      <c r="B46" s="482" t="n"/>
-      <c r="C46" s="482" t="n"/>
-      <c r="D46" s="482" t="n"/>
-      <c r="E46" s="482" t="n"/>
-      <c r="F46" s="482" t="n"/>
-      <c r="G46" s="482" t="n"/>
-      <c r="H46" s="482" t="n"/>
-      <c r="I46" s="482" t="n"/>
-      <c r="J46" s="482" t="n"/>
-      <c r="K46" s="482" t="n"/>
-      <c r="L46" s="482" t="n"/>
-      <c r="M46" s="482" t="n"/>
-      <c r="N46" s="482" t="n"/>
-      <c r="O46" s="482" t="n"/>
-      <c r="P46" s="482" t="n"/>
-      <c r="Q46" s="482" t="n"/>
-      <c r="R46" s="482" t="n"/>
-      <c r="S46" s="482" t="n"/>
-      <c r="T46" s="482" t="n"/>
-      <c r="U46" s="482" t="n"/>
-      <c r="V46" s="482" t="n"/>
-      <c r="W46" s="482" t="n"/>
-      <c r="X46" s="482" t="n"/>
-      <c r="Y46" s="482" t="n"/>
-      <c r="Z46" s="482" t="n"/>
-      <c r="AA46" s="482" t="n"/>
-      <c r="AB46" s="482" t="n"/>
-      <c r="AC46" s="482" t="n"/>
-      <c r="AD46" s="482" t="n"/>
-      <c r="AE46" s="482" t="n"/>
-      <c r="AF46" s="482" t="n"/>
-      <c r="AG46" s="482" t="n"/>
-      <c r="AH46" s="482" t="n"/>
-      <c r="AI46" s="482" t="n"/>
-      <c r="AJ46" s="482" t="n"/>
-      <c r="AK46" s="482" t="n"/>
-      <c r="AL46" s="482" t="n"/>
-      <c r="AM46" s="482" t="n"/>
-      <c r="AN46" s="482" t="n"/>
+      <c r="A46" s="654" t="n"/>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="n"/>
+      <c r="J46" s="10" t="n"/>
+      <c r="K46" s="10" t="n"/>
+      <c r="L46" s="10" t="n"/>
+      <c r="M46" s="10" t="n"/>
+      <c r="N46" s="10" t="n"/>
+      <c r="O46" s="10" t="n"/>
+      <c r="P46" s="10" t="n"/>
+      <c r="Q46" s="10" t="n"/>
+      <c r="R46" s="10" t="n"/>
+      <c r="S46" s="10" t="n"/>
+      <c r="T46" s="10" t="n"/>
+      <c r="U46" s="10" t="n"/>
+      <c r="V46" s="10" t="n"/>
+      <c r="W46" s="10" t="n"/>
+      <c r="X46" s="10" t="n"/>
+      <c r="Y46" s="10" t="n"/>
+      <c r="Z46" s="10" t="n"/>
+      <c r="AA46" s="10" t="n"/>
+      <c r="AB46" s="10" t="n"/>
+      <c r="AC46" s="10" t="n"/>
+      <c r="AD46" s="10" t="n"/>
+      <c r="AE46" s="10" t="n"/>
+      <c r="AF46" s="10" t="n"/>
+      <c r="AG46" s="10" t="n"/>
+      <c r="AH46" s="10" t="n"/>
+      <c r="AI46" s="10" t="n"/>
+      <c r="AJ46" s="10" t="n"/>
+      <c r="AK46" s="10" t="n"/>
+      <c r="AL46" s="10" t="n"/>
+      <c r="AM46" s="10" t="n"/>
+      <c r="AN46" s="10" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="531" t="inlineStr">
+      <c r="A47" s="647" t="inlineStr">
         <is>
           <t>NOTICE  —  Enter data only in designated white input cells. Do not add, delete or resize columns/rows. File naming: FRM-209_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="532" t="n"/>
-      <c r="C47" s="532" t="n"/>
-      <c r="D47" s="532" t="n"/>
-      <c r="E47" s="532" t="n"/>
-      <c r="F47" s="532" t="n"/>
-      <c r="G47" s="532" t="n"/>
-      <c r="H47" s="532" t="n"/>
-      <c r="I47" s="532" t="n"/>
-      <c r="J47" s="532" t="n"/>
-      <c r="K47" s="532" t="n"/>
-      <c r="L47" s="532" t="n"/>
-      <c r="M47" s="532" t="n"/>
-      <c r="N47" s="532" t="n"/>
-      <c r="O47" s="532" t="n"/>
-      <c r="P47" s="532" t="n"/>
-      <c r="Q47" s="532" t="n"/>
-      <c r="R47" s="532" t="n"/>
-      <c r="S47" s="532" t="n"/>
-      <c r="T47" s="532" t="n"/>
-      <c r="U47" s="532" t="n"/>
-      <c r="V47" s="532" t="n"/>
-      <c r="W47" s="532" t="n"/>
-      <c r="X47" s="532" t="n"/>
-      <c r="Y47" s="532" t="n"/>
-      <c r="Z47" s="532" t="n"/>
-      <c r="AA47" s="532" t="n"/>
-      <c r="AB47" s="532" t="n"/>
-      <c r="AC47" s="532" t="n"/>
-      <c r="AD47" s="532" t="n"/>
-      <c r="AE47" s="532" t="n"/>
-      <c r="AF47" s="532" t="n"/>
-      <c r="AG47" s="532" t="n"/>
-      <c r="AH47" s="532" t="n"/>
-      <c r="AI47" s="532" t="n"/>
-      <c r="AJ47" s="532" t="n"/>
-      <c r="AK47" s="532" t="n"/>
-      <c r="AL47" s="532" t="n"/>
-      <c r="AM47" s="532" t="n"/>
-      <c r="AN47" s="533" t="n"/>
+      <c r="B47" s="27" t="n"/>
+      <c r="C47" s="27" t="n"/>
+      <c r="D47" s="27" t="n"/>
+      <c r="E47" s="27" t="n"/>
+      <c r="F47" s="27" t="n"/>
+      <c r="G47" s="27" t="n"/>
+      <c r="H47" s="27" t="n"/>
+      <c r="I47" s="27" t="n"/>
+      <c r="J47" s="27" t="n"/>
+      <c r="K47" s="27" t="n"/>
+      <c r="L47" s="27" t="n"/>
+      <c r="M47" s="27" t="n"/>
+      <c r="N47" s="27" t="n"/>
+      <c r="O47" s="27" t="n"/>
+      <c r="P47" s="27" t="n"/>
+      <c r="Q47" s="27" t="n"/>
+      <c r="R47" s="27" t="n"/>
+      <c r="S47" s="27" t="n"/>
+      <c r="T47" s="27" t="n"/>
+      <c r="U47" s="27" t="n"/>
+      <c r="V47" s="27" t="n"/>
+      <c r="W47" s="27" t="n"/>
+      <c r="X47" s="27" t="n"/>
+      <c r="Y47" s="27" t="n"/>
+      <c r="Z47" s="27" t="n"/>
+      <c r="AA47" s="27" t="n"/>
+      <c r="AB47" s="27" t="n"/>
+      <c r="AC47" s="27" t="n"/>
+      <c r="AD47" s="27" t="n"/>
+      <c r="AE47" s="27" t="n"/>
+      <c r="AF47" s="27" t="n"/>
+      <c r="AG47" s="27" t="n"/>
+      <c r="AH47" s="27" t="n"/>
+      <c r="AI47" s="27" t="n"/>
+      <c r="AJ47" s="27" t="n"/>
+      <c r="AK47" s="27" t="n"/>
+      <c r="AL47" s="27" t="n"/>
+      <c r="AM47" s="27" t="n"/>
+      <c r="AN47" s="28" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="1"/>
     <row r="49" hidden="1" outlineLevel="1"/>
@@ -9299,7 +9998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:CU7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -9931,7 +10630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:CU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -10552,1378 +11251,1378 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="577" t="n"/>
-      <c r="B1" s="493" t="n"/>
-      <c r="C1" s="578" t="inlineStr">
+      <c r="A1" s="333" t="n"/>
+      <c r="B1" s="53" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>RISKS / ACTIONS REGISTER</t>
         </is>
       </c>
-      <c r="D1" s="493" t="n"/>
-      <c r="E1" s="493" t="n"/>
-      <c r="F1" s="493" t="n"/>
-      <c r="G1" s="493" t="n"/>
-      <c r="H1" s="579" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="675" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="I1" s="495" t="inlineStr">
+      <c r="I1" s="676" t="inlineStr">
         <is>
           <t>FRM-209</t>
         </is>
       </c>
-      <c r="J1" s="496" t="n"/>
-      <c r="K1" s="496" t="n"/>
-      <c r="L1" s="496" t="n"/>
-      <c r="M1" s="496" t="n"/>
-      <c r="N1" s="496" t="n"/>
-      <c r="O1" s="496" t="n"/>
-      <c r="P1" s="496" t="n"/>
-      <c r="Q1" s="496" t="n"/>
-      <c r="R1" s="496" t="n"/>
-      <c r="S1" s="496" t="n"/>
-      <c r="T1" s="496" t="n"/>
-      <c r="U1" s="496" t="n"/>
-      <c r="V1" s="496" t="n"/>
-      <c r="W1" s="496" t="n"/>
-      <c r="X1" s="496" t="n"/>
-      <c r="Y1" s="496" t="n"/>
-      <c r="Z1" s="496" t="n"/>
-      <c r="AA1" s="496" t="n"/>
-      <c r="AB1" s="496" t="n"/>
-      <c r="AC1" s="496" t="n"/>
-      <c r="AD1" s="497" t="n"/>
-      <c r="AE1" s="498" t="n"/>
-      <c r="AF1" s="499" t="n"/>
-      <c r="AG1" s="499" t="n"/>
-      <c r="AH1" s="500" t="n"/>
-      <c r="AI1" s="501" t="n"/>
-      <c r="AJ1" s="502" t="n"/>
-      <c r="AK1" s="502" t="n"/>
-      <c r="AL1" s="502" t="n"/>
-      <c r="AM1" s="502" t="n"/>
-      <c r="AN1" s="503" t="n"/>
+      <c r="J1" s="676" t="n"/>
+      <c r="K1" s="676" t="n"/>
+      <c r="L1" s="676" t="n"/>
+      <c r="M1" s="676" t="n"/>
+      <c r="N1" s="676" t="n"/>
+      <c r="O1" s="676" t="n"/>
+      <c r="P1" s="676" t="n"/>
+      <c r="Q1" s="676" t="n"/>
+      <c r="R1" s="676" t="n"/>
+      <c r="S1" s="676" t="n"/>
+      <c r="T1" s="676" t="n"/>
+      <c r="U1" s="676" t="n"/>
+      <c r="V1" s="676" t="n"/>
+      <c r="W1" s="676" t="n"/>
+      <c r="X1" s="676" t="n"/>
+      <c r="Y1" s="676" t="n"/>
+      <c r="Z1" s="676" t="n"/>
+      <c r="AA1" s="676" t="n"/>
+      <c r="AB1" s="676" t="n"/>
+      <c r="AC1" s="676" t="n"/>
+      <c r="AD1" s="676" t="n"/>
+      <c r="AE1" s="677" t="n"/>
+      <c r="AF1" s="677" t="n"/>
+      <c r="AG1" s="677" t="n"/>
+      <c r="AH1" s="677" t="n"/>
+      <c r="AI1" s="634" t="n"/>
+      <c r="AJ1" s="634" t="n"/>
+      <c r="AK1" s="634" t="n"/>
+      <c r="AL1" s="634" t="n"/>
+      <c r="AM1" s="634" t="n"/>
+      <c r="AN1" s="678" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="504" t="n"/>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
-      <c r="H2" s="580" t="inlineStr">
+      <c r="A2" s="9" t="n"/>
+      <c r="B2" s="54" t="n"/>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="679" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="I2" s="506" t="inlineStr">
+      <c r="I2" s="680" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="J2" s="507" t="n"/>
-      <c r="K2" s="507" t="n"/>
-      <c r="L2" s="507" t="n"/>
-      <c r="M2" s="507" t="n"/>
-      <c r="N2" s="507" t="n"/>
-      <c r="O2" s="507" t="n"/>
-      <c r="P2" s="507" t="n"/>
-      <c r="Q2" s="507" t="n"/>
-      <c r="R2" s="507" t="n"/>
-      <c r="S2" s="507" t="n"/>
-      <c r="T2" s="507" t="n"/>
-      <c r="U2" s="507" t="n"/>
-      <c r="V2" s="507" t="n"/>
-      <c r="W2" s="507" t="n"/>
-      <c r="X2" s="507" t="n"/>
-      <c r="Y2" s="507" t="n"/>
-      <c r="Z2" s="507" t="n"/>
-      <c r="AA2" s="507" t="n"/>
-      <c r="AB2" s="507" t="n"/>
-      <c r="AC2" s="507" t="n"/>
-      <c r="AD2" s="508" t="n"/>
-      <c r="AE2" s="509" t="n"/>
-      <c r="AF2" s="510" t="n"/>
-      <c r="AG2" s="510" t="n"/>
-      <c r="AH2" s="511" t="n"/>
-      <c r="AI2" s="512" t="n"/>
-      <c r="AJ2" s="513" t="n"/>
-      <c r="AK2" s="513" t="n"/>
-      <c r="AL2" s="513" t="n"/>
-      <c r="AM2" s="513" t="n"/>
-      <c r="AN2" s="514" t="n"/>
+      <c r="J2" s="680" t="n"/>
+      <c r="K2" s="680" t="n"/>
+      <c r="L2" s="680" t="n"/>
+      <c r="M2" s="680" t="n"/>
+      <c r="N2" s="680" t="n"/>
+      <c r="O2" s="680" t="n"/>
+      <c r="P2" s="680" t="n"/>
+      <c r="Q2" s="680" t="n"/>
+      <c r="R2" s="680" t="n"/>
+      <c r="S2" s="680" t="n"/>
+      <c r="T2" s="680" t="n"/>
+      <c r="U2" s="680" t="n"/>
+      <c r="V2" s="680" t="n"/>
+      <c r="W2" s="680" t="n"/>
+      <c r="X2" s="680" t="n"/>
+      <c r="Y2" s="680" t="n"/>
+      <c r="Z2" s="680" t="n"/>
+      <c r="AA2" s="680" t="n"/>
+      <c r="AB2" s="680" t="n"/>
+      <c r="AC2" s="680" t="n"/>
+      <c r="AD2" s="680" t="n"/>
+      <c r="AE2" s="681" t="n"/>
+      <c r="AF2" s="681" t="n"/>
+      <c r="AG2" s="681" t="n"/>
+      <c r="AH2" s="681" t="n"/>
+      <c r="AI2" s="638" t="n"/>
+      <c r="AJ2" s="638" t="n"/>
+      <c r="AK2" s="638" t="n"/>
+      <c r="AL2" s="638" t="n"/>
+      <c r="AM2" s="638" t="n"/>
+      <c r="AN2" s="682" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="504" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="580" t="inlineStr">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="54" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="679" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="I3" s="506" t="inlineStr">
+      <c r="I3" s="680" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J3" s="507" t="n"/>
-      <c r="K3" s="507" t="n"/>
-      <c r="L3" s="507" t="n"/>
-      <c r="M3" s="507" t="n"/>
-      <c r="N3" s="507" t="n"/>
-      <c r="O3" s="507" t="n"/>
-      <c r="P3" s="507" t="n"/>
-      <c r="Q3" s="507" t="n"/>
-      <c r="R3" s="507" t="n"/>
-      <c r="S3" s="507" t="n"/>
-      <c r="T3" s="507" t="n"/>
-      <c r="U3" s="507" t="n"/>
-      <c r="V3" s="507" t="n"/>
-      <c r="W3" s="507" t="n"/>
-      <c r="X3" s="507" t="n"/>
-      <c r="Y3" s="507" t="n"/>
-      <c r="Z3" s="507" t="n"/>
-      <c r="AA3" s="507" t="n"/>
-      <c r="AB3" s="507" t="n"/>
-      <c r="AC3" s="507" t="n"/>
-      <c r="AD3" s="508" t="n"/>
-      <c r="AE3" s="509" t="n"/>
-      <c r="AF3" s="510" t="n"/>
-      <c r="AG3" s="510" t="n"/>
-      <c r="AH3" s="511" t="n"/>
-      <c r="AI3" s="512" t="n"/>
-      <c r="AJ3" s="513" t="n"/>
-      <c r="AK3" s="513" t="n"/>
-      <c r="AL3" s="513" t="n"/>
-      <c r="AM3" s="513" t="n"/>
-      <c r="AN3" s="514" t="n"/>
+      <c r="J3" s="680" t="n"/>
+      <c r="K3" s="680" t="n"/>
+      <c r="L3" s="680" t="n"/>
+      <c r="M3" s="680" t="n"/>
+      <c r="N3" s="680" t="n"/>
+      <c r="O3" s="680" t="n"/>
+      <c r="P3" s="680" t="n"/>
+      <c r="Q3" s="680" t="n"/>
+      <c r="R3" s="680" t="n"/>
+      <c r="S3" s="680" t="n"/>
+      <c r="T3" s="680" t="n"/>
+      <c r="U3" s="680" t="n"/>
+      <c r="V3" s="680" t="n"/>
+      <c r="W3" s="680" t="n"/>
+      <c r="X3" s="680" t="n"/>
+      <c r="Y3" s="680" t="n"/>
+      <c r="Z3" s="680" t="n"/>
+      <c r="AA3" s="680" t="n"/>
+      <c r="AB3" s="680" t="n"/>
+      <c r="AC3" s="680" t="n"/>
+      <c r="AD3" s="680" t="n"/>
+      <c r="AE3" s="681" t="n"/>
+      <c r="AF3" s="681" t="n"/>
+      <c r="AG3" s="681" t="n"/>
+      <c r="AH3" s="681" t="n"/>
+      <c r="AI3" s="638" t="n"/>
+      <c r="AJ3" s="638" t="n"/>
+      <c r="AK3" s="638" t="n"/>
+      <c r="AL3" s="638" t="n"/>
+      <c r="AM3" s="638" t="n"/>
+      <c r="AN3" s="682" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="504" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="581" t="inlineStr">
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="683" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="580" t="inlineStr">
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="679" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="I4" s="515" t="inlineStr"/>
-      <c r="J4" s="516" t="n"/>
-      <c r="K4" s="516" t="n"/>
-      <c r="L4" s="516" t="n"/>
-      <c r="M4" s="516" t="n"/>
-      <c r="N4" s="516" t="n"/>
-      <c r="O4" s="516" t="n"/>
-      <c r="P4" s="516" t="n"/>
-      <c r="Q4" s="516" t="n"/>
-      <c r="R4" s="516" t="n"/>
-      <c r="S4" s="516" t="n"/>
-      <c r="T4" s="516" t="n"/>
-      <c r="U4" s="516" t="n"/>
-      <c r="V4" s="516" t="n"/>
-      <c r="W4" s="516" t="n"/>
-      <c r="X4" s="516" t="n"/>
-      <c r="Y4" s="516" t="n"/>
-      <c r="Z4" s="516" t="n"/>
-      <c r="AA4" s="516" t="n"/>
-      <c r="AB4" s="516" t="n"/>
-      <c r="AC4" s="516" t="n"/>
-      <c r="AD4" s="517" t="n"/>
-      <c r="AE4" s="509" t="n"/>
-      <c r="AF4" s="510" t="n"/>
-      <c r="AG4" s="510" t="n"/>
-      <c r="AH4" s="511" t="n"/>
-      <c r="AI4" s="512" t="n"/>
-      <c r="AJ4" s="513" t="n"/>
-      <c r="AK4" s="513" t="n"/>
-      <c r="AL4" s="513" t="n"/>
-      <c r="AM4" s="513" t="n"/>
-      <c r="AN4" s="514" t="n"/>
+      <c r="I4" s="684" t="inlineStr"/>
+      <c r="J4" s="684" t="n"/>
+      <c r="K4" s="684" t="n"/>
+      <c r="L4" s="684" t="n"/>
+      <c r="M4" s="684" t="n"/>
+      <c r="N4" s="684" t="n"/>
+      <c r="O4" s="684" t="n"/>
+      <c r="P4" s="684" t="n"/>
+      <c r="Q4" s="684" t="n"/>
+      <c r="R4" s="684" t="n"/>
+      <c r="S4" s="684" t="n"/>
+      <c r="T4" s="684" t="n"/>
+      <c r="U4" s="684" t="n"/>
+      <c r="V4" s="684" t="n"/>
+      <c r="W4" s="684" t="n"/>
+      <c r="X4" s="684" t="n"/>
+      <c r="Y4" s="684" t="n"/>
+      <c r="Z4" s="684" t="n"/>
+      <c r="AA4" s="684" t="n"/>
+      <c r="AB4" s="684" t="n"/>
+      <c r="AC4" s="684" t="n"/>
+      <c r="AD4" s="684" t="n"/>
+      <c r="AE4" s="681" t="n"/>
+      <c r="AF4" s="681" t="n"/>
+      <c r="AG4" s="681" t="n"/>
+      <c r="AH4" s="681" t="n"/>
+      <c r="AI4" s="638" t="n"/>
+      <c r="AJ4" s="638" t="n"/>
+      <c r="AK4" s="638" t="n"/>
+      <c r="AL4" s="638" t="n"/>
+      <c r="AM4" s="638" t="n"/>
+      <c r="AN4" s="682" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="518" t="n"/>
-      <c r="B5" s="519" t="n"/>
-      <c r="C5" s="582" t="inlineStr">
+      <c r="A5" s="18" t="n"/>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="685" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="519" t="n"/>
-      <c r="E5" s="519" t="n"/>
-      <c r="F5" s="519" t="n"/>
-      <c r="G5" s="519" t="n"/>
-      <c r="H5" s="583" t="inlineStr">
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="19" t="n"/>
+      <c r="H5" s="686" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="I5" s="521" t="inlineStr"/>
-      <c r="J5" s="522" t="n"/>
-      <c r="K5" s="522" t="n"/>
-      <c r="L5" s="522" t="n"/>
-      <c r="M5" s="522" t="n"/>
-      <c r="N5" s="522" t="n"/>
-      <c r="O5" s="522" t="n"/>
-      <c r="P5" s="522" t="n"/>
-      <c r="Q5" s="522" t="n"/>
-      <c r="R5" s="522" t="n"/>
-      <c r="S5" s="522" t="n"/>
-      <c r="T5" s="522" t="n"/>
-      <c r="U5" s="522" t="n"/>
-      <c r="V5" s="522" t="n"/>
-      <c r="W5" s="522" t="n"/>
-      <c r="X5" s="522" t="n"/>
-      <c r="Y5" s="522" t="n"/>
-      <c r="Z5" s="522" t="n"/>
-      <c r="AA5" s="522" t="n"/>
-      <c r="AB5" s="522" t="n"/>
-      <c r="AC5" s="522" t="n"/>
-      <c r="AD5" s="523" t="n"/>
-      <c r="AE5" s="524" t="n"/>
-      <c r="AF5" s="525" t="n"/>
-      <c r="AG5" s="525" t="n"/>
-      <c r="AH5" s="526" t="n"/>
-      <c r="AI5" s="527" t="n"/>
-      <c r="AJ5" s="528" t="n"/>
-      <c r="AK5" s="528" t="n"/>
-      <c r="AL5" s="528" t="n"/>
-      <c r="AM5" s="528" t="n"/>
-      <c r="AN5" s="529" t="n"/>
+      <c r="I5" s="687" t="inlineStr"/>
+      <c r="J5" s="687" t="n"/>
+      <c r="K5" s="687" t="n"/>
+      <c r="L5" s="687" t="n"/>
+      <c r="M5" s="687" t="n"/>
+      <c r="N5" s="687" t="n"/>
+      <c r="O5" s="687" t="n"/>
+      <c r="P5" s="687" t="n"/>
+      <c r="Q5" s="687" t="n"/>
+      <c r="R5" s="687" t="n"/>
+      <c r="S5" s="687" t="n"/>
+      <c r="T5" s="687" t="n"/>
+      <c r="U5" s="687" t="n"/>
+      <c r="V5" s="687" t="n"/>
+      <c r="W5" s="687" t="n"/>
+      <c r="X5" s="687" t="n"/>
+      <c r="Y5" s="687" t="n"/>
+      <c r="Z5" s="687" t="n"/>
+      <c r="AA5" s="687" t="n"/>
+      <c r="AB5" s="687" t="n"/>
+      <c r="AC5" s="687" t="n"/>
+      <c r="AD5" s="687" t="n"/>
+      <c r="AE5" s="688" t="n"/>
+      <c r="AF5" s="688" t="n"/>
+      <c r="AG5" s="688" t="n"/>
+      <c r="AH5" s="688" t="n"/>
+      <c r="AI5" s="644" t="n"/>
+      <c r="AJ5" s="644" t="n"/>
+      <c r="AK5" s="644" t="n"/>
+      <c r="AL5" s="644" t="n"/>
+      <c r="AM5" s="644" t="n"/>
+      <c r="AN5" s="689" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="584" t="n"/>
-      <c r="B6" s="530" t="n"/>
-      <c r="C6" s="530" t="n"/>
-      <c r="D6" s="530" t="n"/>
-      <c r="E6" s="530" t="n"/>
-      <c r="F6" s="530" t="n"/>
-      <c r="G6" s="530" t="n"/>
-      <c r="H6" s="530" t="n"/>
-      <c r="I6" s="530" t="n"/>
-      <c r="J6" s="530" t="n"/>
-      <c r="K6" s="530" t="n"/>
-      <c r="L6" s="530" t="n"/>
-      <c r="M6" s="530" t="n"/>
-      <c r="N6" s="530" t="n"/>
-      <c r="O6" s="530" t="n"/>
-      <c r="P6" s="530" t="n"/>
-      <c r="Q6" s="530" t="n"/>
-      <c r="R6" s="530" t="n"/>
-      <c r="S6" s="530" t="n"/>
-      <c r="T6" s="530" t="n"/>
-      <c r="U6" s="530" t="n"/>
-      <c r="V6" s="530" t="n"/>
-      <c r="W6" s="530" t="n"/>
-      <c r="X6" s="530" t="n"/>
-      <c r="Y6" s="530" t="n"/>
-      <c r="Z6" s="530" t="n"/>
-      <c r="AA6" s="530" t="n"/>
-      <c r="AB6" s="530" t="n"/>
-      <c r="AC6" s="530" t="n"/>
-      <c r="AD6" s="530" t="n"/>
-      <c r="AE6" s="530" t="n"/>
-      <c r="AF6" s="530" t="n"/>
-      <c r="AG6" s="530" t="n"/>
-      <c r="AH6" s="530" t="n"/>
-      <c r="AI6" s="530" t="n"/>
-      <c r="AJ6" s="530" t="n"/>
-      <c r="AK6" s="530" t="n"/>
-      <c r="AL6" s="530" t="n"/>
-      <c r="AM6" s="530" t="n"/>
-      <c r="AN6" s="530" t="n"/>
+      <c r="A6" s="690" t="n"/>
+      <c r="B6" s="646" t="n"/>
+      <c r="C6" s="646" t="n"/>
+      <c r="D6" s="646" t="n"/>
+      <c r="E6" s="646" t="n"/>
+      <c r="F6" s="646" t="n"/>
+      <c r="G6" s="646" t="n"/>
+      <c r="H6" s="646" t="n"/>
+      <c r="I6" s="646" t="n"/>
+      <c r="J6" s="646" t="n"/>
+      <c r="K6" s="646" t="n"/>
+      <c r="L6" s="646" t="n"/>
+      <c r="M6" s="646" t="n"/>
+      <c r="N6" s="646" t="n"/>
+      <c r="O6" s="646" t="n"/>
+      <c r="P6" s="646" t="n"/>
+      <c r="Q6" s="646" t="n"/>
+      <c r="R6" s="646" t="n"/>
+      <c r="S6" s="646" t="n"/>
+      <c r="T6" s="646" t="n"/>
+      <c r="U6" s="646" t="n"/>
+      <c r="V6" s="646" t="n"/>
+      <c r="W6" s="646" t="n"/>
+      <c r="X6" s="646" t="n"/>
+      <c r="Y6" s="646" t="n"/>
+      <c r="Z6" s="646" t="n"/>
+      <c r="AA6" s="646" t="n"/>
+      <c r="AB6" s="646" t="n"/>
+      <c r="AC6" s="646" t="n"/>
+      <c r="AD6" s="646" t="n"/>
+      <c r="AE6" s="646" t="n"/>
+      <c r="AF6" s="646" t="n"/>
+      <c r="AG6" s="646" t="n"/>
+      <c r="AH6" s="646" t="n"/>
+      <c r="AI6" s="646" t="n"/>
+      <c r="AJ6" s="646" t="n"/>
+      <c r="AK6" s="646" t="n"/>
+      <c r="AL6" s="646" t="n"/>
+      <c r="AM6" s="646" t="n"/>
+      <c r="AN6" s="646" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="531" t="inlineStr">
+      <c r="A7" s="647" t="inlineStr">
         <is>
           <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
         </is>
       </c>
-      <c r="B7" s="532" t="n"/>
-      <c r="C7" s="532" t="n"/>
-      <c r="D7" s="532" t="n"/>
-      <c r="E7" s="532" t="n"/>
-      <c r="F7" s="532" t="n"/>
-      <c r="G7" s="532" t="n"/>
-      <c r="H7" s="532" t="n"/>
-      <c r="I7" s="532" t="n"/>
-      <c r="J7" s="532" t="n"/>
-      <c r="K7" s="532" t="n"/>
-      <c r="L7" s="532" t="n"/>
-      <c r="M7" s="532" t="n"/>
-      <c r="N7" s="532" t="n"/>
-      <c r="O7" s="532" t="n"/>
-      <c r="P7" s="532" t="n"/>
-      <c r="Q7" s="532" t="n"/>
-      <c r="R7" s="532" t="n"/>
-      <c r="S7" s="532" t="n"/>
-      <c r="T7" s="532" t="n"/>
-      <c r="U7" s="532" t="n"/>
-      <c r="V7" s="532" t="n"/>
-      <c r="W7" s="532" t="n"/>
-      <c r="X7" s="532" t="n"/>
-      <c r="Y7" s="532" t="n"/>
-      <c r="Z7" s="532" t="n"/>
-      <c r="AA7" s="532" t="n"/>
-      <c r="AB7" s="532" t="n"/>
-      <c r="AC7" s="532" t="n"/>
-      <c r="AD7" s="532" t="n"/>
-      <c r="AE7" s="532" t="n"/>
-      <c r="AF7" s="532" t="n"/>
-      <c r="AG7" s="532" t="n"/>
-      <c r="AH7" s="532" t="n"/>
-      <c r="AI7" s="532" t="n"/>
-      <c r="AJ7" s="532" t="n"/>
-      <c r="AK7" s="532" t="n"/>
-      <c r="AL7" s="532" t="n"/>
-      <c r="AM7" s="532" t="n"/>
-      <c r="AN7" s="533" t="n"/>
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="27" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
+      <c r="H7" s="27" t="n"/>
+      <c r="I7" s="27" t="n"/>
+      <c r="J7" s="691" t="n"/>
+      <c r="K7" s="691" t="n"/>
+      <c r="L7" s="691" t="n"/>
+      <c r="M7" s="691" t="n"/>
+      <c r="N7" s="691" t="n"/>
+      <c r="O7" s="691" t="n"/>
+      <c r="P7" s="691" t="n"/>
+      <c r="Q7" s="691" t="n"/>
+      <c r="R7" s="691" t="n"/>
+      <c r="S7" s="691" t="n"/>
+      <c r="T7" s="691" t="n"/>
+      <c r="U7" s="691" t="n"/>
+      <c r="V7" s="691" t="n"/>
+      <c r="W7" s="691" t="n"/>
+      <c r="X7" s="691" t="n"/>
+      <c r="Y7" s="691" t="n"/>
+      <c r="Z7" s="691" t="n"/>
+      <c r="AA7" s="691" t="n"/>
+      <c r="AB7" s="691" t="n"/>
+      <c r="AC7" s="691" t="n"/>
+      <c r="AD7" s="691" t="n"/>
+      <c r="AE7" s="691" t="n"/>
+      <c r="AF7" s="691" t="n"/>
+      <c r="AG7" s="691" t="n"/>
+      <c r="AH7" s="691" t="n"/>
+      <c r="AI7" s="691" t="n"/>
+      <c r="AJ7" s="691" t="n"/>
+      <c r="AK7" s="691" t="n"/>
+      <c r="AL7" s="691" t="n"/>
+      <c r="AM7" s="691" t="n"/>
+      <c r="AN7" s="692" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="585" t="inlineStr">
+      <c r="A8" s="693" t="inlineStr">
         <is>
           <t>Parent Form</t>
         </is>
       </c>
-      <c r="B8" s="535" t="n"/>
-      <c r="C8" s="586" t="inlineStr">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="694" t="inlineStr">
         <is>
           <t>FRM-209 · HIGH-RISK JOB READINESS REVIEW</t>
         </is>
       </c>
-      <c r="D8" s="535" t="n"/>
-      <c r="E8" s="535" t="n"/>
-      <c r="F8" s="587" t="inlineStr">
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="695" t="inlineStr">
         <is>
           <t>Support Tab</t>
         </is>
       </c>
-      <c r="G8" s="535" t="n"/>
-      <c r="H8" s="586" t="inlineStr">
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="694" t="inlineStr">
         <is>
           <t>RISKS_ACTIONS</t>
         </is>
       </c>
-      <c r="I8" s="535" t="n"/>
-      <c r="J8" s="588" t="n"/>
-      <c r="K8" s="589" t="n"/>
-      <c r="L8" s="589" t="n"/>
-      <c r="M8" s="589" t="n"/>
-      <c r="N8" s="589" t="n"/>
-      <c r="O8" s="589" t="n"/>
-      <c r="P8" s="589" t="n"/>
-      <c r="Q8" s="589" t="n"/>
-      <c r="R8" s="589" t="n"/>
-      <c r="S8" s="589" t="n"/>
-      <c r="T8" s="589" t="n"/>
-      <c r="U8" s="589" t="n"/>
-      <c r="V8" s="589" t="n"/>
-      <c r="W8" s="589" t="n"/>
-      <c r="X8" s="589" t="n"/>
-      <c r="Y8" s="589" t="n"/>
-      <c r="Z8" s="589" t="n"/>
-      <c r="AA8" s="589" t="n"/>
-      <c r="AB8" s="589" t="n"/>
-      <c r="AC8" s="589" t="n"/>
-      <c r="AD8" s="589" t="n"/>
-      <c r="AE8" s="589" t="n"/>
-      <c r="AF8" s="589" t="n"/>
-      <c r="AG8" s="589" t="n"/>
-      <c r="AH8" s="589" t="n"/>
-      <c r="AI8" s="589" t="n"/>
-      <c r="AJ8" s="589" t="n"/>
-      <c r="AK8" s="589" t="n"/>
-      <c r="AL8" s="589" t="n"/>
-      <c r="AM8" s="589" t="n"/>
-      <c r="AN8" s="590" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="696" t="n"/>
+      <c r="K8" s="696" t="n"/>
+      <c r="L8" s="696" t="n"/>
+      <c r="M8" s="696" t="n"/>
+      <c r="N8" s="696" t="n"/>
+      <c r="O8" s="696" t="n"/>
+      <c r="P8" s="696" t="n"/>
+      <c r="Q8" s="696" t="n"/>
+      <c r="R8" s="696" t="n"/>
+      <c r="S8" s="696" t="n"/>
+      <c r="T8" s="696" t="n"/>
+      <c r="U8" s="696" t="n"/>
+      <c r="V8" s="696" t="n"/>
+      <c r="W8" s="696" t="n"/>
+      <c r="X8" s="696" t="n"/>
+      <c r="Y8" s="696" t="n"/>
+      <c r="Z8" s="696" t="n"/>
+      <c r="AA8" s="696" t="n"/>
+      <c r="AB8" s="696" t="n"/>
+      <c r="AC8" s="696" t="n"/>
+      <c r="AD8" s="696" t="n"/>
+      <c r="AE8" s="696" t="n"/>
+      <c r="AF8" s="696" t="n"/>
+      <c r="AG8" s="696" t="n"/>
+      <c r="AH8" s="696" t="n"/>
+      <c r="AI8" s="696" t="n"/>
+      <c r="AJ8" s="696" t="n"/>
+      <c r="AK8" s="696" t="n"/>
+      <c r="AL8" s="696" t="n"/>
+      <c r="AM8" s="696" t="n"/>
+      <c r="AN8" s="697" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="591" t="inlineStr">
+      <c r="A9" s="698" t="inlineStr">
         <is>
           <t>Tab Purpose</t>
         </is>
       </c>
-      <c r="B9" s="398" t="n"/>
-      <c r="C9" s="592" t="inlineStr">
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="699" t="inlineStr">
         <is>
           <t>One line per material, capacity, quality or customer-risk condition.</t>
         </is>
       </c>
-      <c r="D9" s="398" t="n"/>
-      <c r="E9" s="398" t="n"/>
-      <c r="F9" s="593" t="inlineStr">
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="700" t="inlineStr">
         <is>
           <t>Working Owner</t>
         </is>
       </c>
-      <c r="G9" s="398" t="n"/>
-      <c r="H9" s="592" t="inlineStr"/>
-      <c r="I9" s="398" t="n"/>
-      <c r="J9" s="594" t="n"/>
-      <c r="K9" s="413" t="n"/>
-      <c r="L9" s="413" t="n"/>
-      <c r="M9" s="413" t="n"/>
-      <c r="N9" s="413" t="n"/>
-      <c r="O9" s="413" t="n"/>
-      <c r="P9" s="413" t="n"/>
-      <c r="Q9" s="413" t="n"/>
-      <c r="R9" s="413" t="n"/>
-      <c r="S9" s="413" t="n"/>
-      <c r="T9" s="413" t="n"/>
-      <c r="U9" s="413" t="n"/>
-      <c r="V9" s="413" t="n"/>
-      <c r="W9" s="413" t="n"/>
-      <c r="X9" s="413" t="n"/>
-      <c r="Y9" s="413" t="n"/>
-      <c r="Z9" s="413" t="n"/>
-      <c r="AA9" s="413" t="n"/>
-      <c r="AB9" s="413" t="n"/>
-      <c r="AC9" s="413" t="n"/>
-      <c r="AD9" s="413" t="n"/>
-      <c r="AE9" s="413" t="n"/>
-      <c r="AF9" s="413" t="n"/>
-      <c r="AG9" s="413" t="n"/>
-      <c r="AH9" s="413" t="n"/>
-      <c r="AI9" s="413" t="n"/>
-      <c r="AJ9" s="413" t="n"/>
-      <c r="AK9" s="413" t="n"/>
-      <c r="AL9" s="413" t="n"/>
-      <c r="AM9" s="413" t="n"/>
-      <c r="AN9" s="595" t="n"/>
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="699" t="inlineStr"/>
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="701" t="n"/>
+      <c r="K9" s="701" t="n"/>
+      <c r="L9" s="701" t="n"/>
+      <c r="M9" s="701" t="n"/>
+      <c r="N9" s="701" t="n"/>
+      <c r="O9" s="701" t="n"/>
+      <c r="P9" s="701" t="n"/>
+      <c r="Q9" s="701" t="n"/>
+      <c r="R9" s="701" t="n"/>
+      <c r="S9" s="701" t="n"/>
+      <c r="T9" s="701" t="n"/>
+      <c r="U9" s="701" t="n"/>
+      <c r="V9" s="701" t="n"/>
+      <c r="W9" s="701" t="n"/>
+      <c r="X9" s="701" t="n"/>
+      <c r="Y9" s="701" t="n"/>
+      <c r="Z9" s="701" t="n"/>
+      <c r="AA9" s="701" t="n"/>
+      <c r="AB9" s="701" t="n"/>
+      <c r="AC9" s="701" t="n"/>
+      <c r="AD9" s="701" t="n"/>
+      <c r="AE9" s="701" t="n"/>
+      <c r="AF9" s="701" t="n"/>
+      <c r="AG9" s="701" t="n"/>
+      <c r="AH9" s="701" t="n"/>
+      <c r="AI9" s="701" t="n"/>
+      <c r="AJ9" s="701" t="n"/>
+      <c r="AK9" s="701" t="n"/>
+      <c r="AL9" s="701" t="n"/>
+      <c r="AM9" s="701" t="n"/>
+      <c r="AN9" s="702" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="591" t="inlineStr">
+      <c r="A10" s="698" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B10" s="398" t="n"/>
-      <c r="C10" s="592" t="inlineStr">
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="699" t="inlineStr">
         <is>
           <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
         </is>
       </c>
-      <c r="D10" s="398" t="n"/>
-      <c r="E10" s="398" t="n"/>
-      <c r="F10" s="593" t="inlineStr">
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="700" t="inlineStr">
         <is>
           <t>Reviewed By</t>
         </is>
       </c>
-      <c r="G10" s="398" t="n"/>
-      <c r="H10" s="592" t="inlineStr"/>
-      <c r="I10" s="398" t="n"/>
-      <c r="J10" s="594" t="n"/>
-      <c r="K10" s="413" t="n"/>
-      <c r="L10" s="413" t="n"/>
-      <c r="M10" s="413" t="n"/>
-      <c r="N10" s="413" t="n"/>
-      <c r="O10" s="413" t="n"/>
-      <c r="P10" s="413" t="n"/>
-      <c r="Q10" s="413" t="n"/>
-      <c r="R10" s="413" t="n"/>
-      <c r="S10" s="413" t="n"/>
-      <c r="T10" s="413" t="n"/>
-      <c r="U10" s="413" t="n"/>
-      <c r="V10" s="413" t="n"/>
-      <c r="W10" s="413" t="n"/>
-      <c r="X10" s="413" t="n"/>
-      <c r="Y10" s="413" t="n"/>
-      <c r="Z10" s="413" t="n"/>
-      <c r="AA10" s="413" t="n"/>
-      <c r="AB10" s="413" t="n"/>
-      <c r="AC10" s="413" t="n"/>
-      <c r="AD10" s="413" t="n"/>
-      <c r="AE10" s="413" t="n"/>
-      <c r="AF10" s="413" t="n"/>
-      <c r="AG10" s="413" t="n"/>
-      <c r="AH10" s="413" t="n"/>
-      <c r="AI10" s="413" t="n"/>
-      <c r="AJ10" s="413" t="n"/>
-      <c r="AK10" s="413" t="n"/>
-      <c r="AL10" s="413" t="n"/>
-      <c r="AM10" s="413" t="n"/>
-      <c r="AN10" s="595" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="699" t="inlineStr"/>
+      <c r="I10" s="13" t="n"/>
+      <c r="J10" s="701" t="n"/>
+      <c r="K10" s="701" t="n"/>
+      <c r="L10" s="701" t="n"/>
+      <c r="M10" s="701" t="n"/>
+      <c r="N10" s="701" t="n"/>
+      <c r="O10" s="701" t="n"/>
+      <c r="P10" s="701" t="n"/>
+      <c r="Q10" s="701" t="n"/>
+      <c r="R10" s="701" t="n"/>
+      <c r="S10" s="701" t="n"/>
+      <c r="T10" s="701" t="n"/>
+      <c r="U10" s="701" t="n"/>
+      <c r="V10" s="701" t="n"/>
+      <c r="W10" s="701" t="n"/>
+      <c r="X10" s="701" t="n"/>
+      <c r="Y10" s="701" t="n"/>
+      <c r="Z10" s="701" t="n"/>
+      <c r="AA10" s="701" t="n"/>
+      <c r="AB10" s="701" t="n"/>
+      <c r="AC10" s="701" t="n"/>
+      <c r="AD10" s="701" t="n"/>
+      <c r="AE10" s="701" t="n"/>
+      <c r="AF10" s="701" t="n"/>
+      <c r="AG10" s="701" t="n"/>
+      <c r="AH10" s="701" t="n"/>
+      <c r="AI10" s="701" t="n"/>
+      <c r="AJ10" s="701" t="n"/>
+      <c r="AK10" s="701" t="n"/>
+      <c r="AL10" s="701" t="n"/>
+      <c r="AM10" s="701" t="n"/>
+      <c r="AN10" s="702" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="591" t="inlineStr">
+      <c r="A11" s="698" t="inlineStr">
         <is>
           <t>Update Trigger</t>
         </is>
       </c>
-      <c r="B11" s="398" t="n"/>
-      <c r="C11" s="592" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="699" t="inlineStr">
         <is>
           <t>Update when the linked review, evidence or follow-up status changes.</t>
         </is>
       </c>
-      <c r="D11" s="398" t="n"/>
-      <c r="E11" s="398" t="n"/>
-      <c r="F11" s="593" t="inlineStr">
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="700" t="inlineStr">
         <is>
           <t>Data Structure</t>
         </is>
       </c>
-      <c r="G11" s="398" t="n"/>
-      <c r="H11" s="592" t="inlineStr">
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="699" t="inlineStr">
         <is>
           <t>Structured Excel Table with filters and print-title rows.</t>
         </is>
       </c>
-      <c r="I11" s="398" t="n"/>
-      <c r="J11" s="573" t="n"/>
-      <c r="K11" s="398" t="n"/>
-      <c r="L11" s="398" t="n"/>
-      <c r="M11" s="398" t="n"/>
-      <c r="N11" s="398" t="n"/>
-      <c r="O11" s="398" t="n"/>
-      <c r="P11" s="398" t="n"/>
-      <c r="Q11" s="398" t="n"/>
-      <c r="R11" s="398" t="n"/>
-      <c r="S11" s="398" t="n"/>
-      <c r="T11" s="398" t="n"/>
-      <c r="U11" s="398" t="n"/>
-      <c r="V11" s="398" t="n"/>
-      <c r="W11" s="398" t="n"/>
-      <c r="X11" s="398" t="n"/>
-      <c r="Y11" s="398" t="n"/>
-      <c r="Z11" s="398" t="n"/>
-      <c r="AA11" s="398" t="n"/>
-      <c r="AB11" s="398" t="n"/>
-      <c r="AC11" s="398" t="n"/>
-      <c r="AD11" s="398" t="n"/>
-      <c r="AE11" s="398" t="n"/>
-      <c r="AF11" s="398" t="n"/>
-      <c r="AG11" s="398" t="n"/>
-      <c r="AH11" s="398" t="n"/>
-      <c r="AI11" s="398" t="n"/>
-      <c r="AJ11" s="398" t="n"/>
-      <c r="AK11" s="398" t="n"/>
-      <c r="AL11" s="398" t="n"/>
-      <c r="AM11" s="398" t="n"/>
-      <c r="AN11" s="542" t="n"/>
+      <c r="I11" s="13" t="n"/>
+      <c r="J11" s="703" t="n"/>
+      <c r="K11" s="703" t="n"/>
+      <c r="L11" s="703" t="n"/>
+      <c r="M11" s="703" t="n"/>
+      <c r="N11" s="703" t="n"/>
+      <c r="O11" s="703" t="n"/>
+      <c r="P11" s="703" t="n"/>
+      <c r="Q11" s="703" t="n"/>
+      <c r="R11" s="703" t="n"/>
+      <c r="S11" s="703" t="n"/>
+      <c r="T11" s="703" t="n"/>
+      <c r="U11" s="703" t="n"/>
+      <c r="V11" s="703" t="n"/>
+      <c r="W11" s="703" t="n"/>
+      <c r="X11" s="703" t="n"/>
+      <c r="Y11" s="703" t="n"/>
+      <c r="Z11" s="703" t="n"/>
+      <c r="AA11" s="703" t="n"/>
+      <c r="AB11" s="703" t="n"/>
+      <c r="AC11" s="703" t="n"/>
+      <c r="AD11" s="703" t="n"/>
+      <c r="AE11" s="703" t="n"/>
+      <c r="AF11" s="703" t="n"/>
+      <c r="AG11" s="703" t="n"/>
+      <c r="AH11" s="703" t="n"/>
+      <c r="AI11" s="703" t="n"/>
+      <c r="AJ11" s="703" t="n"/>
+      <c r="AK11" s="703" t="n"/>
+      <c r="AL11" s="703" t="n"/>
+      <c r="AM11" s="703" t="n"/>
+      <c r="AN11" s="704" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="596" t="inlineStr">
+      <c r="A12" s="705" t="inlineStr">
         <is>
           <t>Retention Rule</t>
         </is>
       </c>
-      <c r="B12" s="544" t="n"/>
-      <c r="C12" s="597" t="inlineStr">
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="706" t="inlineStr">
         <is>
           <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
         </is>
       </c>
-      <c r="D12" s="544" t="n"/>
-      <c r="E12" s="544" t="n"/>
-      <c r="F12" s="598" t="inlineStr">
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="707" t="inlineStr">
         <is>
           <t>Controlled Status</t>
         </is>
       </c>
-      <c r="G12" s="544" t="n"/>
-      <c r="H12" s="597" t="inlineStr">
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="706" t="inlineStr">
         <is>
           <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
         </is>
       </c>
-      <c r="I12" s="544" t="n"/>
-      <c r="J12" s="599" t="n"/>
-      <c r="K12" s="600" t="n"/>
-      <c r="L12" s="600" t="n"/>
-      <c r="M12" s="600" t="n"/>
-      <c r="N12" s="600" t="n"/>
-      <c r="O12" s="600" t="n"/>
-      <c r="P12" s="600" t="n"/>
-      <c r="Q12" s="600" t="n"/>
-      <c r="R12" s="600" t="n"/>
-      <c r="S12" s="600" t="n"/>
-      <c r="T12" s="600" t="n"/>
-      <c r="U12" s="600" t="n"/>
-      <c r="V12" s="600" t="n"/>
-      <c r="W12" s="600" t="n"/>
-      <c r="X12" s="600" t="n"/>
-      <c r="Y12" s="600" t="n"/>
-      <c r="Z12" s="600" t="n"/>
-      <c r="AA12" s="600" t="n"/>
-      <c r="AB12" s="600" t="n"/>
-      <c r="AC12" s="600" t="n"/>
-      <c r="AD12" s="600" t="n"/>
-      <c r="AE12" s="600" t="n"/>
-      <c r="AF12" s="600" t="n"/>
-      <c r="AG12" s="600" t="n"/>
-      <c r="AH12" s="600" t="n"/>
-      <c r="AI12" s="600" t="n"/>
-      <c r="AJ12" s="600" t="n"/>
-      <c r="AK12" s="600" t="n"/>
-      <c r="AL12" s="600" t="n"/>
-      <c r="AM12" s="600" t="n"/>
-      <c r="AN12" s="601" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="708" t="n"/>
+      <c r="K12" s="708" t="n"/>
+      <c r="L12" s="708" t="n"/>
+      <c r="M12" s="708" t="n"/>
+      <c r="N12" s="708" t="n"/>
+      <c r="O12" s="708" t="n"/>
+      <c r="P12" s="708" t="n"/>
+      <c r="Q12" s="708" t="n"/>
+      <c r="R12" s="708" t="n"/>
+      <c r="S12" s="708" t="n"/>
+      <c r="T12" s="708" t="n"/>
+      <c r="U12" s="708" t="n"/>
+      <c r="V12" s="708" t="n"/>
+      <c r="W12" s="708" t="n"/>
+      <c r="X12" s="708" t="n"/>
+      <c r="Y12" s="708" t="n"/>
+      <c r="Z12" s="708" t="n"/>
+      <c r="AA12" s="708" t="n"/>
+      <c r="AB12" s="708" t="n"/>
+      <c r="AC12" s="708" t="n"/>
+      <c r="AD12" s="708" t="n"/>
+      <c r="AE12" s="708" t="n"/>
+      <c r="AF12" s="708" t="n"/>
+      <c r="AG12" s="708" t="n"/>
+      <c r="AH12" s="708" t="n"/>
+      <c r="AI12" s="708" t="n"/>
+      <c r="AJ12" s="708" t="n"/>
+      <c r="AK12" s="708" t="n"/>
+      <c r="AL12" s="708" t="n"/>
+      <c r="AM12" s="708" t="n"/>
+      <c r="AN12" s="709" t="n"/>
     </row>
     <row r="13" ht="3" customHeight="1">
-      <c r="A13" s="449" t="n"/>
-      <c r="B13" s="482" t="n"/>
-      <c r="C13" s="482" t="n"/>
-      <c r="D13" s="482" t="n"/>
-      <c r="E13" s="482" t="n"/>
-      <c r="F13" s="482" t="n"/>
-      <c r="G13" s="482" t="n"/>
-      <c r="H13" s="482" t="n"/>
-      <c r="I13" s="482" t="n"/>
-      <c r="J13" s="410" t="n"/>
-      <c r="K13" s="410" t="n"/>
-      <c r="L13" s="410" t="n"/>
-      <c r="M13" s="410" t="n"/>
-      <c r="N13" s="410" t="n"/>
-      <c r="O13" s="410" t="n"/>
-      <c r="P13" s="410" t="n"/>
-      <c r="Q13" s="410" t="n"/>
-      <c r="R13" s="410" t="n"/>
-      <c r="S13" s="410" t="n"/>
-      <c r="T13" s="410" t="n"/>
-      <c r="U13" s="410" t="n"/>
-      <c r="V13" s="410" t="n"/>
-      <c r="W13" s="410" t="n"/>
-      <c r="X13" s="410" t="n"/>
-      <c r="Y13" s="410" t="n"/>
-      <c r="Z13" s="410" t="n"/>
-      <c r="AA13" s="410" t="n"/>
-      <c r="AB13" s="410" t="n"/>
-      <c r="AC13" s="410" t="n"/>
-      <c r="AD13" s="410" t="n"/>
-      <c r="AE13" s="410" t="n"/>
-      <c r="AF13" s="410" t="n"/>
-      <c r="AG13" s="410" t="n"/>
-      <c r="AH13" s="410" t="n"/>
-      <c r="AI13" s="410" t="n"/>
-      <c r="AJ13" s="410" t="n"/>
-      <c r="AK13" s="410" t="n"/>
-      <c r="AL13" s="410" t="n"/>
-      <c r="AM13" s="410" t="n"/>
-      <c r="AN13" s="410" t="n"/>
+      <c r="A13" s="710" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="654" t="n"/>
+      <c r="K13" s="654" t="n"/>
+      <c r="L13" s="654" t="n"/>
+      <c r="M13" s="654" t="n"/>
+      <c r="N13" s="654" t="n"/>
+      <c r="O13" s="654" t="n"/>
+      <c r="P13" s="654" t="n"/>
+      <c r="Q13" s="654" t="n"/>
+      <c r="R13" s="654" t="n"/>
+      <c r="S13" s="654" t="n"/>
+      <c r="T13" s="654" t="n"/>
+      <c r="U13" s="654" t="n"/>
+      <c r="V13" s="654" t="n"/>
+      <c r="W13" s="654" t="n"/>
+      <c r="X13" s="654" t="n"/>
+      <c r="Y13" s="654" t="n"/>
+      <c r="Z13" s="654" t="n"/>
+      <c r="AA13" s="654" t="n"/>
+      <c r="AB13" s="654" t="n"/>
+      <c r="AC13" s="654" t="n"/>
+      <c r="AD13" s="654" t="n"/>
+      <c r="AE13" s="654" t="n"/>
+      <c r="AF13" s="654" t="n"/>
+      <c r="AG13" s="654" t="n"/>
+      <c r="AH13" s="654" t="n"/>
+      <c r="AI13" s="654" t="n"/>
+      <c r="AJ13" s="654" t="n"/>
+      <c r="AK13" s="654" t="n"/>
+      <c r="AL13" s="654" t="n"/>
+      <c r="AM13" s="654" t="n"/>
+      <c r="AN13" s="654" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="531" t="inlineStr">
+      <c r="A14" s="647" t="inlineStr">
         <is>
           <t>2.  WORKING TABLE / DETAIL LINES</t>
         </is>
       </c>
-      <c r="B14" s="532" t="n"/>
-      <c r="C14" s="532" t="n"/>
-      <c r="D14" s="532" t="n"/>
-      <c r="E14" s="532" t="n"/>
-      <c r="F14" s="532" t="n"/>
-      <c r="G14" s="532" t="n"/>
-      <c r="H14" s="532" t="n"/>
-      <c r="I14" s="532" t="n"/>
-      <c r="J14" s="532" t="n"/>
-      <c r="K14" s="532" t="n"/>
-      <c r="L14" s="532" t="n"/>
-      <c r="M14" s="532" t="n"/>
-      <c r="N14" s="532" t="n"/>
-      <c r="O14" s="532" t="n"/>
-      <c r="P14" s="532" t="n"/>
-      <c r="Q14" s="532" t="n"/>
-      <c r="R14" s="532" t="n"/>
-      <c r="S14" s="532" t="n"/>
-      <c r="T14" s="532" t="n"/>
-      <c r="U14" s="532" t="n"/>
-      <c r="V14" s="532" t="n"/>
-      <c r="W14" s="532" t="n"/>
-      <c r="X14" s="532" t="n"/>
-      <c r="Y14" s="532" t="n"/>
-      <c r="Z14" s="532" t="n"/>
-      <c r="AA14" s="532" t="n"/>
-      <c r="AB14" s="532" t="n"/>
-      <c r="AC14" s="532" t="n"/>
-      <c r="AD14" s="532" t="n"/>
-      <c r="AE14" s="532" t="n"/>
-      <c r="AF14" s="532" t="n"/>
-      <c r="AG14" s="532" t="n"/>
-      <c r="AH14" s="532" t="n"/>
-      <c r="AI14" s="532" t="n"/>
-      <c r="AJ14" s="532" t="n"/>
-      <c r="AK14" s="532" t="n"/>
-      <c r="AL14" s="532" t="n"/>
-      <c r="AM14" s="532" t="n"/>
-      <c r="AN14" s="533" t="n"/>
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="27" t="n"/>
+      <c r="H14" s="27" t="n"/>
+      <c r="I14" s="27" t="n"/>
+      <c r="J14" s="691" t="n"/>
+      <c r="K14" s="691" t="n"/>
+      <c r="L14" s="691" t="n"/>
+      <c r="M14" s="691" t="n"/>
+      <c r="N14" s="691" t="n"/>
+      <c r="O14" s="691" t="n"/>
+      <c r="P14" s="691" t="n"/>
+      <c r="Q14" s="691" t="n"/>
+      <c r="R14" s="691" t="n"/>
+      <c r="S14" s="691" t="n"/>
+      <c r="T14" s="691" t="n"/>
+      <c r="U14" s="691" t="n"/>
+      <c r="V14" s="691" t="n"/>
+      <c r="W14" s="691" t="n"/>
+      <c r="X14" s="691" t="n"/>
+      <c r="Y14" s="691" t="n"/>
+      <c r="Z14" s="691" t="n"/>
+      <c r="AA14" s="691" t="n"/>
+      <c r="AB14" s="691" t="n"/>
+      <c r="AC14" s="691" t="n"/>
+      <c r="AD14" s="691" t="n"/>
+      <c r="AE14" s="691" t="n"/>
+      <c r="AF14" s="691" t="n"/>
+      <c r="AG14" s="691" t="n"/>
+      <c r="AH14" s="691" t="n"/>
+      <c r="AI14" s="691" t="n"/>
+      <c r="AJ14" s="691" t="n"/>
+      <c r="AK14" s="691" t="n"/>
+      <c r="AL14" s="691" t="n"/>
+      <c r="AM14" s="691" t="n"/>
+      <c r="AN14" s="692" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="531" t="inlineStr">
+      <c r="A15" s="647" t="inlineStr">
         <is>
           <t>One line per material, capacity, quality or customer-risk condition.</t>
         </is>
       </c>
-      <c r="B15" s="532" t="n"/>
-      <c r="C15" s="532" t="n"/>
-      <c r="D15" s="532" t="n"/>
-      <c r="E15" s="532" t="n"/>
-      <c r="F15" s="532" t="n"/>
-      <c r="G15" s="532" t="n"/>
-      <c r="H15" s="532" t="n"/>
-      <c r="I15" s="532" t="n"/>
-      <c r="J15" s="532" t="n"/>
-      <c r="K15" s="532" t="n"/>
-      <c r="L15" s="532" t="n"/>
-      <c r="M15" s="532" t="n"/>
-      <c r="N15" s="532" t="n"/>
-      <c r="O15" s="532" t="n"/>
-      <c r="P15" s="532" t="n"/>
-      <c r="Q15" s="532" t="n"/>
-      <c r="R15" s="532" t="n"/>
-      <c r="S15" s="532" t="n"/>
-      <c r="T15" s="532" t="n"/>
-      <c r="U15" s="532" t="n"/>
-      <c r="V15" s="532" t="n"/>
-      <c r="W15" s="532" t="n"/>
-      <c r="X15" s="532" t="n"/>
-      <c r="Y15" s="532" t="n"/>
-      <c r="Z15" s="532" t="n"/>
-      <c r="AA15" s="532" t="n"/>
-      <c r="AB15" s="532" t="n"/>
-      <c r="AC15" s="532" t="n"/>
-      <c r="AD15" s="532" t="n"/>
-      <c r="AE15" s="532" t="n"/>
-      <c r="AF15" s="532" t="n"/>
-      <c r="AG15" s="532" t="n"/>
-      <c r="AH15" s="532" t="n"/>
-      <c r="AI15" s="532" t="n"/>
-      <c r="AJ15" s="532" t="n"/>
-      <c r="AK15" s="532" t="n"/>
-      <c r="AL15" s="532" t="n"/>
-      <c r="AM15" s="532" t="n"/>
-      <c r="AN15" s="533" t="n"/>
+      <c r="B15" s="27" t="n"/>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="27" t="n"/>
+      <c r="H15" s="27" t="n"/>
+      <c r="I15" s="27" t="n"/>
+      <c r="J15" s="691" t="n"/>
+      <c r="K15" s="691" t="n"/>
+      <c r="L15" s="691" t="n"/>
+      <c r="M15" s="691" t="n"/>
+      <c r="N15" s="691" t="n"/>
+      <c r="O15" s="691" t="n"/>
+      <c r="P15" s="691" t="n"/>
+      <c r="Q15" s="691" t="n"/>
+      <c r="R15" s="691" t="n"/>
+      <c r="S15" s="691" t="n"/>
+      <c r="T15" s="691" t="n"/>
+      <c r="U15" s="691" t="n"/>
+      <c r="V15" s="691" t="n"/>
+      <c r="W15" s="691" t="n"/>
+      <c r="X15" s="691" t="n"/>
+      <c r="Y15" s="691" t="n"/>
+      <c r="Z15" s="691" t="n"/>
+      <c r="AA15" s="691" t="n"/>
+      <c r="AB15" s="691" t="n"/>
+      <c r="AC15" s="691" t="n"/>
+      <c r="AD15" s="691" t="n"/>
+      <c r="AE15" s="691" t="n"/>
+      <c r="AF15" s="691" t="n"/>
+      <c r="AG15" s="691" t="n"/>
+      <c r="AH15" s="691" t="n"/>
+      <c r="AI15" s="691" t="n"/>
+      <c r="AJ15" s="691" t="n"/>
+      <c r="AK15" s="691" t="n"/>
+      <c r="AL15" s="691" t="n"/>
+      <c r="AM15" s="691" t="n"/>
+      <c r="AN15" s="692" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="548" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B16" s="549" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>Risk / Readiness Gap</t>
         </is>
       </c>
-      <c r="C16" s="549" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="D16" s="549" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>Containment / Action</t>
         </is>
       </c>
-      <c r="E16" s="549" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F16" s="549" t="inlineStr">
+      <c r="F16" s="37" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="G16" s="549" t="inlineStr">
+      <c r="G16" s="37" t="inlineStr">
         <is>
           <t>Escalation</t>
         </is>
       </c>
-      <c r="H16" s="549" t="inlineStr">
+      <c r="H16" s="37" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I16" s="549" t="inlineStr">
+      <c r="I16" s="37" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="J16" s="549" t="n"/>
-      <c r="K16" s="549" t="n"/>
-      <c r="L16" s="549" t="n"/>
-      <c r="M16" s="549" t="n"/>
-      <c r="N16" s="549" t="n"/>
-      <c r="O16" s="549" t="n"/>
-      <c r="P16" s="549" t="n"/>
-      <c r="Q16" s="549" t="n"/>
-      <c r="R16" s="549" t="n"/>
-      <c r="S16" s="549" t="n"/>
-      <c r="T16" s="549" t="n"/>
-      <c r="U16" s="549" t="n"/>
-      <c r="V16" s="549" t="n"/>
-      <c r="W16" s="549" t="n"/>
-      <c r="X16" s="549" t="n"/>
-      <c r="Y16" s="549" t="n"/>
-      <c r="Z16" s="549" t="n"/>
-      <c r="AA16" s="549" t="n"/>
-      <c r="AB16" s="549" t="n"/>
-      <c r="AC16" s="549" t="n"/>
-      <c r="AD16" s="549" t="n"/>
-      <c r="AE16" s="549" t="n"/>
-      <c r="AF16" s="549" t="n"/>
-      <c r="AG16" s="549" t="n"/>
-      <c r="AH16" s="549" t="n"/>
-      <c r="AI16" s="549" t="n"/>
-      <c r="AJ16" s="549" t="n"/>
-      <c r="AK16" s="549" t="n"/>
-      <c r="AL16" s="549" t="n"/>
-      <c r="AM16" s="549" t="n"/>
-      <c r="AN16" s="551" t="n"/>
+      <c r="J16" s="37" t="n"/>
+      <c r="K16" s="37" t="n"/>
+      <c r="L16" s="37" t="n"/>
+      <c r="M16" s="37" t="n"/>
+      <c r="N16" s="37" t="n"/>
+      <c r="O16" s="37" t="n"/>
+      <c r="P16" s="37" t="n"/>
+      <c r="Q16" s="37" t="n"/>
+      <c r="R16" s="37" t="n"/>
+      <c r="S16" s="37" t="n"/>
+      <c r="T16" s="37" t="n"/>
+      <c r="U16" s="37" t="n"/>
+      <c r="V16" s="37" t="n"/>
+      <c r="W16" s="37" t="n"/>
+      <c r="X16" s="37" t="n"/>
+      <c r="Y16" s="37" t="n"/>
+      <c r="Z16" s="37" t="n"/>
+      <c r="AA16" s="37" t="n"/>
+      <c r="AB16" s="37" t="n"/>
+      <c r="AC16" s="37" t="n"/>
+      <c r="AD16" s="37" t="n"/>
+      <c r="AE16" s="37" t="n"/>
+      <c r="AF16" s="37" t="n"/>
+      <c r="AG16" s="37" t="n"/>
+      <c r="AH16" s="37" t="n"/>
+      <c r="AI16" s="37" t="n"/>
+      <c r="AJ16" s="37" t="n"/>
+      <c r="AK16" s="37" t="n"/>
+      <c r="AL16" s="37" t="n"/>
+      <c r="AM16" s="37" t="n"/>
+      <c r="AN16" s="303" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="602">
+      <c r="A17" s="711">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B17" s="586" t="n"/>
-      <c r="C17" s="603" t="n"/>
-      <c r="D17" s="603" t="n"/>
-      <c r="E17" s="603" t="n"/>
-      <c r="F17" s="604" t="n"/>
-      <c r="G17" s="603" t="n"/>
-      <c r="H17" s="603" t="n"/>
-      <c r="I17" s="603" t="n"/>
-      <c r="J17" s="589" t="n"/>
-      <c r="K17" s="589" t="n"/>
-      <c r="L17" s="589" t="n"/>
-      <c r="M17" s="589" t="n"/>
-      <c r="N17" s="589" t="n"/>
-      <c r="O17" s="589" t="n"/>
-      <c r="P17" s="589" t="n"/>
-      <c r="Q17" s="589" t="n"/>
-      <c r="R17" s="589" t="n"/>
-      <c r="S17" s="589" t="n"/>
-      <c r="T17" s="589" t="n"/>
-      <c r="U17" s="589" t="n"/>
-      <c r="V17" s="589" t="n"/>
-      <c r="W17" s="589" t="n"/>
-      <c r="X17" s="589" t="n"/>
-      <c r="Y17" s="589" t="n"/>
-      <c r="Z17" s="589" t="n"/>
-      <c r="AA17" s="589" t="n"/>
-      <c r="AB17" s="589" t="n"/>
-      <c r="AC17" s="589" t="n"/>
-      <c r="AD17" s="589" t="n"/>
-      <c r="AE17" s="589" t="n"/>
-      <c r="AF17" s="589" t="n"/>
-      <c r="AG17" s="589" t="n"/>
-      <c r="AH17" s="589" t="n"/>
-      <c r="AI17" s="589" t="n"/>
-      <c r="AJ17" s="589" t="n"/>
-      <c r="AK17" s="589" t="n"/>
-      <c r="AL17" s="589" t="n"/>
-      <c r="AM17" s="589" t="n"/>
-      <c r="AN17" s="590" t="n"/>
+      <c r="B17" s="694" t="n"/>
+      <c r="C17" s="694" t="n"/>
+      <c r="D17" s="694" t="n"/>
+      <c r="E17" s="694" t="n"/>
+      <c r="F17" s="712" t="n"/>
+      <c r="G17" s="694" t="n"/>
+      <c r="H17" s="694" t="n"/>
+      <c r="I17" s="694" t="n"/>
+      <c r="J17" s="696" t="n"/>
+      <c r="K17" s="696" t="n"/>
+      <c r="L17" s="696" t="n"/>
+      <c r="M17" s="696" t="n"/>
+      <c r="N17" s="696" t="n"/>
+      <c r="O17" s="696" t="n"/>
+      <c r="P17" s="696" t="n"/>
+      <c r="Q17" s="696" t="n"/>
+      <c r="R17" s="696" t="n"/>
+      <c r="S17" s="696" t="n"/>
+      <c r="T17" s="696" t="n"/>
+      <c r="U17" s="696" t="n"/>
+      <c r="V17" s="696" t="n"/>
+      <c r="W17" s="696" t="n"/>
+      <c r="X17" s="696" t="n"/>
+      <c r="Y17" s="696" t="n"/>
+      <c r="Z17" s="696" t="n"/>
+      <c r="AA17" s="696" t="n"/>
+      <c r="AB17" s="696" t="n"/>
+      <c r="AC17" s="696" t="n"/>
+      <c r="AD17" s="696" t="n"/>
+      <c r="AE17" s="696" t="n"/>
+      <c r="AF17" s="696" t="n"/>
+      <c r="AG17" s="696" t="n"/>
+      <c r="AH17" s="696" t="n"/>
+      <c r="AI17" s="696" t="n"/>
+      <c r="AJ17" s="696" t="n"/>
+      <c r="AK17" s="696" t="n"/>
+      <c r="AL17" s="696" t="n"/>
+      <c r="AM17" s="696" t="n"/>
+      <c r="AN17" s="697" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="605">
+      <c r="A18" s="713">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B18" s="460" t="n"/>
-      <c r="C18" s="606" t="n"/>
-      <c r="D18" s="606" t="n"/>
-      <c r="E18" s="606" t="n"/>
-      <c r="F18" s="607" t="n"/>
-      <c r="G18" s="606" t="n"/>
-      <c r="H18" s="606" t="n"/>
-      <c r="I18" s="606" t="n"/>
-      <c r="J18" s="413" t="n"/>
-      <c r="K18" s="413" t="n"/>
-      <c r="L18" s="413" t="n"/>
-      <c r="M18" s="413" t="n"/>
-      <c r="N18" s="413" t="n"/>
-      <c r="O18" s="413" t="n"/>
-      <c r="P18" s="413" t="n"/>
-      <c r="Q18" s="413" t="n"/>
-      <c r="R18" s="413" t="n"/>
-      <c r="S18" s="413" t="n"/>
-      <c r="T18" s="413" t="n"/>
-      <c r="U18" s="413" t="n"/>
-      <c r="V18" s="413" t="n"/>
-      <c r="W18" s="413" t="n"/>
-      <c r="X18" s="413" t="n"/>
-      <c r="Y18" s="413" t="n"/>
-      <c r="Z18" s="413" t="n"/>
-      <c r="AA18" s="413" t="n"/>
-      <c r="AB18" s="413" t="n"/>
-      <c r="AC18" s="413" t="n"/>
-      <c r="AD18" s="413" t="n"/>
-      <c r="AE18" s="413" t="n"/>
-      <c r="AF18" s="413" t="n"/>
-      <c r="AG18" s="413" t="n"/>
-      <c r="AH18" s="413" t="n"/>
-      <c r="AI18" s="413" t="n"/>
-      <c r="AJ18" s="413" t="n"/>
-      <c r="AK18" s="413" t="n"/>
-      <c r="AL18" s="413" t="n"/>
-      <c r="AM18" s="413" t="n"/>
-      <c r="AN18" s="595" t="n"/>
+      <c r="B18" s="714" t="n"/>
+      <c r="C18" s="714" t="n"/>
+      <c r="D18" s="714" t="n"/>
+      <c r="E18" s="714" t="n"/>
+      <c r="F18" s="715" t="n"/>
+      <c r="G18" s="714" t="n"/>
+      <c r="H18" s="714" t="n"/>
+      <c r="I18" s="714" t="n"/>
+      <c r="J18" s="701" t="n"/>
+      <c r="K18" s="701" t="n"/>
+      <c r="L18" s="701" t="n"/>
+      <c r="M18" s="701" t="n"/>
+      <c r="N18" s="701" t="n"/>
+      <c r="O18" s="701" t="n"/>
+      <c r="P18" s="701" t="n"/>
+      <c r="Q18" s="701" t="n"/>
+      <c r="R18" s="701" t="n"/>
+      <c r="S18" s="701" t="n"/>
+      <c r="T18" s="701" t="n"/>
+      <c r="U18" s="701" t="n"/>
+      <c r="V18" s="701" t="n"/>
+      <c r="W18" s="701" t="n"/>
+      <c r="X18" s="701" t="n"/>
+      <c r="Y18" s="701" t="n"/>
+      <c r="Z18" s="701" t="n"/>
+      <c r="AA18" s="701" t="n"/>
+      <c r="AB18" s="701" t="n"/>
+      <c r="AC18" s="701" t="n"/>
+      <c r="AD18" s="701" t="n"/>
+      <c r="AE18" s="701" t="n"/>
+      <c r="AF18" s="701" t="n"/>
+      <c r="AG18" s="701" t="n"/>
+      <c r="AH18" s="701" t="n"/>
+      <c r="AI18" s="701" t="n"/>
+      <c r="AJ18" s="701" t="n"/>
+      <c r="AK18" s="701" t="n"/>
+      <c r="AL18" s="701" t="n"/>
+      <c r="AM18" s="701" t="n"/>
+      <c r="AN18" s="702" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="605">
+      <c r="A19" s="713">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B19" s="592" t="n"/>
-      <c r="C19" s="608" t="n"/>
-      <c r="D19" s="608" t="n"/>
-      <c r="E19" s="608" t="n"/>
-      <c r="F19" s="609" t="n"/>
-      <c r="G19" s="608" t="n"/>
-      <c r="H19" s="608" t="n"/>
-      <c r="I19" s="608" t="n"/>
-      <c r="J19" s="413" t="n"/>
-      <c r="K19" s="413" t="n"/>
-      <c r="L19" s="413" t="n"/>
-      <c r="M19" s="413" t="n"/>
-      <c r="N19" s="413" t="n"/>
-      <c r="O19" s="413" t="n"/>
-      <c r="P19" s="413" t="n"/>
-      <c r="Q19" s="413" t="n"/>
-      <c r="R19" s="413" t="n"/>
-      <c r="S19" s="413" t="n"/>
-      <c r="T19" s="413" t="n"/>
-      <c r="U19" s="413" t="n"/>
-      <c r="V19" s="413" t="n"/>
-      <c r="W19" s="413" t="n"/>
-      <c r="X19" s="413" t="n"/>
-      <c r="Y19" s="413" t="n"/>
-      <c r="Z19" s="413" t="n"/>
-      <c r="AA19" s="413" t="n"/>
-      <c r="AB19" s="413" t="n"/>
-      <c r="AC19" s="413" t="n"/>
-      <c r="AD19" s="413" t="n"/>
-      <c r="AE19" s="413" t="n"/>
-      <c r="AF19" s="413" t="n"/>
-      <c r="AG19" s="413" t="n"/>
-      <c r="AH19" s="413" t="n"/>
-      <c r="AI19" s="413" t="n"/>
-      <c r="AJ19" s="413" t="n"/>
-      <c r="AK19" s="413" t="n"/>
-      <c r="AL19" s="413" t="n"/>
-      <c r="AM19" s="413" t="n"/>
-      <c r="AN19" s="595" t="n"/>
+      <c r="B19" s="699" t="n"/>
+      <c r="C19" s="699" t="n"/>
+      <c r="D19" s="699" t="n"/>
+      <c r="E19" s="699" t="n"/>
+      <c r="F19" s="716" t="n"/>
+      <c r="G19" s="699" t="n"/>
+      <c r="H19" s="699" t="n"/>
+      <c r="I19" s="699" t="n"/>
+      <c r="J19" s="701" t="n"/>
+      <c r="K19" s="701" t="n"/>
+      <c r="L19" s="701" t="n"/>
+      <c r="M19" s="701" t="n"/>
+      <c r="N19" s="701" t="n"/>
+      <c r="O19" s="701" t="n"/>
+      <c r="P19" s="701" t="n"/>
+      <c r="Q19" s="701" t="n"/>
+      <c r="R19" s="701" t="n"/>
+      <c r="S19" s="701" t="n"/>
+      <c r="T19" s="701" t="n"/>
+      <c r="U19" s="701" t="n"/>
+      <c r="V19" s="701" t="n"/>
+      <c r="W19" s="701" t="n"/>
+      <c r="X19" s="701" t="n"/>
+      <c r="Y19" s="701" t="n"/>
+      <c r="Z19" s="701" t="n"/>
+      <c r="AA19" s="701" t="n"/>
+      <c r="AB19" s="701" t="n"/>
+      <c r="AC19" s="701" t="n"/>
+      <c r="AD19" s="701" t="n"/>
+      <c r="AE19" s="701" t="n"/>
+      <c r="AF19" s="701" t="n"/>
+      <c r="AG19" s="701" t="n"/>
+      <c r="AH19" s="701" t="n"/>
+      <c r="AI19" s="701" t="n"/>
+      <c r="AJ19" s="701" t="n"/>
+      <c r="AK19" s="701" t="n"/>
+      <c r="AL19" s="701" t="n"/>
+      <c r="AM19" s="701" t="n"/>
+      <c r="AN19" s="702" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="605">
+      <c r="A20" s="713">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B20" s="460" t="n"/>
-      <c r="C20" s="606" t="n"/>
-      <c r="D20" s="606" t="n"/>
-      <c r="E20" s="606" t="n"/>
-      <c r="F20" s="607" t="n"/>
-      <c r="G20" s="606" t="n"/>
-      <c r="H20" s="606" t="n"/>
-      <c r="I20" s="606" t="n"/>
-      <c r="J20" s="413" t="n"/>
-      <c r="K20" s="413" t="n"/>
-      <c r="L20" s="413" t="n"/>
-      <c r="M20" s="413" t="n"/>
-      <c r="N20" s="413" t="n"/>
-      <c r="O20" s="413" t="n"/>
-      <c r="P20" s="413" t="n"/>
-      <c r="Q20" s="413" t="n"/>
-      <c r="R20" s="413" t="n"/>
-      <c r="S20" s="413" t="n"/>
-      <c r="T20" s="413" t="n"/>
-      <c r="U20" s="413" t="n"/>
-      <c r="V20" s="413" t="n"/>
-      <c r="W20" s="413" t="n"/>
-      <c r="X20" s="413" t="n"/>
-      <c r="Y20" s="413" t="n"/>
-      <c r="Z20" s="413" t="n"/>
-      <c r="AA20" s="413" t="n"/>
-      <c r="AB20" s="413" t="n"/>
-      <c r="AC20" s="413" t="n"/>
-      <c r="AD20" s="413" t="n"/>
-      <c r="AE20" s="413" t="n"/>
-      <c r="AF20" s="413" t="n"/>
-      <c r="AG20" s="413" t="n"/>
-      <c r="AH20" s="413" t="n"/>
-      <c r="AI20" s="413" t="n"/>
-      <c r="AJ20" s="413" t="n"/>
-      <c r="AK20" s="413" t="n"/>
-      <c r="AL20" s="413" t="n"/>
-      <c r="AM20" s="413" t="n"/>
-      <c r="AN20" s="595" t="n"/>
+      <c r="B20" s="714" t="n"/>
+      <c r="C20" s="714" t="n"/>
+      <c r="D20" s="714" t="n"/>
+      <c r="E20" s="714" t="n"/>
+      <c r="F20" s="715" t="n"/>
+      <c r="G20" s="714" t="n"/>
+      <c r="H20" s="714" t="n"/>
+      <c r="I20" s="714" t="n"/>
+      <c r="J20" s="701" t="n"/>
+      <c r="K20" s="701" t="n"/>
+      <c r="L20" s="701" t="n"/>
+      <c r="M20" s="701" t="n"/>
+      <c r="N20" s="701" t="n"/>
+      <c r="O20" s="701" t="n"/>
+      <c r="P20" s="701" t="n"/>
+      <c r="Q20" s="701" t="n"/>
+      <c r="R20" s="701" t="n"/>
+      <c r="S20" s="701" t="n"/>
+      <c r="T20" s="701" t="n"/>
+      <c r="U20" s="701" t="n"/>
+      <c r="V20" s="701" t="n"/>
+      <c r="W20" s="701" t="n"/>
+      <c r="X20" s="701" t="n"/>
+      <c r="Y20" s="701" t="n"/>
+      <c r="Z20" s="701" t="n"/>
+      <c r="AA20" s="701" t="n"/>
+      <c r="AB20" s="701" t="n"/>
+      <c r="AC20" s="701" t="n"/>
+      <c r="AD20" s="701" t="n"/>
+      <c r="AE20" s="701" t="n"/>
+      <c r="AF20" s="701" t="n"/>
+      <c r="AG20" s="701" t="n"/>
+      <c r="AH20" s="701" t="n"/>
+      <c r="AI20" s="701" t="n"/>
+      <c r="AJ20" s="701" t="n"/>
+      <c r="AK20" s="701" t="n"/>
+      <c r="AL20" s="701" t="n"/>
+      <c r="AM20" s="701" t="n"/>
+      <c r="AN20" s="702" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="605">
+      <c r="A21" s="713">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B21" s="592" t="n"/>
-      <c r="C21" s="608" t="n"/>
-      <c r="D21" s="608" t="n"/>
-      <c r="E21" s="608" t="n"/>
-      <c r="F21" s="609" t="n"/>
-      <c r="G21" s="608" t="n"/>
-      <c r="H21" s="608" t="n"/>
-      <c r="I21" s="608" t="n"/>
-      <c r="J21" s="413" t="n"/>
-      <c r="K21" s="413" t="n"/>
-      <c r="L21" s="413" t="n"/>
-      <c r="M21" s="413" t="n"/>
-      <c r="N21" s="413" t="n"/>
-      <c r="O21" s="413" t="n"/>
-      <c r="P21" s="413" t="n"/>
-      <c r="Q21" s="413" t="n"/>
-      <c r="R21" s="413" t="n"/>
-      <c r="S21" s="413" t="n"/>
-      <c r="T21" s="413" t="n"/>
-      <c r="U21" s="413" t="n"/>
-      <c r="V21" s="413" t="n"/>
-      <c r="W21" s="413" t="n"/>
-      <c r="X21" s="413" t="n"/>
-      <c r="Y21" s="413" t="n"/>
-      <c r="Z21" s="413" t="n"/>
-      <c r="AA21" s="413" t="n"/>
-      <c r="AB21" s="413" t="n"/>
-      <c r="AC21" s="413" t="n"/>
-      <c r="AD21" s="413" t="n"/>
-      <c r="AE21" s="413" t="n"/>
-      <c r="AF21" s="413" t="n"/>
-      <c r="AG21" s="413" t="n"/>
-      <c r="AH21" s="413" t="n"/>
-      <c r="AI21" s="413" t="n"/>
-      <c r="AJ21" s="413" t="n"/>
-      <c r="AK21" s="413" t="n"/>
-      <c r="AL21" s="413" t="n"/>
-      <c r="AM21" s="413" t="n"/>
-      <c r="AN21" s="595" t="n"/>
+      <c r="B21" s="699" t="n"/>
+      <c r="C21" s="699" t="n"/>
+      <c r="D21" s="699" t="n"/>
+      <c r="E21" s="699" t="n"/>
+      <c r="F21" s="716" t="n"/>
+      <c r="G21" s="699" t="n"/>
+      <c r="H21" s="699" t="n"/>
+      <c r="I21" s="699" t="n"/>
+      <c r="J21" s="701" t="n"/>
+      <c r="K21" s="701" t="n"/>
+      <c r="L21" s="701" t="n"/>
+      <c r="M21" s="701" t="n"/>
+      <c r="N21" s="701" t="n"/>
+      <c r="O21" s="701" t="n"/>
+      <c r="P21" s="701" t="n"/>
+      <c r="Q21" s="701" t="n"/>
+      <c r="R21" s="701" t="n"/>
+      <c r="S21" s="701" t="n"/>
+      <c r="T21" s="701" t="n"/>
+      <c r="U21" s="701" t="n"/>
+      <c r="V21" s="701" t="n"/>
+      <c r="W21" s="701" t="n"/>
+      <c r="X21" s="701" t="n"/>
+      <c r="Y21" s="701" t="n"/>
+      <c r="Z21" s="701" t="n"/>
+      <c r="AA21" s="701" t="n"/>
+      <c r="AB21" s="701" t="n"/>
+      <c r="AC21" s="701" t="n"/>
+      <c r="AD21" s="701" t="n"/>
+      <c r="AE21" s="701" t="n"/>
+      <c r="AF21" s="701" t="n"/>
+      <c r="AG21" s="701" t="n"/>
+      <c r="AH21" s="701" t="n"/>
+      <c r="AI21" s="701" t="n"/>
+      <c r="AJ21" s="701" t="n"/>
+      <c r="AK21" s="701" t="n"/>
+      <c r="AL21" s="701" t="n"/>
+      <c r="AM21" s="701" t="n"/>
+      <c r="AN21" s="702" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="605">
+      <c r="A22" s="713">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B22" s="460" t="n"/>
-      <c r="C22" s="606" t="n"/>
-      <c r="D22" s="606" t="n"/>
-      <c r="E22" s="606" t="n"/>
-      <c r="F22" s="607" t="n"/>
-      <c r="G22" s="606" t="n"/>
-      <c r="H22" s="606" t="n"/>
-      <c r="I22" s="606" t="n"/>
-      <c r="J22" s="413" t="n"/>
-      <c r="K22" s="413" t="n"/>
-      <c r="L22" s="413" t="n"/>
-      <c r="M22" s="413" t="n"/>
-      <c r="N22" s="413" t="n"/>
-      <c r="O22" s="413" t="n"/>
-      <c r="P22" s="413" t="n"/>
-      <c r="Q22" s="413" t="n"/>
-      <c r="R22" s="413" t="n"/>
-      <c r="S22" s="413" t="n"/>
-      <c r="T22" s="413" t="n"/>
-      <c r="U22" s="413" t="n"/>
-      <c r="V22" s="413" t="n"/>
-      <c r="W22" s="413" t="n"/>
-      <c r="X22" s="413" t="n"/>
-      <c r="Y22" s="413" t="n"/>
-      <c r="Z22" s="413" t="n"/>
-      <c r="AA22" s="413" t="n"/>
-      <c r="AB22" s="413" t="n"/>
-      <c r="AC22" s="413" t="n"/>
-      <c r="AD22" s="413" t="n"/>
-      <c r="AE22" s="413" t="n"/>
-      <c r="AF22" s="413" t="n"/>
-      <c r="AG22" s="413" t="n"/>
-      <c r="AH22" s="413" t="n"/>
-      <c r="AI22" s="413" t="n"/>
-      <c r="AJ22" s="413" t="n"/>
-      <c r="AK22" s="413" t="n"/>
-      <c r="AL22" s="413" t="n"/>
-      <c r="AM22" s="413" t="n"/>
-      <c r="AN22" s="595" t="n"/>
+      <c r="B22" s="714" t="n"/>
+      <c r="C22" s="714" t="n"/>
+      <c r="D22" s="714" t="n"/>
+      <c r="E22" s="714" t="n"/>
+      <c r="F22" s="715" t="n"/>
+      <c r="G22" s="714" t="n"/>
+      <c r="H22" s="714" t="n"/>
+      <c r="I22" s="714" t="n"/>
+      <c r="J22" s="701" t="n"/>
+      <c r="K22" s="701" t="n"/>
+      <c r="L22" s="701" t="n"/>
+      <c r="M22" s="701" t="n"/>
+      <c r="N22" s="701" t="n"/>
+      <c r="O22" s="701" t="n"/>
+      <c r="P22" s="701" t="n"/>
+      <c r="Q22" s="701" t="n"/>
+      <c r="R22" s="701" t="n"/>
+      <c r="S22" s="701" t="n"/>
+      <c r="T22" s="701" t="n"/>
+      <c r="U22" s="701" t="n"/>
+      <c r="V22" s="701" t="n"/>
+      <c r="W22" s="701" t="n"/>
+      <c r="X22" s="701" t="n"/>
+      <c r="Y22" s="701" t="n"/>
+      <c r="Z22" s="701" t="n"/>
+      <c r="AA22" s="701" t="n"/>
+      <c r="AB22" s="701" t="n"/>
+      <c r="AC22" s="701" t="n"/>
+      <c r="AD22" s="701" t="n"/>
+      <c r="AE22" s="701" t="n"/>
+      <c r="AF22" s="701" t="n"/>
+      <c r="AG22" s="701" t="n"/>
+      <c r="AH22" s="701" t="n"/>
+      <c r="AI22" s="701" t="n"/>
+      <c r="AJ22" s="701" t="n"/>
+      <c r="AK22" s="701" t="n"/>
+      <c r="AL22" s="701" t="n"/>
+      <c r="AM22" s="701" t="n"/>
+      <c r="AN22" s="702" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="605">
+      <c r="A23" s="713">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B23" s="592" t="n"/>
-      <c r="C23" s="608" t="n"/>
-      <c r="D23" s="608" t="n"/>
-      <c r="E23" s="608" t="n"/>
-      <c r="F23" s="609" t="n"/>
-      <c r="G23" s="608" t="n"/>
-      <c r="H23" s="608" t="n"/>
-      <c r="I23" s="608" t="n"/>
-      <c r="J23" s="413" t="n"/>
-      <c r="K23" s="413" t="n"/>
-      <c r="L23" s="413" t="n"/>
-      <c r="M23" s="413" t="n"/>
-      <c r="N23" s="413" t="n"/>
-      <c r="O23" s="413" t="n"/>
-      <c r="P23" s="413" t="n"/>
-      <c r="Q23" s="413" t="n"/>
-      <c r="R23" s="413" t="n"/>
-      <c r="S23" s="413" t="n"/>
-      <c r="T23" s="413" t="n"/>
-      <c r="U23" s="413" t="n"/>
-      <c r="V23" s="413" t="n"/>
-      <c r="W23" s="413" t="n"/>
-      <c r="X23" s="413" t="n"/>
-      <c r="Y23" s="413" t="n"/>
-      <c r="Z23" s="413" t="n"/>
-      <c r="AA23" s="413" t="n"/>
-      <c r="AB23" s="413" t="n"/>
-      <c r="AC23" s="413" t="n"/>
-      <c r="AD23" s="413" t="n"/>
-      <c r="AE23" s="413" t="n"/>
-      <c r="AF23" s="413" t="n"/>
-      <c r="AG23" s="413" t="n"/>
-      <c r="AH23" s="413" t="n"/>
-      <c r="AI23" s="413" t="n"/>
-      <c r="AJ23" s="413" t="n"/>
-      <c r="AK23" s="413" t="n"/>
-      <c r="AL23" s="413" t="n"/>
-      <c r="AM23" s="413" t="n"/>
-      <c r="AN23" s="595" t="n"/>
+      <c r="B23" s="699" t="n"/>
+      <c r="C23" s="699" t="n"/>
+      <c r="D23" s="699" t="n"/>
+      <c r="E23" s="699" t="n"/>
+      <c r="F23" s="716" t="n"/>
+      <c r="G23" s="699" t="n"/>
+      <c r="H23" s="699" t="n"/>
+      <c r="I23" s="699" t="n"/>
+      <c r="J23" s="701" t="n"/>
+      <c r="K23" s="701" t="n"/>
+      <c r="L23" s="701" t="n"/>
+      <c r="M23" s="701" t="n"/>
+      <c r="N23" s="701" t="n"/>
+      <c r="O23" s="701" t="n"/>
+      <c r="P23" s="701" t="n"/>
+      <c r="Q23" s="701" t="n"/>
+      <c r="R23" s="701" t="n"/>
+      <c r="S23" s="701" t="n"/>
+      <c r="T23" s="701" t="n"/>
+      <c r="U23" s="701" t="n"/>
+      <c r="V23" s="701" t="n"/>
+      <c r="W23" s="701" t="n"/>
+      <c r="X23" s="701" t="n"/>
+      <c r="Y23" s="701" t="n"/>
+      <c r="Z23" s="701" t="n"/>
+      <c r="AA23" s="701" t="n"/>
+      <c r="AB23" s="701" t="n"/>
+      <c r="AC23" s="701" t="n"/>
+      <c r="AD23" s="701" t="n"/>
+      <c r="AE23" s="701" t="n"/>
+      <c r="AF23" s="701" t="n"/>
+      <c r="AG23" s="701" t="n"/>
+      <c r="AH23" s="701" t="n"/>
+      <c r="AI23" s="701" t="n"/>
+      <c r="AJ23" s="701" t="n"/>
+      <c r="AK23" s="701" t="n"/>
+      <c r="AL23" s="701" t="n"/>
+      <c r="AM23" s="701" t="n"/>
+      <c r="AN23" s="702" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="605">
+      <c r="A24" s="713">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B24" s="460" t="n"/>
-      <c r="C24" s="606" t="n"/>
-      <c r="D24" s="606" t="n"/>
-      <c r="E24" s="606" t="n"/>
-      <c r="F24" s="607" t="n"/>
-      <c r="G24" s="606" t="n"/>
-      <c r="H24" s="606" t="n"/>
-      <c r="I24" s="606" t="n"/>
-      <c r="J24" s="413" t="n"/>
-      <c r="K24" s="413" t="n"/>
-      <c r="L24" s="413" t="n"/>
-      <c r="M24" s="413" t="n"/>
-      <c r="N24" s="413" t="n"/>
-      <c r="O24" s="413" t="n"/>
-      <c r="P24" s="413" t="n"/>
-      <c r="Q24" s="413" t="n"/>
-      <c r="R24" s="413" t="n"/>
-      <c r="S24" s="413" t="n"/>
-      <c r="T24" s="413" t="n"/>
-      <c r="U24" s="413" t="n"/>
-      <c r="V24" s="413" t="n"/>
-      <c r="W24" s="413" t="n"/>
-      <c r="X24" s="413" t="n"/>
-      <c r="Y24" s="413" t="n"/>
-      <c r="Z24" s="413" t="n"/>
-      <c r="AA24" s="413" t="n"/>
-      <c r="AB24" s="413" t="n"/>
-      <c r="AC24" s="413" t="n"/>
-      <c r="AD24" s="413" t="n"/>
-      <c r="AE24" s="413" t="n"/>
-      <c r="AF24" s="413" t="n"/>
-      <c r="AG24" s="413" t="n"/>
-      <c r="AH24" s="413" t="n"/>
-      <c r="AI24" s="413" t="n"/>
-      <c r="AJ24" s="413" t="n"/>
-      <c r="AK24" s="413" t="n"/>
-      <c r="AL24" s="413" t="n"/>
-      <c r="AM24" s="413" t="n"/>
-      <c r="AN24" s="595" t="n"/>
+      <c r="B24" s="714" t="n"/>
+      <c r="C24" s="714" t="n"/>
+      <c r="D24" s="714" t="n"/>
+      <c r="E24" s="714" t="n"/>
+      <c r="F24" s="715" t="n"/>
+      <c r="G24" s="714" t="n"/>
+      <c r="H24" s="714" t="n"/>
+      <c r="I24" s="714" t="n"/>
+      <c r="J24" s="701" t="n"/>
+      <c r="K24" s="701" t="n"/>
+      <c r="L24" s="701" t="n"/>
+      <c r="M24" s="701" t="n"/>
+      <c r="N24" s="701" t="n"/>
+      <c r="O24" s="701" t="n"/>
+      <c r="P24" s="701" t="n"/>
+      <c r="Q24" s="701" t="n"/>
+      <c r="R24" s="701" t="n"/>
+      <c r="S24" s="701" t="n"/>
+      <c r="T24" s="701" t="n"/>
+      <c r="U24" s="701" t="n"/>
+      <c r="V24" s="701" t="n"/>
+      <c r="W24" s="701" t="n"/>
+      <c r="X24" s="701" t="n"/>
+      <c r="Y24" s="701" t="n"/>
+      <c r="Z24" s="701" t="n"/>
+      <c r="AA24" s="701" t="n"/>
+      <c r="AB24" s="701" t="n"/>
+      <c r="AC24" s="701" t="n"/>
+      <c r="AD24" s="701" t="n"/>
+      <c r="AE24" s="701" t="n"/>
+      <c r="AF24" s="701" t="n"/>
+      <c r="AG24" s="701" t="n"/>
+      <c r="AH24" s="701" t="n"/>
+      <c r="AI24" s="701" t="n"/>
+      <c r="AJ24" s="701" t="n"/>
+      <c r="AK24" s="701" t="n"/>
+      <c r="AL24" s="701" t="n"/>
+      <c r="AM24" s="701" t="n"/>
+      <c r="AN24" s="702" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="605">
+      <c r="A25" s="713">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B25" s="592" t="n"/>
-      <c r="C25" s="608" t="n"/>
-      <c r="D25" s="608" t="n"/>
-      <c r="E25" s="608" t="n"/>
-      <c r="F25" s="609" t="n"/>
-      <c r="G25" s="608" t="n"/>
-      <c r="H25" s="608" t="n"/>
-      <c r="I25" s="608" t="n"/>
-      <c r="J25" s="413" t="n"/>
-      <c r="K25" s="413" t="n"/>
-      <c r="L25" s="413" t="n"/>
-      <c r="M25" s="413" t="n"/>
-      <c r="N25" s="413" t="n"/>
-      <c r="O25" s="413" t="n"/>
-      <c r="P25" s="413" t="n"/>
-      <c r="Q25" s="413" t="n"/>
-      <c r="R25" s="413" t="n"/>
-      <c r="S25" s="413" t="n"/>
-      <c r="T25" s="413" t="n"/>
-      <c r="U25" s="413" t="n"/>
-      <c r="V25" s="413" t="n"/>
-      <c r="W25" s="413" t="n"/>
-      <c r="X25" s="413" t="n"/>
-      <c r="Y25" s="413" t="n"/>
-      <c r="Z25" s="413" t="n"/>
-      <c r="AA25" s="413" t="n"/>
-      <c r="AB25" s="413" t="n"/>
-      <c r="AC25" s="413" t="n"/>
-      <c r="AD25" s="413" t="n"/>
-      <c r="AE25" s="413" t="n"/>
-      <c r="AF25" s="413" t="n"/>
-      <c r="AG25" s="413" t="n"/>
-      <c r="AH25" s="413" t="n"/>
-      <c r="AI25" s="413" t="n"/>
-      <c r="AJ25" s="413" t="n"/>
-      <c r="AK25" s="413" t="n"/>
-      <c r="AL25" s="413" t="n"/>
-      <c r="AM25" s="413" t="n"/>
-      <c r="AN25" s="595" t="n"/>
+      <c r="B25" s="699" t="n"/>
+      <c r="C25" s="699" t="n"/>
+      <c r="D25" s="699" t="n"/>
+      <c r="E25" s="699" t="n"/>
+      <c r="F25" s="716" t="n"/>
+      <c r="G25" s="699" t="n"/>
+      <c r="H25" s="699" t="n"/>
+      <c r="I25" s="699" t="n"/>
+      <c r="J25" s="701" t="n"/>
+      <c r="K25" s="701" t="n"/>
+      <c r="L25" s="701" t="n"/>
+      <c r="M25" s="701" t="n"/>
+      <c r="N25" s="701" t="n"/>
+      <c r="O25" s="701" t="n"/>
+      <c r="P25" s="701" t="n"/>
+      <c r="Q25" s="701" t="n"/>
+      <c r="R25" s="701" t="n"/>
+      <c r="S25" s="701" t="n"/>
+      <c r="T25" s="701" t="n"/>
+      <c r="U25" s="701" t="n"/>
+      <c r="V25" s="701" t="n"/>
+      <c r="W25" s="701" t="n"/>
+      <c r="X25" s="701" t="n"/>
+      <c r="Y25" s="701" t="n"/>
+      <c r="Z25" s="701" t="n"/>
+      <c r="AA25" s="701" t="n"/>
+      <c r="AB25" s="701" t="n"/>
+      <c r="AC25" s="701" t="n"/>
+      <c r="AD25" s="701" t="n"/>
+      <c r="AE25" s="701" t="n"/>
+      <c r="AF25" s="701" t="n"/>
+      <c r="AG25" s="701" t="n"/>
+      <c r="AH25" s="701" t="n"/>
+      <c r="AI25" s="701" t="n"/>
+      <c r="AJ25" s="701" t="n"/>
+      <c r="AK25" s="701" t="n"/>
+      <c r="AL25" s="701" t="n"/>
+      <c r="AM25" s="701" t="n"/>
+      <c r="AN25" s="702" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="605">
+      <c r="A26" s="713">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B26" s="460" t="n"/>
-      <c r="C26" s="606" t="n"/>
-      <c r="D26" s="606" t="n"/>
-      <c r="E26" s="606" t="n"/>
-      <c r="F26" s="607" t="n"/>
-      <c r="G26" s="606" t="n"/>
-      <c r="H26" s="606" t="n"/>
-      <c r="I26" s="606" t="n"/>
-      <c r="J26" s="413" t="n"/>
-      <c r="K26" s="413" t="n"/>
-      <c r="L26" s="413" t="n"/>
-      <c r="M26" s="413" t="n"/>
-      <c r="N26" s="413" t="n"/>
-      <c r="O26" s="413" t="n"/>
-      <c r="P26" s="413" t="n"/>
-      <c r="Q26" s="413" t="n"/>
-      <c r="R26" s="413" t="n"/>
-      <c r="S26" s="413" t="n"/>
-      <c r="T26" s="413" t="n"/>
-      <c r="U26" s="413" t="n"/>
-      <c r="V26" s="413" t="n"/>
-      <c r="W26" s="413" t="n"/>
-      <c r="X26" s="413" t="n"/>
-      <c r="Y26" s="413" t="n"/>
-      <c r="Z26" s="413" t="n"/>
-      <c r="AA26" s="413" t="n"/>
-      <c r="AB26" s="413" t="n"/>
-      <c r="AC26" s="413" t="n"/>
-      <c r="AD26" s="413" t="n"/>
-      <c r="AE26" s="413" t="n"/>
-      <c r="AF26" s="413" t="n"/>
-      <c r="AG26" s="413" t="n"/>
-      <c r="AH26" s="413" t="n"/>
-      <c r="AI26" s="413" t="n"/>
-      <c r="AJ26" s="413" t="n"/>
-      <c r="AK26" s="413" t="n"/>
-      <c r="AL26" s="413" t="n"/>
-      <c r="AM26" s="413" t="n"/>
-      <c r="AN26" s="595" t="n"/>
+      <c r="B26" s="714" t="n"/>
+      <c r="C26" s="714" t="n"/>
+      <c r="D26" s="714" t="n"/>
+      <c r="E26" s="714" t="n"/>
+      <c r="F26" s="715" t="n"/>
+      <c r="G26" s="714" t="n"/>
+      <c r="H26" s="714" t="n"/>
+      <c r="I26" s="714" t="n"/>
+      <c r="J26" s="701" t="n"/>
+      <c r="K26" s="701" t="n"/>
+      <c r="L26" s="701" t="n"/>
+      <c r="M26" s="701" t="n"/>
+      <c r="N26" s="701" t="n"/>
+      <c r="O26" s="701" t="n"/>
+      <c r="P26" s="701" t="n"/>
+      <c r="Q26" s="701" t="n"/>
+      <c r="R26" s="701" t="n"/>
+      <c r="S26" s="701" t="n"/>
+      <c r="T26" s="701" t="n"/>
+      <c r="U26" s="701" t="n"/>
+      <c r="V26" s="701" t="n"/>
+      <c r="W26" s="701" t="n"/>
+      <c r="X26" s="701" t="n"/>
+      <c r="Y26" s="701" t="n"/>
+      <c r="Z26" s="701" t="n"/>
+      <c r="AA26" s="701" t="n"/>
+      <c r="AB26" s="701" t="n"/>
+      <c r="AC26" s="701" t="n"/>
+      <c r="AD26" s="701" t="n"/>
+      <c r="AE26" s="701" t="n"/>
+      <c r="AF26" s="701" t="n"/>
+      <c r="AG26" s="701" t="n"/>
+      <c r="AH26" s="701" t="n"/>
+      <c r="AI26" s="701" t="n"/>
+      <c r="AJ26" s="701" t="n"/>
+      <c r="AK26" s="701" t="n"/>
+      <c r="AL26" s="701" t="n"/>
+      <c r="AM26" s="701" t="n"/>
+      <c r="AN26" s="702" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="610" t="n"/>
-      <c r="B27" s="599" t="n"/>
-      <c r="C27" s="600" t="n"/>
-      <c r="D27" s="600" t="n"/>
-      <c r="E27" s="600" t="n"/>
-      <c r="F27" s="600" t="n"/>
-      <c r="G27" s="600" t="n"/>
-      <c r="H27" s="600" t="n"/>
-      <c r="I27" s="600" t="n"/>
-      <c r="J27" s="600" t="n"/>
-      <c r="K27" s="600" t="n"/>
-      <c r="L27" s="600" t="n"/>
-      <c r="M27" s="600" t="n"/>
-      <c r="N27" s="600" t="n"/>
-      <c r="O27" s="600" t="n"/>
-      <c r="P27" s="600" t="n"/>
-      <c r="Q27" s="600" t="n"/>
-      <c r="R27" s="600" t="n"/>
-      <c r="S27" s="600" t="n"/>
-      <c r="T27" s="600" t="n"/>
-      <c r="U27" s="600" t="n"/>
-      <c r="V27" s="600" t="n"/>
-      <c r="W27" s="600" t="n"/>
-      <c r="X27" s="600" t="n"/>
-      <c r="Y27" s="600" t="n"/>
-      <c r="Z27" s="600" t="n"/>
-      <c r="AA27" s="600" t="n"/>
-      <c r="AB27" s="600" t="n"/>
-      <c r="AC27" s="600" t="n"/>
-      <c r="AD27" s="600" t="n"/>
-      <c r="AE27" s="600" t="n"/>
-      <c r="AF27" s="600" t="n"/>
-      <c r="AG27" s="600" t="n"/>
-      <c r="AH27" s="600" t="n"/>
-      <c r="AI27" s="600" t="n"/>
-      <c r="AJ27" s="600" t="n"/>
-      <c r="AK27" s="600" t="n"/>
-      <c r="AL27" s="600" t="n"/>
-      <c r="AM27" s="600" t="n"/>
-      <c r="AN27" s="601" t="n"/>
+      <c r="A27" s="717" t="n"/>
+      <c r="B27" s="708" t="n"/>
+      <c r="C27" s="708" t="n"/>
+      <c r="D27" s="708" t="n"/>
+      <c r="E27" s="708" t="n"/>
+      <c r="F27" s="708" t="n"/>
+      <c r="G27" s="708" t="n"/>
+      <c r="H27" s="708" t="n"/>
+      <c r="I27" s="708" t="n"/>
+      <c r="J27" s="708" t="n"/>
+      <c r="K27" s="708" t="n"/>
+      <c r="L27" s="708" t="n"/>
+      <c r="M27" s="708" t="n"/>
+      <c r="N27" s="708" t="n"/>
+      <c r="O27" s="708" t="n"/>
+      <c r="P27" s="708" t="n"/>
+      <c r="Q27" s="708" t="n"/>
+      <c r="R27" s="708" t="n"/>
+      <c r="S27" s="708" t="n"/>
+      <c r="T27" s="708" t="n"/>
+      <c r="U27" s="708" t="n"/>
+      <c r="V27" s="708" t="n"/>
+      <c r="W27" s="708" t="n"/>
+      <c r="X27" s="708" t="n"/>
+      <c r="Y27" s="708" t="n"/>
+      <c r="Z27" s="708" t="n"/>
+      <c r="AA27" s="708" t="n"/>
+      <c r="AB27" s="708" t="n"/>
+      <c r="AC27" s="708" t="n"/>
+      <c r="AD27" s="708" t="n"/>
+      <c r="AE27" s="708" t="n"/>
+      <c r="AF27" s="708" t="n"/>
+      <c r="AG27" s="708" t="n"/>
+      <c r="AH27" s="708" t="n"/>
+      <c r="AI27" s="708" t="n"/>
+      <c r="AJ27" s="708" t="n"/>
+      <c r="AK27" s="708" t="n"/>
+      <c r="AL27" s="708" t="n"/>
+      <c r="AM27" s="708" t="n"/>
+      <c r="AN27" s="709" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="531" t="inlineStr">
+      <c r="A28" s="647" t="inlineStr">
         <is>
           <t>NOTICE  —  One line per material, capacity, quality or customer-risk condition.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B28" s="532" t="n"/>
-      <c r="C28" s="532" t="n"/>
-      <c r="D28" s="532" t="n"/>
-      <c r="E28" s="532" t="n"/>
-      <c r="F28" s="532" t="n"/>
-      <c r="G28" s="532" t="n"/>
-      <c r="H28" s="532" t="n"/>
-      <c r="I28" s="532" t="n"/>
-      <c r="J28" s="532" t="n"/>
-      <c r="K28" s="532" t="n"/>
-      <c r="L28" s="532" t="n"/>
-      <c r="M28" s="532" t="n"/>
-      <c r="N28" s="532" t="n"/>
-      <c r="O28" s="532" t="n"/>
-      <c r="P28" s="532" t="n"/>
-      <c r="Q28" s="532" t="n"/>
-      <c r="R28" s="532" t="n"/>
-      <c r="S28" s="532" t="n"/>
-      <c r="T28" s="532" t="n"/>
-      <c r="U28" s="532" t="n"/>
-      <c r="V28" s="532" t="n"/>
-      <c r="W28" s="532" t="n"/>
-      <c r="X28" s="532" t="n"/>
-      <c r="Y28" s="532" t="n"/>
-      <c r="Z28" s="532" t="n"/>
-      <c r="AA28" s="532" t="n"/>
-      <c r="AB28" s="532" t="n"/>
-      <c r="AC28" s="532" t="n"/>
-      <c r="AD28" s="532" t="n"/>
-      <c r="AE28" s="532" t="n"/>
-      <c r="AF28" s="532" t="n"/>
-      <c r="AG28" s="532" t="n"/>
-      <c r="AH28" s="532" t="n"/>
-      <c r="AI28" s="532" t="n"/>
-      <c r="AJ28" s="532" t="n"/>
-      <c r="AK28" s="532" t="n"/>
-      <c r="AL28" s="532" t="n"/>
-      <c r="AM28" s="532" t="n"/>
-      <c r="AN28" s="533" t="n"/>
+      <c r="B28" s="27" t="n"/>
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="27" t="n"/>
+      <c r="E28" s="27" t="n"/>
+      <c r="F28" s="27" t="n"/>
+      <c r="G28" s="27" t="n"/>
+      <c r="H28" s="27" t="n"/>
+      <c r="I28" s="27" t="n"/>
+      <c r="J28" s="691" t="n"/>
+      <c r="K28" s="691" t="n"/>
+      <c r="L28" s="691" t="n"/>
+      <c r="M28" s="691" t="n"/>
+      <c r="N28" s="691" t="n"/>
+      <c r="O28" s="691" t="n"/>
+      <c r="P28" s="691" t="n"/>
+      <c r="Q28" s="691" t="n"/>
+      <c r="R28" s="691" t="n"/>
+      <c r="S28" s="691" t="n"/>
+      <c r="T28" s="691" t="n"/>
+      <c r="U28" s="691" t="n"/>
+      <c r="V28" s="691" t="n"/>
+      <c r="W28" s="691" t="n"/>
+      <c r="X28" s="691" t="n"/>
+      <c r="Y28" s="691" t="n"/>
+      <c r="Z28" s="691" t="n"/>
+      <c r="AA28" s="691" t="n"/>
+      <c r="AB28" s="691" t="n"/>
+      <c r="AC28" s="691" t="n"/>
+      <c r="AD28" s="691" t="n"/>
+      <c r="AE28" s="691" t="n"/>
+      <c r="AF28" s="691" t="n"/>
+      <c r="AG28" s="691" t="n"/>
+      <c r="AH28" s="691" t="n"/>
+      <c r="AI28" s="691" t="n"/>
+      <c r="AJ28" s="691" t="n"/>
+      <c r="AK28" s="691" t="n"/>
+      <c r="AL28" s="691" t="n"/>
+      <c r="AM28" s="691" t="n"/>
+      <c r="AN28" s="692" t="n"/>
     </row>
     <row r="29" hidden="1" outlineLevel="1"/>
     <row r="30" hidden="1" outlineLevel="1"/>
@@ -12141,7 +12840,7 @@
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CFRM-209  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
+    <oddFooter>&amp;C&amp;"Segoe UI"&amp;7 FRM-209  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -12160,7 +12859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:CU11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -12211,12 +12910,12 @@
           <t>REF LINKS</t>
         </is>
       </c>
-      <c r="B1" s="493" t="n"/>
-      <c r="C1" s="493" t="n"/>
-      <c r="D1" s="493" t="n"/>
-      <c r="E1" s="493" t="n"/>
-      <c r="F1" s="493" t="n"/>
-      <c r="G1" s="493" t="n"/>
+      <c r="B1" s="718" t="n"/>
+      <c r="C1" s="718" t="n"/>
+      <c r="D1" s="718" t="n"/>
+      <c r="E1" s="718" t="n"/>
+      <c r="F1" s="718" t="n"/>
+      <c r="G1" s="718" t="n"/>
       <c r="H1" s="612" t="n"/>
       <c r="I1" s="495" t="n"/>
       <c r="J1" s="496" t="n"/>
@@ -12257,12 +12956,6 @@
           <t>Reference release package, planner snapshot and dossier evidence only.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="614" t="n"/>
       <c r="I2" s="506" t="n"/>
       <c r="J2" s="507" t="n"/>

--- a/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
@@ -4,10 +4,10 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM-209_GATE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="veryHidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RISKS_ACTIONS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_RESULT_CORE">'_LISTS'!$A$2:$A$5</definedName>
@@ -826,7 +826,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="380">
+  <borders count="386">
     <border>
       <left/>
       <right/>
@@ -4939,11 +4939,79 @@
         <color rgb="000078D4"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="719">
+  <cellXfs count="765">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6715,6 +6783,126 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="345" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="380" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="381" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="384" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="382" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="383" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="385" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="47" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -6833,6 +7021,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6863,6 +7054,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7162,266 +7356,185 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="630" t="inlineStr"/>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="53" t="n"/>
+      <c r="A1" s="719" t="inlineStr"/>
+      <c r="B1" s="268" t="n"/>
+      <c r="C1" s="268" t="n"/>
+      <c r="D1" s="268" t="n"/>
+      <c r="E1" s="268" t="n"/>
+      <c r="F1" s="268" t="n"/>
+      <c r="G1" s="268" t="n"/>
+      <c r="H1" s="319" t="n"/>
       <c r="I1" s="631" t="inlineStr">
         <is>
           <t>HIGH-RISK JOB READINESS REVIEW</t>
         </is>
       </c>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
-      <c r="W1" s="2" t="n"/>
-      <c r="X1" s="2" t="n"/>
-      <c r="Y1" s="2" t="n"/>
-      <c r="Z1" s="2" t="n"/>
-      <c r="AA1" s="2" t="n"/>
-      <c r="AB1" s="2" t="n"/>
-      <c r="AC1" s="2" t="n"/>
-      <c r="AD1" s="2" t="n"/>
-      <c r="AE1" s="632" t="inlineStr">
+      <c r="J1" s="268" t="n"/>
+      <c r="K1" s="268" t="n"/>
+      <c r="L1" s="268" t="n"/>
+      <c r="M1" s="268" t="n"/>
+      <c r="N1" s="268" t="n"/>
+      <c r="O1" s="268" t="n"/>
+      <c r="P1" s="268" t="n"/>
+      <c r="Q1" s="268" t="n"/>
+      <c r="R1" s="268" t="n"/>
+      <c r="S1" s="268" t="n"/>
+      <c r="T1" s="268" t="n"/>
+      <c r="U1" s="268" t="n"/>
+      <c r="V1" s="268" t="n"/>
+      <c r="W1" s="268" t="n"/>
+      <c r="X1" s="268" t="n"/>
+      <c r="Y1" s="268" t="n"/>
+      <c r="Z1" s="268" t="n"/>
+      <c r="AA1" s="268" t="n"/>
+      <c r="AB1" s="268" t="n"/>
+      <c r="AC1" s="268" t="n"/>
+      <c r="AD1" s="268" t="n"/>
+      <c r="AE1" s="720" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="2" t="n"/>
-      <c r="AG1" s="2" t="n"/>
-      <c r="AH1" s="633" t="n"/>
-      <c r="AI1" s="634" t="inlineStr">
+      <c r="AF1" s="268" t="n"/>
+      <c r="AG1" s="268" t="n"/>
+      <c r="AH1" s="721" t="n"/>
+      <c r="AI1" s="678" t="inlineStr">
         <is>
           <t>FRM-209</t>
         </is>
       </c>
-      <c r="AJ1" s="2" t="n"/>
-      <c r="AK1" s="2" t="n"/>
-      <c r="AL1" s="2" t="n"/>
-      <c r="AM1" s="2" t="n"/>
-      <c r="AN1" s="53" t="n"/>
+      <c r="AJ1" s="268" t="n"/>
+      <c r="AK1" s="268" t="n"/>
+      <c r="AL1" s="268" t="n"/>
+      <c r="AM1" s="268" t="n"/>
+      <c r="AN1" s="319" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="54" t="n"/>
-      <c r="I2" s="9" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="10" t="n"/>
-      <c r="AE2" s="635" t="inlineStr">
+      <c r="A2" s="275" t="n"/>
+      <c r="H2" s="320" t="n"/>
+      <c r="I2" s="275" t="n"/>
+      <c r="AE2" s="722" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="636" t="n"/>
-      <c r="AG2" s="636" t="n"/>
-      <c r="AH2" s="637" t="n"/>
-      <c r="AI2" s="638" t="inlineStr">
+      <c r="AF2" s="723" t="n"/>
+      <c r="AG2" s="723" t="n"/>
+      <c r="AH2" s="724" t="n"/>
+      <c r="AI2" s="682" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="636" t="n"/>
-      <c r="AK2" s="636" t="n"/>
-      <c r="AL2" s="636" t="n"/>
-      <c r="AM2" s="636" t="n"/>
-      <c r="AN2" s="639" t="n"/>
+      <c r="AJ2" s="723" t="n"/>
+      <c r="AK2" s="723" t="n"/>
+      <c r="AL2" s="723" t="n"/>
+      <c r="AM2" s="723" t="n"/>
+      <c r="AN2" s="725" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="54" t="n"/>
-      <c r="I3" s="9" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="10" t="n"/>
-      <c r="AE3" s="635" t="inlineStr">
+      <c r="A3" s="275" t="n"/>
+      <c r="H3" s="320" t="n"/>
+      <c r="I3" s="275" t="n"/>
+      <c r="AE3" s="722" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="636" t="n"/>
-      <c r="AG3" s="636" t="n"/>
-      <c r="AH3" s="637" t="n"/>
-      <c r="AI3" s="638" t="inlineStr">
+      <c r="AF3" s="723" t="n"/>
+      <c r="AG3" s="723" t="n"/>
+      <c r="AH3" s="724" t="n"/>
+      <c r="AI3" s="682" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="636" t="n"/>
-      <c r="AK3" s="636" t="n"/>
-      <c r="AL3" s="636" t="n"/>
-      <c r="AM3" s="636" t="n"/>
-      <c r="AN3" s="639" t="n"/>
+      <c r="AJ3" s="723" t="n"/>
+      <c r="AK3" s="723" t="n"/>
+      <c r="AL3" s="723" t="n"/>
+      <c r="AM3" s="723" t="n"/>
+      <c r="AN3" s="725" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="54" t="n"/>
+      <c r="A4" s="275" t="n"/>
+      <c r="H4" s="320" t="n"/>
       <c r="I4" s="640" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="10" t="n"/>
-      <c r="AE4" s="635" t="inlineStr">
+      <c r="AE4" s="722" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="636" t="n"/>
-      <c r="AG4" s="636" t="n"/>
-      <c r="AH4" s="637" t="n"/>
-      <c r="AI4" s="638" t="inlineStr">
+      <c r="AF4" s="723" t="n"/>
+      <c r="AG4" s="723" t="n"/>
+      <c r="AH4" s="724" t="n"/>
+      <c r="AI4" s="682" t="inlineStr">
         <is>
           <t>Planning / QA / Engineering</t>
         </is>
       </c>
-      <c r="AJ4" s="636" t="n"/>
-      <c r="AK4" s="636" t="n"/>
-      <c r="AL4" s="636" t="n"/>
-      <c r="AM4" s="636" t="n"/>
-      <c r="AN4" s="639" t="n"/>
+      <c r="AJ4" s="723" t="n"/>
+      <c r="AK4" s="723" t="n"/>
+      <c r="AL4" s="723" t="n"/>
+      <c r="AM4" s="723" t="n"/>
+      <c r="AN4" s="725" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="19" t="n"/>
-      <c r="H5" s="24" t="n"/>
+      <c r="A5" s="282" t="n"/>
+      <c r="B5" s="283" t="n"/>
+      <c r="C5" s="283" t="n"/>
+      <c r="D5" s="283" t="n"/>
+      <c r="E5" s="283" t="n"/>
+      <c r="F5" s="283" t="n"/>
+      <c r="G5" s="283" t="n"/>
+      <c r="H5" s="287" t="n"/>
       <c r="I5" s="20" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="19" t="n"/>
-      <c r="K5" s="19" t="n"/>
-      <c r="L5" s="19" t="n"/>
-      <c r="M5" s="19" t="n"/>
-      <c r="N5" s="19" t="n"/>
-      <c r="O5" s="19" t="n"/>
-      <c r="P5" s="19" t="n"/>
-      <c r="Q5" s="19" t="n"/>
-      <c r="R5" s="19" t="n"/>
-      <c r="S5" s="19" t="n"/>
-      <c r="T5" s="19" t="n"/>
-      <c r="U5" s="19" t="n"/>
-      <c r="V5" s="19" t="n"/>
-      <c r="W5" s="19" t="n"/>
-      <c r="X5" s="19" t="n"/>
-      <c r="Y5" s="19" t="n"/>
-      <c r="Z5" s="19" t="n"/>
-      <c r="AA5" s="19" t="n"/>
-      <c r="AB5" s="19" t="n"/>
-      <c r="AC5" s="19" t="n"/>
-      <c r="AD5" s="19" t="n"/>
-      <c r="AE5" s="641" t="inlineStr">
+      <c r="J5" s="283" t="n"/>
+      <c r="K5" s="283" t="n"/>
+      <c r="L5" s="283" t="n"/>
+      <c r="M5" s="283" t="n"/>
+      <c r="N5" s="283" t="n"/>
+      <c r="O5" s="283" t="n"/>
+      <c r="P5" s="283" t="n"/>
+      <c r="Q5" s="283" t="n"/>
+      <c r="R5" s="283" t="n"/>
+      <c r="S5" s="283" t="n"/>
+      <c r="T5" s="283" t="n"/>
+      <c r="U5" s="283" t="n"/>
+      <c r="V5" s="283" t="n"/>
+      <c r="W5" s="283" t="n"/>
+      <c r="X5" s="283" t="n"/>
+      <c r="Y5" s="283" t="n"/>
+      <c r="Z5" s="283" t="n"/>
+      <c r="AA5" s="283" t="n"/>
+      <c r="AB5" s="283" t="n"/>
+      <c r="AC5" s="283" t="n"/>
+      <c r="AD5" s="283" t="n"/>
+      <c r="AE5" s="726" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="642" t="n"/>
-      <c r="AG5" s="642" t="n"/>
-      <c r="AH5" s="643" t="n"/>
-      <c r="AI5" s="644" t="inlineStr">
+      <c r="AF5" s="727" t="n"/>
+      <c r="AG5" s="727" t="n"/>
+      <c r="AH5" s="728" t="n"/>
+      <c r="AI5" s="689" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="642" t="n"/>
-      <c r="AK5" s="642" t="n"/>
-      <c r="AL5" s="642" t="n"/>
-      <c r="AM5" s="642" t="n"/>
-      <c r="AN5" s="645" t="n"/>
+      <c r="AJ5" s="727" t="n"/>
+      <c r="AK5" s="727" t="n"/>
+      <c r="AL5" s="727" t="n"/>
+      <c r="AM5" s="727" t="n"/>
+      <c r="AN5" s="729" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
       <c r="A6" s="646" t="n"/>
@@ -7466,300 +7579,300 @@
       <c r="AN6" s="646" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="647" t="inlineStr">
+      <c r="A7" s="730" t="inlineStr">
         <is>
           <t>1.  HIGH-RISK JOB HEADER / REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
-      <c r="L7" s="27" t="n"/>
-      <c r="M7" s="27" t="n"/>
-      <c r="N7" s="27" t="n"/>
-      <c r="O7" s="27" t="n"/>
-      <c r="P7" s="27" t="n"/>
-      <c r="Q7" s="27" t="n"/>
-      <c r="R7" s="27" t="n"/>
-      <c r="S7" s="27" t="n"/>
-      <c r="T7" s="27" t="n"/>
-      <c r="U7" s="27" t="n"/>
-      <c r="V7" s="27" t="n"/>
-      <c r="W7" s="27" t="n"/>
-      <c r="X7" s="27" t="n"/>
-      <c r="Y7" s="27" t="n"/>
-      <c r="Z7" s="27" t="n"/>
-      <c r="AA7" s="27" t="n"/>
-      <c r="AB7" s="27" t="n"/>
-      <c r="AC7" s="27" t="n"/>
-      <c r="AD7" s="27" t="n"/>
-      <c r="AE7" s="27" t="n"/>
-      <c r="AF7" s="27" t="n"/>
-      <c r="AG7" s="27" t="n"/>
-      <c r="AH7" s="27" t="n"/>
-      <c r="AI7" s="27" t="n"/>
-      <c r="AJ7" s="27" t="n"/>
-      <c r="AK7" s="27" t="n"/>
-      <c r="AL7" s="27" t="n"/>
-      <c r="AM7" s="27" t="n"/>
-      <c r="AN7" s="28" t="n"/>
+      <c r="B7" s="289" t="n"/>
+      <c r="C7" s="289" t="n"/>
+      <c r="D7" s="289" t="n"/>
+      <c r="E7" s="289" t="n"/>
+      <c r="F7" s="289" t="n"/>
+      <c r="G7" s="289" t="n"/>
+      <c r="H7" s="289" t="n"/>
+      <c r="I7" s="289" t="n"/>
+      <c r="J7" s="289" t="n"/>
+      <c r="K7" s="289" t="n"/>
+      <c r="L7" s="289" t="n"/>
+      <c r="M7" s="289" t="n"/>
+      <c r="N7" s="289" t="n"/>
+      <c r="O7" s="289" t="n"/>
+      <c r="P7" s="289" t="n"/>
+      <c r="Q7" s="289" t="n"/>
+      <c r="R7" s="289" t="n"/>
+      <c r="S7" s="289" t="n"/>
+      <c r="T7" s="289" t="n"/>
+      <c r="U7" s="289" t="n"/>
+      <c r="V7" s="289" t="n"/>
+      <c r="W7" s="289" t="n"/>
+      <c r="X7" s="289" t="n"/>
+      <c r="Y7" s="289" t="n"/>
+      <c r="Z7" s="289" t="n"/>
+      <c r="AA7" s="289" t="n"/>
+      <c r="AB7" s="289" t="n"/>
+      <c r="AC7" s="289" t="n"/>
+      <c r="AD7" s="289" t="n"/>
+      <c r="AE7" s="289" t="n"/>
+      <c r="AF7" s="289" t="n"/>
+      <c r="AG7" s="289" t="n"/>
+      <c r="AH7" s="289" t="n"/>
+      <c r="AI7" s="289" t="n"/>
+      <c r="AJ7" s="289" t="n"/>
+      <c r="AK7" s="289" t="n"/>
+      <c r="AL7" s="289" t="n"/>
+      <c r="AM7" s="289" t="n"/>
+      <c r="AN7" s="290" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="648" t="inlineStr">
+      <c r="A8" s="731" t="inlineStr">
         <is>
           <t>Readiness Review ID</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="30" t="inlineStr"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="6" t="n"/>
-      <c r="U8" s="649" t="inlineStr">
+      <c r="B8" s="271" t="n"/>
+      <c r="C8" s="271" t="n"/>
+      <c r="D8" s="271" t="n"/>
+      <c r="E8" s="271" t="n"/>
+      <c r="F8" s="271" t="n"/>
+      <c r="G8" s="272" t="n"/>
+      <c r="H8" s="292" t="inlineStr"/>
+      <c r="I8" s="271" t="n"/>
+      <c r="J8" s="271" t="n"/>
+      <c r="K8" s="271" t="n"/>
+      <c r="L8" s="271" t="n"/>
+      <c r="M8" s="271" t="n"/>
+      <c r="N8" s="271" t="n"/>
+      <c r="O8" s="271" t="n"/>
+      <c r="P8" s="271" t="n"/>
+      <c r="Q8" s="271" t="n"/>
+      <c r="R8" s="271" t="n"/>
+      <c r="S8" s="271" t="n"/>
+      <c r="T8" s="272" t="n"/>
+      <c r="U8" s="732" t="inlineStr">
         <is>
           <t>Job / WO</t>
         </is>
       </c>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-      <c r="Y8" s="5" t="n"/>
-      <c r="Z8" s="5" t="n"/>
-      <c r="AA8" s="6" t="n"/>
-      <c r="AB8" s="30" t="inlineStr"/>
-      <c r="AC8" s="5" t="n"/>
-      <c r="AD8" s="5" t="n"/>
-      <c r="AE8" s="5" t="n"/>
-      <c r="AF8" s="5" t="n"/>
-      <c r="AG8" s="5" t="n"/>
-      <c r="AH8" s="5" t="n"/>
-      <c r="AI8" s="5" t="n"/>
-      <c r="AJ8" s="5" t="n"/>
-      <c r="AK8" s="5" t="n"/>
-      <c r="AL8" s="5" t="n"/>
-      <c r="AM8" s="5" t="n"/>
-      <c r="AN8" s="8" t="n"/>
+      <c r="V8" s="271" t="n"/>
+      <c r="W8" s="271" t="n"/>
+      <c r="X8" s="271" t="n"/>
+      <c r="Y8" s="271" t="n"/>
+      <c r="Z8" s="271" t="n"/>
+      <c r="AA8" s="272" t="n"/>
+      <c r="AB8" s="294" t="inlineStr"/>
+      <c r="AC8" s="271" t="n"/>
+      <c r="AD8" s="271" t="n"/>
+      <c r="AE8" s="271" t="n"/>
+      <c r="AF8" s="271" t="n"/>
+      <c r="AG8" s="271" t="n"/>
+      <c r="AH8" s="271" t="n"/>
+      <c r="AI8" s="271" t="n"/>
+      <c r="AJ8" s="271" t="n"/>
+      <c r="AK8" s="271" t="n"/>
+      <c r="AL8" s="271" t="n"/>
+      <c r="AM8" s="271" t="n"/>
+      <c r="AN8" s="274" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="650" t="inlineStr">
+      <c r="A9" s="733" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="14" t="inlineStr"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="12" t="n"/>
-      <c r="O9" s="12" t="n"/>
-      <c r="P9" s="12" t="n"/>
-      <c r="Q9" s="12" t="n"/>
-      <c r="R9" s="12" t="n"/>
-      <c r="S9" s="12" t="n"/>
-      <c r="T9" s="13" t="n"/>
-      <c r="U9" s="651" t="inlineStr">
+      <c r="B9" s="277" t="n"/>
+      <c r="C9" s="277" t="n"/>
+      <c r="D9" s="277" t="n"/>
+      <c r="E9" s="277" t="n"/>
+      <c r="F9" s="277" t="n"/>
+      <c r="G9" s="278" t="n"/>
+      <c r="H9" s="296" t="inlineStr"/>
+      <c r="I9" s="277" t="n"/>
+      <c r="J9" s="277" t="n"/>
+      <c r="K9" s="277" t="n"/>
+      <c r="L9" s="277" t="n"/>
+      <c r="M9" s="277" t="n"/>
+      <c r="N9" s="277" t="n"/>
+      <c r="O9" s="277" t="n"/>
+      <c r="P9" s="277" t="n"/>
+      <c r="Q9" s="277" t="n"/>
+      <c r="R9" s="277" t="n"/>
+      <c r="S9" s="277" t="n"/>
+      <c r="T9" s="278" t="n"/>
+      <c r="U9" s="734" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="V9" s="12" t="n"/>
-      <c r="W9" s="12" t="n"/>
-      <c r="X9" s="12" t="n"/>
-      <c r="Y9" s="12" t="n"/>
-      <c r="Z9" s="12" t="n"/>
-      <c r="AA9" s="13" t="n"/>
-      <c r="AB9" s="14" t="inlineStr"/>
-      <c r="AC9" s="12" t="n"/>
-      <c r="AD9" s="12" t="n"/>
-      <c r="AE9" s="12" t="n"/>
-      <c r="AF9" s="12" t="n"/>
-      <c r="AG9" s="12" t="n"/>
-      <c r="AH9" s="12" t="n"/>
-      <c r="AI9" s="12" t="n"/>
-      <c r="AJ9" s="12" t="n"/>
-      <c r="AK9" s="12" t="n"/>
-      <c r="AL9" s="12" t="n"/>
-      <c r="AM9" s="12" t="n"/>
-      <c r="AN9" s="15" t="n"/>
+      <c r="V9" s="277" t="n"/>
+      <c r="W9" s="277" t="n"/>
+      <c r="X9" s="277" t="n"/>
+      <c r="Y9" s="277" t="n"/>
+      <c r="Z9" s="277" t="n"/>
+      <c r="AA9" s="278" t="n"/>
+      <c r="AB9" s="279" t="inlineStr"/>
+      <c r="AC9" s="277" t="n"/>
+      <c r="AD9" s="277" t="n"/>
+      <c r="AE9" s="277" t="n"/>
+      <c r="AF9" s="277" t="n"/>
+      <c r="AG9" s="277" t="n"/>
+      <c r="AH9" s="277" t="n"/>
+      <c r="AI9" s="277" t="n"/>
+      <c r="AJ9" s="277" t="n"/>
+      <c r="AK9" s="277" t="n"/>
+      <c r="AL9" s="277" t="n"/>
+      <c r="AM9" s="277" t="n"/>
+      <c r="AN9" s="280" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="650" t="inlineStr">
+      <c r="A10" s="733" t="inlineStr">
         <is>
           <t>Due Date / Commit</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="14" t="inlineStr"/>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
-      <c r="N10" s="12" t="n"/>
-      <c r="O10" s="12" t="n"/>
-      <c r="P10" s="12" t="n"/>
-      <c r="Q10" s="12" t="n"/>
-      <c r="R10" s="12" t="n"/>
-      <c r="S10" s="12" t="n"/>
-      <c r="T10" s="13" t="n"/>
-      <c r="U10" s="651" t="inlineStr">
+      <c r="B10" s="277" t="n"/>
+      <c r="C10" s="277" t="n"/>
+      <c r="D10" s="277" t="n"/>
+      <c r="E10" s="277" t="n"/>
+      <c r="F10" s="277" t="n"/>
+      <c r="G10" s="278" t="n"/>
+      <c r="H10" s="296" t="inlineStr"/>
+      <c r="I10" s="277" t="n"/>
+      <c r="J10" s="277" t="n"/>
+      <c r="K10" s="277" t="n"/>
+      <c r="L10" s="277" t="n"/>
+      <c r="M10" s="277" t="n"/>
+      <c r="N10" s="277" t="n"/>
+      <c r="O10" s="277" t="n"/>
+      <c r="P10" s="277" t="n"/>
+      <c r="Q10" s="277" t="n"/>
+      <c r="R10" s="277" t="n"/>
+      <c r="S10" s="277" t="n"/>
+      <c r="T10" s="278" t="n"/>
+      <c r="U10" s="734" t="inlineStr">
         <is>
           <t>Current Route Step</t>
         </is>
       </c>
-      <c r="V10" s="12" t="n"/>
-      <c r="W10" s="12" t="n"/>
-      <c r="X10" s="12" t="n"/>
-      <c r="Y10" s="12" t="n"/>
-      <c r="Z10" s="12" t="n"/>
-      <c r="AA10" s="13" t="n"/>
-      <c r="AB10" s="14" t="inlineStr"/>
-      <c r="AC10" s="12" t="n"/>
-      <c r="AD10" s="12" t="n"/>
-      <c r="AE10" s="12" t="n"/>
-      <c r="AF10" s="12" t="n"/>
-      <c r="AG10" s="12" t="n"/>
-      <c r="AH10" s="12" t="n"/>
-      <c r="AI10" s="12" t="n"/>
-      <c r="AJ10" s="12" t="n"/>
-      <c r="AK10" s="12" t="n"/>
-      <c r="AL10" s="12" t="n"/>
-      <c r="AM10" s="12" t="n"/>
-      <c r="AN10" s="15" t="n"/>
+      <c r="V10" s="277" t="n"/>
+      <c r="W10" s="277" t="n"/>
+      <c r="X10" s="277" t="n"/>
+      <c r="Y10" s="277" t="n"/>
+      <c r="Z10" s="277" t="n"/>
+      <c r="AA10" s="278" t="n"/>
+      <c r="AB10" s="279" t="inlineStr"/>
+      <c r="AC10" s="277" t="n"/>
+      <c r="AD10" s="277" t="n"/>
+      <c r="AE10" s="277" t="n"/>
+      <c r="AF10" s="277" t="n"/>
+      <c r="AG10" s="277" t="n"/>
+      <c r="AH10" s="277" t="n"/>
+      <c r="AI10" s="277" t="n"/>
+      <c r="AJ10" s="277" t="n"/>
+      <c r="AK10" s="277" t="n"/>
+      <c r="AL10" s="277" t="n"/>
+      <c r="AM10" s="277" t="n"/>
+      <c r="AN10" s="280" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="650" t="inlineStr">
+      <c r="A11" s="733" t="inlineStr">
         <is>
           <t>Top Risk Class</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="14" t="inlineStr"/>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
-      <c r="N11" s="12" t="n"/>
-      <c r="O11" s="12" t="n"/>
-      <c r="P11" s="12" t="n"/>
-      <c r="Q11" s="12" t="n"/>
-      <c r="R11" s="12" t="n"/>
-      <c r="S11" s="12" t="n"/>
-      <c r="T11" s="13" t="n"/>
-      <c r="U11" s="651" t="inlineStr">
+      <c r="B11" s="277" t="n"/>
+      <c r="C11" s="277" t="n"/>
+      <c r="D11" s="277" t="n"/>
+      <c r="E11" s="277" t="n"/>
+      <c r="F11" s="277" t="n"/>
+      <c r="G11" s="278" t="n"/>
+      <c r="H11" s="296" t="inlineStr"/>
+      <c r="I11" s="277" t="n"/>
+      <c r="J11" s="277" t="n"/>
+      <c r="K11" s="277" t="n"/>
+      <c r="L11" s="277" t="n"/>
+      <c r="M11" s="277" t="n"/>
+      <c r="N11" s="277" t="n"/>
+      <c r="O11" s="277" t="n"/>
+      <c r="P11" s="277" t="n"/>
+      <c r="Q11" s="277" t="n"/>
+      <c r="R11" s="277" t="n"/>
+      <c r="S11" s="277" t="n"/>
+      <c r="T11" s="278" t="n"/>
+      <c r="U11" s="734" t="inlineStr">
         <is>
           <t>Commercial / Ops Owner</t>
         </is>
       </c>
-      <c r="V11" s="12" t="n"/>
-      <c r="W11" s="12" t="n"/>
-      <c r="X11" s="12" t="n"/>
-      <c r="Y11" s="12" t="n"/>
-      <c r="Z11" s="12" t="n"/>
-      <c r="AA11" s="13" t="n"/>
-      <c r="AB11" s="14" t="inlineStr"/>
-      <c r="AC11" s="12" t="n"/>
-      <c r="AD11" s="12" t="n"/>
-      <c r="AE11" s="12" t="n"/>
-      <c r="AF11" s="12" t="n"/>
-      <c r="AG11" s="12" t="n"/>
-      <c r="AH11" s="12" t="n"/>
-      <c r="AI11" s="12" t="n"/>
-      <c r="AJ11" s="12" t="n"/>
-      <c r="AK11" s="12" t="n"/>
-      <c r="AL11" s="12" t="n"/>
-      <c r="AM11" s="12" t="n"/>
-      <c r="AN11" s="15" t="n"/>
+      <c r="V11" s="277" t="n"/>
+      <c r="W11" s="277" t="n"/>
+      <c r="X11" s="277" t="n"/>
+      <c r="Y11" s="277" t="n"/>
+      <c r="Z11" s="277" t="n"/>
+      <c r="AA11" s="278" t="n"/>
+      <c r="AB11" s="279" t="inlineStr"/>
+      <c r="AC11" s="277" t="n"/>
+      <c r="AD11" s="277" t="n"/>
+      <c r="AE11" s="277" t="n"/>
+      <c r="AF11" s="277" t="n"/>
+      <c r="AG11" s="277" t="n"/>
+      <c r="AH11" s="277" t="n"/>
+      <c r="AI11" s="277" t="n"/>
+      <c r="AJ11" s="277" t="n"/>
+      <c r="AK11" s="277" t="n"/>
+      <c r="AL11" s="277" t="n"/>
+      <c r="AM11" s="277" t="n"/>
+      <c r="AN11" s="280" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="652" t="inlineStr">
+      <c r="A12" s="735" t="inlineStr">
         <is>
           <t>Evidence Folder</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="22" t="n"/>
-      <c r="H12" s="23" t="inlineStr"/>
-      <c r="I12" s="19" t="n"/>
-      <c r="J12" s="19" t="n"/>
-      <c r="K12" s="19" t="n"/>
-      <c r="L12" s="19" t="n"/>
-      <c r="M12" s="19" t="n"/>
-      <c r="N12" s="19" t="n"/>
-      <c r="O12" s="19" t="n"/>
-      <c r="P12" s="19" t="n"/>
-      <c r="Q12" s="19" t="n"/>
-      <c r="R12" s="19" t="n"/>
-      <c r="S12" s="19" t="n"/>
-      <c r="T12" s="22" t="n"/>
-      <c r="U12" s="653" t="inlineStr">
+      <c r="B12" s="283" t="n"/>
+      <c r="C12" s="283" t="n"/>
+      <c r="D12" s="283" t="n"/>
+      <c r="E12" s="283" t="n"/>
+      <c r="F12" s="283" t="n"/>
+      <c r="G12" s="285" t="n"/>
+      <c r="H12" s="299" t="inlineStr"/>
+      <c r="I12" s="283" t="n"/>
+      <c r="J12" s="283" t="n"/>
+      <c r="K12" s="283" t="n"/>
+      <c r="L12" s="283" t="n"/>
+      <c r="M12" s="283" t="n"/>
+      <c r="N12" s="283" t="n"/>
+      <c r="O12" s="283" t="n"/>
+      <c r="P12" s="283" t="n"/>
+      <c r="Q12" s="283" t="n"/>
+      <c r="R12" s="283" t="n"/>
+      <c r="S12" s="283" t="n"/>
+      <c r="T12" s="285" t="n"/>
+      <c r="U12" s="736" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="V12" s="19" t="n"/>
-      <c r="W12" s="19" t="n"/>
-      <c r="X12" s="19" t="n"/>
-      <c r="Y12" s="19" t="n"/>
-      <c r="Z12" s="19" t="n"/>
-      <c r="AA12" s="22" t="n"/>
-      <c r="AB12" s="23" t="inlineStr"/>
-      <c r="AC12" s="19" t="n"/>
-      <c r="AD12" s="19" t="n"/>
-      <c r="AE12" s="19" t="n"/>
-      <c r="AF12" s="19" t="n"/>
-      <c r="AG12" s="19" t="n"/>
-      <c r="AH12" s="19" t="n"/>
-      <c r="AI12" s="19" t="n"/>
-      <c r="AJ12" s="19" t="n"/>
-      <c r="AK12" s="19" t="n"/>
-      <c r="AL12" s="19" t="n"/>
-      <c r="AM12" s="19" t="n"/>
-      <c r="AN12" s="24" t="n"/>
+      <c r="V12" s="283" t="n"/>
+      <c r="W12" s="283" t="n"/>
+      <c r="X12" s="283" t="n"/>
+      <c r="Y12" s="283" t="n"/>
+      <c r="Z12" s="283" t="n"/>
+      <c r="AA12" s="285" t="n"/>
+      <c r="AB12" s="286" t="inlineStr"/>
+      <c r="AC12" s="283" t="n"/>
+      <c r="AD12" s="283" t="n"/>
+      <c r="AE12" s="283" t="n"/>
+      <c r="AF12" s="283" t="n"/>
+      <c r="AG12" s="283" t="n"/>
+      <c r="AH12" s="283" t="n"/>
+      <c r="AI12" s="283" t="n"/>
+      <c r="AJ12" s="283" t="n"/>
+      <c r="AK12" s="283" t="n"/>
+      <c r="AL12" s="283" t="n"/>
+      <c r="AM12" s="283" t="n"/>
+      <c r="AN12" s="287" t="n"/>
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="654" t="n"/>
@@ -7804,260 +7917,260 @@
       <c r="AN13" s="10" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="647" t="inlineStr">
+      <c r="A14" s="730" t="inlineStr">
         <is>
           <t>2.  READINESS DECISION / OPEN RISK CONDITIONS</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="27" t="n"/>
-      <c r="I14" s="27" t="n"/>
-      <c r="J14" s="27" t="n"/>
-      <c r="K14" s="27" t="n"/>
-      <c r="L14" s="27" t="n"/>
-      <c r="M14" s="27" t="n"/>
-      <c r="N14" s="27" t="n"/>
-      <c r="O14" s="27" t="n"/>
-      <c r="P14" s="27" t="n"/>
-      <c r="Q14" s="27" t="n"/>
-      <c r="R14" s="27" t="n"/>
-      <c r="S14" s="27" t="n"/>
-      <c r="T14" s="27" t="n"/>
-      <c r="U14" s="27" t="n"/>
-      <c r="V14" s="27" t="n"/>
-      <c r="W14" s="27" t="n"/>
-      <c r="X14" s="27" t="n"/>
-      <c r="Y14" s="27" t="n"/>
-      <c r="Z14" s="27" t="n"/>
-      <c r="AA14" s="27" t="n"/>
-      <c r="AB14" s="27" t="n"/>
-      <c r="AC14" s="27" t="n"/>
-      <c r="AD14" s="27" t="n"/>
-      <c r="AE14" s="27" t="n"/>
-      <c r="AF14" s="27" t="n"/>
-      <c r="AG14" s="27" t="n"/>
-      <c r="AH14" s="27" t="n"/>
-      <c r="AI14" s="27" t="n"/>
-      <c r="AJ14" s="27" t="n"/>
-      <c r="AK14" s="27" t="n"/>
-      <c r="AL14" s="27" t="n"/>
-      <c r="AM14" s="27" t="n"/>
-      <c r="AN14" s="28" t="n"/>
+      <c r="B14" s="289" t="n"/>
+      <c r="C14" s="289" t="n"/>
+      <c r="D14" s="289" t="n"/>
+      <c r="E14" s="289" t="n"/>
+      <c r="F14" s="289" t="n"/>
+      <c r="G14" s="289" t="n"/>
+      <c r="H14" s="289" t="n"/>
+      <c r="I14" s="289" t="n"/>
+      <c r="J14" s="289" t="n"/>
+      <c r="K14" s="289" t="n"/>
+      <c r="L14" s="289" t="n"/>
+      <c r="M14" s="289" t="n"/>
+      <c r="N14" s="289" t="n"/>
+      <c r="O14" s="289" t="n"/>
+      <c r="P14" s="289" t="n"/>
+      <c r="Q14" s="289" t="n"/>
+      <c r="R14" s="289" t="n"/>
+      <c r="S14" s="289" t="n"/>
+      <c r="T14" s="289" t="n"/>
+      <c r="U14" s="289" t="n"/>
+      <c r="V14" s="289" t="n"/>
+      <c r="W14" s="289" t="n"/>
+      <c r="X14" s="289" t="n"/>
+      <c r="Y14" s="289" t="n"/>
+      <c r="Z14" s="289" t="n"/>
+      <c r="AA14" s="289" t="n"/>
+      <c r="AB14" s="289" t="n"/>
+      <c r="AC14" s="289" t="n"/>
+      <c r="AD14" s="289" t="n"/>
+      <c r="AE14" s="289" t="n"/>
+      <c r="AF14" s="289" t="n"/>
+      <c r="AG14" s="289" t="n"/>
+      <c r="AH14" s="289" t="n"/>
+      <c r="AI14" s="289" t="n"/>
+      <c r="AJ14" s="289" t="n"/>
+      <c r="AK14" s="289" t="n"/>
+      <c r="AL14" s="289" t="n"/>
+      <c r="AM14" s="289" t="n"/>
+      <c r="AN14" s="290" t="n"/>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="648" t="inlineStr">
+      <c r="A15" s="731" t="inlineStr">
         <is>
           <t>Gate Name / Trigger</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="30" t="inlineStr">
+      <c r="B15" s="271" t="n"/>
+      <c r="C15" s="271" t="n"/>
+      <c r="D15" s="271" t="n"/>
+      <c r="E15" s="271" t="n"/>
+      <c r="F15" s="271" t="n"/>
+      <c r="G15" s="272" t="n"/>
+      <c r="H15" s="292" t="inlineStr">
         <is>
           <t>High-risk job release review</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="5" t="n"/>
-      <c r="T15" s="6" t="n"/>
-      <c r="U15" s="649" t="inlineStr">
+      <c r="I15" s="271" t="n"/>
+      <c r="J15" s="271" t="n"/>
+      <c r="K15" s="271" t="n"/>
+      <c r="L15" s="271" t="n"/>
+      <c r="M15" s="271" t="n"/>
+      <c r="N15" s="271" t="n"/>
+      <c r="O15" s="271" t="n"/>
+      <c r="P15" s="271" t="n"/>
+      <c r="Q15" s="271" t="n"/>
+      <c r="R15" s="271" t="n"/>
+      <c r="S15" s="271" t="n"/>
+      <c r="T15" s="272" t="n"/>
+      <c r="U15" s="732" t="inlineStr">
         <is>
           <t>Gate Conclusion</t>
         </is>
       </c>
-      <c r="V15" s="5" t="n"/>
-      <c r="W15" s="5" t="n"/>
-      <c r="X15" s="5" t="n"/>
-      <c r="Y15" s="5" t="n"/>
-      <c r="Z15" s="5" t="n"/>
-      <c r="AA15" s="6" t="n"/>
-      <c r="AB15" s="30">
+      <c r="V15" s="271" t="n"/>
+      <c r="W15" s="271" t="n"/>
+      <c r="X15" s="271" t="n"/>
+      <c r="Y15" s="271" t="n"/>
+      <c r="Z15" s="271" t="n"/>
+      <c r="AA15" s="272" t="n"/>
+      <c r="AB15" s="294">
         <f>IF(COUNTA(AF22:AF31)=0,"",IF(COUNTIF(AF22:AF31,"FAIL")+COUNTIF(AF22:AF31,"HOLD")&gt;0,"HOLD",IF(COUNTIF(AF22:AF31,"PASS")=COUNTA(AF22:AF31),"APPROVED","CONDITIONAL")))</f>
         <v/>
       </c>
-      <c r="AC15" s="5" t="n"/>
-      <c r="AD15" s="5" t="n"/>
-      <c r="AE15" s="5" t="n"/>
-      <c r="AF15" s="5" t="n"/>
-      <c r="AG15" s="5" t="n"/>
-      <c r="AH15" s="5" t="n"/>
-      <c r="AI15" s="5" t="n"/>
-      <c r="AJ15" s="5" t="n"/>
-      <c r="AK15" s="5" t="n"/>
-      <c r="AL15" s="5" t="n"/>
-      <c r="AM15" s="5" t="n"/>
-      <c r="AN15" s="8" t="n"/>
+      <c r="AC15" s="271" t="n"/>
+      <c r="AD15" s="271" t="n"/>
+      <c r="AE15" s="271" t="n"/>
+      <c r="AF15" s="271" t="n"/>
+      <c r="AG15" s="271" t="n"/>
+      <c r="AH15" s="271" t="n"/>
+      <c r="AI15" s="271" t="n"/>
+      <c r="AJ15" s="271" t="n"/>
+      <c r="AK15" s="271" t="n"/>
+      <c r="AL15" s="271" t="n"/>
+      <c r="AM15" s="271" t="n"/>
+      <c r="AN15" s="274" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="650" t="inlineStr">
+      <c r="A16" s="733" t="inlineStr">
         <is>
           <t>Open Risk / Hold Reason</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="14" t="inlineStr"/>
-      <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
-      <c r="M16" s="12" t="n"/>
-      <c r="N16" s="12" t="n"/>
-      <c r="O16" s="12" t="n"/>
-      <c r="P16" s="12" t="n"/>
-      <c r="Q16" s="12" t="n"/>
-      <c r="R16" s="12" t="n"/>
-      <c r="S16" s="12" t="n"/>
-      <c r="T16" s="13" t="n"/>
-      <c r="U16" s="651" t="inlineStr">
+      <c r="B16" s="277" t="n"/>
+      <c r="C16" s="277" t="n"/>
+      <c r="D16" s="277" t="n"/>
+      <c r="E16" s="277" t="n"/>
+      <c r="F16" s="277" t="n"/>
+      <c r="G16" s="278" t="n"/>
+      <c r="H16" s="296" t="inlineStr"/>
+      <c r="I16" s="277" t="n"/>
+      <c r="J16" s="277" t="n"/>
+      <c r="K16" s="277" t="n"/>
+      <c r="L16" s="277" t="n"/>
+      <c r="M16" s="277" t="n"/>
+      <c r="N16" s="277" t="n"/>
+      <c r="O16" s="277" t="n"/>
+      <c r="P16" s="277" t="n"/>
+      <c r="Q16" s="277" t="n"/>
+      <c r="R16" s="277" t="n"/>
+      <c r="S16" s="277" t="n"/>
+      <c r="T16" s="278" t="n"/>
+      <c r="U16" s="734" t="inlineStr">
         <is>
           <t>Next Step</t>
         </is>
       </c>
-      <c r="V16" s="12" t="n"/>
-      <c r="W16" s="12" t="n"/>
-      <c r="X16" s="12" t="n"/>
-      <c r="Y16" s="12" t="n"/>
-      <c r="Z16" s="12" t="n"/>
-      <c r="AA16" s="13" t="n"/>
-      <c r="AB16" s="14" t="inlineStr"/>
-      <c r="AC16" s="12" t="n"/>
-      <c r="AD16" s="12" t="n"/>
-      <c r="AE16" s="12" t="n"/>
-      <c r="AF16" s="12" t="n"/>
-      <c r="AG16" s="12" t="n"/>
-      <c r="AH16" s="12" t="n"/>
-      <c r="AI16" s="12" t="n"/>
-      <c r="AJ16" s="12" t="n"/>
-      <c r="AK16" s="12" t="n"/>
-      <c r="AL16" s="12" t="n"/>
-      <c r="AM16" s="12" t="n"/>
-      <c r="AN16" s="15" t="n"/>
+      <c r="V16" s="277" t="n"/>
+      <c r="W16" s="277" t="n"/>
+      <c r="X16" s="277" t="n"/>
+      <c r="Y16" s="277" t="n"/>
+      <c r="Z16" s="277" t="n"/>
+      <c r="AA16" s="278" t="n"/>
+      <c r="AB16" s="279" t="inlineStr"/>
+      <c r="AC16" s="277" t="n"/>
+      <c r="AD16" s="277" t="n"/>
+      <c r="AE16" s="277" t="n"/>
+      <c r="AF16" s="277" t="n"/>
+      <c r="AG16" s="277" t="n"/>
+      <c r="AH16" s="277" t="n"/>
+      <c r="AI16" s="277" t="n"/>
+      <c r="AJ16" s="277" t="n"/>
+      <c r="AK16" s="277" t="n"/>
+      <c r="AL16" s="277" t="n"/>
+      <c r="AM16" s="277" t="n"/>
+      <c r="AN16" s="280" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="650" t="inlineStr">
+      <c r="A17" s="733" t="inlineStr">
         <is>
           <t>Action Owner</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="14" t="inlineStr"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
-      <c r="N17" s="12" t="n"/>
-      <c r="O17" s="12" t="n"/>
-      <c r="P17" s="12" t="n"/>
-      <c r="Q17" s="12" t="n"/>
-      <c r="R17" s="12" t="n"/>
-      <c r="S17" s="12" t="n"/>
-      <c r="T17" s="13" t="n"/>
-      <c r="U17" s="651" t="inlineStr">
+      <c r="B17" s="277" t="n"/>
+      <c r="C17" s="277" t="n"/>
+      <c r="D17" s="277" t="n"/>
+      <c r="E17" s="277" t="n"/>
+      <c r="F17" s="277" t="n"/>
+      <c r="G17" s="278" t="n"/>
+      <c r="H17" s="296" t="inlineStr"/>
+      <c r="I17" s="277" t="n"/>
+      <c r="J17" s="277" t="n"/>
+      <c r="K17" s="277" t="n"/>
+      <c r="L17" s="277" t="n"/>
+      <c r="M17" s="277" t="n"/>
+      <c r="N17" s="277" t="n"/>
+      <c r="O17" s="277" t="n"/>
+      <c r="P17" s="277" t="n"/>
+      <c r="Q17" s="277" t="n"/>
+      <c r="R17" s="277" t="n"/>
+      <c r="S17" s="277" t="n"/>
+      <c r="T17" s="278" t="n"/>
+      <c r="U17" s="734" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="V17" s="12" t="n"/>
-      <c r="W17" s="12" t="n"/>
-      <c r="X17" s="12" t="n"/>
-      <c r="Y17" s="12" t="n"/>
-      <c r="Z17" s="12" t="n"/>
-      <c r="AA17" s="13" t="n"/>
-      <c r="AB17" s="14" t="inlineStr"/>
-      <c r="AC17" s="12" t="n"/>
-      <c r="AD17" s="12" t="n"/>
-      <c r="AE17" s="12" t="n"/>
-      <c r="AF17" s="12" t="n"/>
-      <c r="AG17" s="12" t="n"/>
-      <c r="AH17" s="12" t="n"/>
-      <c r="AI17" s="12" t="n"/>
-      <c r="AJ17" s="12" t="n"/>
-      <c r="AK17" s="12" t="n"/>
-      <c r="AL17" s="12" t="n"/>
-      <c r="AM17" s="12" t="n"/>
-      <c r="AN17" s="15" t="n"/>
+      <c r="V17" s="277" t="n"/>
+      <c r="W17" s="277" t="n"/>
+      <c r="X17" s="277" t="n"/>
+      <c r="Y17" s="277" t="n"/>
+      <c r="Z17" s="277" t="n"/>
+      <c r="AA17" s="278" t="n"/>
+      <c r="AB17" s="279" t="inlineStr"/>
+      <c r="AC17" s="277" t="n"/>
+      <c r="AD17" s="277" t="n"/>
+      <c r="AE17" s="277" t="n"/>
+      <c r="AF17" s="277" t="n"/>
+      <c r="AG17" s="277" t="n"/>
+      <c r="AH17" s="277" t="n"/>
+      <c r="AI17" s="277" t="n"/>
+      <c r="AJ17" s="277" t="n"/>
+      <c r="AK17" s="277" t="n"/>
+      <c r="AL17" s="277" t="n"/>
+      <c r="AM17" s="277" t="n"/>
+      <c r="AN17" s="280" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="652" t="inlineStr">
+      <c r="A18" s="735" t="inlineStr">
         <is>
           <t>Escalation if Overdue</t>
         </is>
       </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="19" t="n"/>
-      <c r="F18" s="19" t="n"/>
-      <c r="G18" s="22" t="n"/>
-      <c r="H18" s="23" t="inlineStr"/>
-      <c r="I18" s="19" t="n"/>
-      <c r="J18" s="19" t="n"/>
-      <c r="K18" s="19" t="n"/>
-      <c r="L18" s="19" t="n"/>
-      <c r="M18" s="19" t="n"/>
-      <c r="N18" s="19" t="n"/>
-      <c r="O18" s="19" t="n"/>
-      <c r="P18" s="19" t="n"/>
-      <c r="Q18" s="19" t="n"/>
-      <c r="R18" s="19" t="n"/>
-      <c r="S18" s="19" t="n"/>
-      <c r="T18" s="22" t="n"/>
-      <c r="U18" s="653" t="inlineStr">
+      <c r="B18" s="283" t="n"/>
+      <c r="C18" s="283" t="n"/>
+      <c r="D18" s="283" t="n"/>
+      <c r="E18" s="283" t="n"/>
+      <c r="F18" s="283" t="n"/>
+      <c r="G18" s="285" t="n"/>
+      <c r="H18" s="299" t="inlineStr"/>
+      <c r="I18" s="283" t="n"/>
+      <c r="J18" s="283" t="n"/>
+      <c r="K18" s="283" t="n"/>
+      <c r="L18" s="283" t="n"/>
+      <c r="M18" s="283" t="n"/>
+      <c r="N18" s="283" t="n"/>
+      <c r="O18" s="283" t="n"/>
+      <c r="P18" s="283" t="n"/>
+      <c r="Q18" s="283" t="n"/>
+      <c r="R18" s="283" t="n"/>
+      <c r="S18" s="283" t="n"/>
+      <c r="T18" s="285" t="n"/>
+      <c r="U18" s="736" t="inlineStr">
         <is>
           <t>Gate Status</t>
         </is>
       </c>
-      <c r="V18" s="19" t="n"/>
-      <c r="W18" s="19" t="n"/>
-      <c r="X18" s="19" t="n"/>
-      <c r="Y18" s="19" t="n"/>
-      <c r="Z18" s="19" t="n"/>
-      <c r="AA18" s="22" t="n"/>
-      <c r="AB18" s="23">
+      <c r="V18" s="283" t="n"/>
+      <c r="W18" s="283" t="n"/>
+      <c r="X18" s="283" t="n"/>
+      <c r="Y18" s="283" t="n"/>
+      <c r="Z18" s="283" t="n"/>
+      <c r="AA18" s="285" t="n"/>
+      <c r="AB18" s="286">
         <f>IF(COUNTA(AF22:AF31)=0,"",IF(COUNTIF(AF22:AF31,"FAIL")+COUNTIF(AF22:AF31,"HOLD")&gt;0,"OPEN","CLOSED"))</f>
         <v/>
       </c>
-      <c r="AC18" s="19" t="n"/>
-      <c r="AD18" s="19" t="n"/>
-      <c r="AE18" s="19" t="n"/>
-      <c r="AF18" s="19" t="n"/>
-      <c r="AG18" s="19" t="n"/>
-      <c r="AH18" s="19" t="n"/>
-      <c r="AI18" s="19" t="n"/>
-      <c r="AJ18" s="19" t="n"/>
-      <c r="AK18" s="19" t="n"/>
-      <c r="AL18" s="19" t="n"/>
-      <c r="AM18" s="19" t="n"/>
-      <c r="AN18" s="24" t="n"/>
+      <c r="AC18" s="283" t="n"/>
+      <c r="AD18" s="283" t="n"/>
+      <c r="AE18" s="283" t="n"/>
+      <c r="AF18" s="283" t="n"/>
+      <c r="AG18" s="283" t="n"/>
+      <c r="AH18" s="283" t="n"/>
+      <c r="AI18" s="283" t="n"/>
+      <c r="AJ18" s="283" t="n"/>
+      <c r="AK18" s="283" t="n"/>
+      <c r="AL18" s="283" t="n"/>
+      <c r="AM18" s="283" t="n"/>
+      <c r="AN18" s="287" t="n"/>
     </row>
     <row r="19" ht="3" customHeight="1">
       <c r="A19" s="654" t="n"/>
@@ -8102,680 +8215,680 @@
       <c r="AN19" s="10" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="647" t="inlineStr">
+      <c r="A20" s="730" t="inlineStr">
         <is>
           <t>3.  READINESS CRITERIA / RISK CHECK</t>
         </is>
       </c>
-      <c r="B20" s="27" t="n"/>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="27" t="n"/>
-      <c r="H20" s="27" t="n"/>
-      <c r="I20" s="27" t="n"/>
-      <c r="J20" s="27" t="n"/>
-      <c r="K20" s="27" t="n"/>
-      <c r="L20" s="27" t="n"/>
-      <c r="M20" s="27" t="n"/>
-      <c r="N20" s="27" t="n"/>
-      <c r="O20" s="27" t="n"/>
-      <c r="P20" s="27" t="n"/>
-      <c r="Q20" s="27" t="n"/>
-      <c r="R20" s="27" t="n"/>
-      <c r="S20" s="27" t="n"/>
-      <c r="T20" s="27" t="n"/>
-      <c r="U20" s="27" t="n"/>
-      <c r="V20" s="27" t="n"/>
-      <c r="W20" s="27" t="n"/>
-      <c r="X20" s="27" t="n"/>
-      <c r="Y20" s="27" t="n"/>
-      <c r="Z20" s="27" t="n"/>
-      <c r="AA20" s="27" t="n"/>
-      <c r="AB20" s="27" t="n"/>
-      <c r="AC20" s="27" t="n"/>
-      <c r="AD20" s="27" t="n"/>
-      <c r="AE20" s="27" t="n"/>
-      <c r="AF20" s="27" t="n"/>
-      <c r="AG20" s="27" t="n"/>
-      <c r="AH20" s="27" t="n"/>
-      <c r="AI20" s="27" t="n"/>
-      <c r="AJ20" s="27" t="n"/>
-      <c r="AK20" s="27" t="n"/>
-      <c r="AL20" s="27" t="n"/>
-      <c r="AM20" s="27" t="n"/>
-      <c r="AN20" s="28" t="n"/>
+      <c r="B20" s="289" t="n"/>
+      <c r="C20" s="289" t="n"/>
+      <c r="D20" s="289" t="n"/>
+      <c r="E20" s="289" t="n"/>
+      <c r="F20" s="289" t="n"/>
+      <c r="G20" s="289" t="n"/>
+      <c r="H20" s="289" t="n"/>
+      <c r="I20" s="289" t="n"/>
+      <c r="J20" s="289" t="n"/>
+      <c r="K20" s="289" t="n"/>
+      <c r="L20" s="289" t="n"/>
+      <c r="M20" s="289" t="n"/>
+      <c r="N20" s="289" t="n"/>
+      <c r="O20" s="289" t="n"/>
+      <c r="P20" s="289" t="n"/>
+      <c r="Q20" s="289" t="n"/>
+      <c r="R20" s="289" t="n"/>
+      <c r="S20" s="289" t="n"/>
+      <c r="T20" s="289" t="n"/>
+      <c r="U20" s="289" t="n"/>
+      <c r="V20" s="289" t="n"/>
+      <c r="W20" s="289" t="n"/>
+      <c r="X20" s="289" t="n"/>
+      <c r="Y20" s="289" t="n"/>
+      <c r="Z20" s="289" t="n"/>
+      <c r="AA20" s="289" t="n"/>
+      <c r="AB20" s="289" t="n"/>
+      <c r="AC20" s="289" t="n"/>
+      <c r="AD20" s="289" t="n"/>
+      <c r="AE20" s="289" t="n"/>
+      <c r="AF20" s="289" t="n"/>
+      <c r="AG20" s="289" t="n"/>
+      <c r="AH20" s="289" t="n"/>
+      <c r="AI20" s="289" t="n"/>
+      <c r="AJ20" s="289" t="n"/>
+      <c r="AK20" s="289" t="n"/>
+      <c r="AL20" s="289" t="n"/>
+      <c r="AM20" s="289" t="n"/>
+      <c r="AN20" s="290" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="36" t="inlineStr">
+      <c r="A21" s="301" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="37" t="inlineStr">
+      <c r="B21" s="272" t="n"/>
+      <c r="C21" s="302" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="37" t="inlineStr">
+      <c r="D21" s="271" t="n"/>
+      <c r="E21" s="272" t="n"/>
+      <c r="F21" s="302" t="inlineStr">
         <is>
           <t>Readiness / Risk Item</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="6" t="n"/>
-      <c r="T21" s="37" t="inlineStr">
+      <c r="G21" s="271" t="n"/>
+      <c r="H21" s="271" t="n"/>
+      <c r="I21" s="271" t="n"/>
+      <c r="J21" s="271" t="n"/>
+      <c r="K21" s="271" t="n"/>
+      <c r="L21" s="271" t="n"/>
+      <c r="M21" s="271" t="n"/>
+      <c r="N21" s="271" t="n"/>
+      <c r="O21" s="271" t="n"/>
+      <c r="P21" s="271" t="n"/>
+      <c r="Q21" s="271" t="n"/>
+      <c r="R21" s="271" t="n"/>
+      <c r="S21" s="272" t="n"/>
+      <c r="T21" s="302" t="inlineStr">
         <is>
           <t>Acceptance / Control Rule</t>
         </is>
       </c>
-      <c r="U21" s="5" t="n"/>
-      <c r="V21" s="5" t="n"/>
-      <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="n"/>
-      <c r="Y21" s="5" t="n"/>
-      <c r="Z21" s="5" t="n"/>
-      <c r="AA21" s="5" t="n"/>
-      <c r="AB21" s="5" t="n"/>
-      <c r="AC21" s="5" t="n"/>
-      <c r="AD21" s="5" t="n"/>
-      <c r="AE21" s="6" t="n"/>
-      <c r="AF21" s="37" t="inlineStr">
+      <c r="U21" s="271" t="n"/>
+      <c r="V21" s="271" t="n"/>
+      <c r="W21" s="271" t="n"/>
+      <c r="X21" s="271" t="n"/>
+      <c r="Y21" s="271" t="n"/>
+      <c r="Z21" s="271" t="n"/>
+      <c r="AA21" s="271" t="n"/>
+      <c r="AB21" s="271" t="n"/>
+      <c r="AC21" s="271" t="n"/>
+      <c r="AD21" s="271" t="n"/>
+      <c r="AE21" s="272" t="n"/>
+      <c r="AF21" s="302" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG21" s="5" t="n"/>
-      <c r="AH21" s="5" t="n"/>
-      <c r="AI21" s="6" t="n"/>
-      <c r="AJ21" s="37" t="inlineStr">
+      <c r="AG21" s="271" t="n"/>
+      <c r="AH21" s="271" t="n"/>
+      <c r="AI21" s="272" t="n"/>
+      <c r="AJ21" s="302" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK21" s="5" t="n"/>
-      <c r="AL21" s="6" t="n"/>
-      <c r="AM21" s="37" t="inlineStr">
+      <c r="AK21" s="271" t="n"/>
+      <c r="AL21" s="272" t="n"/>
+      <c r="AM21" s="303" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="AN21" s="8" t="n"/>
+      <c r="AN21" s="274" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="655" t="n">
+      <c r="A22" s="737" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="656" t="inlineStr">
+      <c r="B22" s="272" t="n"/>
+      <c r="C22" s="738" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="657" t="inlineStr">
+      <c r="D22" s="271" t="n"/>
+      <c r="E22" s="272" t="n"/>
+      <c r="F22" s="739" t="inlineStr">
         <is>
           <t>Released baseline package is locked.</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="6" t="n"/>
-      <c r="T22" s="658" t="inlineStr">
+      <c r="G22" s="271" t="n"/>
+      <c r="H22" s="271" t="n"/>
+      <c r="I22" s="271" t="n"/>
+      <c r="J22" s="271" t="n"/>
+      <c r="K22" s="271" t="n"/>
+      <c r="L22" s="271" t="n"/>
+      <c r="M22" s="271" t="n"/>
+      <c r="N22" s="271" t="n"/>
+      <c r="O22" s="271" t="n"/>
+      <c r="P22" s="271" t="n"/>
+      <c r="Q22" s="271" t="n"/>
+      <c r="R22" s="271" t="n"/>
+      <c r="S22" s="272" t="n"/>
+      <c r="T22" s="740" t="inlineStr">
         <is>
           <t>FRM-306 or released package reference is current.</t>
         </is>
       </c>
-      <c r="U22" s="5" t="n"/>
-      <c r="V22" s="5" t="n"/>
-      <c r="W22" s="5" t="n"/>
-      <c r="X22" s="5" t="n"/>
-      <c r="Y22" s="5" t="n"/>
-      <c r="Z22" s="5" t="n"/>
-      <c r="AA22" s="5" t="n"/>
-      <c r="AB22" s="5" t="n"/>
-      <c r="AC22" s="5" t="n"/>
-      <c r="AD22" s="5" t="n"/>
-      <c r="AE22" s="6" t="n"/>
-      <c r="AF22" s="657" t="n"/>
-      <c r="AG22" s="5" t="n"/>
-      <c r="AH22" s="5" t="n"/>
-      <c r="AI22" s="6" t="n"/>
-      <c r="AJ22" s="657" t="n"/>
-      <c r="AK22" s="5" t="n"/>
-      <c r="AL22" s="6" t="n"/>
-      <c r="AM22" s="657" t="n"/>
-      <c r="AN22" s="8" t="n"/>
+      <c r="U22" s="271" t="n"/>
+      <c r="V22" s="271" t="n"/>
+      <c r="W22" s="271" t="n"/>
+      <c r="X22" s="271" t="n"/>
+      <c r="Y22" s="271" t="n"/>
+      <c r="Z22" s="271" t="n"/>
+      <c r="AA22" s="271" t="n"/>
+      <c r="AB22" s="271" t="n"/>
+      <c r="AC22" s="271" t="n"/>
+      <c r="AD22" s="271" t="n"/>
+      <c r="AE22" s="272" t="n"/>
+      <c r="AF22" s="739" t="n"/>
+      <c r="AG22" s="271" t="n"/>
+      <c r="AH22" s="271" t="n"/>
+      <c r="AI22" s="272" t="n"/>
+      <c r="AJ22" s="739" t="n"/>
+      <c r="AK22" s="271" t="n"/>
+      <c r="AL22" s="272" t="n"/>
+      <c r="AM22" s="741" t="n"/>
+      <c r="AN22" s="274" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="659" t="n">
+      <c r="A23" s="742" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="660" t="inlineStr">
+      <c r="B23" s="278" t="n"/>
+      <c r="C23" s="305" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="661" t="inlineStr">
+      <c r="D23" s="277" t="n"/>
+      <c r="E23" s="278" t="n"/>
+      <c r="F23" s="309" t="inlineStr">
         <is>
           <t>Customer / quality package is identified.</t>
         </is>
       </c>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="12" t="n"/>
-      <c r="K23" s="12" t="n"/>
-      <c r="L23" s="12" t="n"/>
-      <c r="M23" s="12" t="n"/>
-      <c r="N23" s="12" t="n"/>
-      <c r="O23" s="12" t="n"/>
-      <c r="P23" s="12" t="n"/>
-      <c r="Q23" s="12" t="n"/>
-      <c r="R23" s="12" t="n"/>
-      <c r="S23" s="13" t="n"/>
-      <c r="T23" s="662" t="inlineStr">
+      <c r="G23" s="277" t="n"/>
+      <c r="H23" s="277" t="n"/>
+      <c r="I23" s="277" t="n"/>
+      <c r="J23" s="277" t="n"/>
+      <c r="K23" s="277" t="n"/>
+      <c r="L23" s="277" t="n"/>
+      <c r="M23" s="277" t="n"/>
+      <c r="N23" s="277" t="n"/>
+      <c r="O23" s="277" t="n"/>
+      <c r="P23" s="277" t="n"/>
+      <c r="Q23" s="277" t="n"/>
+      <c r="R23" s="277" t="n"/>
+      <c r="S23" s="278" t="n"/>
+      <c r="T23" s="307" t="inlineStr">
         <is>
           <t>CSR / cert / packaging rules are visible.</t>
         </is>
       </c>
-      <c r="U23" s="12" t="n"/>
-      <c r="V23" s="12" t="n"/>
-      <c r="W23" s="12" t="n"/>
-      <c r="X23" s="12" t="n"/>
-      <c r="Y23" s="12" t="n"/>
-      <c r="Z23" s="12" t="n"/>
-      <c r="AA23" s="12" t="n"/>
-      <c r="AB23" s="12" t="n"/>
-      <c r="AC23" s="12" t="n"/>
-      <c r="AD23" s="12" t="n"/>
-      <c r="AE23" s="13" t="n"/>
-      <c r="AF23" s="663" t="n"/>
-      <c r="AG23" s="12" t="n"/>
-      <c r="AH23" s="12" t="n"/>
-      <c r="AI23" s="13" t="n"/>
-      <c r="AJ23" s="663" t="n"/>
-      <c r="AK23" s="12" t="n"/>
-      <c r="AL23" s="13" t="n"/>
-      <c r="AM23" s="663" t="n"/>
-      <c r="AN23" s="15" t="n"/>
+      <c r="U23" s="277" t="n"/>
+      <c r="V23" s="277" t="n"/>
+      <c r="W23" s="277" t="n"/>
+      <c r="X23" s="277" t="n"/>
+      <c r="Y23" s="277" t="n"/>
+      <c r="Z23" s="277" t="n"/>
+      <c r="AA23" s="277" t="n"/>
+      <c r="AB23" s="277" t="n"/>
+      <c r="AC23" s="277" t="n"/>
+      <c r="AD23" s="277" t="n"/>
+      <c r="AE23" s="278" t="n"/>
+      <c r="AF23" s="306" t="n"/>
+      <c r="AG23" s="277" t="n"/>
+      <c r="AH23" s="277" t="n"/>
+      <c r="AI23" s="278" t="n"/>
+      <c r="AJ23" s="306" t="n"/>
+      <c r="AK23" s="277" t="n"/>
+      <c r="AL23" s="278" t="n"/>
+      <c r="AM23" s="743" t="n"/>
+      <c r="AN23" s="280" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="659" t="n">
+      <c r="A24" s="742" t="n">
         <v>3</v>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="660" t="inlineStr">
+      <c r="B24" s="278" t="n"/>
+      <c r="C24" s="305" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="663" t="inlineStr">
+      <c r="D24" s="277" t="n"/>
+      <c r="E24" s="278" t="n"/>
+      <c r="F24" s="306" t="inlineStr">
         <is>
           <t>Material / outsource path is feasible.</t>
         </is>
       </c>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="12" t="n"/>
-      <c r="M24" s="12" t="n"/>
-      <c r="N24" s="12" t="n"/>
-      <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
-      <c r="Q24" s="12" t="n"/>
-      <c r="R24" s="12" t="n"/>
-      <c r="S24" s="13" t="n"/>
-      <c r="T24" s="662" t="inlineStr">
+      <c r="G24" s="277" t="n"/>
+      <c r="H24" s="277" t="n"/>
+      <c r="I24" s="277" t="n"/>
+      <c r="J24" s="277" t="n"/>
+      <c r="K24" s="277" t="n"/>
+      <c r="L24" s="277" t="n"/>
+      <c r="M24" s="277" t="n"/>
+      <c r="N24" s="277" t="n"/>
+      <c r="O24" s="277" t="n"/>
+      <c r="P24" s="277" t="n"/>
+      <c r="Q24" s="277" t="n"/>
+      <c r="R24" s="277" t="n"/>
+      <c r="S24" s="278" t="n"/>
+      <c r="T24" s="307" t="inlineStr">
         <is>
           <t>Critical source path is not assumed.</t>
         </is>
       </c>
-      <c r="U24" s="12" t="n"/>
-      <c r="V24" s="12" t="n"/>
-      <c r="W24" s="12" t="n"/>
-      <c r="X24" s="12" t="n"/>
-      <c r="Y24" s="12" t="n"/>
-      <c r="Z24" s="12" t="n"/>
-      <c r="AA24" s="12" t="n"/>
-      <c r="AB24" s="12" t="n"/>
-      <c r="AC24" s="12" t="n"/>
-      <c r="AD24" s="12" t="n"/>
-      <c r="AE24" s="13" t="n"/>
-      <c r="AF24" s="663" t="n"/>
-      <c r="AG24" s="12" t="n"/>
-      <c r="AH24" s="12" t="n"/>
-      <c r="AI24" s="13" t="n"/>
-      <c r="AJ24" s="663" t="n"/>
-      <c r="AK24" s="12" t="n"/>
-      <c r="AL24" s="13" t="n"/>
-      <c r="AM24" s="663" t="n"/>
-      <c r="AN24" s="15" t="n"/>
+      <c r="U24" s="277" t="n"/>
+      <c r="V24" s="277" t="n"/>
+      <c r="W24" s="277" t="n"/>
+      <c r="X24" s="277" t="n"/>
+      <c r="Y24" s="277" t="n"/>
+      <c r="Z24" s="277" t="n"/>
+      <c r="AA24" s="277" t="n"/>
+      <c r="AB24" s="277" t="n"/>
+      <c r="AC24" s="277" t="n"/>
+      <c r="AD24" s="277" t="n"/>
+      <c r="AE24" s="278" t="n"/>
+      <c r="AF24" s="306" t="n"/>
+      <c r="AG24" s="277" t="n"/>
+      <c r="AH24" s="277" t="n"/>
+      <c r="AI24" s="278" t="n"/>
+      <c r="AJ24" s="306" t="n"/>
+      <c r="AK24" s="277" t="n"/>
+      <c r="AL24" s="278" t="n"/>
+      <c r="AM24" s="743" t="n"/>
+      <c r="AN24" s="280" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="659" t="n">
+      <c r="A25" s="742" t="n">
         <v>4</v>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="660" t="inlineStr">
+      <c r="B25" s="278" t="n"/>
+      <c r="C25" s="305" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="661" t="inlineStr">
+      <c r="D25" s="277" t="n"/>
+      <c r="E25" s="278" t="n"/>
+      <c r="F25" s="309" t="inlineStr">
         <is>
           <t>Machine / tooling / gage readiness exists.</t>
         </is>
       </c>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
-      <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="12" t="n"/>
-      <c r="M25" s="12" t="n"/>
-      <c r="N25" s="12" t="n"/>
-      <c r="O25" s="12" t="n"/>
-      <c r="P25" s="12" t="n"/>
-      <c r="Q25" s="12" t="n"/>
-      <c r="R25" s="12" t="n"/>
-      <c r="S25" s="13" t="n"/>
-      <c r="T25" s="662" t="inlineStr">
+      <c r="G25" s="277" t="n"/>
+      <c r="H25" s="277" t="n"/>
+      <c r="I25" s="277" t="n"/>
+      <c r="J25" s="277" t="n"/>
+      <c r="K25" s="277" t="n"/>
+      <c r="L25" s="277" t="n"/>
+      <c r="M25" s="277" t="n"/>
+      <c r="N25" s="277" t="n"/>
+      <c r="O25" s="277" t="n"/>
+      <c r="P25" s="277" t="n"/>
+      <c r="Q25" s="277" t="n"/>
+      <c r="R25" s="277" t="n"/>
+      <c r="S25" s="278" t="n"/>
+      <c r="T25" s="307" t="inlineStr">
         <is>
           <t>Capability and readiness path are visible.</t>
         </is>
       </c>
-      <c r="U25" s="12" t="n"/>
-      <c r="V25" s="12" t="n"/>
-      <c r="W25" s="12" t="n"/>
-      <c r="X25" s="12" t="n"/>
-      <c r="Y25" s="12" t="n"/>
-      <c r="Z25" s="12" t="n"/>
-      <c r="AA25" s="12" t="n"/>
-      <c r="AB25" s="12" t="n"/>
-      <c r="AC25" s="12" t="n"/>
-      <c r="AD25" s="12" t="n"/>
-      <c r="AE25" s="13" t="n"/>
-      <c r="AF25" s="663" t="n"/>
-      <c r="AG25" s="12" t="n"/>
-      <c r="AH25" s="12" t="n"/>
-      <c r="AI25" s="13" t="n"/>
-      <c r="AJ25" s="663" t="n"/>
-      <c r="AK25" s="12" t="n"/>
-      <c r="AL25" s="13" t="n"/>
-      <c r="AM25" s="663" t="n"/>
-      <c r="AN25" s="15" t="n"/>
+      <c r="U25" s="277" t="n"/>
+      <c r="V25" s="277" t="n"/>
+      <c r="W25" s="277" t="n"/>
+      <c r="X25" s="277" t="n"/>
+      <c r="Y25" s="277" t="n"/>
+      <c r="Z25" s="277" t="n"/>
+      <c r="AA25" s="277" t="n"/>
+      <c r="AB25" s="277" t="n"/>
+      <c r="AC25" s="277" t="n"/>
+      <c r="AD25" s="277" t="n"/>
+      <c r="AE25" s="278" t="n"/>
+      <c r="AF25" s="306" t="n"/>
+      <c r="AG25" s="277" t="n"/>
+      <c r="AH25" s="277" t="n"/>
+      <c r="AI25" s="278" t="n"/>
+      <c r="AJ25" s="306" t="n"/>
+      <c r="AK25" s="277" t="n"/>
+      <c r="AL25" s="278" t="n"/>
+      <c r="AM25" s="743" t="n"/>
+      <c r="AN25" s="280" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="659" t="n">
+      <c r="A26" s="742" t="n">
         <v>5</v>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="660" t="inlineStr">
+      <c r="B26" s="278" t="n"/>
+      <c r="C26" s="305" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="663" t="inlineStr">
+      <c r="D26" s="277" t="n"/>
+      <c r="E26" s="278" t="n"/>
+      <c r="F26" s="306" t="inlineStr">
         <is>
           <t>First-piece / FAI strategy is defined.</t>
         </is>
       </c>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n"/>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
-      <c r="M26" s="12" t="n"/>
-      <c r="N26" s="12" t="n"/>
-      <c r="O26" s="12" t="n"/>
-      <c r="P26" s="12" t="n"/>
-      <c r="Q26" s="12" t="n"/>
-      <c r="R26" s="12" t="n"/>
-      <c r="S26" s="13" t="n"/>
-      <c r="T26" s="662" t="inlineStr">
+      <c r="G26" s="277" t="n"/>
+      <c r="H26" s="277" t="n"/>
+      <c r="I26" s="277" t="n"/>
+      <c r="J26" s="277" t="n"/>
+      <c r="K26" s="277" t="n"/>
+      <c r="L26" s="277" t="n"/>
+      <c r="M26" s="277" t="n"/>
+      <c r="N26" s="277" t="n"/>
+      <c r="O26" s="277" t="n"/>
+      <c r="P26" s="277" t="n"/>
+      <c r="Q26" s="277" t="n"/>
+      <c r="R26" s="277" t="n"/>
+      <c r="S26" s="278" t="n"/>
+      <c r="T26" s="307" t="inlineStr">
         <is>
           <t>QA gate logic and owner are visible.</t>
         </is>
       </c>
-      <c r="U26" s="12" t="n"/>
-      <c r="V26" s="12" t="n"/>
-      <c r="W26" s="12" t="n"/>
-      <c r="X26" s="12" t="n"/>
-      <c r="Y26" s="12" t="n"/>
-      <c r="Z26" s="12" t="n"/>
-      <c r="AA26" s="12" t="n"/>
-      <c r="AB26" s="12" t="n"/>
-      <c r="AC26" s="12" t="n"/>
-      <c r="AD26" s="12" t="n"/>
-      <c r="AE26" s="13" t="n"/>
-      <c r="AF26" s="663" t="n"/>
-      <c r="AG26" s="12" t="n"/>
-      <c r="AH26" s="12" t="n"/>
-      <c r="AI26" s="13" t="n"/>
-      <c r="AJ26" s="663" t="n"/>
-      <c r="AK26" s="12" t="n"/>
-      <c r="AL26" s="13" t="n"/>
-      <c r="AM26" s="663" t="n"/>
-      <c r="AN26" s="15" t="n"/>
+      <c r="U26" s="277" t="n"/>
+      <c r="V26" s="277" t="n"/>
+      <c r="W26" s="277" t="n"/>
+      <c r="X26" s="277" t="n"/>
+      <c r="Y26" s="277" t="n"/>
+      <c r="Z26" s="277" t="n"/>
+      <c r="AA26" s="277" t="n"/>
+      <c r="AB26" s="277" t="n"/>
+      <c r="AC26" s="277" t="n"/>
+      <c r="AD26" s="277" t="n"/>
+      <c r="AE26" s="278" t="n"/>
+      <c r="AF26" s="306" t="n"/>
+      <c r="AG26" s="277" t="n"/>
+      <c r="AH26" s="277" t="n"/>
+      <c r="AI26" s="278" t="n"/>
+      <c r="AJ26" s="306" t="n"/>
+      <c r="AK26" s="277" t="n"/>
+      <c r="AL26" s="278" t="n"/>
+      <c r="AM26" s="743" t="n"/>
+      <c r="AN26" s="280" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="659" t="n">
+      <c r="A27" s="742" t="n">
         <v>6</v>
       </c>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="660" t="inlineStr">
+      <c r="B27" s="278" t="n"/>
+      <c r="C27" s="305" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="661" t="inlineStr">
+      <c r="D27" s="277" t="n"/>
+      <c r="E27" s="278" t="n"/>
+      <c r="F27" s="309" t="inlineStr">
         <is>
           <t>Delivery / ship logic is feasible.</t>
         </is>
       </c>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="12" t="n"/>
-      <c r="I27" s="12" t="n"/>
-      <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="12" t="n"/>
-      <c r="M27" s="12" t="n"/>
-      <c r="N27" s="12" t="n"/>
-      <c r="O27" s="12" t="n"/>
-      <c r="P27" s="12" t="n"/>
-      <c r="Q27" s="12" t="n"/>
-      <c r="R27" s="12" t="n"/>
-      <c r="S27" s="13" t="n"/>
-      <c r="T27" s="662" t="inlineStr">
+      <c r="G27" s="277" t="n"/>
+      <c r="H27" s="277" t="n"/>
+      <c r="I27" s="277" t="n"/>
+      <c r="J27" s="277" t="n"/>
+      <c r="K27" s="277" t="n"/>
+      <c r="L27" s="277" t="n"/>
+      <c r="M27" s="277" t="n"/>
+      <c r="N27" s="277" t="n"/>
+      <c r="O27" s="277" t="n"/>
+      <c r="P27" s="277" t="n"/>
+      <c r="Q27" s="277" t="n"/>
+      <c r="R27" s="277" t="n"/>
+      <c r="S27" s="278" t="n"/>
+      <c r="T27" s="307" t="inlineStr">
         <is>
           <t>Commitment and ship impact are realistic.</t>
         </is>
       </c>
-      <c r="U27" s="12" t="n"/>
-      <c r="V27" s="12" t="n"/>
-      <c r="W27" s="12" t="n"/>
-      <c r="X27" s="12" t="n"/>
-      <c r="Y27" s="12" t="n"/>
-      <c r="Z27" s="12" t="n"/>
-      <c r="AA27" s="12" t="n"/>
-      <c r="AB27" s="12" t="n"/>
-      <c r="AC27" s="12" t="n"/>
-      <c r="AD27" s="12" t="n"/>
-      <c r="AE27" s="13" t="n"/>
-      <c r="AF27" s="663" t="n"/>
-      <c r="AG27" s="12" t="n"/>
-      <c r="AH27" s="12" t="n"/>
-      <c r="AI27" s="13" t="n"/>
-      <c r="AJ27" s="663" t="n"/>
-      <c r="AK27" s="12" t="n"/>
-      <c r="AL27" s="13" t="n"/>
-      <c r="AM27" s="663" t="n"/>
-      <c r="AN27" s="15" t="n"/>
+      <c r="U27" s="277" t="n"/>
+      <c r="V27" s="277" t="n"/>
+      <c r="W27" s="277" t="n"/>
+      <c r="X27" s="277" t="n"/>
+      <c r="Y27" s="277" t="n"/>
+      <c r="Z27" s="277" t="n"/>
+      <c r="AA27" s="277" t="n"/>
+      <c r="AB27" s="277" t="n"/>
+      <c r="AC27" s="277" t="n"/>
+      <c r="AD27" s="277" t="n"/>
+      <c r="AE27" s="278" t="n"/>
+      <c r="AF27" s="306" t="n"/>
+      <c r="AG27" s="277" t="n"/>
+      <c r="AH27" s="277" t="n"/>
+      <c r="AI27" s="278" t="n"/>
+      <c r="AJ27" s="306" t="n"/>
+      <c r="AK27" s="277" t="n"/>
+      <c r="AL27" s="278" t="n"/>
+      <c r="AM27" s="743" t="n"/>
+      <c r="AN27" s="280" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="659" t="n">
+      <c r="A28" s="742" t="n">
         <v>7</v>
       </c>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="660" t="inlineStr">
+      <c r="B28" s="278" t="n"/>
+      <c r="C28" s="305" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="663" t="inlineStr">
+      <c r="D28" s="277" t="n"/>
+      <c r="E28" s="278" t="n"/>
+      <c r="F28" s="306" t="inlineStr">
         <is>
           <t>Top abnormal / failure mode is explicit.</t>
         </is>
       </c>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="12" t="n"/>
-      <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
-      <c r="L28" s="12" t="n"/>
-      <c r="M28" s="12" t="n"/>
-      <c r="N28" s="12" t="n"/>
-      <c r="O28" s="12" t="n"/>
-      <c r="P28" s="12" t="n"/>
-      <c r="Q28" s="12" t="n"/>
-      <c r="R28" s="12" t="n"/>
-      <c r="S28" s="13" t="n"/>
-      <c r="T28" s="662" t="inlineStr">
+      <c r="G28" s="277" t="n"/>
+      <c r="H28" s="277" t="n"/>
+      <c r="I28" s="277" t="n"/>
+      <c r="J28" s="277" t="n"/>
+      <c r="K28" s="277" t="n"/>
+      <c r="L28" s="277" t="n"/>
+      <c r="M28" s="277" t="n"/>
+      <c r="N28" s="277" t="n"/>
+      <c r="O28" s="277" t="n"/>
+      <c r="P28" s="277" t="n"/>
+      <c r="Q28" s="277" t="n"/>
+      <c r="R28" s="277" t="n"/>
+      <c r="S28" s="278" t="n"/>
+      <c r="T28" s="307" t="inlineStr">
         <is>
           <t>Most severe risk is named, not hidden.</t>
         </is>
       </c>
-      <c r="U28" s="12" t="n"/>
-      <c r="V28" s="12" t="n"/>
-      <c r="W28" s="12" t="n"/>
-      <c r="X28" s="12" t="n"/>
-      <c r="Y28" s="12" t="n"/>
-      <c r="Z28" s="12" t="n"/>
-      <c r="AA28" s="12" t="n"/>
-      <c r="AB28" s="12" t="n"/>
-      <c r="AC28" s="12" t="n"/>
-      <c r="AD28" s="12" t="n"/>
-      <c r="AE28" s="13" t="n"/>
-      <c r="AF28" s="663" t="n"/>
-      <c r="AG28" s="12" t="n"/>
-      <c r="AH28" s="12" t="n"/>
-      <c r="AI28" s="13" t="n"/>
-      <c r="AJ28" s="663" t="n"/>
-      <c r="AK28" s="12" t="n"/>
-      <c r="AL28" s="13" t="n"/>
-      <c r="AM28" s="663" t="n"/>
-      <c r="AN28" s="15" t="n"/>
+      <c r="U28" s="277" t="n"/>
+      <c r="V28" s="277" t="n"/>
+      <c r="W28" s="277" t="n"/>
+      <c r="X28" s="277" t="n"/>
+      <c r="Y28" s="277" t="n"/>
+      <c r="Z28" s="277" t="n"/>
+      <c r="AA28" s="277" t="n"/>
+      <c r="AB28" s="277" t="n"/>
+      <c r="AC28" s="277" t="n"/>
+      <c r="AD28" s="277" t="n"/>
+      <c r="AE28" s="278" t="n"/>
+      <c r="AF28" s="306" t="n"/>
+      <c r="AG28" s="277" t="n"/>
+      <c r="AH28" s="277" t="n"/>
+      <c r="AI28" s="278" t="n"/>
+      <c r="AJ28" s="306" t="n"/>
+      <c r="AK28" s="277" t="n"/>
+      <c r="AL28" s="278" t="n"/>
+      <c r="AM28" s="743" t="n"/>
+      <c r="AN28" s="280" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="659" t="n">
+      <c r="A29" s="742" t="n">
         <v>8</v>
       </c>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="660" t="inlineStr">
+      <c r="B29" s="278" t="n"/>
+      <c r="C29" s="305" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="661" t="inlineStr">
+      <c r="D29" s="277" t="n"/>
+      <c r="E29" s="278" t="n"/>
+      <c r="F29" s="309" t="inlineStr">
         <is>
           <t>Containment / contingency exists.</t>
         </is>
       </c>
-      <c r="G29" s="12" t="n"/>
-      <c r="H29" s="12" t="n"/>
-      <c r="I29" s="12" t="n"/>
-      <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="12" t="n"/>
-      <c r="M29" s="12" t="n"/>
-      <c r="N29" s="12" t="n"/>
-      <c r="O29" s="12" t="n"/>
-      <c r="P29" s="12" t="n"/>
-      <c r="Q29" s="12" t="n"/>
-      <c r="R29" s="12" t="n"/>
-      <c r="S29" s="13" t="n"/>
-      <c r="T29" s="662" t="inlineStr">
+      <c r="G29" s="277" t="n"/>
+      <c r="H29" s="277" t="n"/>
+      <c r="I29" s="277" t="n"/>
+      <c r="J29" s="277" t="n"/>
+      <c r="K29" s="277" t="n"/>
+      <c r="L29" s="277" t="n"/>
+      <c r="M29" s="277" t="n"/>
+      <c r="N29" s="277" t="n"/>
+      <c r="O29" s="277" t="n"/>
+      <c r="P29" s="277" t="n"/>
+      <c r="Q29" s="277" t="n"/>
+      <c r="R29" s="277" t="n"/>
+      <c r="S29" s="278" t="n"/>
+      <c r="T29" s="307" t="inlineStr">
         <is>
           <t>Recovery path exists if primary plan fails.</t>
         </is>
       </c>
-      <c r="U29" s="12" t="n"/>
-      <c r="V29" s="12" t="n"/>
-      <c r="W29" s="12" t="n"/>
-      <c r="X29" s="12" t="n"/>
-      <c r="Y29" s="12" t="n"/>
-      <c r="Z29" s="12" t="n"/>
-      <c r="AA29" s="12" t="n"/>
-      <c r="AB29" s="12" t="n"/>
-      <c r="AC29" s="12" t="n"/>
-      <c r="AD29" s="12" t="n"/>
-      <c r="AE29" s="13" t="n"/>
-      <c r="AF29" s="663" t="n"/>
-      <c r="AG29" s="12" t="n"/>
-      <c r="AH29" s="12" t="n"/>
-      <c r="AI29" s="13" t="n"/>
-      <c r="AJ29" s="663" t="n"/>
-      <c r="AK29" s="12" t="n"/>
-      <c r="AL29" s="13" t="n"/>
-      <c r="AM29" s="663" t="n"/>
-      <c r="AN29" s="15" t="n"/>
+      <c r="U29" s="277" t="n"/>
+      <c r="V29" s="277" t="n"/>
+      <c r="W29" s="277" t="n"/>
+      <c r="X29" s="277" t="n"/>
+      <c r="Y29" s="277" t="n"/>
+      <c r="Z29" s="277" t="n"/>
+      <c r="AA29" s="277" t="n"/>
+      <c r="AB29" s="277" t="n"/>
+      <c r="AC29" s="277" t="n"/>
+      <c r="AD29" s="277" t="n"/>
+      <c r="AE29" s="278" t="n"/>
+      <c r="AF29" s="306" t="n"/>
+      <c r="AG29" s="277" t="n"/>
+      <c r="AH29" s="277" t="n"/>
+      <c r="AI29" s="278" t="n"/>
+      <c r="AJ29" s="306" t="n"/>
+      <c r="AK29" s="277" t="n"/>
+      <c r="AL29" s="278" t="n"/>
+      <c r="AM29" s="743" t="n"/>
+      <c r="AN29" s="280" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="659" t="n">
+      <c r="A30" s="742" t="n">
         <v>9</v>
       </c>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="660" t="inlineStr">
+      <c r="B30" s="278" t="n"/>
+      <c r="C30" s="305" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="663" t="inlineStr">
+      <c r="D30" s="277" t="n"/>
+      <c r="E30" s="278" t="n"/>
+      <c r="F30" s="306" t="inlineStr">
         <is>
           <t>Conditional-release authority is explicit.</t>
         </is>
       </c>
-      <c r="G30" s="12" t="n"/>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="12" t="n"/>
-      <c r="J30" s="12" t="n"/>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="12" t="n"/>
-      <c r="M30" s="12" t="n"/>
-      <c r="N30" s="12" t="n"/>
-      <c r="O30" s="12" t="n"/>
-      <c r="P30" s="12" t="n"/>
-      <c r="Q30" s="12" t="n"/>
-      <c r="R30" s="12" t="n"/>
-      <c r="S30" s="13" t="n"/>
-      <c r="T30" s="662" t="inlineStr">
+      <c r="G30" s="277" t="n"/>
+      <c r="H30" s="277" t="n"/>
+      <c r="I30" s="277" t="n"/>
+      <c r="J30" s="277" t="n"/>
+      <c r="K30" s="277" t="n"/>
+      <c r="L30" s="277" t="n"/>
+      <c r="M30" s="277" t="n"/>
+      <c r="N30" s="277" t="n"/>
+      <c r="O30" s="277" t="n"/>
+      <c r="P30" s="277" t="n"/>
+      <c r="Q30" s="277" t="n"/>
+      <c r="R30" s="277" t="n"/>
+      <c r="S30" s="278" t="n"/>
+      <c r="T30" s="307" t="inlineStr">
         <is>
           <t>No conditional release without named owner.</t>
         </is>
       </c>
-      <c r="U30" s="12" t="n"/>
-      <c r="V30" s="12" t="n"/>
-      <c r="W30" s="12" t="n"/>
-      <c r="X30" s="12" t="n"/>
-      <c r="Y30" s="12" t="n"/>
-      <c r="Z30" s="12" t="n"/>
-      <c r="AA30" s="12" t="n"/>
-      <c r="AB30" s="12" t="n"/>
-      <c r="AC30" s="12" t="n"/>
-      <c r="AD30" s="12" t="n"/>
-      <c r="AE30" s="13" t="n"/>
-      <c r="AF30" s="663" t="n"/>
-      <c r="AG30" s="12" t="n"/>
-      <c r="AH30" s="12" t="n"/>
-      <c r="AI30" s="13" t="n"/>
-      <c r="AJ30" s="663" t="n"/>
-      <c r="AK30" s="12" t="n"/>
-      <c r="AL30" s="13" t="n"/>
-      <c r="AM30" s="663" t="n"/>
-      <c r="AN30" s="15" t="n"/>
+      <c r="U30" s="277" t="n"/>
+      <c r="V30" s="277" t="n"/>
+      <c r="W30" s="277" t="n"/>
+      <c r="X30" s="277" t="n"/>
+      <c r="Y30" s="277" t="n"/>
+      <c r="Z30" s="277" t="n"/>
+      <c r="AA30" s="277" t="n"/>
+      <c r="AB30" s="277" t="n"/>
+      <c r="AC30" s="277" t="n"/>
+      <c r="AD30" s="277" t="n"/>
+      <c r="AE30" s="278" t="n"/>
+      <c r="AF30" s="306" t="n"/>
+      <c r="AG30" s="277" t="n"/>
+      <c r="AH30" s="277" t="n"/>
+      <c r="AI30" s="278" t="n"/>
+      <c r="AJ30" s="306" t="n"/>
+      <c r="AK30" s="277" t="n"/>
+      <c r="AL30" s="278" t="n"/>
+      <c r="AM30" s="743" t="n"/>
+      <c r="AN30" s="280" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="664" t="n">
+      <c r="A31" s="744" t="n">
         <v>10</v>
       </c>
-      <c r="B31" s="22" t="n"/>
-      <c r="C31" s="665" t="inlineStr">
+      <c r="B31" s="285" t="n"/>
+      <c r="C31" s="310" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="22" t="n"/>
-      <c r="F31" s="666" t="inlineStr">
+      <c r="D31" s="283" t="n"/>
+      <c r="E31" s="285" t="n"/>
+      <c r="F31" s="311" t="inlineStr">
         <is>
           <t>Evidence path and dossier traceability exist.</t>
         </is>
       </c>
-      <c r="G31" s="19" t="n"/>
-      <c r="H31" s="19" t="n"/>
-      <c r="I31" s="19" t="n"/>
-      <c r="J31" s="19" t="n"/>
-      <c r="K31" s="19" t="n"/>
-      <c r="L31" s="19" t="n"/>
-      <c r="M31" s="19" t="n"/>
-      <c r="N31" s="19" t="n"/>
-      <c r="O31" s="19" t="n"/>
-      <c r="P31" s="19" t="n"/>
-      <c r="Q31" s="19" t="n"/>
-      <c r="R31" s="19" t="n"/>
-      <c r="S31" s="22" t="n"/>
-      <c r="T31" s="667" t="inlineStr">
+      <c r="G31" s="283" t="n"/>
+      <c r="H31" s="283" t="n"/>
+      <c r="I31" s="283" t="n"/>
+      <c r="J31" s="283" t="n"/>
+      <c r="K31" s="283" t="n"/>
+      <c r="L31" s="283" t="n"/>
+      <c r="M31" s="283" t="n"/>
+      <c r="N31" s="283" t="n"/>
+      <c r="O31" s="283" t="n"/>
+      <c r="P31" s="283" t="n"/>
+      <c r="Q31" s="283" t="n"/>
+      <c r="R31" s="283" t="n"/>
+      <c r="S31" s="285" t="n"/>
+      <c r="T31" s="312" t="inlineStr">
         <is>
           <t>Decision can be reconstructed later.</t>
         </is>
       </c>
-      <c r="U31" s="19" t="n"/>
-      <c r="V31" s="19" t="n"/>
-      <c r="W31" s="19" t="n"/>
-      <c r="X31" s="19" t="n"/>
-      <c r="Y31" s="19" t="n"/>
-      <c r="Z31" s="19" t="n"/>
-      <c r="AA31" s="19" t="n"/>
-      <c r="AB31" s="19" t="n"/>
-      <c r="AC31" s="19" t="n"/>
-      <c r="AD31" s="19" t="n"/>
-      <c r="AE31" s="22" t="n"/>
-      <c r="AF31" s="668" t="n"/>
-      <c r="AG31" s="19" t="n"/>
-      <c r="AH31" s="19" t="n"/>
-      <c r="AI31" s="22" t="n"/>
-      <c r="AJ31" s="668" t="n"/>
-      <c r="AK31" s="19" t="n"/>
-      <c r="AL31" s="22" t="n"/>
-      <c r="AM31" s="668" t="n"/>
-      <c r="AN31" s="24" t="n"/>
+      <c r="U31" s="283" t="n"/>
+      <c r="V31" s="283" t="n"/>
+      <c r="W31" s="283" t="n"/>
+      <c r="X31" s="283" t="n"/>
+      <c r="Y31" s="283" t="n"/>
+      <c r="Z31" s="283" t="n"/>
+      <c r="AA31" s="283" t="n"/>
+      <c r="AB31" s="283" t="n"/>
+      <c r="AC31" s="283" t="n"/>
+      <c r="AD31" s="283" t="n"/>
+      <c r="AE31" s="285" t="n"/>
+      <c r="AF31" s="745" t="n"/>
+      <c r="AG31" s="283" t="n"/>
+      <c r="AH31" s="283" t="n"/>
+      <c r="AI31" s="285" t="n"/>
+      <c r="AJ31" s="745" t="n"/>
+      <c r="AK31" s="283" t="n"/>
+      <c r="AL31" s="285" t="n"/>
+      <c r="AM31" s="746" t="n"/>
+      <c r="AN31" s="287" t="n"/>
     </row>
     <row r="32" ht="3" customHeight="1">
       <c r="A32" s="654" t="n"/>
@@ -8820,340 +8933,340 @@
       <c r="AN32" s="10" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="647" t="inlineStr">
+      <c r="A33" s="730" t="inlineStr">
         <is>
           <t>4.  OPEN RISK ACTIONS / CONTAINMENT</t>
         </is>
       </c>
-      <c r="B33" s="27" t="n"/>
-      <c r="C33" s="27" t="n"/>
-      <c r="D33" s="27" t="n"/>
-      <c r="E33" s="27" t="n"/>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="27" t="n"/>
-      <c r="H33" s="27" t="n"/>
-      <c r="I33" s="27" t="n"/>
-      <c r="J33" s="27" t="n"/>
-      <c r="K33" s="27" t="n"/>
-      <c r="L33" s="27" t="n"/>
-      <c r="M33" s="27" t="n"/>
-      <c r="N33" s="27" t="n"/>
-      <c r="O33" s="27" t="n"/>
-      <c r="P33" s="27" t="n"/>
-      <c r="Q33" s="27" t="n"/>
-      <c r="R33" s="27" t="n"/>
-      <c r="S33" s="27" t="n"/>
-      <c r="T33" s="27" t="n"/>
-      <c r="U33" s="27" t="n"/>
-      <c r="V33" s="27" t="n"/>
-      <c r="W33" s="27" t="n"/>
-      <c r="X33" s="27" t="n"/>
-      <c r="Y33" s="27" t="n"/>
-      <c r="Z33" s="27" t="n"/>
-      <c r="AA33" s="27" t="n"/>
-      <c r="AB33" s="27" t="n"/>
-      <c r="AC33" s="27" t="n"/>
-      <c r="AD33" s="27" t="n"/>
-      <c r="AE33" s="27" t="n"/>
-      <c r="AF33" s="27" t="n"/>
-      <c r="AG33" s="27" t="n"/>
-      <c r="AH33" s="27" t="n"/>
-      <c r="AI33" s="27" t="n"/>
-      <c r="AJ33" s="27" t="n"/>
-      <c r="AK33" s="27" t="n"/>
-      <c r="AL33" s="27" t="n"/>
-      <c r="AM33" s="27" t="n"/>
-      <c r="AN33" s="28" t="n"/>
+      <c r="B33" s="289" t="n"/>
+      <c r="C33" s="289" t="n"/>
+      <c r="D33" s="289" t="n"/>
+      <c r="E33" s="289" t="n"/>
+      <c r="F33" s="289" t="n"/>
+      <c r="G33" s="289" t="n"/>
+      <c r="H33" s="289" t="n"/>
+      <c r="I33" s="289" t="n"/>
+      <c r="J33" s="289" t="n"/>
+      <c r="K33" s="289" t="n"/>
+      <c r="L33" s="289" t="n"/>
+      <c r="M33" s="289" t="n"/>
+      <c r="N33" s="289" t="n"/>
+      <c r="O33" s="289" t="n"/>
+      <c r="P33" s="289" t="n"/>
+      <c r="Q33" s="289" t="n"/>
+      <c r="R33" s="289" t="n"/>
+      <c r="S33" s="289" t="n"/>
+      <c r="T33" s="289" t="n"/>
+      <c r="U33" s="289" t="n"/>
+      <c r="V33" s="289" t="n"/>
+      <c r="W33" s="289" t="n"/>
+      <c r="X33" s="289" t="n"/>
+      <c r="Y33" s="289" t="n"/>
+      <c r="Z33" s="289" t="n"/>
+      <c r="AA33" s="289" t="n"/>
+      <c r="AB33" s="289" t="n"/>
+      <c r="AC33" s="289" t="n"/>
+      <c r="AD33" s="289" t="n"/>
+      <c r="AE33" s="289" t="n"/>
+      <c r="AF33" s="289" t="n"/>
+      <c r="AG33" s="289" t="n"/>
+      <c r="AH33" s="289" t="n"/>
+      <c r="AI33" s="289" t="n"/>
+      <c r="AJ33" s="289" t="n"/>
+      <c r="AK33" s="289" t="n"/>
+      <c r="AL33" s="289" t="n"/>
+      <c r="AM33" s="289" t="n"/>
+      <c r="AN33" s="290" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="36" t="inlineStr">
+      <c r="A34" s="301" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="37" t="inlineStr">
+      <c r="B34" s="272" t="n"/>
+      <c r="C34" s="302" t="inlineStr">
         <is>
           <t>Risk / Readiness Gap</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n"/>
-      <c r="L34" s="6" t="n"/>
-      <c r="M34" s="37" t="inlineStr">
+      <c r="D34" s="271" t="n"/>
+      <c r="E34" s="271" t="n"/>
+      <c r="F34" s="271" t="n"/>
+      <c r="G34" s="271" t="n"/>
+      <c r="H34" s="271" t="n"/>
+      <c r="I34" s="271" t="n"/>
+      <c r="J34" s="271" t="n"/>
+      <c r="K34" s="271" t="n"/>
+      <c r="L34" s="272" t="n"/>
+      <c r="M34" s="302" t="inlineStr">
         <is>
           <t>Required Containment / Action</t>
         </is>
       </c>
-      <c r="N34" s="5" t="n"/>
-      <c r="O34" s="5" t="n"/>
-      <c r="P34" s="5" t="n"/>
-      <c r="Q34" s="5" t="n"/>
-      <c r="R34" s="5" t="n"/>
-      <c r="S34" s="5" t="n"/>
-      <c r="T34" s="5" t="n"/>
-      <c r="U34" s="5" t="n"/>
-      <c r="V34" s="5" t="n"/>
-      <c r="W34" s="5" t="n"/>
-      <c r="X34" s="6" t="n"/>
-      <c r="Y34" s="37" t="inlineStr">
+      <c r="N34" s="271" t="n"/>
+      <c r="O34" s="271" t="n"/>
+      <c r="P34" s="271" t="n"/>
+      <c r="Q34" s="271" t="n"/>
+      <c r="R34" s="271" t="n"/>
+      <c r="S34" s="271" t="n"/>
+      <c r="T34" s="271" t="n"/>
+      <c r="U34" s="271" t="n"/>
+      <c r="V34" s="271" t="n"/>
+      <c r="W34" s="271" t="n"/>
+      <c r="X34" s="272" t="n"/>
+      <c r="Y34" s="302" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="Z34" s="5" t="n"/>
-      <c r="AA34" s="5" t="n"/>
-      <c r="AB34" s="5" t="n"/>
-      <c r="AC34" s="6" t="n"/>
-      <c r="AD34" s="37" t="inlineStr">
+      <c r="Z34" s="271" t="n"/>
+      <c r="AA34" s="271" t="n"/>
+      <c r="AB34" s="271" t="n"/>
+      <c r="AC34" s="272" t="n"/>
+      <c r="AD34" s="302" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="AE34" s="5" t="n"/>
-      <c r="AF34" s="5" t="n"/>
-      <c r="AG34" s="5" t="n"/>
-      <c r="AH34" s="6" t="n"/>
-      <c r="AI34" s="37" t="inlineStr">
+      <c r="AE34" s="271" t="n"/>
+      <c r="AF34" s="271" t="n"/>
+      <c r="AG34" s="271" t="n"/>
+      <c r="AH34" s="272" t="n"/>
+      <c r="AI34" s="302" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AJ34" s="5" t="n"/>
-      <c r="AK34" s="6" t="n"/>
-      <c r="AL34" s="37" t="inlineStr">
+      <c r="AJ34" s="271" t="n"/>
+      <c r="AK34" s="272" t="n"/>
+      <c r="AL34" s="303" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="AM34" s="5" t="n"/>
-      <c r="AN34" s="8" t="n"/>
+      <c r="AM34" s="271" t="n"/>
+      <c r="AN34" s="274" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="669" t="n">
+      <c r="A35" s="747" t="n">
         <v>1</v>
       </c>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="657" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
-      <c r="L35" s="6" t="n"/>
-      <c r="M35" s="657" t="n"/>
-      <c r="N35" s="5" t="n"/>
-      <c r="O35" s="5" t="n"/>
-      <c r="P35" s="5" t="n"/>
-      <c r="Q35" s="5" t="n"/>
-      <c r="R35" s="5" t="n"/>
-      <c r="S35" s="5" t="n"/>
-      <c r="T35" s="5" t="n"/>
-      <c r="U35" s="5" t="n"/>
-      <c r="V35" s="5" t="n"/>
-      <c r="W35" s="5" t="n"/>
-      <c r="X35" s="6" t="n"/>
-      <c r="Y35" s="657" t="n"/>
-      <c r="Z35" s="5" t="n"/>
-      <c r="AA35" s="5" t="n"/>
-      <c r="AB35" s="5" t="n"/>
-      <c r="AC35" s="6" t="n"/>
-      <c r="AD35" s="657" t="n"/>
-      <c r="AE35" s="5" t="n"/>
-      <c r="AF35" s="5" t="n"/>
-      <c r="AG35" s="5" t="n"/>
-      <c r="AH35" s="6" t="n"/>
-      <c r="AI35" s="657" t="n"/>
-      <c r="AJ35" s="5" t="n"/>
-      <c r="AK35" s="6" t="n"/>
-      <c r="AL35" s="657" t="n"/>
-      <c r="AM35" s="5" t="n"/>
-      <c r="AN35" s="8" t="n"/>
+      <c r="B35" s="272" t="n"/>
+      <c r="C35" s="739" t="n"/>
+      <c r="D35" s="271" t="n"/>
+      <c r="E35" s="271" t="n"/>
+      <c r="F35" s="271" t="n"/>
+      <c r="G35" s="271" t="n"/>
+      <c r="H35" s="271" t="n"/>
+      <c r="I35" s="271" t="n"/>
+      <c r="J35" s="271" t="n"/>
+      <c r="K35" s="271" t="n"/>
+      <c r="L35" s="272" t="n"/>
+      <c r="M35" s="739" t="n"/>
+      <c r="N35" s="271" t="n"/>
+      <c r="O35" s="271" t="n"/>
+      <c r="P35" s="271" t="n"/>
+      <c r="Q35" s="271" t="n"/>
+      <c r="R35" s="271" t="n"/>
+      <c r="S35" s="271" t="n"/>
+      <c r="T35" s="271" t="n"/>
+      <c r="U35" s="271" t="n"/>
+      <c r="V35" s="271" t="n"/>
+      <c r="W35" s="271" t="n"/>
+      <c r="X35" s="272" t="n"/>
+      <c r="Y35" s="739" t="n"/>
+      <c r="Z35" s="271" t="n"/>
+      <c r="AA35" s="271" t="n"/>
+      <c r="AB35" s="271" t="n"/>
+      <c r="AC35" s="272" t="n"/>
+      <c r="AD35" s="739" t="n"/>
+      <c r="AE35" s="271" t="n"/>
+      <c r="AF35" s="271" t="n"/>
+      <c r="AG35" s="271" t="n"/>
+      <c r="AH35" s="272" t="n"/>
+      <c r="AI35" s="739" t="n"/>
+      <c r="AJ35" s="271" t="n"/>
+      <c r="AK35" s="272" t="n"/>
+      <c r="AL35" s="741" t="n"/>
+      <c r="AM35" s="271" t="n"/>
+      <c r="AN35" s="274" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="670" t="n">
+      <c r="A36" s="748" t="n">
         <v>2</v>
       </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="663" t="n"/>
-      <c r="D36" s="12" t="n"/>
-      <c r="E36" s="12" t="n"/>
-      <c r="F36" s="12" t="n"/>
-      <c r="G36" s="12" t="n"/>
-      <c r="H36" s="12" t="n"/>
-      <c r="I36" s="12" t="n"/>
-      <c r="J36" s="12" t="n"/>
-      <c r="K36" s="12" t="n"/>
-      <c r="L36" s="13" t="n"/>
-      <c r="M36" s="663" t="n"/>
-      <c r="N36" s="12" t="n"/>
-      <c r="O36" s="12" t="n"/>
-      <c r="P36" s="12" t="n"/>
-      <c r="Q36" s="12" t="n"/>
-      <c r="R36" s="12" t="n"/>
-      <c r="S36" s="12" t="n"/>
-      <c r="T36" s="12" t="n"/>
-      <c r="U36" s="12" t="n"/>
-      <c r="V36" s="12" t="n"/>
-      <c r="W36" s="12" t="n"/>
-      <c r="X36" s="13" t="n"/>
-      <c r="Y36" s="663" t="n"/>
-      <c r="Z36" s="12" t="n"/>
-      <c r="AA36" s="12" t="n"/>
-      <c r="AB36" s="12" t="n"/>
-      <c r="AC36" s="13" t="n"/>
-      <c r="AD36" s="663" t="n"/>
-      <c r="AE36" s="12" t="n"/>
-      <c r="AF36" s="12" t="n"/>
-      <c r="AG36" s="12" t="n"/>
-      <c r="AH36" s="13" t="n"/>
-      <c r="AI36" s="663" t="n"/>
-      <c r="AJ36" s="12" t="n"/>
-      <c r="AK36" s="13" t="n"/>
-      <c r="AL36" s="663" t="n"/>
-      <c r="AM36" s="12" t="n"/>
-      <c r="AN36" s="15" t="n"/>
+      <c r="B36" s="278" t="n"/>
+      <c r="C36" s="306" t="n"/>
+      <c r="D36" s="277" t="n"/>
+      <c r="E36" s="277" t="n"/>
+      <c r="F36" s="277" t="n"/>
+      <c r="G36" s="277" t="n"/>
+      <c r="H36" s="277" t="n"/>
+      <c r="I36" s="277" t="n"/>
+      <c r="J36" s="277" t="n"/>
+      <c r="K36" s="277" t="n"/>
+      <c r="L36" s="278" t="n"/>
+      <c r="M36" s="306" t="n"/>
+      <c r="N36" s="277" t="n"/>
+      <c r="O36" s="277" t="n"/>
+      <c r="P36" s="277" t="n"/>
+      <c r="Q36" s="277" t="n"/>
+      <c r="R36" s="277" t="n"/>
+      <c r="S36" s="277" t="n"/>
+      <c r="T36" s="277" t="n"/>
+      <c r="U36" s="277" t="n"/>
+      <c r="V36" s="277" t="n"/>
+      <c r="W36" s="277" t="n"/>
+      <c r="X36" s="278" t="n"/>
+      <c r="Y36" s="306" t="n"/>
+      <c r="Z36" s="277" t="n"/>
+      <c r="AA36" s="277" t="n"/>
+      <c r="AB36" s="277" t="n"/>
+      <c r="AC36" s="278" t="n"/>
+      <c r="AD36" s="306" t="n"/>
+      <c r="AE36" s="277" t="n"/>
+      <c r="AF36" s="277" t="n"/>
+      <c r="AG36" s="277" t="n"/>
+      <c r="AH36" s="278" t="n"/>
+      <c r="AI36" s="306" t="n"/>
+      <c r="AJ36" s="277" t="n"/>
+      <c r="AK36" s="278" t="n"/>
+      <c r="AL36" s="743" t="n"/>
+      <c r="AM36" s="277" t="n"/>
+      <c r="AN36" s="280" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="670" t="n">
+      <c r="A37" s="748" t="n">
         <v>3</v>
       </c>
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="663" t="n"/>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n"/>
-      <c r="G37" s="12" t="n"/>
-      <c r="H37" s="12" t="n"/>
-      <c r="I37" s="12" t="n"/>
-      <c r="J37" s="12" t="n"/>
-      <c r="K37" s="12" t="n"/>
-      <c r="L37" s="13" t="n"/>
-      <c r="M37" s="663" t="n"/>
-      <c r="N37" s="12" t="n"/>
-      <c r="O37" s="12" t="n"/>
-      <c r="P37" s="12" t="n"/>
-      <c r="Q37" s="12" t="n"/>
-      <c r="R37" s="12" t="n"/>
-      <c r="S37" s="12" t="n"/>
-      <c r="T37" s="12" t="n"/>
-      <c r="U37" s="12" t="n"/>
-      <c r="V37" s="12" t="n"/>
-      <c r="W37" s="12" t="n"/>
-      <c r="X37" s="13" t="n"/>
-      <c r="Y37" s="663" t="n"/>
-      <c r="Z37" s="12" t="n"/>
-      <c r="AA37" s="12" t="n"/>
-      <c r="AB37" s="12" t="n"/>
-      <c r="AC37" s="13" t="n"/>
-      <c r="AD37" s="663" t="n"/>
-      <c r="AE37" s="12" t="n"/>
-      <c r="AF37" s="12" t="n"/>
-      <c r="AG37" s="12" t="n"/>
-      <c r="AH37" s="13" t="n"/>
-      <c r="AI37" s="663" t="n"/>
-      <c r="AJ37" s="12" t="n"/>
-      <c r="AK37" s="13" t="n"/>
-      <c r="AL37" s="663" t="n"/>
-      <c r="AM37" s="12" t="n"/>
-      <c r="AN37" s="15" t="n"/>
+      <c r="B37" s="278" t="n"/>
+      <c r="C37" s="306" t="n"/>
+      <c r="D37" s="277" t="n"/>
+      <c r="E37" s="277" t="n"/>
+      <c r="F37" s="277" t="n"/>
+      <c r="G37" s="277" t="n"/>
+      <c r="H37" s="277" t="n"/>
+      <c r="I37" s="277" t="n"/>
+      <c r="J37" s="277" t="n"/>
+      <c r="K37" s="277" t="n"/>
+      <c r="L37" s="278" t="n"/>
+      <c r="M37" s="306" t="n"/>
+      <c r="N37" s="277" t="n"/>
+      <c r="O37" s="277" t="n"/>
+      <c r="P37" s="277" t="n"/>
+      <c r="Q37" s="277" t="n"/>
+      <c r="R37" s="277" t="n"/>
+      <c r="S37" s="277" t="n"/>
+      <c r="T37" s="277" t="n"/>
+      <c r="U37" s="277" t="n"/>
+      <c r="V37" s="277" t="n"/>
+      <c r="W37" s="277" t="n"/>
+      <c r="X37" s="278" t="n"/>
+      <c r="Y37" s="306" t="n"/>
+      <c r="Z37" s="277" t="n"/>
+      <c r="AA37" s="277" t="n"/>
+      <c r="AB37" s="277" t="n"/>
+      <c r="AC37" s="278" t="n"/>
+      <c r="AD37" s="306" t="n"/>
+      <c r="AE37" s="277" t="n"/>
+      <c r="AF37" s="277" t="n"/>
+      <c r="AG37" s="277" t="n"/>
+      <c r="AH37" s="278" t="n"/>
+      <c r="AI37" s="306" t="n"/>
+      <c r="AJ37" s="277" t="n"/>
+      <c r="AK37" s="278" t="n"/>
+      <c r="AL37" s="743" t="n"/>
+      <c r="AM37" s="277" t="n"/>
+      <c r="AN37" s="280" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="670" t="n">
+      <c r="A38" s="748" t="n">
         <v>4</v>
       </c>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="663" t="n"/>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="12" t="n"/>
-      <c r="G38" s="12" t="n"/>
-      <c r="H38" s="12" t="n"/>
-      <c r="I38" s="12" t="n"/>
-      <c r="J38" s="12" t="n"/>
-      <c r="K38" s="12" t="n"/>
-      <c r="L38" s="13" t="n"/>
-      <c r="M38" s="663" t="n"/>
-      <c r="N38" s="12" t="n"/>
-      <c r="O38" s="12" t="n"/>
-      <c r="P38" s="12" t="n"/>
-      <c r="Q38" s="12" t="n"/>
-      <c r="R38" s="12" t="n"/>
-      <c r="S38" s="12" t="n"/>
-      <c r="T38" s="12" t="n"/>
-      <c r="U38" s="12" t="n"/>
-      <c r="V38" s="12" t="n"/>
-      <c r="W38" s="12" t="n"/>
-      <c r="X38" s="13" t="n"/>
-      <c r="Y38" s="663" t="n"/>
-      <c r="Z38" s="12" t="n"/>
-      <c r="AA38" s="12" t="n"/>
-      <c r="AB38" s="12" t="n"/>
-      <c r="AC38" s="13" t="n"/>
-      <c r="AD38" s="663" t="n"/>
-      <c r="AE38" s="12" t="n"/>
-      <c r="AF38" s="12" t="n"/>
-      <c r="AG38" s="12" t="n"/>
-      <c r="AH38" s="13" t="n"/>
-      <c r="AI38" s="663" t="n"/>
-      <c r="AJ38" s="12" t="n"/>
-      <c r="AK38" s="13" t="n"/>
-      <c r="AL38" s="663" t="n"/>
-      <c r="AM38" s="12" t="n"/>
-      <c r="AN38" s="15" t="n"/>
+      <c r="B38" s="278" t="n"/>
+      <c r="C38" s="306" t="n"/>
+      <c r="D38" s="277" t="n"/>
+      <c r="E38" s="277" t="n"/>
+      <c r="F38" s="277" t="n"/>
+      <c r="G38" s="277" t="n"/>
+      <c r="H38" s="277" t="n"/>
+      <c r="I38" s="277" t="n"/>
+      <c r="J38" s="277" t="n"/>
+      <c r="K38" s="277" t="n"/>
+      <c r="L38" s="278" t="n"/>
+      <c r="M38" s="306" t="n"/>
+      <c r="N38" s="277" t="n"/>
+      <c r="O38" s="277" t="n"/>
+      <c r="P38" s="277" t="n"/>
+      <c r="Q38" s="277" t="n"/>
+      <c r="R38" s="277" t="n"/>
+      <c r="S38" s="277" t="n"/>
+      <c r="T38" s="277" t="n"/>
+      <c r="U38" s="277" t="n"/>
+      <c r="V38" s="277" t="n"/>
+      <c r="W38" s="277" t="n"/>
+      <c r="X38" s="278" t="n"/>
+      <c r="Y38" s="306" t="n"/>
+      <c r="Z38" s="277" t="n"/>
+      <c r="AA38" s="277" t="n"/>
+      <c r="AB38" s="277" t="n"/>
+      <c r="AC38" s="278" t="n"/>
+      <c r="AD38" s="306" t="n"/>
+      <c r="AE38" s="277" t="n"/>
+      <c r="AF38" s="277" t="n"/>
+      <c r="AG38" s="277" t="n"/>
+      <c r="AH38" s="278" t="n"/>
+      <c r="AI38" s="306" t="n"/>
+      <c r="AJ38" s="277" t="n"/>
+      <c r="AK38" s="278" t="n"/>
+      <c r="AL38" s="743" t="n"/>
+      <c r="AM38" s="277" t="n"/>
+      <c r="AN38" s="280" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="671" t="n">
+      <c r="A39" s="749" t="n">
         <v>5</v>
       </c>
-      <c r="B39" s="22" t="n"/>
-      <c r="C39" s="668" t="n"/>
-      <c r="D39" s="19" t="n"/>
-      <c r="E39" s="19" t="n"/>
-      <c r="F39" s="19" t="n"/>
-      <c r="G39" s="19" t="n"/>
-      <c r="H39" s="19" t="n"/>
-      <c r="I39" s="19" t="n"/>
-      <c r="J39" s="19" t="n"/>
-      <c r="K39" s="19" t="n"/>
-      <c r="L39" s="22" t="n"/>
-      <c r="M39" s="668" t="n"/>
-      <c r="N39" s="19" t="n"/>
-      <c r="O39" s="19" t="n"/>
-      <c r="P39" s="19" t="n"/>
-      <c r="Q39" s="19" t="n"/>
-      <c r="R39" s="19" t="n"/>
-      <c r="S39" s="19" t="n"/>
-      <c r="T39" s="19" t="n"/>
-      <c r="U39" s="19" t="n"/>
-      <c r="V39" s="19" t="n"/>
-      <c r="W39" s="19" t="n"/>
-      <c r="X39" s="22" t="n"/>
-      <c r="Y39" s="668" t="n"/>
-      <c r="Z39" s="19" t="n"/>
-      <c r="AA39" s="19" t="n"/>
-      <c r="AB39" s="19" t="n"/>
-      <c r="AC39" s="22" t="n"/>
-      <c r="AD39" s="668" t="n"/>
-      <c r="AE39" s="19" t="n"/>
-      <c r="AF39" s="19" t="n"/>
-      <c r="AG39" s="19" t="n"/>
-      <c r="AH39" s="22" t="n"/>
-      <c r="AI39" s="668" t="n"/>
-      <c r="AJ39" s="19" t="n"/>
-      <c r="AK39" s="22" t="n"/>
-      <c r="AL39" s="668" t="n"/>
-      <c r="AM39" s="19" t="n"/>
-      <c r="AN39" s="24" t="n"/>
+      <c r="B39" s="285" t="n"/>
+      <c r="C39" s="745" t="n"/>
+      <c r="D39" s="283" t="n"/>
+      <c r="E39" s="283" t="n"/>
+      <c r="F39" s="283" t="n"/>
+      <c r="G39" s="283" t="n"/>
+      <c r="H39" s="283" t="n"/>
+      <c r="I39" s="283" t="n"/>
+      <c r="J39" s="283" t="n"/>
+      <c r="K39" s="283" t="n"/>
+      <c r="L39" s="285" t="n"/>
+      <c r="M39" s="745" t="n"/>
+      <c r="N39" s="283" t="n"/>
+      <c r="O39" s="283" t="n"/>
+      <c r="P39" s="283" t="n"/>
+      <c r="Q39" s="283" t="n"/>
+      <c r="R39" s="283" t="n"/>
+      <c r="S39" s="283" t="n"/>
+      <c r="T39" s="283" t="n"/>
+      <c r="U39" s="283" t="n"/>
+      <c r="V39" s="283" t="n"/>
+      <c r="W39" s="283" t="n"/>
+      <c r="X39" s="285" t="n"/>
+      <c r="Y39" s="745" t="n"/>
+      <c r="Z39" s="283" t="n"/>
+      <c r="AA39" s="283" t="n"/>
+      <c r="AB39" s="283" t="n"/>
+      <c r="AC39" s="285" t="n"/>
+      <c r="AD39" s="745" t="n"/>
+      <c r="AE39" s="283" t="n"/>
+      <c r="AF39" s="283" t="n"/>
+      <c r="AG39" s="283" t="n"/>
+      <c r="AH39" s="285" t="n"/>
+      <c r="AI39" s="745" t="n"/>
+      <c r="AJ39" s="283" t="n"/>
+      <c r="AK39" s="285" t="n"/>
+      <c r="AL39" s="746" t="n"/>
+      <c r="AM39" s="283" t="n"/>
+      <c r="AN39" s="287" t="n"/>
     </row>
     <row r="40" ht="3" customHeight="1">
       <c r="A40" s="654" t="n"/>
@@ -9198,242 +9311,172 @@
       <c r="AN40" s="10" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="647" t="inlineStr">
+      <c r="A41" s="730" t="inlineStr">
         <is>
           <t>5.  APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B41" s="27" t="n"/>
-      <c r="C41" s="27" t="n"/>
-      <c r="D41" s="27" t="n"/>
-      <c r="E41" s="27" t="n"/>
-      <c r="F41" s="27" t="n"/>
-      <c r="G41" s="27" t="n"/>
-      <c r="H41" s="27" t="n"/>
-      <c r="I41" s="27" t="n"/>
-      <c r="J41" s="27" t="n"/>
-      <c r="K41" s="27" t="n"/>
-      <c r="L41" s="27" t="n"/>
-      <c r="M41" s="27" t="n"/>
-      <c r="N41" s="27" t="n"/>
-      <c r="O41" s="27" t="n"/>
-      <c r="P41" s="27" t="n"/>
-      <c r="Q41" s="27" t="n"/>
-      <c r="R41" s="27" t="n"/>
-      <c r="S41" s="27" t="n"/>
-      <c r="T41" s="27" t="n"/>
-      <c r="U41" s="27" t="n"/>
-      <c r="V41" s="27" t="n"/>
-      <c r="W41" s="27" t="n"/>
-      <c r="X41" s="27" t="n"/>
-      <c r="Y41" s="27" t="n"/>
-      <c r="Z41" s="27" t="n"/>
-      <c r="AA41" s="27" t="n"/>
-      <c r="AB41" s="27" t="n"/>
-      <c r="AC41" s="27" t="n"/>
-      <c r="AD41" s="27" t="n"/>
-      <c r="AE41" s="27" t="n"/>
-      <c r="AF41" s="27" t="n"/>
-      <c r="AG41" s="27" t="n"/>
-      <c r="AH41" s="27" t="n"/>
-      <c r="AI41" s="27" t="n"/>
-      <c r="AJ41" s="27" t="n"/>
-      <c r="AK41" s="27" t="n"/>
-      <c r="AL41" s="27" t="n"/>
-      <c r="AM41" s="27" t="n"/>
-      <c r="AN41" s="28" t="n"/>
+      <c r="B41" s="289" t="n"/>
+      <c r="C41" s="289" t="n"/>
+      <c r="D41" s="289" t="n"/>
+      <c r="E41" s="289" t="n"/>
+      <c r="F41" s="289" t="n"/>
+      <c r="G41" s="289" t="n"/>
+      <c r="H41" s="289" t="n"/>
+      <c r="I41" s="289" t="n"/>
+      <c r="J41" s="289" t="n"/>
+      <c r="K41" s="289" t="n"/>
+      <c r="L41" s="289" t="n"/>
+      <c r="M41" s="289" t="n"/>
+      <c r="N41" s="289" t="n"/>
+      <c r="O41" s="289" t="n"/>
+      <c r="P41" s="289" t="n"/>
+      <c r="Q41" s="289" t="n"/>
+      <c r="R41" s="289" t="n"/>
+      <c r="S41" s="289" t="n"/>
+      <c r="T41" s="289" t="n"/>
+      <c r="U41" s="289" t="n"/>
+      <c r="V41" s="289" t="n"/>
+      <c r="W41" s="289" t="n"/>
+      <c r="X41" s="289" t="n"/>
+      <c r="Y41" s="289" t="n"/>
+      <c r="Z41" s="289" t="n"/>
+      <c r="AA41" s="289" t="n"/>
+      <c r="AB41" s="289" t="n"/>
+      <c r="AC41" s="289" t="n"/>
+      <c r="AD41" s="289" t="n"/>
+      <c r="AE41" s="289" t="n"/>
+      <c r="AF41" s="289" t="n"/>
+      <c r="AG41" s="289" t="n"/>
+      <c r="AH41" s="289" t="n"/>
+      <c r="AI41" s="289" t="n"/>
+      <c r="AJ41" s="289" t="n"/>
+      <c r="AK41" s="289" t="n"/>
+      <c r="AL41" s="289" t="n"/>
+      <c r="AM41" s="289" t="n"/>
+      <c r="AN41" s="290" t="n"/>
     </row>
     <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="655" t="inlineStr">
+      <c r="A42" s="737" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="6" t="n"/>
-      <c r="N42" s="672" t="inlineStr">
+      <c r="B42" s="271" t="n"/>
+      <c r="C42" s="271" t="n"/>
+      <c r="D42" s="271" t="n"/>
+      <c r="E42" s="271" t="n"/>
+      <c r="F42" s="271" t="n"/>
+      <c r="G42" s="271" t="n"/>
+      <c r="H42" s="271" t="n"/>
+      <c r="I42" s="271" t="n"/>
+      <c r="J42" s="271" t="n"/>
+      <c r="K42" s="271" t="n"/>
+      <c r="L42" s="271" t="n"/>
+      <c r="M42" s="272" t="n"/>
+      <c r="N42" s="750" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="O42" s="5" t="n"/>
-      <c r="P42" s="5" t="n"/>
-      <c r="Q42" s="5" t="n"/>
-      <c r="R42" s="5" t="n"/>
-      <c r="S42" s="5" t="n"/>
-      <c r="T42" s="5" t="n"/>
-      <c r="U42" s="5" t="n"/>
-      <c r="V42" s="5" t="n"/>
-      <c r="W42" s="5" t="n"/>
-      <c r="X42" s="5" t="n"/>
-      <c r="Y42" s="5" t="n"/>
-      <c r="Z42" s="6" t="n"/>
-      <c r="AA42" s="672" t="inlineStr">
+      <c r="O42" s="271" t="n"/>
+      <c r="P42" s="271" t="n"/>
+      <c r="Q42" s="271" t="n"/>
+      <c r="R42" s="271" t="n"/>
+      <c r="S42" s="271" t="n"/>
+      <c r="T42" s="271" t="n"/>
+      <c r="U42" s="271" t="n"/>
+      <c r="V42" s="271" t="n"/>
+      <c r="W42" s="271" t="n"/>
+      <c r="X42" s="271" t="n"/>
+      <c r="Y42" s="271" t="n"/>
+      <c r="Z42" s="272" t="n"/>
+      <c r="AA42" s="751" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AB42" s="5" t="n"/>
-      <c r="AC42" s="5" t="n"/>
-      <c r="AD42" s="5" t="n"/>
-      <c r="AE42" s="5" t="n"/>
-      <c r="AF42" s="5" t="n"/>
-      <c r="AG42" s="5" t="n"/>
-      <c r="AH42" s="5" t="n"/>
-      <c r="AI42" s="5" t="n"/>
-      <c r="AJ42" s="5" t="n"/>
-      <c r="AK42" s="5" t="n"/>
-      <c r="AL42" s="5" t="n"/>
-      <c r="AM42" s="5" t="n"/>
-      <c r="AN42" s="8" t="n"/>
+      <c r="AB42" s="271" t="n"/>
+      <c r="AC42" s="271" t="n"/>
+      <c r="AD42" s="271" t="n"/>
+      <c r="AE42" s="271" t="n"/>
+      <c r="AF42" s="271" t="n"/>
+      <c r="AG42" s="271" t="n"/>
+      <c r="AH42" s="271" t="n"/>
+      <c r="AI42" s="271" t="n"/>
+      <c r="AJ42" s="271" t="n"/>
+      <c r="AK42" s="271" t="n"/>
+      <c r="AL42" s="271" t="n"/>
+      <c r="AM42" s="271" t="n"/>
+      <c r="AN42" s="274" t="n"/>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="673" t="inlineStr">
+      <c r="A43" s="752" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="12" t="n"/>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="12" t="n"/>
-      <c r="G43" s="12" t="n"/>
-      <c r="H43" s="12" t="n"/>
-      <c r="I43" s="12" t="n"/>
-      <c r="J43" s="12" t="n"/>
-      <c r="K43" s="12" t="n"/>
-      <c r="L43" s="12" t="n"/>
-      <c r="M43" s="13" t="n"/>
-      <c r="N43" s="674" t="inlineStr">
+      <c r="M43" s="753" t="n"/>
+      <c r="N43" s="754" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="O43" s="12" t="n"/>
-      <c r="P43" s="12" t="n"/>
-      <c r="Q43" s="12" t="n"/>
-      <c r="R43" s="12" t="n"/>
-      <c r="S43" s="12" t="n"/>
-      <c r="T43" s="12" t="n"/>
-      <c r="U43" s="12" t="n"/>
-      <c r="V43" s="12" t="n"/>
-      <c r="W43" s="12" t="n"/>
-      <c r="X43" s="12" t="n"/>
-      <c r="Y43" s="12" t="n"/>
-      <c r="Z43" s="13" t="n"/>
-      <c r="AA43" s="674" t="inlineStr">
+      <c r="Z43" s="753" t="n"/>
+      <c r="AA43" s="755" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="AB43" s="12" t="n"/>
-      <c r="AC43" s="12" t="n"/>
-      <c r="AD43" s="12" t="n"/>
-      <c r="AE43" s="12" t="n"/>
-      <c r="AF43" s="12" t="n"/>
-      <c r="AG43" s="12" t="n"/>
-      <c r="AH43" s="12" t="n"/>
-      <c r="AI43" s="12" t="n"/>
-      <c r="AJ43" s="12" t="n"/>
-      <c r="AK43" s="12" t="n"/>
-      <c r="AL43" s="12" t="n"/>
-      <c r="AM43" s="12" t="n"/>
-      <c r="AN43" s="15" t="n"/>
+      <c r="AN43" s="320" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="16" t="n"/>
-      <c r="B44" s="12" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="12" t="n"/>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="12" t="n"/>
-      <c r="G44" s="12" t="n"/>
-      <c r="H44" s="12" t="n"/>
-      <c r="I44" s="12" t="n"/>
-      <c r="J44" s="12" t="n"/>
-      <c r="K44" s="12" t="n"/>
-      <c r="L44" s="12" t="n"/>
-      <c r="M44" s="13" t="n"/>
-      <c r="N44" s="12" t="n"/>
-      <c r="O44" s="12" t="n"/>
-      <c r="P44" s="12" t="n"/>
-      <c r="Q44" s="12" t="n"/>
-      <c r="R44" s="12" t="n"/>
-      <c r="S44" s="12" t="n"/>
-      <c r="T44" s="12" t="n"/>
-      <c r="U44" s="12" t="n"/>
-      <c r="V44" s="12" t="n"/>
-      <c r="W44" s="12" t="n"/>
-      <c r="X44" s="12" t="n"/>
-      <c r="Y44" s="12" t="n"/>
-      <c r="Z44" s="13" t="n"/>
-      <c r="AA44" s="12" t="n"/>
-      <c r="AB44" s="12" t="n"/>
-      <c r="AC44" s="12" t="n"/>
-      <c r="AD44" s="12" t="n"/>
-      <c r="AE44" s="12" t="n"/>
-      <c r="AF44" s="12" t="n"/>
-      <c r="AG44" s="12" t="n"/>
-      <c r="AH44" s="12" t="n"/>
-      <c r="AI44" s="12" t="n"/>
-      <c r="AJ44" s="12" t="n"/>
-      <c r="AK44" s="12" t="n"/>
-      <c r="AL44" s="12" t="n"/>
-      <c r="AM44" s="12" t="n"/>
-      <c r="AN44" s="15" t="n"/>
+      <c r="A44" s="275" t="n"/>
+      <c r="M44" s="753" t="n"/>
+      <c r="Z44" s="753" t="n"/>
+      <c r="AN44" s="320" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="18" t="n"/>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-      <c r="E45" s="19" t="n"/>
-      <c r="F45" s="19" t="n"/>
-      <c r="G45" s="19" t="n"/>
-      <c r="H45" s="19" t="n"/>
-      <c r="I45" s="19" t="n"/>
-      <c r="J45" s="19" t="n"/>
-      <c r="K45" s="19" t="n"/>
-      <c r="L45" s="19" t="n"/>
-      <c r="M45" s="22" t="n"/>
-      <c r="N45" s="19" t="n"/>
-      <c r="O45" s="19" t="n"/>
-      <c r="P45" s="19" t="n"/>
-      <c r="Q45" s="19" t="n"/>
-      <c r="R45" s="19" t="n"/>
-      <c r="S45" s="19" t="n"/>
-      <c r="T45" s="19" t="n"/>
-      <c r="U45" s="19" t="n"/>
-      <c r="V45" s="19" t="n"/>
-      <c r="W45" s="19" t="n"/>
-      <c r="X45" s="19" t="n"/>
-      <c r="Y45" s="19" t="n"/>
-      <c r="Z45" s="22" t="n"/>
-      <c r="AA45" s="19" t="n"/>
-      <c r="AB45" s="19" t="n"/>
-      <c r="AC45" s="19" t="n"/>
-      <c r="AD45" s="19" t="n"/>
-      <c r="AE45" s="19" t="n"/>
-      <c r="AF45" s="19" t="n"/>
-      <c r="AG45" s="19" t="n"/>
-      <c r="AH45" s="19" t="n"/>
-      <c r="AI45" s="19" t="n"/>
-      <c r="AJ45" s="19" t="n"/>
-      <c r="AK45" s="19" t="n"/>
-      <c r="AL45" s="19" t="n"/>
-      <c r="AM45" s="19" t="n"/>
-      <c r="AN45" s="24" t="n"/>
+      <c r="A45" s="281" t="n"/>
+      <c r="B45" s="277" t="n"/>
+      <c r="C45" s="277" t="n"/>
+      <c r="D45" s="277" t="n"/>
+      <c r="E45" s="277" t="n"/>
+      <c r="F45" s="277" t="n"/>
+      <c r="G45" s="277" t="n"/>
+      <c r="H45" s="277" t="n"/>
+      <c r="I45" s="277" t="n"/>
+      <c r="J45" s="277" t="n"/>
+      <c r="K45" s="277" t="n"/>
+      <c r="L45" s="277" t="n"/>
+      <c r="M45" s="278" t="n"/>
+      <c r="N45" s="277" t="n"/>
+      <c r="O45" s="277" t="n"/>
+      <c r="P45" s="277" t="n"/>
+      <c r="Q45" s="277" t="n"/>
+      <c r="R45" s="277" t="n"/>
+      <c r="S45" s="277" t="n"/>
+      <c r="T45" s="277" t="n"/>
+      <c r="U45" s="277" t="n"/>
+      <c r="V45" s="277" t="n"/>
+      <c r="W45" s="277" t="n"/>
+      <c r="X45" s="277" t="n"/>
+      <c r="Y45" s="277" t="n"/>
+      <c r="Z45" s="278" t="n"/>
+      <c r="AA45" s="277" t="n"/>
+      <c r="AB45" s="277" t="n"/>
+      <c r="AC45" s="277" t="n"/>
+      <c r="AD45" s="277" t="n"/>
+      <c r="AE45" s="277" t="n"/>
+      <c r="AF45" s="277" t="n"/>
+      <c r="AG45" s="277" t="n"/>
+      <c r="AH45" s="277" t="n"/>
+      <c r="AI45" s="277" t="n"/>
+      <c r="AJ45" s="277" t="n"/>
+      <c r="AK45" s="277" t="n"/>
+      <c r="AL45" s="277" t="n"/>
+      <c r="AM45" s="277" t="n"/>
+      <c r="AN45" s="280" t="n"/>
     </row>
     <row r="46" ht="3" customHeight="1">
       <c r="A46" s="654" t="n"/>
@@ -9478,50 +9521,50 @@
       <c r="AN46" s="10" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="647" t="inlineStr">
+      <c r="A47" s="730" t="inlineStr">
         <is>
           <t>NOTICE  —  Enter data only in designated white input cells. Do not add, delete or resize columns/rows. File naming: FRM-209_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="27" t="n"/>
-      <c r="C47" s="27" t="n"/>
-      <c r="D47" s="27" t="n"/>
-      <c r="E47" s="27" t="n"/>
-      <c r="F47" s="27" t="n"/>
-      <c r="G47" s="27" t="n"/>
-      <c r="H47" s="27" t="n"/>
-      <c r="I47" s="27" t="n"/>
-      <c r="J47" s="27" t="n"/>
-      <c r="K47" s="27" t="n"/>
-      <c r="L47" s="27" t="n"/>
-      <c r="M47" s="27" t="n"/>
-      <c r="N47" s="27" t="n"/>
-      <c r="O47" s="27" t="n"/>
-      <c r="P47" s="27" t="n"/>
-      <c r="Q47" s="27" t="n"/>
-      <c r="R47" s="27" t="n"/>
-      <c r="S47" s="27" t="n"/>
-      <c r="T47" s="27" t="n"/>
-      <c r="U47" s="27" t="n"/>
-      <c r="V47" s="27" t="n"/>
-      <c r="W47" s="27" t="n"/>
-      <c r="X47" s="27" t="n"/>
-      <c r="Y47" s="27" t="n"/>
-      <c r="Z47" s="27" t="n"/>
-      <c r="AA47" s="27" t="n"/>
-      <c r="AB47" s="27" t="n"/>
-      <c r="AC47" s="27" t="n"/>
-      <c r="AD47" s="27" t="n"/>
-      <c r="AE47" s="27" t="n"/>
-      <c r="AF47" s="27" t="n"/>
-      <c r="AG47" s="27" t="n"/>
-      <c r="AH47" s="27" t="n"/>
-      <c r="AI47" s="27" t="n"/>
-      <c r="AJ47" s="27" t="n"/>
-      <c r="AK47" s="27" t="n"/>
-      <c r="AL47" s="27" t="n"/>
-      <c r="AM47" s="27" t="n"/>
-      <c r="AN47" s="28" t="n"/>
+      <c r="B47" s="289" t="n"/>
+      <c r="C47" s="289" t="n"/>
+      <c r="D47" s="289" t="n"/>
+      <c r="E47" s="289" t="n"/>
+      <c r="F47" s="289" t="n"/>
+      <c r="G47" s="289" t="n"/>
+      <c r="H47" s="289" t="n"/>
+      <c r="I47" s="289" t="n"/>
+      <c r="J47" s="289" t="n"/>
+      <c r="K47" s="289" t="n"/>
+      <c r="L47" s="289" t="n"/>
+      <c r="M47" s="289" t="n"/>
+      <c r="N47" s="289" t="n"/>
+      <c r="O47" s="289" t="n"/>
+      <c r="P47" s="289" t="n"/>
+      <c r="Q47" s="289" t="n"/>
+      <c r="R47" s="289" t="n"/>
+      <c r="S47" s="289" t="n"/>
+      <c r="T47" s="289" t="n"/>
+      <c r="U47" s="289" t="n"/>
+      <c r="V47" s="289" t="n"/>
+      <c r="W47" s="289" t="n"/>
+      <c r="X47" s="289" t="n"/>
+      <c r="Y47" s="289" t="n"/>
+      <c r="Z47" s="289" t="n"/>
+      <c r="AA47" s="289" t="n"/>
+      <c r="AB47" s="289" t="n"/>
+      <c r="AC47" s="289" t="n"/>
+      <c r="AD47" s="289" t="n"/>
+      <c r="AE47" s="289" t="n"/>
+      <c r="AF47" s="289" t="n"/>
+      <c r="AG47" s="289" t="n"/>
+      <c r="AH47" s="289" t="n"/>
+      <c r="AI47" s="289" t="n"/>
+      <c r="AJ47" s="289" t="n"/>
+      <c r="AK47" s="289" t="n"/>
+      <c r="AL47" s="289" t="n"/>
+      <c r="AM47" s="289" t="n"/>
+      <c r="AN47" s="290" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="1"/>
     <row r="49" hidden="1" outlineLevel="1"/>
@@ -9998,7 +10041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU7"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -10630,7 +10673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU6"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -11251,17 +11294,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="333" t="n"/>
-      <c r="B1" s="53" t="n"/>
+      <c r="A1" s="386" t="n"/>
+      <c r="B1" s="319" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
           <t>RISKS / ACTIONS REGISTER</t>
         </is>
       </c>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
+      <c r="D1" s="268" t="n"/>
+      <c r="E1" s="268" t="n"/>
+      <c r="F1" s="268" t="n"/>
+      <c r="G1" s="268" t="n"/>
       <c r="H1" s="675" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -11305,13 +11348,9 @@
       <c r="AN1" s="678" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="B2" s="54" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
+      <c r="A2" s="275" t="n"/>
+      <c r="B2" s="320" t="n"/>
+      <c r="C2" s="275" t="n"/>
       <c r="H2" s="679" t="inlineStr">
         <is>
           <t>Revision</t>
@@ -11355,13 +11394,9 @@
       <c r="AN2" s="682" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="B3" s="54" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
+      <c r="A3" s="275" t="n"/>
+      <c r="B3" s="320" t="n"/>
+      <c r="C3" s="275" t="n"/>
       <c r="H3" s="679" t="inlineStr">
         <is>
           <t>Eff. Date</t>
@@ -11405,17 +11440,13 @@
       <c r="AN3" s="682" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="B4" s="54" t="n"/>
+      <c r="A4" s="275" t="n"/>
+      <c r="B4" s="320" t="n"/>
       <c r="C4" s="683" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
       <c r="H4" s="679" t="inlineStr">
         <is>
           <t>Owner</t>
@@ -11455,17 +11486,17 @@
       <c r="AN4" s="682" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="24" t="n"/>
+      <c r="A5" s="282" t="n"/>
+      <c r="B5" s="287" t="n"/>
       <c r="C5" s="685" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="19" t="n"/>
+      <c r="D5" s="283" t="n"/>
+      <c r="E5" s="283" t="n"/>
+      <c r="F5" s="283" t="n"/>
+      <c r="G5" s="283" t="n"/>
       <c r="H5" s="686" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -11552,14 +11583,14 @@
           <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
+      <c r="B7" s="289" t="n"/>
+      <c r="C7" s="289" t="n"/>
+      <c r="D7" s="289" t="n"/>
+      <c r="E7" s="289" t="n"/>
+      <c r="F7" s="289" t="n"/>
+      <c r="G7" s="289" t="n"/>
+      <c r="H7" s="289" t="n"/>
+      <c r="I7" s="289" t="n"/>
       <c r="J7" s="691" t="n"/>
       <c r="K7" s="691" t="n"/>
       <c r="L7" s="691" t="n"/>
@@ -11593,31 +11624,31 @@
       <c r="AN7" s="692" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="693" t="inlineStr">
+      <c r="A8" s="756" t="inlineStr">
         <is>
           <t>Parent Form</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="694" t="inlineStr">
+      <c r="B8" s="272" t="n"/>
+      <c r="C8" s="757" t="inlineStr">
         <is>
           <t>FRM-209 · HIGH-RISK JOB READINESS REVIEW</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="695" t="inlineStr">
+      <c r="D8" s="271" t="n"/>
+      <c r="E8" s="272" t="n"/>
+      <c r="F8" s="758" t="inlineStr">
         <is>
           <t>Support Tab</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="694" t="inlineStr">
+      <c r="G8" s="272" t="n"/>
+      <c r="H8" s="757" t="inlineStr">
         <is>
           <t>RISKS_ACTIONS</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n"/>
+      <c r="I8" s="272" t="n"/>
       <c r="J8" s="696" t="n"/>
       <c r="K8" s="696" t="n"/>
       <c r="L8" s="696" t="n"/>
@@ -11651,27 +11682,27 @@
       <c r="AN8" s="697" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="698" t="inlineStr">
+      <c r="A9" s="759" t="inlineStr">
         <is>
           <t>Tab Purpose</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="699" t="inlineStr">
+      <c r="B9" s="278" t="n"/>
+      <c r="C9" s="760" t="inlineStr">
         <is>
           <t>One line per material, capacity, quality or customer-risk condition.</t>
         </is>
       </c>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="700" t="inlineStr">
+      <c r="D9" s="277" t="n"/>
+      <c r="E9" s="278" t="n"/>
+      <c r="F9" s="761" t="inlineStr">
         <is>
           <t>Working Owner</t>
         </is>
       </c>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="699" t="inlineStr"/>
-      <c r="I9" s="13" t="n"/>
+      <c r="G9" s="278" t="n"/>
+      <c r="H9" s="760" t="inlineStr"/>
+      <c r="I9" s="278" t="n"/>
       <c r="J9" s="701" t="n"/>
       <c r="K9" s="701" t="n"/>
       <c r="L9" s="701" t="n"/>
@@ -11705,27 +11736,27 @@
       <c r="AN9" s="702" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="698" t="inlineStr">
+      <c r="A10" s="759" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="699" t="inlineStr">
+      <c r="B10" s="278" t="n"/>
+      <c r="C10" s="760" t="inlineStr">
         <is>
           <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="700" t="inlineStr">
+      <c r="D10" s="277" t="n"/>
+      <c r="E10" s="278" t="n"/>
+      <c r="F10" s="761" t="inlineStr">
         <is>
           <t>Reviewed By</t>
         </is>
       </c>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="699" t="inlineStr"/>
-      <c r="I10" s="13" t="n"/>
+      <c r="G10" s="278" t="n"/>
+      <c r="H10" s="760" t="inlineStr"/>
+      <c r="I10" s="278" t="n"/>
       <c r="J10" s="701" t="n"/>
       <c r="K10" s="701" t="n"/>
       <c r="L10" s="701" t="n"/>
@@ -11759,31 +11790,31 @@
       <c r="AN10" s="702" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="698" t="inlineStr">
+      <c r="A11" s="759" t="inlineStr">
         <is>
           <t>Update Trigger</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="699" t="inlineStr">
+      <c r="B11" s="278" t="n"/>
+      <c r="C11" s="760" t="inlineStr">
         <is>
           <t>Update when the linked review, evidence or follow-up status changes.</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="700" t="inlineStr">
+      <c r="D11" s="277" t="n"/>
+      <c r="E11" s="278" t="n"/>
+      <c r="F11" s="761" t="inlineStr">
         <is>
           <t>Data Structure</t>
         </is>
       </c>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="699" t="inlineStr">
+      <c r="G11" s="278" t="n"/>
+      <c r="H11" s="760" t="inlineStr">
         <is>
           <t>Structured Excel Table with filters and print-title rows.</t>
         </is>
       </c>
-      <c r="I11" s="13" t="n"/>
+      <c r="I11" s="278" t="n"/>
       <c r="J11" s="703" t="n"/>
       <c r="K11" s="703" t="n"/>
       <c r="L11" s="703" t="n"/>
@@ -11817,31 +11848,31 @@
       <c r="AN11" s="704" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="705" t="inlineStr">
+      <c r="A12" s="762" t="inlineStr">
         <is>
           <t>Retention Rule</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="706" t="inlineStr">
+      <c r="B12" s="285" t="n"/>
+      <c r="C12" s="763" t="inlineStr">
         <is>
           <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
         </is>
       </c>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="22" t="n"/>
-      <c r="F12" s="707" t="inlineStr">
+      <c r="D12" s="283" t="n"/>
+      <c r="E12" s="285" t="n"/>
+      <c r="F12" s="764" t="inlineStr">
         <is>
           <t>Controlled Status</t>
         </is>
       </c>
-      <c r="G12" s="22" t="n"/>
-      <c r="H12" s="706" t="inlineStr">
+      <c r="G12" s="285" t="n"/>
+      <c r="H12" s="763" t="inlineStr">
         <is>
           <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
         </is>
       </c>
-      <c r="I12" s="22" t="n"/>
+      <c r="I12" s="285" t="n"/>
       <c r="J12" s="708" t="n"/>
       <c r="K12" s="708" t="n"/>
       <c r="L12" s="708" t="n"/>
@@ -11922,14 +11953,14 @@
           <t>2.  WORKING TABLE / DETAIL LINES</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="27" t="n"/>
-      <c r="I14" s="27" t="n"/>
+      <c r="B14" s="289" t="n"/>
+      <c r="C14" s="289" t="n"/>
+      <c r="D14" s="289" t="n"/>
+      <c r="E14" s="289" t="n"/>
+      <c r="F14" s="289" t="n"/>
+      <c r="G14" s="289" t="n"/>
+      <c r="H14" s="289" t="n"/>
+      <c r="I14" s="289" t="n"/>
       <c r="J14" s="691" t="n"/>
       <c r="K14" s="691" t="n"/>
       <c r="L14" s="691" t="n"/>
@@ -11968,14 +11999,14 @@
           <t>One line per material, capacity, quality or customer-risk condition.</t>
         </is>
       </c>
-      <c r="B15" s="27" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="27" t="n"/>
-      <c r="E15" s="27" t="n"/>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="27" t="n"/>
-      <c r="H15" s="27" t="n"/>
-      <c r="I15" s="27" t="n"/>
+      <c r="B15" s="289" t="n"/>
+      <c r="C15" s="289" t="n"/>
+      <c r="D15" s="289" t="n"/>
+      <c r="E15" s="289" t="n"/>
+      <c r="F15" s="289" t="n"/>
+      <c r="G15" s="289" t="n"/>
+      <c r="H15" s="289" t="n"/>
+      <c r="I15" s="289" t="n"/>
       <c r="J15" s="691" t="n"/>
       <c r="K15" s="691" t="n"/>
       <c r="L15" s="691" t="n"/>
@@ -12584,14 +12615,14 @@
           <t>NOTICE  —  One line per material, capacity, quality or customer-risk condition.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B28" s="27" t="n"/>
-      <c r="C28" s="27" t="n"/>
-      <c r="D28" s="27" t="n"/>
-      <c r="E28" s="27" t="n"/>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="27" t="n"/>
-      <c r="H28" s="27" t="n"/>
-      <c r="I28" s="27" t="n"/>
+      <c r="B28" s="289" t="n"/>
+      <c r="C28" s="289" t="n"/>
+      <c r="D28" s="289" t="n"/>
+      <c r="E28" s="289" t="n"/>
+      <c r="F28" s="289" t="n"/>
+      <c r="G28" s="289" t="n"/>
+      <c r="H28" s="289" t="n"/>
+      <c r="I28" s="289" t="n"/>
       <c r="J28" s="691" t="n"/>
       <c r="K28" s="691" t="n"/>
       <c r="L28" s="691" t="n"/>
@@ -12859,7 +12890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CU11"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>

--- a/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
@@ -28,12 +28,461 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
+  </si>
+  <si>
+    <t>1.  HIGH-RISK JOB HEADER / REFERENCE INFORMATION</t>
+  </si>
+  <si>
+    <t>2.  READINESS DECISION / OPEN RISK CONDITIONS</t>
+  </si>
+  <si>
+    <t>2.  WORKING TABLE / DETAIL LINES</t>
+  </si>
+  <si>
+    <t>3.  READINESS CRITERIA / RISK CHECK</t>
+  </si>
+  <si>
+    <t>4.  OPEN RISK ACTIONS / CONTAINMENT</t>
+  </si>
+  <si>
+    <t>5.  APPROVAL / SIGN-OFF</t>
+  </si>
+  <si>
+    <t>=IF(COUNTA(AF22:AF31)=0,"",IF(COUNTIF(AF22:AF31,"FAIL")+COUNTIF(AF22:AF31,"HOLD")&gt;0,"HOLD",IF(COUNTIF(AF22:AF31,"PASS")=COUNTA(AF22:AF31),"APPROVED","CONDITIONAL")))</t>
+  </si>
+  <si>
+    <t>=IF(COUNTA(AF22:AF31)=0,"",IF(COUNTIF(AF22:AF31,"FAIL")+COUNTIF(AF22:AF31,"HOLD")&gt;0,"OPEN","CLOSED"))</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$17)+1</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>Acceptance / Control Rule</t>
+  </si>
+  <si>
+    <t>Action Owner</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Approved by</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>CONDITIONAL</t>
+  </si>
+  <si>
+    <t>CRITICAL</t>
+  </si>
+  <si>
+    <t>CSR / cert / packaging rules are visible.</t>
+  </si>
+  <si>
+    <t>CUST-001 Alpha Semi</t>
+  </si>
+  <si>
+    <t>CUST-002 NovaFab</t>
+  </si>
+  <si>
+    <t>CUST-003 Orion Tech</t>
+  </si>
+  <si>
+    <t>Capability and readiness path are visible.</t>
+  </si>
+  <si>
+    <t>Cat.</t>
+  </si>
+  <si>
+    <t>Commercial / Ops Owner</t>
+  </si>
+  <si>
+    <t>Commitment and ship impact are realistic.</t>
+  </si>
+  <si>
+    <t>Conditional-release authority is explicit.</t>
+  </si>
+  <si>
+    <t>Containment / Action</t>
+  </si>
+  <si>
+    <t>Containment / contingency exists.</t>
+  </si>
+  <si>
+    <t>Controlled Status</t>
+  </si>
+  <si>
+    <t>Critical source path is not assumed.</t>
+  </si>
+  <si>
+    <t>Current Route Step</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Customer / quality package is identified.</t>
+  </si>
+  <si>
+    <t>Data Structure</t>
+  </si>
+  <si>
+    <t>Decision can be reconstructed later.</t>
+  </si>
+  <si>
+    <t>Delivery / ship logic is feasible.</t>
+  </si>
+  <si>
+    <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
+  </si>
+  <si>
+    <t>Document / Record</t>
+  </si>
+  <si>
+    <t>Due Date</t>
+  </si>
+  <si>
+    <t>Due Date / Commit</t>
+  </si>
+  <si>
+    <t>Eff. Date</t>
+  </si>
+  <si>
+    <t>Engineering Lead</t>
+  </si>
+  <si>
+    <t>Escalation</t>
+  </si>
+  <si>
+    <t>Escalation if Overdue</t>
+  </si>
+  <si>
+    <t>Evidence Folder</t>
+  </si>
+  <si>
+    <t>Evidence Ref</t>
+  </si>
+  <si>
+    <t>Evidence path and dossier traceability exist.</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>FRM-209</t>
+  </si>
+  <si>
+    <t>FRM-209 · HIGH-RISK JOB READINESS REVIEW</t>
+  </si>
+  <si>
+    <t>FRM-306 or released package reference is current.</t>
+  </si>
+  <si>
+    <t>First-piece / FAI strategy is defined.</t>
+  </si>
+  <si>
+    <t>Form Code</t>
+  </si>
+  <si>
+    <t>Gate Conclusion</t>
+  </si>
+  <si>
+    <t>Gate Name / Trigger</t>
+  </si>
+  <si>
+    <t>Gate Status</t>
+  </si>
+  <si>
+    <t>General Manager</t>
+  </si>
+  <si>
+    <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>HIGH-RISK JOB READINESS REVIEW</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>High-risk job release review</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>JOB-240001</t>
+  </si>
+  <si>
+    <t>JOB-240002</t>
+  </si>
+  <si>
+    <t>JOB-240003</t>
+  </si>
+  <si>
+    <t>Job / WO</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>MONITORING</t>
+  </si>
+  <si>
+    <t>Machine / tooling / gage readiness exists.</t>
+  </si>
+  <si>
+    <t>Material / outsource path is feasible.</t>
+  </si>
+  <si>
+    <t>Most severe risk is named, not hidden.</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NOTICE  —  Enter data only in designated white input cells. Do not add, delete or resize columns/rows. File naming: FRM-209_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
+  </si>
+  <si>
+    <t>NOTICE  —  One line per material, capacity, quality or customer-risk condition.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
+  </si>
+  <si>
+    <t>Name  /  Signature  /  Date</t>
+  </si>
+  <si>
+    <t>Next Step</t>
+  </si>
+  <si>
+    <t>No conditional release without named owner.</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>One line per material, capacity, quality or customer-risk condition.</t>
+  </si>
+  <si>
+    <t>Open Risk / Hold Reason</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>PN-1001 / Rev.A</t>
+  </si>
+  <si>
+    <t>PN-1002 / Rev.B</t>
+  </si>
+  <si>
+    <t>PN-1003 / Rev.C</t>
+  </si>
+  <si>
+    <t>Parent Form</t>
+  </si>
+  <si>
+    <t>Part No. / Revision</t>
+  </si>
+  <si>
+    <t>Planning / QA / Engineering</t>
+  </si>
+  <si>
+    <t>Planning Lead</t>
+  </si>
+  <si>
+    <t>Prepared by</t>
+  </si>
+  <si>
+    <t>Production Supervisor</t>
+  </si>
+  <si>
+    <t>QA Engineer</t>
+  </si>
+  <si>
+    <t>QA gate logic and owner are visible.</t>
+  </si>
+  <si>
+    <t>Quality Management System  ·  Controlled Document</t>
+  </si>
+  <si>
+    <t>REF LINKS</t>
+  </si>
+  <si>
+    <t>REF_CUSTOMER_MASTER</t>
+  </si>
+  <si>
+    <t>REF_JOB_WO_MASTER</t>
+  </si>
+  <si>
+    <t>REF_OWNER_PERSON_MASTER</t>
+  </si>
+  <si>
+    <t>REF_PART_REV_MASTER</t>
+  </si>
+  <si>
+    <t>REJECT</t>
+  </si>
+  <si>
+    <t>RISKS / ACTIONS REGISTER</t>
+  </si>
+  <si>
+    <t>RISKS_ACTIONS</t>
+  </si>
+  <si>
+    <t>RSK</t>
+  </si>
+  <si>
+    <t>Readiness / Risk Item</t>
+  </si>
+  <si>
+    <t>Readiness Review ID</t>
+  </si>
+  <si>
+    <t>Record Status</t>
+  </si>
+  <si>
+    <t>Recovery path exists if primary plan fails.</t>
+  </si>
+  <si>
+    <t>Ref Type</t>
+  </si>
+  <si>
+    <t>Ref.</t>
+  </si>
+  <si>
+    <t>Reference release package, planner snapshot and dossier evidence only.</t>
+  </si>
+  <si>
+    <t>Released baseline package is locked.</t>
+  </si>
+  <si>
+    <t>Required Containment / Action</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Retention Rule</t>
+  </si>
+  <si>
+    <t>Reviewed By</t>
+  </si>
+  <si>
+    <t>Reviewed by</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>Risk / Readiness Gap</t>
+  </si>
+  <si>
+    <t>SUPERSEDED</t>
+  </si>
+  <si>
+    <t>Setup Technician</t>
+  </si>
+  <si>
+    <t>Source of Truth</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Structured Excel Table with filters and print-title rows.</t>
+  </si>
+  <si>
+    <t>Support Tab</t>
+  </si>
+  <si>
+    <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
+  </si>
+  <si>
+    <t>System of Record</t>
+  </si>
+  <si>
+    <t>Tab Purpose</t>
+  </si>
+  <si>
+    <t>Top Risk Class</t>
+  </si>
+  <si>
+    <t>Top abnormal / failure mode is explicit.</t>
+  </si>
+  <si>
+    <t>Unique Ref</t>
+  </si>
+  <si>
+    <t>Update Trigger</t>
+  </si>
+  <si>
+    <t>Update when the linked review, evidence or follow-up status changes.</t>
+  </si>
+  <si>
+    <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>VAL_DECISION_GATE_CORE</t>
+  </si>
+  <si>
+    <t>VAL_RESULT_CORE</t>
+  </si>
+  <si>
+    <t>VAL_RISK_LEVEL_CORE</t>
+  </si>
+  <si>
+    <t>VAL_STATUS_CORE</t>
+  </si>
+  <si>
+    <t>VOID</t>
+  </si>
+  <si>
+    <t>Verified by</t>
+  </si>
+  <si>
+    <t>Working Owner</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="90">
+  <fonts count="91">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -542,8 +991,13 @@
       <color rgb="001B3A6B"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007B4F00"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="57">
+  <fills count="58">
     <fill>
       <patternFill/>
     </fill>
@@ -825,8 +1279,13 @@
         <fgColor rgb="000C2D48"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="386">
+  <borders count="389">
     <border>
       <left/>
       <right/>
@@ -5007,11 +5466,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="765">
+  <cellXfs count="768">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6902,6 +7395,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="57" borderId="386" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="57" borderId="387" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="57" borderId="388" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9520,51 +10022,51 @@
       <c r="AM46" s="10" t="n"/>
       <c r="AN46" s="10" t="n"/>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="730" t="inlineStr">
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="765" t="inlineStr">
         <is>
           <t>NOTICE  —  Enter data only in designated white input cells. Do not add, delete or resize columns/rows. File naming: FRM-209_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="289" t="n"/>
-      <c r="C47" s="289" t="n"/>
-      <c r="D47" s="289" t="n"/>
-      <c r="E47" s="289" t="n"/>
-      <c r="F47" s="289" t="n"/>
-      <c r="G47" s="289" t="n"/>
-      <c r="H47" s="289" t="n"/>
-      <c r="I47" s="289" t="n"/>
-      <c r="J47" s="289" t="n"/>
-      <c r="K47" s="289" t="n"/>
-      <c r="L47" s="289" t="n"/>
-      <c r="M47" s="289" t="n"/>
-      <c r="N47" s="289" t="n"/>
-      <c r="O47" s="289" t="n"/>
-      <c r="P47" s="289" t="n"/>
-      <c r="Q47" s="289" t="n"/>
-      <c r="R47" s="289" t="n"/>
-      <c r="S47" s="289" t="n"/>
-      <c r="T47" s="289" t="n"/>
-      <c r="U47" s="289" t="n"/>
-      <c r="V47" s="289" t="n"/>
-      <c r="W47" s="289" t="n"/>
-      <c r="X47" s="289" t="n"/>
-      <c r="Y47" s="289" t="n"/>
-      <c r="Z47" s="289" t="n"/>
-      <c r="AA47" s="289" t="n"/>
-      <c r="AB47" s="289" t="n"/>
-      <c r="AC47" s="289" t="n"/>
-      <c r="AD47" s="289" t="n"/>
-      <c r="AE47" s="289" t="n"/>
-      <c r="AF47" s="289" t="n"/>
-      <c r="AG47" s="289" t="n"/>
-      <c r="AH47" s="289" t="n"/>
-      <c r="AI47" s="289" t="n"/>
-      <c r="AJ47" s="289" t="n"/>
-      <c r="AK47" s="289" t="n"/>
-      <c r="AL47" s="289" t="n"/>
-      <c r="AM47" s="289" t="n"/>
-      <c r="AN47" s="290" t="n"/>
+      <c r="B47" s="766" t="n"/>
+      <c r="C47" s="766" t="n"/>
+      <c r="D47" s="766" t="n"/>
+      <c r="E47" s="766" t="n"/>
+      <c r="F47" s="766" t="n"/>
+      <c r="G47" s="766" t="n"/>
+      <c r="H47" s="766" t="n"/>
+      <c r="I47" s="766" t="n"/>
+      <c r="J47" s="766" t="n"/>
+      <c r="K47" s="766" t="n"/>
+      <c r="L47" s="766" t="n"/>
+      <c r="M47" s="766" t="n"/>
+      <c r="N47" s="766" t="n"/>
+      <c r="O47" s="766" t="n"/>
+      <c r="P47" s="766" t="n"/>
+      <c r="Q47" s="766" t="n"/>
+      <c r="R47" s="766" t="n"/>
+      <c r="S47" s="766" t="n"/>
+      <c r="T47" s="766" t="n"/>
+      <c r="U47" s="766" t="n"/>
+      <c r="V47" s="766" t="n"/>
+      <c r="W47" s="766" t="n"/>
+      <c r="X47" s="766" t="n"/>
+      <c r="Y47" s="766" t="n"/>
+      <c r="Z47" s="766" t="n"/>
+      <c r="AA47" s="766" t="n"/>
+      <c r="AB47" s="766" t="n"/>
+      <c r="AC47" s="766" t="n"/>
+      <c r="AD47" s="766" t="n"/>
+      <c r="AE47" s="766" t="n"/>
+      <c r="AF47" s="766" t="n"/>
+      <c r="AG47" s="766" t="n"/>
+      <c r="AH47" s="766" t="n"/>
+      <c r="AI47" s="766" t="n"/>
+      <c r="AJ47" s="766" t="n"/>
+      <c r="AK47" s="766" t="n"/>
+      <c r="AL47" s="766" t="n"/>
+      <c r="AM47" s="766" t="n"/>
+      <c r="AN47" s="767" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="1"/>
     <row r="49" hidden="1" outlineLevel="1"/>
@@ -12609,51 +13111,51 @@
       <c r="AM27" s="708" t="n"/>
       <c r="AN27" s="709" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="647" t="inlineStr">
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="765" t="inlineStr">
         <is>
           <t>NOTICE  —  One line per material, capacity, quality or customer-risk condition.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B28" s="289" t="n"/>
-      <c r="C28" s="289" t="n"/>
-      <c r="D28" s="289" t="n"/>
-      <c r="E28" s="289" t="n"/>
-      <c r="F28" s="289" t="n"/>
-      <c r="G28" s="289" t="n"/>
-      <c r="H28" s="289" t="n"/>
-      <c r="I28" s="289" t="n"/>
-      <c r="J28" s="691" t="n"/>
-      <c r="K28" s="691" t="n"/>
-      <c r="L28" s="691" t="n"/>
-      <c r="M28" s="691" t="n"/>
-      <c r="N28" s="691" t="n"/>
-      <c r="O28" s="691" t="n"/>
-      <c r="P28" s="691" t="n"/>
-      <c r="Q28" s="691" t="n"/>
-      <c r="R28" s="691" t="n"/>
-      <c r="S28" s="691" t="n"/>
-      <c r="T28" s="691" t="n"/>
-      <c r="U28" s="691" t="n"/>
-      <c r="V28" s="691" t="n"/>
-      <c r="W28" s="691" t="n"/>
-      <c r="X28" s="691" t="n"/>
-      <c r="Y28" s="691" t="n"/>
-      <c r="Z28" s="691" t="n"/>
-      <c r="AA28" s="691" t="n"/>
-      <c r="AB28" s="691" t="n"/>
-      <c r="AC28" s="691" t="n"/>
-      <c r="AD28" s="691" t="n"/>
-      <c r="AE28" s="691" t="n"/>
-      <c r="AF28" s="691" t="n"/>
-      <c r="AG28" s="691" t="n"/>
-      <c r="AH28" s="691" t="n"/>
-      <c r="AI28" s="691" t="n"/>
-      <c r="AJ28" s="691" t="n"/>
-      <c r="AK28" s="691" t="n"/>
-      <c r="AL28" s="691" t="n"/>
-      <c r="AM28" s="691" t="n"/>
-      <c r="AN28" s="692" t="n"/>
+      <c r="B28" s="766" t="n"/>
+      <c r="C28" s="766" t="n"/>
+      <c r="D28" s="766" t="n"/>
+      <c r="E28" s="766" t="n"/>
+      <c r="F28" s="766" t="n"/>
+      <c r="G28" s="766" t="n"/>
+      <c r="H28" s="766" t="n"/>
+      <c r="I28" s="766" t="n"/>
+      <c r="J28" s="766" t="n"/>
+      <c r="K28" s="766" t="n"/>
+      <c r="L28" s="766" t="n"/>
+      <c r="M28" s="766" t="n"/>
+      <c r="N28" s="766" t="n"/>
+      <c r="O28" s="766" t="n"/>
+      <c r="P28" s="766" t="n"/>
+      <c r="Q28" s="766" t="n"/>
+      <c r="R28" s="766" t="n"/>
+      <c r="S28" s="766" t="n"/>
+      <c r="T28" s="766" t="n"/>
+      <c r="U28" s="766" t="n"/>
+      <c r="V28" s="766" t="n"/>
+      <c r="W28" s="766" t="n"/>
+      <c r="X28" s="766" t="n"/>
+      <c r="Y28" s="766" t="n"/>
+      <c r="Z28" s="766" t="n"/>
+      <c r="AA28" s="766" t="n"/>
+      <c r="AB28" s="766" t="n"/>
+      <c r="AC28" s="766" t="n"/>
+      <c r="AD28" s="766" t="n"/>
+      <c r="AE28" s="766" t="n"/>
+      <c r="AF28" s="766" t="n"/>
+      <c r="AG28" s="766" t="n"/>
+      <c r="AH28" s="766" t="n"/>
+      <c r="AI28" s="766" t="n"/>
+      <c r="AJ28" s="766" t="n"/>
+      <c r="AK28" s="766" t="n"/>
+      <c r="AL28" s="766" t="n"/>
+      <c r="AM28" s="766" t="n"/>
+      <c r="AN28" s="767" t="n"/>
     </row>
     <row r="29" hidden="1" outlineLevel="1"/>
     <row r="30" hidden="1" outlineLevel="1"/>

--- a/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
@@ -5,9 +5,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM-209_GATE" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="veryHidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RISKS_ACTIONS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="5" state="veryHidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RISKS_ACTIONS" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_RESULT_CORE">'_LISTS'!$A$2:$A$5</definedName>
@@ -20,16 +18,15 @@
     <definedName name="REF_OWNER_PERSON_MASTER">'_IMPORT'!$D$2:$D$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'FRM-209_GATE'!$1:$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'FRM-209_GATE'!$A$1:$AN$47</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'RISKS_ACTIONS'!$1:$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'RISKS_ACTIONS'!$A$1:$I$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'REF_LINKS'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'RISKS_ACTIONS'!$1:$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'RISKS_ACTIONS'!$A$1:$I$28</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
   <si>
     <t>#</t>
   </si>
@@ -91,15 +88,6 @@
     <t>CSR / cert / packaging rules are visible.</t>
   </si>
   <si>
-    <t>CUST-001 Alpha Semi</t>
-  </si>
-  <si>
-    <t>CUST-002 NovaFab</t>
-  </si>
-  <si>
-    <t>CUST-003 Orion Tech</t>
-  </si>
-  <si>
     <t>Capability and readiness path are visible.</t>
   </si>
   <si>
@@ -148,9 +136,6 @@
     <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
   </si>
   <si>
-    <t>Document / Record</t>
-  </si>
-  <si>
     <t>Due Date</t>
   </si>
   <si>
@@ -158,9 +143,6 @@
   </si>
   <si>
     <t>Eff. Date</t>
-  </si>
-  <si>
-    <t>Engineering Lead</t>
   </si>
   <si>
     <t>Escalation</t>
@@ -229,15 +211,6 @@
     <t>Impact</t>
   </si>
   <si>
-    <t>JOB-240001</t>
-  </si>
-  <si>
-    <t>JOB-240002</t>
-  </si>
-  <si>
-    <t>JOB-240003</t>
-  </si>
-  <si>
     <t>Job / WO</t>
   </si>
   <si>
@@ -277,9 +250,6 @@
     <t>No conditional release without named owner.</t>
   </si>
   <si>
-    <t>Note</t>
-  </si>
-  <si>
     <t>OPEN</t>
   </si>
   <si>
@@ -295,15 +265,6 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>PN-1001 / Rev.A</t>
-  </si>
-  <si>
-    <t>PN-1002 / Rev.B</t>
-  </si>
-  <si>
-    <t>PN-1003 / Rev.C</t>
-  </si>
-  <si>
     <t>Parent Form</t>
   </si>
   <si>
@@ -313,37 +274,13 @@
     <t>Planning / QA / Engineering</t>
   </si>
   <si>
-    <t>Planning Lead</t>
-  </si>
-  <si>
     <t>Prepared by</t>
-  </si>
-  <si>
-    <t>Production Supervisor</t>
-  </si>
-  <si>
-    <t>QA Engineer</t>
   </si>
   <si>
     <t>QA gate logic and owner are visible.</t>
   </si>
   <si>
     <t>Quality Management System  ·  Controlled Document</t>
-  </si>
-  <si>
-    <t>REF LINKS</t>
-  </si>
-  <si>
-    <t>REF_CUSTOMER_MASTER</t>
-  </si>
-  <si>
-    <t>REF_JOB_WO_MASTER</t>
-  </si>
-  <si>
-    <t>REF_OWNER_PERSON_MASTER</t>
-  </si>
-  <si>
-    <t>REF_PART_REV_MASTER</t>
   </si>
   <si>
     <t>REJECT</t>
@@ -370,13 +307,7 @@
     <t>Recovery path exists if primary plan fails.</t>
   </si>
   <si>
-    <t>Ref Type</t>
-  </si>
-  <si>
     <t>Ref.</t>
-  </si>
-  <si>
-    <t>Reference release package, planner snapshot and dossier evidence only.</t>
   </si>
   <si>
     <t>Released baseline package is locked.</t>
@@ -406,9 +337,6 @@
     <t>SUPERSEDED</t>
   </si>
   <si>
-    <t>Setup Technician</t>
-  </si>
-  <si>
     <t>Source of Truth</t>
   </si>
   <si>
@@ -424,9 +352,6 @@
     <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
   </si>
   <si>
-    <t>System of Record</t>
-  </si>
-  <si>
     <t>Tab Purpose</t>
   </si>
   <si>
@@ -434,9 +359,6 @@
   </si>
   <si>
     <t>Top abnormal / failure mode is explicit.</t>
-  </si>
-  <si>
-    <t>Unique Ref</t>
   </si>
   <si>
     <t>Update Trigger</t>
@@ -1285,7 +1207,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="389">
+  <borders count="394">
     <border>
       <left/>
       <right/>
@@ -5499,12 +5421,70 @@
       <bottom style="thin">
         <color rgb="00F9A825"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="768">
+  <cellXfs count="771">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -7405,6 +7385,11 @@
     <xf numFmtId="0" fontId="90" fillId="57" borderId="388" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="90" fillId="57" borderId="389" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="392" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="393" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -7566,39 +7551,6 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1303776" cy="376089"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RISKS_ACTIONS" displayName="RISKS_ACTIONS" ref="A16:I26" headerRowCount="1">
   <autoFilter ref="A16:I26"/>
@@ -7614,22 +7566,6 @@
     <tableColumn id="9" name="Evidence Ref"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="REF_LINKS" displayName="REF_LINKS" ref="A3:G11" headerRowCount="1">
-  <autoFilter ref="A3:G11"/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="Ref Type"/>
-    <tableColumn id="2" name="Document / Record"/>
-    <tableColumn id="3" name="System of Record"/>
-    <tableColumn id="4" name="Unique Ref"/>
-    <tableColumn id="5" name="Owner"/>
-    <tableColumn id="6" name="Status"/>
-    <tableColumn id="7" name="Note"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
@@ -11173,581 +11109,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AN6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2.33" customWidth="1" min="1" max="1"/>
-    <col width="2.33" customWidth="1" min="2" max="2"/>
-    <col width="2.33" customWidth="1" min="3" max="3"/>
-    <col width="2.33" customWidth="1" min="4" max="4"/>
-    <col hidden="1" width="2.33" customWidth="1" min="5" max="16384"/>
-    <col width="2.33" customWidth="1" min="6" max="6"/>
-    <col width="2.33" customWidth="1" min="7" max="7"/>
-    <col width="2.33" customWidth="1" min="8" max="8"/>
-    <col width="2.33" customWidth="1" min="9" max="9"/>
-    <col width="2.33" customWidth="1" min="10" max="10"/>
-    <col width="2.33" customWidth="1" min="11" max="11"/>
-    <col width="2.33" customWidth="1" min="12" max="12"/>
-    <col width="2.33" customWidth="1" min="13" max="13"/>
-    <col width="2.33" customWidth="1" min="14" max="14"/>
-    <col width="2.33" customWidth="1" min="15" max="15"/>
-    <col width="2.33" customWidth="1" min="16" max="16"/>
-    <col width="2.33" customWidth="1" min="17" max="17"/>
-    <col width="2.33" customWidth="1" min="18" max="18"/>
-    <col width="2.33" customWidth="1" min="19" max="19"/>
-    <col width="2.33" customWidth="1" min="20" max="20"/>
-    <col width="2.33" customWidth="1" min="21" max="21"/>
-    <col width="2.33" customWidth="1" min="22" max="22"/>
-    <col width="2.33" customWidth="1" min="23" max="23"/>
-    <col width="2.33" customWidth="1" min="24" max="24"/>
-    <col width="2.33" customWidth="1" min="25" max="25"/>
-    <col width="2.33" customWidth="1" min="26" max="26"/>
-    <col width="2.33" customWidth="1" min="27" max="27"/>
-    <col width="2.33" customWidth="1" min="28" max="28"/>
-    <col width="2.33" customWidth="1" min="29" max="29"/>
-    <col width="2.33" customWidth="1" min="30" max="30"/>
-    <col width="2.33" customWidth="1" min="31" max="31"/>
-    <col width="2.33" customWidth="1" min="32" max="32"/>
-    <col width="2.33" customWidth="1" min="33" max="33"/>
-    <col width="2.33" customWidth="1" min="34" max="34"/>
-    <col width="2.33" customWidth="1" min="35" max="35"/>
-    <col width="2.33" customWidth="1" min="36" max="36"/>
-    <col width="2.33" customWidth="1" min="37" max="37"/>
-    <col width="2.33" customWidth="1" min="38" max="38"/>
-    <col width="2.33" customWidth="1" min="39" max="39"/>
-    <col width="2.33" customWidth="1" min="40" max="40"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="576" t="inlineStr">
-        <is>
-          <t>REF_CUSTOMER_MASTER</t>
-        </is>
-      </c>
-      <c r="B1" s="535" t="inlineStr">
-        <is>
-          <t>REF_PART_REV_MASTER</t>
-        </is>
-      </c>
-      <c r="C1" s="535" t="inlineStr">
-        <is>
-          <t>REF_JOB_WO_MASTER</t>
-        </is>
-      </c>
-      <c r="D1" s="535" t="inlineStr">
-        <is>
-          <t>REF_OWNER_PERSON_MASTER</t>
-        </is>
-      </c>
-      <c r="E1" s="535" t="n"/>
-      <c r="F1" s="535" t="n"/>
-      <c r="G1" s="535" t="n"/>
-      <c r="H1" s="535" t="n"/>
-      <c r="I1" s="535" t="n"/>
-      <c r="J1" s="535" t="n"/>
-      <c r="K1" s="535" t="n"/>
-      <c r="L1" s="535" t="n"/>
-      <c r="M1" s="535" t="n"/>
-      <c r="N1" s="535" t="n"/>
-      <c r="O1" s="535" t="n"/>
-      <c r="P1" s="535" t="n"/>
-      <c r="Q1" s="535" t="n"/>
-      <c r="R1" s="535" t="n"/>
-      <c r="S1" s="535" t="n"/>
-      <c r="T1" s="535" t="n"/>
-      <c r="U1" s="535" t="n"/>
-      <c r="V1" s="535" t="n"/>
-      <c r="W1" s="535" t="n"/>
-      <c r="X1" s="535" t="n"/>
-      <c r="Y1" s="535" t="n"/>
-      <c r="Z1" s="535" t="n"/>
-      <c r="AA1" s="535" t="n"/>
-      <c r="AB1" s="535" t="n"/>
-      <c r="AC1" s="535" t="n"/>
-      <c r="AD1" s="535" t="n"/>
-      <c r="AE1" s="535" t="n"/>
-      <c r="AF1" s="535" t="n"/>
-      <c r="AG1" s="535" t="n"/>
-      <c r="AH1" s="535" t="n"/>
-      <c r="AI1" s="535" t="n"/>
-      <c r="AJ1" s="535" t="n"/>
-      <c r="AK1" s="535" t="n"/>
-      <c r="AL1" s="535" t="n"/>
-      <c r="AM1" s="535" t="n"/>
-      <c r="AN1" s="538" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="572" t="inlineStr">
-        <is>
-          <t>CUST-001 Alpha Semi</t>
-        </is>
-      </c>
-      <c r="B2" s="398" t="inlineStr">
-        <is>
-          <t>PN-1001 / Rev.A</t>
-        </is>
-      </c>
-      <c r="C2" s="398" t="inlineStr">
-        <is>
-          <t>JOB-240001</t>
-        </is>
-      </c>
-      <c r="D2" s="398" t="inlineStr">
-        <is>
-          <t>Planning Lead</t>
-        </is>
-      </c>
-      <c r="E2" s="398" t="n"/>
-      <c r="F2" s="398" t="n"/>
-      <c r="G2" s="398" t="n"/>
-      <c r="H2" s="398" t="n"/>
-      <c r="I2" s="398" t="n"/>
-      <c r="J2" s="398" t="n"/>
-      <c r="K2" s="398" t="n"/>
-      <c r="L2" s="398" t="n"/>
-      <c r="M2" s="398" t="n"/>
-      <c r="N2" s="398" t="n"/>
-      <c r="O2" s="398" t="n"/>
-      <c r="P2" s="398" t="n"/>
-      <c r="Q2" s="398" t="n"/>
-      <c r="R2" s="398" t="n"/>
-      <c r="S2" s="398" t="n"/>
-      <c r="T2" s="398" t="n"/>
-      <c r="U2" s="398" t="n"/>
-      <c r="V2" s="398" t="n"/>
-      <c r="W2" s="398" t="n"/>
-      <c r="X2" s="398" t="n"/>
-      <c r="Y2" s="398" t="n"/>
-      <c r="Z2" s="398" t="n"/>
-      <c r="AA2" s="398" t="n"/>
-      <c r="AB2" s="398" t="n"/>
-      <c r="AC2" s="398" t="n"/>
-      <c r="AD2" s="398" t="n"/>
-      <c r="AE2" s="398" t="n"/>
-      <c r="AF2" s="398" t="n"/>
-      <c r="AG2" s="398" t="n"/>
-      <c r="AH2" s="398" t="n"/>
-      <c r="AI2" s="398" t="n"/>
-      <c r="AJ2" s="398" t="n"/>
-      <c r="AK2" s="398" t="n"/>
-      <c r="AL2" s="398" t="n"/>
-      <c r="AM2" s="398" t="n"/>
-      <c r="AN2" s="542" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="572" t="inlineStr">
-        <is>
-          <t>CUST-002 NovaFab</t>
-        </is>
-      </c>
-      <c r="B3" s="398" t="inlineStr">
-        <is>
-          <t>PN-1002 / Rev.B</t>
-        </is>
-      </c>
-      <c r="C3" s="398" t="inlineStr">
-        <is>
-          <t>JOB-240002</t>
-        </is>
-      </c>
-      <c r="D3" s="398" t="inlineStr">
-        <is>
-          <t>Production Supervisor</t>
-        </is>
-      </c>
-      <c r="E3" s="398" t="n"/>
-      <c r="F3" s="398" t="n"/>
-      <c r="G3" s="398" t="n"/>
-      <c r="H3" s="398" t="n"/>
-      <c r="I3" s="398" t="n"/>
-      <c r="J3" s="398" t="n"/>
-      <c r="K3" s="398" t="n"/>
-      <c r="L3" s="398" t="n"/>
-      <c r="M3" s="398" t="n"/>
-      <c r="N3" s="398" t="n"/>
-      <c r="O3" s="398" t="n"/>
-      <c r="P3" s="398" t="n"/>
-      <c r="Q3" s="398" t="n"/>
-      <c r="R3" s="398" t="n"/>
-      <c r="S3" s="398" t="n"/>
-      <c r="T3" s="398" t="n"/>
-      <c r="U3" s="398" t="n"/>
-      <c r="V3" s="398" t="n"/>
-      <c r="W3" s="398" t="n"/>
-      <c r="X3" s="398" t="n"/>
-      <c r="Y3" s="398" t="n"/>
-      <c r="Z3" s="398" t="n"/>
-      <c r="AA3" s="398" t="n"/>
-      <c r="AB3" s="398" t="n"/>
-      <c r="AC3" s="398" t="n"/>
-      <c r="AD3" s="398" t="n"/>
-      <c r="AE3" s="398" t="n"/>
-      <c r="AF3" s="398" t="n"/>
-      <c r="AG3" s="398" t="n"/>
-      <c r="AH3" s="398" t="n"/>
-      <c r="AI3" s="398" t="n"/>
-      <c r="AJ3" s="398" t="n"/>
-      <c r="AK3" s="398" t="n"/>
-      <c r="AL3" s="398" t="n"/>
-      <c r="AM3" s="398" t="n"/>
-      <c r="AN3" s="542" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="572" t="inlineStr">
-        <is>
-          <t>CUST-003 Orion Tech</t>
-        </is>
-      </c>
-      <c r="B4" s="398" t="inlineStr">
-        <is>
-          <t>PN-1003 / Rev.C</t>
-        </is>
-      </c>
-      <c r="C4" s="398" t="inlineStr">
-        <is>
-          <t>JOB-240003</t>
-        </is>
-      </c>
-      <c r="D4" s="398" t="inlineStr">
-        <is>
-          <t>QA Engineer</t>
-        </is>
-      </c>
-      <c r="E4" s="398" t="n"/>
-      <c r="F4" s="398" t="n"/>
-      <c r="G4" s="398" t="n"/>
-      <c r="H4" s="398" t="n"/>
-      <c r="I4" s="398" t="n"/>
-      <c r="J4" s="398" t="n"/>
-      <c r="K4" s="398" t="n"/>
-      <c r="L4" s="398" t="n"/>
-      <c r="M4" s="398" t="n"/>
-      <c r="N4" s="398" t="n"/>
-      <c r="O4" s="398" t="n"/>
-      <c r="P4" s="398" t="n"/>
-      <c r="Q4" s="398" t="n"/>
-      <c r="R4" s="398" t="n"/>
-      <c r="S4" s="398" t="n"/>
-      <c r="T4" s="398" t="n"/>
-      <c r="U4" s="398" t="n"/>
-      <c r="V4" s="398" t="n"/>
-      <c r="W4" s="398" t="n"/>
-      <c r="X4" s="398" t="n"/>
-      <c r="Y4" s="398" t="n"/>
-      <c r="Z4" s="398" t="n"/>
-      <c r="AA4" s="398" t="n"/>
-      <c r="AB4" s="398" t="n"/>
-      <c r="AC4" s="398" t="n"/>
-      <c r="AD4" s="398" t="n"/>
-      <c r="AE4" s="398" t="n"/>
-      <c r="AF4" s="398" t="n"/>
-      <c r="AG4" s="398" t="n"/>
-      <c r="AH4" s="398" t="n"/>
-      <c r="AI4" s="398" t="n"/>
-      <c r="AJ4" s="398" t="n"/>
-      <c r="AK4" s="398" t="n"/>
-      <c r="AL4" s="398" t="n"/>
-      <c r="AM4" s="398" t="n"/>
-      <c r="AN4" s="542" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="572" t="n"/>
-      <c r="B5" s="398" t="n"/>
-      <c r="C5" s="398" t="n"/>
-      <c r="D5" s="398" t="inlineStr">
-        <is>
-          <t>Engineering Lead</t>
-        </is>
-      </c>
-      <c r="E5" s="398" t="n"/>
-      <c r="F5" s="398" t="n"/>
-      <c r="G5" s="398" t="n"/>
-      <c r="H5" s="398" t="n"/>
-      <c r="I5" s="398" t="n"/>
-      <c r="J5" s="398" t="n"/>
-      <c r="K5" s="398" t="n"/>
-      <c r="L5" s="398" t="n"/>
-      <c r="M5" s="398" t="n"/>
-      <c r="N5" s="398" t="n"/>
-      <c r="O5" s="398" t="n"/>
-      <c r="P5" s="398" t="n"/>
-      <c r="Q5" s="398" t="n"/>
-      <c r="R5" s="398" t="n"/>
-      <c r="S5" s="398" t="n"/>
-      <c r="T5" s="398" t="n"/>
-      <c r="U5" s="398" t="n"/>
-      <c r="V5" s="398" t="n"/>
-      <c r="W5" s="398" t="n"/>
-      <c r="X5" s="398" t="n"/>
-      <c r="Y5" s="398" t="n"/>
-      <c r="Z5" s="398" t="n"/>
-      <c r="AA5" s="398" t="n"/>
-      <c r="AB5" s="398" t="n"/>
-      <c r="AC5" s="398" t="n"/>
-      <c r="AD5" s="398" t="n"/>
-      <c r="AE5" s="398" t="n"/>
-      <c r="AF5" s="398" t="n"/>
-      <c r="AG5" s="398" t="n"/>
-      <c r="AH5" s="398" t="n"/>
-      <c r="AI5" s="398" t="n"/>
-      <c r="AJ5" s="398" t="n"/>
-      <c r="AK5" s="398" t="n"/>
-      <c r="AL5" s="398" t="n"/>
-      <c r="AM5" s="398" t="n"/>
-      <c r="AN5" s="542" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="574" t="n"/>
-      <c r="B6" s="544" t="n"/>
-      <c r="C6" s="544" t="n"/>
-      <c r="D6" s="544" t="inlineStr">
-        <is>
-          <t>Setup Technician</t>
-        </is>
-      </c>
-      <c r="E6" s="544" t="n"/>
-      <c r="F6" s="544" t="n"/>
-      <c r="G6" s="544" t="n"/>
-      <c r="H6" s="544" t="n"/>
-      <c r="I6" s="544" t="n"/>
-      <c r="J6" s="544" t="n"/>
-      <c r="K6" s="544" t="n"/>
-      <c r="L6" s="544" t="n"/>
-      <c r="M6" s="544" t="n"/>
-      <c r="N6" s="544" t="n"/>
-      <c r="O6" s="544" t="n"/>
-      <c r="P6" s="544" t="n"/>
-      <c r="Q6" s="544" t="n"/>
-      <c r="R6" s="544" t="n"/>
-      <c r="S6" s="544" t="n"/>
-      <c r="T6" s="544" t="n"/>
-      <c r="U6" s="544" t="n"/>
-      <c r="V6" s="544" t="n"/>
-      <c r="W6" s="544" t="n"/>
-      <c r="X6" s="544" t="n"/>
-      <c r="Y6" s="544" t="n"/>
-      <c r="Z6" s="544" t="n"/>
-      <c r="AA6" s="544" t="n"/>
-      <c r="AB6" s="544" t="n"/>
-      <c r="AC6" s="544" t="n"/>
-      <c r="AD6" s="544" t="n"/>
-      <c r="AE6" s="544" t="n"/>
-      <c r="AF6" s="544" t="n"/>
-      <c r="AG6" s="544" t="n"/>
-      <c r="AH6" s="544" t="n"/>
-      <c r="AI6" s="544" t="n"/>
-      <c r="AJ6" s="544" t="n"/>
-      <c r="AK6" s="544" t="n"/>
-      <c r="AL6" s="544" t="n"/>
-      <c r="AM6" s="544" t="n"/>
-      <c r="AN6" s="547" t="n"/>
-    </row>
-    <row r="7" hidden="1"/>
-    <row r="8" hidden="1"/>
-    <row r="9" hidden="1"/>
-    <row r="10" hidden="1"/>
-    <row r="11" hidden="1"/>
-    <row r="12" hidden="1"/>
-    <row r="13" hidden="1"/>
-    <row r="14" hidden="1"/>
-    <row r="15" hidden="1"/>
-    <row r="16" hidden="1"/>
-    <row r="17" hidden="1"/>
-    <row r="18" hidden="1"/>
-    <row r="19" hidden="1"/>
-    <row r="20" hidden="1"/>
-    <row r="21" hidden="1"/>
-    <row r="22" hidden="1"/>
-    <row r="23" hidden="1"/>
-    <row r="24" hidden="1"/>
-    <row r="25" hidden="1"/>
-    <row r="26" hidden="1"/>
-    <row r="27" hidden="1"/>
-    <row r="28" hidden="1"/>
-    <row r="29" hidden="1"/>
-    <row r="30" hidden="1"/>
-    <row r="31" hidden="1"/>
-    <row r="32" hidden="1"/>
-    <row r="33" hidden="1"/>
-    <row r="34" hidden="1"/>
-    <row r="35" hidden="1"/>
-    <row r="36" hidden="1"/>
-    <row r="37" hidden="1"/>
-    <row r="38" hidden="1"/>
-    <row r="39" hidden="1"/>
-    <row r="40" hidden="1"/>
-    <row r="41" hidden="1"/>
-    <row r="42" hidden="1"/>
-    <row r="43" hidden="1"/>
-    <row r="44" hidden="1"/>
-    <row r="45" hidden="1"/>
-    <row r="46" hidden="1"/>
-    <row r="47" hidden="1"/>
-    <row r="48" hidden="1"/>
-    <row r="49" hidden="1"/>
-    <row r="50" hidden="1"/>
-    <row r="51" hidden="1"/>
-    <row r="52" hidden="1"/>
-    <row r="53" hidden="1"/>
-    <row r="54" hidden="1"/>
-    <row r="55" hidden="1"/>
-    <row r="56" hidden="1"/>
-    <row r="57" hidden="1"/>
-    <row r="58" hidden="1"/>
-    <row r="59" hidden="1"/>
-    <row r="60" hidden="1"/>
-    <row r="61" hidden="1"/>
-    <row r="62" hidden="1"/>
-    <row r="63" hidden="1"/>
-    <row r="64" hidden="1"/>
-    <row r="65" hidden="1"/>
-    <row r="66" hidden="1"/>
-    <row r="67" hidden="1"/>
-    <row r="68" hidden="1"/>
-    <row r="69" hidden="1"/>
-    <row r="70" hidden="1"/>
-    <row r="71" hidden="1"/>
-    <row r="72" hidden="1"/>
-    <row r="73" hidden="1"/>
-    <row r="74" hidden="1"/>
-    <row r="75" hidden="1"/>
-    <row r="76" hidden="1"/>
-    <row r="77" hidden="1"/>
-    <row r="78" hidden="1"/>
-    <row r="79" hidden="1"/>
-    <row r="80" hidden="1"/>
-    <row r="81" hidden="1"/>
-    <row r="82" hidden="1"/>
-    <row r="83" hidden="1"/>
-    <row r="84" hidden="1"/>
-    <row r="85" hidden="1"/>
-    <row r="86" hidden="1"/>
-    <row r="87" hidden="1"/>
-    <row r="88" hidden="1"/>
-    <row r="89" hidden="1"/>
-    <row r="90" hidden="1"/>
-    <row r="91" hidden="1"/>
-    <row r="92" hidden="1"/>
-    <row r="93" hidden="1"/>
-    <row r="94" hidden="1"/>
-    <row r="95" hidden="1"/>
-    <row r="96" hidden="1"/>
-    <row r="97" hidden="1"/>
-    <row r="98" hidden="1"/>
-    <row r="99" hidden="1"/>
-    <row r="100" hidden="1"/>
-    <row r="101" hidden="1"/>
-    <row r="102" hidden="1"/>
-    <row r="103" hidden="1"/>
-    <row r="104" hidden="1"/>
-    <row r="105" hidden="1"/>
-    <row r="106" hidden="1"/>
-    <row r="107" hidden="1"/>
-    <row r="108" hidden="1"/>
-    <row r="109" hidden="1"/>
-    <row r="110" hidden="1"/>
-    <row r="111" hidden="1"/>
-    <row r="112" hidden="1"/>
-    <row r="113" hidden="1"/>
-    <row r="114" hidden="1"/>
-    <row r="115" hidden="1"/>
-    <row r="116" hidden="1"/>
-    <row r="117" hidden="1"/>
-    <row r="118" hidden="1"/>
-    <row r="119" hidden="1"/>
-    <row r="120" hidden="1"/>
-    <row r="121" hidden="1"/>
-    <row r="122" hidden="1"/>
-    <row r="123" hidden="1"/>
-    <row r="124" hidden="1"/>
-    <row r="125" hidden="1"/>
-    <row r="126" hidden="1"/>
-    <row r="127" hidden="1"/>
-    <row r="128" hidden="1"/>
-    <row r="129" hidden="1"/>
-    <row r="130" hidden="1"/>
-    <row r="131" hidden="1"/>
-    <row r="132" hidden="1"/>
-    <row r="133" hidden="1"/>
-    <row r="134" hidden="1"/>
-    <row r="135" hidden="1"/>
-    <row r="136" hidden="1"/>
-    <row r="137" hidden="1"/>
-    <row r="138" hidden="1"/>
-    <row r="139" hidden="1"/>
-    <row r="140" hidden="1"/>
-    <row r="141" hidden="1"/>
-    <row r="142" hidden="1"/>
-    <row r="143" hidden="1"/>
-    <row r="144" hidden="1"/>
-    <row r="145" hidden="1"/>
-    <row r="146" hidden="1"/>
-    <row r="147" hidden="1"/>
-    <row r="148" hidden="1"/>
-    <row r="149" hidden="1"/>
-    <row r="150" hidden="1"/>
-    <row r="151" hidden="1"/>
-    <row r="152" hidden="1"/>
-    <row r="153" hidden="1"/>
-    <row r="154" hidden="1"/>
-    <row r="155" hidden="1"/>
-    <row r="156" hidden="1"/>
-    <row r="157" hidden="1"/>
-    <row r="158" hidden="1"/>
-    <row r="159" hidden="1"/>
-    <row r="160" hidden="1"/>
-    <row r="161" hidden="1"/>
-    <row r="162" hidden="1"/>
-    <row r="163" hidden="1"/>
-    <row r="164" hidden="1"/>
-    <row r="165" hidden="1"/>
-    <row r="166" hidden="1"/>
-    <row r="167" hidden="1"/>
-    <row r="168" hidden="1"/>
-    <row r="169" hidden="1"/>
-    <row r="170" hidden="1"/>
-    <row r="171" hidden="1"/>
-    <row r="172" hidden="1"/>
-    <row r="173" hidden="1"/>
-    <row r="174" hidden="1"/>
-    <row r="175" hidden="1"/>
-    <row r="176" hidden="1"/>
-    <row r="177" hidden="1"/>
-    <row r="178" hidden="1"/>
-    <row r="179" hidden="1"/>
-    <row r="180" hidden="1"/>
-    <row r="181" hidden="1"/>
-    <row r="182" hidden="1"/>
-    <row r="183" hidden="1"/>
-    <row r="184" hidden="1"/>
-    <row r="185" hidden="1"/>
-    <row r="186" hidden="1"/>
-    <row r="187" hidden="1"/>
-    <row r="188" hidden="1"/>
-    <row r="189" hidden="1"/>
-    <row r="190" hidden="1"/>
-    <row r="191" hidden="1"/>
-    <row r="192" hidden="1"/>
-    <row r="193" hidden="1"/>
-    <row r="194" hidden="1"/>
-    <row r="195" hidden="1"/>
-    <row r="196" hidden="1"/>
-    <row r="197" hidden="1"/>
-    <row r="198" hidden="1"/>
-    <row r="199" hidden="1"/>
-    <row r="200" hidden="1"/>
-  </sheetData>
-  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN28"/>
@@ -13384,759 +12745,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AN11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2.33" customWidth="1" min="1" max="1"/>
-    <col width="2.33" customWidth="1" min="2" max="2"/>
-    <col width="2.33" customWidth="1" min="3" max="3"/>
-    <col width="2.33" customWidth="1" min="4" max="4"/>
-    <col width="2.33" customWidth="1" min="5" max="5"/>
-    <col width="2.33" customWidth="1" min="6" max="6"/>
-    <col width="2.33" customWidth="1" min="7" max="7"/>
-    <col hidden="1" width="2.33" customWidth="1" min="8" max="16384"/>
-    <col width="2.33" customWidth="1" min="9" max="9"/>
-    <col width="2.33" customWidth="1" min="10" max="10"/>
-    <col width="2.33" customWidth="1" min="11" max="11"/>
-    <col width="2.33" customWidth="1" min="12" max="12"/>
-    <col width="2.33" customWidth="1" min="13" max="13"/>
-    <col width="2.33" customWidth="1" min="14" max="14"/>
-    <col width="2.33" customWidth="1" min="15" max="15"/>
-    <col width="2.33" customWidth="1" min="16" max="16"/>
-    <col width="2.33" customWidth="1" min="17" max="17"/>
-    <col width="2.33" customWidth="1" min="18" max="18"/>
-    <col width="2.33" customWidth="1" min="19" max="19"/>
-    <col width="2.33" customWidth="1" min="20" max="20"/>
-    <col width="2.33" customWidth="1" min="21" max="21"/>
-    <col width="2.33" customWidth="1" min="22" max="22"/>
-    <col width="2.33" customWidth="1" min="23" max="23"/>
-    <col width="2.33" customWidth="1" min="24" max="24"/>
-    <col width="2.33" customWidth="1" min="25" max="25"/>
-    <col width="2.33" customWidth="1" min="26" max="26"/>
-    <col width="2.33" customWidth="1" min="27" max="27"/>
-    <col width="2.33" customWidth="1" min="28" max="28"/>
-    <col width="2.33" customWidth="1" min="29" max="29"/>
-    <col width="2.33" customWidth="1" min="30" max="30"/>
-    <col width="2.33" customWidth="1" min="31" max="31"/>
-    <col width="2.33" customWidth="1" min="32" max="32"/>
-    <col width="2.33" customWidth="1" min="33" max="33"/>
-    <col width="2.33" customWidth="1" min="34" max="34"/>
-    <col width="2.33" customWidth="1" min="35" max="35"/>
-    <col width="2.33" customWidth="1" min="36" max="36"/>
-    <col width="2.33" customWidth="1" min="37" max="37"/>
-    <col width="2.33" customWidth="1" min="38" max="38"/>
-    <col width="2.33" customWidth="1" min="39" max="39"/>
-    <col width="2.33" customWidth="1" min="40" max="40"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="611" t="inlineStr">
-        <is>
-          <t>REF LINKS</t>
-        </is>
-      </c>
-      <c r="B1" s="718" t="n"/>
-      <c r="C1" s="718" t="n"/>
-      <c r="D1" s="718" t="n"/>
-      <c r="E1" s="718" t="n"/>
-      <c r="F1" s="718" t="n"/>
-      <c r="G1" s="718" t="n"/>
-      <c r="H1" s="612" t="n"/>
-      <c r="I1" s="495" t="n"/>
-      <c r="J1" s="496" t="n"/>
-      <c r="K1" s="496" t="n"/>
-      <c r="L1" s="496" t="n"/>
-      <c r="M1" s="496" t="n"/>
-      <c r="N1" s="496" t="n"/>
-      <c r="O1" s="496" t="n"/>
-      <c r="P1" s="496" t="n"/>
-      <c r="Q1" s="496" t="n"/>
-      <c r="R1" s="496" t="n"/>
-      <c r="S1" s="496" t="n"/>
-      <c r="T1" s="496" t="n"/>
-      <c r="U1" s="496" t="n"/>
-      <c r="V1" s="496" t="n"/>
-      <c r="W1" s="496" t="n"/>
-      <c r="X1" s="496" t="n"/>
-      <c r="Y1" s="496" t="n"/>
-      <c r="Z1" s="496" t="n"/>
-      <c r="AA1" s="496" t="n"/>
-      <c r="AB1" s="496" t="n"/>
-      <c r="AC1" s="496" t="n"/>
-      <c r="AD1" s="497" t="n"/>
-      <c r="AE1" s="498" t="n"/>
-      <c r="AF1" s="499" t="n"/>
-      <c r="AG1" s="499" t="n"/>
-      <c r="AH1" s="500" t="n"/>
-      <c r="AI1" s="501" t="n"/>
-      <c r="AJ1" s="502" t="n"/>
-      <c r="AK1" s="502" t="n"/>
-      <c r="AL1" s="502" t="n"/>
-      <c r="AM1" s="502" t="n"/>
-      <c r="AN1" s="503" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="613" t="inlineStr">
-        <is>
-          <t>Reference release package, planner snapshot and dossier evidence only.</t>
-        </is>
-      </c>
-      <c r="H2" s="614" t="n"/>
-      <c r="I2" s="506" t="n"/>
-      <c r="J2" s="507" t="n"/>
-      <c r="K2" s="507" t="n"/>
-      <c r="L2" s="507" t="n"/>
-      <c r="M2" s="507" t="n"/>
-      <c r="N2" s="507" t="n"/>
-      <c r="O2" s="507" t="n"/>
-      <c r="P2" s="507" t="n"/>
-      <c r="Q2" s="507" t="n"/>
-      <c r="R2" s="507" t="n"/>
-      <c r="S2" s="507" t="n"/>
-      <c r="T2" s="507" t="n"/>
-      <c r="U2" s="507" t="n"/>
-      <c r="V2" s="507" t="n"/>
-      <c r="W2" s="507" t="n"/>
-      <c r="X2" s="507" t="n"/>
-      <c r="Y2" s="507" t="n"/>
-      <c r="Z2" s="507" t="n"/>
-      <c r="AA2" s="507" t="n"/>
-      <c r="AB2" s="507" t="n"/>
-      <c r="AC2" s="507" t="n"/>
-      <c r="AD2" s="508" t="n"/>
-      <c r="AE2" s="509" t="n"/>
-      <c r="AF2" s="510" t="n"/>
-      <c r="AG2" s="510" t="n"/>
-      <c r="AH2" s="511" t="n"/>
-      <c r="AI2" s="512" t="n"/>
-      <c r="AJ2" s="513" t="n"/>
-      <c r="AK2" s="513" t="n"/>
-      <c r="AL2" s="513" t="n"/>
-      <c r="AM2" s="513" t="n"/>
-      <c r="AN2" s="514" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="615" t="inlineStr">
-        <is>
-          <t>Ref Type</t>
-        </is>
-      </c>
-      <c r="B3" s="616" t="inlineStr">
-        <is>
-          <t>Document / Record</t>
-        </is>
-      </c>
-      <c r="C3" s="616" t="inlineStr">
-        <is>
-          <t>System of Record</t>
-        </is>
-      </c>
-      <c r="D3" s="616" t="inlineStr">
-        <is>
-          <t>Unique Ref</t>
-        </is>
-      </c>
-      <c r="E3" s="616" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F3" s="616" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G3" s="616" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="H3" s="614" t="n"/>
-      <c r="I3" s="506" t="n"/>
-      <c r="J3" s="507" t="n"/>
-      <c r="K3" s="507" t="n"/>
-      <c r="L3" s="507" t="n"/>
-      <c r="M3" s="507" t="n"/>
-      <c r="N3" s="507" t="n"/>
-      <c r="O3" s="507" t="n"/>
-      <c r="P3" s="507" t="n"/>
-      <c r="Q3" s="507" t="n"/>
-      <c r="R3" s="507" t="n"/>
-      <c r="S3" s="507" t="n"/>
-      <c r="T3" s="507" t="n"/>
-      <c r="U3" s="507" t="n"/>
-      <c r="V3" s="507" t="n"/>
-      <c r="W3" s="507" t="n"/>
-      <c r="X3" s="507" t="n"/>
-      <c r="Y3" s="507" t="n"/>
-      <c r="Z3" s="507" t="n"/>
-      <c r="AA3" s="507" t="n"/>
-      <c r="AB3" s="507" t="n"/>
-      <c r="AC3" s="507" t="n"/>
-      <c r="AD3" s="508" t="n"/>
-      <c r="AE3" s="509" t="n"/>
-      <c r="AF3" s="510" t="n"/>
-      <c r="AG3" s="510" t="n"/>
-      <c r="AH3" s="511" t="n"/>
-      <c r="AI3" s="512" t="n"/>
-      <c r="AJ3" s="513" t="n"/>
-      <c r="AK3" s="513" t="n"/>
-      <c r="AL3" s="513" t="n"/>
-      <c r="AM3" s="513" t="n"/>
-      <c r="AN3" s="514" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="617" t="n"/>
-      <c r="B4" s="618" t="n"/>
-      <c r="C4" s="618" t="n"/>
-      <c r="D4" s="618" t="n"/>
-      <c r="E4" s="618" t="n"/>
-      <c r="F4" s="618" t="n"/>
-      <c r="G4" s="618" t="n"/>
-      <c r="H4" s="614" t="n"/>
-      <c r="I4" s="515" t="n"/>
-      <c r="J4" s="516" t="n"/>
-      <c r="K4" s="516" t="n"/>
-      <c r="L4" s="516" t="n"/>
-      <c r="M4" s="516" t="n"/>
-      <c r="N4" s="516" t="n"/>
-      <c r="O4" s="516" t="n"/>
-      <c r="P4" s="516" t="n"/>
-      <c r="Q4" s="516" t="n"/>
-      <c r="R4" s="516" t="n"/>
-      <c r="S4" s="516" t="n"/>
-      <c r="T4" s="516" t="n"/>
-      <c r="U4" s="516" t="n"/>
-      <c r="V4" s="516" t="n"/>
-      <c r="W4" s="516" t="n"/>
-      <c r="X4" s="516" t="n"/>
-      <c r="Y4" s="516" t="n"/>
-      <c r="Z4" s="516" t="n"/>
-      <c r="AA4" s="516" t="n"/>
-      <c r="AB4" s="516" t="n"/>
-      <c r="AC4" s="516" t="n"/>
-      <c r="AD4" s="517" t="n"/>
-      <c r="AE4" s="509" t="n"/>
-      <c r="AF4" s="510" t="n"/>
-      <c r="AG4" s="510" t="n"/>
-      <c r="AH4" s="511" t="n"/>
-      <c r="AI4" s="512" t="n"/>
-      <c r="AJ4" s="513" t="n"/>
-      <c r="AK4" s="513" t="n"/>
-      <c r="AL4" s="513" t="n"/>
-      <c r="AM4" s="513" t="n"/>
-      <c r="AN4" s="514" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="619" t="n"/>
-      <c r="B5" s="620" t="n"/>
-      <c r="C5" s="620" t="n"/>
-      <c r="D5" s="620" t="n"/>
-      <c r="E5" s="620" t="n"/>
-      <c r="F5" s="620" t="n"/>
-      <c r="G5" s="620" t="n"/>
-      <c r="H5" s="621" t="n"/>
-      <c r="I5" s="521" t="n"/>
-      <c r="J5" s="522" t="n"/>
-      <c r="K5" s="522" t="n"/>
-      <c r="L5" s="522" t="n"/>
-      <c r="M5" s="522" t="n"/>
-      <c r="N5" s="522" t="n"/>
-      <c r="O5" s="522" t="n"/>
-      <c r="P5" s="522" t="n"/>
-      <c r="Q5" s="522" t="n"/>
-      <c r="R5" s="522" t="n"/>
-      <c r="S5" s="522" t="n"/>
-      <c r="T5" s="522" t="n"/>
-      <c r="U5" s="522" t="n"/>
-      <c r="V5" s="522" t="n"/>
-      <c r="W5" s="522" t="n"/>
-      <c r="X5" s="522" t="n"/>
-      <c r="Y5" s="522" t="n"/>
-      <c r="Z5" s="522" t="n"/>
-      <c r="AA5" s="522" t="n"/>
-      <c r="AB5" s="522" t="n"/>
-      <c r="AC5" s="522" t="n"/>
-      <c r="AD5" s="523" t="n"/>
-      <c r="AE5" s="524" t="n"/>
-      <c r="AF5" s="525" t="n"/>
-      <c r="AG5" s="525" t="n"/>
-      <c r="AH5" s="526" t="n"/>
-      <c r="AI5" s="527" t="n"/>
-      <c r="AJ5" s="528" t="n"/>
-      <c r="AK5" s="528" t="n"/>
-      <c r="AL5" s="528" t="n"/>
-      <c r="AM5" s="528" t="n"/>
-      <c r="AN5" s="529" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="622" t="n"/>
-      <c r="B6" s="623" t="n"/>
-      <c r="C6" s="623" t="n"/>
-      <c r="D6" s="623" t="n"/>
-      <c r="E6" s="623" t="n"/>
-      <c r="F6" s="623" t="n"/>
-      <c r="G6" s="623" t="n"/>
-      <c r="H6" s="535" t="n"/>
-      <c r="I6" s="535" t="n"/>
-      <c r="J6" s="535" t="n"/>
-      <c r="K6" s="535" t="n"/>
-      <c r="L6" s="535" t="n"/>
-      <c r="M6" s="535" t="n"/>
-      <c r="N6" s="535" t="n"/>
-      <c r="O6" s="535" t="n"/>
-      <c r="P6" s="535" t="n"/>
-      <c r="Q6" s="535" t="n"/>
-      <c r="R6" s="535" t="n"/>
-      <c r="S6" s="535" t="n"/>
-      <c r="T6" s="535" t="n"/>
-      <c r="U6" s="535" t="n"/>
-      <c r="V6" s="535" t="n"/>
-      <c r="W6" s="535" t="n"/>
-      <c r="X6" s="535" t="n"/>
-      <c r="Y6" s="535" t="n"/>
-      <c r="Z6" s="535" t="n"/>
-      <c r="AA6" s="535" t="n"/>
-      <c r="AB6" s="535" t="n"/>
-      <c r="AC6" s="535" t="n"/>
-      <c r="AD6" s="535" t="n"/>
-      <c r="AE6" s="535" t="n"/>
-      <c r="AF6" s="535" t="n"/>
-      <c r="AG6" s="535" t="n"/>
-      <c r="AH6" s="535" t="n"/>
-      <c r="AI6" s="535" t="n"/>
-      <c r="AJ6" s="535" t="n"/>
-      <c r="AK6" s="535" t="n"/>
-      <c r="AL6" s="535" t="n"/>
-      <c r="AM6" s="535" t="n"/>
-      <c r="AN6" s="538" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="624" t="n"/>
-      <c r="B7" s="625" t="n"/>
-      <c r="C7" s="625" t="n"/>
-      <c r="D7" s="625" t="n"/>
-      <c r="E7" s="625" t="n"/>
-      <c r="F7" s="625" t="n"/>
-      <c r="G7" s="625" t="n"/>
-      <c r="H7" s="398" t="n"/>
-      <c r="I7" s="398" t="n"/>
-      <c r="J7" s="398" t="n"/>
-      <c r="K7" s="398" t="n"/>
-      <c r="L7" s="398" t="n"/>
-      <c r="M7" s="398" t="n"/>
-      <c r="N7" s="398" t="n"/>
-      <c r="O7" s="398" t="n"/>
-      <c r="P7" s="398" t="n"/>
-      <c r="Q7" s="398" t="n"/>
-      <c r="R7" s="398" t="n"/>
-      <c r="S7" s="398" t="n"/>
-      <c r="T7" s="398" t="n"/>
-      <c r="U7" s="398" t="n"/>
-      <c r="V7" s="398" t="n"/>
-      <c r="W7" s="398" t="n"/>
-      <c r="X7" s="398" t="n"/>
-      <c r="Y7" s="398" t="n"/>
-      <c r="Z7" s="398" t="n"/>
-      <c r="AA7" s="398" t="n"/>
-      <c r="AB7" s="398" t="n"/>
-      <c r="AC7" s="398" t="n"/>
-      <c r="AD7" s="398" t="n"/>
-      <c r="AE7" s="398" t="n"/>
-      <c r="AF7" s="398" t="n"/>
-      <c r="AG7" s="398" t="n"/>
-      <c r="AH7" s="398" t="n"/>
-      <c r="AI7" s="398" t="n"/>
-      <c r="AJ7" s="398" t="n"/>
-      <c r="AK7" s="398" t="n"/>
-      <c r="AL7" s="398" t="n"/>
-      <c r="AM7" s="398" t="n"/>
-      <c r="AN7" s="542" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="626" t="n"/>
-      <c r="B8" s="627" t="n"/>
-      <c r="C8" s="627" t="n"/>
-      <c r="D8" s="627" t="n"/>
-      <c r="E8" s="627" t="n"/>
-      <c r="F8" s="627" t="n"/>
-      <c r="G8" s="627" t="n"/>
-      <c r="H8" s="413" t="n"/>
-      <c r="I8" s="413" t="n"/>
-      <c r="J8" s="413" t="n"/>
-      <c r="K8" s="413" t="n"/>
-      <c r="L8" s="413" t="n"/>
-      <c r="M8" s="413" t="n"/>
-      <c r="N8" s="413" t="n"/>
-      <c r="O8" s="413" t="n"/>
-      <c r="P8" s="413" t="n"/>
-      <c r="Q8" s="413" t="n"/>
-      <c r="R8" s="413" t="n"/>
-      <c r="S8" s="413" t="n"/>
-      <c r="T8" s="413" t="n"/>
-      <c r="U8" s="413" t="n"/>
-      <c r="V8" s="413" t="n"/>
-      <c r="W8" s="413" t="n"/>
-      <c r="X8" s="413" t="n"/>
-      <c r="Y8" s="413" t="n"/>
-      <c r="Z8" s="413" t="n"/>
-      <c r="AA8" s="413" t="n"/>
-      <c r="AB8" s="413" t="n"/>
-      <c r="AC8" s="413" t="n"/>
-      <c r="AD8" s="413" t="n"/>
-      <c r="AE8" s="413" t="n"/>
-      <c r="AF8" s="413" t="n"/>
-      <c r="AG8" s="413" t="n"/>
-      <c r="AH8" s="413" t="n"/>
-      <c r="AI8" s="413" t="n"/>
-      <c r="AJ8" s="413" t="n"/>
-      <c r="AK8" s="413" t="n"/>
-      <c r="AL8" s="413" t="n"/>
-      <c r="AM8" s="413" t="n"/>
-      <c r="AN8" s="595" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="624" t="n"/>
-      <c r="B9" s="625" t="n"/>
-      <c r="C9" s="625" t="n"/>
-      <c r="D9" s="625" t="n"/>
-      <c r="E9" s="625" t="n"/>
-      <c r="F9" s="625" t="n"/>
-      <c r="G9" s="625" t="n"/>
-      <c r="H9" s="413" t="n"/>
-      <c r="I9" s="413" t="n"/>
-      <c r="J9" s="413" t="n"/>
-      <c r="K9" s="413" t="n"/>
-      <c r="L9" s="413" t="n"/>
-      <c r="M9" s="413" t="n"/>
-      <c r="N9" s="413" t="n"/>
-      <c r="O9" s="413" t="n"/>
-      <c r="P9" s="413" t="n"/>
-      <c r="Q9" s="413" t="n"/>
-      <c r="R9" s="413" t="n"/>
-      <c r="S9" s="413" t="n"/>
-      <c r="T9" s="413" t="n"/>
-      <c r="U9" s="413" t="n"/>
-      <c r="V9" s="413" t="n"/>
-      <c r="W9" s="413" t="n"/>
-      <c r="X9" s="413" t="n"/>
-      <c r="Y9" s="413" t="n"/>
-      <c r="Z9" s="413" t="n"/>
-      <c r="AA9" s="413" t="n"/>
-      <c r="AB9" s="413" t="n"/>
-      <c r="AC9" s="413" t="n"/>
-      <c r="AD9" s="413" t="n"/>
-      <c r="AE9" s="413" t="n"/>
-      <c r="AF9" s="413" t="n"/>
-      <c r="AG9" s="413" t="n"/>
-      <c r="AH9" s="413" t="n"/>
-      <c r="AI9" s="413" t="n"/>
-      <c r="AJ9" s="413" t="n"/>
-      <c r="AK9" s="413" t="n"/>
-      <c r="AL9" s="413" t="n"/>
-      <c r="AM9" s="413" t="n"/>
-      <c r="AN9" s="595" t="n"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="626" t="n"/>
-      <c r="B10" s="627" t="n"/>
-      <c r="C10" s="627" t="n"/>
-      <c r="D10" s="627" t="n"/>
-      <c r="E10" s="627" t="n"/>
-      <c r="F10" s="627" t="n"/>
-      <c r="G10" s="627" t="n"/>
-      <c r="H10" s="413" t="n"/>
-      <c r="I10" s="413" t="n"/>
-      <c r="J10" s="413" t="n"/>
-      <c r="K10" s="413" t="n"/>
-      <c r="L10" s="413" t="n"/>
-      <c r="M10" s="413" t="n"/>
-      <c r="N10" s="413" t="n"/>
-      <c r="O10" s="413" t="n"/>
-      <c r="P10" s="413" t="n"/>
-      <c r="Q10" s="413" t="n"/>
-      <c r="R10" s="413" t="n"/>
-      <c r="S10" s="413" t="n"/>
-      <c r="T10" s="413" t="n"/>
-      <c r="U10" s="413" t="n"/>
-      <c r="V10" s="413" t="n"/>
-      <c r="W10" s="413" t="n"/>
-      <c r="X10" s="413" t="n"/>
-      <c r="Y10" s="413" t="n"/>
-      <c r="Z10" s="413" t="n"/>
-      <c r="AA10" s="413" t="n"/>
-      <c r="AB10" s="413" t="n"/>
-      <c r="AC10" s="413" t="n"/>
-      <c r="AD10" s="413" t="n"/>
-      <c r="AE10" s="413" t="n"/>
-      <c r="AF10" s="413" t="n"/>
-      <c r="AG10" s="413" t="n"/>
-      <c r="AH10" s="413" t="n"/>
-      <c r="AI10" s="413" t="n"/>
-      <c r="AJ10" s="413" t="n"/>
-      <c r="AK10" s="413" t="n"/>
-      <c r="AL10" s="413" t="n"/>
-      <c r="AM10" s="413" t="n"/>
-      <c r="AN10" s="595" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="628" t="n"/>
-      <c r="B11" s="629" t="n"/>
-      <c r="C11" s="629" t="n"/>
-      <c r="D11" s="629" t="n"/>
-      <c r="E11" s="629" t="n"/>
-      <c r="F11" s="629" t="n"/>
-      <c r="G11" s="629" t="n"/>
-      <c r="H11" s="600" t="n"/>
-      <c r="I11" s="600" t="n"/>
-      <c r="J11" s="600" t="n"/>
-      <c r="K11" s="600" t="n"/>
-      <c r="L11" s="600" t="n"/>
-      <c r="M11" s="600" t="n"/>
-      <c r="N11" s="600" t="n"/>
-      <c r="O11" s="600" t="n"/>
-      <c r="P11" s="600" t="n"/>
-      <c r="Q11" s="600" t="n"/>
-      <c r="R11" s="600" t="n"/>
-      <c r="S11" s="600" t="n"/>
-      <c r="T11" s="600" t="n"/>
-      <c r="U11" s="600" t="n"/>
-      <c r="V11" s="600" t="n"/>
-      <c r="W11" s="600" t="n"/>
-      <c r="X11" s="600" t="n"/>
-      <c r="Y11" s="600" t="n"/>
-      <c r="Z11" s="600" t="n"/>
-      <c r="AA11" s="600" t="n"/>
-      <c r="AB11" s="600" t="n"/>
-      <c r="AC11" s="600" t="n"/>
-      <c r="AD11" s="600" t="n"/>
-      <c r="AE11" s="600" t="n"/>
-      <c r="AF11" s="600" t="n"/>
-      <c r="AG11" s="600" t="n"/>
-      <c r="AH11" s="600" t="n"/>
-      <c r="AI11" s="600" t="n"/>
-      <c r="AJ11" s="600" t="n"/>
-      <c r="AK11" s="600" t="n"/>
-      <c r="AL11" s="600" t="n"/>
-      <c r="AM11" s="600" t="n"/>
-      <c r="AN11" s="601" t="n"/>
-    </row>
-    <row r="12" hidden="1"/>
-    <row r="13" hidden="1"/>
-    <row r="14" hidden="1"/>
-    <row r="15" hidden="1"/>
-    <row r="16" hidden="1"/>
-    <row r="17" hidden="1"/>
-    <row r="18" hidden="1"/>
-    <row r="19" hidden="1"/>
-    <row r="20" hidden="1"/>
-    <row r="21" hidden="1"/>
-    <row r="22" hidden="1"/>
-    <row r="23" hidden="1"/>
-    <row r="24" hidden="1"/>
-    <row r="25" hidden="1"/>
-    <row r="26" hidden="1"/>
-    <row r="27" hidden="1"/>
-    <row r="28" hidden="1"/>
-    <row r="29" hidden="1"/>
-    <row r="30" hidden="1"/>
-    <row r="31" hidden="1"/>
-    <row r="32" hidden="1"/>
-    <row r="33" hidden="1"/>
-    <row r="34" hidden="1"/>
-    <row r="35" hidden="1"/>
-    <row r="36" hidden="1"/>
-    <row r="37" hidden="1"/>
-    <row r="38" hidden="1"/>
-    <row r="39" hidden="1"/>
-    <row r="40" hidden="1"/>
-    <row r="41" hidden="1"/>
-    <row r="42" hidden="1"/>
-    <row r="43" hidden="1"/>
-    <row r="44" hidden="1"/>
-    <row r="45" hidden="1"/>
-    <row r="46" hidden="1"/>
-    <row r="47" hidden="1"/>
-    <row r="48" hidden="1"/>
-    <row r="49" hidden="1"/>
-    <row r="50" hidden="1"/>
-    <row r="51" hidden="1"/>
-    <row r="52" hidden="1"/>
-    <row r="53" hidden="1"/>
-    <row r="54" hidden="1"/>
-    <row r="55" hidden="1"/>
-    <row r="56" hidden="1"/>
-    <row r="57" hidden="1"/>
-    <row r="58" hidden="1"/>
-    <row r="59" hidden="1"/>
-    <row r="60" hidden="1"/>
-    <row r="61" hidden="1"/>
-    <row r="62" hidden="1"/>
-    <row r="63" hidden="1"/>
-    <row r="64" hidden="1"/>
-    <row r="65" hidden="1"/>
-    <row r="66" hidden="1"/>
-    <row r="67" hidden="1"/>
-    <row r="68" hidden="1"/>
-    <row r="69" hidden="1"/>
-    <row r="70" hidden="1"/>
-    <row r="71" hidden="1"/>
-    <row r="72" hidden="1"/>
-    <row r="73" hidden="1"/>
-    <row r="74" hidden="1"/>
-    <row r="75" hidden="1"/>
-    <row r="76" hidden="1"/>
-    <row r="77" hidden="1"/>
-    <row r="78" hidden="1"/>
-    <row r="79" hidden="1"/>
-    <row r="80" hidden="1"/>
-    <row r="81" hidden="1"/>
-    <row r="82" hidden="1"/>
-    <row r="83" hidden="1"/>
-    <row r="84" hidden="1"/>
-    <row r="85" hidden="1"/>
-    <row r="86" hidden="1"/>
-    <row r="87" hidden="1"/>
-    <row r="88" hidden="1"/>
-    <row r="89" hidden="1"/>
-    <row r="90" hidden="1"/>
-    <row r="91" hidden="1"/>
-    <row r="92" hidden="1"/>
-    <row r="93" hidden="1"/>
-    <row r="94" hidden="1"/>
-    <row r="95" hidden="1"/>
-    <row r="96" hidden="1"/>
-    <row r="97" hidden="1"/>
-    <row r="98" hidden="1"/>
-    <row r="99" hidden="1"/>
-    <row r="100" hidden="1"/>
-    <row r="101" hidden="1"/>
-    <row r="102" hidden="1"/>
-    <row r="103" hidden="1"/>
-    <row r="104" hidden="1"/>
-    <row r="105" hidden="1"/>
-    <row r="106" hidden="1"/>
-    <row r="107" hidden="1"/>
-    <row r="108" hidden="1"/>
-    <row r="109" hidden="1"/>
-    <row r="110" hidden="1"/>
-    <row r="111" hidden="1"/>
-    <row r="112" hidden="1"/>
-    <row r="113" hidden="1"/>
-    <row r="114" hidden="1"/>
-    <row r="115" hidden="1"/>
-    <row r="116" hidden="1"/>
-    <row r="117" hidden="1"/>
-    <row r="118" hidden="1"/>
-    <row r="119" hidden="1"/>
-    <row r="120" hidden="1"/>
-    <row r="121" hidden="1"/>
-    <row r="122" hidden="1"/>
-    <row r="123" hidden="1"/>
-    <row r="124" hidden="1"/>
-    <row r="125" hidden="1"/>
-    <row r="126" hidden="1"/>
-    <row r="127" hidden="1"/>
-    <row r="128" hidden="1"/>
-    <row r="129" hidden="1"/>
-    <row r="130" hidden="1"/>
-    <row r="131" hidden="1"/>
-    <row r="132" hidden="1"/>
-    <row r="133" hidden="1"/>
-    <row r="134" hidden="1"/>
-    <row r="135" hidden="1"/>
-    <row r="136" hidden="1"/>
-    <row r="137" hidden="1"/>
-    <row r="138" hidden="1"/>
-    <row r="139" hidden="1"/>
-    <row r="140" hidden="1"/>
-    <row r="141" hidden="1"/>
-    <row r="142" hidden="1"/>
-    <row r="143" hidden="1"/>
-    <row r="144" hidden="1"/>
-    <row r="145" hidden="1"/>
-    <row r="146" hidden="1"/>
-    <row r="147" hidden="1"/>
-    <row r="148" hidden="1"/>
-    <row r="149" hidden="1"/>
-    <row r="150" hidden="1"/>
-    <row r="151" hidden="1"/>
-    <row r="152" hidden="1"/>
-    <row r="153" hidden="1"/>
-    <row r="154" hidden="1"/>
-    <row r="155" hidden="1"/>
-    <row r="156" hidden="1"/>
-    <row r="157" hidden="1"/>
-    <row r="158" hidden="1"/>
-    <row r="159" hidden="1"/>
-    <row r="160" hidden="1"/>
-    <row r="161" hidden="1"/>
-    <row r="162" hidden="1"/>
-    <row r="163" hidden="1"/>
-    <row r="164" hidden="1"/>
-    <row r="165" hidden="1"/>
-    <row r="166" hidden="1"/>
-    <row r="167" hidden="1"/>
-    <row r="168" hidden="1"/>
-    <row r="169" hidden="1"/>
-    <row r="170" hidden="1"/>
-    <row r="171" hidden="1"/>
-    <row r="172" hidden="1"/>
-    <row r="173" hidden="1"/>
-    <row r="174" hidden="1"/>
-    <row r="175" hidden="1"/>
-    <row r="176" hidden="1"/>
-    <row r="177" hidden="1"/>
-    <row r="178" hidden="1"/>
-    <row r="179" hidden="1"/>
-    <row r="180" hidden="1"/>
-    <row r="181" hidden="1"/>
-    <row r="182" hidden="1"/>
-    <row r="183" hidden="1"/>
-    <row r="184" hidden="1"/>
-    <row r="185" hidden="1"/>
-    <row r="186" hidden="1"/>
-    <row r="187" hidden="1"/>
-    <row r="188" hidden="1"/>
-    <row r="189" hidden="1"/>
-    <row r="190" hidden="1"/>
-    <row r="191" hidden="1"/>
-    <row r="192" hidden="1"/>
-    <row r="193" hidden="1"/>
-    <row r="194" hidden="1"/>
-    <row r="195" hidden="1"/>
-    <row r="196" hidden="1"/>
-    <row r="197" hidden="1"/>
-    <row r="198" hidden="1"/>
-    <row r="199" hidden="1"/>
-    <row r="200" hidden="1"/>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="E4:E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use controlled value from REF_OWNER_PERSON_MASTER." prompt="Select from REF_OWNER_PERSON_MASTER." type="list">
-      <formula1>=REF_OWNER_PERSON_MASTER</formula1>
-    </dataValidation>
-    <dataValidation sqref="F4:F11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use controlled value from VAL_STATUS_CORE." prompt="Select from VAL_STATUS_CORE." type="list">
-      <formula1>=VAL_STATUS_CORE</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
@@ -25,386 +25,12 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
-  </si>
-  <si>
-    <t>1.  HIGH-RISK JOB HEADER / REFERENCE INFORMATION</t>
-  </si>
-  <si>
-    <t>2.  READINESS DECISION / OPEN RISK CONDITIONS</t>
-  </si>
-  <si>
-    <t>2.  WORKING TABLE / DETAIL LINES</t>
-  </si>
-  <si>
-    <t>3.  READINESS CRITERIA / RISK CHECK</t>
-  </si>
-  <si>
-    <t>4.  OPEN RISK ACTIONS / CONTAINMENT</t>
-  </si>
-  <si>
-    <t>5.  APPROVAL / SIGN-OFF</t>
-  </si>
-  <si>
-    <t>=IF(COUNTA(AF22:AF31)=0,"",IF(COUNTIF(AF22:AF31,"FAIL")+COUNTIF(AF22:AF31,"HOLD")&gt;0,"HOLD",IF(COUNTIF(AF22:AF31,"PASS")=COUNTA(AF22:AF31),"APPROVED","CONDITIONAL")))</t>
-  </si>
-  <si>
-    <t>=IF(COUNTA(AF22:AF31)=0,"",IF(COUNTIF(AF22:AF31,"FAIL")+COUNTIF(AF22:AF31,"HOLD")&gt;0,"OPEN","CLOSED"))</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$17)+1</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>Acceptance / Control Rule</t>
-  </si>
-  <si>
-    <t>Action Owner</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Approved by</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>CONDITIONAL</t>
-  </si>
-  <si>
-    <t>CRITICAL</t>
-  </si>
-  <si>
-    <t>CSR / cert / packaging rules are visible.</t>
-  </si>
-  <si>
-    <t>Capability and readiness path are visible.</t>
-  </si>
-  <si>
-    <t>Cat.</t>
-  </si>
-  <si>
-    <t>Commercial / Ops Owner</t>
-  </si>
-  <si>
-    <t>Commitment and ship impact are realistic.</t>
-  </si>
-  <si>
-    <t>Conditional-release authority is explicit.</t>
-  </si>
-  <si>
-    <t>Containment / Action</t>
-  </si>
-  <si>
-    <t>Containment / contingency exists.</t>
-  </si>
-  <si>
-    <t>Controlled Status</t>
-  </si>
-  <si>
-    <t>Critical source path is not assumed.</t>
-  </si>
-  <si>
-    <t>Current Route Step</t>
-  </si>
-  <si>
-    <t>Customer</t>
-  </si>
-  <si>
-    <t>Customer / quality package is identified.</t>
-  </si>
-  <si>
-    <t>Data Structure</t>
-  </si>
-  <si>
-    <t>Decision can be reconstructed later.</t>
-  </si>
-  <si>
-    <t>Delivery / ship logic is feasible.</t>
-  </si>
-  <si>
-    <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
-  </si>
-  <si>
-    <t>Due Date</t>
-  </si>
-  <si>
-    <t>Due Date / Commit</t>
-  </si>
-  <si>
-    <t>Eff. Date</t>
-  </si>
-  <si>
-    <t>Escalation</t>
-  </si>
-  <si>
-    <t>Escalation if Overdue</t>
-  </si>
-  <si>
-    <t>Evidence Folder</t>
-  </si>
-  <si>
-    <t>Evidence Ref</t>
-  </si>
-  <si>
-    <t>Evidence path and dossier traceability exist.</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>FRM-209</t>
-  </si>
-  <si>
-    <t>FRM-209 · HIGH-RISK JOB READINESS REVIEW</t>
-  </si>
-  <si>
-    <t>FRM-306 or released package reference is current.</t>
-  </si>
-  <si>
-    <t>First-piece / FAI strategy is defined.</t>
-  </si>
-  <si>
-    <t>Form Code</t>
-  </si>
-  <si>
-    <t>Gate Conclusion</t>
-  </si>
-  <si>
-    <t>Gate Name / Trigger</t>
-  </si>
-  <si>
-    <t>Gate Status</t>
-  </si>
-  <si>
-    <t>General Manager</t>
-  </si>
-  <si>
-    <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>HIGH-RISK JOB READINESS REVIEW</t>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>High-risk job release review</t>
-  </si>
-  <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
-    <t>Impact</t>
-  </si>
-  <si>
-    <t>Job / WO</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>MONITORING</t>
-  </si>
-  <si>
-    <t>Machine / tooling / gage readiness exists.</t>
-  </si>
-  <si>
-    <t>Material / outsource path is feasible.</t>
-  </si>
-  <si>
-    <t>Most severe risk is named, not hidden.</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>NOTICE  —  Enter data only in designated white input cells. Do not add, delete or resize columns/rows. File naming: FRM-209_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
-  </si>
-  <si>
-    <t>NOTICE  —  One line per material, capacity, quality or customer-risk condition.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
-  </si>
-  <si>
-    <t>Name  /  Signature  /  Date</t>
-  </si>
-  <si>
-    <t>Next Step</t>
-  </si>
-  <si>
-    <t>No conditional release without named owner.</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>One line per material, capacity, quality or customer-risk condition.</t>
-  </si>
-  <si>
-    <t>Open Risk / Hold Reason</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>Parent Form</t>
-  </si>
-  <si>
-    <t>Part No. / Revision</t>
-  </si>
-  <si>
-    <t>Planning / QA / Engineering</t>
-  </si>
-  <si>
-    <t>Prepared by</t>
-  </si>
-  <si>
-    <t>QA gate logic and owner are visible.</t>
-  </si>
-  <si>
-    <t>Quality Management System  ·  Controlled Document</t>
-  </si>
-  <si>
-    <t>REJECT</t>
-  </si>
-  <si>
-    <t>RISKS / ACTIONS REGISTER</t>
-  </si>
-  <si>
-    <t>RISKS_ACTIONS</t>
-  </si>
-  <si>
-    <t>RSK</t>
-  </si>
-  <si>
-    <t>Readiness / Risk Item</t>
-  </si>
-  <si>
-    <t>Readiness Review ID</t>
-  </si>
-  <si>
-    <t>Record Status</t>
-  </si>
-  <si>
-    <t>Recovery path exists if primary plan fails.</t>
-  </si>
-  <si>
-    <t>Ref.</t>
-  </si>
-  <si>
-    <t>Released baseline package is locked.</t>
-  </si>
-  <si>
-    <t>Required Containment / Action</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Retention Rule</t>
-  </si>
-  <si>
-    <t>Reviewed By</t>
-  </si>
-  <si>
-    <t>Reviewed by</t>
-  </si>
-  <si>
-    <t>Revision</t>
-  </si>
-  <si>
-    <t>Risk / Readiness Gap</t>
-  </si>
-  <si>
-    <t>SUPERSEDED</t>
-  </si>
-  <si>
-    <t>Source of Truth</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Structured Excel Table with filters and print-title rows.</t>
-  </si>
-  <si>
-    <t>Support Tab</t>
-  </si>
-  <si>
-    <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
-  </si>
-  <si>
-    <t>Tab Purpose</t>
-  </si>
-  <si>
-    <t>Top Risk Class</t>
-  </si>
-  <si>
-    <t>Top abnormal / failure mode is explicit.</t>
-  </si>
-  <si>
-    <t>Update Trigger</t>
-  </si>
-  <si>
-    <t>Update when the linked review, evidence or follow-up status changes.</t>
-  </si>
-  <si>
-    <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
-  </si>
-  <si>
-    <t>V0</t>
-  </si>
-  <si>
-    <t>VAL_DECISION_GATE_CORE</t>
-  </si>
-  <si>
-    <t>VAL_RESULT_CORE</t>
-  </si>
-  <si>
-    <t>VAL_RISK_LEVEL_CORE</t>
-  </si>
-  <si>
-    <t>VAL_STATUS_CORE</t>
-  </si>
-  <si>
-    <t>VOID</t>
-  </si>
-  <si>
-    <t>Verified by</t>
-  </si>
-  <si>
-    <t>Working Owner</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="91">
+  <fonts count="92">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -918,6 +544,9 @@
       <color rgb="007B4F00"/>
       <sz val="7"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
   <fills count="58">
     <fill>
@@ -1207,7 +836,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="394">
+  <borders count="395">
     <border>
       <left/>
       <right/>
@@ -5479,12 +5108,22 @@
         <color rgb="00F9A825"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="771">
+  <cellXfs count="791">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -7390,6 +7029,40 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="392" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="393" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="91" fillId="4" borderId="314" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="315" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="316" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="317" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="320" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="53" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="302" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="323" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="324" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="325" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="53" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="394" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="52" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -10479,7 +10152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -10524,397 +10197,818 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="402" t="inlineStr">
-        <is>
-          <t>VAL_RESULT_CORE</t>
-        </is>
-      </c>
-      <c r="B1" s="402" t="inlineStr">
-        <is>
-          <t>VAL_DECISION_GATE_CORE</t>
-        </is>
-      </c>
-      <c r="C1" s="402" t="inlineStr">
-        <is>
-          <t>VAL_STATUS_CORE</t>
-        </is>
-      </c>
-      <c r="D1" s="402" t="inlineStr">
-        <is>
-          <t>VAL_RISK_LEVEL_CORE</t>
-        </is>
-      </c>
-      <c r="E1" s="402" t="n"/>
-      <c r="F1" s="402" t="n"/>
-      <c r="G1" s="402" t="n"/>
-      <c r="H1" s="402" t="n"/>
-      <c r="I1" s="402" t="n"/>
-      <c r="J1" s="402" t="n"/>
-      <c r="K1" s="402" t="n"/>
-      <c r="L1" s="402" t="n"/>
-      <c r="M1" s="402" t="n"/>
-      <c r="N1" s="402" t="n"/>
-      <c r="O1" s="402" t="n"/>
-      <c r="P1" s="402" t="n"/>
-      <c r="Q1" s="402" t="n"/>
-      <c r="R1" s="402" t="n"/>
-      <c r="S1" s="402" t="n"/>
-      <c r="T1" s="402" t="n"/>
-      <c r="U1" s="402" t="n"/>
-      <c r="V1" s="402" t="n"/>
-      <c r="W1" s="402" t="n"/>
-      <c r="X1" s="402" t="n"/>
-      <c r="Y1" s="402" t="n"/>
-      <c r="Z1" s="402" t="n"/>
-      <c r="AA1" s="402" t="n"/>
-      <c r="AB1" s="402" t="n"/>
-      <c r="AC1" s="402" t="n"/>
-      <c r="AD1" s="402" t="n"/>
-      <c r="AE1" s="402" t="n"/>
-      <c r="AF1" s="402" t="n"/>
-      <c r="AG1" s="402" t="n"/>
-      <c r="AH1" s="402" t="n"/>
-      <c r="AI1" s="402" t="n"/>
-      <c r="AJ1" s="402" t="n"/>
-      <c r="AK1" s="402" t="n"/>
-      <c r="AL1" s="402" t="n"/>
-      <c r="AM1" s="402" t="n"/>
-      <c r="AN1" s="402" t="n"/>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="771" t="n"/>
+      <c r="B1" s="772" t="n"/>
+      <c r="C1" s="772" t="n"/>
+      <c r="D1" s="772" t="n"/>
+      <c r="E1" s="772" t="n"/>
+      <c r="F1" s="772" t="n"/>
+      <c r="G1" s="772" t="n"/>
+      <c r="H1" s="773" t="n"/>
+      <c r="I1" s="774" t="inlineStr">
+        <is>
+          <t>HIGH-RISK JOB READINESS REVIEW</t>
+        </is>
+      </c>
+      <c r="J1" s="772" t="n"/>
+      <c r="K1" s="772" t="n"/>
+      <c r="L1" s="772" t="n"/>
+      <c r="M1" s="772" t="n"/>
+      <c r="N1" s="772" t="n"/>
+      <c r="O1" s="772" t="n"/>
+      <c r="P1" s="772" t="n"/>
+      <c r="Q1" s="772" t="n"/>
+      <c r="R1" s="772" t="n"/>
+      <c r="S1" s="772" t="n"/>
+      <c r="T1" s="772" t="n"/>
+      <c r="U1" s="772" t="n"/>
+      <c r="V1" s="772" t="n"/>
+      <c r="W1" s="772" t="n"/>
+      <c r="X1" s="772" t="n"/>
+      <c r="Y1" s="772" t="n"/>
+      <c r="Z1" s="772" t="n"/>
+      <c r="AA1" s="772" t="n"/>
+      <c r="AB1" s="772" t="n"/>
+      <c r="AC1" s="772" t="n"/>
+      <c r="AD1" s="773" t="n"/>
+      <c r="AE1" s="499" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="772" t="n"/>
+      <c r="AG1" s="772" t="n"/>
+      <c r="AH1" s="775" t="n"/>
+      <c r="AI1" s="502" t="inlineStr">
+        <is>
+          <t>FRM-209</t>
+        </is>
+      </c>
+      <c r="AJ1" s="772" t="n"/>
+      <c r="AK1" s="772" t="n"/>
+      <c r="AL1" s="772" t="n"/>
+      <c r="AM1" s="772" t="n"/>
+      <c r="AN1" s="773" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" s="402" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B2" s="402" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="C2" s="402" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="D2" s="402" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="E2" s="402" t="n"/>
-      <c r="F2" s="402" t="n"/>
-      <c r="G2" s="402" t="n"/>
-      <c r="H2" s="402" t="n"/>
-      <c r="I2" s="402" t="n"/>
-      <c r="J2" s="402" t="n"/>
-      <c r="K2" s="402" t="n"/>
-      <c r="L2" s="402" t="n"/>
-      <c r="M2" s="402" t="n"/>
-      <c r="N2" s="402" t="n"/>
-      <c r="O2" s="402" t="n"/>
-      <c r="P2" s="402" t="n"/>
-      <c r="Q2" s="402" t="n"/>
-      <c r="R2" s="402" t="n"/>
-      <c r="S2" s="402" t="n"/>
-      <c r="T2" s="402" t="n"/>
-      <c r="U2" s="402" t="n"/>
-      <c r="V2" s="402" t="n"/>
-      <c r="W2" s="402" t="n"/>
-      <c r="X2" s="402" t="n"/>
-      <c r="Y2" s="402" t="n"/>
-      <c r="Z2" s="402" t="n"/>
-      <c r="AA2" s="402" t="n"/>
-      <c r="AB2" s="402" t="n"/>
-      <c r="AC2" s="402" t="n"/>
-      <c r="AD2" s="402" t="n"/>
-      <c r="AE2" s="402" t="n"/>
-      <c r="AF2" s="402" t="n"/>
-      <c r="AG2" s="402" t="n"/>
-      <c r="AH2" s="402" t="n"/>
-      <c r="AI2" s="402" t="n"/>
-      <c r="AJ2" s="402" t="n"/>
-      <c r="AK2" s="402" t="n"/>
-      <c r="AL2" s="402" t="n"/>
-      <c r="AM2" s="402" t="n"/>
-      <c r="AN2" s="402" t="n"/>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="776" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="777" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="777" t="n"/>
+      <c r="AE2" s="778" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="10" t="n"/>
+      <c r="AG2" s="10" t="n"/>
+      <c r="AH2" s="779" t="n"/>
+      <c r="AI2" s="780" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="AJ2" s="10" t="n"/>
+      <c r="AK2" s="10" t="n"/>
+      <c r="AL2" s="10" t="n"/>
+      <c r="AM2" s="10" t="n"/>
+      <c r="AN2" s="777" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="402" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="B3" s="402" t="inlineStr">
-        <is>
-          <t>CONDITIONAL</t>
-        </is>
-      </c>
-      <c r="C3" s="402" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
-        </is>
-      </c>
-      <c r="D3" s="402" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="E3" s="402" t="n"/>
-      <c r="F3" s="402" t="n"/>
-      <c r="G3" s="402" t="n"/>
-      <c r="H3" s="402" t="n"/>
-      <c r="I3" s="402" t="n"/>
-      <c r="J3" s="402" t="n"/>
-      <c r="K3" s="402" t="n"/>
-      <c r="L3" s="402" t="n"/>
-      <c r="M3" s="402" t="n"/>
-      <c r="N3" s="402" t="n"/>
-      <c r="O3" s="402" t="n"/>
-      <c r="P3" s="402" t="n"/>
-      <c r="Q3" s="402" t="n"/>
-      <c r="R3" s="402" t="n"/>
-      <c r="S3" s="402" t="n"/>
-      <c r="T3" s="402" t="n"/>
-      <c r="U3" s="402" t="n"/>
-      <c r="V3" s="402" t="n"/>
-      <c r="W3" s="402" t="n"/>
-      <c r="X3" s="402" t="n"/>
-      <c r="Y3" s="402" t="n"/>
-      <c r="Z3" s="402" t="n"/>
-      <c r="AA3" s="402" t="n"/>
-      <c r="AB3" s="402" t="n"/>
-      <c r="AC3" s="402" t="n"/>
-      <c r="AD3" s="402" t="n"/>
-      <c r="AE3" s="402" t="n"/>
-      <c r="AF3" s="402" t="n"/>
-      <c r="AG3" s="402" t="n"/>
-      <c r="AH3" s="402" t="n"/>
-      <c r="AI3" s="402" t="n"/>
-      <c r="AJ3" s="402" t="n"/>
-      <c r="AK3" s="402" t="n"/>
-      <c r="AL3" s="402" t="n"/>
-      <c r="AM3" s="402" t="n"/>
-      <c r="AN3" s="402" t="n"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="776" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="777" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="777" t="n"/>
+      <c r="AE3" s="778" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="779" t="n"/>
+      <c r="AI3" s="780" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="777" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="402" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="B4" s="402" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="C4" s="402" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="D4" s="402" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E4" s="402" t="n"/>
-      <c r="F4" s="402" t="n"/>
-      <c r="G4" s="402" t="n"/>
-      <c r="H4" s="402" t="n"/>
-      <c r="I4" s="402" t="n"/>
-      <c r="J4" s="402" t="n"/>
-      <c r="K4" s="402" t="n"/>
-      <c r="L4" s="402" t="n"/>
-      <c r="M4" s="402" t="n"/>
-      <c r="N4" s="402" t="n"/>
-      <c r="O4" s="402" t="n"/>
-      <c r="P4" s="402" t="n"/>
-      <c r="Q4" s="402" t="n"/>
-      <c r="R4" s="402" t="n"/>
-      <c r="S4" s="402" t="n"/>
-      <c r="T4" s="402" t="n"/>
-      <c r="U4" s="402" t="n"/>
-      <c r="V4" s="402" t="n"/>
-      <c r="W4" s="402" t="n"/>
-      <c r="X4" s="402" t="n"/>
-      <c r="Y4" s="402" t="n"/>
-      <c r="Z4" s="402" t="n"/>
-      <c r="AA4" s="402" t="n"/>
-      <c r="AB4" s="402" t="n"/>
-      <c r="AC4" s="402" t="n"/>
-      <c r="AD4" s="402" t="n"/>
-      <c r="AE4" s="402" t="n"/>
-      <c r="AF4" s="402" t="n"/>
-      <c r="AG4" s="402" t="n"/>
-      <c r="AH4" s="402" t="n"/>
-      <c r="AI4" s="402" t="n"/>
-      <c r="AJ4" s="402" t="n"/>
-      <c r="AK4" s="402" t="n"/>
-      <c r="AL4" s="402" t="n"/>
-      <c r="AM4" s="402" t="n"/>
-      <c r="AN4" s="402" t="n"/>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="776" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="777" t="n"/>
+      <c r="I4" s="781" t="inlineStr">
+        <is>
+          <t>Quality Management System  ·  Controlled Document</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="777" t="n"/>
+      <c r="AE4" s="778" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="779" t="n"/>
+      <c r="AI4" s="780" t="inlineStr">
+        <is>
+          <t>Planning / QA / Engineering</t>
+        </is>
+      </c>
+      <c r="AJ4" s="10" t="n"/>
+      <c r="AK4" s="10" t="n"/>
+      <c r="AL4" s="10" t="n"/>
+      <c r="AM4" s="10" t="n"/>
+      <c r="AN4" s="777" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="402" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B5" s="402" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="C5" s="402" t="inlineStr">
-        <is>
-          <t>MONITORING</t>
-        </is>
-      </c>
-      <c r="D5" s="402" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="E5" s="402" t="n"/>
-      <c r="F5" s="402" t="n"/>
-      <c r="G5" s="402" t="n"/>
-      <c r="H5" s="402" t="n"/>
-      <c r="I5" s="402" t="n"/>
-      <c r="J5" s="402" t="n"/>
-      <c r="K5" s="402" t="n"/>
-      <c r="L5" s="402" t="n"/>
-      <c r="M5" s="402" t="n"/>
-      <c r="N5" s="402" t="n"/>
-      <c r="O5" s="402" t="n"/>
-      <c r="P5" s="402" t="n"/>
-      <c r="Q5" s="402" t="n"/>
-      <c r="R5" s="402" t="n"/>
-      <c r="S5" s="402" t="n"/>
-      <c r="T5" s="402" t="n"/>
-      <c r="U5" s="402" t="n"/>
-      <c r="V5" s="402" t="n"/>
-      <c r="W5" s="402" t="n"/>
-      <c r="X5" s="402" t="n"/>
-      <c r="Y5" s="402" t="n"/>
-      <c r="Z5" s="402" t="n"/>
-      <c r="AA5" s="402" t="n"/>
-      <c r="AB5" s="402" t="n"/>
-      <c r="AC5" s="402" t="n"/>
-      <c r="AD5" s="402" t="n"/>
-      <c r="AE5" s="402" t="n"/>
-      <c r="AF5" s="402" t="n"/>
-      <c r="AG5" s="402" t="n"/>
-      <c r="AH5" s="402" t="n"/>
-      <c r="AI5" s="402" t="n"/>
-      <c r="AJ5" s="402" t="n"/>
-      <c r="AK5" s="402" t="n"/>
-      <c r="AL5" s="402" t="n"/>
-      <c r="AM5" s="402" t="n"/>
-      <c r="AN5" s="402" t="n"/>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="782" t="n"/>
+      <c r="B5" s="783" t="n"/>
+      <c r="C5" s="783" t="n"/>
+      <c r="D5" s="783" t="n"/>
+      <c r="E5" s="783" t="n"/>
+      <c r="F5" s="783" t="n"/>
+      <c r="G5" s="783" t="n"/>
+      <c r="H5" s="784" t="n"/>
+      <c r="I5" s="785" t="inlineStr">
+        <is>
+          <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
+        </is>
+      </c>
+      <c r="J5" s="783" t="n"/>
+      <c r="K5" s="783" t="n"/>
+      <c r="L5" s="783" t="n"/>
+      <c r="M5" s="783" t="n"/>
+      <c r="N5" s="783" t="n"/>
+      <c r="O5" s="783" t="n"/>
+      <c r="P5" s="783" t="n"/>
+      <c r="Q5" s="783" t="n"/>
+      <c r="R5" s="783" t="n"/>
+      <c r="S5" s="783" t="n"/>
+      <c r="T5" s="783" t="n"/>
+      <c r="U5" s="783" t="n"/>
+      <c r="V5" s="783" t="n"/>
+      <c r="W5" s="783" t="n"/>
+      <c r="X5" s="783" t="n"/>
+      <c r="Y5" s="783" t="n"/>
+      <c r="Z5" s="783" t="n"/>
+      <c r="AA5" s="783" t="n"/>
+      <c r="AB5" s="783" t="n"/>
+      <c r="AC5" s="783" t="n"/>
+      <c r="AD5" s="784" t="n"/>
+      <c r="AE5" s="786" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="783" t="n"/>
+      <c r="AG5" s="783" t="n"/>
+      <c r="AH5" s="787" t="n"/>
+      <c r="AI5" s="788" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="AJ5" s="783" t="n"/>
+      <c r="AK5" s="783" t="n"/>
+      <c r="AL5" s="783" t="n"/>
+      <c r="AM5" s="783" t="n"/>
+      <c r="AN5" s="784" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="402" t="n"/>
-      <c r="B6" s="402" t="n"/>
-      <c r="C6" s="402" t="inlineStr">
-        <is>
-          <t>SUPERSEDED</t>
-        </is>
-      </c>
-      <c r="D6" s="402" t="n"/>
-      <c r="E6" s="402" t="n"/>
-      <c r="F6" s="402" t="n"/>
-      <c r="G6" s="402" t="n"/>
-      <c r="H6" s="402" t="n"/>
-      <c r="I6" s="402" t="n"/>
-      <c r="J6" s="402" t="n"/>
-      <c r="K6" s="402" t="n"/>
-      <c r="L6" s="402" t="n"/>
-      <c r="M6" s="402" t="n"/>
-      <c r="N6" s="402" t="n"/>
-      <c r="O6" s="402" t="n"/>
-      <c r="P6" s="402" t="n"/>
-      <c r="Q6" s="402" t="n"/>
-      <c r="R6" s="402" t="n"/>
-      <c r="S6" s="402" t="n"/>
-      <c r="T6" s="402" t="n"/>
-      <c r="U6" s="402" t="n"/>
-      <c r="V6" s="402" t="n"/>
-      <c r="W6" s="402" t="n"/>
-      <c r="X6" s="402" t="n"/>
-      <c r="Y6" s="402" t="n"/>
-      <c r="Z6" s="402" t="n"/>
-      <c r="AA6" s="402" t="n"/>
-      <c r="AB6" s="402" t="n"/>
-      <c r="AC6" s="402" t="n"/>
-      <c r="AD6" s="402" t="n"/>
-      <c r="AE6" s="402" t="n"/>
-      <c r="AF6" s="402" t="n"/>
-      <c r="AG6" s="402" t="n"/>
-      <c r="AH6" s="402" t="n"/>
-      <c r="AI6" s="402" t="n"/>
-      <c r="AJ6" s="402" t="n"/>
-      <c r="AK6" s="402" t="n"/>
-      <c r="AL6" s="402" t="n"/>
-      <c r="AM6" s="402" t="n"/>
-      <c r="AN6" s="402" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="789" t="n"/>
+      <c r="B6" s="789" t="n"/>
+      <c r="C6" s="789" t="n"/>
+      <c r="D6" s="789" t="n"/>
+      <c r="E6" s="789" t="n"/>
+      <c r="F6" s="789" t="n"/>
+      <c r="G6" s="789" t="n"/>
+      <c r="H6" s="789" t="n"/>
+      <c r="I6" s="789" t="n"/>
+      <c r="J6" s="789" t="n"/>
+      <c r="K6" s="789" t="n"/>
+      <c r="L6" s="789" t="n"/>
+      <c r="M6" s="789" t="n"/>
+      <c r="N6" s="789" t="n"/>
+      <c r="O6" s="789" t="n"/>
+      <c r="P6" s="789" t="n"/>
+      <c r="Q6" s="789" t="n"/>
+      <c r="R6" s="789" t="n"/>
+      <c r="S6" s="789" t="n"/>
+      <c r="T6" s="789" t="n"/>
+      <c r="U6" s="789" t="n"/>
+      <c r="V6" s="789" t="n"/>
+      <c r="W6" s="789" t="n"/>
+      <c r="X6" s="789" t="n"/>
+      <c r="Y6" s="789" t="n"/>
+      <c r="Z6" s="789" t="n"/>
+      <c r="AA6" s="789" t="n"/>
+      <c r="AB6" s="789" t="n"/>
+      <c r="AC6" s="789" t="n"/>
+      <c r="AD6" s="789" t="n"/>
+      <c r="AE6" s="789" t="n"/>
+      <c r="AF6" s="789" t="n"/>
+      <c r="AG6" s="789" t="n"/>
+      <c r="AH6" s="789" t="n"/>
+      <c r="AI6" s="789" t="n"/>
+      <c r="AJ6" s="789" t="n"/>
+      <c r="AK6" s="789" t="n"/>
+      <c r="AL6" s="789" t="n"/>
+      <c r="AM6" s="789" t="n"/>
+      <c r="AN6" s="789" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="402" t="n"/>
-      <c r="B7" s="402" t="n"/>
+      <c r="A7" s="402" t="inlineStr">
+        <is>
+          <t>VAL_RESULT_CORE</t>
+        </is>
+      </c>
+      <c r="B7" s="402" t="inlineStr">
+        <is>
+          <t>VAL_DECISION_GATE_CORE</t>
+        </is>
+      </c>
       <c r="C7" s="402" t="inlineStr">
         <is>
+          <t>VAL_STATUS_CORE</t>
+        </is>
+      </c>
+      <c r="D7" s="402" t="inlineStr">
+        <is>
+          <t>VAL_RISK_LEVEL_CORE</t>
+        </is>
+      </c>
+      <c r="E7" s="790" t="n"/>
+      <c r="F7" s="790" t="n"/>
+      <c r="G7" s="790" t="n"/>
+      <c r="H7" s="790" t="n"/>
+      <c r="I7" s="790" t="n"/>
+      <c r="J7" s="790" t="n"/>
+      <c r="K7" s="790" t="n"/>
+      <c r="L7" s="790" t="n"/>
+      <c r="M7" s="790" t="n"/>
+      <c r="N7" s="790" t="n"/>
+      <c r="O7" s="790" t="n"/>
+      <c r="P7" s="790" t="n"/>
+      <c r="Q7" s="790" t="n"/>
+      <c r="R7" s="790" t="n"/>
+      <c r="S7" s="790" t="n"/>
+      <c r="T7" s="790" t="n"/>
+      <c r="U7" s="790" t="n"/>
+      <c r="V7" s="790" t="n"/>
+      <c r="W7" s="790" t="n"/>
+      <c r="X7" s="790" t="n"/>
+      <c r="Y7" s="790" t="n"/>
+      <c r="Z7" s="790" t="n"/>
+      <c r="AA7" s="790" t="n"/>
+      <c r="AB7" s="790" t="n"/>
+      <c r="AC7" s="790" t="n"/>
+      <c r="AD7" s="790" t="n"/>
+      <c r="AE7" s="790" t="n"/>
+      <c r="AF7" s="790" t="n"/>
+      <c r="AG7" s="790" t="n"/>
+      <c r="AH7" s="790" t="n"/>
+      <c r="AI7" s="790" t="n"/>
+      <c r="AJ7" s="790" t="n"/>
+      <c r="AK7" s="790" t="n"/>
+      <c r="AL7" s="790" t="n"/>
+      <c r="AM7" s="790" t="n"/>
+      <c r="AN7" s="790" t="n"/>
+    </row>
+    <row r="8" hidden="1">
+      <c r="A8" s="402" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B8" s="402" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="C8" s="402" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D8" s="402" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="E8" s="790" t="n"/>
+      <c r="F8" s="790" t="n"/>
+      <c r="G8" s="790" t="n"/>
+      <c r="H8" s="790" t="n"/>
+      <c r="I8" s="790" t="n"/>
+      <c r="J8" s="790" t="n"/>
+      <c r="K8" s="790" t="n"/>
+      <c r="L8" s="790" t="n"/>
+      <c r="M8" s="790" t="n"/>
+      <c r="N8" s="790" t="n"/>
+      <c r="O8" s="790" t="n"/>
+      <c r="P8" s="790" t="n"/>
+      <c r="Q8" s="790" t="n"/>
+      <c r="R8" s="790" t="n"/>
+      <c r="S8" s="790" t="n"/>
+      <c r="T8" s="790" t="n"/>
+      <c r="U8" s="790" t="n"/>
+      <c r="V8" s="790" t="n"/>
+      <c r="W8" s="790" t="n"/>
+      <c r="X8" s="790" t="n"/>
+      <c r="Y8" s="790" t="n"/>
+      <c r="Z8" s="790" t="n"/>
+      <c r="AA8" s="790" t="n"/>
+      <c r="AB8" s="790" t="n"/>
+      <c r="AC8" s="790" t="n"/>
+      <c r="AD8" s="790" t="n"/>
+      <c r="AE8" s="790" t="n"/>
+      <c r="AF8" s="790" t="n"/>
+      <c r="AG8" s="790" t="n"/>
+      <c r="AH8" s="790" t="n"/>
+      <c r="AI8" s="790" t="n"/>
+      <c r="AJ8" s="790" t="n"/>
+      <c r="AK8" s="790" t="n"/>
+      <c r="AL8" s="790" t="n"/>
+      <c r="AM8" s="790" t="n"/>
+      <c r="AN8" s="790" t="n"/>
+    </row>
+    <row r="9" hidden="1">
+      <c r="A9" s="402" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="B9" s="402" t="inlineStr">
+        <is>
+          <t>CONDITIONAL</t>
+        </is>
+      </c>
+      <c r="C9" s="402" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="D9" s="402" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E9" s="790" t="n"/>
+      <c r="F9" s="790" t="n"/>
+      <c r="G9" s="790" t="n"/>
+      <c r="H9" s="790" t="n"/>
+      <c r="I9" s="790" t="n"/>
+      <c r="J9" s="790" t="n"/>
+      <c r="K9" s="790" t="n"/>
+      <c r="L9" s="790" t="n"/>
+      <c r="M9" s="790" t="n"/>
+      <c r="N9" s="790" t="n"/>
+      <c r="O9" s="790" t="n"/>
+      <c r="P9" s="790" t="n"/>
+      <c r="Q9" s="790" t="n"/>
+      <c r="R9" s="790" t="n"/>
+      <c r="S9" s="790" t="n"/>
+      <c r="T9" s="790" t="n"/>
+      <c r="U9" s="790" t="n"/>
+      <c r="V9" s="790" t="n"/>
+      <c r="W9" s="790" t="n"/>
+      <c r="X9" s="790" t="n"/>
+      <c r="Y9" s="790" t="n"/>
+      <c r="Z9" s="790" t="n"/>
+      <c r="AA9" s="790" t="n"/>
+      <c r="AB9" s="790" t="n"/>
+      <c r="AC9" s="790" t="n"/>
+      <c r="AD9" s="790" t="n"/>
+      <c r="AE9" s="790" t="n"/>
+      <c r="AF9" s="790" t="n"/>
+      <c r="AG9" s="790" t="n"/>
+      <c r="AH9" s="790" t="n"/>
+      <c r="AI9" s="790" t="n"/>
+      <c r="AJ9" s="790" t="n"/>
+      <c r="AK9" s="790" t="n"/>
+      <c r="AL9" s="790" t="n"/>
+      <c r="AM9" s="790" t="n"/>
+      <c r="AN9" s="790" t="n"/>
+    </row>
+    <row r="10" hidden="1">
+      <c r="A10" s="402" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="B10" s="402" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="C10" s="402" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D10" s="402" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E10" s="790" t="n"/>
+      <c r="F10" s="790" t="n"/>
+      <c r="G10" s="790" t="n"/>
+      <c r="H10" s="790" t="n"/>
+      <c r="I10" s="790" t="n"/>
+      <c r="J10" s="790" t="n"/>
+      <c r="K10" s="790" t="n"/>
+      <c r="L10" s="790" t="n"/>
+      <c r="M10" s="790" t="n"/>
+      <c r="N10" s="790" t="n"/>
+      <c r="O10" s="790" t="n"/>
+      <c r="P10" s="790" t="n"/>
+      <c r="Q10" s="790" t="n"/>
+      <c r="R10" s="790" t="n"/>
+      <c r="S10" s="790" t="n"/>
+      <c r="T10" s="790" t="n"/>
+      <c r="U10" s="790" t="n"/>
+      <c r="V10" s="790" t="n"/>
+      <c r="W10" s="790" t="n"/>
+      <c r="X10" s="790" t="n"/>
+      <c r="Y10" s="790" t="n"/>
+      <c r="Z10" s="790" t="n"/>
+      <c r="AA10" s="790" t="n"/>
+      <c r="AB10" s="790" t="n"/>
+      <c r="AC10" s="790" t="n"/>
+      <c r="AD10" s="790" t="n"/>
+      <c r="AE10" s="790" t="n"/>
+      <c r="AF10" s="790" t="n"/>
+      <c r="AG10" s="790" t="n"/>
+      <c r="AH10" s="790" t="n"/>
+      <c r="AI10" s="790" t="n"/>
+      <c r="AJ10" s="790" t="n"/>
+      <c r="AK10" s="790" t="n"/>
+      <c r="AL10" s="790" t="n"/>
+      <c r="AM10" s="790" t="n"/>
+      <c r="AN10" s="790" t="n"/>
+    </row>
+    <row r="11" hidden="1">
+      <c r="A11" s="402" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B11" s="402" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="C11" s="402" t="inlineStr">
+        <is>
+          <t>MONITORING</t>
+        </is>
+      </c>
+      <c r="D11" s="402" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="E11" s="790" t="n"/>
+      <c r="F11" s="790" t="n"/>
+      <c r="G11" s="790" t="n"/>
+      <c r="H11" s="790" t="n"/>
+      <c r="I11" s="790" t="n"/>
+      <c r="J11" s="790" t="n"/>
+      <c r="K11" s="790" t="n"/>
+      <c r="L11" s="790" t="n"/>
+      <c r="M11" s="790" t="n"/>
+      <c r="N11" s="790" t="n"/>
+      <c r="O11" s="790" t="n"/>
+      <c r="P11" s="790" t="n"/>
+      <c r="Q11" s="790" t="n"/>
+      <c r="R11" s="790" t="n"/>
+      <c r="S11" s="790" t="n"/>
+      <c r="T11" s="790" t="n"/>
+      <c r="U11" s="790" t="n"/>
+      <c r="V11" s="790" t="n"/>
+      <c r="W11" s="790" t="n"/>
+      <c r="X11" s="790" t="n"/>
+      <c r="Y11" s="790" t="n"/>
+      <c r="Z11" s="790" t="n"/>
+      <c r="AA11" s="790" t="n"/>
+      <c r="AB11" s="790" t="n"/>
+      <c r="AC11" s="790" t="n"/>
+      <c r="AD11" s="790" t="n"/>
+      <c r="AE11" s="790" t="n"/>
+      <c r="AF11" s="790" t="n"/>
+      <c r="AG11" s="790" t="n"/>
+      <c r="AH11" s="790" t="n"/>
+      <c r="AI11" s="790" t="n"/>
+      <c r="AJ11" s="790" t="n"/>
+      <c r="AK11" s="790" t="n"/>
+      <c r="AL11" s="790" t="n"/>
+      <c r="AM11" s="790" t="n"/>
+      <c r="AN11" s="790" t="n"/>
+    </row>
+    <row r="12" hidden="1">
+      <c r="A12" s="790" t="n"/>
+      <c r="B12" s="790" t="n"/>
+      <c r="C12" s="402" t="inlineStr">
+        <is>
+          <t>SUPERSEDED</t>
+        </is>
+      </c>
+      <c r="D12" s="790" t="n"/>
+      <c r="E12" s="790" t="n"/>
+      <c r="F12" s="790" t="n"/>
+      <c r="G12" s="790" t="n"/>
+      <c r="H12" s="790" t="n"/>
+      <c r="I12" s="790" t="n"/>
+      <c r="J12" s="790" t="n"/>
+      <c r="K12" s="790" t="n"/>
+      <c r="L12" s="790" t="n"/>
+      <c r="M12" s="790" t="n"/>
+      <c r="N12" s="790" t="n"/>
+      <c r="O12" s="790" t="n"/>
+      <c r="P12" s="790" t="n"/>
+      <c r="Q12" s="790" t="n"/>
+      <c r="R12" s="790" t="n"/>
+      <c r="S12" s="790" t="n"/>
+      <c r="T12" s="790" t="n"/>
+      <c r="U12" s="790" t="n"/>
+      <c r="V12" s="790" t="n"/>
+      <c r="W12" s="790" t="n"/>
+      <c r="X12" s="790" t="n"/>
+      <c r="Y12" s="790" t="n"/>
+      <c r="Z12" s="790" t="n"/>
+      <c r="AA12" s="790" t="n"/>
+      <c r="AB12" s="790" t="n"/>
+      <c r="AC12" s="790" t="n"/>
+      <c r="AD12" s="790" t="n"/>
+      <c r="AE12" s="790" t="n"/>
+      <c r="AF12" s="790" t="n"/>
+      <c r="AG12" s="790" t="n"/>
+      <c r="AH12" s="790" t="n"/>
+      <c r="AI12" s="790" t="n"/>
+      <c r="AJ12" s="790" t="n"/>
+      <c r="AK12" s="790" t="n"/>
+      <c r="AL12" s="790" t="n"/>
+      <c r="AM12" s="790" t="n"/>
+      <c r="AN12" s="790" t="n"/>
+    </row>
+    <row r="13" hidden="1">
+      <c r="A13" s="790" t="n"/>
+      <c r="B13" s="790" t="n"/>
+      <c r="C13" s="402" t="inlineStr">
+        <is>
           <t>VOID</t>
         </is>
       </c>
-      <c r="D7" s="402" t="n"/>
-      <c r="E7" s="402" t="n"/>
-      <c r="F7" s="402" t="n"/>
-      <c r="G7" s="402" t="n"/>
-      <c r="H7" s="402" t="n"/>
-      <c r="I7" s="402" t="n"/>
-      <c r="J7" s="402" t="n"/>
-      <c r="K7" s="402" t="n"/>
-      <c r="L7" s="402" t="n"/>
-      <c r="M7" s="402" t="n"/>
-      <c r="N7" s="402" t="n"/>
-      <c r="O7" s="402" t="n"/>
-      <c r="P7" s="402" t="n"/>
-      <c r="Q7" s="402" t="n"/>
-      <c r="R7" s="402" t="n"/>
-      <c r="S7" s="402" t="n"/>
-      <c r="T7" s="402" t="n"/>
-      <c r="U7" s="402" t="n"/>
-      <c r="V7" s="402" t="n"/>
-      <c r="W7" s="402" t="n"/>
-      <c r="X7" s="402" t="n"/>
-      <c r="Y7" s="402" t="n"/>
-      <c r="Z7" s="402" t="n"/>
-      <c r="AA7" s="402" t="n"/>
-      <c r="AB7" s="402" t="n"/>
-      <c r="AC7" s="402" t="n"/>
-      <c r="AD7" s="402" t="n"/>
-      <c r="AE7" s="402" t="n"/>
-      <c r="AF7" s="402" t="n"/>
-      <c r="AG7" s="402" t="n"/>
-      <c r="AH7" s="402" t="n"/>
-      <c r="AI7" s="402" t="n"/>
-      <c r="AJ7" s="402" t="n"/>
-      <c r="AK7" s="402" t="n"/>
-      <c r="AL7" s="402" t="n"/>
-      <c r="AM7" s="402" t="n"/>
-      <c r="AN7" s="402" t="n"/>
+      <c r="D13" s="790" t="n"/>
+      <c r="E13" s="790" t="n"/>
+      <c r="F13" s="790" t="n"/>
+      <c r="G13" s="790" t="n"/>
+      <c r="H13" s="790" t="n"/>
+      <c r="I13" s="790" t="n"/>
+      <c r="J13" s="790" t="n"/>
+      <c r="K13" s="790" t="n"/>
+      <c r="L13" s="790" t="n"/>
+      <c r="M13" s="790" t="n"/>
+      <c r="N13" s="790" t="n"/>
+      <c r="O13" s="790" t="n"/>
+      <c r="P13" s="790" t="n"/>
+      <c r="Q13" s="790" t="n"/>
+      <c r="R13" s="790" t="n"/>
+      <c r="S13" s="790" t="n"/>
+      <c r="T13" s="790" t="n"/>
+      <c r="U13" s="790" t="n"/>
+      <c r="V13" s="790" t="n"/>
+      <c r="W13" s="790" t="n"/>
+      <c r="X13" s="790" t="n"/>
+      <c r="Y13" s="790" t="n"/>
+      <c r="Z13" s="790" t="n"/>
+      <c r="AA13" s="790" t="n"/>
+      <c r="AB13" s="790" t="n"/>
+      <c r="AC13" s="790" t="n"/>
+      <c r="AD13" s="790" t="n"/>
+      <c r="AE13" s="790" t="n"/>
+      <c r="AF13" s="790" t="n"/>
+      <c r="AG13" s="790" t="n"/>
+      <c r="AH13" s="790" t="n"/>
+      <c r="AI13" s="790" t="n"/>
+      <c r="AJ13" s="790" t="n"/>
+      <c r="AK13" s="790" t="n"/>
+      <c r="AL13" s="790" t="n"/>
+      <c r="AM13" s="790" t="n"/>
+      <c r="AN13" s="790" t="n"/>
     </row>
-    <row r="8" hidden="1"/>
-    <row r="9" hidden="1"/>
-    <row r="10" hidden="1"/>
-    <row r="11" hidden="1"/>
-    <row r="12" hidden="1"/>
-    <row r="13" hidden="1"/>
-    <row r="14" hidden="1"/>
-    <row r="15" hidden="1"/>
-    <row r="16" hidden="1"/>
+    <row r="14" hidden="1">
+      <c r="A14" s="790" t="n"/>
+      <c r="B14" s="790" t="n"/>
+      <c r="C14" s="790" t="n"/>
+      <c r="D14" s="790" t="n"/>
+      <c r="E14" s="790" t="n"/>
+      <c r="F14" s="790" t="n"/>
+      <c r="G14" s="790" t="n"/>
+      <c r="H14" s="790" t="n"/>
+      <c r="I14" s="790" t="n"/>
+      <c r="J14" s="790" t="n"/>
+      <c r="K14" s="790" t="n"/>
+      <c r="L14" s="790" t="n"/>
+      <c r="M14" s="790" t="n"/>
+      <c r="N14" s="790" t="n"/>
+      <c r="O14" s="790" t="n"/>
+      <c r="P14" s="790" t="n"/>
+      <c r="Q14" s="790" t="n"/>
+      <c r="R14" s="790" t="n"/>
+      <c r="S14" s="790" t="n"/>
+      <c r="T14" s="790" t="n"/>
+      <c r="U14" s="790" t="n"/>
+      <c r="V14" s="790" t="n"/>
+      <c r="W14" s="790" t="n"/>
+      <c r="X14" s="790" t="n"/>
+      <c r="Y14" s="790" t="n"/>
+      <c r="Z14" s="790" t="n"/>
+      <c r="AA14" s="790" t="n"/>
+      <c r="AB14" s="790" t="n"/>
+      <c r="AC14" s="790" t="n"/>
+      <c r="AD14" s="790" t="n"/>
+      <c r="AE14" s="790" t="n"/>
+      <c r="AF14" s="790" t="n"/>
+      <c r="AG14" s="790" t="n"/>
+      <c r="AH14" s="790" t="n"/>
+      <c r="AI14" s="790" t="n"/>
+      <c r="AJ14" s="790" t="n"/>
+      <c r="AK14" s="790" t="n"/>
+      <c r="AL14" s="790" t="n"/>
+      <c r="AM14" s="790" t="n"/>
+      <c r="AN14" s="790" t="n"/>
+    </row>
+    <row r="15" hidden="1">
+      <c r="A15" s="790" t="n"/>
+      <c r="B15" s="790" t="n"/>
+      <c r="C15" s="790" t="n"/>
+      <c r="D15" s="790" t="n"/>
+      <c r="E15" s="790" t="n"/>
+      <c r="F15" s="790" t="n"/>
+      <c r="G15" s="790" t="n"/>
+      <c r="H15" s="790" t="n"/>
+      <c r="I15" s="790" t="n"/>
+      <c r="J15" s="790" t="n"/>
+      <c r="K15" s="790" t="n"/>
+      <c r="L15" s="790" t="n"/>
+      <c r="M15" s="790" t="n"/>
+      <c r="N15" s="790" t="n"/>
+      <c r="O15" s="790" t="n"/>
+      <c r="P15" s="790" t="n"/>
+      <c r="Q15" s="790" t="n"/>
+      <c r="R15" s="790" t="n"/>
+      <c r="S15" s="790" t="n"/>
+      <c r="T15" s="790" t="n"/>
+      <c r="U15" s="790" t="n"/>
+      <c r="V15" s="790" t="n"/>
+      <c r="W15" s="790" t="n"/>
+      <c r="X15" s="790" t="n"/>
+      <c r="Y15" s="790" t="n"/>
+      <c r="Z15" s="790" t="n"/>
+      <c r="AA15" s="790" t="n"/>
+      <c r="AB15" s="790" t="n"/>
+      <c r="AC15" s="790" t="n"/>
+      <c r="AD15" s="790" t="n"/>
+      <c r="AE15" s="790" t="n"/>
+      <c r="AF15" s="790" t="n"/>
+      <c r="AG15" s="790" t="n"/>
+      <c r="AH15" s="790" t="n"/>
+      <c r="AI15" s="790" t="n"/>
+      <c r="AJ15" s="790" t="n"/>
+      <c r="AK15" s="790" t="n"/>
+      <c r="AL15" s="790" t="n"/>
+      <c r="AM15" s="790" t="n"/>
+      <c r="AN15" s="790" t="n"/>
+    </row>
+    <row r="16" hidden="1">
+      <c r="A16" s="790" t="n"/>
+      <c r="B16" s="790" t="n"/>
+      <c r="C16" s="790" t="n"/>
+      <c r="D16" s="790" t="n"/>
+      <c r="E16" s="790" t="n"/>
+      <c r="F16" s="790" t="n"/>
+      <c r="G16" s="790" t="n"/>
+      <c r="H16" s="790" t="n"/>
+      <c r="I16" s="790" t="n"/>
+      <c r="J16" s="790" t="n"/>
+      <c r="K16" s="790" t="n"/>
+      <c r="L16" s="790" t="n"/>
+      <c r="M16" s="790" t="n"/>
+      <c r="N16" s="790" t="n"/>
+      <c r="O16" s="790" t="n"/>
+      <c r="P16" s="790" t="n"/>
+      <c r="Q16" s="790" t="n"/>
+      <c r="R16" s="790" t="n"/>
+      <c r="S16" s="790" t="n"/>
+      <c r="T16" s="790" t="n"/>
+      <c r="U16" s="790" t="n"/>
+      <c r="V16" s="790" t="n"/>
+      <c r="W16" s="790" t="n"/>
+      <c r="X16" s="790" t="n"/>
+      <c r="Y16" s="790" t="n"/>
+      <c r="Z16" s="790" t="n"/>
+      <c r="AA16" s="790" t="n"/>
+      <c r="AB16" s="790" t="n"/>
+      <c r="AC16" s="790" t="n"/>
+      <c r="AD16" s="790" t="n"/>
+      <c r="AE16" s="790" t="n"/>
+      <c r="AF16" s="790" t="n"/>
+      <c r="AG16" s="790" t="n"/>
+      <c r="AH16" s="790" t="n"/>
+      <c r="AI16" s="790" t="n"/>
+      <c r="AJ16" s="790" t="n"/>
+      <c r="AK16" s="790" t="n"/>
+      <c r="AL16" s="790" t="n"/>
+      <c r="AM16" s="790" t="n"/>
+      <c r="AN16" s="790" t="n"/>
+    </row>
     <row r="17" hidden="1"/>
     <row r="18" hidden="1"/>
     <row r="19" hidden="1"/>
@@ -11100,6 +11194,22 @@
     <row r="199" hidden="1"/>
     <row r="200" hidden="1"/>
   </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
+  </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
@@ -836,7 +836,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="395">
+  <borders count="397">
     <border>
       <left/>
       <right/>
@@ -5119,11 +5119,34 @@
         <color rgb="002C9CD7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="791">
+  <cellXfs count="846">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -7063,6 +7086,139 @@
     </xf>
     <xf numFmtId="0" fontId="91" fillId="52" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="91" fillId="4" borderId="347" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="348" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="368" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="91" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="91" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="91" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="91" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="91" fillId="4" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="396" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -7163,11 +7319,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>253512</colOff>
-      <row>0</row>
-      <rowOff>340740</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="941616" cy="271620"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7181,9 +7337,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7196,11 +7349,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>63378</colOff>
-      <row>0</row>
-      <rowOff>442597</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="235404" cy="67905"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7214,9 +7367,36 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1123950" cy="323850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -7423,50 +7603,50 @@
   <dimension ref="A1:AN47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2.329999923706055" customWidth="1" min="1" max="1"/>
-    <col width="2.329999923706055" customWidth="1" min="2" max="2"/>
-    <col width="2.329999923706055" customWidth="1" min="3" max="3"/>
-    <col width="2.329999923706055" customWidth="1" min="4" max="4"/>
-    <col width="2.329999923706055" customWidth="1" min="5" max="5"/>
-    <col width="2.329999923706055" customWidth="1" min="6" max="6"/>
-    <col width="2.329999923706055" customWidth="1" min="7" max="7"/>
-    <col width="2.329999923706055" customWidth="1" min="8" max="8"/>
-    <col width="2.329999923706055" customWidth="1" min="9" max="9"/>
-    <col width="2.329999923706055" customWidth="1" min="10" max="10"/>
-    <col width="2.329999923706055" customWidth="1" min="11" max="11"/>
-    <col width="2.329999923706055" customWidth="1" min="12" max="12"/>
-    <col width="2.329999923706055" customWidth="1" min="13" max="13"/>
-    <col width="2.329999923706055" customWidth="1" min="14" max="14"/>
-    <col width="2.329999923706055" customWidth="1" min="15" max="15"/>
-    <col width="2.329999923706055" customWidth="1" min="16" max="16"/>
-    <col width="2.329999923706055" customWidth="1" min="17" max="17"/>
-    <col width="2.329999923706055" customWidth="1" min="18" max="18"/>
-    <col width="2.329999923706055" customWidth="1" min="19" max="19"/>
-    <col width="2.329999923706055" customWidth="1" min="20" max="20"/>
-    <col width="2.329999923706055" customWidth="1" min="21" max="21"/>
-    <col width="2.329999923706055" customWidth="1" min="22" max="22"/>
-    <col width="2.329999923706055" customWidth="1" min="23" max="23"/>
-    <col width="2.329999923706055" customWidth="1" min="24" max="24"/>
-    <col width="2.329999923706055" customWidth="1" min="25" max="25"/>
-    <col width="2.329999923706055" customWidth="1" min="26" max="26"/>
-    <col width="2.329999923706055" customWidth="1" min="27" max="27"/>
-    <col width="2.329999923706055" customWidth="1" min="28" max="28"/>
-    <col width="2.329999923706055" customWidth="1" min="29" max="29"/>
-    <col width="2.329999923706055" customWidth="1" min="30" max="30"/>
-    <col width="2.329999923706055" customWidth="1" min="31" max="31"/>
-    <col width="2.329999923706055" customWidth="1" min="32" max="32"/>
-    <col width="2.329999923706055" customWidth="1" min="33" max="33"/>
-    <col width="2.329999923706055" customWidth="1" min="34" max="34"/>
-    <col width="2.329999923706055" customWidth="1" min="35" max="35"/>
-    <col width="2.329999923706055" customWidth="1" min="36" max="36"/>
-    <col width="2.329999923706055" customWidth="1" min="37" max="37"/>
-    <col width="2.329999923706055" customWidth="1" min="38" max="38"/>
-    <col width="2.329999923706055" customWidth="1" min="39" max="39"/>
-    <col width="2.329999923706055" customWidth="1" min="40" max="40"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
     <col hidden="1" outlineLevel="1" width="13" customWidth="1" min="41" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="719" t="inlineStr"/>
       <c r="B1" s="268" t="n"/>
       <c r="C1" s="268" t="n"/>
@@ -7475,7 +7655,7 @@
       <c r="F1" s="268" t="n"/>
       <c r="G1" s="268" t="n"/>
       <c r="H1" s="319" t="n"/>
-      <c r="I1" s="631" t="inlineStr">
+      <c r="I1" s="845" t="inlineStr">
         <is>
           <t>HIGH-RISK JOB READINESS REVIEW</t>
         </is>
@@ -7500,7 +7680,7 @@
       <c r="AA1" s="268" t="n"/>
       <c r="AB1" s="268" t="n"/>
       <c r="AC1" s="268" t="n"/>
-      <c r="AD1" s="268" t="n"/>
+      <c r="AD1" s="319" t="n"/>
       <c r="AE1" s="720" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -7521,219 +7701,296 @@
       <c r="AN1" s="319" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="H2" s="320" t="n"/>
-      <c r="I2" s="275" t="n"/>
-      <c r="AE2" s="722" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="791" t="n"/>
+      <c r="C2" s="791" t="n"/>
+      <c r="D2" s="791" t="n"/>
+      <c r="E2" s="791" t="n"/>
+      <c r="F2" s="791" t="n"/>
+      <c r="G2" s="791" t="n"/>
+      <c r="H2" s="792" t="n"/>
+      <c r="I2" s="791" t="n"/>
+      <c r="J2" s="791" t="n"/>
+      <c r="K2" s="791" t="n"/>
+      <c r="L2" s="791" t="n"/>
+      <c r="M2" s="791" t="n"/>
+      <c r="N2" s="791" t="n"/>
+      <c r="O2" s="791" t="n"/>
+      <c r="P2" s="791" t="n"/>
+      <c r="Q2" s="791" t="n"/>
+      <c r="R2" s="791" t="n"/>
+      <c r="S2" s="791" t="n"/>
+      <c r="T2" s="791" t="n"/>
+      <c r="U2" s="791" t="n"/>
+      <c r="V2" s="791" t="n"/>
+      <c r="W2" s="791" t="n"/>
+      <c r="X2" s="791" t="n"/>
+      <c r="Y2" s="791" t="n"/>
+      <c r="Z2" s="791" t="n"/>
+      <c r="AA2" s="791" t="n"/>
+      <c r="AB2" s="791" t="n"/>
+      <c r="AC2" s="791" t="n"/>
+      <c r="AD2" s="792" t="n"/>
+      <c r="AE2" s="793" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="723" t="n"/>
-      <c r="AG2" s="723" t="n"/>
-      <c r="AH2" s="724" t="n"/>
-      <c r="AI2" s="682" t="inlineStr">
+      <c r="AF2" s="794" t="n"/>
+      <c r="AG2" s="794" t="n"/>
+      <c r="AH2" s="795" t="n"/>
+      <c r="AI2" s="796" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="723" t="n"/>
-      <c r="AK2" s="723" t="n"/>
-      <c r="AL2" s="723" t="n"/>
-      <c r="AM2" s="723" t="n"/>
-      <c r="AN2" s="725" t="n"/>
+      <c r="AJ2" s="797" t="n"/>
+      <c r="AK2" s="797" t="n"/>
+      <c r="AL2" s="797" t="n"/>
+      <c r="AM2" s="797" t="n"/>
+      <c r="AN2" s="798" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="H3" s="320" t="n"/>
-      <c r="I3" s="275" t="n"/>
-      <c r="AE3" s="722" t="inlineStr">
+      <c r="A3" s="799" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="800" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="800" t="n"/>
+      <c r="AE3" s="801" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="723" t="n"/>
-      <c r="AG3" s="723" t="n"/>
-      <c r="AH3" s="724" t="n"/>
-      <c r="AI3" s="682" t="inlineStr">
+      <c r="AF3" s="802" t="n"/>
+      <c r="AG3" s="802" t="n"/>
+      <c r="AH3" s="803" t="n"/>
+      <c r="AI3" s="699" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="723" t="n"/>
-      <c r="AK3" s="723" t="n"/>
-      <c r="AL3" s="723" t="n"/>
-      <c r="AM3" s="723" t="n"/>
-      <c r="AN3" s="725" t="n"/>
+      <c r="AJ3" s="804" t="n"/>
+      <c r="AK3" s="804" t="n"/>
+      <c r="AL3" s="804" t="n"/>
+      <c r="AM3" s="804" t="n"/>
+      <c r="AN3" s="805" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="H4" s="320" t="n"/>
-      <c r="I4" s="640" t="inlineStr">
+      <c r="A4" s="799" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="800" t="n"/>
+      <c r="I4" s="342" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="AE4" s="722" t="inlineStr">
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="800" t="n"/>
+      <c r="AE4" s="801" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="723" t="n"/>
-      <c r="AG4" s="723" t="n"/>
-      <c r="AH4" s="724" t="n"/>
-      <c r="AI4" s="682" t="inlineStr">
+      <c r="AF4" s="802" t="n"/>
+      <c r="AG4" s="802" t="n"/>
+      <c r="AH4" s="803" t="n"/>
+      <c r="AI4" s="699" t="inlineStr">
         <is>
           <t>Planning / QA / Engineering</t>
         </is>
       </c>
-      <c r="AJ4" s="723" t="n"/>
-      <c r="AK4" s="723" t="n"/>
-      <c r="AL4" s="723" t="n"/>
-      <c r="AM4" s="723" t="n"/>
-      <c r="AN4" s="725" t="n"/>
+      <c r="AJ4" s="804" t="n"/>
+      <c r="AK4" s="804" t="n"/>
+      <c r="AL4" s="804" t="n"/>
+      <c r="AM4" s="804" t="n"/>
+      <c r="AN4" s="805" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="282" t="n"/>
-      <c r="B5" s="283" t="n"/>
-      <c r="C5" s="283" t="n"/>
-      <c r="D5" s="283" t="n"/>
-      <c r="E5" s="283" t="n"/>
-      <c r="F5" s="283" t="n"/>
-      <c r="G5" s="283" t="n"/>
-      <c r="H5" s="287" t="n"/>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="A5" s="799" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="800" t="n"/>
+      <c r="I5" s="581" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="283" t="n"/>
-      <c r="K5" s="283" t="n"/>
-      <c r="L5" s="283" t="n"/>
-      <c r="M5" s="283" t="n"/>
-      <c r="N5" s="283" t="n"/>
-      <c r="O5" s="283" t="n"/>
-      <c r="P5" s="283" t="n"/>
-      <c r="Q5" s="283" t="n"/>
-      <c r="R5" s="283" t="n"/>
-      <c r="S5" s="283" t="n"/>
-      <c r="T5" s="283" t="n"/>
-      <c r="U5" s="283" t="n"/>
-      <c r="V5" s="283" t="n"/>
-      <c r="W5" s="283" t="n"/>
-      <c r="X5" s="283" t="n"/>
-      <c r="Y5" s="283" t="n"/>
-      <c r="Z5" s="283" t="n"/>
-      <c r="AA5" s="283" t="n"/>
-      <c r="AB5" s="283" t="n"/>
-      <c r="AC5" s="283" t="n"/>
-      <c r="AD5" s="283" t="n"/>
-      <c r="AE5" s="726" t="inlineStr">
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="800" t="n"/>
+      <c r="AE5" s="801" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="727" t="n"/>
-      <c r="AG5" s="727" t="n"/>
-      <c r="AH5" s="728" t="n"/>
-      <c r="AI5" s="689" t="inlineStr">
+      <c r="AF5" s="802" t="n"/>
+      <c r="AG5" s="802" t="n"/>
+      <c r="AH5" s="803" t="n"/>
+      <c r="AI5" s="699" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="727" t="n"/>
-      <c r="AK5" s="727" t="n"/>
-      <c r="AL5" s="727" t="n"/>
-      <c r="AM5" s="727" t="n"/>
-      <c r="AN5" s="729" t="n"/>
+      <c r="AJ5" s="804" t="n"/>
+      <c r="AK5" s="804" t="n"/>
+      <c r="AL5" s="804" t="n"/>
+      <c r="AM5" s="804" t="n"/>
+      <c r="AN5" s="805" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="646" t="n"/>
-      <c r="B6" s="646" t="n"/>
-      <c r="C6" s="646" t="n"/>
-      <c r="D6" s="646" t="n"/>
-      <c r="E6" s="646" t="n"/>
-      <c r="F6" s="646" t="n"/>
-      <c r="G6" s="646" t="n"/>
-      <c r="H6" s="646" t="n"/>
-      <c r="I6" s="646" t="n"/>
-      <c r="J6" s="646" t="n"/>
-      <c r="K6" s="646" t="n"/>
-      <c r="L6" s="646" t="n"/>
-      <c r="M6" s="646" t="n"/>
-      <c r="N6" s="646" t="n"/>
-      <c r="O6" s="646" t="n"/>
-      <c r="P6" s="646" t="n"/>
-      <c r="Q6" s="646" t="n"/>
-      <c r="R6" s="646" t="n"/>
-      <c r="S6" s="646" t="n"/>
-      <c r="T6" s="646" t="n"/>
-      <c r="U6" s="646" t="n"/>
-      <c r="V6" s="646" t="n"/>
-      <c r="W6" s="646" t="n"/>
-      <c r="X6" s="646" t="n"/>
-      <c r="Y6" s="646" t="n"/>
-      <c r="Z6" s="646" t="n"/>
-      <c r="AA6" s="646" t="n"/>
-      <c r="AB6" s="646" t="n"/>
-      <c r="AC6" s="646" t="n"/>
-      <c r="AD6" s="646" t="n"/>
-      <c r="AE6" s="646" t="n"/>
-      <c r="AF6" s="646" t="n"/>
-      <c r="AG6" s="646" t="n"/>
-      <c r="AH6" s="646" t="n"/>
-      <c r="AI6" s="646" t="n"/>
-      <c r="AJ6" s="646" t="n"/>
-      <c r="AK6" s="646" t="n"/>
-      <c r="AL6" s="646" t="n"/>
-      <c r="AM6" s="646" t="n"/>
-      <c r="AN6" s="646" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="806" t="n"/>
+      <c r="B6" s="807" t="n"/>
+      <c r="C6" s="807" t="n"/>
+      <c r="D6" s="807" t="n"/>
+      <c r="E6" s="807" t="n"/>
+      <c r="F6" s="807" t="n"/>
+      <c r="G6" s="807" t="n"/>
+      <c r="H6" s="808" t="n"/>
+      <c r="I6" s="807" t="n"/>
+      <c r="J6" s="807" t="n"/>
+      <c r="K6" s="807" t="n"/>
+      <c r="L6" s="807" t="n"/>
+      <c r="M6" s="807" t="n"/>
+      <c r="N6" s="807" t="n"/>
+      <c r="O6" s="807" t="n"/>
+      <c r="P6" s="807" t="n"/>
+      <c r="Q6" s="807" t="n"/>
+      <c r="R6" s="807" t="n"/>
+      <c r="S6" s="807" t="n"/>
+      <c r="T6" s="807" t="n"/>
+      <c r="U6" s="807" t="n"/>
+      <c r="V6" s="807" t="n"/>
+      <c r="W6" s="807" t="n"/>
+      <c r="X6" s="807" t="n"/>
+      <c r="Y6" s="807" t="n"/>
+      <c r="Z6" s="807" t="n"/>
+      <c r="AA6" s="807" t="n"/>
+      <c r="AB6" s="807" t="n"/>
+      <c r="AC6" s="807" t="n"/>
+      <c r="AD6" s="808" t="n"/>
+      <c r="AE6" s="809" t="n"/>
+      <c r="AF6" s="809" t="n"/>
+      <c r="AG6" s="809" t="n"/>
+      <c r="AH6" s="810" t="n"/>
+      <c r="AI6" s="811" t="n"/>
+      <c r="AJ6" s="811" t="n"/>
+      <c r="AK6" s="811" t="n"/>
+      <c r="AL6" s="811" t="n"/>
+      <c r="AM6" s="811" t="n"/>
+      <c r="AN6" s="812" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="730" t="inlineStr">
-        <is>
-          <t>1.  HIGH-RISK JOB HEADER / REFERENCE INFORMATION</t>
-        </is>
-      </c>
-      <c r="B7" s="289" t="n"/>
-      <c r="C7" s="289" t="n"/>
-      <c r="D7" s="289" t="n"/>
-      <c r="E7" s="289" t="n"/>
-      <c r="F7" s="289" t="n"/>
-      <c r="G7" s="289" t="n"/>
-      <c r="H7" s="289" t="n"/>
-      <c r="I7" s="289" t="n"/>
-      <c r="J7" s="289" t="n"/>
-      <c r="K7" s="289" t="n"/>
-      <c r="L7" s="289" t="n"/>
-      <c r="M7" s="289" t="n"/>
-      <c r="N7" s="289" t="n"/>
-      <c r="O7" s="289" t="n"/>
-      <c r="P7" s="289" t="n"/>
-      <c r="Q7" s="289" t="n"/>
-      <c r="R7" s="289" t="n"/>
-      <c r="S7" s="289" t="n"/>
-      <c r="T7" s="289" t="n"/>
-      <c r="U7" s="289" t="n"/>
-      <c r="V7" s="289" t="n"/>
-      <c r="W7" s="289" t="n"/>
-      <c r="X7" s="289" t="n"/>
-      <c r="Y7" s="289" t="n"/>
-      <c r="Z7" s="289" t="n"/>
-      <c r="AA7" s="289" t="n"/>
-      <c r="AB7" s="289" t="n"/>
-      <c r="AC7" s="289" t="n"/>
-      <c r="AD7" s="289" t="n"/>
-      <c r="AE7" s="289" t="n"/>
-      <c r="AF7" s="289" t="n"/>
-      <c r="AG7" s="289" t="n"/>
-      <c r="AH7" s="289" t="n"/>
-      <c r="AI7" s="289" t="n"/>
-      <c r="AJ7" s="289" t="n"/>
-      <c r="AK7" s="289" t="n"/>
-      <c r="AL7" s="289" t="n"/>
-      <c r="AM7" s="289" t="n"/>
-      <c r="AN7" s="290" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="813" t="n"/>
+      <c r="B7" s="814" t="n"/>
+      <c r="C7" s="814" t="n"/>
+      <c r="D7" s="814" t="n"/>
+      <c r="E7" s="814" t="n"/>
+      <c r="F7" s="814" t="n"/>
+      <c r="G7" s="814" t="n"/>
+      <c r="H7" s="814" t="n"/>
+      <c r="I7" s="814" t="n"/>
+      <c r="J7" s="814" t="n"/>
+      <c r="K7" s="814" t="n"/>
+      <c r="L7" s="814" t="n"/>
+      <c r="M7" s="814" t="n"/>
+      <c r="N7" s="814" t="n"/>
+      <c r="O7" s="814" t="n"/>
+      <c r="P7" s="814" t="n"/>
+      <c r="Q7" s="814" t="n"/>
+      <c r="R7" s="814" t="n"/>
+      <c r="S7" s="814" t="n"/>
+      <c r="T7" s="814" t="n"/>
+      <c r="U7" s="814" t="n"/>
+      <c r="V7" s="814" t="n"/>
+      <c r="W7" s="814" t="n"/>
+      <c r="X7" s="814" t="n"/>
+      <c r="Y7" s="814" t="n"/>
+      <c r="Z7" s="814" t="n"/>
+      <c r="AA7" s="814" t="n"/>
+      <c r="AB7" s="814" t="n"/>
+      <c r="AC7" s="814" t="n"/>
+      <c r="AD7" s="814" t="n"/>
+      <c r="AE7" s="814" t="n"/>
+      <c r="AF7" s="814" t="n"/>
+      <c r="AG7" s="814" t="n"/>
+      <c r="AH7" s="814" t="n"/>
+      <c r="AI7" s="814" t="n"/>
+      <c r="AJ7" s="814" t="n"/>
+      <c r="AK7" s="814" t="n"/>
+      <c r="AL7" s="814" t="n"/>
+      <c r="AM7" s="814" t="n"/>
+      <c r="AN7" s="814" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="731" t="inlineStr">
@@ -7987,45 +8244,45 @@
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="654" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
-      <c r="I13" s="10" t="n"/>
-      <c r="J13" s="10" t="n"/>
-      <c r="K13" s="10" t="n"/>
-      <c r="L13" s="10" t="n"/>
-      <c r="M13" s="10" t="n"/>
-      <c r="N13" s="10" t="n"/>
-      <c r="O13" s="10" t="n"/>
-      <c r="P13" s="10" t="n"/>
-      <c r="Q13" s="10" t="n"/>
-      <c r="R13" s="10" t="n"/>
-      <c r="S13" s="10" t="n"/>
-      <c r="T13" s="10" t="n"/>
-      <c r="U13" s="10" t="n"/>
-      <c r="V13" s="10" t="n"/>
-      <c r="W13" s="10" t="n"/>
-      <c r="X13" s="10" t="n"/>
-      <c r="Y13" s="10" t="n"/>
-      <c r="Z13" s="10" t="n"/>
-      <c r="AA13" s="10" t="n"/>
-      <c r="AB13" s="10" t="n"/>
-      <c r="AC13" s="10" t="n"/>
-      <c r="AD13" s="10" t="n"/>
-      <c r="AE13" s="10" t="n"/>
-      <c r="AF13" s="10" t="n"/>
-      <c r="AG13" s="10" t="n"/>
-      <c r="AH13" s="10" t="n"/>
-      <c r="AI13" s="10" t="n"/>
-      <c r="AJ13" s="10" t="n"/>
-      <c r="AK13" s="10" t="n"/>
-      <c r="AL13" s="10" t="n"/>
-      <c r="AM13" s="10" t="n"/>
-      <c r="AN13" s="10" t="n"/>
+      <c r="B13" s="654" t="n"/>
+      <c r="C13" s="654" t="n"/>
+      <c r="D13" s="654" t="n"/>
+      <c r="E13" s="654" t="n"/>
+      <c r="F13" s="654" t="n"/>
+      <c r="G13" s="654" t="n"/>
+      <c r="H13" s="654" t="n"/>
+      <c r="I13" s="654" t="n"/>
+      <c r="J13" s="654" t="n"/>
+      <c r="K13" s="654" t="n"/>
+      <c r="L13" s="654" t="n"/>
+      <c r="M13" s="654" t="n"/>
+      <c r="N13" s="654" t="n"/>
+      <c r="O13" s="654" t="n"/>
+      <c r="P13" s="654" t="n"/>
+      <c r="Q13" s="654" t="n"/>
+      <c r="R13" s="654" t="n"/>
+      <c r="S13" s="654" t="n"/>
+      <c r="T13" s="654" t="n"/>
+      <c r="U13" s="654" t="n"/>
+      <c r="V13" s="654" t="n"/>
+      <c r="W13" s="654" t="n"/>
+      <c r="X13" s="654" t="n"/>
+      <c r="Y13" s="654" t="n"/>
+      <c r="Z13" s="654" t="n"/>
+      <c r="AA13" s="654" t="n"/>
+      <c r="AB13" s="654" t="n"/>
+      <c r="AC13" s="654" t="n"/>
+      <c r="AD13" s="654" t="n"/>
+      <c r="AE13" s="654" t="n"/>
+      <c r="AF13" s="654" t="n"/>
+      <c r="AG13" s="654" t="n"/>
+      <c r="AH13" s="654" t="n"/>
+      <c r="AI13" s="654" t="n"/>
+      <c r="AJ13" s="654" t="n"/>
+      <c r="AK13" s="654" t="n"/>
+      <c r="AL13" s="654" t="n"/>
+      <c r="AM13" s="654" t="n"/>
+      <c r="AN13" s="654" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="730" t="inlineStr">
@@ -8285,45 +8542,45 @@
     </row>
     <row r="19" ht="3" customHeight="1">
       <c r="A19" s="654" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="10" t="n"/>
-      <c r="J19" s="10" t="n"/>
-      <c r="K19" s="10" t="n"/>
-      <c r="L19" s="10" t="n"/>
-      <c r="M19" s="10" t="n"/>
-      <c r="N19" s="10" t="n"/>
-      <c r="O19" s="10" t="n"/>
-      <c r="P19" s="10" t="n"/>
-      <c r="Q19" s="10" t="n"/>
-      <c r="R19" s="10" t="n"/>
-      <c r="S19" s="10" t="n"/>
-      <c r="T19" s="10" t="n"/>
-      <c r="U19" s="10" t="n"/>
-      <c r="V19" s="10" t="n"/>
-      <c r="W19" s="10" t="n"/>
-      <c r="X19" s="10" t="n"/>
-      <c r="Y19" s="10" t="n"/>
-      <c r="Z19" s="10" t="n"/>
-      <c r="AA19" s="10" t="n"/>
-      <c r="AB19" s="10" t="n"/>
-      <c r="AC19" s="10" t="n"/>
-      <c r="AD19" s="10" t="n"/>
-      <c r="AE19" s="10" t="n"/>
-      <c r="AF19" s="10" t="n"/>
-      <c r="AG19" s="10" t="n"/>
-      <c r="AH19" s="10" t="n"/>
-      <c r="AI19" s="10" t="n"/>
-      <c r="AJ19" s="10" t="n"/>
-      <c r="AK19" s="10" t="n"/>
-      <c r="AL19" s="10" t="n"/>
-      <c r="AM19" s="10" t="n"/>
-      <c r="AN19" s="10" t="n"/>
+      <c r="B19" s="654" t="n"/>
+      <c r="C19" s="654" t="n"/>
+      <c r="D19" s="654" t="n"/>
+      <c r="E19" s="654" t="n"/>
+      <c r="F19" s="654" t="n"/>
+      <c r="G19" s="654" t="n"/>
+      <c r="H19" s="654" t="n"/>
+      <c r="I19" s="654" t="n"/>
+      <c r="J19" s="654" t="n"/>
+      <c r="K19" s="654" t="n"/>
+      <c r="L19" s="654" t="n"/>
+      <c r="M19" s="654" t="n"/>
+      <c r="N19" s="654" t="n"/>
+      <c r="O19" s="654" t="n"/>
+      <c r="P19" s="654" t="n"/>
+      <c r="Q19" s="654" t="n"/>
+      <c r="R19" s="654" t="n"/>
+      <c r="S19" s="654" t="n"/>
+      <c r="T19" s="654" t="n"/>
+      <c r="U19" s="654" t="n"/>
+      <c r="V19" s="654" t="n"/>
+      <c r="W19" s="654" t="n"/>
+      <c r="X19" s="654" t="n"/>
+      <c r="Y19" s="654" t="n"/>
+      <c r="Z19" s="654" t="n"/>
+      <c r="AA19" s="654" t="n"/>
+      <c r="AB19" s="654" t="n"/>
+      <c r="AC19" s="654" t="n"/>
+      <c r="AD19" s="654" t="n"/>
+      <c r="AE19" s="654" t="n"/>
+      <c r="AF19" s="654" t="n"/>
+      <c r="AG19" s="654" t="n"/>
+      <c r="AH19" s="654" t="n"/>
+      <c r="AI19" s="654" t="n"/>
+      <c r="AJ19" s="654" t="n"/>
+      <c r="AK19" s="654" t="n"/>
+      <c r="AL19" s="654" t="n"/>
+      <c r="AM19" s="654" t="n"/>
+      <c r="AN19" s="654" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="730" t="inlineStr">
@@ -9003,45 +9260,45 @@
     </row>
     <row r="32" ht="3" customHeight="1">
       <c r="A32" s="654" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
-      <c r="H32" s="10" t="n"/>
-      <c r="I32" s="10" t="n"/>
-      <c r="J32" s="10" t="n"/>
-      <c r="K32" s="10" t="n"/>
-      <c r="L32" s="10" t="n"/>
-      <c r="M32" s="10" t="n"/>
-      <c r="N32" s="10" t="n"/>
-      <c r="O32" s="10" t="n"/>
-      <c r="P32" s="10" t="n"/>
-      <c r="Q32" s="10" t="n"/>
-      <c r="R32" s="10" t="n"/>
-      <c r="S32" s="10" t="n"/>
-      <c r="T32" s="10" t="n"/>
-      <c r="U32" s="10" t="n"/>
-      <c r="V32" s="10" t="n"/>
-      <c r="W32" s="10" t="n"/>
-      <c r="X32" s="10" t="n"/>
-      <c r="Y32" s="10" t="n"/>
-      <c r="Z32" s="10" t="n"/>
-      <c r="AA32" s="10" t="n"/>
-      <c r="AB32" s="10" t="n"/>
-      <c r="AC32" s="10" t="n"/>
-      <c r="AD32" s="10" t="n"/>
-      <c r="AE32" s="10" t="n"/>
-      <c r="AF32" s="10" t="n"/>
-      <c r="AG32" s="10" t="n"/>
-      <c r="AH32" s="10" t="n"/>
-      <c r="AI32" s="10" t="n"/>
-      <c r="AJ32" s="10" t="n"/>
-      <c r="AK32" s="10" t="n"/>
-      <c r="AL32" s="10" t="n"/>
-      <c r="AM32" s="10" t="n"/>
-      <c r="AN32" s="10" t="n"/>
+      <c r="B32" s="654" t="n"/>
+      <c r="C32" s="654" t="n"/>
+      <c r="D32" s="654" t="n"/>
+      <c r="E32" s="654" t="n"/>
+      <c r="F32" s="654" t="n"/>
+      <c r="G32" s="654" t="n"/>
+      <c r="H32" s="654" t="n"/>
+      <c r="I32" s="654" t="n"/>
+      <c r="J32" s="654" t="n"/>
+      <c r="K32" s="654" t="n"/>
+      <c r="L32" s="654" t="n"/>
+      <c r="M32" s="654" t="n"/>
+      <c r="N32" s="654" t="n"/>
+      <c r="O32" s="654" t="n"/>
+      <c r="P32" s="654" t="n"/>
+      <c r="Q32" s="654" t="n"/>
+      <c r="R32" s="654" t="n"/>
+      <c r="S32" s="654" t="n"/>
+      <c r="T32" s="654" t="n"/>
+      <c r="U32" s="654" t="n"/>
+      <c r="V32" s="654" t="n"/>
+      <c r="W32" s="654" t="n"/>
+      <c r="X32" s="654" t="n"/>
+      <c r="Y32" s="654" t="n"/>
+      <c r="Z32" s="654" t="n"/>
+      <c r="AA32" s="654" t="n"/>
+      <c r="AB32" s="654" t="n"/>
+      <c r="AC32" s="654" t="n"/>
+      <c r="AD32" s="654" t="n"/>
+      <c r="AE32" s="654" t="n"/>
+      <c r="AF32" s="654" t="n"/>
+      <c r="AG32" s="654" t="n"/>
+      <c r="AH32" s="654" t="n"/>
+      <c r="AI32" s="654" t="n"/>
+      <c r="AJ32" s="654" t="n"/>
+      <c r="AK32" s="654" t="n"/>
+      <c r="AL32" s="654" t="n"/>
+      <c r="AM32" s="654" t="n"/>
+      <c r="AN32" s="654" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="730" t="inlineStr">
@@ -9381,45 +9638,45 @@
     </row>
     <row r="40" ht="3" customHeight="1">
       <c r="A40" s="654" t="n"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="10" t="n"/>
-      <c r="H40" s="10" t="n"/>
-      <c r="I40" s="10" t="n"/>
-      <c r="J40" s="10" t="n"/>
-      <c r="K40" s="10" t="n"/>
-      <c r="L40" s="10" t="n"/>
-      <c r="M40" s="10" t="n"/>
-      <c r="N40" s="10" t="n"/>
-      <c r="O40" s="10" t="n"/>
-      <c r="P40" s="10" t="n"/>
-      <c r="Q40" s="10" t="n"/>
-      <c r="R40" s="10" t="n"/>
-      <c r="S40" s="10" t="n"/>
-      <c r="T40" s="10" t="n"/>
-      <c r="U40" s="10" t="n"/>
-      <c r="V40" s="10" t="n"/>
-      <c r="W40" s="10" t="n"/>
-      <c r="X40" s="10" t="n"/>
-      <c r="Y40" s="10" t="n"/>
-      <c r="Z40" s="10" t="n"/>
-      <c r="AA40" s="10" t="n"/>
-      <c r="AB40" s="10" t="n"/>
-      <c r="AC40" s="10" t="n"/>
-      <c r="AD40" s="10" t="n"/>
-      <c r="AE40" s="10" t="n"/>
-      <c r="AF40" s="10" t="n"/>
-      <c r="AG40" s="10" t="n"/>
-      <c r="AH40" s="10" t="n"/>
-      <c r="AI40" s="10" t="n"/>
-      <c r="AJ40" s="10" t="n"/>
-      <c r="AK40" s="10" t="n"/>
-      <c r="AL40" s="10" t="n"/>
-      <c r="AM40" s="10" t="n"/>
-      <c r="AN40" s="10" t="n"/>
+      <c r="B40" s="654" t="n"/>
+      <c r="C40" s="654" t="n"/>
+      <c r="D40" s="654" t="n"/>
+      <c r="E40" s="654" t="n"/>
+      <c r="F40" s="654" t="n"/>
+      <c r="G40" s="654" t="n"/>
+      <c r="H40" s="654" t="n"/>
+      <c r="I40" s="654" t="n"/>
+      <c r="J40" s="654" t="n"/>
+      <c r="K40" s="654" t="n"/>
+      <c r="L40" s="654" t="n"/>
+      <c r="M40" s="654" t="n"/>
+      <c r="N40" s="654" t="n"/>
+      <c r="O40" s="654" t="n"/>
+      <c r="P40" s="654" t="n"/>
+      <c r="Q40" s="654" t="n"/>
+      <c r="R40" s="654" t="n"/>
+      <c r="S40" s="654" t="n"/>
+      <c r="T40" s="654" t="n"/>
+      <c r="U40" s="654" t="n"/>
+      <c r="V40" s="654" t="n"/>
+      <c r="W40" s="654" t="n"/>
+      <c r="X40" s="654" t="n"/>
+      <c r="Y40" s="654" t="n"/>
+      <c r="Z40" s="654" t="n"/>
+      <c r="AA40" s="654" t="n"/>
+      <c r="AB40" s="654" t="n"/>
+      <c r="AC40" s="654" t="n"/>
+      <c r="AD40" s="654" t="n"/>
+      <c r="AE40" s="654" t="n"/>
+      <c r="AF40" s="654" t="n"/>
+      <c r="AG40" s="654" t="n"/>
+      <c r="AH40" s="654" t="n"/>
+      <c r="AI40" s="654" t="n"/>
+      <c r="AJ40" s="654" t="n"/>
+      <c r="AK40" s="654" t="n"/>
+      <c r="AL40" s="654" t="n"/>
+      <c r="AM40" s="654" t="n"/>
+      <c r="AN40" s="654" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="730" t="inlineStr">
@@ -9591,91 +9848,91 @@
     </row>
     <row r="46" ht="3" customHeight="1">
       <c r="A46" s="654" t="n"/>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="10" t="n"/>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="10" t="n"/>
-      <c r="G46" s="10" t="n"/>
-      <c r="H46" s="10" t="n"/>
-      <c r="I46" s="10" t="n"/>
-      <c r="J46" s="10" t="n"/>
-      <c r="K46" s="10" t="n"/>
-      <c r="L46" s="10" t="n"/>
-      <c r="M46" s="10" t="n"/>
-      <c r="N46" s="10" t="n"/>
-      <c r="O46" s="10" t="n"/>
-      <c r="P46" s="10" t="n"/>
-      <c r="Q46" s="10" t="n"/>
-      <c r="R46" s="10" t="n"/>
-      <c r="S46" s="10" t="n"/>
-      <c r="T46" s="10" t="n"/>
-      <c r="U46" s="10" t="n"/>
-      <c r="V46" s="10" t="n"/>
-      <c r="W46" s="10" t="n"/>
-      <c r="X46" s="10" t="n"/>
-      <c r="Y46" s="10" t="n"/>
-      <c r="Z46" s="10" t="n"/>
-      <c r="AA46" s="10" t="n"/>
-      <c r="AB46" s="10" t="n"/>
-      <c r="AC46" s="10" t="n"/>
-      <c r="AD46" s="10" t="n"/>
-      <c r="AE46" s="10" t="n"/>
-      <c r="AF46" s="10" t="n"/>
-      <c r="AG46" s="10" t="n"/>
-      <c r="AH46" s="10" t="n"/>
-      <c r="AI46" s="10" t="n"/>
-      <c r="AJ46" s="10" t="n"/>
-      <c r="AK46" s="10" t="n"/>
-      <c r="AL46" s="10" t="n"/>
-      <c r="AM46" s="10" t="n"/>
-      <c r="AN46" s="10" t="n"/>
+      <c r="B46" s="654" t="n"/>
+      <c r="C46" s="654" t="n"/>
+      <c r="D46" s="654" t="n"/>
+      <c r="E46" s="654" t="n"/>
+      <c r="F46" s="654" t="n"/>
+      <c r="G46" s="654" t="n"/>
+      <c r="H46" s="654" t="n"/>
+      <c r="I46" s="654" t="n"/>
+      <c r="J46" s="654" t="n"/>
+      <c r="K46" s="654" t="n"/>
+      <c r="L46" s="654" t="n"/>
+      <c r="M46" s="654" t="n"/>
+      <c r="N46" s="654" t="n"/>
+      <c r="O46" s="654" t="n"/>
+      <c r="P46" s="654" t="n"/>
+      <c r="Q46" s="654" t="n"/>
+      <c r="R46" s="654" t="n"/>
+      <c r="S46" s="654" t="n"/>
+      <c r="T46" s="654" t="n"/>
+      <c r="U46" s="654" t="n"/>
+      <c r="V46" s="654" t="n"/>
+      <c r="W46" s="654" t="n"/>
+      <c r="X46" s="654" t="n"/>
+      <c r="Y46" s="654" t="n"/>
+      <c r="Z46" s="654" t="n"/>
+      <c r="AA46" s="654" t="n"/>
+      <c r="AB46" s="654" t="n"/>
+      <c r="AC46" s="654" t="n"/>
+      <c r="AD46" s="654" t="n"/>
+      <c r="AE46" s="654" t="n"/>
+      <c r="AF46" s="654" t="n"/>
+      <c r="AG46" s="654" t="n"/>
+      <c r="AH46" s="654" t="n"/>
+      <c r="AI46" s="654" t="n"/>
+      <c r="AJ46" s="654" t="n"/>
+      <c r="AK46" s="654" t="n"/>
+      <c r="AL46" s="654" t="n"/>
+      <c r="AM46" s="654" t="n"/>
+      <c r="AN46" s="654" t="n"/>
     </row>
     <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="765" t="inlineStr">
+      <c r="A47" s="370" t="inlineStr">
         <is>
           <t>NOTICE  —  Enter data only in designated white input cells. Do not add, delete or resize columns/rows. File naming: FRM-209_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="766" t="n"/>
-      <c r="C47" s="766" t="n"/>
-      <c r="D47" s="766" t="n"/>
-      <c r="E47" s="766" t="n"/>
-      <c r="F47" s="766" t="n"/>
-      <c r="G47" s="766" t="n"/>
-      <c r="H47" s="766" t="n"/>
-      <c r="I47" s="766" t="n"/>
-      <c r="J47" s="766" t="n"/>
-      <c r="K47" s="766" t="n"/>
-      <c r="L47" s="766" t="n"/>
-      <c r="M47" s="766" t="n"/>
-      <c r="N47" s="766" t="n"/>
-      <c r="O47" s="766" t="n"/>
-      <c r="P47" s="766" t="n"/>
-      <c r="Q47" s="766" t="n"/>
-      <c r="R47" s="766" t="n"/>
-      <c r="S47" s="766" t="n"/>
-      <c r="T47" s="766" t="n"/>
-      <c r="U47" s="766" t="n"/>
-      <c r="V47" s="766" t="n"/>
-      <c r="W47" s="766" t="n"/>
-      <c r="X47" s="766" t="n"/>
-      <c r="Y47" s="766" t="n"/>
-      <c r="Z47" s="766" t="n"/>
-      <c r="AA47" s="766" t="n"/>
-      <c r="AB47" s="766" t="n"/>
-      <c r="AC47" s="766" t="n"/>
-      <c r="AD47" s="766" t="n"/>
-      <c r="AE47" s="766" t="n"/>
-      <c r="AF47" s="766" t="n"/>
-      <c r="AG47" s="766" t="n"/>
-      <c r="AH47" s="766" t="n"/>
-      <c r="AI47" s="766" t="n"/>
-      <c r="AJ47" s="766" t="n"/>
-      <c r="AK47" s="766" t="n"/>
-      <c r="AL47" s="766" t="n"/>
-      <c r="AM47" s="766" t="n"/>
-      <c r="AN47" s="767" t="n"/>
+      <c r="B47" s="371" t="n"/>
+      <c r="C47" s="371" t="n"/>
+      <c r="D47" s="371" t="n"/>
+      <c r="E47" s="371" t="n"/>
+      <c r="F47" s="371" t="n"/>
+      <c r="G47" s="371" t="n"/>
+      <c r="H47" s="371" t="n"/>
+      <c r="I47" s="371" t="n"/>
+      <c r="J47" s="371" t="n"/>
+      <c r="K47" s="371" t="n"/>
+      <c r="L47" s="371" t="n"/>
+      <c r="M47" s="371" t="n"/>
+      <c r="N47" s="371" t="n"/>
+      <c r="O47" s="371" t="n"/>
+      <c r="P47" s="371" t="n"/>
+      <c r="Q47" s="371" t="n"/>
+      <c r="R47" s="371" t="n"/>
+      <c r="S47" s="371" t="n"/>
+      <c r="T47" s="371" t="n"/>
+      <c r="U47" s="371" t="n"/>
+      <c r="V47" s="371" t="n"/>
+      <c r="W47" s="371" t="n"/>
+      <c r="X47" s="371" t="n"/>
+      <c r="Y47" s="371" t="n"/>
+      <c r="Z47" s="371" t="n"/>
+      <c r="AA47" s="371" t="n"/>
+      <c r="AB47" s="371" t="n"/>
+      <c r="AC47" s="371" t="n"/>
+      <c r="AD47" s="371" t="n"/>
+      <c r="AE47" s="371" t="n"/>
+      <c r="AF47" s="371" t="n"/>
+      <c r="AG47" s="371" t="n"/>
+      <c r="AH47" s="371" t="n"/>
+      <c r="AI47" s="371" t="n"/>
+      <c r="AJ47" s="371" t="n"/>
+      <c r="AK47" s="371" t="n"/>
+      <c r="AL47" s="371" t="n"/>
+      <c r="AM47" s="371" t="n"/>
+      <c r="AN47" s="372" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="1"/>
     <row r="49" hidden="1" outlineLevel="1"/>
@@ -10197,367 +10454,351 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="771" t="n"/>
-      <c r="B1" s="772" t="n"/>
-      <c r="C1" s="772" t="n"/>
-      <c r="D1" s="772" t="n"/>
-      <c r="E1" s="772" t="n"/>
-      <c r="F1" s="772" t="n"/>
-      <c r="G1" s="772" t="n"/>
-      <c r="H1" s="773" t="n"/>
-      <c r="I1" s="774" t="inlineStr">
+    <row r="1" hidden="1">
+      <c r="A1" s="815" t="n"/>
+      <c r="B1" s="718" t="n"/>
+      <c r="C1" s="718" t="n"/>
+      <c r="D1" s="718" t="n"/>
+      <c r="E1" s="718" t="n"/>
+      <c r="F1" s="718" t="n"/>
+      <c r="G1" s="718" t="n"/>
+      <c r="H1" s="816" t="n"/>
+      <c r="I1" s="817" t="inlineStr">
         <is>
           <t>HIGH-RISK JOB READINESS REVIEW</t>
         </is>
       </c>
-      <c r="J1" s="772" t="n"/>
-      <c r="K1" s="772" t="n"/>
-      <c r="L1" s="772" t="n"/>
-      <c r="M1" s="772" t="n"/>
-      <c r="N1" s="772" t="n"/>
-      <c r="O1" s="772" t="n"/>
-      <c r="P1" s="772" t="n"/>
-      <c r="Q1" s="772" t="n"/>
-      <c r="R1" s="772" t="n"/>
-      <c r="S1" s="772" t="n"/>
-      <c r="T1" s="772" t="n"/>
-      <c r="U1" s="772" t="n"/>
-      <c r="V1" s="772" t="n"/>
-      <c r="W1" s="772" t="n"/>
-      <c r="X1" s="772" t="n"/>
-      <c r="Y1" s="772" t="n"/>
-      <c r="Z1" s="772" t="n"/>
-      <c r="AA1" s="772" t="n"/>
-      <c r="AB1" s="772" t="n"/>
-      <c r="AC1" s="772" t="n"/>
-      <c r="AD1" s="773" t="n"/>
-      <c r="AE1" s="499" t="inlineStr">
+      <c r="J1" s="718" t="n"/>
+      <c r="K1" s="718" t="n"/>
+      <c r="L1" s="718" t="n"/>
+      <c r="M1" s="718" t="n"/>
+      <c r="N1" s="718" t="n"/>
+      <c r="O1" s="718" t="n"/>
+      <c r="P1" s="718" t="n"/>
+      <c r="Q1" s="718" t="n"/>
+      <c r="R1" s="718" t="n"/>
+      <c r="S1" s="718" t="n"/>
+      <c r="T1" s="718" t="n"/>
+      <c r="U1" s="718" t="n"/>
+      <c r="V1" s="718" t="n"/>
+      <c r="W1" s="718" t="n"/>
+      <c r="X1" s="718" t="n"/>
+      <c r="Y1" s="718" t="n"/>
+      <c r="Z1" s="718" t="n"/>
+      <c r="AA1" s="718" t="n"/>
+      <c r="AB1" s="718" t="n"/>
+      <c r="AC1" s="718" t="n"/>
+      <c r="AD1" s="816" t="n"/>
+      <c r="AE1" s="500" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="772" t="n"/>
-      <c r="AG1" s="772" t="n"/>
-      <c r="AH1" s="775" t="n"/>
-      <c r="AI1" s="502" t="inlineStr">
+      <c r="AF1" s="718" t="n"/>
+      <c r="AG1" s="718" t="n"/>
+      <c r="AH1" s="818" t="n"/>
+      <c r="AI1" s="503" t="inlineStr">
         <is>
           <t>FRM-209</t>
         </is>
       </c>
-      <c r="AJ1" s="772" t="n"/>
-      <c r="AK1" s="772" t="n"/>
-      <c r="AL1" s="772" t="n"/>
-      <c r="AM1" s="772" t="n"/>
-      <c r="AN1" s="773" t="n"/>
+      <c r="AJ1" s="718" t="n"/>
+      <c r="AK1" s="718" t="n"/>
+      <c r="AL1" s="718" t="n"/>
+      <c r="AM1" s="718" t="n"/>
+      <c r="AN1" s="816" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="776" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="777" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="777" t="n"/>
-      <c r="AE2" s="778" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="791" t="n"/>
+      <c r="C2" s="791" t="n"/>
+      <c r="D2" s="791" t="n"/>
+      <c r="E2" s="791" t="n"/>
+      <c r="F2" s="791" t="n"/>
+      <c r="G2" s="791" t="n"/>
+      <c r="H2" s="792" t="n"/>
+      <c r="I2" s="791" t="n"/>
+      <c r="J2" s="791" t="n"/>
+      <c r="K2" s="791" t="n"/>
+      <c r="L2" s="791" t="n"/>
+      <c r="M2" s="791" t="n"/>
+      <c r="N2" s="791" t="n"/>
+      <c r="O2" s="791" t="n"/>
+      <c r="P2" s="791" t="n"/>
+      <c r="Q2" s="791" t="n"/>
+      <c r="R2" s="791" t="n"/>
+      <c r="S2" s="791" t="n"/>
+      <c r="T2" s="791" t="n"/>
+      <c r="U2" s="791" t="n"/>
+      <c r="V2" s="791" t="n"/>
+      <c r="W2" s="791" t="n"/>
+      <c r="X2" s="791" t="n"/>
+      <c r="Y2" s="791" t="n"/>
+      <c r="Z2" s="791" t="n"/>
+      <c r="AA2" s="791" t="n"/>
+      <c r="AB2" s="791" t="n"/>
+      <c r="AC2" s="791" t="n"/>
+      <c r="AD2" s="792" t="n"/>
+      <c r="AE2" s="793" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="10" t="n"/>
-      <c r="AG2" s="10" t="n"/>
-      <c r="AH2" s="779" t="n"/>
-      <c r="AI2" s="780" t="inlineStr">
+      <c r="AF2" s="794" t="n"/>
+      <c r="AG2" s="794" t="n"/>
+      <c r="AH2" s="795" t="n"/>
+      <c r="AI2" s="796" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="10" t="n"/>
-      <c r="AK2" s="10" t="n"/>
-      <c r="AL2" s="10" t="n"/>
-      <c r="AM2" s="10" t="n"/>
-      <c r="AN2" s="777" t="n"/>
+      <c r="AJ2" s="797" t="n"/>
+      <c r="AK2" s="797" t="n"/>
+      <c r="AL2" s="797" t="n"/>
+      <c r="AM2" s="797" t="n"/>
+      <c r="AN2" s="798" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="776" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="777" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="777" t="n"/>
-      <c r="AE3" s="778" t="inlineStr">
+      <c r="A3" s="799" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="800" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="800" t="n"/>
+      <c r="AE3" s="801" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="10" t="n"/>
-      <c r="AH3" s="779" t="n"/>
-      <c r="AI3" s="780" t="inlineStr">
+      <c r="AF3" s="802" t="n"/>
+      <c r="AG3" s="802" t="n"/>
+      <c r="AH3" s="803" t="n"/>
+      <c r="AI3" s="699" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="10" t="n"/>
-      <c r="AK3" s="10" t="n"/>
-      <c r="AL3" s="10" t="n"/>
-      <c r="AM3" s="10" t="n"/>
-      <c r="AN3" s="777" t="n"/>
+      <c r="AJ3" s="804" t="n"/>
+      <c r="AK3" s="804" t="n"/>
+      <c r="AL3" s="804" t="n"/>
+      <c r="AM3" s="804" t="n"/>
+      <c r="AN3" s="805" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="776" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="777" t="n"/>
-      <c r="I4" s="781" t="inlineStr">
+      <c r="A4" s="799" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="800" t="n"/>
+      <c r="I4" s="342" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="777" t="n"/>
-      <c r="AE4" s="778" t="inlineStr">
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="800" t="n"/>
+      <c r="AE4" s="801" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="10" t="n"/>
-      <c r="AG4" s="10" t="n"/>
-      <c r="AH4" s="779" t="n"/>
-      <c r="AI4" s="780" t="inlineStr">
+      <c r="AF4" s="802" t="n"/>
+      <c r="AG4" s="802" t="n"/>
+      <c r="AH4" s="803" t="n"/>
+      <c r="AI4" s="699" t="inlineStr">
         <is>
           <t>Planning / QA / Engineering</t>
         </is>
       </c>
-      <c r="AJ4" s="10" t="n"/>
-      <c r="AK4" s="10" t="n"/>
-      <c r="AL4" s="10" t="n"/>
-      <c r="AM4" s="10" t="n"/>
-      <c r="AN4" s="777" t="n"/>
+      <c r="AJ4" s="804" t="n"/>
+      <c r="AK4" s="804" t="n"/>
+      <c r="AL4" s="804" t="n"/>
+      <c r="AM4" s="804" t="n"/>
+      <c r="AN4" s="805" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="782" t="n"/>
-      <c r="B5" s="783" t="n"/>
-      <c r="C5" s="783" t="n"/>
-      <c r="D5" s="783" t="n"/>
-      <c r="E5" s="783" t="n"/>
-      <c r="F5" s="783" t="n"/>
-      <c r="G5" s="783" t="n"/>
-      <c r="H5" s="784" t="n"/>
-      <c r="I5" s="785" t="inlineStr">
+      <c r="A5" s="799" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="800" t="n"/>
+      <c r="I5" s="581" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="783" t="n"/>
-      <c r="K5" s="783" t="n"/>
-      <c r="L5" s="783" t="n"/>
-      <c r="M5" s="783" t="n"/>
-      <c r="N5" s="783" t="n"/>
-      <c r="O5" s="783" t="n"/>
-      <c r="P5" s="783" t="n"/>
-      <c r="Q5" s="783" t="n"/>
-      <c r="R5" s="783" t="n"/>
-      <c r="S5" s="783" t="n"/>
-      <c r="T5" s="783" t="n"/>
-      <c r="U5" s="783" t="n"/>
-      <c r="V5" s="783" t="n"/>
-      <c r="W5" s="783" t="n"/>
-      <c r="X5" s="783" t="n"/>
-      <c r="Y5" s="783" t="n"/>
-      <c r="Z5" s="783" t="n"/>
-      <c r="AA5" s="783" t="n"/>
-      <c r="AB5" s="783" t="n"/>
-      <c r="AC5" s="783" t="n"/>
-      <c r="AD5" s="784" t="n"/>
-      <c r="AE5" s="786" t="inlineStr">
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="800" t="n"/>
+      <c r="AE5" s="801" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="783" t="n"/>
-      <c r="AG5" s="783" t="n"/>
-      <c r="AH5" s="787" t="n"/>
-      <c r="AI5" s="788" t="inlineStr">
+      <c r="AF5" s="802" t="n"/>
+      <c r="AG5" s="802" t="n"/>
+      <c r="AH5" s="803" t="n"/>
+      <c r="AI5" s="699" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="783" t="n"/>
-      <c r="AK5" s="783" t="n"/>
-      <c r="AL5" s="783" t="n"/>
-      <c r="AM5" s="783" t="n"/>
-      <c r="AN5" s="784" t="n"/>
+      <c r="AJ5" s="804" t="n"/>
+      <c r="AK5" s="804" t="n"/>
+      <c r="AL5" s="804" t="n"/>
+      <c r="AM5" s="804" t="n"/>
+      <c r="AN5" s="805" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="789" t="n"/>
-      <c r="B6" s="789" t="n"/>
-      <c r="C6" s="789" t="n"/>
-      <c r="D6" s="789" t="n"/>
-      <c r="E6" s="789" t="n"/>
-      <c r="F6" s="789" t="n"/>
-      <c r="G6" s="789" t="n"/>
-      <c r="H6" s="789" t="n"/>
-      <c r="I6" s="789" t="n"/>
-      <c r="J6" s="789" t="n"/>
-      <c r="K6" s="789" t="n"/>
-      <c r="L6" s="789" t="n"/>
-      <c r="M6" s="789" t="n"/>
-      <c r="N6" s="789" t="n"/>
-      <c r="O6" s="789" t="n"/>
-      <c r="P6" s="789" t="n"/>
-      <c r="Q6" s="789" t="n"/>
-      <c r="R6" s="789" t="n"/>
-      <c r="S6" s="789" t="n"/>
-      <c r="T6" s="789" t="n"/>
-      <c r="U6" s="789" t="n"/>
-      <c r="V6" s="789" t="n"/>
-      <c r="W6" s="789" t="n"/>
-      <c r="X6" s="789" t="n"/>
-      <c r="Y6" s="789" t="n"/>
-      <c r="Z6" s="789" t="n"/>
-      <c r="AA6" s="789" t="n"/>
-      <c r="AB6" s="789" t="n"/>
-      <c r="AC6" s="789" t="n"/>
-      <c r="AD6" s="789" t="n"/>
-      <c r="AE6" s="789" t="n"/>
-      <c r="AF6" s="789" t="n"/>
-      <c r="AG6" s="789" t="n"/>
-      <c r="AH6" s="789" t="n"/>
-      <c r="AI6" s="789" t="n"/>
-      <c r="AJ6" s="789" t="n"/>
-      <c r="AK6" s="789" t="n"/>
-      <c r="AL6" s="789" t="n"/>
-      <c r="AM6" s="789" t="n"/>
-      <c r="AN6" s="789" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="819" t="n"/>
+      <c r="B6" s="820" t="n"/>
+      <c r="C6" s="820" t="n"/>
+      <c r="D6" s="820" t="n"/>
+      <c r="E6" s="820" t="n"/>
+      <c r="F6" s="820" t="n"/>
+      <c r="G6" s="820" t="n"/>
+      <c r="H6" s="821" t="n"/>
+      <c r="I6" s="820" t="n"/>
+      <c r="J6" s="820" t="n"/>
+      <c r="K6" s="820" t="n"/>
+      <c r="L6" s="820" t="n"/>
+      <c r="M6" s="820" t="n"/>
+      <c r="N6" s="820" t="n"/>
+      <c r="O6" s="820" t="n"/>
+      <c r="P6" s="820" t="n"/>
+      <c r="Q6" s="820" t="n"/>
+      <c r="R6" s="820" t="n"/>
+      <c r="S6" s="820" t="n"/>
+      <c r="T6" s="820" t="n"/>
+      <c r="U6" s="820" t="n"/>
+      <c r="V6" s="820" t="n"/>
+      <c r="W6" s="820" t="n"/>
+      <c r="X6" s="820" t="n"/>
+      <c r="Y6" s="820" t="n"/>
+      <c r="Z6" s="820" t="n"/>
+      <c r="AA6" s="820" t="n"/>
+      <c r="AB6" s="820" t="n"/>
+      <c r="AC6" s="820" t="n"/>
+      <c r="AD6" s="821" t="n"/>
+      <c r="AE6" s="822" t="n"/>
+      <c r="AF6" s="822" t="n"/>
+      <c r="AG6" s="822" t="n"/>
+      <c r="AH6" s="823" t="n"/>
+      <c r="AI6" s="824" t="n"/>
+      <c r="AJ6" s="824" t="n"/>
+      <c r="AK6" s="824" t="n"/>
+      <c r="AL6" s="824" t="n"/>
+      <c r="AM6" s="824" t="n"/>
+      <c r="AN6" s="825" t="n"/>
     </row>
-    <row r="7">
-      <c r="A7" s="402" t="inlineStr">
-        <is>
-          <t>VAL_RESULT_CORE</t>
-        </is>
-      </c>
-      <c r="B7" s="402" t="inlineStr">
-        <is>
-          <t>VAL_DECISION_GATE_CORE</t>
-        </is>
-      </c>
-      <c r="C7" s="402" t="inlineStr">
-        <is>
-          <t>VAL_STATUS_CORE</t>
-        </is>
-      </c>
-      <c r="D7" s="402" t="inlineStr">
-        <is>
-          <t>VAL_RISK_LEVEL_CORE</t>
-        </is>
-      </c>
-      <c r="E7" s="790" t="n"/>
-      <c r="F7" s="790" t="n"/>
-      <c r="G7" s="790" t="n"/>
-      <c r="H7" s="790" t="n"/>
-      <c r="I7" s="790" t="n"/>
-      <c r="J7" s="790" t="n"/>
-      <c r="K7" s="790" t="n"/>
-      <c r="L7" s="790" t="n"/>
-      <c r="M7" s="790" t="n"/>
-      <c r="N7" s="790" t="n"/>
-      <c r="O7" s="790" t="n"/>
-      <c r="P7" s="790" t="n"/>
-      <c r="Q7" s="790" t="n"/>
-      <c r="R7" s="790" t="n"/>
-      <c r="S7" s="790" t="n"/>
-      <c r="T7" s="790" t="n"/>
-      <c r="U7" s="790" t="n"/>
-      <c r="V7" s="790" t="n"/>
-      <c r="W7" s="790" t="n"/>
-      <c r="X7" s="790" t="n"/>
-      <c r="Y7" s="790" t="n"/>
-      <c r="Z7" s="790" t="n"/>
-      <c r="AA7" s="790" t="n"/>
-      <c r="AB7" s="790" t="n"/>
-      <c r="AC7" s="790" t="n"/>
-      <c r="AD7" s="790" t="n"/>
-      <c r="AE7" s="790" t="n"/>
-      <c r="AF7" s="790" t="n"/>
-      <c r="AG7" s="790" t="n"/>
-      <c r="AH7" s="790" t="n"/>
-      <c r="AI7" s="790" t="n"/>
-      <c r="AJ7" s="790" t="n"/>
-      <c r="AK7" s="790" t="n"/>
-      <c r="AL7" s="790" t="n"/>
-      <c r="AM7" s="790" t="n"/>
-      <c r="AN7" s="790" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="826" t="n"/>
+      <c r="B7" s="826" t="n"/>
+      <c r="C7" s="826" t="n"/>
+      <c r="D7" s="826" t="n"/>
+      <c r="E7" s="827" t="n"/>
+      <c r="F7" s="827" t="n"/>
+      <c r="G7" s="827" t="n"/>
+      <c r="H7" s="827" t="n"/>
+      <c r="I7" s="827" t="n"/>
+      <c r="J7" s="827" t="n"/>
+      <c r="K7" s="827" t="n"/>
+      <c r="L7" s="827" t="n"/>
+      <c r="M7" s="827" t="n"/>
+      <c r="N7" s="827" t="n"/>
+      <c r="O7" s="827" t="n"/>
+      <c r="P7" s="827" t="n"/>
+      <c r="Q7" s="827" t="n"/>
+      <c r="R7" s="827" t="n"/>
+      <c r="S7" s="827" t="n"/>
+      <c r="T7" s="827" t="n"/>
+      <c r="U7" s="827" t="n"/>
+      <c r="V7" s="827" t="n"/>
+      <c r="W7" s="827" t="n"/>
+      <c r="X7" s="827" t="n"/>
+      <c r="Y7" s="827" t="n"/>
+      <c r="Z7" s="827" t="n"/>
+      <c r="AA7" s="827" t="n"/>
+      <c r="AB7" s="827" t="n"/>
+      <c r="AC7" s="827" t="n"/>
+      <c r="AD7" s="827" t="n"/>
+      <c r="AE7" s="827" t="n"/>
+      <c r="AF7" s="827" t="n"/>
+      <c r="AG7" s="827" t="n"/>
+      <c r="AH7" s="827" t="n"/>
+      <c r="AI7" s="827" t="n"/>
+      <c r="AJ7" s="827" t="n"/>
+      <c r="AK7" s="827" t="n"/>
+      <c r="AL7" s="827" t="n"/>
+      <c r="AM7" s="827" t="n"/>
+      <c r="AN7" s="827" t="n"/>
     </row>
     <row r="8" hidden="1">
       <c r="A8" s="402" t="inlineStr">
@@ -11212,6 +11453,7 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11266,7 +11508,7 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="386" t="n"/>
       <c r="B1" s="319" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -11321,280 +11563,288 @@
       <c r="AN1" s="678" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="B2" s="320" t="n"/>
-      <c r="C2" s="275" t="n"/>
-      <c r="H2" s="679" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="791" t="n"/>
+      <c r="C2" s="791" t="n"/>
+      <c r="D2" s="791" t="n"/>
+      <c r="E2" s="791" t="n"/>
+      <c r="F2" s="791" t="n"/>
+      <c r="G2" s="791" t="n"/>
+      <c r="H2" s="828" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="I2" s="680" t="inlineStr">
+      <c r="I2" s="335" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="J2" s="680" t="n"/>
-      <c r="K2" s="680" t="n"/>
-      <c r="L2" s="680" t="n"/>
-      <c r="M2" s="680" t="n"/>
-      <c r="N2" s="680" t="n"/>
-      <c r="O2" s="680" t="n"/>
-      <c r="P2" s="680" t="n"/>
-      <c r="Q2" s="680" t="n"/>
-      <c r="R2" s="680" t="n"/>
-      <c r="S2" s="680" t="n"/>
-      <c r="T2" s="680" t="n"/>
-      <c r="U2" s="680" t="n"/>
-      <c r="V2" s="680" t="n"/>
-      <c r="W2" s="680" t="n"/>
-      <c r="X2" s="680" t="n"/>
-      <c r="Y2" s="680" t="n"/>
-      <c r="Z2" s="680" t="n"/>
-      <c r="AA2" s="680" t="n"/>
-      <c r="AB2" s="680" t="n"/>
-      <c r="AC2" s="680" t="n"/>
-      <c r="AD2" s="680" t="n"/>
-      <c r="AE2" s="681" t="n"/>
-      <c r="AF2" s="681" t="n"/>
-      <c r="AG2" s="681" t="n"/>
-      <c r="AH2" s="681" t="n"/>
-      <c r="AI2" s="638" t="n"/>
-      <c r="AJ2" s="638" t="n"/>
-      <c r="AK2" s="638" t="n"/>
-      <c r="AL2" s="638" t="n"/>
-      <c r="AM2" s="638" t="n"/>
-      <c r="AN2" s="682" t="n"/>
+      <c r="J2" s="676" t="n"/>
+      <c r="K2" s="676" t="n"/>
+      <c r="L2" s="676" t="n"/>
+      <c r="M2" s="676" t="n"/>
+      <c r="N2" s="676" t="n"/>
+      <c r="O2" s="676" t="n"/>
+      <c r="P2" s="676" t="n"/>
+      <c r="Q2" s="676" t="n"/>
+      <c r="R2" s="676" t="n"/>
+      <c r="S2" s="676" t="n"/>
+      <c r="T2" s="676" t="n"/>
+      <c r="U2" s="676" t="n"/>
+      <c r="V2" s="676" t="n"/>
+      <c r="W2" s="676" t="n"/>
+      <c r="X2" s="676" t="n"/>
+      <c r="Y2" s="676" t="n"/>
+      <c r="Z2" s="676" t="n"/>
+      <c r="AA2" s="676" t="n"/>
+      <c r="AB2" s="676" t="n"/>
+      <c r="AC2" s="676" t="n"/>
+      <c r="AD2" s="829" t="n"/>
+      <c r="AE2" s="830" t="n"/>
+      <c r="AF2" s="830" t="n"/>
+      <c r="AG2" s="830" t="n"/>
+      <c r="AH2" s="831" t="n"/>
+      <c r="AI2" s="832" t="n"/>
+      <c r="AJ2" s="832" t="n"/>
+      <c r="AK2" s="832" t="n"/>
+      <c r="AL2" s="832" t="n"/>
+      <c r="AM2" s="832" t="n"/>
+      <c r="AN2" s="833" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="B3" s="320" t="n"/>
-      <c r="C3" s="275" t="n"/>
-      <c r="H3" s="679" t="inlineStr">
+      <c r="A3" s="799" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="834" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="I3" s="680" t="inlineStr">
+      <c r="I3" s="342" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J3" s="680" t="n"/>
-      <c r="K3" s="680" t="n"/>
-      <c r="L3" s="680" t="n"/>
-      <c r="M3" s="680" t="n"/>
-      <c r="N3" s="680" t="n"/>
-      <c r="O3" s="680" t="n"/>
-      <c r="P3" s="680" t="n"/>
-      <c r="Q3" s="680" t="n"/>
-      <c r="R3" s="680" t="n"/>
-      <c r="S3" s="680" t="n"/>
-      <c r="T3" s="680" t="n"/>
-      <c r="U3" s="680" t="n"/>
-      <c r="V3" s="680" t="n"/>
-      <c r="W3" s="680" t="n"/>
-      <c r="X3" s="680" t="n"/>
-      <c r="Y3" s="680" t="n"/>
-      <c r="Z3" s="680" t="n"/>
-      <c r="AA3" s="680" t="n"/>
-      <c r="AB3" s="680" t="n"/>
-      <c r="AC3" s="680" t="n"/>
-      <c r="AD3" s="680" t="n"/>
-      <c r="AE3" s="681" t="n"/>
-      <c r="AF3" s="681" t="n"/>
-      <c r="AG3" s="681" t="n"/>
-      <c r="AH3" s="681" t="n"/>
-      <c r="AI3" s="638" t="n"/>
-      <c r="AJ3" s="638" t="n"/>
-      <c r="AK3" s="638" t="n"/>
-      <c r="AL3" s="638" t="n"/>
-      <c r="AM3" s="638" t="n"/>
-      <c r="AN3" s="682" t="n"/>
+      <c r="J3" s="835" t="n"/>
+      <c r="K3" s="835" t="n"/>
+      <c r="L3" s="835" t="n"/>
+      <c r="M3" s="835" t="n"/>
+      <c r="N3" s="835" t="n"/>
+      <c r="O3" s="835" t="n"/>
+      <c r="P3" s="835" t="n"/>
+      <c r="Q3" s="835" t="n"/>
+      <c r="R3" s="835" t="n"/>
+      <c r="S3" s="835" t="n"/>
+      <c r="T3" s="835" t="n"/>
+      <c r="U3" s="835" t="n"/>
+      <c r="V3" s="835" t="n"/>
+      <c r="W3" s="835" t="n"/>
+      <c r="X3" s="835" t="n"/>
+      <c r="Y3" s="835" t="n"/>
+      <c r="Z3" s="835" t="n"/>
+      <c r="AA3" s="835" t="n"/>
+      <c r="AB3" s="835" t="n"/>
+      <c r="AC3" s="835" t="n"/>
+      <c r="AD3" s="836" t="n"/>
+      <c r="AE3" s="837" t="n"/>
+      <c r="AF3" s="837" t="n"/>
+      <c r="AG3" s="837" t="n"/>
+      <c r="AH3" s="838" t="n"/>
+      <c r="AI3" s="839" t="n"/>
+      <c r="AJ3" s="839" t="n"/>
+      <c r="AK3" s="839" t="n"/>
+      <c r="AL3" s="839" t="n"/>
+      <c r="AM3" s="839" t="n"/>
+      <c r="AN3" s="840" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="B4" s="320" t="n"/>
-      <c r="C4" s="683" t="inlineStr">
+      <c r="A4" s="799" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="581" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="H4" s="679" t="inlineStr">
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="834" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="I4" s="684" t="inlineStr"/>
-      <c r="J4" s="684" t="n"/>
-      <c r="K4" s="684" t="n"/>
-      <c r="L4" s="684" t="n"/>
-      <c r="M4" s="684" t="n"/>
-      <c r="N4" s="684" t="n"/>
-      <c r="O4" s="684" t="n"/>
-      <c r="P4" s="684" t="n"/>
-      <c r="Q4" s="684" t="n"/>
-      <c r="R4" s="684" t="n"/>
-      <c r="S4" s="684" t="n"/>
-      <c r="T4" s="684" t="n"/>
-      <c r="U4" s="684" t="n"/>
-      <c r="V4" s="684" t="n"/>
-      <c r="W4" s="684" t="n"/>
-      <c r="X4" s="684" t="n"/>
-      <c r="Y4" s="684" t="n"/>
-      <c r="Z4" s="684" t="n"/>
-      <c r="AA4" s="684" t="n"/>
-      <c r="AB4" s="684" t="n"/>
-      <c r="AC4" s="684" t="n"/>
-      <c r="AD4" s="684" t="n"/>
-      <c r="AE4" s="681" t="n"/>
-      <c r="AF4" s="681" t="n"/>
-      <c r="AG4" s="681" t="n"/>
-      <c r="AH4" s="681" t="n"/>
-      <c r="AI4" s="638" t="n"/>
-      <c r="AJ4" s="638" t="n"/>
-      <c r="AK4" s="638" t="n"/>
-      <c r="AL4" s="638" t="n"/>
-      <c r="AM4" s="638" t="n"/>
-      <c r="AN4" s="682" t="n"/>
+      <c r="I4" s="516" t="inlineStr"/>
+      <c r="J4" s="516" t="n"/>
+      <c r="K4" s="516" t="n"/>
+      <c r="L4" s="516" t="n"/>
+      <c r="M4" s="516" t="n"/>
+      <c r="N4" s="516" t="n"/>
+      <c r="O4" s="516" t="n"/>
+      <c r="P4" s="516" t="n"/>
+      <c r="Q4" s="516" t="n"/>
+      <c r="R4" s="516" t="n"/>
+      <c r="S4" s="516" t="n"/>
+      <c r="T4" s="516" t="n"/>
+      <c r="U4" s="516" t="n"/>
+      <c r="V4" s="516" t="n"/>
+      <c r="W4" s="516" t="n"/>
+      <c r="X4" s="516" t="n"/>
+      <c r="Y4" s="516" t="n"/>
+      <c r="Z4" s="516" t="n"/>
+      <c r="AA4" s="516" t="n"/>
+      <c r="AB4" s="516" t="n"/>
+      <c r="AC4" s="516" t="n"/>
+      <c r="AD4" s="841" t="n"/>
+      <c r="AE4" s="837" t="n"/>
+      <c r="AF4" s="837" t="n"/>
+      <c r="AG4" s="837" t="n"/>
+      <c r="AH4" s="838" t="n"/>
+      <c r="AI4" s="839" t="n"/>
+      <c r="AJ4" s="839" t="n"/>
+      <c r="AK4" s="839" t="n"/>
+      <c r="AL4" s="839" t="n"/>
+      <c r="AM4" s="839" t="n"/>
+      <c r="AN4" s="840" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="282" t="n"/>
-      <c r="B5" s="287" t="n"/>
-      <c r="C5" s="685" t="inlineStr">
+      <c r="A5" s="799" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="842" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="283" t="n"/>
-      <c r="E5" s="283" t="n"/>
-      <c r="F5" s="283" t="n"/>
-      <c r="G5" s="283" t="n"/>
-      <c r="H5" s="686" t="inlineStr">
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="834" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="I5" s="687" t="inlineStr"/>
-      <c r="J5" s="687" t="n"/>
-      <c r="K5" s="687" t="n"/>
-      <c r="L5" s="687" t="n"/>
-      <c r="M5" s="687" t="n"/>
-      <c r="N5" s="687" t="n"/>
-      <c r="O5" s="687" t="n"/>
-      <c r="P5" s="687" t="n"/>
-      <c r="Q5" s="687" t="n"/>
-      <c r="R5" s="687" t="n"/>
-      <c r="S5" s="687" t="n"/>
-      <c r="T5" s="687" t="n"/>
-      <c r="U5" s="687" t="n"/>
-      <c r="V5" s="687" t="n"/>
-      <c r="W5" s="687" t="n"/>
-      <c r="X5" s="687" t="n"/>
-      <c r="Y5" s="687" t="n"/>
-      <c r="Z5" s="687" t="n"/>
-      <c r="AA5" s="687" t="n"/>
-      <c r="AB5" s="687" t="n"/>
-      <c r="AC5" s="687" t="n"/>
-      <c r="AD5" s="687" t="n"/>
-      <c r="AE5" s="688" t="n"/>
-      <c r="AF5" s="688" t="n"/>
-      <c r="AG5" s="688" t="n"/>
-      <c r="AH5" s="688" t="n"/>
-      <c r="AI5" s="644" t="n"/>
-      <c r="AJ5" s="644" t="n"/>
-      <c r="AK5" s="644" t="n"/>
-      <c r="AL5" s="644" t="n"/>
-      <c r="AM5" s="644" t="n"/>
-      <c r="AN5" s="689" t="n"/>
+      <c r="I5" s="843" t="inlineStr"/>
+      <c r="J5" s="843" t="n"/>
+      <c r="K5" s="843" t="n"/>
+      <c r="L5" s="843" t="n"/>
+      <c r="M5" s="843" t="n"/>
+      <c r="N5" s="843" t="n"/>
+      <c r="O5" s="843" t="n"/>
+      <c r="P5" s="843" t="n"/>
+      <c r="Q5" s="843" t="n"/>
+      <c r="R5" s="843" t="n"/>
+      <c r="S5" s="843" t="n"/>
+      <c r="T5" s="843" t="n"/>
+      <c r="U5" s="843" t="n"/>
+      <c r="V5" s="843" t="n"/>
+      <c r="W5" s="843" t="n"/>
+      <c r="X5" s="843" t="n"/>
+      <c r="Y5" s="843" t="n"/>
+      <c r="Z5" s="843" t="n"/>
+      <c r="AA5" s="843" t="n"/>
+      <c r="AB5" s="843" t="n"/>
+      <c r="AC5" s="843" t="n"/>
+      <c r="AD5" s="844" t="n"/>
+      <c r="AE5" s="837" t="n"/>
+      <c r="AF5" s="837" t="n"/>
+      <c r="AG5" s="837" t="n"/>
+      <c r="AH5" s="838" t="n"/>
+      <c r="AI5" s="839" t="n"/>
+      <c r="AJ5" s="839" t="n"/>
+      <c r="AK5" s="839" t="n"/>
+      <c r="AL5" s="839" t="n"/>
+      <c r="AM5" s="839" t="n"/>
+      <c r="AN5" s="840" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="690" t="n"/>
-      <c r="B6" s="646" t="n"/>
-      <c r="C6" s="646" t="n"/>
-      <c r="D6" s="646" t="n"/>
-      <c r="E6" s="646" t="n"/>
-      <c r="F6" s="646" t="n"/>
-      <c r="G6" s="646" t="n"/>
-      <c r="H6" s="646" t="n"/>
-      <c r="I6" s="646" t="n"/>
-      <c r="J6" s="646" t="n"/>
-      <c r="K6" s="646" t="n"/>
-      <c r="L6" s="646" t="n"/>
-      <c r="M6" s="646" t="n"/>
-      <c r="N6" s="646" t="n"/>
-      <c r="O6" s="646" t="n"/>
-      <c r="P6" s="646" t="n"/>
-      <c r="Q6" s="646" t="n"/>
-      <c r="R6" s="646" t="n"/>
-      <c r="S6" s="646" t="n"/>
-      <c r="T6" s="646" t="n"/>
-      <c r="U6" s="646" t="n"/>
-      <c r="V6" s="646" t="n"/>
-      <c r="W6" s="646" t="n"/>
-      <c r="X6" s="646" t="n"/>
-      <c r="Y6" s="646" t="n"/>
-      <c r="Z6" s="646" t="n"/>
-      <c r="AA6" s="646" t="n"/>
-      <c r="AB6" s="646" t="n"/>
-      <c r="AC6" s="646" t="n"/>
-      <c r="AD6" s="646" t="n"/>
-      <c r="AE6" s="646" t="n"/>
-      <c r="AF6" s="646" t="n"/>
-      <c r="AG6" s="646" t="n"/>
-      <c r="AH6" s="646" t="n"/>
-      <c r="AI6" s="646" t="n"/>
-      <c r="AJ6" s="646" t="n"/>
-      <c r="AK6" s="646" t="n"/>
-      <c r="AL6" s="646" t="n"/>
-      <c r="AM6" s="646" t="n"/>
-      <c r="AN6" s="646" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="352" t="n"/>
+      <c r="B6" s="807" t="n"/>
+      <c r="C6" s="807" t="n"/>
+      <c r="D6" s="807" t="n"/>
+      <c r="E6" s="807" t="n"/>
+      <c r="F6" s="807" t="n"/>
+      <c r="G6" s="807" t="n"/>
+      <c r="H6" s="808" t="n"/>
+      <c r="I6" s="807" t="n"/>
+      <c r="J6" s="807" t="n"/>
+      <c r="K6" s="807" t="n"/>
+      <c r="L6" s="807" t="n"/>
+      <c r="M6" s="807" t="n"/>
+      <c r="N6" s="807" t="n"/>
+      <c r="O6" s="807" t="n"/>
+      <c r="P6" s="807" t="n"/>
+      <c r="Q6" s="807" t="n"/>
+      <c r="R6" s="807" t="n"/>
+      <c r="S6" s="807" t="n"/>
+      <c r="T6" s="807" t="n"/>
+      <c r="U6" s="807" t="n"/>
+      <c r="V6" s="807" t="n"/>
+      <c r="W6" s="807" t="n"/>
+      <c r="X6" s="807" t="n"/>
+      <c r="Y6" s="807" t="n"/>
+      <c r="Z6" s="807" t="n"/>
+      <c r="AA6" s="807" t="n"/>
+      <c r="AB6" s="807" t="n"/>
+      <c r="AC6" s="807" t="n"/>
+      <c r="AD6" s="808" t="n"/>
+      <c r="AE6" s="809" t="n"/>
+      <c r="AF6" s="809" t="n"/>
+      <c r="AG6" s="809" t="n"/>
+      <c r="AH6" s="810" t="n"/>
+      <c r="AI6" s="811" t="n"/>
+      <c r="AJ6" s="811" t="n"/>
+      <c r="AK6" s="811" t="n"/>
+      <c r="AL6" s="811" t="n"/>
+      <c r="AM6" s="811" t="n"/>
+      <c r="AN6" s="812" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="647" t="inlineStr">
-        <is>
-          <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
-        </is>
-      </c>
-      <c r="B7" s="289" t="n"/>
-      <c r="C7" s="289" t="n"/>
-      <c r="D7" s="289" t="n"/>
-      <c r="E7" s="289" t="n"/>
-      <c r="F7" s="289" t="n"/>
-      <c r="G7" s="289" t="n"/>
-      <c r="H7" s="289" t="n"/>
-      <c r="I7" s="289" t="n"/>
-      <c r="J7" s="691" t="n"/>
-      <c r="K7" s="691" t="n"/>
-      <c r="L7" s="691" t="n"/>
-      <c r="M7" s="691" t="n"/>
-      <c r="N7" s="691" t="n"/>
-      <c r="O7" s="691" t="n"/>
-      <c r="P7" s="691" t="n"/>
-      <c r="Q7" s="691" t="n"/>
-      <c r="R7" s="691" t="n"/>
-      <c r="S7" s="691" t="n"/>
-      <c r="T7" s="691" t="n"/>
-      <c r="U7" s="691" t="n"/>
-      <c r="V7" s="691" t="n"/>
-      <c r="W7" s="691" t="n"/>
-      <c r="X7" s="691" t="n"/>
-      <c r="Y7" s="691" t="n"/>
-      <c r="Z7" s="691" t="n"/>
-      <c r="AA7" s="691" t="n"/>
-      <c r="AB7" s="691" t="n"/>
-      <c r="AC7" s="691" t="n"/>
-      <c r="AD7" s="691" t="n"/>
-      <c r="AE7" s="691" t="n"/>
-      <c r="AF7" s="691" t="n"/>
-      <c r="AG7" s="691" t="n"/>
-      <c r="AH7" s="691" t="n"/>
-      <c r="AI7" s="691" t="n"/>
-      <c r="AJ7" s="691" t="n"/>
-      <c r="AK7" s="691" t="n"/>
-      <c r="AL7" s="691" t="n"/>
-      <c r="AM7" s="691" t="n"/>
-      <c r="AN7" s="692" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="813" t="n"/>
+      <c r="B7" s="814" t="n"/>
+      <c r="C7" s="814" t="n"/>
+      <c r="D7" s="814" t="n"/>
+      <c r="E7" s="814" t="n"/>
+      <c r="F7" s="814" t="n"/>
+      <c r="G7" s="814" t="n"/>
+      <c r="H7" s="814" t="n"/>
+      <c r="I7" s="814" t="n"/>
+      <c r="J7" s="813" t="n"/>
+      <c r="K7" s="813" t="n"/>
+      <c r="L7" s="813" t="n"/>
+      <c r="M7" s="813" t="n"/>
+      <c r="N7" s="813" t="n"/>
+      <c r="O7" s="813" t="n"/>
+      <c r="P7" s="813" t="n"/>
+      <c r="Q7" s="813" t="n"/>
+      <c r="R7" s="813" t="n"/>
+      <c r="S7" s="813" t="n"/>
+      <c r="T7" s="813" t="n"/>
+      <c r="U7" s="813" t="n"/>
+      <c r="V7" s="813" t="n"/>
+      <c r="W7" s="813" t="n"/>
+      <c r="X7" s="813" t="n"/>
+      <c r="Y7" s="813" t="n"/>
+      <c r="Z7" s="813" t="n"/>
+      <c r="AA7" s="813" t="n"/>
+      <c r="AB7" s="813" t="n"/>
+      <c r="AC7" s="813" t="n"/>
+      <c r="AD7" s="813" t="n"/>
+      <c r="AE7" s="813" t="n"/>
+      <c r="AF7" s="813" t="n"/>
+      <c r="AG7" s="813" t="n"/>
+      <c r="AH7" s="813" t="n"/>
+      <c r="AI7" s="813" t="n"/>
+      <c r="AJ7" s="813" t="n"/>
+      <c r="AK7" s="813" t="n"/>
+      <c r="AL7" s="813" t="n"/>
+      <c r="AM7" s="813" t="n"/>
+      <c r="AN7" s="813" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="756" t="inlineStr">
@@ -11880,14 +12130,14 @@
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="710" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
-      <c r="I13" s="10" t="n"/>
+      <c r="B13" s="654" t="n"/>
+      <c r="C13" s="654" t="n"/>
+      <c r="D13" s="654" t="n"/>
+      <c r="E13" s="654" t="n"/>
+      <c r="F13" s="654" t="n"/>
+      <c r="G13" s="654" t="n"/>
+      <c r="H13" s="654" t="n"/>
+      <c r="I13" s="654" t="n"/>
       <c r="J13" s="654" t="n"/>
       <c r="K13" s="654" t="n"/>
       <c r="L13" s="654" t="n"/>
@@ -12583,50 +12833,50 @@
       <c r="AN27" s="709" t="n"/>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="765" t="inlineStr">
+      <c r="A28" s="370" t="inlineStr">
         <is>
           <t>NOTICE  —  One line per material, capacity, quality or customer-risk condition.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B28" s="766" t="n"/>
-      <c r="C28" s="766" t="n"/>
-      <c r="D28" s="766" t="n"/>
-      <c r="E28" s="766" t="n"/>
-      <c r="F28" s="766" t="n"/>
-      <c r="G28" s="766" t="n"/>
-      <c r="H28" s="766" t="n"/>
-      <c r="I28" s="766" t="n"/>
-      <c r="J28" s="766" t="n"/>
-      <c r="K28" s="766" t="n"/>
-      <c r="L28" s="766" t="n"/>
-      <c r="M28" s="766" t="n"/>
-      <c r="N28" s="766" t="n"/>
-      <c r="O28" s="766" t="n"/>
-      <c r="P28" s="766" t="n"/>
-      <c r="Q28" s="766" t="n"/>
-      <c r="R28" s="766" t="n"/>
-      <c r="S28" s="766" t="n"/>
-      <c r="T28" s="766" t="n"/>
-      <c r="U28" s="766" t="n"/>
-      <c r="V28" s="766" t="n"/>
-      <c r="W28" s="766" t="n"/>
-      <c r="X28" s="766" t="n"/>
-      <c r="Y28" s="766" t="n"/>
-      <c r="Z28" s="766" t="n"/>
-      <c r="AA28" s="766" t="n"/>
-      <c r="AB28" s="766" t="n"/>
-      <c r="AC28" s="766" t="n"/>
-      <c r="AD28" s="766" t="n"/>
-      <c r="AE28" s="766" t="n"/>
-      <c r="AF28" s="766" t="n"/>
-      <c r="AG28" s="766" t="n"/>
-      <c r="AH28" s="766" t="n"/>
-      <c r="AI28" s="766" t="n"/>
-      <c r="AJ28" s="766" t="n"/>
-      <c r="AK28" s="766" t="n"/>
-      <c r="AL28" s="766" t="n"/>
-      <c r="AM28" s="766" t="n"/>
-      <c r="AN28" s="767" t="n"/>
+      <c r="B28" s="371" t="n"/>
+      <c r="C28" s="371" t="n"/>
+      <c r="D28" s="371" t="n"/>
+      <c r="E28" s="371" t="n"/>
+      <c r="F28" s="371" t="n"/>
+      <c r="G28" s="371" t="n"/>
+      <c r="H28" s="371" t="n"/>
+      <c r="I28" s="371" t="n"/>
+      <c r="J28" s="371" t="n"/>
+      <c r="K28" s="371" t="n"/>
+      <c r="L28" s="371" t="n"/>
+      <c r="M28" s="371" t="n"/>
+      <c r="N28" s="371" t="n"/>
+      <c r="O28" s="371" t="n"/>
+      <c r="P28" s="371" t="n"/>
+      <c r="Q28" s="371" t="n"/>
+      <c r="R28" s="371" t="n"/>
+      <c r="S28" s="371" t="n"/>
+      <c r="T28" s="371" t="n"/>
+      <c r="U28" s="371" t="n"/>
+      <c r="V28" s="371" t="n"/>
+      <c r="W28" s="371" t="n"/>
+      <c r="X28" s="371" t="n"/>
+      <c r="Y28" s="371" t="n"/>
+      <c r="Z28" s="371" t="n"/>
+      <c r="AA28" s="371" t="n"/>
+      <c r="AB28" s="371" t="n"/>
+      <c r="AC28" s="371" t="n"/>
+      <c r="AD28" s="371" t="n"/>
+      <c r="AE28" s="371" t="n"/>
+      <c r="AF28" s="371" t="n"/>
+      <c r="AG28" s="371" t="n"/>
+      <c r="AH28" s="371" t="n"/>
+      <c r="AI28" s="371" t="n"/>
+      <c r="AJ28" s="371" t="n"/>
+      <c r="AK28" s="371" t="n"/>
+      <c r="AL28" s="371" t="n"/>
+      <c r="AM28" s="371" t="n"/>
+      <c r="AN28" s="372" t="n"/>
     </row>
     <row r="29" hidden="1" outlineLevel="1"/>
     <row r="30" hidden="1" outlineLevel="1"/>

--- a/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
@@ -4,8 +4,10 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM-209_GATE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RISKS_ACTIONS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RISKS_ACTIONS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_RESULT_CORE">'_LISTS'!$A$2:$A$5</definedName>
@@ -18,8 +20,9 @@
     <definedName name="REF_OWNER_PERSON_MASTER">'_IMPORT'!$D$2:$D$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'FRM-209_GATE'!$1:$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'FRM-209_GATE'!$A$1:$AN$47</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'RISKS_ACTIONS'!$1:$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'RISKS_ACTIONS'!$A$1:$I$28</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'RISKS_ACTIONS'!$1:$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'RISKS_ACTIONS'!$A$1:$I$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'REF_LINKS'!$A$1:$G$11</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -30,7 +33,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="92">
+  <fonts count="82">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -496,59 +499,8 @@
       <color rgb="00163A70"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color theme="1"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="000C2D48"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="000C2D48"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="001565C0"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="007A8FA6"/>
-      <sz val="7"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="00BBCCCC"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="001B3A6B"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="007B4F00"/>
-      <sz val="7"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-    </font>
   </fonts>
-  <fills count="58">
+  <fills count="52">
     <fill>
       <patternFill/>
     </fill>
@@ -805,38 +757,8 @@
         <fgColor rgb="00F7F9FC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002C9CD7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E4F0F9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001565C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F0F7FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000C2D48"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF8E1"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="397">
+  <borders count="290">
     <border>
       <left/>
       <right/>
@@ -3976,1177 +3898,11 @@
         <color rgb="000078D4"/>
       </bottom>
     </border>
-    <border/>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C5D9E8"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C5D9E8"/>
-      </left>
-      <right style="medium">
-        <color rgb="002C9CD7"/>
-      </right>
-      <top style="medium">
-        <color rgb="002C9CD7"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002C9CD7"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00C5D9E8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00E2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="000078D4"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00E2E8F0"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00E2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E2E8F0"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="000078D4"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E2E8F0"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00E2E8F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000078D4"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00E2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E2E8F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000078D4"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="000078D4"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E2E8F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000078D4"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00E2E8F0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00E2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E2E8F0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00E2E8F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000078D4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00E2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E2E8F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000078D4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="000078D4"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E2E8F0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="000078D4"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E2E8F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000078D4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00F9A825"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="00F9A825"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00F9A825"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00F9A825"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00F9A825"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00F9A825"/>
-      </right>
-      <top style="thin">
-        <color rgb="00F9A825"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00F9A825"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00F9A825"/>
-      </left>
-      <right style="thin">
-        <color rgb="00F9A825"/>
-      </right>
-      <top style="thin">
-        <color rgb="00F9A825"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00F9A825"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00F9A825"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00F9A825"/>
-      </right>
-      <top style="thin">
-        <color rgb="00F9A825"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00F9A825"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00F9A825"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00F9A825"/>
-      </right>
-      <top style="thin">
-        <color rgb="00F9A825"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00F9A825"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C5D9E8"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="002C9CD7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="000078D4"/>
-      </left>
-      <right style="thin">
-        <color rgb="000078D4"/>
-      </right>
-      <top style="thin">
-        <color rgb="000078D4"/>
-      </top>
-      <bottom/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="846">
+  <cellXfs count="394">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6074,1150 +4830,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="4" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="294" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="295" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="296" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="300" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="47" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="6" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="8" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="301" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="7" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="302" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="48" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="50" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="51" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="311" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="307" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="312" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="309" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="310" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="313" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="306" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="308" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="311" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="307" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="312" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="309" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="310" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="313" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="306" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="308" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="4" borderId="314" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="315" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="316" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="84" fillId="4" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="4" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="4" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="53" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="53" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="53" borderId="317" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="320" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="84" fillId="4" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="4" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="53" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="53" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="53" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="4" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="4" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="323" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="324" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="325" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="4" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="4" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="4" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="53" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="53" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="53" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="52" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="54" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="54" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="54" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="335" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="337" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="339" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="327" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="330" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="56" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="56" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="56" borderId="340" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="56" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="47" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="55" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="47" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="8" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="55" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="47" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="8" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="55" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="4" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="4" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="338" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="326" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="329" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="334" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="52" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="337" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="339" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="55" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="55" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="55" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="4" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="4" borderId="316" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="80" fillId="4" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="4" borderId="320" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="4" borderId="325" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="51" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="51" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="51" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="51" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="89" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="373" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="374" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="375" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="376" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="86" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="288" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="377" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="378" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="377" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="379" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="47" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="47" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="47" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="4" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="376" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="4" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="377" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="377" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="379" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="345" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="4" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="380" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="381" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="384" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="382" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="383" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="385" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="47" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="57" borderId="386" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="57" borderId="387" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="57" borderId="388" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="57" borderId="389" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="392" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="393" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="91" fillId="4" borderId="314" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="315" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="316" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="317" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="320" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="85" fillId="53" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="302" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="323" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="324" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="325" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="53" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="394" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="52" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="91" fillId="4" borderId="347" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="348" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="368" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="91" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="91" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="91" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="91" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="4" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="91" fillId="4" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="4" borderId="396" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7319,9 +4931,44 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
+      <colOff>161925</colOff>
+      <row>0</row>
+      <rowOff>314325</rowOff>
+    </from>
+    <ext cx="1123950" cy="323850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="/xl/media/image1.png"/>
+        <cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>161925</colOff>
+      <row>0</row>
+      <rowOff>314325</rowOff>
     </from>
     <ext cx="1123950" cy="323850"/>
     <pic>
@@ -7337,36 +4984,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7379,9 +4999,9 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
+      <colOff>161925</colOff>
+      <row>0</row>
+      <rowOff>314325</rowOff>
     </from>
     <ext cx="1123950" cy="323850"/>
     <pic>
@@ -7419,6 +5039,22 @@
     <tableColumn id="9" name="Evidence Ref"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="REF_LINKS" displayName="REF_LINKS" ref="A3:G11" headerRowCount="1">
+  <autoFilter ref="A3:G11"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Ref Type"/>
+    <tableColumn id="2" name="Document / Record"/>
+    <tableColumn id="3" name="System of Record"/>
+    <tableColumn id="4" name="Unique Ref"/>
+    <tableColumn id="5" name="Owner"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="Note"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
@@ -7603,59 +5239,59 @@
   <dimension ref="A1:AN47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2.33" customWidth="1" min="1" max="1"/>
-    <col width="2.33" customWidth="1" min="2" max="2"/>
-    <col width="2.33" customWidth="1" min="3" max="3"/>
-    <col width="2.33" customWidth="1" min="4" max="4"/>
-    <col width="2.33" customWidth="1" min="5" max="5"/>
-    <col width="2.33" customWidth="1" min="6" max="6"/>
-    <col width="2.33" customWidth="1" min="7" max="7"/>
-    <col width="2.33" customWidth="1" min="8" max="8"/>
-    <col width="2.33" customWidth="1" min="9" max="9"/>
-    <col width="2.33" customWidth="1" min="10" max="10"/>
-    <col width="2.33" customWidth="1" min="11" max="11"/>
-    <col width="2.33" customWidth="1" min="12" max="12"/>
-    <col width="2.33" customWidth="1" min="13" max="13"/>
-    <col width="2.33" customWidth="1" min="14" max="14"/>
-    <col width="2.33" customWidth="1" min="15" max="15"/>
-    <col width="2.33" customWidth="1" min="16" max="16"/>
-    <col width="2.33" customWidth="1" min="17" max="17"/>
-    <col width="2.33" customWidth="1" min="18" max="18"/>
-    <col width="2.33" customWidth="1" min="19" max="19"/>
-    <col width="2.33" customWidth="1" min="20" max="20"/>
-    <col width="2.33" customWidth="1" min="21" max="21"/>
-    <col width="2.33" customWidth="1" min="22" max="22"/>
-    <col width="2.33" customWidth="1" min="23" max="23"/>
-    <col width="2.33" customWidth="1" min="24" max="24"/>
-    <col width="2.33" customWidth="1" min="25" max="25"/>
-    <col width="2.33" customWidth="1" min="26" max="26"/>
-    <col width="2.33" customWidth="1" min="27" max="27"/>
-    <col width="2.33" customWidth="1" min="28" max="28"/>
-    <col width="2.33" customWidth="1" min="29" max="29"/>
-    <col width="2.33" customWidth="1" min="30" max="30"/>
-    <col width="2.33" customWidth="1" min="31" max="31"/>
-    <col width="2.33" customWidth="1" min="32" max="32"/>
-    <col width="2.33" customWidth="1" min="33" max="33"/>
-    <col width="2.33" customWidth="1" min="34" max="34"/>
-    <col width="2.33" customWidth="1" min="35" max="35"/>
-    <col width="2.33" customWidth="1" min="36" max="36"/>
-    <col width="2.33" customWidth="1" min="37" max="37"/>
-    <col width="2.33" customWidth="1" min="38" max="38"/>
-    <col width="2.33" customWidth="1" min="39" max="39"/>
-    <col width="2.33" customWidth="1" min="40" max="40"/>
+    <col width="2.329999923706055" customWidth="1" min="1" max="1"/>
+    <col width="2.329999923706055" customWidth="1" min="2" max="2"/>
+    <col width="2.329999923706055" customWidth="1" min="3" max="3"/>
+    <col width="2.329999923706055" customWidth="1" min="4" max="4"/>
+    <col width="2.329999923706055" customWidth="1" min="5" max="5"/>
+    <col width="2.329999923706055" customWidth="1" min="6" max="6"/>
+    <col width="2.329999923706055" customWidth="1" min="7" max="7"/>
+    <col width="2.329999923706055" customWidth="1" min="8" max="8"/>
+    <col width="2.329999923706055" customWidth="1" min="9" max="9"/>
+    <col width="2.329999923706055" customWidth="1" min="10" max="10"/>
+    <col width="2.329999923706055" customWidth="1" min="11" max="11"/>
+    <col width="2.329999923706055" customWidth="1" min="12" max="12"/>
+    <col width="2.329999923706055" customWidth="1" min="13" max="13"/>
+    <col width="2.329999923706055" customWidth="1" min="14" max="14"/>
+    <col width="2.329999923706055" customWidth="1" min="15" max="15"/>
+    <col width="2.329999923706055" customWidth="1" min="16" max="16"/>
+    <col width="2.329999923706055" customWidth="1" min="17" max="17"/>
+    <col width="2.329999923706055" customWidth="1" min="18" max="18"/>
+    <col width="2.329999923706055" customWidth="1" min="19" max="19"/>
+    <col width="2.329999923706055" customWidth="1" min="20" max="20"/>
+    <col width="2.329999923706055" customWidth="1" min="21" max="21"/>
+    <col width="2.329999923706055" customWidth="1" min="22" max="22"/>
+    <col width="2.329999923706055" customWidth="1" min="23" max="23"/>
+    <col width="2.329999923706055" customWidth="1" min="24" max="24"/>
+    <col width="2.329999923706055" customWidth="1" min="25" max="25"/>
+    <col width="2.329999923706055" customWidth="1" min="26" max="26"/>
+    <col width="2.329999923706055" customWidth="1" min="27" max="27"/>
+    <col width="2.329999923706055" customWidth="1" min="28" max="28"/>
+    <col width="2.329999923706055" customWidth="1" min="29" max="29"/>
+    <col width="2.329999923706055" customWidth="1" min="30" max="30"/>
+    <col width="2.329999923706055" customWidth="1" min="31" max="31"/>
+    <col width="2.329999923706055" customWidth="1" min="32" max="32"/>
+    <col width="2.329999923706055" customWidth="1" min="33" max="33"/>
+    <col width="2.329999923706055" customWidth="1" min="34" max="34"/>
+    <col width="2.329999923706055" customWidth="1" min="35" max="35"/>
+    <col width="2.329999923706055" customWidth="1" min="36" max="36"/>
+    <col width="2.329999923706055" customWidth="1" min="37" max="37"/>
+    <col width="2.329999923706055" customWidth="1" min="38" max="38"/>
+    <col width="2.329999923706055" customWidth="1" min="39" max="39"/>
+    <col width="2.329999923706055" customWidth="1" min="40" max="40"/>
     <col hidden="1" outlineLevel="1" width="13" customWidth="1" min="41" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" hidden="1">
-      <c r="A1" s="719" t="inlineStr"/>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="267" t="inlineStr"/>
       <c r="B1" s="268" t="n"/>
       <c r="C1" s="268" t="n"/>
       <c r="D1" s="268" t="n"/>
       <c r="E1" s="268" t="n"/>
       <c r="F1" s="268" t="n"/>
       <c r="G1" s="268" t="n"/>
-      <c r="H1" s="319" t="n"/>
-      <c r="I1" s="845" t="inlineStr">
+      <c r="H1" s="268" t="n"/>
+      <c r="I1" s="332" t="inlineStr">
         <is>
           <t>HIGH-RISK JOB READINESS REVIEW</t>
         </is>
@@ -7680,320 +5316,222 @@
       <c r="AA1" s="268" t="n"/>
       <c r="AB1" s="268" t="n"/>
       <c r="AC1" s="268" t="n"/>
-      <c r="AD1" s="319" t="n"/>
-      <c r="AE1" s="720" t="inlineStr">
+      <c r="AD1" s="268" t="n"/>
+      <c r="AE1" s="270" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="268" t="n"/>
-      <c r="AG1" s="268" t="n"/>
-      <c r="AH1" s="721" t="n"/>
-      <c r="AI1" s="678" t="inlineStr">
+      <c r="AF1" s="271" t="n"/>
+      <c r="AG1" s="271" t="n"/>
+      <c r="AH1" s="272" t="n"/>
+      <c r="AI1" s="273" t="inlineStr">
         <is>
           <t>FRM-209</t>
         </is>
       </c>
-      <c r="AJ1" s="268" t="n"/>
-      <c r="AK1" s="268" t="n"/>
-      <c r="AL1" s="268" t="n"/>
-      <c r="AM1" s="268" t="n"/>
-      <c r="AN1" s="319" t="n"/>
+      <c r="AJ1" s="271" t="n"/>
+      <c r="AK1" s="271" t="n"/>
+      <c r="AL1" s="271" t="n"/>
+      <c r="AM1" s="271" t="n"/>
+      <c r="AN1" s="274" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="791" t="n"/>
-      <c r="C2" s="791" t="n"/>
-      <c r="D2" s="791" t="n"/>
-      <c r="E2" s="791" t="n"/>
-      <c r="F2" s="791" t="n"/>
-      <c r="G2" s="791" t="n"/>
-      <c r="H2" s="792" t="n"/>
-      <c r="I2" s="791" t="n"/>
-      <c r="J2" s="791" t="n"/>
-      <c r="K2" s="791" t="n"/>
-      <c r="L2" s="791" t="n"/>
-      <c r="M2" s="791" t="n"/>
-      <c r="N2" s="791" t="n"/>
-      <c r="O2" s="791" t="n"/>
-      <c r="P2" s="791" t="n"/>
-      <c r="Q2" s="791" t="n"/>
-      <c r="R2" s="791" t="n"/>
-      <c r="S2" s="791" t="n"/>
-      <c r="T2" s="791" t="n"/>
-      <c r="U2" s="791" t="n"/>
-      <c r="V2" s="791" t="n"/>
-      <c r="W2" s="791" t="n"/>
-      <c r="X2" s="791" t="n"/>
-      <c r="Y2" s="791" t="n"/>
-      <c r="Z2" s="791" t="n"/>
-      <c r="AA2" s="791" t="n"/>
-      <c r="AB2" s="791" t="n"/>
-      <c r="AC2" s="791" t="n"/>
-      <c r="AD2" s="792" t="n"/>
-      <c r="AE2" s="793" t="inlineStr">
+      <c r="A2" s="275" t="n"/>
+      <c r="I2" s="275" t="n"/>
+      <c r="AE2" s="276" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="794" t="n"/>
-      <c r="AG2" s="794" t="n"/>
-      <c r="AH2" s="795" t="n"/>
-      <c r="AI2" s="796" t="inlineStr">
+      <c r="AF2" s="277" t="n"/>
+      <c r="AG2" s="277" t="n"/>
+      <c r="AH2" s="278" t="n"/>
+      <c r="AI2" s="279" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="797" t="n"/>
-      <c r="AK2" s="797" t="n"/>
-      <c r="AL2" s="797" t="n"/>
-      <c r="AM2" s="797" t="n"/>
-      <c r="AN2" s="798" t="n"/>
+      <c r="AJ2" s="277" t="n"/>
+      <c r="AK2" s="277" t="n"/>
+      <c r="AL2" s="277" t="n"/>
+      <c r="AM2" s="277" t="n"/>
+      <c r="AN2" s="280" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="799" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="800" t="n"/>
-      <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
-      <c r="K3" s="25" t="n"/>
-      <c r="L3" s="25" t="n"/>
-      <c r="M3" s="25" t="n"/>
-      <c r="N3" s="25" t="n"/>
-      <c r="O3" s="25" t="n"/>
-      <c r="P3" s="25" t="n"/>
-      <c r="Q3" s="25" t="n"/>
-      <c r="R3" s="25" t="n"/>
-      <c r="S3" s="25" t="n"/>
-      <c r="T3" s="25" t="n"/>
-      <c r="U3" s="25" t="n"/>
-      <c r="V3" s="25" t="n"/>
-      <c r="W3" s="25" t="n"/>
-      <c r="X3" s="25" t="n"/>
-      <c r="Y3" s="25" t="n"/>
-      <c r="Z3" s="25" t="n"/>
-      <c r="AA3" s="25" t="n"/>
-      <c r="AB3" s="25" t="n"/>
-      <c r="AC3" s="25" t="n"/>
-      <c r="AD3" s="800" t="n"/>
-      <c r="AE3" s="801" t="inlineStr">
+      <c r="A3" s="275" t="n"/>
+      <c r="I3" s="281" t="n"/>
+      <c r="J3" s="277" t="n"/>
+      <c r="K3" s="277" t="n"/>
+      <c r="L3" s="277" t="n"/>
+      <c r="M3" s="277" t="n"/>
+      <c r="N3" s="277" t="n"/>
+      <c r="O3" s="277" t="n"/>
+      <c r="P3" s="277" t="n"/>
+      <c r="Q3" s="277" t="n"/>
+      <c r="R3" s="277" t="n"/>
+      <c r="S3" s="277" t="n"/>
+      <c r="T3" s="277" t="n"/>
+      <c r="U3" s="277" t="n"/>
+      <c r="V3" s="277" t="n"/>
+      <c r="W3" s="277" t="n"/>
+      <c r="X3" s="277" t="n"/>
+      <c r="Y3" s="277" t="n"/>
+      <c r="Z3" s="277" t="n"/>
+      <c r="AA3" s="277" t="n"/>
+      <c r="AB3" s="277" t="n"/>
+      <c r="AC3" s="277" t="n"/>
+      <c r="AD3" s="277" t="n"/>
+      <c r="AE3" s="276" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="802" t="n"/>
-      <c r="AG3" s="802" t="n"/>
-      <c r="AH3" s="803" t="n"/>
-      <c r="AI3" s="699" t="inlineStr">
+      <c r="AF3" s="277" t="n"/>
+      <c r="AG3" s="277" t="n"/>
+      <c r="AH3" s="278" t="n"/>
+      <c r="AI3" s="279" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="804" t="n"/>
-      <c r="AK3" s="804" t="n"/>
-      <c r="AL3" s="804" t="n"/>
-      <c r="AM3" s="804" t="n"/>
-      <c r="AN3" s="805" t="n"/>
+      <c r="AJ3" s="277" t="n"/>
+      <c r="AK3" s="277" t="n"/>
+      <c r="AL3" s="277" t="n"/>
+      <c r="AM3" s="277" t="n"/>
+      <c r="AN3" s="280" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="799" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="800" t="n"/>
-      <c r="I4" s="342" t="inlineStr">
+      <c r="A4" s="275" t="n"/>
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="J4" s="25" t="n"/>
-      <c r="K4" s="25" t="n"/>
-      <c r="L4" s="25" t="n"/>
-      <c r="M4" s="25" t="n"/>
-      <c r="N4" s="25" t="n"/>
-      <c r="O4" s="25" t="n"/>
-      <c r="P4" s="25" t="n"/>
-      <c r="Q4" s="25" t="n"/>
-      <c r="R4" s="25" t="n"/>
-      <c r="S4" s="25" t="n"/>
-      <c r="T4" s="25" t="n"/>
-      <c r="U4" s="25" t="n"/>
-      <c r="V4" s="25" t="n"/>
-      <c r="W4" s="25" t="n"/>
-      <c r="X4" s="25" t="n"/>
-      <c r="Y4" s="25" t="n"/>
-      <c r="Z4" s="25" t="n"/>
-      <c r="AA4" s="25" t="n"/>
-      <c r="AB4" s="25" t="n"/>
-      <c r="AC4" s="25" t="n"/>
-      <c r="AD4" s="800" t="n"/>
-      <c r="AE4" s="801" t="inlineStr">
+      <c r="AE4" s="276" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="802" t="n"/>
-      <c r="AG4" s="802" t="n"/>
-      <c r="AH4" s="803" t="n"/>
-      <c r="AI4" s="699" t="inlineStr">
+      <c r="AF4" s="277" t="n"/>
+      <c r="AG4" s="277" t="n"/>
+      <c r="AH4" s="278" t="n"/>
+      <c r="AI4" s="279" t="inlineStr">
         <is>
           <t>Planning / QA / Engineering</t>
         </is>
       </c>
-      <c r="AJ4" s="804" t="n"/>
-      <c r="AK4" s="804" t="n"/>
-      <c r="AL4" s="804" t="n"/>
-      <c r="AM4" s="804" t="n"/>
-      <c r="AN4" s="805" t="n"/>
+      <c r="AJ4" s="277" t="n"/>
+      <c r="AK4" s="277" t="n"/>
+      <c r="AL4" s="277" t="n"/>
+      <c r="AM4" s="277" t="n"/>
+      <c r="AN4" s="280" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="799" t="n"/>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="25" t="n"/>
-      <c r="H5" s="800" t="n"/>
-      <c r="I5" s="581" t="inlineStr">
+      <c r="A5" s="282" t="n"/>
+      <c r="B5" s="283" t="n"/>
+      <c r="C5" s="283" t="n"/>
+      <c r="D5" s="283" t="n"/>
+      <c r="E5" s="283" t="n"/>
+      <c r="F5" s="283" t="n"/>
+      <c r="G5" s="283" t="n"/>
+      <c r="H5" s="283" t="n"/>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="25" t="n"/>
-      <c r="K5" s="25" t="n"/>
-      <c r="L5" s="25" t="n"/>
-      <c r="M5" s="25" t="n"/>
-      <c r="N5" s="25" t="n"/>
-      <c r="O5" s="25" t="n"/>
-      <c r="P5" s="25" t="n"/>
-      <c r="Q5" s="25" t="n"/>
-      <c r="R5" s="25" t="n"/>
-      <c r="S5" s="25" t="n"/>
-      <c r="T5" s="25" t="n"/>
-      <c r="U5" s="25" t="n"/>
-      <c r="V5" s="25" t="n"/>
-      <c r="W5" s="25" t="n"/>
-      <c r="X5" s="25" t="n"/>
-      <c r="Y5" s="25" t="n"/>
-      <c r="Z5" s="25" t="n"/>
-      <c r="AA5" s="25" t="n"/>
-      <c r="AB5" s="25" t="n"/>
-      <c r="AC5" s="25" t="n"/>
-      <c r="AD5" s="800" t="n"/>
-      <c r="AE5" s="801" t="inlineStr">
+      <c r="J5" s="283" t="n"/>
+      <c r="K5" s="283" t="n"/>
+      <c r="L5" s="283" t="n"/>
+      <c r="M5" s="283" t="n"/>
+      <c r="N5" s="283" t="n"/>
+      <c r="O5" s="283" t="n"/>
+      <c r="P5" s="283" t="n"/>
+      <c r="Q5" s="283" t="n"/>
+      <c r="R5" s="283" t="n"/>
+      <c r="S5" s="283" t="n"/>
+      <c r="T5" s="283" t="n"/>
+      <c r="U5" s="283" t="n"/>
+      <c r="V5" s="283" t="n"/>
+      <c r="W5" s="283" t="n"/>
+      <c r="X5" s="283" t="n"/>
+      <c r="Y5" s="283" t="n"/>
+      <c r="Z5" s="283" t="n"/>
+      <c r="AA5" s="283" t="n"/>
+      <c r="AB5" s="283" t="n"/>
+      <c r="AC5" s="283" t="n"/>
+      <c r="AD5" s="283" t="n"/>
+      <c r="AE5" s="284" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="802" t="n"/>
-      <c r="AG5" s="802" t="n"/>
-      <c r="AH5" s="803" t="n"/>
-      <c r="AI5" s="699" t="inlineStr">
+      <c r="AF5" s="283" t="n"/>
+      <c r="AG5" s="283" t="n"/>
+      <c r="AH5" s="285" t="n"/>
+      <c r="AI5" s="286" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="804" t="n"/>
-      <c r="AK5" s="804" t="n"/>
-      <c r="AL5" s="804" t="n"/>
-      <c r="AM5" s="804" t="n"/>
-      <c r="AN5" s="805" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="806" t="n"/>
-      <c r="B6" s="807" t="n"/>
-      <c r="C6" s="807" t="n"/>
-      <c r="D6" s="807" t="n"/>
-      <c r="E6" s="807" t="n"/>
-      <c r="F6" s="807" t="n"/>
-      <c r="G6" s="807" t="n"/>
-      <c r="H6" s="808" t="n"/>
-      <c r="I6" s="807" t="n"/>
-      <c r="J6" s="807" t="n"/>
-      <c r="K6" s="807" t="n"/>
-      <c r="L6" s="807" t="n"/>
-      <c r="M6" s="807" t="n"/>
-      <c r="N6" s="807" t="n"/>
-      <c r="O6" s="807" t="n"/>
-      <c r="P6" s="807" t="n"/>
-      <c r="Q6" s="807" t="n"/>
-      <c r="R6" s="807" t="n"/>
-      <c r="S6" s="807" t="n"/>
-      <c r="T6" s="807" t="n"/>
-      <c r="U6" s="807" t="n"/>
-      <c r="V6" s="807" t="n"/>
-      <c r="W6" s="807" t="n"/>
-      <c r="X6" s="807" t="n"/>
-      <c r="Y6" s="807" t="n"/>
-      <c r="Z6" s="807" t="n"/>
-      <c r="AA6" s="807" t="n"/>
-      <c r="AB6" s="807" t="n"/>
-      <c r="AC6" s="807" t="n"/>
-      <c r="AD6" s="808" t="n"/>
-      <c r="AE6" s="809" t="n"/>
-      <c r="AF6" s="809" t="n"/>
-      <c r="AG6" s="809" t="n"/>
-      <c r="AH6" s="810" t="n"/>
-      <c r="AI6" s="811" t="n"/>
-      <c r="AJ6" s="811" t="n"/>
-      <c r="AK6" s="811" t="n"/>
-      <c r="AL6" s="811" t="n"/>
-      <c r="AM6" s="811" t="n"/>
-      <c r="AN6" s="812" t="n"/>
-    </row>
-    <row r="7" ht="4" customHeight="1">
-      <c r="A7" s="813" t="n"/>
-      <c r="B7" s="814" t="n"/>
-      <c r="C7" s="814" t="n"/>
-      <c r="D7" s="814" t="n"/>
-      <c r="E7" s="814" t="n"/>
-      <c r="F7" s="814" t="n"/>
-      <c r="G7" s="814" t="n"/>
-      <c r="H7" s="814" t="n"/>
-      <c r="I7" s="814" t="n"/>
-      <c r="J7" s="814" t="n"/>
-      <c r="K7" s="814" t="n"/>
-      <c r="L7" s="814" t="n"/>
-      <c r="M7" s="814" t="n"/>
-      <c r="N7" s="814" t="n"/>
-      <c r="O7" s="814" t="n"/>
-      <c r="P7" s="814" t="n"/>
-      <c r="Q7" s="814" t="n"/>
-      <c r="R7" s="814" t="n"/>
-      <c r="S7" s="814" t="n"/>
-      <c r="T7" s="814" t="n"/>
-      <c r="U7" s="814" t="n"/>
-      <c r="V7" s="814" t="n"/>
-      <c r="W7" s="814" t="n"/>
-      <c r="X7" s="814" t="n"/>
-      <c r="Y7" s="814" t="n"/>
-      <c r="Z7" s="814" t="n"/>
-      <c r="AA7" s="814" t="n"/>
-      <c r="AB7" s="814" t="n"/>
-      <c r="AC7" s="814" t="n"/>
-      <c r="AD7" s="814" t="n"/>
-      <c r="AE7" s="814" t="n"/>
-      <c r="AF7" s="814" t="n"/>
-      <c r="AG7" s="814" t="n"/>
-      <c r="AH7" s="814" t="n"/>
-      <c r="AI7" s="814" t="n"/>
-      <c r="AJ7" s="814" t="n"/>
-      <c r="AK7" s="814" t="n"/>
-      <c r="AL7" s="814" t="n"/>
-      <c r="AM7" s="814" t="n"/>
-      <c r="AN7" s="814" t="n"/>
+      <c r="AJ5" s="283" t="n"/>
+      <c r="AK5" s="283" t="n"/>
+      <c r="AL5" s="283" t="n"/>
+      <c r="AM5" s="283" t="n"/>
+      <c r="AN5" s="287" t="n"/>
+    </row>
+    <row r="6" ht="4" customHeight="1">
+      <c r="A6" s="25" t="inlineStr"/>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="288" t="inlineStr">
+        <is>
+          <t>1.  HIGH-RISK JOB HEADER / REFERENCE INFORMATION</t>
+        </is>
+      </c>
+      <c r="B7" s="289" t="n"/>
+      <c r="C7" s="289" t="n"/>
+      <c r="D7" s="289" t="n"/>
+      <c r="E7" s="289" t="n"/>
+      <c r="F7" s="289" t="n"/>
+      <c r="G7" s="289" t="n"/>
+      <c r="H7" s="289" t="n"/>
+      <c r="I7" s="289" t="n"/>
+      <c r="J7" s="289" t="n"/>
+      <c r="K7" s="289" t="n"/>
+      <c r="L7" s="289" t="n"/>
+      <c r="M7" s="289" t="n"/>
+      <c r="N7" s="289" t="n"/>
+      <c r="O7" s="289" t="n"/>
+      <c r="P7" s="289" t="n"/>
+      <c r="Q7" s="289" t="n"/>
+      <c r="R7" s="289" t="n"/>
+      <c r="S7" s="289" t="n"/>
+      <c r="T7" s="289" t="n"/>
+      <c r="U7" s="289" t="n"/>
+      <c r="V7" s="289" t="n"/>
+      <c r="W7" s="289" t="n"/>
+      <c r="X7" s="289" t="n"/>
+      <c r="Y7" s="289" t="n"/>
+      <c r="Z7" s="289" t="n"/>
+      <c r="AA7" s="289" t="n"/>
+      <c r="AB7" s="289" t="n"/>
+      <c r="AC7" s="289" t="n"/>
+      <c r="AD7" s="289" t="n"/>
+      <c r="AE7" s="289" t="n"/>
+      <c r="AF7" s="289" t="n"/>
+      <c r="AG7" s="289" t="n"/>
+      <c r="AH7" s="289" t="n"/>
+      <c r="AI7" s="289" t="n"/>
+      <c r="AJ7" s="289" t="n"/>
+      <c r="AK7" s="289" t="n"/>
+      <c r="AL7" s="289" t="n"/>
+      <c r="AM7" s="289" t="n"/>
+      <c r="AN7" s="290" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="731" t="inlineStr">
+      <c r="A8" s="291" t="inlineStr">
         <is>
           <t>Readiness Review ID</t>
         </is>
@@ -8017,7 +5555,7 @@
       <c r="R8" s="271" t="n"/>
       <c r="S8" s="271" t="n"/>
       <c r="T8" s="272" t="n"/>
-      <c r="U8" s="732" t="inlineStr">
+      <c r="U8" s="293" t="inlineStr">
         <is>
           <t>Job / WO</t>
         </is>
@@ -8043,7 +5581,7 @@
       <c r="AN8" s="274" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="733" t="inlineStr">
+      <c r="A9" s="295" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
@@ -8067,7 +5605,7 @@
       <c r="R9" s="277" t="n"/>
       <c r="S9" s="277" t="n"/>
       <c r="T9" s="278" t="n"/>
-      <c r="U9" s="734" t="inlineStr">
+      <c r="U9" s="297" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
@@ -8092,8 +5630,8 @@
       <c r="AM9" s="277" t="n"/>
       <c r="AN9" s="280" t="n"/>
     </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="733" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="295" t="inlineStr">
         <is>
           <t>Due Date / Commit</t>
         </is>
@@ -8117,7 +5655,7 @@
       <c r="R10" s="277" t="n"/>
       <c r="S10" s="277" t="n"/>
       <c r="T10" s="278" t="n"/>
-      <c r="U10" s="734" t="inlineStr">
+      <c r="U10" s="297" t="inlineStr">
         <is>
           <t>Current Route Step</t>
         </is>
@@ -8143,7 +5681,7 @@
       <c r="AN10" s="280" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="733" t="inlineStr">
+      <c r="A11" s="295" t="inlineStr">
         <is>
           <t>Top Risk Class</t>
         </is>
@@ -8167,7 +5705,7 @@
       <c r="R11" s="277" t="n"/>
       <c r="S11" s="277" t="n"/>
       <c r="T11" s="278" t="n"/>
-      <c r="U11" s="734" t="inlineStr">
+      <c r="U11" s="297" t="inlineStr">
         <is>
           <t>Commercial / Ops Owner</t>
         </is>
@@ -8193,7 +5731,7 @@
       <c r="AN11" s="280" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="735" t="inlineStr">
+      <c r="A12" s="298" t="inlineStr">
         <is>
           <t>Evidence Folder</t>
         </is>
@@ -8217,7 +5755,7 @@
       <c r="R12" s="283" t="n"/>
       <c r="S12" s="283" t="n"/>
       <c r="T12" s="285" t="n"/>
-      <c r="U12" s="736" t="inlineStr">
+      <c r="U12" s="300" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
@@ -8242,50 +5780,11 @@
       <c r="AM12" s="283" t="n"/>
       <c r="AN12" s="287" t="n"/>
     </row>
-    <row r="13" ht="3" customHeight="1">
-      <c r="A13" s="654" t="n"/>
-      <c r="B13" s="654" t="n"/>
-      <c r="C13" s="654" t="n"/>
-      <c r="D13" s="654" t="n"/>
-      <c r="E13" s="654" t="n"/>
-      <c r="F13" s="654" t="n"/>
-      <c r="G13" s="654" t="n"/>
-      <c r="H13" s="654" t="n"/>
-      <c r="I13" s="654" t="n"/>
-      <c r="J13" s="654" t="n"/>
-      <c r="K13" s="654" t="n"/>
-      <c r="L13" s="654" t="n"/>
-      <c r="M13" s="654" t="n"/>
-      <c r="N13" s="654" t="n"/>
-      <c r="O13" s="654" t="n"/>
-      <c r="P13" s="654" t="n"/>
-      <c r="Q13" s="654" t="n"/>
-      <c r="R13" s="654" t="n"/>
-      <c r="S13" s="654" t="n"/>
-      <c r="T13" s="654" t="n"/>
-      <c r="U13" s="654" t="n"/>
-      <c r="V13" s="654" t="n"/>
-      <c r="W13" s="654" t="n"/>
-      <c r="X13" s="654" t="n"/>
-      <c r="Y13" s="654" t="n"/>
-      <c r="Z13" s="654" t="n"/>
-      <c r="AA13" s="654" t="n"/>
-      <c r="AB13" s="654" t="n"/>
-      <c r="AC13" s="654" t="n"/>
-      <c r="AD13" s="654" t="n"/>
-      <c r="AE13" s="654" t="n"/>
-      <c r="AF13" s="654" t="n"/>
-      <c r="AG13" s="654" t="n"/>
-      <c r="AH13" s="654" t="n"/>
-      <c r="AI13" s="654" t="n"/>
-      <c r="AJ13" s="654" t="n"/>
-      <c r="AK13" s="654" t="n"/>
-      <c r="AL13" s="654" t="n"/>
-      <c r="AM13" s="654" t="n"/>
-      <c r="AN13" s="654" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="730" t="inlineStr">
+    <row r="13" ht="4" customHeight="1">
+      <c r="A13" s="25" t="n"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="288" t="inlineStr">
         <is>
           <t>2.  READINESS DECISION / OPEN RISK CONDITIONS</t>
         </is>
@@ -8330,8 +5829,8 @@
       <c r="AM14" s="289" t="n"/>
       <c r="AN14" s="290" t="n"/>
     </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="731" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="291" t="inlineStr">
         <is>
           <t>Gate Name / Trigger</t>
         </is>
@@ -8359,7 +5858,7 @@
       <c r="R15" s="271" t="n"/>
       <c r="S15" s="271" t="n"/>
       <c r="T15" s="272" t="n"/>
-      <c r="U15" s="732" t="inlineStr">
+      <c r="U15" s="293" t="inlineStr">
         <is>
           <t>Gate Conclusion</t>
         </is>
@@ -8388,7 +5887,7 @@
       <c r="AN15" s="274" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="733" t="inlineStr">
+      <c r="A16" s="295" t="inlineStr">
         <is>
           <t>Open Risk / Hold Reason</t>
         </is>
@@ -8412,7 +5911,7 @@
       <c r="R16" s="277" t="n"/>
       <c r="S16" s="277" t="n"/>
       <c r="T16" s="278" t="n"/>
-      <c r="U16" s="734" t="inlineStr">
+      <c r="U16" s="297" t="inlineStr">
         <is>
           <t>Next Step</t>
         </is>
@@ -8438,7 +5937,7 @@
       <c r="AN16" s="280" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="733" t="inlineStr">
+      <c r="A17" s="295" t="inlineStr">
         <is>
           <t>Action Owner</t>
         </is>
@@ -8462,7 +5961,7 @@
       <c r="R17" s="277" t="n"/>
       <c r="S17" s="277" t="n"/>
       <c r="T17" s="278" t="n"/>
-      <c r="U17" s="734" t="inlineStr">
+      <c r="U17" s="297" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
@@ -8488,7 +5987,7 @@
       <c r="AN17" s="280" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="735" t="inlineStr">
+      <c r="A18" s="298" t="inlineStr">
         <is>
           <t>Escalation if Overdue</t>
         </is>
@@ -8512,7 +6011,7 @@
       <c r="R18" s="283" t="n"/>
       <c r="S18" s="283" t="n"/>
       <c r="T18" s="285" t="n"/>
-      <c r="U18" s="736" t="inlineStr">
+      <c r="U18" s="300" t="inlineStr">
         <is>
           <t>Gate Status</t>
         </is>
@@ -8540,50 +6039,11 @@
       <c r="AM18" s="283" t="n"/>
       <c r="AN18" s="287" t="n"/>
     </row>
-    <row r="19" ht="3" customHeight="1">
-      <c r="A19" s="654" t="n"/>
-      <c r="B19" s="654" t="n"/>
-      <c r="C19" s="654" t="n"/>
-      <c r="D19" s="654" t="n"/>
-      <c r="E19" s="654" t="n"/>
-      <c r="F19" s="654" t="n"/>
-      <c r="G19" s="654" t="n"/>
-      <c r="H19" s="654" t="n"/>
-      <c r="I19" s="654" t="n"/>
-      <c r="J19" s="654" t="n"/>
-      <c r="K19" s="654" t="n"/>
-      <c r="L19" s="654" t="n"/>
-      <c r="M19" s="654" t="n"/>
-      <c r="N19" s="654" t="n"/>
-      <c r="O19" s="654" t="n"/>
-      <c r="P19" s="654" t="n"/>
-      <c r="Q19" s="654" t="n"/>
-      <c r="R19" s="654" t="n"/>
-      <c r="S19" s="654" t="n"/>
-      <c r="T19" s="654" t="n"/>
-      <c r="U19" s="654" t="n"/>
-      <c r="V19" s="654" t="n"/>
-      <c r="W19" s="654" t="n"/>
-      <c r="X19" s="654" t="n"/>
-      <c r="Y19" s="654" t="n"/>
-      <c r="Z19" s="654" t="n"/>
-      <c r="AA19" s="654" t="n"/>
-      <c r="AB19" s="654" t="n"/>
-      <c r="AC19" s="654" t="n"/>
-      <c r="AD19" s="654" t="n"/>
-      <c r="AE19" s="654" t="n"/>
-      <c r="AF19" s="654" t="n"/>
-      <c r="AG19" s="654" t="n"/>
-      <c r="AH19" s="654" t="n"/>
-      <c r="AI19" s="654" t="n"/>
-      <c r="AJ19" s="654" t="n"/>
-      <c r="AK19" s="654" t="n"/>
-      <c r="AL19" s="654" t="n"/>
-      <c r="AM19" s="654" t="n"/>
-      <c r="AN19" s="654" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="730" t="inlineStr">
+    <row r="19" ht="4" customHeight="1">
+      <c r="A19" s="25" t="n"/>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="288" t="inlineStr">
         <is>
           <t>3.  READINESS CRITERIA / RISK CHECK</t>
         </is>
@@ -8628,7 +6088,7 @@
       <c r="AM20" s="289" t="n"/>
       <c r="AN20" s="290" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1">
+    <row r="21" ht="17" customHeight="1">
       <c r="A21" s="301" t="inlineStr">
         <is>
           <t>#</t>
@@ -8699,66 +6159,66 @@
       <c r="AN21" s="274" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="737" t="n">
+      <c r="A22" s="304" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="272" t="n"/>
-      <c r="C22" s="738" t="inlineStr">
+      <c r="B22" s="328" t="n"/>
+      <c r="C22" s="305" t="inlineStr">
         <is>
           <t>RSK</t>
         </is>
       </c>
-      <c r="D22" s="271" t="n"/>
-      <c r="E22" s="272" t="n"/>
-      <c r="F22" s="739" t="inlineStr">
+      <c r="D22" s="277" t="n"/>
+      <c r="E22" s="278" t="n"/>
+      <c r="F22" s="306" t="inlineStr">
         <is>
           <t>Released baseline package is locked.</t>
         </is>
       </c>
-      <c r="G22" s="271" t="n"/>
-      <c r="H22" s="271" t="n"/>
-      <c r="I22" s="271" t="n"/>
-      <c r="J22" s="271" t="n"/>
-      <c r="K22" s="271" t="n"/>
-      <c r="L22" s="271" t="n"/>
-      <c r="M22" s="271" t="n"/>
-      <c r="N22" s="271" t="n"/>
-      <c r="O22" s="271" t="n"/>
-      <c r="P22" s="271" t="n"/>
-      <c r="Q22" s="271" t="n"/>
-      <c r="R22" s="271" t="n"/>
-      <c r="S22" s="272" t="n"/>
-      <c r="T22" s="740" t="inlineStr">
+      <c r="G22" s="277" t="n"/>
+      <c r="H22" s="277" t="n"/>
+      <c r="I22" s="277" t="n"/>
+      <c r="J22" s="277" t="n"/>
+      <c r="K22" s="277" t="n"/>
+      <c r="L22" s="277" t="n"/>
+      <c r="M22" s="277" t="n"/>
+      <c r="N22" s="277" t="n"/>
+      <c r="O22" s="277" t="n"/>
+      <c r="P22" s="277" t="n"/>
+      <c r="Q22" s="277" t="n"/>
+      <c r="R22" s="277" t="n"/>
+      <c r="S22" s="278" t="n"/>
+      <c r="T22" s="307" t="inlineStr">
         <is>
           <t>FRM-306 or released package reference is current.</t>
         </is>
       </c>
-      <c r="U22" s="271" t="n"/>
-      <c r="V22" s="271" t="n"/>
-      <c r="W22" s="271" t="n"/>
-      <c r="X22" s="271" t="n"/>
-      <c r="Y22" s="271" t="n"/>
-      <c r="Z22" s="271" t="n"/>
-      <c r="AA22" s="271" t="n"/>
-      <c r="AB22" s="271" t="n"/>
-      <c r="AC22" s="271" t="n"/>
-      <c r="AD22" s="271" t="n"/>
-      <c r="AE22" s="272" t="n"/>
-      <c r="AF22" s="739" t="n"/>
-      <c r="AG22" s="271" t="n"/>
-      <c r="AH22" s="271" t="n"/>
-      <c r="AI22" s="272" t="n"/>
-      <c r="AJ22" s="739" t="n"/>
-      <c r="AK22" s="271" t="n"/>
-      <c r="AL22" s="272" t="n"/>
-      <c r="AM22" s="741" t="n"/>
-      <c r="AN22" s="274" t="n"/>
+      <c r="U22" s="277" t="n"/>
+      <c r="V22" s="277" t="n"/>
+      <c r="W22" s="277" t="n"/>
+      <c r="X22" s="277" t="n"/>
+      <c r="Y22" s="277" t="n"/>
+      <c r="Z22" s="277" t="n"/>
+      <c r="AA22" s="277" t="n"/>
+      <c r="AB22" s="277" t="n"/>
+      <c r="AC22" s="277" t="n"/>
+      <c r="AD22" s="277" t="n"/>
+      <c r="AE22" s="278" t="n"/>
+      <c r="AF22" s="308" t="n"/>
+      <c r="AG22" s="329" t="n"/>
+      <c r="AH22" s="329" t="n"/>
+      <c r="AI22" s="328" t="n"/>
+      <c r="AJ22" s="308" t="n"/>
+      <c r="AK22" s="329" t="n"/>
+      <c r="AL22" s="328" t="n"/>
+      <c r="AM22" s="308" t="n"/>
+      <c r="AN22" s="328" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="742" t="n">
+      <c r="A23" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="278" t="n"/>
+      <c r="B23" s="328" t="n"/>
       <c r="C23" s="305" t="inlineStr">
         <is>
           <t>RSK</t>
@@ -8800,21 +6260,21 @@
       <c r="AC23" s="277" t="n"/>
       <c r="AD23" s="277" t="n"/>
       <c r="AE23" s="278" t="n"/>
-      <c r="AF23" s="306" t="n"/>
-      <c r="AG23" s="277" t="n"/>
-      <c r="AH23" s="277" t="n"/>
-      <c r="AI23" s="278" t="n"/>
-      <c r="AJ23" s="306" t="n"/>
-      <c r="AK23" s="277" t="n"/>
-      <c r="AL23" s="278" t="n"/>
-      <c r="AM23" s="743" t="n"/>
-      <c r="AN23" s="280" t="n"/>
+      <c r="AF23" s="308" t="n"/>
+      <c r="AG23" s="329" t="n"/>
+      <c r="AH23" s="329" t="n"/>
+      <c r="AI23" s="328" t="n"/>
+      <c r="AJ23" s="308" t="n"/>
+      <c r="AK23" s="329" t="n"/>
+      <c r="AL23" s="328" t="n"/>
+      <c r="AM23" s="308" t="n"/>
+      <c r="AN23" s="328" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="742" t="n">
+      <c r="A24" s="304" t="n">
         <v>3</v>
       </c>
-      <c r="B24" s="278" t="n"/>
+      <c r="B24" s="328" t="n"/>
       <c r="C24" s="305" t="inlineStr">
         <is>
           <t>RSK</t>
@@ -8856,21 +6316,21 @@
       <c r="AC24" s="277" t="n"/>
       <c r="AD24" s="277" t="n"/>
       <c r="AE24" s="278" t="n"/>
-      <c r="AF24" s="306" t="n"/>
-      <c r="AG24" s="277" t="n"/>
-      <c r="AH24" s="277" t="n"/>
-      <c r="AI24" s="278" t="n"/>
-      <c r="AJ24" s="306" t="n"/>
-      <c r="AK24" s="277" t="n"/>
-      <c r="AL24" s="278" t="n"/>
-      <c r="AM24" s="743" t="n"/>
-      <c r="AN24" s="280" t="n"/>
+      <c r="AF24" s="308" t="n"/>
+      <c r="AG24" s="329" t="n"/>
+      <c r="AH24" s="329" t="n"/>
+      <c r="AI24" s="328" t="n"/>
+      <c r="AJ24" s="308" t="n"/>
+      <c r="AK24" s="329" t="n"/>
+      <c r="AL24" s="328" t="n"/>
+      <c r="AM24" s="308" t="n"/>
+      <c r="AN24" s="328" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="742" t="n">
+      <c r="A25" s="304" t="n">
         <v>4</v>
       </c>
-      <c r="B25" s="278" t="n"/>
+      <c r="B25" s="328" t="n"/>
       <c r="C25" s="305" t="inlineStr">
         <is>
           <t>RSK</t>
@@ -8912,21 +6372,21 @@
       <c r="AC25" s="277" t="n"/>
       <c r="AD25" s="277" t="n"/>
       <c r="AE25" s="278" t="n"/>
-      <c r="AF25" s="306" t="n"/>
-      <c r="AG25" s="277" t="n"/>
-      <c r="AH25" s="277" t="n"/>
-      <c r="AI25" s="278" t="n"/>
-      <c r="AJ25" s="306" t="n"/>
-      <c r="AK25" s="277" t="n"/>
-      <c r="AL25" s="278" t="n"/>
-      <c r="AM25" s="743" t="n"/>
-      <c r="AN25" s="280" t="n"/>
+      <c r="AF25" s="308" t="n"/>
+      <c r="AG25" s="329" t="n"/>
+      <c r="AH25" s="329" t="n"/>
+      <c r="AI25" s="328" t="n"/>
+      <c r="AJ25" s="308" t="n"/>
+      <c r="AK25" s="329" t="n"/>
+      <c r="AL25" s="328" t="n"/>
+      <c r="AM25" s="308" t="n"/>
+      <c r="AN25" s="328" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="742" t="n">
+      <c r="A26" s="304" t="n">
         <v>5</v>
       </c>
-      <c r="B26" s="278" t="n"/>
+      <c r="B26" s="328" t="n"/>
       <c r="C26" s="305" t="inlineStr">
         <is>
           <t>RSK</t>
@@ -8968,21 +6428,21 @@
       <c r="AC26" s="277" t="n"/>
       <c r="AD26" s="277" t="n"/>
       <c r="AE26" s="278" t="n"/>
-      <c r="AF26" s="306" t="n"/>
-      <c r="AG26" s="277" t="n"/>
-      <c r="AH26" s="277" t="n"/>
-      <c r="AI26" s="278" t="n"/>
-      <c r="AJ26" s="306" t="n"/>
-      <c r="AK26" s="277" t="n"/>
-      <c r="AL26" s="278" t="n"/>
-      <c r="AM26" s="743" t="n"/>
-      <c r="AN26" s="280" t="n"/>
+      <c r="AF26" s="308" t="n"/>
+      <c r="AG26" s="329" t="n"/>
+      <c r="AH26" s="329" t="n"/>
+      <c r="AI26" s="328" t="n"/>
+      <c r="AJ26" s="308" t="n"/>
+      <c r="AK26" s="329" t="n"/>
+      <c r="AL26" s="328" t="n"/>
+      <c r="AM26" s="308" t="n"/>
+      <c r="AN26" s="328" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="742" t="n">
+      <c r="A27" s="304" t="n">
         <v>6</v>
       </c>
-      <c r="B27" s="278" t="n"/>
+      <c r="B27" s="328" t="n"/>
       <c r="C27" s="305" t="inlineStr">
         <is>
           <t>RSK</t>
@@ -9024,21 +6484,21 @@
       <c r="AC27" s="277" t="n"/>
       <c r="AD27" s="277" t="n"/>
       <c r="AE27" s="278" t="n"/>
-      <c r="AF27" s="306" t="n"/>
-      <c r="AG27" s="277" t="n"/>
-      <c r="AH27" s="277" t="n"/>
-      <c r="AI27" s="278" t="n"/>
-      <c r="AJ27" s="306" t="n"/>
-      <c r="AK27" s="277" t="n"/>
-      <c r="AL27" s="278" t="n"/>
-      <c r="AM27" s="743" t="n"/>
-      <c r="AN27" s="280" t="n"/>
+      <c r="AF27" s="308" t="n"/>
+      <c r="AG27" s="329" t="n"/>
+      <c r="AH27" s="329" t="n"/>
+      <c r="AI27" s="328" t="n"/>
+      <c r="AJ27" s="308" t="n"/>
+      <c r="AK27" s="329" t="n"/>
+      <c r="AL27" s="328" t="n"/>
+      <c r="AM27" s="308" t="n"/>
+      <c r="AN27" s="328" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="742" t="n">
+      <c r="A28" s="304" t="n">
         <v>7</v>
       </c>
-      <c r="B28" s="278" t="n"/>
+      <c r="B28" s="328" t="n"/>
       <c r="C28" s="305" t="inlineStr">
         <is>
           <t>RSK</t>
@@ -9080,21 +6540,21 @@
       <c r="AC28" s="277" t="n"/>
       <c r="AD28" s="277" t="n"/>
       <c r="AE28" s="278" t="n"/>
-      <c r="AF28" s="306" t="n"/>
-      <c r="AG28" s="277" t="n"/>
-      <c r="AH28" s="277" t="n"/>
-      <c r="AI28" s="278" t="n"/>
-      <c r="AJ28" s="306" t="n"/>
-      <c r="AK28" s="277" t="n"/>
-      <c r="AL28" s="278" t="n"/>
-      <c r="AM28" s="743" t="n"/>
-      <c r="AN28" s="280" t="n"/>
+      <c r="AF28" s="308" t="n"/>
+      <c r="AG28" s="329" t="n"/>
+      <c r="AH28" s="329" t="n"/>
+      <c r="AI28" s="328" t="n"/>
+      <c r="AJ28" s="308" t="n"/>
+      <c r="AK28" s="329" t="n"/>
+      <c r="AL28" s="328" t="n"/>
+      <c r="AM28" s="308" t="n"/>
+      <c r="AN28" s="328" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="742" t="n">
+      <c r="A29" s="304" t="n">
         <v>8</v>
       </c>
-      <c r="B29" s="278" t="n"/>
+      <c r="B29" s="328" t="n"/>
       <c r="C29" s="305" t="inlineStr">
         <is>
           <t>RSK</t>
@@ -9136,21 +6596,21 @@
       <c r="AC29" s="277" t="n"/>
       <c r="AD29" s="277" t="n"/>
       <c r="AE29" s="278" t="n"/>
-      <c r="AF29" s="306" t="n"/>
-      <c r="AG29" s="277" t="n"/>
-      <c r="AH29" s="277" t="n"/>
-      <c r="AI29" s="278" t="n"/>
-      <c r="AJ29" s="306" t="n"/>
-      <c r="AK29" s="277" t="n"/>
-      <c r="AL29" s="278" t="n"/>
-      <c r="AM29" s="743" t="n"/>
-      <c r="AN29" s="280" t="n"/>
+      <c r="AF29" s="308" t="n"/>
+      <c r="AG29" s="329" t="n"/>
+      <c r="AH29" s="329" t="n"/>
+      <c r="AI29" s="328" t="n"/>
+      <c r="AJ29" s="308" t="n"/>
+      <c r="AK29" s="329" t="n"/>
+      <c r="AL29" s="328" t="n"/>
+      <c r="AM29" s="308" t="n"/>
+      <c r="AN29" s="328" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="742" t="n">
+      <c r="A30" s="304" t="n">
         <v>9</v>
       </c>
-      <c r="B30" s="278" t="n"/>
+      <c r="B30" s="328" t="n"/>
       <c r="C30" s="305" t="inlineStr">
         <is>
           <t>RSK</t>
@@ -9192,21 +6652,21 @@
       <c r="AC30" s="277" t="n"/>
       <c r="AD30" s="277" t="n"/>
       <c r="AE30" s="278" t="n"/>
-      <c r="AF30" s="306" t="n"/>
-      <c r="AG30" s="277" t="n"/>
-      <c r="AH30" s="277" t="n"/>
-      <c r="AI30" s="278" t="n"/>
-      <c r="AJ30" s="306" t="n"/>
-      <c r="AK30" s="277" t="n"/>
-      <c r="AL30" s="278" t="n"/>
-      <c r="AM30" s="743" t="n"/>
-      <c r="AN30" s="280" t="n"/>
+      <c r="AF30" s="308" t="n"/>
+      <c r="AG30" s="329" t="n"/>
+      <c r="AH30" s="329" t="n"/>
+      <c r="AI30" s="328" t="n"/>
+      <c r="AJ30" s="308" t="n"/>
+      <c r="AK30" s="329" t="n"/>
+      <c r="AL30" s="328" t="n"/>
+      <c r="AM30" s="308" t="n"/>
+      <c r="AN30" s="328" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="744" t="n">
+      <c r="A31" s="304" t="n">
         <v>10</v>
       </c>
-      <c r="B31" s="285" t="n"/>
+      <c r="B31" s="328" t="n"/>
       <c r="C31" s="310" t="inlineStr">
         <is>
           <t>RSK</t>
@@ -9248,60 +6708,21 @@
       <c r="AC31" s="283" t="n"/>
       <c r="AD31" s="283" t="n"/>
       <c r="AE31" s="285" t="n"/>
-      <c r="AF31" s="745" t="n"/>
-      <c r="AG31" s="283" t="n"/>
-      <c r="AH31" s="283" t="n"/>
-      <c r="AI31" s="285" t="n"/>
-      <c r="AJ31" s="745" t="n"/>
-      <c r="AK31" s="283" t="n"/>
-      <c r="AL31" s="285" t="n"/>
-      <c r="AM31" s="746" t="n"/>
-      <c r="AN31" s="287" t="n"/>
-    </row>
-    <row r="32" ht="3" customHeight="1">
-      <c r="A32" s="654" t="n"/>
-      <c r="B32" s="654" t="n"/>
-      <c r="C32" s="654" t="n"/>
-      <c r="D32" s="654" t="n"/>
-      <c r="E32" s="654" t="n"/>
-      <c r="F32" s="654" t="n"/>
-      <c r="G32" s="654" t="n"/>
-      <c r="H32" s="654" t="n"/>
-      <c r="I32" s="654" t="n"/>
-      <c r="J32" s="654" t="n"/>
-      <c r="K32" s="654" t="n"/>
-      <c r="L32" s="654" t="n"/>
-      <c r="M32" s="654" t="n"/>
-      <c r="N32" s="654" t="n"/>
-      <c r="O32" s="654" t="n"/>
-      <c r="P32" s="654" t="n"/>
-      <c r="Q32" s="654" t="n"/>
-      <c r="R32" s="654" t="n"/>
-      <c r="S32" s="654" t="n"/>
-      <c r="T32" s="654" t="n"/>
-      <c r="U32" s="654" t="n"/>
-      <c r="V32" s="654" t="n"/>
-      <c r="W32" s="654" t="n"/>
-      <c r="X32" s="654" t="n"/>
-      <c r="Y32" s="654" t="n"/>
-      <c r="Z32" s="654" t="n"/>
-      <c r="AA32" s="654" t="n"/>
-      <c r="AB32" s="654" t="n"/>
-      <c r="AC32" s="654" t="n"/>
-      <c r="AD32" s="654" t="n"/>
-      <c r="AE32" s="654" t="n"/>
-      <c r="AF32" s="654" t="n"/>
-      <c r="AG32" s="654" t="n"/>
-      <c r="AH32" s="654" t="n"/>
-      <c r="AI32" s="654" t="n"/>
-      <c r="AJ32" s="654" t="n"/>
-      <c r="AK32" s="654" t="n"/>
-      <c r="AL32" s="654" t="n"/>
-      <c r="AM32" s="654" t="n"/>
-      <c r="AN32" s="654" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="730" t="inlineStr">
+      <c r="AF31" s="308" t="n"/>
+      <c r="AG31" s="329" t="n"/>
+      <c r="AH31" s="329" t="n"/>
+      <c r="AI31" s="328" t="n"/>
+      <c r="AJ31" s="308" t="n"/>
+      <c r="AK31" s="329" t="n"/>
+      <c r="AL31" s="328" t="n"/>
+      <c r="AM31" s="308" t="n"/>
+      <c r="AN31" s="328" t="n"/>
+    </row>
+    <row r="32" ht="4" customHeight="1">
+      <c r="A32" s="25" t="n"/>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="288" t="inlineStr">
         <is>
           <t>4.  OPEN RISK ACTIONS / CONTAINMENT</t>
         </is>
@@ -9346,7 +6767,7 @@
       <c r="AM33" s="289" t="n"/>
       <c r="AN33" s="290" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1">
+    <row r="34" ht="17" customHeight="1">
       <c r="A34" s="301" t="inlineStr">
         <is>
           <t>#</t>
@@ -9417,269 +6838,230 @@
       <c r="AN34" s="274" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="747" t="n">
+      <c r="A35" s="313" t="n">
         <v>1</v>
       </c>
-      <c r="B35" s="272" t="n"/>
-      <c r="C35" s="739" t="n"/>
-      <c r="D35" s="271" t="n"/>
-      <c r="E35" s="271" t="n"/>
-      <c r="F35" s="271" t="n"/>
-      <c r="G35" s="271" t="n"/>
-      <c r="H35" s="271" t="n"/>
-      <c r="I35" s="271" t="n"/>
-      <c r="J35" s="271" t="n"/>
-      <c r="K35" s="271" t="n"/>
-      <c r="L35" s="272" t="n"/>
-      <c r="M35" s="739" t="n"/>
-      <c r="N35" s="271" t="n"/>
-      <c r="O35" s="271" t="n"/>
-      <c r="P35" s="271" t="n"/>
-      <c r="Q35" s="271" t="n"/>
-      <c r="R35" s="271" t="n"/>
-      <c r="S35" s="271" t="n"/>
-      <c r="T35" s="271" t="n"/>
-      <c r="U35" s="271" t="n"/>
-      <c r="V35" s="271" t="n"/>
-      <c r="W35" s="271" t="n"/>
-      <c r="X35" s="272" t="n"/>
-      <c r="Y35" s="739" t="n"/>
-      <c r="Z35" s="271" t="n"/>
-      <c r="AA35" s="271" t="n"/>
-      <c r="AB35" s="271" t="n"/>
-      <c r="AC35" s="272" t="n"/>
-      <c r="AD35" s="739" t="n"/>
-      <c r="AE35" s="271" t="n"/>
-      <c r="AF35" s="271" t="n"/>
-      <c r="AG35" s="271" t="n"/>
-      <c r="AH35" s="272" t="n"/>
-      <c r="AI35" s="739" t="n"/>
-      <c r="AJ35" s="271" t="n"/>
-      <c r="AK35" s="272" t="n"/>
-      <c r="AL35" s="741" t="n"/>
-      <c r="AM35" s="271" t="n"/>
-      <c r="AN35" s="274" t="n"/>
+      <c r="B35" s="278" t="n"/>
+      <c r="C35" s="308" t="n"/>
+      <c r="D35" s="329" t="n"/>
+      <c r="E35" s="329" t="n"/>
+      <c r="F35" s="329" t="n"/>
+      <c r="G35" s="329" t="n"/>
+      <c r="H35" s="329" t="n"/>
+      <c r="I35" s="329" t="n"/>
+      <c r="J35" s="329" t="n"/>
+      <c r="K35" s="329" t="n"/>
+      <c r="L35" s="328" t="n"/>
+      <c r="M35" s="308" t="n"/>
+      <c r="N35" s="329" t="n"/>
+      <c r="O35" s="329" t="n"/>
+      <c r="P35" s="329" t="n"/>
+      <c r="Q35" s="329" t="n"/>
+      <c r="R35" s="329" t="n"/>
+      <c r="S35" s="329" t="n"/>
+      <c r="T35" s="329" t="n"/>
+      <c r="U35" s="329" t="n"/>
+      <c r="V35" s="329" t="n"/>
+      <c r="W35" s="329" t="n"/>
+      <c r="X35" s="328" t="n"/>
+      <c r="Y35" s="308" t="n"/>
+      <c r="Z35" s="329" t="n"/>
+      <c r="AA35" s="329" t="n"/>
+      <c r="AB35" s="329" t="n"/>
+      <c r="AC35" s="328" t="n"/>
+      <c r="AD35" s="308" t="n"/>
+      <c r="AE35" s="329" t="n"/>
+      <c r="AF35" s="329" t="n"/>
+      <c r="AG35" s="329" t="n"/>
+      <c r="AH35" s="328" t="n"/>
+      <c r="AI35" s="308" t="n"/>
+      <c r="AJ35" s="329" t="n"/>
+      <c r="AK35" s="328" t="n"/>
+      <c r="AL35" s="308" t="n"/>
+      <c r="AM35" s="329" t="n"/>
+      <c r="AN35" s="328" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="748" t="n">
+      <c r="A36" s="313" t="n">
         <v>2</v>
       </c>
       <c r="B36" s="278" t="n"/>
-      <c r="C36" s="306" t="n"/>
-      <c r="D36" s="277" t="n"/>
-      <c r="E36" s="277" t="n"/>
-      <c r="F36" s="277" t="n"/>
-      <c r="G36" s="277" t="n"/>
-      <c r="H36" s="277" t="n"/>
-      <c r="I36" s="277" t="n"/>
-      <c r="J36" s="277" t="n"/>
-      <c r="K36" s="277" t="n"/>
-      <c r="L36" s="278" t="n"/>
-      <c r="M36" s="306" t="n"/>
-      <c r="N36" s="277" t="n"/>
-      <c r="O36" s="277" t="n"/>
-      <c r="P36" s="277" t="n"/>
-      <c r="Q36" s="277" t="n"/>
-      <c r="R36" s="277" t="n"/>
-      <c r="S36" s="277" t="n"/>
-      <c r="T36" s="277" t="n"/>
-      <c r="U36" s="277" t="n"/>
-      <c r="V36" s="277" t="n"/>
-      <c r="W36" s="277" t="n"/>
-      <c r="X36" s="278" t="n"/>
-      <c r="Y36" s="306" t="n"/>
-      <c r="Z36" s="277" t="n"/>
-      <c r="AA36" s="277" t="n"/>
-      <c r="AB36" s="277" t="n"/>
-      <c r="AC36" s="278" t="n"/>
-      <c r="AD36" s="306" t="n"/>
-      <c r="AE36" s="277" t="n"/>
-      <c r="AF36" s="277" t="n"/>
-      <c r="AG36" s="277" t="n"/>
-      <c r="AH36" s="278" t="n"/>
-      <c r="AI36" s="306" t="n"/>
-      <c r="AJ36" s="277" t="n"/>
-      <c r="AK36" s="278" t="n"/>
-      <c r="AL36" s="743" t="n"/>
-      <c r="AM36" s="277" t="n"/>
-      <c r="AN36" s="280" t="n"/>
+      <c r="C36" s="308" t="n"/>
+      <c r="D36" s="329" t="n"/>
+      <c r="E36" s="329" t="n"/>
+      <c r="F36" s="329" t="n"/>
+      <c r="G36" s="329" t="n"/>
+      <c r="H36" s="329" t="n"/>
+      <c r="I36" s="329" t="n"/>
+      <c r="J36" s="329" t="n"/>
+      <c r="K36" s="329" t="n"/>
+      <c r="L36" s="328" t="n"/>
+      <c r="M36" s="308" t="n"/>
+      <c r="N36" s="329" t="n"/>
+      <c r="O36" s="329" t="n"/>
+      <c r="P36" s="329" t="n"/>
+      <c r="Q36" s="329" t="n"/>
+      <c r="R36" s="329" t="n"/>
+      <c r="S36" s="329" t="n"/>
+      <c r="T36" s="329" t="n"/>
+      <c r="U36" s="329" t="n"/>
+      <c r="V36" s="329" t="n"/>
+      <c r="W36" s="329" t="n"/>
+      <c r="X36" s="328" t="n"/>
+      <c r="Y36" s="308" t="n"/>
+      <c r="Z36" s="329" t="n"/>
+      <c r="AA36" s="329" t="n"/>
+      <c r="AB36" s="329" t="n"/>
+      <c r="AC36" s="328" t="n"/>
+      <c r="AD36" s="308" t="n"/>
+      <c r="AE36" s="329" t="n"/>
+      <c r="AF36" s="329" t="n"/>
+      <c r="AG36" s="329" t="n"/>
+      <c r="AH36" s="328" t="n"/>
+      <c r="AI36" s="308" t="n"/>
+      <c r="AJ36" s="329" t="n"/>
+      <c r="AK36" s="328" t="n"/>
+      <c r="AL36" s="308" t="n"/>
+      <c r="AM36" s="329" t="n"/>
+      <c r="AN36" s="328" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="748" t="n">
+      <c r="A37" s="313" t="n">
         <v>3</v>
       </c>
       <c r="B37" s="278" t="n"/>
-      <c r="C37" s="306" t="n"/>
-      <c r="D37" s="277" t="n"/>
-      <c r="E37" s="277" t="n"/>
-      <c r="F37" s="277" t="n"/>
-      <c r="G37" s="277" t="n"/>
-      <c r="H37" s="277" t="n"/>
-      <c r="I37" s="277" t="n"/>
-      <c r="J37" s="277" t="n"/>
-      <c r="K37" s="277" t="n"/>
-      <c r="L37" s="278" t="n"/>
-      <c r="M37" s="306" t="n"/>
-      <c r="N37" s="277" t="n"/>
-      <c r="O37" s="277" t="n"/>
-      <c r="P37" s="277" t="n"/>
-      <c r="Q37" s="277" t="n"/>
-      <c r="R37" s="277" t="n"/>
-      <c r="S37" s="277" t="n"/>
-      <c r="T37" s="277" t="n"/>
-      <c r="U37" s="277" t="n"/>
-      <c r="V37" s="277" t="n"/>
-      <c r="W37" s="277" t="n"/>
-      <c r="X37" s="278" t="n"/>
-      <c r="Y37" s="306" t="n"/>
-      <c r="Z37" s="277" t="n"/>
-      <c r="AA37" s="277" t="n"/>
-      <c r="AB37" s="277" t="n"/>
-      <c r="AC37" s="278" t="n"/>
-      <c r="AD37" s="306" t="n"/>
-      <c r="AE37" s="277" t="n"/>
-      <c r="AF37" s="277" t="n"/>
-      <c r="AG37" s="277" t="n"/>
-      <c r="AH37" s="278" t="n"/>
-      <c r="AI37" s="306" t="n"/>
-      <c r="AJ37" s="277" t="n"/>
-      <c r="AK37" s="278" t="n"/>
-      <c r="AL37" s="743" t="n"/>
-      <c r="AM37" s="277" t="n"/>
-      <c r="AN37" s="280" t="n"/>
+      <c r="C37" s="308" t="n"/>
+      <c r="D37" s="329" t="n"/>
+      <c r="E37" s="329" t="n"/>
+      <c r="F37" s="329" t="n"/>
+      <c r="G37" s="329" t="n"/>
+      <c r="H37" s="329" t="n"/>
+      <c r="I37" s="329" t="n"/>
+      <c r="J37" s="329" t="n"/>
+      <c r="K37" s="329" t="n"/>
+      <c r="L37" s="328" t="n"/>
+      <c r="M37" s="308" t="n"/>
+      <c r="N37" s="329" t="n"/>
+      <c r="O37" s="329" t="n"/>
+      <c r="P37" s="329" t="n"/>
+      <c r="Q37" s="329" t="n"/>
+      <c r="R37" s="329" t="n"/>
+      <c r="S37" s="329" t="n"/>
+      <c r="T37" s="329" t="n"/>
+      <c r="U37" s="329" t="n"/>
+      <c r="V37" s="329" t="n"/>
+      <c r="W37" s="329" t="n"/>
+      <c r="X37" s="328" t="n"/>
+      <c r="Y37" s="308" t="n"/>
+      <c r="Z37" s="329" t="n"/>
+      <c r="AA37" s="329" t="n"/>
+      <c r="AB37" s="329" t="n"/>
+      <c r="AC37" s="328" t="n"/>
+      <c r="AD37" s="308" t="n"/>
+      <c r="AE37" s="329" t="n"/>
+      <c r="AF37" s="329" t="n"/>
+      <c r="AG37" s="329" t="n"/>
+      <c r="AH37" s="328" t="n"/>
+      <c r="AI37" s="308" t="n"/>
+      <c r="AJ37" s="329" t="n"/>
+      <c r="AK37" s="328" t="n"/>
+      <c r="AL37" s="308" t="n"/>
+      <c r="AM37" s="329" t="n"/>
+      <c r="AN37" s="328" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="748" t="n">
+      <c r="A38" s="313" t="n">
         <v>4</v>
       </c>
       <c r="B38" s="278" t="n"/>
-      <c r="C38" s="306" t="n"/>
-      <c r="D38" s="277" t="n"/>
-      <c r="E38" s="277" t="n"/>
-      <c r="F38" s="277" t="n"/>
-      <c r="G38" s="277" t="n"/>
-      <c r="H38" s="277" t="n"/>
-      <c r="I38" s="277" t="n"/>
-      <c r="J38" s="277" t="n"/>
-      <c r="K38" s="277" t="n"/>
-      <c r="L38" s="278" t="n"/>
-      <c r="M38" s="306" t="n"/>
-      <c r="N38" s="277" t="n"/>
-      <c r="O38" s="277" t="n"/>
-      <c r="P38" s="277" t="n"/>
-      <c r="Q38" s="277" t="n"/>
-      <c r="R38" s="277" t="n"/>
-      <c r="S38" s="277" t="n"/>
-      <c r="T38" s="277" t="n"/>
-      <c r="U38" s="277" t="n"/>
-      <c r="V38" s="277" t="n"/>
-      <c r="W38" s="277" t="n"/>
-      <c r="X38" s="278" t="n"/>
-      <c r="Y38" s="306" t="n"/>
-      <c r="Z38" s="277" t="n"/>
-      <c r="AA38" s="277" t="n"/>
-      <c r="AB38" s="277" t="n"/>
-      <c r="AC38" s="278" t="n"/>
-      <c r="AD38" s="306" t="n"/>
-      <c r="AE38" s="277" t="n"/>
-      <c r="AF38" s="277" t="n"/>
-      <c r="AG38" s="277" t="n"/>
-      <c r="AH38" s="278" t="n"/>
-      <c r="AI38" s="306" t="n"/>
-      <c r="AJ38" s="277" t="n"/>
-      <c r="AK38" s="278" t="n"/>
-      <c r="AL38" s="743" t="n"/>
-      <c r="AM38" s="277" t="n"/>
-      <c r="AN38" s="280" t="n"/>
+      <c r="C38" s="308" t="n"/>
+      <c r="D38" s="329" t="n"/>
+      <c r="E38" s="329" t="n"/>
+      <c r="F38" s="329" t="n"/>
+      <c r="G38" s="329" t="n"/>
+      <c r="H38" s="329" t="n"/>
+      <c r="I38" s="329" t="n"/>
+      <c r="J38" s="329" t="n"/>
+      <c r="K38" s="329" t="n"/>
+      <c r="L38" s="328" t="n"/>
+      <c r="M38" s="308" t="n"/>
+      <c r="N38" s="329" t="n"/>
+      <c r="O38" s="329" t="n"/>
+      <c r="P38" s="329" t="n"/>
+      <c r="Q38" s="329" t="n"/>
+      <c r="R38" s="329" t="n"/>
+      <c r="S38" s="329" t="n"/>
+      <c r="T38" s="329" t="n"/>
+      <c r="U38" s="329" t="n"/>
+      <c r="V38" s="329" t="n"/>
+      <c r="W38" s="329" t="n"/>
+      <c r="X38" s="328" t="n"/>
+      <c r="Y38" s="308" t="n"/>
+      <c r="Z38" s="329" t="n"/>
+      <c r="AA38" s="329" t="n"/>
+      <c r="AB38" s="329" t="n"/>
+      <c r="AC38" s="328" t="n"/>
+      <c r="AD38" s="308" t="n"/>
+      <c r="AE38" s="329" t="n"/>
+      <c r="AF38" s="329" t="n"/>
+      <c r="AG38" s="329" t="n"/>
+      <c r="AH38" s="328" t="n"/>
+      <c r="AI38" s="308" t="n"/>
+      <c r="AJ38" s="329" t="n"/>
+      <c r="AK38" s="328" t="n"/>
+      <c r="AL38" s="308" t="n"/>
+      <c r="AM38" s="329" t="n"/>
+      <c r="AN38" s="328" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="749" t="n">
+      <c r="A39" s="314" t="n">
         <v>5</v>
       </c>
       <c r="B39" s="285" t="n"/>
-      <c r="C39" s="745" t="n"/>
-      <c r="D39" s="283" t="n"/>
-      <c r="E39" s="283" t="n"/>
-      <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="n"/>
-      <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="n"/>
-      <c r="J39" s="283" t="n"/>
-      <c r="K39" s="283" t="n"/>
-      <c r="L39" s="285" t="n"/>
-      <c r="M39" s="745" t="n"/>
-      <c r="N39" s="283" t="n"/>
-      <c r="O39" s="283" t="n"/>
-      <c r="P39" s="283" t="n"/>
-      <c r="Q39" s="283" t="n"/>
-      <c r="R39" s="283" t="n"/>
-      <c r="S39" s="283" t="n"/>
-      <c r="T39" s="283" t="n"/>
-      <c r="U39" s="283" t="n"/>
-      <c r="V39" s="283" t="n"/>
-      <c r="W39" s="283" t="n"/>
-      <c r="X39" s="285" t="n"/>
-      <c r="Y39" s="745" t="n"/>
-      <c r="Z39" s="283" t="n"/>
-      <c r="AA39" s="283" t="n"/>
-      <c r="AB39" s="283" t="n"/>
-      <c r="AC39" s="285" t="n"/>
-      <c r="AD39" s="745" t="n"/>
-      <c r="AE39" s="283" t="n"/>
-      <c r="AF39" s="283" t="n"/>
-      <c r="AG39" s="283" t="n"/>
-      <c r="AH39" s="285" t="n"/>
-      <c r="AI39" s="745" t="n"/>
-      <c r="AJ39" s="283" t="n"/>
-      <c r="AK39" s="285" t="n"/>
-      <c r="AL39" s="746" t="n"/>
-      <c r="AM39" s="283" t="n"/>
-      <c r="AN39" s="287" t="n"/>
-    </row>
-    <row r="40" ht="3" customHeight="1">
-      <c r="A40" s="654" t="n"/>
-      <c r="B40" s="654" t="n"/>
-      <c r="C40" s="654" t="n"/>
-      <c r="D40" s="654" t="n"/>
-      <c r="E40" s="654" t="n"/>
-      <c r="F40" s="654" t="n"/>
-      <c r="G40" s="654" t="n"/>
-      <c r="H40" s="654" t="n"/>
-      <c r="I40" s="654" t="n"/>
-      <c r="J40" s="654" t="n"/>
-      <c r="K40" s="654" t="n"/>
-      <c r="L40" s="654" t="n"/>
-      <c r="M40" s="654" t="n"/>
-      <c r="N40" s="654" t="n"/>
-      <c r="O40" s="654" t="n"/>
-      <c r="P40" s="654" t="n"/>
-      <c r="Q40" s="654" t="n"/>
-      <c r="R40" s="654" t="n"/>
-      <c r="S40" s="654" t="n"/>
-      <c r="T40" s="654" t="n"/>
-      <c r="U40" s="654" t="n"/>
-      <c r="V40" s="654" t="n"/>
-      <c r="W40" s="654" t="n"/>
-      <c r="X40" s="654" t="n"/>
-      <c r="Y40" s="654" t="n"/>
-      <c r="Z40" s="654" t="n"/>
-      <c r="AA40" s="654" t="n"/>
-      <c r="AB40" s="654" t="n"/>
-      <c r="AC40" s="654" t="n"/>
-      <c r="AD40" s="654" t="n"/>
-      <c r="AE40" s="654" t="n"/>
-      <c r="AF40" s="654" t="n"/>
-      <c r="AG40" s="654" t="n"/>
-      <c r="AH40" s="654" t="n"/>
-      <c r="AI40" s="654" t="n"/>
-      <c r="AJ40" s="654" t="n"/>
-      <c r="AK40" s="654" t="n"/>
-      <c r="AL40" s="654" t="n"/>
-      <c r="AM40" s="654" t="n"/>
-      <c r="AN40" s="654" t="n"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="730" t="inlineStr">
+      <c r="C39" s="308" t="n"/>
+      <c r="D39" s="329" t="n"/>
+      <c r="E39" s="329" t="n"/>
+      <c r="F39" s="329" t="n"/>
+      <c r="G39" s="329" t="n"/>
+      <c r="H39" s="329" t="n"/>
+      <c r="I39" s="329" t="n"/>
+      <c r="J39" s="329" t="n"/>
+      <c r="K39" s="329" t="n"/>
+      <c r="L39" s="328" t="n"/>
+      <c r="M39" s="308" t="n"/>
+      <c r="N39" s="329" t="n"/>
+      <c r="O39" s="329" t="n"/>
+      <c r="P39" s="329" t="n"/>
+      <c r="Q39" s="329" t="n"/>
+      <c r="R39" s="329" t="n"/>
+      <c r="S39" s="329" t="n"/>
+      <c r="T39" s="329" t="n"/>
+      <c r="U39" s="329" t="n"/>
+      <c r="V39" s="329" t="n"/>
+      <c r="W39" s="329" t="n"/>
+      <c r="X39" s="328" t="n"/>
+      <c r="Y39" s="308" t="n"/>
+      <c r="Z39" s="329" t="n"/>
+      <c r="AA39" s="329" t="n"/>
+      <c r="AB39" s="329" t="n"/>
+      <c r="AC39" s="328" t="n"/>
+      <c r="AD39" s="308" t="n"/>
+      <c r="AE39" s="329" t="n"/>
+      <c r="AF39" s="329" t="n"/>
+      <c r="AG39" s="329" t="n"/>
+      <c r="AH39" s="328" t="n"/>
+      <c r="AI39" s="308" t="n"/>
+      <c r="AJ39" s="329" t="n"/>
+      <c r="AK39" s="328" t="n"/>
+      <c r="AL39" s="308" t="n"/>
+      <c r="AM39" s="329" t="n"/>
+      <c r="AN39" s="328" t="n"/>
+    </row>
+    <row r="40" ht="4" customHeight="1">
+      <c r="A40" s="25" t="n"/>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="288" t="inlineStr">
         <is>
           <t>5.  APPROVAL / SIGN-OFF</t>
         </is>
@@ -9724,215 +7106,212 @@
       <c r="AM41" s="289" t="n"/>
       <c r="AN41" s="290" t="n"/>
     </row>
-    <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="737" t="inlineStr">
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="315" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B42" s="271" t="n"/>
-      <c r="C42" s="271" t="n"/>
-      <c r="D42" s="271" t="n"/>
-      <c r="E42" s="271" t="n"/>
-      <c r="F42" s="271" t="n"/>
-      <c r="G42" s="271" t="n"/>
-      <c r="H42" s="271" t="n"/>
-      <c r="I42" s="271" t="n"/>
-      <c r="J42" s="271" t="n"/>
-      <c r="K42" s="271" t="n"/>
-      <c r="L42" s="271" t="n"/>
-      <c r="M42" s="272" t="n"/>
-      <c r="N42" s="750" t="inlineStr">
+      <c r="B42" s="289" t="n"/>
+      <c r="C42" s="289" t="n"/>
+      <c r="D42" s="289" t="n"/>
+      <c r="E42" s="289" t="n"/>
+      <c r="F42" s="289" t="n"/>
+      <c r="G42" s="289" t="n"/>
+      <c r="H42" s="289" t="n"/>
+      <c r="I42" s="289" t="n"/>
+      <c r="J42" s="289" t="n"/>
+      <c r="K42" s="289" t="n"/>
+      <c r="L42" s="289" t="n"/>
+      <c r="M42" s="289" t="n"/>
+      <c r="N42" s="316" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="O42" s="271" t="n"/>
-      <c r="P42" s="271" t="n"/>
-      <c r="Q42" s="271" t="n"/>
-      <c r="R42" s="271" t="n"/>
-      <c r="S42" s="271" t="n"/>
-      <c r="T42" s="271" t="n"/>
-      <c r="U42" s="271" t="n"/>
-      <c r="V42" s="271" t="n"/>
-      <c r="W42" s="271" t="n"/>
-      <c r="X42" s="271" t="n"/>
-      <c r="Y42" s="271" t="n"/>
-      <c r="Z42" s="272" t="n"/>
-      <c r="AA42" s="751" t="inlineStr">
+      <c r="O42" s="289" t="n"/>
+      <c r="P42" s="289" t="n"/>
+      <c r="Q42" s="289" t="n"/>
+      <c r="R42" s="289" t="n"/>
+      <c r="S42" s="289" t="n"/>
+      <c r="T42" s="289" t="n"/>
+      <c r="U42" s="289" t="n"/>
+      <c r="V42" s="289" t="n"/>
+      <c r="W42" s="289" t="n"/>
+      <c r="X42" s="289" t="n"/>
+      <c r="Y42" s="289" t="n"/>
+      <c r="Z42" s="289" t="n"/>
+      <c r="AA42" s="317" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AB42" s="271" t="n"/>
-      <c r="AC42" s="271" t="n"/>
-      <c r="AD42" s="271" t="n"/>
-      <c r="AE42" s="271" t="n"/>
-      <c r="AF42" s="271" t="n"/>
-      <c r="AG42" s="271" t="n"/>
-      <c r="AH42" s="271" t="n"/>
-      <c r="AI42" s="271" t="n"/>
-      <c r="AJ42" s="271" t="n"/>
-      <c r="AK42" s="271" t="n"/>
-      <c r="AL42" s="271" t="n"/>
-      <c r="AM42" s="271" t="n"/>
-      <c r="AN42" s="274" t="n"/>
+      <c r="AB42" s="289" t="n"/>
+      <c r="AC42" s="289" t="n"/>
+      <c r="AD42" s="289" t="n"/>
+      <c r="AE42" s="289" t="n"/>
+      <c r="AF42" s="289" t="n"/>
+      <c r="AG42" s="289" t="n"/>
+      <c r="AH42" s="289" t="n"/>
+      <c r="AI42" s="289" t="n"/>
+      <c r="AJ42" s="289" t="n"/>
+      <c r="AK42" s="289" t="n"/>
+      <c r="AL42" s="289" t="n"/>
+      <c r="AM42" s="289" t="n"/>
+      <c r="AN42" s="290" t="n"/>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="752" t="inlineStr">
+      <c r="A43" s="318" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="M43" s="753" t="n"/>
-      <c r="N43" s="754" t="inlineStr">
+      <c r="B43" s="268" t="n"/>
+      <c r="C43" s="268" t="n"/>
+      <c r="D43" s="268" t="n"/>
+      <c r="E43" s="268" t="n"/>
+      <c r="F43" s="268" t="n"/>
+      <c r="G43" s="268" t="n"/>
+      <c r="H43" s="268" t="n"/>
+      <c r="I43" s="268" t="n"/>
+      <c r="J43" s="268" t="n"/>
+      <c r="K43" s="268" t="n"/>
+      <c r="L43" s="268" t="n"/>
+      <c r="M43" s="319" t="n"/>
+      <c r="N43" s="318" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="Z43" s="753" t="n"/>
-      <c r="AA43" s="755" t="inlineStr">
+      <c r="O43" s="268" t="n"/>
+      <c r="P43" s="268" t="n"/>
+      <c r="Q43" s="268" t="n"/>
+      <c r="R43" s="268" t="n"/>
+      <c r="S43" s="268" t="n"/>
+      <c r="T43" s="268" t="n"/>
+      <c r="U43" s="268" t="n"/>
+      <c r="V43" s="268" t="n"/>
+      <c r="W43" s="268" t="n"/>
+      <c r="X43" s="268" t="n"/>
+      <c r="Y43" s="268" t="n"/>
+      <c r="Z43" s="319" t="n"/>
+      <c r="AA43" s="318" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="AN43" s="320" t="n"/>
-    </row>
-    <row r="44" ht="20" customHeight="1">
+      <c r="AB43" s="268" t="n"/>
+      <c r="AC43" s="268" t="n"/>
+      <c r="AD43" s="268" t="n"/>
+      <c r="AE43" s="268" t="n"/>
+      <c r="AF43" s="268" t="n"/>
+      <c r="AG43" s="268" t="n"/>
+      <c r="AH43" s="268" t="n"/>
+      <c r="AI43" s="268" t="n"/>
+      <c r="AJ43" s="268" t="n"/>
+      <c r="AK43" s="268" t="n"/>
+      <c r="AL43" s="268" t="n"/>
+      <c r="AM43" s="268" t="n"/>
+      <c r="AN43" s="319" t="n"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
       <c r="A44" s="275" t="n"/>
-      <c r="M44" s="753" t="n"/>
-      <c r="Z44" s="753" t="n"/>
+      <c r="M44" s="320" t="n"/>
+      <c r="N44" s="275" t="n"/>
+      <c r="Z44" s="320" t="n"/>
+      <c r="AA44" s="275" t="n"/>
       <c r="AN44" s="320" t="n"/>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="281" t="n"/>
-      <c r="B45" s="277" t="n"/>
-      <c r="C45" s="277" t="n"/>
-      <c r="D45" s="277" t="n"/>
-      <c r="E45" s="277" t="n"/>
-      <c r="F45" s="277" t="n"/>
-      <c r="G45" s="277" t="n"/>
-      <c r="H45" s="277" t="n"/>
-      <c r="I45" s="277" t="n"/>
-      <c r="J45" s="277" t="n"/>
-      <c r="K45" s="277" t="n"/>
-      <c r="L45" s="277" t="n"/>
-      <c r="M45" s="278" t="n"/>
-      <c r="N45" s="277" t="n"/>
-      <c r="O45" s="277" t="n"/>
-      <c r="P45" s="277" t="n"/>
-      <c r="Q45" s="277" t="n"/>
-      <c r="R45" s="277" t="n"/>
-      <c r="S45" s="277" t="n"/>
-      <c r="T45" s="277" t="n"/>
-      <c r="U45" s="277" t="n"/>
-      <c r="V45" s="277" t="n"/>
-      <c r="W45" s="277" t="n"/>
-      <c r="X45" s="277" t="n"/>
-      <c r="Y45" s="277" t="n"/>
-      <c r="Z45" s="278" t="n"/>
-      <c r="AA45" s="277" t="n"/>
-      <c r="AB45" s="277" t="n"/>
-      <c r="AC45" s="277" t="n"/>
-      <c r="AD45" s="277" t="n"/>
-      <c r="AE45" s="277" t="n"/>
-      <c r="AF45" s="277" t="n"/>
-      <c r="AG45" s="277" t="n"/>
-      <c r="AH45" s="277" t="n"/>
-      <c r="AI45" s="277" t="n"/>
-      <c r="AJ45" s="277" t="n"/>
-      <c r="AK45" s="277" t="n"/>
-      <c r="AL45" s="277" t="n"/>
-      <c r="AM45" s="277" t="n"/>
-      <c r="AN45" s="280" t="n"/>
-    </row>
-    <row r="46" ht="3" customHeight="1">
-      <c r="A46" s="654" t="n"/>
-      <c r="B46" s="654" t="n"/>
-      <c r="C46" s="654" t="n"/>
-      <c r="D46" s="654" t="n"/>
-      <c r="E46" s="654" t="n"/>
-      <c r="F46" s="654" t="n"/>
-      <c r="G46" s="654" t="n"/>
-      <c r="H46" s="654" t="n"/>
-      <c r="I46" s="654" t="n"/>
-      <c r="J46" s="654" t="n"/>
-      <c r="K46" s="654" t="n"/>
-      <c r="L46" s="654" t="n"/>
-      <c r="M46" s="654" t="n"/>
-      <c r="N46" s="654" t="n"/>
-      <c r="O46" s="654" t="n"/>
-      <c r="P46" s="654" t="n"/>
-      <c r="Q46" s="654" t="n"/>
-      <c r="R46" s="654" t="n"/>
-      <c r="S46" s="654" t="n"/>
-      <c r="T46" s="654" t="n"/>
-      <c r="U46" s="654" t="n"/>
-      <c r="V46" s="654" t="n"/>
-      <c r="W46" s="654" t="n"/>
-      <c r="X46" s="654" t="n"/>
-      <c r="Y46" s="654" t="n"/>
-      <c r="Z46" s="654" t="n"/>
-      <c r="AA46" s="654" t="n"/>
-      <c r="AB46" s="654" t="n"/>
-      <c r="AC46" s="654" t="n"/>
-      <c r="AD46" s="654" t="n"/>
-      <c r="AE46" s="654" t="n"/>
-      <c r="AF46" s="654" t="n"/>
-      <c r="AG46" s="654" t="n"/>
-      <c r="AH46" s="654" t="n"/>
-      <c r="AI46" s="654" t="n"/>
-      <c r="AJ46" s="654" t="n"/>
-      <c r="AK46" s="654" t="n"/>
-      <c r="AL46" s="654" t="n"/>
-      <c r="AM46" s="654" t="n"/>
-      <c r="AN46" s="654" t="n"/>
-    </row>
-    <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="370" t="inlineStr">
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="282" t="n"/>
+      <c r="B45" s="283" t="n"/>
+      <c r="C45" s="283" t="n"/>
+      <c r="D45" s="283" t="n"/>
+      <c r="E45" s="283" t="n"/>
+      <c r="F45" s="283" t="n"/>
+      <c r="G45" s="283" t="n"/>
+      <c r="H45" s="283" t="n"/>
+      <c r="I45" s="283" t="n"/>
+      <c r="J45" s="283" t="n"/>
+      <c r="K45" s="283" t="n"/>
+      <c r="L45" s="283" t="n"/>
+      <c r="M45" s="287" t="n"/>
+      <c r="N45" s="282" t="n"/>
+      <c r="O45" s="283" t="n"/>
+      <c r="P45" s="283" t="n"/>
+      <c r="Q45" s="283" t="n"/>
+      <c r="R45" s="283" t="n"/>
+      <c r="S45" s="283" t="n"/>
+      <c r="T45" s="283" t="n"/>
+      <c r="U45" s="283" t="n"/>
+      <c r="V45" s="283" t="n"/>
+      <c r="W45" s="283" t="n"/>
+      <c r="X45" s="283" t="n"/>
+      <c r="Y45" s="283" t="n"/>
+      <c r="Z45" s="287" t="n"/>
+      <c r="AA45" s="282" t="n"/>
+      <c r="AB45" s="283" t="n"/>
+      <c r="AC45" s="283" t="n"/>
+      <c r="AD45" s="283" t="n"/>
+      <c r="AE45" s="283" t="n"/>
+      <c r="AF45" s="283" t="n"/>
+      <c r="AG45" s="283" t="n"/>
+      <c r="AH45" s="283" t="n"/>
+      <c r="AI45" s="283" t="n"/>
+      <c r="AJ45" s="283" t="n"/>
+      <c r="AK45" s="283" t="n"/>
+      <c r="AL45" s="283" t="n"/>
+      <c r="AM45" s="283" t="n"/>
+      <c r="AN45" s="287" t="n"/>
+    </row>
+    <row r="46" ht="4" customHeight="1">
+      <c r="A46" s="25" t="n"/>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="321" t="inlineStr">
         <is>
           <t>NOTICE  —  Enter data only in designated white input cells. Do not add, delete or resize columns/rows. File naming: FRM-209_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="371" t="n"/>
-      <c r="C47" s="371" t="n"/>
-      <c r="D47" s="371" t="n"/>
-      <c r="E47" s="371" t="n"/>
-      <c r="F47" s="371" t="n"/>
-      <c r="G47" s="371" t="n"/>
-      <c r="H47" s="371" t="n"/>
-      <c r="I47" s="371" t="n"/>
-      <c r="J47" s="371" t="n"/>
-      <c r="K47" s="371" t="n"/>
-      <c r="L47" s="371" t="n"/>
-      <c r="M47" s="371" t="n"/>
-      <c r="N47" s="371" t="n"/>
-      <c r="O47" s="371" t="n"/>
-      <c r="P47" s="371" t="n"/>
-      <c r="Q47" s="371" t="n"/>
-      <c r="R47" s="371" t="n"/>
-      <c r="S47" s="371" t="n"/>
-      <c r="T47" s="371" t="n"/>
-      <c r="U47" s="371" t="n"/>
-      <c r="V47" s="371" t="n"/>
-      <c r="W47" s="371" t="n"/>
-      <c r="X47" s="371" t="n"/>
-      <c r="Y47" s="371" t="n"/>
-      <c r="Z47" s="371" t="n"/>
-      <c r="AA47" s="371" t="n"/>
-      <c r="AB47" s="371" t="n"/>
-      <c r="AC47" s="371" t="n"/>
-      <c r="AD47" s="371" t="n"/>
-      <c r="AE47" s="371" t="n"/>
-      <c r="AF47" s="371" t="n"/>
-      <c r="AG47" s="371" t="n"/>
-      <c r="AH47" s="371" t="n"/>
-      <c r="AI47" s="371" t="n"/>
-      <c r="AJ47" s="371" t="n"/>
-      <c r="AK47" s="371" t="n"/>
-      <c r="AL47" s="371" t="n"/>
-      <c r="AM47" s="371" t="n"/>
-      <c r="AN47" s="372" t="n"/>
+      <c r="B47" s="289" t="n"/>
+      <c r="C47" s="289" t="n"/>
+      <c r="D47" s="289" t="n"/>
+      <c r="E47" s="289" t="n"/>
+      <c r="F47" s="289" t="n"/>
+      <c r="G47" s="289" t="n"/>
+      <c r="H47" s="289" t="n"/>
+      <c r="I47" s="289" t="n"/>
+      <c r="J47" s="289" t="n"/>
+      <c r="K47" s="289" t="n"/>
+      <c r="L47" s="289" t="n"/>
+      <c r="M47" s="289" t="n"/>
+      <c r="N47" s="289" t="n"/>
+      <c r="O47" s="289" t="n"/>
+      <c r="P47" s="289" t="n"/>
+      <c r="Q47" s="289" t="n"/>
+      <c r="R47" s="289" t="n"/>
+      <c r="S47" s="289" t="n"/>
+      <c r="T47" s="289" t="n"/>
+      <c r="U47" s="289" t="n"/>
+      <c r="V47" s="289" t="n"/>
+      <c r="W47" s="289" t="n"/>
+      <c r="X47" s="289" t="n"/>
+      <c r="Y47" s="289" t="n"/>
+      <c r="Z47" s="289" t="n"/>
+      <c r="AA47" s="289" t="n"/>
+      <c r="AB47" s="289" t="n"/>
+      <c r="AC47" s="289" t="n"/>
+      <c r="AD47" s="289" t="n"/>
+      <c r="AE47" s="289" t="n"/>
+      <c r="AF47" s="289" t="n"/>
+      <c r="AG47" s="289" t="n"/>
+      <c r="AH47" s="289" t="n"/>
+      <c r="AI47" s="289" t="n"/>
+      <c r="AJ47" s="289" t="n"/>
+      <c r="AK47" s="289" t="n"/>
+      <c r="AL47" s="289" t="n"/>
+      <c r="AM47" s="289" t="n"/>
+      <c r="AN47" s="290" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="1"/>
     <row r="49" hidden="1" outlineLevel="1"/>
@@ -10088,7 +7467,7 @@
     <row r="199" hidden="1" outlineLevel="1"/>
     <row r="200" hidden="1" outlineLevel="1"/>
   </sheetData>
-  <mergeCells count="181">
+  <mergeCells count="187">
     <mergeCell ref="AM26:AN26"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="AF23:AI23"/>
@@ -10097,6 +7476,7 @@
     <mergeCell ref="AB17:AN17"/>
     <mergeCell ref="AM29:AN29"/>
     <mergeCell ref="AM23:AN23"/>
+    <mergeCell ref="A32:AN32"/>
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="A14:AN14"/>
     <mergeCell ref="I4:AD4"/>
@@ -10115,6 +7495,7 @@
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="T31:AE31"/>
+    <mergeCell ref="A40:AN40"/>
     <mergeCell ref="AJ29:AL29"/>
     <mergeCell ref="AD36:AH36"/>
     <mergeCell ref="T28:AE28"/>
@@ -10126,6 +7507,7 @@
     <mergeCell ref="F28:S28"/>
     <mergeCell ref="T30:AE30"/>
     <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A6:AN6"/>
     <mergeCell ref="AJ21:AL21"/>
     <mergeCell ref="AM25:AN25"/>
     <mergeCell ref="AI34:AK34"/>
@@ -10166,6 +7548,7 @@
     <mergeCell ref="H8:T8"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="AJ26:AL26"/>
+    <mergeCell ref="A13:AN13"/>
     <mergeCell ref="AF24:AI24"/>
     <mergeCell ref="AI3:AN3"/>
     <mergeCell ref="AL35:AN35"/>
@@ -10209,6 +7592,7 @@
     <mergeCell ref="AA43:AN45"/>
     <mergeCell ref="Y35:AC35"/>
     <mergeCell ref="F24:S24"/>
+    <mergeCell ref="A19:AN19"/>
     <mergeCell ref="T23:AE23"/>
     <mergeCell ref="A1:H5"/>
     <mergeCell ref="F26:S26"/>
@@ -10234,6 +7618,7 @@
     <mergeCell ref="AM21:AN21"/>
     <mergeCell ref="N43:Z45"/>
     <mergeCell ref="AL36:AN36"/>
+    <mergeCell ref="A46:AN46"/>
     <mergeCell ref="H11:T11"/>
     <mergeCell ref="AM27:AN27"/>
     <mergeCell ref="AB11:AN11"/>
@@ -10409,847 +7794,149 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN16"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2.33" customWidth="1" min="1" max="1"/>
-    <col width="2.33" customWidth="1" min="2" max="2"/>
-    <col width="2.33" customWidth="1" min="3" max="3"/>
-    <col width="2.33" customWidth="1" min="4" max="4"/>
-    <col hidden="1" width="2.33" customWidth="1" min="5" max="16384"/>
-    <col width="2.33" customWidth="1" min="6" max="6"/>
-    <col width="2.33" customWidth="1" min="7" max="7"/>
-    <col width="2.33" customWidth="1" min="8" max="8"/>
-    <col width="2.33" customWidth="1" min="9" max="9"/>
-    <col width="2.33" customWidth="1" min="10" max="10"/>
-    <col width="2.33" customWidth="1" min="11" max="11"/>
-    <col width="2.33" customWidth="1" min="12" max="12"/>
-    <col width="2.33" customWidth="1" min="13" max="13"/>
-    <col width="2.33" customWidth="1" min="14" max="14"/>
-    <col width="2.33" customWidth="1" min="15" max="15"/>
-    <col width="2.33" customWidth="1" min="16" max="16"/>
-    <col width="2.33" customWidth="1" min="17" max="17"/>
-    <col width="2.33" customWidth="1" min="18" max="18"/>
-    <col width="2.33" customWidth="1" min="19" max="19"/>
-    <col width="2.33" customWidth="1" min="20" max="20"/>
-    <col width="2.33" customWidth="1" min="21" max="21"/>
-    <col width="2.33" customWidth="1" min="22" max="22"/>
-    <col width="2.33" customWidth="1" min="23" max="23"/>
-    <col width="2.33" customWidth="1" min="24" max="24"/>
-    <col width="2.33" customWidth="1" min="25" max="25"/>
-    <col width="2.33" customWidth="1" min="26" max="26"/>
-    <col width="2.33" customWidth="1" min="27" max="27"/>
-    <col width="2.33" customWidth="1" min="28" max="28"/>
-    <col width="2.33" customWidth="1" min="29" max="29"/>
-    <col width="2.33" customWidth="1" min="30" max="30"/>
-    <col width="2.33" customWidth="1" min="31" max="31"/>
-    <col width="2.33" customWidth="1" min="32" max="32"/>
-    <col width="2.33" customWidth="1" min="33" max="33"/>
-    <col width="2.33" customWidth="1" min="34" max="34"/>
-    <col width="2.33" customWidth="1" min="35" max="35"/>
-    <col width="2.33" customWidth="1" min="36" max="36"/>
-    <col width="2.33" customWidth="1" min="37" max="37"/>
-    <col width="2.33" customWidth="1" min="38" max="38"/>
-    <col width="2.33" customWidth="1" min="39" max="39"/>
-    <col width="2.33" customWidth="1" min="40" max="40"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col hidden="1" width="20" customWidth="1" min="5" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" hidden="1">
-      <c r="A1" s="815" t="n"/>
-      <c r="B1" s="718" t="n"/>
-      <c r="C1" s="718" t="n"/>
-      <c r="D1" s="718" t="n"/>
-      <c r="E1" s="718" t="n"/>
-      <c r="F1" s="718" t="n"/>
-      <c r="G1" s="718" t="n"/>
-      <c r="H1" s="816" t="n"/>
-      <c r="I1" s="817" t="inlineStr">
-        <is>
-          <t>HIGH-RISK JOB READINESS REVIEW</t>
-        </is>
-      </c>
-      <c r="J1" s="718" t="n"/>
-      <c r="K1" s="718" t="n"/>
-      <c r="L1" s="718" t="n"/>
-      <c r="M1" s="718" t="n"/>
-      <c r="N1" s="718" t="n"/>
-      <c r="O1" s="718" t="n"/>
-      <c r="P1" s="718" t="n"/>
-      <c r="Q1" s="718" t="n"/>
-      <c r="R1" s="718" t="n"/>
-      <c r="S1" s="718" t="n"/>
-      <c r="T1" s="718" t="n"/>
-      <c r="U1" s="718" t="n"/>
-      <c r="V1" s="718" t="n"/>
-      <c r="W1" s="718" t="n"/>
-      <c r="X1" s="718" t="n"/>
-      <c r="Y1" s="718" t="n"/>
-      <c r="Z1" s="718" t="n"/>
-      <c r="AA1" s="718" t="n"/>
-      <c r="AB1" s="718" t="n"/>
-      <c r="AC1" s="718" t="n"/>
-      <c r="AD1" s="816" t="n"/>
-      <c r="AE1" s="500" t="inlineStr">
-        <is>
-          <t>Form Code</t>
-        </is>
-      </c>
-      <c r="AF1" s="718" t="n"/>
-      <c r="AG1" s="718" t="n"/>
-      <c r="AH1" s="818" t="n"/>
-      <c r="AI1" s="503" t="inlineStr">
-        <is>
-          <t>FRM-209</t>
-        </is>
-      </c>
-      <c r="AJ1" s="718" t="n"/>
-      <c r="AK1" s="718" t="n"/>
-      <c r="AL1" s="718" t="n"/>
-      <c r="AM1" s="718" t="n"/>
-      <c r="AN1" s="816" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="791" t="n"/>
-      <c r="C2" s="791" t="n"/>
-      <c r="D2" s="791" t="n"/>
-      <c r="E2" s="791" t="n"/>
-      <c r="F2" s="791" t="n"/>
-      <c r="G2" s="791" t="n"/>
-      <c r="H2" s="792" t="n"/>
-      <c r="I2" s="791" t="n"/>
-      <c r="J2" s="791" t="n"/>
-      <c r="K2" s="791" t="n"/>
-      <c r="L2" s="791" t="n"/>
-      <c r="M2" s="791" t="n"/>
-      <c r="N2" s="791" t="n"/>
-      <c r="O2" s="791" t="n"/>
-      <c r="P2" s="791" t="n"/>
-      <c r="Q2" s="791" t="n"/>
-      <c r="R2" s="791" t="n"/>
-      <c r="S2" s="791" t="n"/>
-      <c r="T2" s="791" t="n"/>
-      <c r="U2" s="791" t="n"/>
-      <c r="V2" s="791" t="n"/>
-      <c r="W2" s="791" t="n"/>
-      <c r="X2" s="791" t="n"/>
-      <c r="Y2" s="791" t="n"/>
-      <c r="Z2" s="791" t="n"/>
-      <c r="AA2" s="791" t="n"/>
-      <c r="AB2" s="791" t="n"/>
-      <c r="AC2" s="791" t="n"/>
-      <c r="AD2" s="792" t="n"/>
-      <c r="AE2" s="793" t="inlineStr">
-        <is>
-          <t>Revision</t>
-        </is>
-      </c>
-      <c r="AF2" s="794" t="n"/>
-      <c r="AG2" s="794" t="n"/>
-      <c r="AH2" s="795" t="n"/>
-      <c r="AI2" s="796" t="inlineStr">
-        <is>
-          <t>V0</t>
-        </is>
-      </c>
-      <c r="AJ2" s="797" t="n"/>
-      <c r="AK2" s="797" t="n"/>
-      <c r="AL2" s="797" t="n"/>
-      <c r="AM2" s="797" t="n"/>
-      <c r="AN2" s="798" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="799" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="800" t="n"/>
-      <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
-      <c r="K3" s="25" t="n"/>
-      <c r="L3" s="25" t="n"/>
-      <c r="M3" s="25" t="n"/>
-      <c r="N3" s="25" t="n"/>
-      <c r="O3" s="25" t="n"/>
-      <c r="P3" s="25" t="n"/>
-      <c r="Q3" s="25" t="n"/>
-      <c r="R3" s="25" t="n"/>
-      <c r="S3" s="25" t="n"/>
-      <c r="T3" s="25" t="n"/>
-      <c r="U3" s="25" t="n"/>
-      <c r="V3" s="25" t="n"/>
-      <c r="W3" s="25" t="n"/>
-      <c r="X3" s="25" t="n"/>
-      <c r="Y3" s="25" t="n"/>
-      <c r="Z3" s="25" t="n"/>
-      <c r="AA3" s="25" t="n"/>
-      <c r="AB3" s="25" t="n"/>
-      <c r="AC3" s="25" t="n"/>
-      <c r="AD3" s="800" t="n"/>
-      <c r="AE3" s="801" t="inlineStr">
-        <is>
-          <t>Eff. Date</t>
-        </is>
-      </c>
-      <c r="AF3" s="802" t="n"/>
-      <c r="AG3" s="802" t="n"/>
-      <c r="AH3" s="803" t="n"/>
-      <c r="AI3" s="699" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
-      <c r="AJ3" s="804" t="n"/>
-      <c r="AK3" s="804" t="n"/>
-      <c r="AL3" s="804" t="n"/>
-      <c r="AM3" s="804" t="n"/>
-      <c r="AN3" s="805" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="799" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="800" t="n"/>
-      <c r="I4" s="342" t="inlineStr">
-        <is>
-          <t>Quality Management System  ·  Controlled Document</t>
-        </is>
-      </c>
-      <c r="J4" s="25" t="n"/>
-      <c r="K4" s="25" t="n"/>
-      <c r="L4" s="25" t="n"/>
-      <c r="M4" s="25" t="n"/>
-      <c r="N4" s="25" t="n"/>
-      <c r="O4" s="25" t="n"/>
-      <c r="P4" s="25" t="n"/>
-      <c r="Q4" s="25" t="n"/>
-      <c r="R4" s="25" t="n"/>
-      <c r="S4" s="25" t="n"/>
-      <c r="T4" s="25" t="n"/>
-      <c r="U4" s="25" t="n"/>
-      <c r="V4" s="25" t="n"/>
-      <c r="W4" s="25" t="n"/>
-      <c r="X4" s="25" t="n"/>
-      <c r="Y4" s="25" t="n"/>
-      <c r="Z4" s="25" t="n"/>
-      <c r="AA4" s="25" t="n"/>
-      <c r="AB4" s="25" t="n"/>
-      <c r="AC4" s="25" t="n"/>
-      <c r="AD4" s="800" t="n"/>
-      <c r="AE4" s="801" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="AF4" s="802" t="n"/>
-      <c r="AG4" s="802" t="n"/>
-      <c r="AH4" s="803" t="n"/>
-      <c r="AI4" s="699" t="inlineStr">
-        <is>
-          <t>Planning / QA / Engineering</t>
-        </is>
-      </c>
-      <c r="AJ4" s="804" t="n"/>
-      <c r="AK4" s="804" t="n"/>
-      <c r="AL4" s="804" t="n"/>
-      <c r="AM4" s="804" t="n"/>
-      <c r="AN4" s="805" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="799" t="n"/>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="25" t="n"/>
-      <c r="H5" s="800" t="n"/>
-      <c r="I5" s="581" t="inlineStr">
-        <is>
-          <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
-        </is>
-      </c>
-      <c r="J5" s="25" t="n"/>
-      <c r="K5" s="25" t="n"/>
-      <c r="L5" s="25" t="n"/>
-      <c r="M5" s="25" t="n"/>
-      <c r="N5" s="25" t="n"/>
-      <c r="O5" s="25" t="n"/>
-      <c r="P5" s="25" t="n"/>
-      <c r="Q5" s="25" t="n"/>
-      <c r="R5" s="25" t="n"/>
-      <c r="S5" s="25" t="n"/>
-      <c r="T5" s="25" t="n"/>
-      <c r="U5" s="25" t="n"/>
-      <c r="V5" s="25" t="n"/>
-      <c r="W5" s="25" t="n"/>
-      <c r="X5" s="25" t="n"/>
-      <c r="Y5" s="25" t="n"/>
-      <c r="Z5" s="25" t="n"/>
-      <c r="AA5" s="25" t="n"/>
-      <c r="AB5" s="25" t="n"/>
-      <c r="AC5" s="25" t="n"/>
-      <c r="AD5" s="800" t="n"/>
-      <c r="AE5" s="801" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="AF5" s="802" t="n"/>
-      <c r="AG5" s="802" t="n"/>
-      <c r="AH5" s="803" t="n"/>
-      <c r="AI5" s="699" t="inlineStr">
-        <is>
-          <t>General Manager</t>
-        </is>
-      </c>
-      <c r="AJ5" s="804" t="n"/>
-      <c r="AK5" s="804" t="n"/>
-      <c r="AL5" s="804" t="n"/>
-      <c r="AM5" s="804" t="n"/>
-      <c r="AN5" s="805" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="819" t="n"/>
-      <c r="B6" s="820" t="n"/>
-      <c r="C6" s="820" t="n"/>
-      <c r="D6" s="820" t="n"/>
-      <c r="E6" s="820" t="n"/>
-      <c r="F6" s="820" t="n"/>
-      <c r="G6" s="820" t="n"/>
-      <c r="H6" s="821" t="n"/>
-      <c r="I6" s="820" t="n"/>
-      <c r="J6" s="820" t="n"/>
-      <c r="K6" s="820" t="n"/>
-      <c r="L6" s="820" t="n"/>
-      <c r="M6" s="820" t="n"/>
-      <c r="N6" s="820" t="n"/>
-      <c r="O6" s="820" t="n"/>
-      <c r="P6" s="820" t="n"/>
-      <c r="Q6" s="820" t="n"/>
-      <c r="R6" s="820" t="n"/>
-      <c r="S6" s="820" t="n"/>
-      <c r="T6" s="820" t="n"/>
-      <c r="U6" s="820" t="n"/>
-      <c r="V6" s="820" t="n"/>
-      <c r="W6" s="820" t="n"/>
-      <c r="X6" s="820" t="n"/>
-      <c r="Y6" s="820" t="n"/>
-      <c r="Z6" s="820" t="n"/>
-      <c r="AA6" s="820" t="n"/>
-      <c r="AB6" s="820" t="n"/>
-      <c r="AC6" s="820" t="n"/>
-      <c r="AD6" s="821" t="n"/>
-      <c r="AE6" s="822" t="n"/>
-      <c r="AF6" s="822" t="n"/>
-      <c r="AG6" s="822" t="n"/>
-      <c r="AH6" s="823" t="n"/>
-      <c r="AI6" s="824" t="n"/>
-      <c r="AJ6" s="824" t="n"/>
-      <c r="AK6" s="824" t="n"/>
-      <c r="AL6" s="824" t="n"/>
-      <c r="AM6" s="824" t="n"/>
-      <c r="AN6" s="825" t="n"/>
-    </row>
-    <row r="7" ht="4" customHeight="1">
-      <c r="A7" s="826" t="n"/>
-      <c r="B7" s="826" t="n"/>
-      <c r="C7" s="826" t="n"/>
-      <c r="D7" s="826" t="n"/>
-      <c r="E7" s="827" t="n"/>
-      <c r="F7" s="827" t="n"/>
-      <c r="G7" s="827" t="n"/>
-      <c r="H7" s="827" t="n"/>
-      <c r="I7" s="827" t="n"/>
-      <c r="J7" s="827" t="n"/>
-      <c r="K7" s="827" t="n"/>
-      <c r="L7" s="827" t="n"/>
-      <c r="M7" s="827" t="n"/>
-      <c r="N7" s="827" t="n"/>
-      <c r="O7" s="827" t="n"/>
-      <c r="P7" s="827" t="n"/>
-      <c r="Q7" s="827" t="n"/>
-      <c r="R7" s="827" t="n"/>
-      <c r="S7" s="827" t="n"/>
-      <c r="T7" s="827" t="n"/>
-      <c r="U7" s="827" t="n"/>
-      <c r="V7" s="827" t="n"/>
-      <c r="W7" s="827" t="n"/>
-      <c r="X7" s="827" t="n"/>
-      <c r="Y7" s="827" t="n"/>
-      <c r="Z7" s="827" t="n"/>
-      <c r="AA7" s="827" t="n"/>
-      <c r="AB7" s="827" t="n"/>
-      <c r="AC7" s="827" t="n"/>
-      <c r="AD7" s="827" t="n"/>
-      <c r="AE7" s="827" t="n"/>
-      <c r="AF7" s="827" t="n"/>
-      <c r="AG7" s="827" t="n"/>
-      <c r="AH7" s="827" t="n"/>
-      <c r="AI7" s="827" t="n"/>
-      <c r="AJ7" s="827" t="n"/>
-      <c r="AK7" s="827" t="n"/>
-      <c r="AL7" s="827" t="n"/>
-      <c r="AM7" s="827" t="n"/>
-      <c r="AN7" s="827" t="n"/>
-    </row>
-    <row r="8" hidden="1">
-      <c r="A8" s="402" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>VAL_RESULT_CORE</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>VAL_DECISION_GATE_CORE</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>VAL_STATUS_CORE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>VAL_RISK_LEVEL_CORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B8" s="402" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="C8" s="402" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="D8" s="402" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="E8" s="790" t="n"/>
-      <c r="F8" s="790" t="n"/>
-      <c r="G8" s="790" t="n"/>
-      <c r="H8" s="790" t="n"/>
-      <c r="I8" s="790" t="n"/>
-      <c r="J8" s="790" t="n"/>
-      <c r="K8" s="790" t="n"/>
-      <c r="L8" s="790" t="n"/>
-      <c r="M8" s="790" t="n"/>
-      <c r="N8" s="790" t="n"/>
-      <c r="O8" s="790" t="n"/>
-      <c r="P8" s="790" t="n"/>
-      <c r="Q8" s="790" t="n"/>
-      <c r="R8" s="790" t="n"/>
-      <c r="S8" s="790" t="n"/>
-      <c r="T8" s="790" t="n"/>
-      <c r="U8" s="790" t="n"/>
-      <c r="V8" s="790" t="n"/>
-      <c r="W8" s="790" t="n"/>
-      <c r="X8" s="790" t="n"/>
-      <c r="Y8" s="790" t="n"/>
-      <c r="Z8" s="790" t="n"/>
-      <c r="AA8" s="790" t="n"/>
-      <c r="AB8" s="790" t="n"/>
-      <c r="AC8" s="790" t="n"/>
-      <c r="AD8" s="790" t="n"/>
-      <c r="AE8" s="790" t="n"/>
-      <c r="AF8" s="790" t="n"/>
-      <c r="AG8" s="790" t="n"/>
-      <c r="AH8" s="790" t="n"/>
-      <c r="AI8" s="790" t="n"/>
-      <c r="AJ8" s="790" t="n"/>
-      <c r="AK8" s="790" t="n"/>
-      <c r="AL8" s="790" t="n"/>
-      <c r="AM8" s="790" t="n"/>
-      <c r="AN8" s="790" t="n"/>
-    </row>
-    <row r="9" hidden="1">
-      <c r="A9" s="402" t="inlineStr">
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="B9" s="402" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="C9" s="402" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>IN PROGRESS</t>
         </is>
       </c>
-      <c r="D9" s="402" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="E9" s="790" t="n"/>
-      <c r="F9" s="790" t="n"/>
-      <c r="G9" s="790" t="n"/>
-      <c r="H9" s="790" t="n"/>
-      <c r="I9" s="790" t="n"/>
-      <c r="J9" s="790" t="n"/>
-      <c r="K9" s="790" t="n"/>
-      <c r="L9" s="790" t="n"/>
-      <c r="M9" s="790" t="n"/>
-      <c r="N9" s="790" t="n"/>
-      <c r="O9" s="790" t="n"/>
-      <c r="P9" s="790" t="n"/>
-      <c r="Q9" s="790" t="n"/>
-      <c r="R9" s="790" t="n"/>
-      <c r="S9" s="790" t="n"/>
-      <c r="T9" s="790" t="n"/>
-      <c r="U9" s="790" t="n"/>
-      <c r="V9" s="790" t="n"/>
-      <c r="W9" s="790" t="n"/>
-      <c r="X9" s="790" t="n"/>
-      <c r="Y9" s="790" t="n"/>
-      <c r="Z9" s="790" t="n"/>
-      <c r="AA9" s="790" t="n"/>
-      <c r="AB9" s="790" t="n"/>
-      <c r="AC9" s="790" t="n"/>
-      <c r="AD9" s="790" t="n"/>
-      <c r="AE9" s="790" t="n"/>
-      <c r="AF9" s="790" t="n"/>
-      <c r="AG9" s="790" t="n"/>
-      <c r="AH9" s="790" t="n"/>
-      <c r="AI9" s="790" t="n"/>
-      <c r="AJ9" s="790" t="n"/>
-      <c r="AK9" s="790" t="n"/>
-      <c r="AL9" s="790" t="n"/>
-      <c r="AM9" s="790" t="n"/>
-      <c r="AN9" s="790" t="n"/>
-    </row>
-    <row r="10" hidden="1">
-      <c r="A10" s="402" t="inlineStr">
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="B10" s="402" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="C10" s="402" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="D10" s="402" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="E10" s="790" t="n"/>
-      <c r="F10" s="790" t="n"/>
-      <c r="G10" s="790" t="n"/>
-      <c r="H10" s="790" t="n"/>
-      <c r="I10" s="790" t="n"/>
-      <c r="J10" s="790" t="n"/>
-      <c r="K10" s="790" t="n"/>
-      <c r="L10" s="790" t="n"/>
-      <c r="M10" s="790" t="n"/>
-      <c r="N10" s="790" t="n"/>
-      <c r="O10" s="790" t="n"/>
-      <c r="P10" s="790" t="n"/>
-      <c r="Q10" s="790" t="n"/>
-      <c r="R10" s="790" t="n"/>
-      <c r="S10" s="790" t="n"/>
-      <c r="T10" s="790" t="n"/>
-      <c r="U10" s="790" t="n"/>
-      <c r="V10" s="790" t="n"/>
-      <c r="W10" s="790" t="n"/>
-      <c r="X10" s="790" t="n"/>
-      <c r="Y10" s="790" t="n"/>
-      <c r="Z10" s="790" t="n"/>
-      <c r="AA10" s="790" t="n"/>
-      <c r="AB10" s="790" t="n"/>
-      <c r="AC10" s="790" t="n"/>
-      <c r="AD10" s="790" t="n"/>
-      <c r="AE10" s="790" t="n"/>
-      <c r="AF10" s="790" t="n"/>
-      <c r="AG10" s="790" t="n"/>
-      <c r="AH10" s="790" t="n"/>
-      <c r="AI10" s="790" t="n"/>
-      <c r="AJ10" s="790" t="n"/>
-      <c r="AK10" s="790" t="n"/>
-      <c r="AL10" s="790" t="n"/>
-      <c r="AM10" s="790" t="n"/>
-      <c r="AN10" s="790" t="n"/>
-    </row>
-    <row r="11" hidden="1">
-      <c r="A11" s="402" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="B11" s="402" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
-      <c r="C11" s="402" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>MONITORING</t>
         </is>
       </c>
-      <c r="D11" s="402" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="E11" s="790" t="n"/>
-      <c r="F11" s="790" t="n"/>
-      <c r="G11" s="790" t="n"/>
-      <c r="H11" s="790" t="n"/>
-      <c r="I11" s="790" t="n"/>
-      <c r="J11" s="790" t="n"/>
-      <c r="K11" s="790" t="n"/>
-      <c r="L11" s="790" t="n"/>
-      <c r="M11" s="790" t="n"/>
-      <c r="N11" s="790" t="n"/>
-      <c r="O11" s="790" t="n"/>
-      <c r="P11" s="790" t="n"/>
-      <c r="Q11" s="790" t="n"/>
-      <c r="R11" s="790" t="n"/>
-      <c r="S11" s="790" t="n"/>
-      <c r="T11" s="790" t="n"/>
-      <c r="U11" s="790" t="n"/>
-      <c r="V11" s="790" t="n"/>
-      <c r="W11" s="790" t="n"/>
-      <c r="X11" s="790" t="n"/>
-      <c r="Y11" s="790" t="n"/>
-      <c r="Z11" s="790" t="n"/>
-      <c r="AA11" s="790" t="n"/>
-      <c r="AB11" s="790" t="n"/>
-      <c r="AC11" s="790" t="n"/>
-      <c r="AD11" s="790" t="n"/>
-      <c r="AE11" s="790" t="n"/>
-      <c r="AF11" s="790" t="n"/>
-      <c r="AG11" s="790" t="n"/>
-      <c r="AH11" s="790" t="n"/>
-      <c r="AI11" s="790" t="n"/>
-      <c r="AJ11" s="790" t="n"/>
-      <c r="AK11" s="790" t="n"/>
-      <c r="AL11" s="790" t="n"/>
-      <c r="AM11" s="790" t="n"/>
-      <c r="AN11" s="790" t="n"/>
-    </row>
-    <row r="12" hidden="1">
-      <c r="A12" s="790" t="n"/>
-      <c r="B12" s="790" t="n"/>
-      <c r="C12" s="402" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
         <is>
           <t>SUPERSEDED</t>
         </is>
       </c>
-      <c r="D12" s="790" t="n"/>
-      <c r="E12" s="790" t="n"/>
-      <c r="F12" s="790" t="n"/>
-      <c r="G12" s="790" t="n"/>
-      <c r="H12" s="790" t="n"/>
-      <c r="I12" s="790" t="n"/>
-      <c r="J12" s="790" t="n"/>
-      <c r="K12" s="790" t="n"/>
-      <c r="L12" s="790" t="n"/>
-      <c r="M12" s="790" t="n"/>
-      <c r="N12" s="790" t="n"/>
-      <c r="O12" s="790" t="n"/>
-      <c r="P12" s="790" t="n"/>
-      <c r="Q12" s="790" t="n"/>
-      <c r="R12" s="790" t="n"/>
-      <c r="S12" s="790" t="n"/>
-      <c r="T12" s="790" t="n"/>
-      <c r="U12" s="790" t="n"/>
-      <c r="V12" s="790" t="n"/>
-      <c r="W12" s="790" t="n"/>
-      <c r="X12" s="790" t="n"/>
-      <c r="Y12" s="790" t="n"/>
-      <c r="Z12" s="790" t="n"/>
-      <c r="AA12" s="790" t="n"/>
-      <c r="AB12" s="790" t="n"/>
-      <c r="AC12" s="790" t="n"/>
-      <c r="AD12" s="790" t="n"/>
-      <c r="AE12" s="790" t="n"/>
-      <c r="AF12" s="790" t="n"/>
-      <c r="AG12" s="790" t="n"/>
-      <c r="AH12" s="790" t="n"/>
-      <c r="AI12" s="790" t="n"/>
-      <c r="AJ12" s="790" t="n"/>
-      <c r="AK12" s="790" t="n"/>
-      <c r="AL12" s="790" t="n"/>
-      <c r="AM12" s="790" t="n"/>
-      <c r="AN12" s="790" t="n"/>
-    </row>
-    <row r="13" hidden="1">
-      <c r="A13" s="790" t="n"/>
-      <c r="B13" s="790" t="n"/>
-      <c r="C13" s="402" t="inlineStr">
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
         <is>
           <t>VOID</t>
         </is>
       </c>
-      <c r="D13" s="790" t="n"/>
-      <c r="E13" s="790" t="n"/>
-      <c r="F13" s="790" t="n"/>
-      <c r="G13" s="790" t="n"/>
-      <c r="H13" s="790" t="n"/>
-      <c r="I13" s="790" t="n"/>
-      <c r="J13" s="790" t="n"/>
-      <c r="K13" s="790" t="n"/>
-      <c r="L13" s="790" t="n"/>
-      <c r="M13" s="790" t="n"/>
-      <c r="N13" s="790" t="n"/>
-      <c r="O13" s="790" t="n"/>
-      <c r="P13" s="790" t="n"/>
-      <c r="Q13" s="790" t="n"/>
-      <c r="R13" s="790" t="n"/>
-      <c r="S13" s="790" t="n"/>
-      <c r="T13" s="790" t="n"/>
-      <c r="U13" s="790" t="n"/>
-      <c r="V13" s="790" t="n"/>
-      <c r="W13" s="790" t="n"/>
-      <c r="X13" s="790" t="n"/>
-      <c r="Y13" s="790" t="n"/>
-      <c r="Z13" s="790" t="n"/>
-      <c r="AA13" s="790" t="n"/>
-      <c r="AB13" s="790" t="n"/>
-      <c r="AC13" s="790" t="n"/>
-      <c r="AD13" s="790" t="n"/>
-      <c r="AE13" s="790" t="n"/>
-      <c r="AF13" s="790" t="n"/>
-      <c r="AG13" s="790" t="n"/>
-      <c r="AH13" s="790" t="n"/>
-      <c r="AI13" s="790" t="n"/>
-      <c r="AJ13" s="790" t="n"/>
-      <c r="AK13" s="790" t="n"/>
-      <c r="AL13" s="790" t="n"/>
-      <c r="AM13" s="790" t="n"/>
-      <c r="AN13" s="790" t="n"/>
-    </row>
-    <row r="14" hidden="1">
-      <c r="A14" s="790" t="n"/>
-      <c r="B14" s="790" t="n"/>
-      <c r="C14" s="790" t="n"/>
-      <c r="D14" s="790" t="n"/>
-      <c r="E14" s="790" t="n"/>
-      <c r="F14" s="790" t="n"/>
-      <c r="G14" s="790" t="n"/>
-      <c r="H14" s="790" t="n"/>
-      <c r="I14" s="790" t="n"/>
-      <c r="J14" s="790" t="n"/>
-      <c r="K14" s="790" t="n"/>
-      <c r="L14" s="790" t="n"/>
-      <c r="M14" s="790" t="n"/>
-      <c r="N14" s="790" t="n"/>
-      <c r="O14" s="790" t="n"/>
-      <c r="P14" s="790" t="n"/>
-      <c r="Q14" s="790" t="n"/>
-      <c r="R14" s="790" t="n"/>
-      <c r="S14" s="790" t="n"/>
-      <c r="T14" s="790" t="n"/>
-      <c r="U14" s="790" t="n"/>
-      <c r="V14" s="790" t="n"/>
-      <c r="W14" s="790" t="n"/>
-      <c r="X14" s="790" t="n"/>
-      <c r="Y14" s="790" t="n"/>
-      <c r="Z14" s="790" t="n"/>
-      <c r="AA14" s="790" t="n"/>
-      <c r="AB14" s="790" t="n"/>
-      <c r="AC14" s="790" t="n"/>
-      <c r="AD14" s="790" t="n"/>
-      <c r="AE14" s="790" t="n"/>
-      <c r="AF14" s="790" t="n"/>
-      <c r="AG14" s="790" t="n"/>
-      <c r="AH14" s="790" t="n"/>
-      <c r="AI14" s="790" t="n"/>
-      <c r="AJ14" s="790" t="n"/>
-      <c r="AK14" s="790" t="n"/>
-      <c r="AL14" s="790" t="n"/>
-      <c r="AM14" s="790" t="n"/>
-      <c r="AN14" s="790" t="n"/>
-    </row>
-    <row r="15" hidden="1">
-      <c r="A15" s="790" t="n"/>
-      <c r="B15" s="790" t="n"/>
-      <c r="C15" s="790" t="n"/>
-      <c r="D15" s="790" t="n"/>
-      <c r="E15" s="790" t="n"/>
-      <c r="F15" s="790" t="n"/>
-      <c r="G15" s="790" t="n"/>
-      <c r="H15" s="790" t="n"/>
-      <c r="I15" s="790" t="n"/>
-      <c r="J15" s="790" t="n"/>
-      <c r="K15" s="790" t="n"/>
-      <c r="L15" s="790" t="n"/>
-      <c r="M15" s="790" t="n"/>
-      <c r="N15" s="790" t="n"/>
-      <c r="O15" s="790" t="n"/>
-      <c r="P15" s="790" t="n"/>
-      <c r="Q15" s="790" t="n"/>
-      <c r="R15" s="790" t="n"/>
-      <c r="S15" s="790" t="n"/>
-      <c r="T15" s="790" t="n"/>
-      <c r="U15" s="790" t="n"/>
-      <c r="V15" s="790" t="n"/>
-      <c r="W15" s="790" t="n"/>
-      <c r="X15" s="790" t="n"/>
-      <c r="Y15" s="790" t="n"/>
-      <c r="Z15" s="790" t="n"/>
-      <c r="AA15" s="790" t="n"/>
-      <c r="AB15" s="790" t="n"/>
-      <c r="AC15" s="790" t="n"/>
-      <c r="AD15" s="790" t="n"/>
-      <c r="AE15" s="790" t="n"/>
-      <c r="AF15" s="790" t="n"/>
-      <c r="AG15" s="790" t="n"/>
-      <c r="AH15" s="790" t="n"/>
-      <c r="AI15" s="790" t="n"/>
-      <c r="AJ15" s="790" t="n"/>
-      <c r="AK15" s="790" t="n"/>
-      <c r="AL15" s="790" t="n"/>
-      <c r="AM15" s="790" t="n"/>
-      <c r="AN15" s="790" t="n"/>
-    </row>
-    <row r="16" hidden="1">
-      <c r="A16" s="790" t="n"/>
-      <c r="B16" s="790" t="n"/>
-      <c r="C16" s="790" t="n"/>
-      <c r="D16" s="790" t="n"/>
-      <c r="E16" s="790" t="n"/>
-      <c r="F16" s="790" t="n"/>
-      <c r="G16" s="790" t="n"/>
-      <c r="H16" s="790" t="n"/>
-      <c r="I16" s="790" t="n"/>
-      <c r="J16" s="790" t="n"/>
-      <c r="K16" s="790" t="n"/>
-      <c r="L16" s="790" t="n"/>
-      <c r="M16" s="790" t="n"/>
-      <c r="N16" s="790" t="n"/>
-      <c r="O16" s="790" t="n"/>
-      <c r="P16" s="790" t="n"/>
-      <c r="Q16" s="790" t="n"/>
-      <c r="R16" s="790" t="n"/>
-      <c r="S16" s="790" t="n"/>
-      <c r="T16" s="790" t="n"/>
-      <c r="U16" s="790" t="n"/>
-      <c r="V16" s="790" t="n"/>
-      <c r="W16" s="790" t="n"/>
-      <c r="X16" s="790" t="n"/>
-      <c r="Y16" s="790" t="n"/>
-      <c r="Z16" s="790" t="n"/>
-      <c r="AA16" s="790" t="n"/>
-      <c r="AB16" s="790" t="n"/>
-      <c r="AC16" s="790" t="n"/>
-      <c r="AD16" s="790" t="n"/>
-      <c r="AE16" s="790" t="n"/>
-      <c r="AF16" s="790" t="n"/>
-      <c r="AG16" s="790" t="n"/>
-      <c r="AH16" s="790" t="n"/>
-      <c r="AI16" s="790" t="n"/>
-      <c r="AJ16" s="790" t="n"/>
-      <c r="AK16" s="790" t="n"/>
-      <c r="AL16" s="790" t="n"/>
-      <c r="AM16" s="790" t="n"/>
-      <c r="AN16" s="790" t="n"/>
-    </row>
+    </row>
+    <row r="8" hidden="1"/>
+    <row r="9" hidden="1"/>
+    <row r="10" hidden="1"/>
+    <row r="11" hidden="1"/>
+    <row r="12" hidden="1"/>
+    <row r="13" hidden="1"/>
+    <row r="14" hidden="1"/>
+    <row r="15" hidden="1"/>
+    <row r="16" hidden="1"/>
     <row r="17" hidden="1"/>
     <row r="18" hidden="1"/>
     <row r="19" hidden="1"/>
@@ -11435,25 +8122,7 @@
     <row r="199" hidden="1"/>
     <row r="200" hidden="1"/>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="AI2:AN2"/>
-    <mergeCell ref="I1:AD3"/>
-    <mergeCell ref="AE4:AH4"/>
-    <mergeCell ref="AI1:AN1"/>
-    <mergeCell ref="I5:AD5"/>
-    <mergeCell ref="AE3:AH3"/>
-    <mergeCell ref="AI5:AN5"/>
-    <mergeCell ref="A1:H5"/>
-    <mergeCell ref="AI4:AN4"/>
-    <mergeCell ref="AE2:AH2"/>
-    <mergeCell ref="I4:AD4"/>
-    <mergeCell ref="AI3:AN3"/>
-    <mergeCell ref="AE1:AH1"/>
-    <mergeCell ref="AE5:AH5"/>
-  </mergeCells>
-  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -11461,57 +8130,340 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col hidden="1" width="13" customWidth="1" min="5" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>REF_CUSTOMER_MASTER</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>REF_PART_REV_MASTER</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>REF_JOB_WO_MASTER</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>REF_OWNER_PERSON_MASTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CUST-001 Alpha Semi</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PN-1001 / Rev.A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>JOB-240001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Planning Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CUST-002 NovaFab</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PN-1002 / Rev.B</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>JOB-240002</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Production Supervisor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CUST-003 Orion Tech</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PN-1003 / Rev.C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>JOB-240003</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Engineering Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Setup Technician</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1"/>
+    <row r="8" hidden="1"/>
+    <row r="9" hidden="1"/>
+    <row r="10" hidden="1"/>
+    <row r="11" hidden="1"/>
+    <row r="12" hidden="1"/>
+    <row r="13" hidden="1"/>
+    <row r="14" hidden="1"/>
+    <row r="15" hidden="1"/>
+    <row r="16" hidden="1"/>
+    <row r="17" hidden="1"/>
+    <row r="18" hidden="1"/>
+    <row r="19" hidden="1"/>
+    <row r="20" hidden="1"/>
+    <row r="21" hidden="1"/>
+    <row r="22" hidden="1"/>
+    <row r="23" hidden="1"/>
+    <row r="24" hidden="1"/>
+    <row r="25" hidden="1"/>
+    <row r="26" hidden="1"/>
+    <row r="27" hidden="1"/>
+    <row r="28" hidden="1"/>
+    <row r="29" hidden="1"/>
+    <row r="30" hidden="1"/>
+    <row r="31" hidden="1"/>
+    <row r="32" hidden="1"/>
+    <row r="33" hidden="1"/>
+    <row r="34" hidden="1"/>
+    <row r="35" hidden="1"/>
+    <row r="36" hidden="1"/>
+    <row r="37" hidden="1"/>
+    <row r="38" hidden="1"/>
+    <row r="39" hidden="1"/>
+    <row r="40" hidden="1"/>
+    <row r="41" hidden="1"/>
+    <row r="42" hidden="1"/>
+    <row r="43" hidden="1"/>
+    <row r="44" hidden="1"/>
+    <row r="45" hidden="1"/>
+    <row r="46" hidden="1"/>
+    <row r="47" hidden="1"/>
+    <row r="48" hidden="1"/>
+    <row r="49" hidden="1"/>
+    <row r="50" hidden="1"/>
+    <row r="51" hidden="1"/>
+    <row r="52" hidden="1"/>
+    <row r="53" hidden="1"/>
+    <row r="54" hidden="1"/>
+    <row r="55" hidden="1"/>
+    <row r="56" hidden="1"/>
+    <row r="57" hidden="1"/>
+    <row r="58" hidden="1"/>
+    <row r="59" hidden="1"/>
+    <row r="60" hidden="1"/>
+    <row r="61" hidden="1"/>
+    <row r="62" hidden="1"/>
+    <row r="63" hidden="1"/>
+    <row r="64" hidden="1"/>
+    <row r="65" hidden="1"/>
+    <row r="66" hidden="1"/>
+    <row r="67" hidden="1"/>
+    <row r="68" hidden="1"/>
+    <row r="69" hidden="1"/>
+    <row r="70" hidden="1"/>
+    <row r="71" hidden="1"/>
+    <row r="72" hidden="1"/>
+    <row r="73" hidden="1"/>
+    <row r="74" hidden="1"/>
+    <row r="75" hidden="1"/>
+    <row r="76" hidden="1"/>
+    <row r="77" hidden="1"/>
+    <row r="78" hidden="1"/>
+    <row r="79" hidden="1"/>
+    <row r="80" hidden="1"/>
+    <row r="81" hidden="1"/>
+    <row r="82" hidden="1"/>
+    <row r="83" hidden="1"/>
+    <row r="84" hidden="1"/>
+    <row r="85" hidden="1"/>
+    <row r="86" hidden="1"/>
+    <row r="87" hidden="1"/>
+    <row r="88" hidden="1"/>
+    <row r="89" hidden="1"/>
+    <row r="90" hidden="1"/>
+    <row r="91" hidden="1"/>
+    <row r="92" hidden="1"/>
+    <row r="93" hidden="1"/>
+    <row r="94" hidden="1"/>
+    <row r="95" hidden="1"/>
+    <row r="96" hidden="1"/>
+    <row r="97" hidden="1"/>
+    <row r="98" hidden="1"/>
+    <row r="99" hidden="1"/>
+    <row r="100" hidden="1"/>
+    <row r="101" hidden="1"/>
+    <row r="102" hidden="1"/>
+    <row r="103" hidden="1"/>
+    <row r="104" hidden="1"/>
+    <row r="105" hidden="1"/>
+    <row r="106" hidden="1"/>
+    <row r="107" hidden="1"/>
+    <row r="108" hidden="1"/>
+    <row r="109" hidden="1"/>
+    <row r="110" hidden="1"/>
+    <row r="111" hidden="1"/>
+    <row r="112" hidden="1"/>
+    <row r="113" hidden="1"/>
+    <row r="114" hidden="1"/>
+    <row r="115" hidden="1"/>
+    <row r="116" hidden="1"/>
+    <row r="117" hidden="1"/>
+    <row r="118" hidden="1"/>
+    <row r="119" hidden="1"/>
+    <row r="120" hidden="1"/>
+    <row r="121" hidden="1"/>
+    <row r="122" hidden="1"/>
+    <row r="123" hidden="1"/>
+    <row r="124" hidden="1"/>
+    <row r="125" hidden="1"/>
+    <row r="126" hidden="1"/>
+    <row r="127" hidden="1"/>
+    <row r="128" hidden="1"/>
+    <row r="129" hidden="1"/>
+    <row r="130" hidden="1"/>
+    <row r="131" hidden="1"/>
+    <row r="132" hidden="1"/>
+    <row r="133" hidden="1"/>
+    <row r="134" hidden="1"/>
+    <row r="135" hidden="1"/>
+    <row r="136" hidden="1"/>
+    <row r="137" hidden="1"/>
+    <row r="138" hidden="1"/>
+    <row r="139" hidden="1"/>
+    <row r="140" hidden="1"/>
+    <row r="141" hidden="1"/>
+    <row r="142" hidden="1"/>
+    <row r="143" hidden="1"/>
+    <row r="144" hidden="1"/>
+    <row r="145" hidden="1"/>
+    <row r="146" hidden="1"/>
+    <row r="147" hidden="1"/>
+    <row r="148" hidden="1"/>
+    <row r="149" hidden="1"/>
+    <row r="150" hidden="1"/>
+    <row r="151" hidden="1"/>
+    <row r="152" hidden="1"/>
+    <row r="153" hidden="1"/>
+    <row r="154" hidden="1"/>
+    <row r="155" hidden="1"/>
+    <row r="156" hidden="1"/>
+    <row r="157" hidden="1"/>
+    <row r="158" hidden="1"/>
+    <row r="159" hidden="1"/>
+    <row r="160" hidden="1"/>
+    <row r="161" hidden="1"/>
+    <row r="162" hidden="1"/>
+    <row r="163" hidden="1"/>
+    <row r="164" hidden="1"/>
+    <row r="165" hidden="1"/>
+    <row r="166" hidden="1"/>
+    <row r="167" hidden="1"/>
+    <row r="168" hidden="1"/>
+    <row r="169" hidden="1"/>
+    <row r="170" hidden="1"/>
+    <row r="171" hidden="1"/>
+    <row r="172" hidden="1"/>
+    <row r="173" hidden="1"/>
+    <row r="174" hidden="1"/>
+    <row r="175" hidden="1"/>
+    <row r="176" hidden="1"/>
+    <row r="177" hidden="1"/>
+    <row r="178" hidden="1"/>
+    <row r="179" hidden="1"/>
+    <row r="180" hidden="1"/>
+    <row r="181" hidden="1"/>
+    <row r="182" hidden="1"/>
+    <row r="183" hidden="1"/>
+    <row r="184" hidden="1"/>
+    <row r="185" hidden="1"/>
+    <row r="186" hidden="1"/>
+    <row r="187" hidden="1"/>
+    <row r="188" hidden="1"/>
+    <row r="189" hidden="1"/>
+    <row r="190" hidden="1"/>
+    <row r="191" hidden="1"/>
+    <row r="192" hidden="1"/>
+    <row r="193" hidden="1"/>
+    <row r="194" hidden="1"/>
+    <row r="195" hidden="1"/>
+    <row r="196" hidden="1"/>
+    <row r="197" hidden="1"/>
+    <row r="198" hidden="1"/>
+    <row r="199" hidden="1"/>
+    <row r="200" hidden="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN28"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2.33" customWidth="1" min="1" max="1"/>
-    <col width="2.33" customWidth="1" min="2" max="2"/>
-    <col width="2.33" customWidth="1" min="3" max="3"/>
-    <col width="2.33" customWidth="1" min="4" max="4"/>
-    <col width="2.33" customWidth="1" min="5" max="5"/>
-    <col width="2.33" customWidth="1" min="6" max="6"/>
-    <col width="2.33" customWidth="1" min="7" max="7"/>
-    <col width="2.33" customWidth="1" min="8" max="8"/>
-    <col width="2.33" customWidth="1" min="9" max="9"/>
-    <col hidden="1" outlineLevel="1" width="2.33" customWidth="1" min="10" max="16384"/>
-    <col width="2.33" customWidth="1" min="11" max="11"/>
-    <col width="2.33" customWidth="1" min="12" max="12"/>
-    <col width="2.33" customWidth="1" min="13" max="13"/>
-    <col width="2.33" customWidth="1" min="14" max="14"/>
-    <col width="2.33" customWidth="1" min="15" max="15"/>
-    <col width="2.33" customWidth="1" min="16" max="16"/>
-    <col width="2.33" customWidth="1" min="17" max="17"/>
-    <col width="2.33" customWidth="1" min="18" max="18"/>
-    <col width="2.33" customWidth="1" min="19" max="19"/>
-    <col width="2.33" customWidth="1" min="20" max="20"/>
-    <col width="2.33" customWidth="1" min="21" max="21"/>
-    <col width="2.33" customWidth="1" min="22" max="22"/>
-    <col width="2.33" customWidth="1" min="23" max="23"/>
-    <col width="2.33" customWidth="1" min="24" max="24"/>
-    <col width="2.33" customWidth="1" min="25" max="25"/>
-    <col width="2.33" customWidth="1" min="26" max="26"/>
-    <col width="2.33" customWidth="1" min="27" max="27"/>
-    <col width="2.33" customWidth="1" min="28" max="28"/>
-    <col width="2.33" customWidth="1" min="29" max="29"/>
-    <col width="2.33" customWidth="1" min="30" max="30"/>
-    <col width="2.33" customWidth="1" min="31" max="31"/>
-    <col width="2.33" customWidth="1" min="32" max="32"/>
-    <col width="2.33" customWidth="1" min="33" max="33"/>
-    <col width="2.33" customWidth="1" min="34" max="34"/>
-    <col width="2.33" customWidth="1" min="35" max="35"/>
-    <col width="2.33" customWidth="1" min="36" max="36"/>
-    <col width="2.33" customWidth="1" min="37" max="37"/>
-    <col width="2.33" customWidth="1" min="38" max="38"/>
-    <col width="2.33" customWidth="1" min="39" max="39"/>
-    <col width="2.33" customWidth="1" min="40" max="40"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="13.53" customWidth="1" min="2" max="2"/>
+    <col width="16.23" customWidth="1" min="3" max="3"/>
+    <col width="16.23" customWidth="1" min="4" max="4"/>
+    <col width="8.119999999999999" customWidth="1" min="5" max="5"/>
+    <col width="8.789999999999999" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="8.119999999999999" customWidth="1" min="8" max="8"/>
+    <col width="10.82" customWidth="1" min="9" max="9"/>
+    <col hidden="1" outlineLevel="1" width="13" customWidth="1" min="10" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" hidden="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="386" t="n"/>
       <c r="B1" s="319" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="387" t="inlineStr">
         <is>
           <t>RISKS / ACTIONS REGISTER</t>
         </is>
@@ -11519,659 +8471,257 @@
       <c r="D1" s="268" t="n"/>
       <c r="E1" s="268" t="n"/>
       <c r="F1" s="268" t="n"/>
-      <c r="G1" s="268" t="n"/>
-      <c r="H1" s="675" t="inlineStr">
+      <c r="G1" s="319" t="n"/>
+      <c r="H1" s="337" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="I1" s="676" t="inlineStr">
+      <c r="I1" s="338" t="inlineStr">
         <is>
           <t>FRM-209</t>
         </is>
       </c>
-      <c r="J1" s="676" t="n"/>
-      <c r="K1" s="676" t="n"/>
-      <c r="L1" s="676" t="n"/>
-      <c r="M1" s="676" t="n"/>
-      <c r="N1" s="676" t="n"/>
-      <c r="O1" s="676" t="n"/>
-      <c r="P1" s="676" t="n"/>
-      <c r="Q1" s="676" t="n"/>
-      <c r="R1" s="676" t="n"/>
-      <c r="S1" s="676" t="n"/>
-      <c r="T1" s="676" t="n"/>
-      <c r="U1" s="676" t="n"/>
-      <c r="V1" s="676" t="n"/>
-      <c r="W1" s="676" t="n"/>
-      <c r="X1" s="676" t="n"/>
-      <c r="Y1" s="676" t="n"/>
-      <c r="Z1" s="676" t="n"/>
-      <c r="AA1" s="676" t="n"/>
-      <c r="AB1" s="676" t="n"/>
-      <c r="AC1" s="676" t="n"/>
-      <c r="AD1" s="676" t="n"/>
-      <c r="AE1" s="677" t="n"/>
-      <c r="AF1" s="677" t="n"/>
-      <c r="AG1" s="677" t="n"/>
-      <c r="AH1" s="677" t="n"/>
-      <c r="AI1" s="634" t="n"/>
-      <c r="AJ1" s="634" t="n"/>
-      <c r="AK1" s="634" t="n"/>
-      <c r="AL1" s="634" t="n"/>
-      <c r="AM1" s="634" t="n"/>
-      <c r="AN1" s="678" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="791" t="n"/>
-      <c r="C2" s="791" t="n"/>
-      <c r="D2" s="791" t="n"/>
-      <c r="E2" s="791" t="n"/>
-      <c r="F2" s="791" t="n"/>
-      <c r="G2" s="791" t="n"/>
-      <c r="H2" s="828" t="inlineStr">
+      <c r="A2" s="275" t="n"/>
+      <c r="B2" s="320" t="n"/>
+      <c r="C2" s="275" t="n"/>
+      <c r="G2" s="320" t="n"/>
+      <c r="H2" s="344" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="I2" s="335" t="inlineStr">
+      <c r="I2" s="345" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="J2" s="676" t="n"/>
-      <c r="K2" s="676" t="n"/>
-      <c r="L2" s="676" t="n"/>
-      <c r="M2" s="676" t="n"/>
-      <c r="N2" s="676" t="n"/>
-      <c r="O2" s="676" t="n"/>
-      <c r="P2" s="676" t="n"/>
-      <c r="Q2" s="676" t="n"/>
-      <c r="R2" s="676" t="n"/>
-      <c r="S2" s="676" t="n"/>
-      <c r="T2" s="676" t="n"/>
-      <c r="U2" s="676" t="n"/>
-      <c r="V2" s="676" t="n"/>
-      <c r="W2" s="676" t="n"/>
-      <c r="X2" s="676" t="n"/>
-      <c r="Y2" s="676" t="n"/>
-      <c r="Z2" s="676" t="n"/>
-      <c r="AA2" s="676" t="n"/>
-      <c r="AB2" s="676" t="n"/>
-      <c r="AC2" s="676" t="n"/>
-      <c r="AD2" s="829" t="n"/>
-      <c r="AE2" s="830" t="n"/>
-      <c r="AF2" s="830" t="n"/>
-      <c r="AG2" s="830" t="n"/>
-      <c r="AH2" s="831" t="n"/>
-      <c r="AI2" s="832" t="n"/>
-      <c r="AJ2" s="832" t="n"/>
-      <c r="AK2" s="832" t="n"/>
-      <c r="AL2" s="832" t="n"/>
-      <c r="AM2" s="832" t="n"/>
-      <c r="AN2" s="833" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="799" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="834" t="inlineStr">
+      <c r="A3" s="275" t="n"/>
+      <c r="B3" s="320" t="n"/>
+      <c r="C3" s="282" t="n"/>
+      <c r="D3" s="283" t="n"/>
+      <c r="E3" s="283" t="n"/>
+      <c r="F3" s="283" t="n"/>
+      <c r="G3" s="287" t="n"/>
+      <c r="H3" s="344" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="I3" s="342" t="inlineStr">
+      <c r="I3" s="345" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="J3" s="835" t="n"/>
-      <c r="K3" s="835" t="n"/>
-      <c r="L3" s="835" t="n"/>
-      <c r="M3" s="835" t="n"/>
-      <c r="N3" s="835" t="n"/>
-      <c r="O3" s="835" t="n"/>
-      <c r="P3" s="835" t="n"/>
-      <c r="Q3" s="835" t="n"/>
-      <c r="R3" s="835" t="n"/>
-      <c r="S3" s="835" t="n"/>
-      <c r="T3" s="835" t="n"/>
-      <c r="U3" s="835" t="n"/>
-      <c r="V3" s="835" t="n"/>
-      <c r="W3" s="835" t="n"/>
-      <c r="X3" s="835" t="n"/>
-      <c r="Y3" s="835" t="n"/>
-      <c r="Z3" s="835" t="n"/>
-      <c r="AA3" s="835" t="n"/>
-      <c r="AB3" s="835" t="n"/>
-      <c r="AC3" s="835" t="n"/>
-      <c r="AD3" s="836" t="n"/>
-      <c r="AE3" s="837" t="n"/>
-      <c r="AF3" s="837" t="n"/>
-      <c r="AG3" s="837" t="n"/>
-      <c r="AH3" s="838" t="n"/>
-      <c r="AI3" s="839" t="n"/>
-      <c r="AJ3" s="839" t="n"/>
-      <c r="AK3" s="839" t="n"/>
-      <c r="AL3" s="839" t="n"/>
-      <c r="AM3" s="839" t="n"/>
-      <c r="AN3" s="840" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="799" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="581" t="inlineStr">
+      <c r="A4" s="275" t="n"/>
+      <c r="B4" s="320" t="n"/>
+      <c r="C4" s="388" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="834" t="inlineStr">
+      <c r="D4" s="289" t="n"/>
+      <c r="E4" s="289" t="n"/>
+      <c r="F4" s="289" t="n"/>
+      <c r="G4" s="290" t="n"/>
+      <c r="H4" s="344" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="I4" s="516" t="inlineStr"/>
-      <c r="J4" s="516" t="n"/>
-      <c r="K4" s="516" t="n"/>
-      <c r="L4" s="516" t="n"/>
-      <c r="M4" s="516" t="n"/>
-      <c r="N4" s="516" t="n"/>
-      <c r="O4" s="516" t="n"/>
-      <c r="P4" s="516" t="n"/>
-      <c r="Q4" s="516" t="n"/>
-      <c r="R4" s="516" t="n"/>
-      <c r="S4" s="516" t="n"/>
-      <c r="T4" s="516" t="n"/>
-      <c r="U4" s="516" t="n"/>
-      <c r="V4" s="516" t="n"/>
-      <c r="W4" s="516" t="n"/>
-      <c r="X4" s="516" t="n"/>
-      <c r="Y4" s="516" t="n"/>
-      <c r="Z4" s="516" t="n"/>
-      <c r="AA4" s="516" t="n"/>
-      <c r="AB4" s="516" t="n"/>
-      <c r="AC4" s="516" t="n"/>
-      <c r="AD4" s="841" t="n"/>
-      <c r="AE4" s="837" t="n"/>
-      <c r="AF4" s="837" t="n"/>
-      <c r="AG4" s="837" t="n"/>
-      <c r="AH4" s="838" t="n"/>
-      <c r="AI4" s="839" t="n"/>
-      <c r="AJ4" s="839" t="n"/>
-      <c r="AK4" s="839" t="n"/>
-      <c r="AL4" s="839" t="n"/>
-      <c r="AM4" s="839" t="n"/>
-      <c r="AN4" s="840" t="n"/>
+      <c r="I4" s="345" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="799" t="n"/>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="842" t="inlineStr">
+      <c r="A5" s="282" t="n"/>
+      <c r="B5" s="287" t="n"/>
+      <c r="C5" s="389" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="25" t="n"/>
-      <c r="H5" s="834" t="inlineStr">
+      <c r="D5" s="289" t="n"/>
+      <c r="E5" s="289" t="n"/>
+      <c r="F5" s="289" t="n"/>
+      <c r="G5" s="290" t="n"/>
+      <c r="H5" s="357" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="I5" s="843" t="inlineStr"/>
-      <c r="J5" s="843" t="n"/>
-      <c r="K5" s="843" t="n"/>
-      <c r="L5" s="843" t="n"/>
-      <c r="M5" s="843" t="n"/>
-      <c r="N5" s="843" t="n"/>
-      <c r="O5" s="843" t="n"/>
-      <c r="P5" s="843" t="n"/>
-      <c r="Q5" s="843" t="n"/>
-      <c r="R5" s="843" t="n"/>
-      <c r="S5" s="843" t="n"/>
-      <c r="T5" s="843" t="n"/>
-      <c r="U5" s="843" t="n"/>
-      <c r="V5" s="843" t="n"/>
-      <c r="W5" s="843" t="n"/>
-      <c r="X5" s="843" t="n"/>
-      <c r="Y5" s="843" t="n"/>
-      <c r="Z5" s="843" t="n"/>
-      <c r="AA5" s="843" t="n"/>
-      <c r="AB5" s="843" t="n"/>
-      <c r="AC5" s="843" t="n"/>
-      <c r="AD5" s="844" t="n"/>
-      <c r="AE5" s="837" t="n"/>
-      <c r="AF5" s="837" t="n"/>
-      <c r="AG5" s="837" t="n"/>
-      <c r="AH5" s="838" t="n"/>
-      <c r="AI5" s="839" t="n"/>
-      <c r="AJ5" s="839" t="n"/>
-      <c r="AK5" s="839" t="n"/>
-      <c r="AL5" s="839" t="n"/>
-      <c r="AM5" s="839" t="n"/>
-      <c r="AN5" s="840" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="352" t="n"/>
-      <c r="B6" s="807" t="n"/>
-      <c r="C6" s="807" t="n"/>
-      <c r="D6" s="807" t="n"/>
-      <c r="E6" s="807" t="n"/>
-      <c r="F6" s="807" t="n"/>
-      <c r="G6" s="807" t="n"/>
-      <c r="H6" s="808" t="n"/>
-      <c r="I6" s="807" t="n"/>
-      <c r="J6" s="807" t="n"/>
-      <c r="K6" s="807" t="n"/>
-      <c r="L6" s="807" t="n"/>
-      <c r="M6" s="807" t="n"/>
-      <c r="N6" s="807" t="n"/>
-      <c r="O6" s="807" t="n"/>
-      <c r="P6" s="807" t="n"/>
-      <c r="Q6" s="807" t="n"/>
-      <c r="R6" s="807" t="n"/>
-      <c r="S6" s="807" t="n"/>
-      <c r="T6" s="807" t="n"/>
-      <c r="U6" s="807" t="n"/>
-      <c r="V6" s="807" t="n"/>
-      <c r="W6" s="807" t="n"/>
-      <c r="X6" s="807" t="n"/>
-      <c r="Y6" s="807" t="n"/>
-      <c r="Z6" s="807" t="n"/>
-      <c r="AA6" s="807" t="n"/>
-      <c r="AB6" s="807" t="n"/>
-      <c r="AC6" s="807" t="n"/>
-      <c r="AD6" s="808" t="n"/>
-      <c r="AE6" s="809" t="n"/>
-      <c r="AF6" s="809" t="n"/>
-      <c r="AG6" s="809" t="n"/>
-      <c r="AH6" s="810" t="n"/>
-      <c r="AI6" s="811" t="n"/>
-      <c r="AJ6" s="811" t="n"/>
-      <c r="AK6" s="811" t="n"/>
-      <c r="AL6" s="811" t="n"/>
-      <c r="AM6" s="811" t="n"/>
-      <c r="AN6" s="812" t="n"/>
-    </row>
-    <row r="7" ht="4" customHeight="1">
-      <c r="A7" s="813" t="n"/>
-      <c r="B7" s="814" t="n"/>
-      <c r="C7" s="814" t="n"/>
-      <c r="D7" s="814" t="n"/>
-      <c r="E7" s="814" t="n"/>
-      <c r="F7" s="814" t="n"/>
-      <c r="G7" s="814" t="n"/>
-      <c r="H7" s="814" t="n"/>
-      <c r="I7" s="814" t="n"/>
-      <c r="J7" s="813" t="n"/>
-      <c r="K7" s="813" t="n"/>
-      <c r="L7" s="813" t="n"/>
-      <c r="M7" s="813" t="n"/>
-      <c r="N7" s="813" t="n"/>
-      <c r="O7" s="813" t="n"/>
-      <c r="P7" s="813" t="n"/>
-      <c r="Q7" s="813" t="n"/>
-      <c r="R7" s="813" t="n"/>
-      <c r="S7" s="813" t="n"/>
-      <c r="T7" s="813" t="n"/>
-      <c r="U7" s="813" t="n"/>
-      <c r="V7" s="813" t="n"/>
-      <c r="W7" s="813" t="n"/>
-      <c r="X7" s="813" t="n"/>
-      <c r="Y7" s="813" t="n"/>
-      <c r="Z7" s="813" t="n"/>
-      <c r="AA7" s="813" t="n"/>
-      <c r="AB7" s="813" t="n"/>
-      <c r="AC7" s="813" t="n"/>
-      <c r="AD7" s="813" t="n"/>
-      <c r="AE7" s="813" t="n"/>
-      <c r="AF7" s="813" t="n"/>
-      <c r="AG7" s="813" t="n"/>
-      <c r="AH7" s="813" t="n"/>
-      <c r="AI7" s="813" t="n"/>
-      <c r="AJ7" s="813" t="n"/>
-      <c r="AK7" s="813" t="n"/>
-      <c r="AL7" s="813" t="n"/>
-      <c r="AM7" s="813" t="n"/>
-      <c r="AN7" s="813" t="n"/>
+      <c r="I5" s="358" t="inlineStr"/>
+    </row>
+    <row r="6" ht="4" customHeight="1">
+      <c r="A6" s="386" t="n"/>
+      <c r="B6" s="289" t="n"/>
+      <c r="C6" s="289" t="n"/>
+      <c r="D6" s="289" t="n"/>
+      <c r="E6" s="289" t="n"/>
+      <c r="F6" s="289" t="n"/>
+      <c r="G6" s="289" t="n"/>
+      <c r="H6" s="289" t="n"/>
+      <c r="I6" s="290" t="n"/>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="390" t="inlineStr">
+        <is>
+          <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
+        </is>
+      </c>
+      <c r="B7" s="289" t="n"/>
+      <c r="C7" s="289" t="n"/>
+      <c r="D7" s="289" t="n"/>
+      <c r="E7" s="289" t="n"/>
+      <c r="F7" s="289" t="n"/>
+      <c r="G7" s="289" t="n"/>
+      <c r="H7" s="289" t="n"/>
+      <c r="I7" s="290" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="756" t="inlineStr">
+      <c r="A8" s="391" t="inlineStr">
         <is>
           <t>Parent Form</t>
         </is>
       </c>
-      <c r="B8" s="272" t="n"/>
-      <c r="C8" s="757" t="inlineStr">
+      <c r="B8" s="290" t="n"/>
+      <c r="C8" s="392" t="inlineStr">
         <is>
           <t>FRM-209 · HIGH-RISK JOB READINESS REVIEW</t>
         </is>
       </c>
-      <c r="D8" s="271" t="n"/>
-      <c r="E8" s="272" t="n"/>
-      <c r="F8" s="758" t="inlineStr">
+      <c r="D8" s="289" t="n"/>
+      <c r="E8" s="290" t="n"/>
+      <c r="F8" s="391" t="inlineStr">
         <is>
           <t>Support Tab</t>
         </is>
       </c>
-      <c r="G8" s="272" t="n"/>
-      <c r="H8" s="757" t="inlineStr">
+      <c r="G8" s="290" t="n"/>
+      <c r="H8" s="392" t="inlineStr">
         <is>
           <t>RISKS_ACTIONS</t>
         </is>
       </c>
-      <c r="I8" s="272" t="n"/>
-      <c r="J8" s="696" t="n"/>
-      <c r="K8" s="696" t="n"/>
-      <c r="L8" s="696" t="n"/>
-      <c r="M8" s="696" t="n"/>
-      <c r="N8" s="696" t="n"/>
-      <c r="O8" s="696" t="n"/>
-      <c r="P8" s="696" t="n"/>
-      <c r="Q8" s="696" t="n"/>
-      <c r="R8" s="696" t="n"/>
-      <c r="S8" s="696" t="n"/>
-      <c r="T8" s="696" t="n"/>
-      <c r="U8" s="696" t="n"/>
-      <c r="V8" s="696" t="n"/>
-      <c r="W8" s="696" t="n"/>
-      <c r="X8" s="696" t="n"/>
-      <c r="Y8" s="696" t="n"/>
-      <c r="Z8" s="696" t="n"/>
-      <c r="AA8" s="696" t="n"/>
-      <c r="AB8" s="696" t="n"/>
-      <c r="AC8" s="696" t="n"/>
-      <c r="AD8" s="696" t="n"/>
-      <c r="AE8" s="696" t="n"/>
-      <c r="AF8" s="696" t="n"/>
-      <c r="AG8" s="696" t="n"/>
-      <c r="AH8" s="696" t="n"/>
-      <c r="AI8" s="696" t="n"/>
-      <c r="AJ8" s="696" t="n"/>
-      <c r="AK8" s="696" t="n"/>
-      <c r="AL8" s="696" t="n"/>
-      <c r="AM8" s="696" t="n"/>
-      <c r="AN8" s="697" t="n"/>
+      <c r="I8" s="290" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="759" t="inlineStr">
+      <c r="A9" s="391" t="inlineStr">
         <is>
           <t>Tab Purpose</t>
         </is>
       </c>
-      <c r="B9" s="278" t="n"/>
-      <c r="C9" s="760" t="inlineStr">
+      <c r="B9" s="290" t="n"/>
+      <c r="C9" s="392" t="inlineStr">
         <is>
           <t>One line per material, capacity, quality or customer-risk condition.</t>
         </is>
       </c>
-      <c r="D9" s="277" t="n"/>
-      <c r="E9" s="278" t="n"/>
-      <c r="F9" s="761" t="inlineStr">
+      <c r="D9" s="289" t="n"/>
+      <c r="E9" s="290" t="n"/>
+      <c r="F9" s="391" t="inlineStr">
         <is>
           <t>Working Owner</t>
         </is>
       </c>
-      <c r="G9" s="278" t="n"/>
-      <c r="H9" s="760" t="inlineStr"/>
-      <c r="I9" s="278" t="n"/>
-      <c r="J9" s="701" t="n"/>
-      <c r="K9" s="701" t="n"/>
-      <c r="L9" s="701" t="n"/>
-      <c r="M9" s="701" t="n"/>
-      <c r="N9" s="701" t="n"/>
-      <c r="O9" s="701" t="n"/>
-      <c r="P9" s="701" t="n"/>
-      <c r="Q9" s="701" t="n"/>
-      <c r="R9" s="701" t="n"/>
-      <c r="S9" s="701" t="n"/>
-      <c r="T9" s="701" t="n"/>
-      <c r="U9" s="701" t="n"/>
-      <c r="V9" s="701" t="n"/>
-      <c r="W9" s="701" t="n"/>
-      <c r="X9" s="701" t="n"/>
-      <c r="Y9" s="701" t="n"/>
-      <c r="Z9" s="701" t="n"/>
-      <c r="AA9" s="701" t="n"/>
-      <c r="AB9" s="701" t="n"/>
-      <c r="AC9" s="701" t="n"/>
-      <c r="AD9" s="701" t="n"/>
-      <c r="AE9" s="701" t="n"/>
-      <c r="AF9" s="701" t="n"/>
-      <c r="AG9" s="701" t="n"/>
-      <c r="AH9" s="701" t="n"/>
-      <c r="AI9" s="701" t="n"/>
-      <c r="AJ9" s="701" t="n"/>
-      <c r="AK9" s="701" t="n"/>
-      <c r="AL9" s="701" t="n"/>
-      <c r="AM9" s="701" t="n"/>
-      <c r="AN9" s="702" t="n"/>
+      <c r="G9" s="290" t="n"/>
+      <c r="H9" s="392" t="inlineStr"/>
+      <c r="I9" s="290" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="759" t="inlineStr">
+      <c r="A10" s="391" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B10" s="278" t="n"/>
-      <c r="C10" s="760" t="inlineStr">
+      <c r="B10" s="290" t="n"/>
+      <c r="C10" s="392" t="inlineStr">
         <is>
           <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
         </is>
       </c>
-      <c r="D10" s="277" t="n"/>
-      <c r="E10" s="278" t="n"/>
-      <c r="F10" s="761" t="inlineStr">
+      <c r="D10" s="289" t="n"/>
+      <c r="E10" s="290" t="n"/>
+      <c r="F10" s="391" t="inlineStr">
         <is>
           <t>Reviewed By</t>
         </is>
       </c>
-      <c r="G10" s="278" t="n"/>
-      <c r="H10" s="760" t="inlineStr"/>
-      <c r="I10" s="278" t="n"/>
-      <c r="J10" s="701" t="n"/>
-      <c r="K10" s="701" t="n"/>
-      <c r="L10" s="701" t="n"/>
-      <c r="M10" s="701" t="n"/>
-      <c r="N10" s="701" t="n"/>
-      <c r="O10" s="701" t="n"/>
-      <c r="P10" s="701" t="n"/>
-      <c r="Q10" s="701" t="n"/>
-      <c r="R10" s="701" t="n"/>
-      <c r="S10" s="701" t="n"/>
-      <c r="T10" s="701" t="n"/>
-      <c r="U10" s="701" t="n"/>
-      <c r="V10" s="701" t="n"/>
-      <c r="W10" s="701" t="n"/>
-      <c r="X10" s="701" t="n"/>
-      <c r="Y10" s="701" t="n"/>
-      <c r="Z10" s="701" t="n"/>
-      <c r="AA10" s="701" t="n"/>
-      <c r="AB10" s="701" t="n"/>
-      <c r="AC10" s="701" t="n"/>
-      <c r="AD10" s="701" t="n"/>
-      <c r="AE10" s="701" t="n"/>
-      <c r="AF10" s="701" t="n"/>
-      <c r="AG10" s="701" t="n"/>
-      <c r="AH10" s="701" t="n"/>
-      <c r="AI10" s="701" t="n"/>
-      <c r="AJ10" s="701" t="n"/>
-      <c r="AK10" s="701" t="n"/>
-      <c r="AL10" s="701" t="n"/>
-      <c r="AM10" s="701" t="n"/>
-      <c r="AN10" s="702" t="n"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="759" t="inlineStr">
+      <c r="G10" s="290" t="n"/>
+      <c r="H10" s="392" t="inlineStr"/>
+      <c r="I10" s="290" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="391" t="inlineStr">
         <is>
           <t>Update Trigger</t>
         </is>
       </c>
-      <c r="B11" s="278" t="n"/>
-      <c r="C11" s="760" t="inlineStr">
+      <c r="B11" s="290" t="n"/>
+      <c r="C11" s="392" t="inlineStr">
         <is>
           <t>Update when the linked review, evidence or follow-up status changes.</t>
         </is>
       </c>
-      <c r="D11" s="277" t="n"/>
-      <c r="E11" s="278" t="n"/>
-      <c r="F11" s="761" t="inlineStr">
+      <c r="D11" s="289" t="n"/>
+      <c r="E11" s="290" t="n"/>
+      <c r="F11" s="391" t="inlineStr">
         <is>
           <t>Data Structure</t>
         </is>
       </c>
-      <c r="G11" s="278" t="n"/>
-      <c r="H11" s="760" t="inlineStr">
+      <c r="G11" s="290" t="n"/>
+      <c r="H11" s="392" t="inlineStr">
         <is>
           <t>Structured Excel Table with filters and print-title rows.</t>
         </is>
       </c>
-      <c r="I11" s="278" t="n"/>
-      <c r="J11" s="703" t="n"/>
-      <c r="K11" s="703" t="n"/>
-      <c r="L11" s="703" t="n"/>
-      <c r="M11" s="703" t="n"/>
-      <c r="N11" s="703" t="n"/>
-      <c r="O11" s="703" t="n"/>
-      <c r="P11" s="703" t="n"/>
-      <c r="Q11" s="703" t="n"/>
-      <c r="R11" s="703" t="n"/>
-      <c r="S11" s="703" t="n"/>
-      <c r="T11" s="703" t="n"/>
-      <c r="U11" s="703" t="n"/>
-      <c r="V11" s="703" t="n"/>
-      <c r="W11" s="703" t="n"/>
-      <c r="X11" s="703" t="n"/>
-      <c r="Y11" s="703" t="n"/>
-      <c r="Z11" s="703" t="n"/>
-      <c r="AA11" s="703" t="n"/>
-      <c r="AB11" s="703" t="n"/>
-      <c r="AC11" s="703" t="n"/>
-      <c r="AD11" s="703" t="n"/>
-      <c r="AE11" s="703" t="n"/>
-      <c r="AF11" s="703" t="n"/>
-      <c r="AG11" s="703" t="n"/>
-      <c r="AH11" s="703" t="n"/>
-      <c r="AI11" s="703" t="n"/>
-      <c r="AJ11" s="703" t="n"/>
-      <c r="AK11" s="703" t="n"/>
-      <c r="AL11" s="703" t="n"/>
-      <c r="AM11" s="703" t="n"/>
-      <c r="AN11" s="704" t="n"/>
+      <c r="I11" s="290" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="762" t="inlineStr">
+      <c r="A12" s="391" t="inlineStr">
         <is>
           <t>Retention Rule</t>
         </is>
       </c>
-      <c r="B12" s="285" t="n"/>
-      <c r="C12" s="763" t="inlineStr">
+      <c r="B12" s="290" t="n"/>
+      <c r="C12" s="392" t="inlineStr">
         <is>
           <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
         </is>
       </c>
-      <c r="D12" s="283" t="n"/>
-      <c r="E12" s="285" t="n"/>
-      <c r="F12" s="764" t="inlineStr">
+      <c r="D12" s="289" t="n"/>
+      <c r="E12" s="290" t="n"/>
+      <c r="F12" s="391" t="inlineStr">
         <is>
           <t>Controlled Status</t>
         </is>
       </c>
-      <c r="G12" s="285" t="n"/>
-      <c r="H12" s="763" t="inlineStr">
+      <c r="G12" s="290" t="n"/>
+      <c r="H12" s="392" t="inlineStr">
         <is>
           <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
         </is>
       </c>
-      <c r="I12" s="285" t="n"/>
-      <c r="J12" s="708" t="n"/>
-      <c r="K12" s="708" t="n"/>
-      <c r="L12" s="708" t="n"/>
-      <c r="M12" s="708" t="n"/>
-      <c r="N12" s="708" t="n"/>
-      <c r="O12" s="708" t="n"/>
-      <c r="P12" s="708" t="n"/>
-      <c r="Q12" s="708" t="n"/>
-      <c r="R12" s="708" t="n"/>
-      <c r="S12" s="708" t="n"/>
-      <c r="T12" s="708" t="n"/>
-      <c r="U12" s="708" t="n"/>
-      <c r="V12" s="708" t="n"/>
-      <c r="W12" s="708" t="n"/>
-      <c r="X12" s="708" t="n"/>
-      <c r="Y12" s="708" t="n"/>
-      <c r="Z12" s="708" t="n"/>
-      <c r="AA12" s="708" t="n"/>
-      <c r="AB12" s="708" t="n"/>
-      <c r="AC12" s="708" t="n"/>
-      <c r="AD12" s="708" t="n"/>
-      <c r="AE12" s="708" t="n"/>
-      <c r="AF12" s="708" t="n"/>
-      <c r="AG12" s="708" t="n"/>
-      <c r="AH12" s="708" t="n"/>
-      <c r="AI12" s="708" t="n"/>
-      <c r="AJ12" s="708" t="n"/>
-      <c r="AK12" s="708" t="n"/>
-      <c r="AL12" s="708" t="n"/>
-      <c r="AM12" s="708" t="n"/>
-      <c r="AN12" s="709" t="n"/>
-    </row>
-    <row r="13" ht="3" customHeight="1">
-      <c r="A13" s="710" t="n"/>
-      <c r="B13" s="654" t="n"/>
-      <c r="C13" s="654" t="n"/>
-      <c r="D13" s="654" t="n"/>
-      <c r="E13" s="654" t="n"/>
-      <c r="F13" s="654" t="n"/>
-      <c r="G13" s="654" t="n"/>
-      <c r="H13" s="654" t="n"/>
-      <c r="I13" s="654" t="n"/>
-      <c r="J13" s="654" t="n"/>
-      <c r="K13" s="654" t="n"/>
-      <c r="L13" s="654" t="n"/>
-      <c r="M13" s="654" t="n"/>
-      <c r="N13" s="654" t="n"/>
-      <c r="O13" s="654" t="n"/>
-      <c r="P13" s="654" t="n"/>
-      <c r="Q13" s="654" t="n"/>
-      <c r="R13" s="654" t="n"/>
-      <c r="S13" s="654" t="n"/>
-      <c r="T13" s="654" t="n"/>
-      <c r="U13" s="654" t="n"/>
-      <c r="V13" s="654" t="n"/>
-      <c r="W13" s="654" t="n"/>
-      <c r="X13" s="654" t="n"/>
-      <c r="Y13" s="654" t="n"/>
-      <c r="Z13" s="654" t="n"/>
-      <c r="AA13" s="654" t="n"/>
-      <c r="AB13" s="654" t="n"/>
-      <c r="AC13" s="654" t="n"/>
-      <c r="AD13" s="654" t="n"/>
-      <c r="AE13" s="654" t="n"/>
-      <c r="AF13" s="654" t="n"/>
-      <c r="AG13" s="654" t="n"/>
-      <c r="AH13" s="654" t="n"/>
-      <c r="AI13" s="654" t="n"/>
-      <c r="AJ13" s="654" t="n"/>
-      <c r="AK13" s="654" t="n"/>
-      <c r="AL13" s="654" t="n"/>
-      <c r="AM13" s="654" t="n"/>
-      <c r="AN13" s="654" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="647" t="inlineStr">
+      <c r="I12" s="290" t="n"/>
+    </row>
+    <row r="13" ht="4" customHeight="1">
+      <c r="A13" s="386" t="n"/>
+      <c r="B13" s="289" t="n"/>
+      <c r="C13" s="289" t="n"/>
+      <c r="D13" s="289" t="n"/>
+      <c r="E13" s="289" t="n"/>
+      <c r="F13" s="289" t="n"/>
+      <c r="G13" s="289" t="n"/>
+      <c r="H13" s="289" t="n"/>
+      <c r="I13" s="290" t="n"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="390" t="inlineStr">
         <is>
           <t>2.  WORKING TABLE / DETAIL LINES</t>
         </is>
@@ -12183,41 +8733,10 @@
       <c r="F14" s="289" t="n"/>
       <c r="G14" s="289" t="n"/>
       <c r="H14" s="289" t="n"/>
-      <c r="I14" s="289" t="n"/>
-      <c r="J14" s="691" t="n"/>
-      <c r="K14" s="691" t="n"/>
-      <c r="L14" s="691" t="n"/>
-      <c r="M14" s="691" t="n"/>
-      <c r="N14" s="691" t="n"/>
-      <c r="O14" s="691" t="n"/>
-      <c r="P14" s="691" t="n"/>
-      <c r="Q14" s="691" t="n"/>
-      <c r="R14" s="691" t="n"/>
-      <c r="S14" s="691" t="n"/>
-      <c r="T14" s="691" t="n"/>
-      <c r="U14" s="691" t="n"/>
-      <c r="V14" s="691" t="n"/>
-      <c r="W14" s="691" t="n"/>
-      <c r="X14" s="691" t="n"/>
-      <c r="Y14" s="691" t="n"/>
-      <c r="Z14" s="691" t="n"/>
-      <c r="AA14" s="691" t="n"/>
-      <c r="AB14" s="691" t="n"/>
-      <c r="AC14" s="691" t="n"/>
-      <c r="AD14" s="691" t="n"/>
-      <c r="AE14" s="691" t="n"/>
-      <c r="AF14" s="691" t="n"/>
-      <c r="AG14" s="691" t="n"/>
-      <c r="AH14" s="691" t="n"/>
-      <c r="AI14" s="691" t="n"/>
-      <c r="AJ14" s="691" t="n"/>
-      <c r="AK14" s="691" t="n"/>
-      <c r="AL14" s="691" t="n"/>
-      <c r="AM14" s="691" t="n"/>
-      <c r="AN14" s="692" t="n"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="647" t="inlineStr">
+      <c r="I14" s="290" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="393" t="inlineStr">
         <is>
           <t>One line per material, capacity, quality or customer-risk condition.</t>
         </is>
@@ -12229,654 +8748,209 @@
       <c r="F15" s="289" t="n"/>
       <c r="G15" s="289" t="n"/>
       <c r="H15" s="289" t="n"/>
-      <c r="I15" s="289" t="n"/>
-      <c r="J15" s="691" t="n"/>
-      <c r="K15" s="691" t="n"/>
-      <c r="L15" s="691" t="n"/>
-      <c r="M15" s="691" t="n"/>
-      <c r="N15" s="691" t="n"/>
-      <c r="O15" s="691" t="n"/>
-      <c r="P15" s="691" t="n"/>
-      <c r="Q15" s="691" t="n"/>
-      <c r="R15" s="691" t="n"/>
-      <c r="S15" s="691" t="n"/>
-      <c r="T15" s="691" t="n"/>
-      <c r="U15" s="691" t="n"/>
-      <c r="V15" s="691" t="n"/>
-      <c r="W15" s="691" t="n"/>
-      <c r="X15" s="691" t="n"/>
-      <c r="Y15" s="691" t="n"/>
-      <c r="Z15" s="691" t="n"/>
-      <c r="AA15" s="691" t="n"/>
-      <c r="AB15" s="691" t="n"/>
-      <c r="AC15" s="691" t="n"/>
-      <c r="AD15" s="691" t="n"/>
-      <c r="AE15" s="691" t="n"/>
-      <c r="AF15" s="691" t="n"/>
-      <c r="AG15" s="691" t="n"/>
-      <c r="AH15" s="691" t="n"/>
-      <c r="AI15" s="691" t="n"/>
-      <c r="AJ15" s="691" t="n"/>
-      <c r="AK15" s="691" t="n"/>
-      <c r="AL15" s="691" t="n"/>
-      <c r="AM15" s="691" t="n"/>
-      <c r="AN15" s="692" t="n"/>
+      <c r="I15" s="290" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="A16" s="373" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B16" s="37" t="inlineStr">
+      <c r="B16" s="374" t="inlineStr">
         <is>
           <t>Risk / Readiness Gap</t>
         </is>
       </c>
-      <c r="C16" s="37" t="inlineStr">
+      <c r="C16" s="374" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="D16" s="37" t="inlineStr">
+      <c r="D16" s="374" t="inlineStr">
         <is>
           <t>Containment / Action</t>
         </is>
       </c>
-      <c r="E16" s="37" t="inlineStr">
+      <c r="E16" s="374" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F16" s="37" t="inlineStr">
+      <c r="F16" s="374" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="G16" s="37" t="inlineStr">
+      <c r="G16" s="374" t="inlineStr">
         <is>
           <t>Escalation</t>
         </is>
       </c>
-      <c r="H16" s="37" t="inlineStr">
+      <c r="H16" s="374" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I16" s="37" t="inlineStr">
+      <c r="I16" s="375" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="J16" s="37" t="n"/>
-      <c r="K16" s="37" t="n"/>
-      <c r="L16" s="37" t="n"/>
-      <c r="M16" s="37" t="n"/>
-      <c r="N16" s="37" t="n"/>
-      <c r="O16" s="37" t="n"/>
-      <c r="P16" s="37" t="n"/>
-      <c r="Q16" s="37" t="n"/>
-      <c r="R16" s="37" t="n"/>
-      <c r="S16" s="37" t="n"/>
-      <c r="T16" s="37" t="n"/>
-      <c r="U16" s="37" t="n"/>
-      <c r="V16" s="37" t="n"/>
-      <c r="W16" s="37" t="n"/>
-      <c r="X16" s="37" t="n"/>
-      <c r="Y16" s="37" t="n"/>
-      <c r="Z16" s="37" t="n"/>
-      <c r="AA16" s="37" t="n"/>
-      <c r="AB16" s="37" t="n"/>
-      <c r="AC16" s="37" t="n"/>
-      <c r="AD16" s="37" t="n"/>
-      <c r="AE16" s="37" t="n"/>
-      <c r="AF16" s="37" t="n"/>
-      <c r="AG16" s="37" t="n"/>
-      <c r="AH16" s="37" t="n"/>
-      <c r="AI16" s="37" t="n"/>
-      <c r="AJ16" s="37" t="n"/>
-      <c r="AK16" s="37" t="n"/>
-      <c r="AL16" s="37" t="n"/>
-      <c r="AM16" s="37" t="n"/>
-      <c r="AN16" s="303" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="711">
+      <c r="A17" s="376">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B17" s="694" t="n"/>
-      <c r="C17" s="694" t="n"/>
-      <c r="D17" s="694" t="n"/>
-      <c r="E17" s="694" t="n"/>
-      <c r="F17" s="712" t="n"/>
-      <c r="G17" s="694" t="n"/>
-      <c r="H17" s="694" t="n"/>
-      <c r="I17" s="694" t="n"/>
-      <c r="J17" s="696" t="n"/>
-      <c r="K17" s="696" t="n"/>
-      <c r="L17" s="696" t="n"/>
-      <c r="M17" s="696" t="n"/>
-      <c r="N17" s="696" t="n"/>
-      <c r="O17" s="696" t="n"/>
-      <c r="P17" s="696" t="n"/>
-      <c r="Q17" s="696" t="n"/>
-      <c r="R17" s="696" t="n"/>
-      <c r="S17" s="696" t="n"/>
-      <c r="T17" s="696" t="n"/>
-      <c r="U17" s="696" t="n"/>
-      <c r="V17" s="696" t="n"/>
-      <c r="W17" s="696" t="n"/>
-      <c r="X17" s="696" t="n"/>
-      <c r="Y17" s="696" t="n"/>
-      <c r="Z17" s="696" t="n"/>
-      <c r="AA17" s="696" t="n"/>
-      <c r="AB17" s="696" t="n"/>
-      <c r="AC17" s="696" t="n"/>
-      <c r="AD17" s="696" t="n"/>
-      <c r="AE17" s="696" t="n"/>
-      <c r="AF17" s="696" t="n"/>
-      <c r="AG17" s="696" t="n"/>
-      <c r="AH17" s="696" t="n"/>
-      <c r="AI17" s="696" t="n"/>
-      <c r="AJ17" s="696" t="n"/>
-      <c r="AK17" s="696" t="n"/>
-      <c r="AL17" s="696" t="n"/>
-      <c r="AM17" s="696" t="n"/>
-      <c r="AN17" s="697" t="n"/>
+      <c r="B17" s="377" t="n"/>
+      <c r="C17" s="377" t="n"/>
+      <c r="D17" s="377" t="n"/>
+      <c r="E17" s="377" t="n"/>
+      <c r="F17" s="378" t="n"/>
+      <c r="G17" s="377" t="n"/>
+      <c r="H17" s="377" t="n"/>
+      <c r="I17" s="345" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="713">
+      <c r="A18" s="376">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B18" s="714" t="n"/>
-      <c r="C18" s="714" t="n"/>
-      <c r="D18" s="714" t="n"/>
-      <c r="E18" s="714" t="n"/>
-      <c r="F18" s="715" t="n"/>
-      <c r="G18" s="714" t="n"/>
-      <c r="H18" s="714" t="n"/>
-      <c r="I18" s="714" t="n"/>
-      <c r="J18" s="701" t="n"/>
-      <c r="K18" s="701" t="n"/>
-      <c r="L18" s="701" t="n"/>
-      <c r="M18" s="701" t="n"/>
-      <c r="N18" s="701" t="n"/>
-      <c r="O18" s="701" t="n"/>
-      <c r="P18" s="701" t="n"/>
-      <c r="Q18" s="701" t="n"/>
-      <c r="R18" s="701" t="n"/>
-      <c r="S18" s="701" t="n"/>
-      <c r="T18" s="701" t="n"/>
-      <c r="U18" s="701" t="n"/>
-      <c r="V18" s="701" t="n"/>
-      <c r="W18" s="701" t="n"/>
-      <c r="X18" s="701" t="n"/>
-      <c r="Y18" s="701" t="n"/>
-      <c r="Z18" s="701" t="n"/>
-      <c r="AA18" s="701" t="n"/>
-      <c r="AB18" s="701" t="n"/>
-      <c r="AC18" s="701" t="n"/>
-      <c r="AD18" s="701" t="n"/>
-      <c r="AE18" s="701" t="n"/>
-      <c r="AF18" s="701" t="n"/>
-      <c r="AG18" s="701" t="n"/>
-      <c r="AH18" s="701" t="n"/>
-      <c r="AI18" s="701" t="n"/>
-      <c r="AJ18" s="701" t="n"/>
-      <c r="AK18" s="701" t="n"/>
-      <c r="AL18" s="701" t="n"/>
-      <c r="AM18" s="701" t="n"/>
-      <c r="AN18" s="702" t="n"/>
+      <c r="B18" s="379" t="n"/>
+      <c r="C18" s="379" t="n"/>
+      <c r="D18" s="379" t="n"/>
+      <c r="E18" s="379" t="n"/>
+      <c r="F18" s="380" t="n"/>
+      <c r="G18" s="379" t="n"/>
+      <c r="H18" s="379" t="n"/>
+      <c r="I18" s="381" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="713">
+      <c r="A19" s="376">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B19" s="699" t="n"/>
-      <c r="C19" s="699" t="n"/>
-      <c r="D19" s="699" t="n"/>
-      <c r="E19" s="699" t="n"/>
-      <c r="F19" s="716" t="n"/>
-      <c r="G19" s="699" t="n"/>
-      <c r="H19" s="699" t="n"/>
-      <c r="I19" s="699" t="n"/>
-      <c r="J19" s="701" t="n"/>
-      <c r="K19" s="701" t="n"/>
-      <c r="L19" s="701" t="n"/>
-      <c r="M19" s="701" t="n"/>
-      <c r="N19" s="701" t="n"/>
-      <c r="O19" s="701" t="n"/>
-      <c r="P19" s="701" t="n"/>
-      <c r="Q19" s="701" t="n"/>
-      <c r="R19" s="701" t="n"/>
-      <c r="S19" s="701" t="n"/>
-      <c r="T19" s="701" t="n"/>
-      <c r="U19" s="701" t="n"/>
-      <c r="V19" s="701" t="n"/>
-      <c r="W19" s="701" t="n"/>
-      <c r="X19" s="701" t="n"/>
-      <c r="Y19" s="701" t="n"/>
-      <c r="Z19" s="701" t="n"/>
-      <c r="AA19" s="701" t="n"/>
-      <c r="AB19" s="701" t="n"/>
-      <c r="AC19" s="701" t="n"/>
-      <c r="AD19" s="701" t="n"/>
-      <c r="AE19" s="701" t="n"/>
-      <c r="AF19" s="701" t="n"/>
-      <c r="AG19" s="701" t="n"/>
-      <c r="AH19" s="701" t="n"/>
-      <c r="AI19" s="701" t="n"/>
-      <c r="AJ19" s="701" t="n"/>
-      <c r="AK19" s="701" t="n"/>
-      <c r="AL19" s="701" t="n"/>
-      <c r="AM19" s="701" t="n"/>
-      <c r="AN19" s="702" t="n"/>
+      <c r="B19" s="377" t="n"/>
+      <c r="C19" s="377" t="n"/>
+      <c r="D19" s="377" t="n"/>
+      <c r="E19" s="377" t="n"/>
+      <c r="F19" s="378" t="n"/>
+      <c r="G19" s="377" t="n"/>
+      <c r="H19" s="377" t="n"/>
+      <c r="I19" s="345" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="713">
+      <c r="A20" s="376">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B20" s="714" t="n"/>
-      <c r="C20" s="714" t="n"/>
-      <c r="D20" s="714" t="n"/>
-      <c r="E20" s="714" t="n"/>
-      <c r="F20" s="715" t="n"/>
-      <c r="G20" s="714" t="n"/>
-      <c r="H20" s="714" t="n"/>
-      <c r="I20" s="714" t="n"/>
-      <c r="J20" s="701" t="n"/>
-      <c r="K20" s="701" t="n"/>
-      <c r="L20" s="701" t="n"/>
-      <c r="M20" s="701" t="n"/>
-      <c r="N20" s="701" t="n"/>
-      <c r="O20" s="701" t="n"/>
-      <c r="P20" s="701" t="n"/>
-      <c r="Q20" s="701" t="n"/>
-      <c r="R20" s="701" t="n"/>
-      <c r="S20" s="701" t="n"/>
-      <c r="T20" s="701" t="n"/>
-      <c r="U20" s="701" t="n"/>
-      <c r="V20" s="701" t="n"/>
-      <c r="W20" s="701" t="n"/>
-      <c r="X20" s="701" t="n"/>
-      <c r="Y20" s="701" t="n"/>
-      <c r="Z20" s="701" t="n"/>
-      <c r="AA20" s="701" t="n"/>
-      <c r="AB20" s="701" t="n"/>
-      <c r="AC20" s="701" t="n"/>
-      <c r="AD20" s="701" t="n"/>
-      <c r="AE20" s="701" t="n"/>
-      <c r="AF20" s="701" t="n"/>
-      <c r="AG20" s="701" t="n"/>
-      <c r="AH20" s="701" t="n"/>
-      <c r="AI20" s="701" t="n"/>
-      <c r="AJ20" s="701" t="n"/>
-      <c r="AK20" s="701" t="n"/>
-      <c r="AL20" s="701" t="n"/>
-      <c r="AM20" s="701" t="n"/>
-      <c r="AN20" s="702" t="n"/>
+      <c r="B20" s="379" t="n"/>
+      <c r="C20" s="379" t="n"/>
+      <c r="D20" s="379" t="n"/>
+      <c r="E20" s="379" t="n"/>
+      <c r="F20" s="380" t="n"/>
+      <c r="G20" s="379" t="n"/>
+      <c r="H20" s="379" t="n"/>
+      <c r="I20" s="381" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="713">
+      <c r="A21" s="376">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B21" s="699" t="n"/>
-      <c r="C21" s="699" t="n"/>
-      <c r="D21" s="699" t="n"/>
-      <c r="E21" s="699" t="n"/>
-      <c r="F21" s="716" t="n"/>
-      <c r="G21" s="699" t="n"/>
-      <c r="H21" s="699" t="n"/>
-      <c r="I21" s="699" t="n"/>
-      <c r="J21" s="701" t="n"/>
-      <c r="K21" s="701" t="n"/>
-      <c r="L21" s="701" t="n"/>
-      <c r="M21" s="701" t="n"/>
-      <c r="N21" s="701" t="n"/>
-      <c r="O21" s="701" t="n"/>
-      <c r="P21" s="701" t="n"/>
-      <c r="Q21" s="701" t="n"/>
-      <c r="R21" s="701" t="n"/>
-      <c r="S21" s="701" t="n"/>
-      <c r="T21" s="701" t="n"/>
-      <c r="U21" s="701" t="n"/>
-      <c r="V21" s="701" t="n"/>
-      <c r="W21" s="701" t="n"/>
-      <c r="X21" s="701" t="n"/>
-      <c r="Y21" s="701" t="n"/>
-      <c r="Z21" s="701" t="n"/>
-      <c r="AA21" s="701" t="n"/>
-      <c r="AB21" s="701" t="n"/>
-      <c r="AC21" s="701" t="n"/>
-      <c r="AD21" s="701" t="n"/>
-      <c r="AE21" s="701" t="n"/>
-      <c r="AF21" s="701" t="n"/>
-      <c r="AG21" s="701" t="n"/>
-      <c r="AH21" s="701" t="n"/>
-      <c r="AI21" s="701" t="n"/>
-      <c r="AJ21" s="701" t="n"/>
-      <c r="AK21" s="701" t="n"/>
-      <c r="AL21" s="701" t="n"/>
-      <c r="AM21" s="701" t="n"/>
-      <c r="AN21" s="702" t="n"/>
+      <c r="B21" s="377" t="n"/>
+      <c r="C21" s="377" t="n"/>
+      <c r="D21" s="377" t="n"/>
+      <c r="E21" s="377" t="n"/>
+      <c r="F21" s="378" t="n"/>
+      <c r="G21" s="377" t="n"/>
+      <c r="H21" s="377" t="n"/>
+      <c r="I21" s="345" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="713">
+      <c r="A22" s="376">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B22" s="714" t="n"/>
-      <c r="C22" s="714" t="n"/>
-      <c r="D22" s="714" t="n"/>
-      <c r="E22" s="714" t="n"/>
-      <c r="F22" s="715" t="n"/>
-      <c r="G22" s="714" t="n"/>
-      <c r="H22" s="714" t="n"/>
-      <c r="I22" s="714" t="n"/>
-      <c r="J22" s="701" t="n"/>
-      <c r="K22" s="701" t="n"/>
-      <c r="L22" s="701" t="n"/>
-      <c r="M22" s="701" t="n"/>
-      <c r="N22" s="701" t="n"/>
-      <c r="O22" s="701" t="n"/>
-      <c r="P22" s="701" t="n"/>
-      <c r="Q22" s="701" t="n"/>
-      <c r="R22" s="701" t="n"/>
-      <c r="S22" s="701" t="n"/>
-      <c r="T22" s="701" t="n"/>
-      <c r="U22" s="701" t="n"/>
-      <c r="V22" s="701" t="n"/>
-      <c r="W22" s="701" t="n"/>
-      <c r="X22" s="701" t="n"/>
-      <c r="Y22" s="701" t="n"/>
-      <c r="Z22" s="701" t="n"/>
-      <c r="AA22" s="701" t="n"/>
-      <c r="AB22" s="701" t="n"/>
-      <c r="AC22" s="701" t="n"/>
-      <c r="AD22" s="701" t="n"/>
-      <c r="AE22" s="701" t="n"/>
-      <c r="AF22" s="701" t="n"/>
-      <c r="AG22" s="701" t="n"/>
-      <c r="AH22" s="701" t="n"/>
-      <c r="AI22" s="701" t="n"/>
-      <c r="AJ22" s="701" t="n"/>
-      <c r="AK22" s="701" t="n"/>
-      <c r="AL22" s="701" t="n"/>
-      <c r="AM22" s="701" t="n"/>
-      <c r="AN22" s="702" t="n"/>
+      <c r="B22" s="379" t="n"/>
+      <c r="C22" s="379" t="n"/>
+      <c r="D22" s="379" t="n"/>
+      <c r="E22" s="379" t="n"/>
+      <c r="F22" s="380" t="n"/>
+      <c r="G22" s="379" t="n"/>
+      <c r="H22" s="379" t="n"/>
+      <c r="I22" s="381" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="713">
+      <c r="A23" s="376">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B23" s="699" t="n"/>
-      <c r="C23" s="699" t="n"/>
-      <c r="D23" s="699" t="n"/>
-      <c r="E23" s="699" t="n"/>
-      <c r="F23" s="716" t="n"/>
-      <c r="G23" s="699" t="n"/>
-      <c r="H23" s="699" t="n"/>
-      <c r="I23" s="699" t="n"/>
-      <c r="J23" s="701" t="n"/>
-      <c r="K23" s="701" t="n"/>
-      <c r="L23" s="701" t="n"/>
-      <c r="M23" s="701" t="n"/>
-      <c r="N23" s="701" t="n"/>
-      <c r="O23" s="701" t="n"/>
-      <c r="P23" s="701" t="n"/>
-      <c r="Q23" s="701" t="n"/>
-      <c r="R23" s="701" t="n"/>
-      <c r="S23" s="701" t="n"/>
-      <c r="T23" s="701" t="n"/>
-      <c r="U23" s="701" t="n"/>
-      <c r="V23" s="701" t="n"/>
-      <c r="W23" s="701" t="n"/>
-      <c r="X23" s="701" t="n"/>
-      <c r="Y23" s="701" t="n"/>
-      <c r="Z23" s="701" t="n"/>
-      <c r="AA23" s="701" t="n"/>
-      <c r="AB23" s="701" t="n"/>
-      <c r="AC23" s="701" t="n"/>
-      <c r="AD23" s="701" t="n"/>
-      <c r="AE23" s="701" t="n"/>
-      <c r="AF23" s="701" t="n"/>
-      <c r="AG23" s="701" t="n"/>
-      <c r="AH23" s="701" t="n"/>
-      <c r="AI23" s="701" t="n"/>
-      <c r="AJ23" s="701" t="n"/>
-      <c r="AK23" s="701" t="n"/>
-      <c r="AL23" s="701" t="n"/>
-      <c r="AM23" s="701" t="n"/>
-      <c r="AN23" s="702" t="n"/>
+      <c r="B23" s="377" t="n"/>
+      <c r="C23" s="377" t="n"/>
+      <c r="D23" s="377" t="n"/>
+      <c r="E23" s="377" t="n"/>
+      <c r="F23" s="378" t="n"/>
+      <c r="G23" s="377" t="n"/>
+      <c r="H23" s="377" t="n"/>
+      <c r="I23" s="345" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="713">
+      <c r="A24" s="376">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B24" s="714" t="n"/>
-      <c r="C24" s="714" t="n"/>
-      <c r="D24" s="714" t="n"/>
-      <c r="E24" s="714" t="n"/>
-      <c r="F24" s="715" t="n"/>
-      <c r="G24" s="714" t="n"/>
-      <c r="H24" s="714" t="n"/>
-      <c r="I24" s="714" t="n"/>
-      <c r="J24" s="701" t="n"/>
-      <c r="K24" s="701" t="n"/>
-      <c r="L24" s="701" t="n"/>
-      <c r="M24" s="701" t="n"/>
-      <c r="N24" s="701" t="n"/>
-      <c r="O24" s="701" t="n"/>
-      <c r="P24" s="701" t="n"/>
-      <c r="Q24" s="701" t="n"/>
-      <c r="R24" s="701" t="n"/>
-      <c r="S24" s="701" t="n"/>
-      <c r="T24" s="701" t="n"/>
-      <c r="U24" s="701" t="n"/>
-      <c r="V24" s="701" t="n"/>
-      <c r="W24" s="701" t="n"/>
-      <c r="X24" s="701" t="n"/>
-      <c r="Y24" s="701" t="n"/>
-      <c r="Z24" s="701" t="n"/>
-      <c r="AA24" s="701" t="n"/>
-      <c r="AB24" s="701" t="n"/>
-      <c r="AC24" s="701" t="n"/>
-      <c r="AD24" s="701" t="n"/>
-      <c r="AE24" s="701" t="n"/>
-      <c r="AF24" s="701" t="n"/>
-      <c r="AG24" s="701" t="n"/>
-      <c r="AH24" s="701" t="n"/>
-      <c r="AI24" s="701" t="n"/>
-      <c r="AJ24" s="701" t="n"/>
-      <c r="AK24" s="701" t="n"/>
-      <c r="AL24" s="701" t="n"/>
-      <c r="AM24" s="701" t="n"/>
-      <c r="AN24" s="702" t="n"/>
+      <c r="B24" s="379" t="n"/>
+      <c r="C24" s="379" t="n"/>
+      <c r="D24" s="379" t="n"/>
+      <c r="E24" s="379" t="n"/>
+      <c r="F24" s="380" t="n"/>
+      <c r="G24" s="379" t="n"/>
+      <c r="H24" s="379" t="n"/>
+      <c r="I24" s="381" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="713">
+      <c r="A25" s="376">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B25" s="699" t="n"/>
-      <c r="C25" s="699" t="n"/>
-      <c r="D25" s="699" t="n"/>
-      <c r="E25" s="699" t="n"/>
-      <c r="F25" s="716" t="n"/>
-      <c r="G25" s="699" t="n"/>
-      <c r="H25" s="699" t="n"/>
-      <c r="I25" s="699" t="n"/>
-      <c r="J25" s="701" t="n"/>
-      <c r="K25" s="701" t="n"/>
-      <c r="L25" s="701" t="n"/>
-      <c r="M25" s="701" t="n"/>
-      <c r="N25" s="701" t="n"/>
-      <c r="O25" s="701" t="n"/>
-      <c r="P25" s="701" t="n"/>
-      <c r="Q25" s="701" t="n"/>
-      <c r="R25" s="701" t="n"/>
-      <c r="S25" s="701" t="n"/>
-      <c r="T25" s="701" t="n"/>
-      <c r="U25" s="701" t="n"/>
-      <c r="V25" s="701" t="n"/>
-      <c r="W25" s="701" t="n"/>
-      <c r="X25" s="701" t="n"/>
-      <c r="Y25" s="701" t="n"/>
-      <c r="Z25" s="701" t="n"/>
-      <c r="AA25" s="701" t="n"/>
-      <c r="AB25" s="701" t="n"/>
-      <c r="AC25" s="701" t="n"/>
-      <c r="AD25" s="701" t="n"/>
-      <c r="AE25" s="701" t="n"/>
-      <c r="AF25" s="701" t="n"/>
-      <c r="AG25" s="701" t="n"/>
-      <c r="AH25" s="701" t="n"/>
-      <c r="AI25" s="701" t="n"/>
-      <c r="AJ25" s="701" t="n"/>
-      <c r="AK25" s="701" t="n"/>
-      <c r="AL25" s="701" t="n"/>
-      <c r="AM25" s="701" t="n"/>
-      <c r="AN25" s="702" t="n"/>
+      <c r="B25" s="377" t="n"/>
+      <c r="C25" s="377" t="n"/>
+      <c r="D25" s="377" t="n"/>
+      <c r="E25" s="377" t="n"/>
+      <c r="F25" s="378" t="n"/>
+      <c r="G25" s="377" t="n"/>
+      <c r="H25" s="377" t="n"/>
+      <c r="I25" s="345" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="713">
+      <c r="A26" s="382">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B26" s="714" t="n"/>
-      <c r="C26" s="714" t="n"/>
-      <c r="D26" s="714" t="n"/>
-      <c r="E26" s="714" t="n"/>
-      <c r="F26" s="715" t="n"/>
-      <c r="G26" s="714" t="n"/>
-      <c r="H26" s="714" t="n"/>
-      <c r="I26" s="714" t="n"/>
-      <c r="J26" s="701" t="n"/>
-      <c r="K26" s="701" t="n"/>
-      <c r="L26" s="701" t="n"/>
-      <c r="M26" s="701" t="n"/>
-      <c r="N26" s="701" t="n"/>
-      <c r="O26" s="701" t="n"/>
-      <c r="P26" s="701" t="n"/>
-      <c r="Q26" s="701" t="n"/>
-      <c r="R26" s="701" t="n"/>
-      <c r="S26" s="701" t="n"/>
-      <c r="T26" s="701" t="n"/>
-      <c r="U26" s="701" t="n"/>
-      <c r="V26" s="701" t="n"/>
-      <c r="W26" s="701" t="n"/>
-      <c r="X26" s="701" t="n"/>
-      <c r="Y26" s="701" t="n"/>
-      <c r="Z26" s="701" t="n"/>
-      <c r="AA26" s="701" t="n"/>
-      <c r="AB26" s="701" t="n"/>
-      <c r="AC26" s="701" t="n"/>
-      <c r="AD26" s="701" t="n"/>
-      <c r="AE26" s="701" t="n"/>
-      <c r="AF26" s="701" t="n"/>
-      <c r="AG26" s="701" t="n"/>
-      <c r="AH26" s="701" t="n"/>
-      <c r="AI26" s="701" t="n"/>
-      <c r="AJ26" s="701" t="n"/>
-      <c r="AK26" s="701" t="n"/>
-      <c r="AL26" s="701" t="n"/>
-      <c r="AM26" s="701" t="n"/>
-      <c r="AN26" s="702" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="717" t="n"/>
-      <c r="B27" s="708" t="n"/>
-      <c r="C27" s="708" t="n"/>
-      <c r="D27" s="708" t="n"/>
-      <c r="E27" s="708" t="n"/>
-      <c r="F27" s="708" t="n"/>
-      <c r="G27" s="708" t="n"/>
-      <c r="H27" s="708" t="n"/>
-      <c r="I27" s="708" t="n"/>
-      <c r="J27" s="708" t="n"/>
-      <c r="K27" s="708" t="n"/>
-      <c r="L27" s="708" t="n"/>
-      <c r="M27" s="708" t="n"/>
-      <c r="N27" s="708" t="n"/>
-      <c r="O27" s="708" t="n"/>
-      <c r="P27" s="708" t="n"/>
-      <c r="Q27" s="708" t="n"/>
-      <c r="R27" s="708" t="n"/>
-      <c r="S27" s="708" t="n"/>
-      <c r="T27" s="708" t="n"/>
-      <c r="U27" s="708" t="n"/>
-      <c r="V27" s="708" t="n"/>
-      <c r="W27" s="708" t="n"/>
-      <c r="X27" s="708" t="n"/>
-      <c r="Y27" s="708" t="n"/>
-      <c r="Z27" s="708" t="n"/>
-      <c r="AA27" s="708" t="n"/>
-      <c r="AB27" s="708" t="n"/>
-      <c r="AC27" s="708" t="n"/>
-      <c r="AD27" s="708" t="n"/>
-      <c r="AE27" s="708" t="n"/>
-      <c r="AF27" s="708" t="n"/>
-      <c r="AG27" s="708" t="n"/>
-      <c r="AH27" s="708" t="n"/>
-      <c r="AI27" s="708" t="n"/>
-      <c r="AJ27" s="708" t="n"/>
-      <c r="AK27" s="708" t="n"/>
-      <c r="AL27" s="708" t="n"/>
-      <c r="AM27" s="708" t="n"/>
-      <c r="AN27" s="709" t="n"/>
-    </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="370" t="inlineStr">
+      <c r="B26" s="383" t="n"/>
+      <c r="C26" s="383" t="n"/>
+      <c r="D26" s="383" t="n"/>
+      <c r="E26" s="383" t="n"/>
+      <c r="F26" s="384" t="n"/>
+      <c r="G26" s="383" t="n"/>
+      <c r="H26" s="383" t="n"/>
+      <c r="I26" s="385" t="n"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="393" t="inlineStr">
         <is>
           <t>NOTICE  —  One line per material, capacity, quality or customer-risk condition.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B28" s="371" t="n"/>
-      <c r="C28" s="371" t="n"/>
-      <c r="D28" s="371" t="n"/>
-      <c r="E28" s="371" t="n"/>
-      <c r="F28" s="371" t="n"/>
-      <c r="G28" s="371" t="n"/>
-      <c r="H28" s="371" t="n"/>
-      <c r="I28" s="371" t="n"/>
-      <c r="J28" s="371" t="n"/>
-      <c r="K28" s="371" t="n"/>
-      <c r="L28" s="371" t="n"/>
-      <c r="M28" s="371" t="n"/>
-      <c r="N28" s="371" t="n"/>
-      <c r="O28" s="371" t="n"/>
-      <c r="P28" s="371" t="n"/>
-      <c r="Q28" s="371" t="n"/>
-      <c r="R28" s="371" t="n"/>
-      <c r="S28" s="371" t="n"/>
-      <c r="T28" s="371" t="n"/>
-      <c r="U28" s="371" t="n"/>
-      <c r="V28" s="371" t="n"/>
-      <c r="W28" s="371" t="n"/>
-      <c r="X28" s="371" t="n"/>
-      <c r="Y28" s="371" t="n"/>
-      <c r="Z28" s="371" t="n"/>
-      <c r="AA28" s="371" t="n"/>
-      <c r="AB28" s="371" t="n"/>
-      <c r="AC28" s="371" t="n"/>
-      <c r="AD28" s="371" t="n"/>
-      <c r="AE28" s="371" t="n"/>
-      <c r="AF28" s="371" t="n"/>
-      <c r="AG28" s="371" t="n"/>
-      <c r="AH28" s="371" t="n"/>
-      <c r="AI28" s="371" t="n"/>
-      <c r="AJ28" s="371" t="n"/>
-      <c r="AK28" s="371" t="n"/>
-      <c r="AL28" s="371" t="n"/>
-      <c r="AM28" s="371" t="n"/>
-      <c r="AN28" s="372" t="n"/>
+      <c r="B28" s="289" t="n"/>
+      <c r="C28" s="289" t="n"/>
+      <c r="D28" s="289" t="n"/>
+      <c r="E28" s="289" t="n"/>
+      <c r="F28" s="289" t="n"/>
+      <c r="G28" s="289" t="n"/>
+      <c r="H28" s="289" t="n"/>
+      <c r="I28" s="290" t="n"/>
     </row>
     <row r="29" hidden="1" outlineLevel="1"/>
     <row r="30" hidden="1" outlineLevel="1"/>
@@ -13051,7 +9125,7 @@
     <row r="199" hidden="1" outlineLevel="1"/>
     <row r="200" hidden="1" outlineLevel="1"/>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="30">
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="F10:G10"/>
@@ -13072,11 +9146,13 @@
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="C1:G3"/>
     <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="H12:I12"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A6:I6"/>
     <mergeCell ref="H8:I8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C10:E10"/>
@@ -13094,7 +9170,7 @@
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;"Segoe UI"&amp;7 FRM-209  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
+    <oddFooter>&amp;CFRM-209  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -13105,4 +9181,364 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col hidden="1" width="13" customWidth="1" min="8" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="322" t="inlineStr">
+        <is>
+          <t>REF LINKS</t>
+        </is>
+      </c>
+      <c r="B1" s="330" t="n"/>
+      <c r="C1" s="330" t="n"/>
+      <c r="D1" s="330" t="n"/>
+      <c r="E1" s="330" t="n"/>
+      <c r="F1" s="330" t="n"/>
+      <c r="G1" s="331" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="323" t="inlineStr">
+        <is>
+          <t>Reference release package, planner snapshot and dossier evidence only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="324" t="inlineStr">
+        <is>
+          <t>Ref Type</t>
+        </is>
+      </c>
+      <c r="B3" s="324" t="inlineStr">
+        <is>
+          <t>Document / Record</t>
+        </is>
+      </c>
+      <c r="C3" s="324" t="inlineStr">
+        <is>
+          <t>System of Record</t>
+        </is>
+      </c>
+      <c r="D3" s="324" t="inlineStr">
+        <is>
+          <t>Unique Ref</t>
+        </is>
+      </c>
+      <c r="E3" s="324" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F3" s="324" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G3" s="324" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="308" t="n"/>
+      <c r="B4" s="308" t="n"/>
+      <c r="C4" s="308" t="n"/>
+      <c r="D4" s="308" t="n"/>
+      <c r="E4" s="308" t="n"/>
+      <c r="F4" s="308" t="n"/>
+      <c r="G4" s="308" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="327" t="n"/>
+      <c r="B5" s="327" t="n"/>
+      <c r="C5" s="327" t="n"/>
+      <c r="D5" s="327" t="n"/>
+      <c r="E5" s="327" t="n"/>
+      <c r="F5" s="327" t="n"/>
+      <c r="G5" s="327" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="308" t="n"/>
+      <c r="B6" s="308" t="n"/>
+      <c r="C6" s="308" t="n"/>
+      <c r="D6" s="308" t="n"/>
+      <c r="E6" s="308" t="n"/>
+      <c r="F6" s="308" t="n"/>
+      <c r="G6" s="308" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="327" t="n"/>
+      <c r="B7" s="327" t="n"/>
+      <c r="C7" s="327" t="n"/>
+      <c r="D7" s="327" t="n"/>
+      <c r="E7" s="327" t="n"/>
+      <c r="F7" s="327" t="n"/>
+      <c r="G7" s="327" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="308" t="n"/>
+      <c r="B8" s="308" t="n"/>
+      <c r="C8" s="308" t="n"/>
+      <c r="D8" s="308" t="n"/>
+      <c r="E8" s="308" t="n"/>
+      <c r="F8" s="308" t="n"/>
+      <c r="G8" s="308" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="327" t="n"/>
+      <c r="B9" s="327" t="n"/>
+      <c r="C9" s="327" t="n"/>
+      <c r="D9" s="327" t="n"/>
+      <c r="E9" s="327" t="n"/>
+      <c r="F9" s="327" t="n"/>
+      <c r="G9" s="327" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="308" t="n"/>
+      <c r="B10" s="308" t="n"/>
+      <c r="C10" s="308" t="n"/>
+      <c r="D10" s="308" t="n"/>
+      <c r="E10" s="308" t="n"/>
+      <c r="F10" s="308" t="n"/>
+      <c r="G10" s="308" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="327" t="n"/>
+      <c r="B11" s="327" t="n"/>
+      <c r="C11" s="327" t="n"/>
+      <c r="D11" s="327" t="n"/>
+      <c r="E11" s="327" t="n"/>
+      <c r="F11" s="327" t="n"/>
+      <c r="G11" s="327" t="n"/>
+    </row>
+    <row r="12" hidden="1"/>
+    <row r="13" hidden="1"/>
+    <row r="14" hidden="1"/>
+    <row r="15" hidden="1"/>
+    <row r="16" hidden="1"/>
+    <row r="17" hidden="1"/>
+    <row r="18" hidden="1"/>
+    <row r="19" hidden="1"/>
+    <row r="20" hidden="1"/>
+    <row r="21" hidden="1"/>
+    <row r="22" hidden="1"/>
+    <row r="23" hidden="1"/>
+    <row r="24" hidden="1"/>
+    <row r="25" hidden="1"/>
+    <row r="26" hidden="1"/>
+    <row r="27" hidden="1"/>
+    <row r="28" hidden="1"/>
+    <row r="29" hidden="1"/>
+    <row r="30" hidden="1"/>
+    <row r="31" hidden="1"/>
+    <row r="32" hidden="1"/>
+    <row r="33" hidden="1"/>
+    <row r="34" hidden="1"/>
+    <row r="35" hidden="1"/>
+    <row r="36" hidden="1"/>
+    <row r="37" hidden="1"/>
+    <row r="38" hidden="1"/>
+    <row r="39" hidden="1"/>
+    <row r="40" hidden="1"/>
+    <row r="41" hidden="1"/>
+    <row r="42" hidden="1"/>
+    <row r="43" hidden="1"/>
+    <row r="44" hidden="1"/>
+    <row r="45" hidden="1"/>
+    <row r="46" hidden="1"/>
+    <row r="47" hidden="1"/>
+    <row r="48" hidden="1"/>
+    <row r="49" hidden="1"/>
+    <row r="50" hidden="1"/>
+    <row r="51" hidden="1"/>
+    <row r="52" hidden="1"/>
+    <row r="53" hidden="1"/>
+    <row r="54" hidden="1"/>
+    <row r="55" hidden="1"/>
+    <row r="56" hidden="1"/>
+    <row r="57" hidden="1"/>
+    <row r="58" hidden="1"/>
+    <row r="59" hidden="1"/>
+    <row r="60" hidden="1"/>
+    <row r="61" hidden="1"/>
+    <row r="62" hidden="1"/>
+    <row r="63" hidden="1"/>
+    <row r="64" hidden="1"/>
+    <row r="65" hidden="1"/>
+    <row r="66" hidden="1"/>
+    <row r="67" hidden="1"/>
+    <row r="68" hidden="1"/>
+    <row r="69" hidden="1"/>
+    <row r="70" hidden="1"/>
+    <row r="71" hidden="1"/>
+    <row r="72" hidden="1"/>
+    <row r="73" hidden="1"/>
+    <row r="74" hidden="1"/>
+    <row r="75" hidden="1"/>
+    <row r="76" hidden="1"/>
+    <row r="77" hidden="1"/>
+    <row r="78" hidden="1"/>
+    <row r="79" hidden="1"/>
+    <row r="80" hidden="1"/>
+    <row r="81" hidden="1"/>
+    <row r="82" hidden="1"/>
+    <row r="83" hidden="1"/>
+    <row r="84" hidden="1"/>
+    <row r="85" hidden="1"/>
+    <row r="86" hidden="1"/>
+    <row r="87" hidden="1"/>
+    <row r="88" hidden="1"/>
+    <row r="89" hidden="1"/>
+    <row r="90" hidden="1"/>
+    <row r="91" hidden="1"/>
+    <row r="92" hidden="1"/>
+    <row r="93" hidden="1"/>
+    <row r="94" hidden="1"/>
+    <row r="95" hidden="1"/>
+    <row r="96" hidden="1"/>
+    <row r="97" hidden="1"/>
+    <row r="98" hidden="1"/>
+    <row r="99" hidden="1"/>
+    <row r="100" hidden="1"/>
+    <row r="101" hidden="1"/>
+    <row r="102" hidden="1"/>
+    <row r="103" hidden="1"/>
+    <row r="104" hidden="1"/>
+    <row r="105" hidden="1"/>
+    <row r="106" hidden="1"/>
+    <row r="107" hidden="1"/>
+    <row r="108" hidden="1"/>
+    <row r="109" hidden="1"/>
+    <row r="110" hidden="1"/>
+    <row r="111" hidden="1"/>
+    <row r="112" hidden="1"/>
+    <row r="113" hidden="1"/>
+    <row r="114" hidden="1"/>
+    <row r="115" hidden="1"/>
+    <row r="116" hidden="1"/>
+    <row r="117" hidden="1"/>
+    <row r="118" hidden="1"/>
+    <row r="119" hidden="1"/>
+    <row r="120" hidden="1"/>
+    <row r="121" hidden="1"/>
+    <row r="122" hidden="1"/>
+    <row r="123" hidden="1"/>
+    <row r="124" hidden="1"/>
+    <row r="125" hidden="1"/>
+    <row r="126" hidden="1"/>
+    <row r="127" hidden="1"/>
+    <row r="128" hidden="1"/>
+    <row r="129" hidden="1"/>
+    <row r="130" hidden="1"/>
+    <row r="131" hidden="1"/>
+    <row r="132" hidden="1"/>
+    <row r="133" hidden="1"/>
+    <row r="134" hidden="1"/>
+    <row r="135" hidden="1"/>
+    <row r="136" hidden="1"/>
+    <row r="137" hidden="1"/>
+    <row r="138" hidden="1"/>
+    <row r="139" hidden="1"/>
+    <row r="140" hidden="1"/>
+    <row r="141" hidden="1"/>
+    <row r="142" hidden="1"/>
+    <row r="143" hidden="1"/>
+    <row r="144" hidden="1"/>
+    <row r="145" hidden="1"/>
+    <row r="146" hidden="1"/>
+    <row r="147" hidden="1"/>
+    <row r="148" hidden="1"/>
+    <row r="149" hidden="1"/>
+    <row r="150" hidden="1"/>
+    <row r="151" hidden="1"/>
+    <row r="152" hidden="1"/>
+    <row r="153" hidden="1"/>
+    <row r="154" hidden="1"/>
+    <row r="155" hidden="1"/>
+    <row r="156" hidden="1"/>
+    <row r="157" hidden="1"/>
+    <row r="158" hidden="1"/>
+    <row r="159" hidden="1"/>
+    <row r="160" hidden="1"/>
+    <row r="161" hidden="1"/>
+    <row r="162" hidden="1"/>
+    <row r="163" hidden="1"/>
+    <row r="164" hidden="1"/>
+    <row r="165" hidden="1"/>
+    <row r="166" hidden="1"/>
+    <row r="167" hidden="1"/>
+    <row r="168" hidden="1"/>
+    <row r="169" hidden="1"/>
+    <row r="170" hidden="1"/>
+    <row r="171" hidden="1"/>
+    <row r="172" hidden="1"/>
+    <row r="173" hidden="1"/>
+    <row r="174" hidden="1"/>
+    <row r="175" hidden="1"/>
+    <row r="176" hidden="1"/>
+    <row r="177" hidden="1"/>
+    <row r="178" hidden="1"/>
+    <row r="179" hidden="1"/>
+    <row r="180" hidden="1"/>
+    <row r="181" hidden="1"/>
+    <row r="182" hidden="1"/>
+    <row r="183" hidden="1"/>
+    <row r="184" hidden="1"/>
+    <row r="185" hidden="1"/>
+    <row r="186" hidden="1"/>
+    <row r="187" hidden="1"/>
+    <row r="188" hidden="1"/>
+    <row r="189" hidden="1"/>
+    <row r="190" hidden="1"/>
+    <row r="191" hidden="1"/>
+    <row r="192" hidden="1"/>
+    <row r="193" hidden="1"/>
+    <row r="194" hidden="1"/>
+    <row r="195" hidden="1"/>
+    <row r="196" hidden="1"/>
+    <row r="197" hidden="1"/>
+    <row r="198" hidden="1"/>
+    <row r="199" hidden="1"/>
+    <row r="200" hidden="1"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="E4:E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use controlled value from REF_OWNER_PERSON_MASTER." prompt="Select from REF_OWNER_PERSON_MASTER." type="list">
+      <formula1>=REF_OWNER_PERSON_MASTER</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use controlled value from VAL_STATUS_CORE." prompt="Select from VAL_STATUS_CORE." type="list">
+      <formula1>=VAL_STATUS_CORE</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
@@ -5017,6 +5017,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -8937,6 +8940,7 @@
       <c r="H26" s="383" t="n"/>
       <c r="I26" s="385" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="393" t="inlineStr">
         <is>

--- a/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
@@ -4,10 +4,10 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM-209_GATE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="veryHidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RISKS_ACTIONS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_RESULT_CORE">'_LISTS'!$A$2:$A$5</definedName>
@@ -8940,7 +8940,6 @@
       <c r="H26" s="383" t="n"/>
       <c r="I26" s="385" t="n"/>
     </row>
-    <row r="27"/>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="393" t="inlineStr">
         <is>

--- a/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
@@ -5421,7 +5421,7 @@
       <c r="AH4" s="278" t="n"/>
       <c r="AI4" s="279" t="inlineStr">
         <is>
-          <t>Planning / QA / Engineering</t>
+          <t>Planning / QA</t>
         </is>
       </c>
       <c r="AJ4" s="277" t="n"/>

--- a/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
@@ -4,10 +4,11 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM-209_GATE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="veryHidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RISKS_ACTIONS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="5" state="veryHidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REV_HISTORY" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_RESULT_CORE">'_LISTS'!$A$2:$A$5</definedName>
@@ -4835,6 +4836,41 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -4962,39 +4998,6 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -5239,7 +5242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN47"/>
+  <dimension ref="A1:AW47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.329999923706055" customWidth="1" min="1" max="1"/>
@@ -5352,7 +5355,7 @@
       <c r="AH2" s="278" t="n"/>
       <c r="AI2" s="279" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="AJ2" s="277" t="n"/>
@@ -5395,7 +5398,7 @@
       <c r="AH3" s="278" t="n"/>
       <c r="AI3" s="279" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AJ3" s="277" t="n"/>
@@ -5421,7 +5424,7 @@
       <c r="AH4" s="278" t="n"/>
       <c r="AI4" s="279" t="inlineStr">
         <is>
-          <t>Planning / QA</t>
+          <t>Planning / QA / Engineering</t>
         </is>
       </c>
       <c r="AJ4" s="277" t="n"/>
@@ -5736,7 +5739,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="298" t="inlineStr">
         <is>
-          <t>Evidence Folder</t>
+          <t>Linked FRM-207 / FRM-131</t>
         </is>
       </c>
       <c r="B12" s="283" t="n"/>
@@ -5760,7 +5763,7 @@
       <c r="T12" s="285" t="n"/>
       <c r="U12" s="300" t="inlineStr">
         <is>
-          <t>Record Status</t>
+          <t>Ref: SOP-201</t>
         </is>
       </c>
       <c r="V12" s="283" t="n"/>
@@ -5769,7 +5772,11 @@
       <c r="Y12" s="283" t="n"/>
       <c r="Z12" s="283" t="n"/>
       <c r="AA12" s="285" t="n"/>
-      <c r="AB12" s="286" t="inlineStr"/>
+      <c r="AB12" s="286" t="inlineStr">
+        <is>
+          <t>Retain: 10 years per QMS schedule</t>
+        </is>
+      </c>
       <c r="AC12" s="283" t="n"/>
       <c r="AD12" s="283" t="n"/>
       <c r="AE12" s="283" t="n"/>
@@ -7659,6 +7666,28 @@
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="H16:T16"/>
   </mergeCells>
+  <conditionalFormatting sqref="AF22:AF31">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"FAIL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"HOLD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD35:AD39">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+      <formula>"FAIL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
+      <formula>"HOLD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
+      <formula>"PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="38">
     <dataValidation sqref="AF22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use controlled value from VAL_RESULT_CORE." prompt="Select from VAL_RESULT_CORE." type="list">
       <formula1>=VAL_RESULT_CORE</formula1>
@@ -9539,9 +9568,88 @@
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial release</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QMS Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cross-ref: FRM-207, FRM-131; Parent ref: SOP-201; CF: checklist Result; CF: action Status</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QMS Upgrade</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-209_High_Risk_Job_Readiness_Review.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="89">
+  <fonts count="90">
     <font>
       <name val="Arial"/>
       <family val="2"/>
@@ -519,6 +519,12 @@
     </font>
     <font>
       <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="004C1D95"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
       <color rgb="00CBD5E1"/>
       <sz val="8"/>
     </font>
@@ -528,7 +534,7 @@
       <sz val="6"/>
     </font>
   </fonts>
-  <fills count="56">
+  <fills count="57">
     <fill>
       <patternFill/>
     </fill>
@@ -814,6 +820,12 @@
         <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E8FF"/>
+        <bgColor rgb="00F3E8FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="252">
     <border>
@@ -3644,7 +3656,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="518">
+  <cellXfs count="519">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -4862,6 +4874,9 @@
     <xf numFmtId="0" fontId="86" fillId="55" borderId="238" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="87" fillId="56" borderId="238" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="49" borderId="238" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="47" borderId="238" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="79" fillId="49" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4878,7 +4893,7 @@
     <xf numFmtId="0" fontId="79" fillId="49" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="47" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="88" fillId="47" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="214" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4886,7 +4901,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="235" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="88" fillId="48" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="89" fillId="48" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4998,6 +5013,98 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>Số công việc
+Job được đánh giá HIGH hoặc CRITICAL risk trong FRM-207.</t>
+      </text>
+    </comment>
+    <comment ref="U9" authorId="0" shapeId="0">
+      <text>
+        <t>Mã chi tiết / Phiên bản
+Part cần xem xét readiness.</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>Ngày xem xét
+Ngày thực hiện readiness review.</t>
+      </text>
+    </comment>
+    <comment ref="U10" authorId="0" shapeId="0">
+      <text>
+        <t>Người chủ trì
+Engineering Lead hoặc QA Manager chủ trì.</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>Đánh giá sẵn sàng
+Review cấp cao cho job rủi ro cao.
+Cần GM approval trước khi release.</t>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0" shapeId="0">
+      <text>
+        <t>Năng lực máy
+Xác nhận máy đạt Cpk cho tất cả critical features.
+Nếu chưa có data → yêu cầu trial run trước.</t>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0" shapeId="0">
+      <text>
+        <t>Chiến lược dao cụ
+Đã xác nhận tuổi thọ dao, có dao backup sẵn.</t>
+      </text>
+    </comment>
+    <comment ref="F16" authorId="0" shapeId="0">
+      <text>
+        <t>Vật liệu
+Material cert khớp spec, đã nhận và IQC passed.</t>
+      </text>
+    </comment>
+    <comment ref="F17" authorId="0" shapeId="0">
+      <text>
+        <t>Kế hoạch kiểm tra
+CMM program validated, MSA/GRR current.
+Gages calibrated và đủ capability.</t>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0" shapeId="0">
+      <text>
+        <t>Gia công ngoài
+Nhà cung cấp qualified, capacity confirmed.
+NA nếu không có outsource.</t>
+      </text>
+    </comment>
+    <comment ref="F19" authorId="0" shapeId="0">
+      <text>
+        <t>Kế hoạch dự phòng
+PFMEA đã review, mitigation cho từng failure mode.</t>
+      </text>
+    </comment>
+    <comment ref="F20" authorId="0" shapeId="0">
+      <text>
+        <t>Năng lực operator
+Operator phải có skill level ≥3 cho loại part này.</t>
+      </text>
+    </comment>
+    <comment ref="F21" authorId="0" shapeId="0">
+      <text>
+        <t>Phê duyệt quản lý
+GM ký chấp nhận rủi ro và cho phép tiến hành.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5907,8 +6014,9 @@
       <c r="AN13" s="479" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="264">
-      <c r="A14" s="490" t="n">
-        <v>1</v>
+      <c r="A14" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B14" s="491" t="n"/>
       <c r="C14" s="492" t="inlineStr">
@@ -5940,7 +6048,7 @@
       <c r="U14" s="491" t="n"/>
       <c r="V14" s="495" t="inlineStr">
         <is>
-          <t>Process capability data available.</t>
+          <t>Process capability data or equivalent evidence.</t>
         </is>
       </c>
       <c r="W14" s="493" t="n"/>
@@ -5963,8 +6071,9 @@
       <c r="AN14" s="498" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="264">
-      <c r="A15" s="490" t="n">
-        <v>2</v>
+      <c r="A15" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B15" s="491" t="n"/>
       <c r="C15" s="499" t="inlineStr">
@@ -5996,7 +6105,7 @@
       <c r="U15" s="491" t="n"/>
       <c r="V15" s="495" t="inlineStr">
         <is>
-          <t>Tool list reviewed and approved.</t>
+          <t>Tool list reviewed, backup plan documented.</t>
         </is>
       </c>
       <c r="W15" s="493" t="n"/>
@@ -6019,8 +6128,9 @@
       <c r="AN15" s="498" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="264">
-      <c r="A16" s="490" t="n">
-        <v>3</v>
+      <c r="A16" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B16" s="491" t="n"/>
       <c r="C16" s="499" t="inlineStr">
@@ -6052,7 +6162,7 @@
       <c r="U16" s="491" t="n"/>
       <c r="V16" s="495" t="inlineStr">
         <is>
-          <t>Material cert matches spec.</t>
+          <t>Material cert matches spec, on hand.</t>
         </is>
       </c>
       <c r="W16" s="493" t="n"/>
@@ -6075,8 +6185,9 @@
       <c r="AN16" s="498" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="264">
-      <c r="A17" s="490" t="n">
-        <v>4</v>
+      <c r="A17" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B17" s="491" t="n"/>
       <c r="C17" s="501" t="inlineStr">
@@ -6131,8 +6242,9 @@
       <c r="AN17" s="498" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="264">
-      <c r="A18" s="490" t="n">
-        <v>5</v>
+      <c r="A18" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B18" s="491" t="n"/>
       <c r="C18" s="492" t="inlineStr">
@@ -6144,7 +6256,7 @@
       <c r="E18" s="491" t="n"/>
       <c r="F18" s="494" t="inlineStr">
         <is>
-          <t>Outsource processes confirmed (lead time, capability).</t>
+          <t>Outsource processes confirmed.</t>
         </is>
       </c>
       <c r="G18" s="493" t="n"/>
@@ -6164,7 +6276,7 @@
       <c r="U18" s="491" t="n"/>
       <c r="V18" s="495" t="inlineStr">
         <is>
-          <t>Supplier qualified and available.</t>
+          <t>Supplier qualified, capacity confirmed.</t>
         </is>
       </c>
       <c r="W18" s="493" t="n"/>
@@ -6187,8 +6299,9 @@
       <c r="AN18" s="498" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="264">
-      <c r="A19" s="490" t="n">
-        <v>6</v>
+      <c r="A19" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B19" s="491" t="n"/>
       <c r="C19" s="502" t="inlineStr">
@@ -6220,7 +6333,7 @@
       <c r="U19" s="491" t="n"/>
       <c r="V19" s="495" t="inlineStr">
         <is>
-          <t>PFMEA or risk sheet reviewed.</t>
+          <t>PFMEA or risk sheet reviewed, mitigations in place.</t>
         </is>
       </c>
       <c r="W19" s="493" t="n"/>
@@ -6243,13 +6356,14 @@
       <c r="AN19" s="498" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="264">
-      <c r="A20" s="490" t="n">
-        <v>7</v>
+      <c r="A20" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B20" s="491" t="n"/>
-      <c r="C20" s="501" t="inlineStr">
-        <is>
-          <t>QUA</t>
+      <c r="C20" s="502" t="inlineStr">
+        <is>
+          <t>HR</t>
         </is>
       </c>
       <c r="D20" s="493" t="n"/>
@@ -6276,7 +6390,7 @@
       <c r="U20" s="491" t="n"/>
       <c r="V20" s="495" t="inlineStr">
         <is>
-          <t>Training record current.</t>
+          <t>Training record current for this skill level.</t>
         </is>
       </c>
       <c r="W20" s="493" t="n"/>
@@ -6299,13 +6413,14 @@
       <c r="AN20" s="498" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="264">
-      <c r="A21" s="490" t="n">
-        <v>8</v>
+      <c r="A21" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B21" s="491" t="n"/>
-      <c r="C21" s="502" t="inlineStr">
-        <is>
-          <t>OPS</t>
+      <c r="C21" s="503" t="inlineStr">
+        <is>
+          <t>MGT</t>
         </is>
       </c>
       <c r="D21" s="493" t="n"/>
@@ -6332,7 +6447,7 @@
       <c r="U21" s="491" t="n"/>
       <c r="V21" s="495" t="inlineStr">
         <is>
-          <t>Risk accepted at appropriate level.</t>
+          <t>Risk accepted and signed off at GM level.</t>
         </is>
       </c>
       <c r="W21" s="493" t="n"/>
@@ -6355,14 +6470,15 @@
       <c r="AN21" s="498" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="264">
-      <c r="A22" s="490" t="n">
-        <v>9</v>
+      <c r="A22" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B22" s="491" t="n"/>
-      <c r="C22" s="503" t="n"/>
+      <c r="C22" s="504" t="n"/>
       <c r="D22" s="493" t="n"/>
       <c r="E22" s="491" t="n"/>
-      <c r="F22" s="504" t="n"/>
+      <c r="F22" s="505" t="n"/>
       <c r="G22" s="493" t="n"/>
       <c r="H22" s="493" t="n"/>
       <c r="I22" s="493" t="n"/>
@@ -6378,7 +6494,7 @@
       <c r="S22" s="493" t="n"/>
       <c r="T22" s="493" t="n"/>
       <c r="U22" s="491" t="n"/>
-      <c r="V22" s="503" t="n"/>
+      <c r="V22" s="504" t="n"/>
       <c r="W22" s="493" t="n"/>
       <c r="X22" s="493" t="n"/>
       <c r="Y22" s="493" t="n"/>
@@ -6399,14 +6515,15 @@
       <c r="AN22" s="498" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="264">
-      <c r="A23" s="505" t="n">
-        <v>10</v>
+      <c r="A23" s="506">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B23" s="482" t="n"/>
-      <c r="C23" s="506" t="n"/>
+      <c r="C23" s="507" t="n"/>
       <c r="D23" s="481" t="n"/>
       <c r="E23" s="482" t="n"/>
-      <c r="F23" s="507" t="n"/>
+      <c r="F23" s="508" t="n"/>
       <c r="G23" s="481" t="n"/>
       <c r="H23" s="481" t="n"/>
       <c r="I23" s="481" t="n"/>
@@ -6422,7 +6539,7 @@
       <c r="S23" s="481" t="n"/>
       <c r="T23" s="481" t="n"/>
       <c r="U23" s="482" t="n"/>
-      <c r="V23" s="506" t="n"/>
+      <c r="V23" s="507" t="n"/>
       <c r="W23" s="481" t="n"/>
       <c r="X23" s="481" t="n"/>
       <c r="Y23" s="481" t="n"/>
@@ -6432,11 +6549,11 @@
       <c r="AC23" s="481" t="n"/>
       <c r="AD23" s="481" t="n"/>
       <c r="AE23" s="482" t="n"/>
-      <c r="AF23" s="508" t="n"/>
+      <c r="AF23" s="509" t="n"/>
       <c r="AG23" s="481" t="n"/>
       <c r="AH23" s="481" t="n"/>
       <c r="AI23" s="482" t="n"/>
-      <c r="AJ23" s="509" t="n"/>
+      <c r="AJ23" s="510" t="n"/>
       <c r="AK23" s="481" t="n"/>
       <c r="AL23" s="481" t="n"/>
       <c r="AM23" s="481" t="n"/>
@@ -6531,7 +6648,7 @@
       <c r="AN25" s="472" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1" s="264">
-      <c r="A26" s="510" t="inlineStr">
+      <c r="A26" s="511" t="inlineStr">
         <is>
           <t>Review Lead</t>
         </is>
@@ -6555,7 +6672,7 @@
       <c r="R26" s="471" t="n"/>
       <c r="S26" s="471" t="n"/>
       <c r="T26" s="472" t="n"/>
-      <c r="U26" s="510" t="inlineStr">
+      <c r="U26" s="511" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
@@ -6581,63 +6698,63 @@
       <c r="AN26" s="472" t="n"/>
     </row>
     <row r="27" ht="26" customHeight="1" s="264">
-      <c r="A27" s="511" t="inlineStr">
+      <c r="A27" s="512" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="B27" s="512" t="n"/>
-      <c r="C27" s="512" t="n"/>
-      <c r="D27" s="512" t="n"/>
-      <c r="E27" s="512" t="n"/>
-      <c r="F27" s="512" t="n"/>
-      <c r="G27" s="512" t="n"/>
-      <c r="H27" s="512" t="n"/>
-      <c r="I27" s="512" t="n"/>
-      <c r="J27" s="512" t="n"/>
-      <c r="K27" s="512" t="n"/>
-      <c r="L27" s="512" t="n"/>
-      <c r="M27" s="512" t="n"/>
-      <c r="N27" s="512" t="n"/>
-      <c r="O27" s="512" t="n"/>
-      <c r="P27" s="512" t="n"/>
-      <c r="Q27" s="512" t="n"/>
-      <c r="R27" s="512" t="n"/>
-      <c r="S27" s="512" t="n"/>
-      <c r="T27" s="513" t="n"/>
-      <c r="U27" s="511" t="inlineStr">
+      <c r="B27" s="513" t="n"/>
+      <c r="C27" s="513" t="n"/>
+      <c r="D27" s="513" t="n"/>
+      <c r="E27" s="513" t="n"/>
+      <c r="F27" s="513" t="n"/>
+      <c r="G27" s="513" t="n"/>
+      <c r="H27" s="513" t="n"/>
+      <c r="I27" s="513" t="n"/>
+      <c r="J27" s="513" t="n"/>
+      <c r="K27" s="513" t="n"/>
+      <c r="L27" s="513" t="n"/>
+      <c r="M27" s="513" t="n"/>
+      <c r="N27" s="513" t="n"/>
+      <c r="O27" s="513" t="n"/>
+      <c r="P27" s="513" t="n"/>
+      <c r="Q27" s="513" t="n"/>
+      <c r="R27" s="513" t="n"/>
+      <c r="S27" s="513" t="n"/>
+      <c r="T27" s="514" t="n"/>
+      <c r="U27" s="512" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="V27" s="512" t="n"/>
-      <c r="W27" s="512" t="n"/>
-      <c r="X27" s="512" t="n"/>
-      <c r="Y27" s="512" t="n"/>
-      <c r="Z27" s="512" t="n"/>
-      <c r="AA27" s="512" t="n"/>
-      <c r="AB27" s="512" t="n"/>
-      <c r="AC27" s="512" t="n"/>
-      <c r="AD27" s="512" t="n"/>
-      <c r="AE27" s="512" t="n"/>
-      <c r="AF27" s="512" t="n"/>
-      <c r="AG27" s="512" t="n"/>
-      <c r="AH27" s="512" t="n"/>
-      <c r="AI27" s="512" t="n"/>
-      <c r="AJ27" s="512" t="n"/>
-      <c r="AK27" s="512" t="n"/>
-      <c r="AL27" s="512" t="n"/>
-      <c r="AM27" s="512" t="n"/>
-      <c r="AN27" s="513" t="n"/>
+      <c r="V27" s="513" t="n"/>
+      <c r="W27" s="513" t="n"/>
+      <c r="X27" s="513" t="n"/>
+      <c r="Y27" s="513" t="n"/>
+      <c r="Z27" s="513" t="n"/>
+      <c r="AA27" s="513" t="n"/>
+      <c r="AB27" s="513" t="n"/>
+      <c r="AC27" s="513" t="n"/>
+      <c r="AD27" s="513" t="n"/>
+      <c r="AE27" s="513" t="n"/>
+      <c r="AF27" s="513" t="n"/>
+      <c r="AG27" s="513" t="n"/>
+      <c r="AH27" s="513" t="n"/>
+      <c r="AI27" s="513" t="n"/>
+      <c r="AJ27" s="513" t="n"/>
+      <c r="AK27" s="513" t="n"/>
+      <c r="AL27" s="513" t="n"/>
+      <c r="AM27" s="513" t="n"/>
+      <c r="AN27" s="514" t="n"/>
     </row>
     <row r="28" ht="26" customHeight="1" s="264">
-      <c r="A28" s="514" t="n"/>
-      <c r="T28" s="515" t="n"/>
-      <c r="U28" s="514" t="n"/>
-      <c r="AN28" s="515" t="n"/>
+      <c r="A28" s="515" t="n"/>
+      <c r="T28" s="516" t="n"/>
+      <c r="U28" s="515" t="n"/>
+      <c r="AN28" s="516" t="n"/>
     </row>
     <row r="29" ht="26" customHeight="1" s="264">
-      <c r="A29" s="516" t="n"/>
+      <c r="A29" s="517" t="n"/>
       <c r="B29" s="481" t="n"/>
       <c r="C29" s="481" t="n"/>
       <c r="D29" s="481" t="n"/>
@@ -6657,7 +6774,7 @@
       <c r="R29" s="481" t="n"/>
       <c r="S29" s="481" t="n"/>
       <c r="T29" s="486" t="n"/>
-      <c r="U29" s="516" t="n"/>
+      <c r="U29" s="517" t="n"/>
       <c r="V29" s="481" t="n"/>
       <c r="W29" s="481" t="n"/>
       <c r="X29" s="481" t="n"/>
@@ -6721,9 +6838,9 @@
       <c r="AN30" s="26" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1" s="264">
-      <c r="A31" s="517" t="inlineStr">
-        <is>
-          <t>NOTICE — Required for HIGH/CRITICAL risk jobs. Ref: SOP-201. Retain: 10 years.</t>
+      <c r="A31" s="518" t="inlineStr">
+        <is>
+          <t>NOTICE — Required when FRM-207 identifies HIGH/CRITICAL risk. GM must approve before job release. Ref: SOP-201. Retain: 10 years.</t>
         </is>
       </c>
       <c r="B31" s="471" t="n"/>
@@ -6888,6 +7005,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
